--- a/data/WIIT.MI.xlsx
+++ b/data/WIIT.MI.xlsx
@@ -54491,6 +54491,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2354">
+      <c r="A2354" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B2354" t="n">
+        <v>60959</v>
+      </c>
+      <c r="C2354" t="n">
+        <v>29.2999992370605</v>
+      </c>
+      <c r="D2354" t="n">
+        <v>28.3999996185303</v>
+      </c>
+      <c r="E2354" t="n">
+        <v>28.8999996185303</v>
+      </c>
+      <c r="F2354" t="n">
+        <v>29.4500007629395</v>
+      </c>
+      <c r="G2354" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/WIIT.MI.xlsx
+++ b/data/WIIT.MI.xlsx
@@ -54499,7 +54499,7 @@
         <v>60959</v>
       </c>
       <c r="C2354" t="n">
-        <v>29.2999992370605</v>
+        <v>29.4500007629395</v>
       </c>
       <c r="D2354" t="n">
         <v>28.3999996185303</v>
@@ -54511,6 +54511,29 @@
         <v>29.4500007629395</v>
       </c>
       <c r="G2354" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2355">
+      <c r="A2355" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B2355" t="n">
+        <v>29514</v>
+      </c>
+      <c r="C2355" t="n">
+        <v>29.2999992370605</v>
+      </c>
+      <c r="D2355" t="n">
+        <v>28.6499996185303</v>
+      </c>
+      <c r="E2355" t="n">
+        <v>29.1000003814697</v>
+      </c>
+      <c r="F2355" t="n">
+        <v>29.0499992370605</v>
+      </c>
+      <c r="G2355" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/WIIT.MI.xlsx
+++ b/data/WIIT.MI.xlsx
@@ -54537,6 +54537,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2356">
+      <c r="A2356" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B2356" t="n">
+        <v>77749</v>
+      </c>
+      <c r="C2356" t="n">
+        <v>30.2999992370605</v>
+      </c>
+      <c r="D2356" t="n">
+        <v>28.9500007629395</v>
+      </c>
+      <c r="E2356" t="n">
+        <v>29.2999992370605</v>
+      </c>
+      <c r="F2356" t="n">
+        <v>30.2000007629395</v>
+      </c>
+      <c r="G2356" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/WIIT.MI.xlsx
+++ b/data/WIIT.MI.xlsx
@@ -54560,6 +54560,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2357">
+      <c r="A2357" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B2357" t="n">
+        <v>35668</v>
+      </c>
+      <c r="C2357" t="n">
+        <v>30.9500007629395</v>
+      </c>
+      <c r="D2357" t="n">
+        <v>30</v>
+      </c>
+      <c r="E2357" t="n">
+        <v>30.6000003814697</v>
+      </c>
+      <c r="F2357" t="n">
+        <v>30.1000003814697</v>
+      </c>
+      <c r="G2357" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/WIIT.MI.xlsx
+++ b/data/WIIT.MI.xlsx
@@ -54401,22 +54401,22 @@
     </row>
     <row r="2350">
       <c r="A2350" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B2350" t="n">
-        <v>21561</v>
+        <v>24495</v>
       </c>
       <c r="C2350" t="n">
-        <v>28.8500003814697</v>
+        <v>29.2999992370605</v>
       </c>
       <c r="D2350" t="n">
-        <v>28.3500003814697</v>
+        <v>28.6499996185303</v>
       </c>
       <c r="E2350" t="n">
-        <v>28.5499992370605</v>
+        <v>29.25</v>
       </c>
       <c r="F2350" t="n">
-        <v>28.75</v>
+        <v>28.7000007629395</v>
       </c>
       <c r="G2350" t="s">
         <v>7</v>
@@ -54424,22 +54424,22 @@
     </row>
     <row r="2351">
       <c r="A2351" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B2351" t="n">
-        <v>29265</v>
+        <v>21561</v>
       </c>
       <c r="C2351" t="n">
-        <v>29.1000003814697</v>
+        <v>28.8500003814697</v>
       </c>
       <c r="D2351" t="n">
-        <v>28.2999992370605</v>
+        <v>28.3500003814697</v>
       </c>
       <c r="E2351" t="n">
-        <v>29.1000003814697</v>
+        <v>28.5499992370605</v>
       </c>
       <c r="F2351" t="n">
-        <v>28.6000003814697</v>
+        <v>28.75</v>
       </c>
       <c r="G2351" t="s">
         <v>7</v>
@@ -54447,22 +54447,22 @@
     </row>
     <row r="2352">
       <c r="A2352" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B2352" t="n">
-        <v>48154</v>
+        <v>29265</v>
       </c>
       <c r="C2352" t="n">
-        <v>29.5499992370605</v>
+        <v>29.1000003814697</v>
       </c>
       <c r="D2352" t="n">
-        <v>28.4500007629395</v>
+        <v>28.2999992370605</v>
       </c>
       <c r="E2352" t="n">
-        <v>28.4500007629395</v>
+        <v>29.1000003814697</v>
       </c>
       <c r="F2352" t="n">
-        <v>29.3999996185303</v>
+        <v>28.6000003814697</v>
       </c>
       <c r="G2352" t="s">
         <v>7</v>
@@ -54470,22 +54470,22 @@
     </row>
     <row r="2353">
       <c r="A2353" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B2353" t="n">
-        <v>70225</v>
+        <v>48154</v>
       </c>
       <c r="C2353" t="n">
-        <v>29.5</v>
+        <v>29.5499992370605</v>
       </c>
       <c r="D2353" t="n">
-        <v>28.8500003814697</v>
+        <v>28.4500007629395</v>
       </c>
       <c r="E2353" t="n">
+        <v>28.4500007629395</v>
+      </c>
+      <c r="F2353" t="n">
         <v>29.3999996185303</v>
-      </c>
-      <c r="F2353" t="n">
-        <v>28.8999996185303</v>
       </c>
       <c r="G2353" t="s">
         <v>7</v>
@@ -54493,22 +54493,22 @@
     </row>
     <row r="2354">
       <c r="A2354" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B2354" t="n">
-        <v>60959</v>
+        <v>70225</v>
       </c>
       <c r="C2354" t="n">
-        <v>29.4500007629395</v>
+        <v>29.5</v>
       </c>
       <c r="D2354" t="n">
-        <v>28.3999996185303</v>
+        <v>28.8500003814697</v>
       </c>
       <c r="E2354" t="n">
+        <v>29.3999996185303</v>
+      </c>
+      <c r="F2354" t="n">
         <v>28.8999996185303</v>
-      </c>
-      <c r="F2354" t="n">
-        <v>29.4500007629395</v>
       </c>
       <c r="G2354" t="s">
         <v>7</v>
@@ -54516,22 +54516,22 @@
     </row>
     <row r="2355">
       <c r="A2355" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B2355" t="n">
-        <v>29514</v>
+        <v>60959</v>
       </c>
       <c r="C2355" t="n">
-        <v>29.2999992370605</v>
+        <v>29.4500007629395</v>
       </c>
       <c r="D2355" t="n">
-        <v>28.6499996185303</v>
+        <v>28.3999996185303</v>
       </c>
       <c r="E2355" t="n">
-        <v>29.1000003814697</v>
+        <v>28.8999996185303</v>
       </c>
       <c r="F2355" t="n">
-        <v>29.0499992370605</v>
+        <v>29.4500007629395</v>
       </c>
       <c r="G2355" t="s">
         <v>7</v>
@@ -54539,22 +54539,22 @@
     </row>
     <row r="2356">
       <c r="A2356" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B2356" t="n">
-        <v>77749</v>
+        <v>29514</v>
       </c>
       <c r="C2356" t="n">
-        <v>30.2999992370605</v>
+        <v>29.2999992370605</v>
       </c>
       <c r="D2356" t="n">
-        <v>28.9500007629395</v>
+        <v>28.6499996185303</v>
       </c>
       <c r="E2356" t="n">
-        <v>29.2999992370605</v>
+        <v>29.1000003814697</v>
       </c>
       <c r="F2356" t="n">
-        <v>30.2000007629395</v>
+        <v>29.0499992370605</v>
       </c>
       <c r="G2356" t="s">
         <v>7</v>
@@ -54562,24 +54562,47 @@
     </row>
     <row r="2357">
       <c r="A2357" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B2357" t="n">
-        <v>35668</v>
+        <v>77749</v>
       </c>
       <c r="C2357" t="n">
-        <v>30.9500007629395</v>
+        <v>30.2999992370605</v>
       </c>
       <c r="D2357" t="n">
-        <v>30</v>
+        <v>28.9500007629395</v>
       </c>
       <c r="E2357" t="n">
-        <v>30.6000003814697</v>
+        <v>29.2999992370605</v>
       </c>
       <c r="F2357" t="n">
-        <v>30.1000003814697</v>
+        <v>30.2000007629395</v>
       </c>
       <c r="G2357" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2358">
+      <c r="A2358" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B2358" t="n">
+        <v>24294</v>
+      </c>
+      <c r="C2358" t="n">
+        <v>30.25</v>
+      </c>
+      <c r="D2358" t="n">
+        <v>29.3500003814697</v>
+      </c>
+      <c r="E2358" t="n">
+        <v>29.7000007629395</v>
+      </c>
+      <c r="F2358" t="n">
+        <v>29.7000007629395</v>
+      </c>
+      <c r="G2358" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/WIIT.MI.xlsx
+++ b/data/WIIT.MI.xlsx
@@ -473,7 +473,7 @@
         <v>5.125</v>
       </c>
       <c r="G4" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>5.125</v>
       </c>
       <c r="G5" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>5.125</v>
       </c>
       <c r="G6" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>5.125</v>
       </c>
       <c r="G7" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>5.125</v>
       </c>
       <c r="G8" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>5.125</v>
       </c>
       <c r="G9" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>5.125</v>
       </c>
       <c r="G10" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>5.125</v>
       </c>
       <c r="G11" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>5.125</v>
       </c>
       <c r="G12" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>5.125</v>
       </c>
       <c r="G13" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>5.125</v>
       </c>
       <c r="G14" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>5.125</v>
       </c>
       <c r="G15" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>5.125</v>
       </c>
       <c r="G16" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>5.125</v>
       </c>
       <c r="G17" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>5.125</v>
       </c>
       <c r="G18" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>5.125</v>
       </c>
       <c r="G19" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>5.125</v>
       </c>
       <c r="G20" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>5.125</v>
       </c>
       <c r="G21" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>5.125</v>
       </c>
       <c r="G22" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>5.125</v>
       </c>
       <c r="G23" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>5.125</v>
       </c>
       <c r="G24" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>5.125</v>
       </c>
       <c r="G25" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>5.125</v>
       </c>
       <c r="G26" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>5.125</v>
       </c>
       <c r="G27" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>5.125</v>
       </c>
       <c r="G28" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>5.125</v>
       </c>
       <c r="G29" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>5.125</v>
       </c>
       <c r="G30" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>5.125</v>
       </c>
       <c r="G31" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>5.125</v>
       </c>
       <c r="G32" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>5.125</v>
       </c>
       <c r="G33" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>5.125</v>
       </c>
       <c r="G34" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>5.125</v>
       </c>
       <c r="G35" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>5.125</v>
       </c>
       <c r="G36" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>5.125</v>
       </c>
       <c r="G37" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>5.125</v>
       </c>
       <c r="G38" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>5.125</v>
       </c>
       <c r="G39" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>5.125</v>
       </c>
       <c r="G40" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>5.125</v>
       </c>
       <c r="G41" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>5.125</v>
       </c>
       <c r="G42" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>5.125</v>
       </c>
       <c r="G43" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>5.125</v>
       </c>
       <c r="G44" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>5.125</v>
       </c>
       <c r="G45" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>5.125</v>
       </c>
       <c r="G46" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>5.125</v>
       </c>
       <c r="G47" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>5.125</v>
       </c>
       <c r="G48" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>5.125</v>
       </c>
       <c r="G49" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>5.125</v>
       </c>
       <c r="G50" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>5.125</v>
       </c>
       <c r="G51" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>5.125</v>
       </c>
       <c r="G52" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>5.125</v>
       </c>
       <c r="G53" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>5.125</v>
       </c>
       <c r="G54" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>5.125</v>
       </c>
       <c r="G55" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>5.125</v>
       </c>
       <c r="G56" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>5.125</v>
       </c>
       <c r="G57" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>5.125</v>
       </c>
       <c r="G58" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>5.125</v>
       </c>
       <c r="G59" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>5.125</v>
       </c>
       <c r="G60" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>5.125</v>
       </c>
       <c r="G61" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>5.125</v>
       </c>
       <c r="G62" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>5.125</v>
       </c>
       <c r="G63" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>5.125</v>
       </c>
       <c r="G64" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>5.125</v>
       </c>
       <c r="G65" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>5.125</v>
       </c>
       <c r="G66" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>5.125</v>
       </c>
       <c r="G67" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>5.125</v>
       </c>
       <c r="G68" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>5.125</v>
       </c>
       <c r="G69" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>5.125</v>
       </c>
       <c r="G70" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5.125</v>
       </c>
       <c r="G71" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>5.125</v>
       </c>
       <c r="G72" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>5.125</v>
       </c>
       <c r="G73" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>5.125</v>
       </c>
       <c r="G74" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>5.125</v>
       </c>
       <c r="G75" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>5.125</v>
       </c>
       <c r="G76" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>5.125</v>
       </c>
       <c r="G77" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>5.125</v>
       </c>
       <c r="G78" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>5.125</v>
       </c>
       <c r="G79" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>5.125</v>
       </c>
       <c r="G80" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>5.125</v>
       </c>
       <c r="G81" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>5.125</v>
       </c>
       <c r="G82" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>5.125</v>
       </c>
       <c r="G83" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>5.125</v>
       </c>
       <c r="G84" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>5.125</v>
       </c>
       <c r="G85" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>5.125</v>
       </c>
       <c r="G86" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>5.125</v>
       </c>
       <c r="G87" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>5.125</v>
       </c>
       <c r="G88" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>5.125</v>
       </c>
       <c r="G89" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>5.125</v>
       </c>
       <c r="G90" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>5.125</v>
       </c>
       <c r="G91" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>5.125</v>
       </c>
       <c r="G92" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>5.125</v>
       </c>
       <c r="G93" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>5.125</v>
       </c>
       <c r="G94" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>5.125</v>
       </c>
       <c r="G95" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>5.125</v>
       </c>
       <c r="G96" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>5.125</v>
       </c>
       <c r="G97" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>5.125</v>
       </c>
       <c r="G98" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>5.125</v>
       </c>
       <c r="G99" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>5.125</v>
       </c>
       <c r="G100" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>5.125</v>
       </c>
       <c r="G101" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>5.125</v>
       </c>
       <c r="G102" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>5.125</v>
       </c>
       <c r="G103" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>5.125</v>
       </c>
       <c r="G104" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>5.125</v>
       </c>
       <c r="G105" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>5.125</v>
       </c>
       <c r="G106" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>5.125</v>
       </c>
       <c r="G107" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>5.125</v>
       </c>
       <c r="G108" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>5.125</v>
       </c>
       <c r="G109" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>5.125</v>
       </c>
       <c r="G110" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>5.125</v>
       </c>
       <c r="G111" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>5.125</v>
       </c>
       <c r="G112" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>5.125</v>
       </c>
       <c r="G113" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>5.125</v>
       </c>
       <c r="G114" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>5.125</v>
       </c>
       <c r="G115" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>5.125</v>
       </c>
       <c r="G116" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>5.125</v>
       </c>
       <c r="G117" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>5.125</v>
       </c>
       <c r="G118" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>5.125</v>
       </c>
       <c r="G119" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>5.125</v>
       </c>
       <c r="G120" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>5.125</v>
       </c>
       <c r="G121" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>5.125</v>
       </c>
       <c r="G122" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>5.125</v>
       </c>
       <c r="G123" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>5.125</v>
       </c>
       <c r="G124" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>5.125</v>
       </c>
       <c r="G125" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>5.125</v>
       </c>
       <c r="G126" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.125</v>
       </c>
       <c r="G127" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>5.125</v>
       </c>
       <c r="G128" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>5.125</v>
       </c>
       <c r="G129" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>5.125</v>
       </c>
       <c r="G130" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>5.125</v>
       </c>
       <c r="G131" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>5.125</v>
       </c>
       <c r="G132" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>5.125</v>
       </c>
       <c r="G133" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>5.125</v>
       </c>
       <c r="G134" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>5.125</v>
       </c>
       <c r="G135" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>5.125</v>
       </c>
       <c r="G136" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>5.125</v>
       </c>
       <c r="G137" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>5.125</v>
       </c>
       <c r="G138" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>5.125</v>
       </c>
       <c r="G139" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>5.125</v>
       </c>
       <c r="G140" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>5.125</v>
       </c>
       <c r="G141" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>5.125</v>
       </c>
       <c r="G142" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>5.125</v>
       </c>
       <c r="G143" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>5.125</v>
       </c>
       <c r="G144" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>5.125</v>
       </c>
       <c r="G145" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>5.125</v>
       </c>
       <c r="G146" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>5.125</v>
       </c>
       <c r="G147" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>5.125</v>
       </c>
       <c r="G148" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>5.125</v>
       </c>
       <c r="G149" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>5.125</v>
       </c>
       <c r="G150" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>5.125</v>
       </c>
       <c r="G151" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>5.125</v>
       </c>
       <c r="G152" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>5.125</v>
       </c>
       <c r="G153" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>5.125</v>
       </c>
       <c r="G154" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>5.125</v>
       </c>
       <c r="G155" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>5.125</v>
       </c>
       <c r="G156" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>5.125</v>
       </c>
       <c r="G157" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>5.125</v>
       </c>
       <c r="G158" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>5.125</v>
       </c>
       <c r="G159" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>5.125</v>
       </c>
       <c r="G160" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>5.125</v>
       </c>
       <c r="G161" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>5.125</v>
       </c>
       <c r="G162" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>5.125</v>
       </c>
       <c r="G163" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>5.125</v>
       </c>
       <c r="G164" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>5.125</v>
       </c>
       <c r="G165" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>5.125</v>
       </c>
       <c r="G166" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>5.125</v>
       </c>
       <c r="G167" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>5.125</v>
       </c>
       <c r="G168" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>5.125</v>
       </c>
       <c r="G169" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>5.125</v>
       </c>
       <c r="G170" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>5.125</v>
       </c>
       <c r="G171" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>5.125</v>
       </c>
       <c r="G172" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>5.125</v>
       </c>
       <c r="G173" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>5.125</v>
       </c>
       <c r="G174" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>5.125</v>
       </c>
       <c r="G175" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>5.125</v>
       </c>
       <c r="G176" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>5.125</v>
       </c>
       <c r="G177" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>5.125</v>
       </c>
       <c r="G178" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>5.125</v>
       </c>
       <c r="G179" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>5.125</v>
       </c>
       <c r="G180" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>5.125</v>
       </c>
       <c r="G181" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>5.125</v>
       </c>
       <c r="G182" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>5.125</v>
       </c>
       <c r="G183" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>5.125</v>
       </c>
       <c r="G184" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>5.125</v>
       </c>
       <c r="G185" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>5.125</v>
       </c>
       <c r="G186" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>5.125</v>
       </c>
       <c r="G187" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>5.125</v>
       </c>
       <c r="G188" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>5.125</v>
       </c>
       <c r="G189" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>5.125</v>
       </c>
       <c r="G190" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>5.125</v>
       </c>
       <c r="G191" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>5.125</v>
       </c>
       <c r="G192" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>5.125</v>
       </c>
       <c r="G193" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>5.125</v>
       </c>
       <c r="G194" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>5.125</v>
       </c>
       <c r="G195" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>5.125</v>
       </c>
       <c r="G196" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>5.125</v>
       </c>
       <c r="G197" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>5.125</v>
       </c>
       <c r="G198" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>5.125</v>
       </c>
       <c r="G199" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>5.125</v>
       </c>
       <c r="G200" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>5.125</v>
       </c>
       <c r="G201" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>5.125</v>
       </c>
       <c r="G202" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>5.125</v>
       </c>
       <c r="G203" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>5.125</v>
       </c>
       <c r="G204" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>5.125</v>
       </c>
       <c r="G205" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>5.125</v>
       </c>
       <c r="G206" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>5.125</v>
       </c>
       <c r="G207" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>5.125</v>
       </c>
       <c r="G208" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>5.125</v>
       </c>
       <c r="G209" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>5.125</v>
       </c>
       <c r="G210" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>5.125</v>
       </c>
       <c r="G211" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>5.125</v>
       </c>
       <c r="G212" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>5.125</v>
       </c>
       <c r="G213" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>5.125</v>
       </c>
       <c r="G214" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>5.125</v>
       </c>
       <c r="G215" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>5.125</v>
       </c>
       <c r="G216" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>5.125</v>
       </c>
       <c r="G217" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>5.125</v>
       </c>
       <c r="G218" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>5.125</v>
       </c>
       <c r="G219" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>5.125</v>
       </c>
       <c r="G220" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>5.125</v>
       </c>
       <c r="G221" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>5.125</v>
       </c>
       <c r="G222" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>5.125</v>
       </c>
       <c r="G223" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>5.125</v>
       </c>
       <c r="G224" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>5.125</v>
       </c>
       <c r="G225" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>5.125</v>
       </c>
       <c r="G226" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>5.125</v>
       </c>
       <c r="G227" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>5.125</v>
       </c>
       <c r="G228" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>5.125</v>
       </c>
       <c r="G229" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>5.125</v>
       </c>
       <c r="G230" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>5.125</v>
       </c>
       <c r="G231" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>5.125</v>
       </c>
       <c r="G232" t="n">
-        <v>4.51277875900269</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G274" t="n">
-        <v>4.51098775863647</v>
+        <v>4.51098823547363</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G275" t="n">
-        <v>4.41253423690796</v>
+        <v>4.4125337600708</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G276" t="n">
-        <v>4.52888965606689</v>
+        <v>4.52888870239258</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G277" t="n">
-        <v>4.49308776855469</v>
+        <v>4.49308729171753</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>5</v>
       </c>
       <c r="G279" t="n">
-        <v>4.47518730163574</v>
+        <v>4.47518634796143</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>5</v>
       </c>
       <c r="G280" t="n">
-        <v>4.47518730163574</v>
+        <v>4.47518634796143</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>5</v>
       </c>
       <c r="G281" t="n">
-        <v>4.47518730163574</v>
+        <v>4.47518634796143</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G282" t="n">
-        <v>4.49308776855469</v>
+        <v>4.49308729171753</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G283" t="n">
-        <v>4.43938493728638</v>
+        <v>4.43938541412354</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G284" t="n">
-        <v>4.49308776855469</v>
+        <v>4.49308729171753</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>5</v>
       </c>
       <c r="G285" t="n">
-        <v>4.47518730163574</v>
+        <v>4.47518634796143</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>5</v>
       </c>
       <c r="G290" t="n">
-        <v>4.47518730163574</v>
+        <v>4.47518634796143</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G291" t="n">
-        <v>4.54678964614868</v>
+        <v>4.54678916931152</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G292" t="n">
-        <v>4.54678964614868</v>
+        <v>4.54678916931152</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G293" t="n">
-        <v>4.54678964614868</v>
+        <v>4.54678916931152</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G295" t="n">
-        <v>4.54678964614868</v>
+        <v>4.54678916931152</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G296" t="n">
-        <v>4.51098775863647</v>
+        <v>4.51098823547363</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G297" t="n">
-        <v>4.52888965606689</v>
+        <v>4.52888870239258</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G298" t="n">
-        <v>4.51098775863647</v>
+        <v>4.51098823547363</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>4.51098775863647</v>
+        <v>4.51098823547363</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G300" t="n">
-        <v>4.49308776855469</v>
+        <v>4.49308729171753</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G301" t="n">
-        <v>4.49308776855469</v>
+        <v>4.49308729171753</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>4.49308776855469</v>
+        <v>4.49308729171753</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G303" t="n">
-        <v>4.43043422698975</v>
+        <v>4.4304347038269</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G304" t="n">
-        <v>4.43043422698975</v>
+        <v>4.4304347038269</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G305" t="n">
-        <v>4.38568305969238</v>
+        <v>4.38568353652954</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G306" t="n">
-        <v>4.34093046188354</v>
+        <v>4.34093141555786</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G307" t="n">
-        <v>4.30512952804565</v>
+        <v>4.30513000488281</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G308" t="n">
-        <v>4.29617977142334</v>
+        <v>4.29617929458618</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G311" t="n">
-        <v>4.27827787399292</v>
+        <v>4.27827882766724</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G312" t="n">
-        <v>4.27827787399292</v>
+        <v>4.27827882766724</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>4.45728635787964</v>
+        <v>4.45728588104248</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>4.43938493728638</v>
+        <v>4.43938541412354</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G315" t="n">
-        <v>4.3677830696106</v>
+        <v>4.36778211593628</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G317" t="n">
-        <v>4.3230299949646</v>
+        <v>4.32302951812744</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G318" t="n">
-        <v>4.3230299949646</v>
+        <v>4.32302951812744</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G319" t="n">
-        <v>4.35883188247681</v>
+        <v>4.35883140563965</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G321" t="n">
-        <v>4.23352670669556</v>
+        <v>4.2335262298584</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G322" t="n">
-        <v>4.3230299949646</v>
+        <v>4.32302951812744</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G323" t="n">
-        <v>4.34988117218018</v>
+        <v>4.34988164901733</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G328" t="n">
-        <v>3.90236306190491</v>
+        <v>3.90236258506775</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G329" t="n">
-        <v>3.99186754226685</v>
+        <v>3.99186658859253</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G331" t="n">
-        <v>4.08137035369873</v>
+        <v>4.08137083053589</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G332" t="n">
-        <v>4.13507270812988</v>
+        <v>4.13507175445557</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G336" t="n">
-        <v>3.99186754226685</v>
+        <v>3.99186658859253</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G340" t="n">
-        <v>3.90236306190491</v>
+        <v>3.90236258506775</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G341" t="n">
-        <v>3.86656188964844</v>
+        <v>3.86656141281128</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>3.76810717582703</v>
+        <v>3.76810765266418</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G343" t="n">
-        <v>3.84866046905518</v>
+        <v>3.84866070747375</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G344" t="n">
-        <v>3.78600788116455</v>
+        <v>3.78600835800171</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G345" t="n">
-        <v>3.7054545879364</v>
+        <v>3.70545434951782</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G346" t="n">
-        <v>3.66965246200562</v>
+        <v>3.66965317726135</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G347" t="n">
-        <v>3.60700011253357</v>
+        <v>3.60700082778931</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G350" t="n">
-        <v>3.5711989402771</v>
+        <v>3.57119941711426</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G351" t="n">
-        <v>3.53539776802063</v>
+        <v>3.53539752960205</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>4</v>
       </c>
       <c r="G352" t="n">
-        <v>3.58014893531799</v>
+        <v>3.58014917373657</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G355" t="n">
-        <v>3.44589352607727</v>
+        <v>3.44589376449585</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G357" t="n">
-        <v>3.39219117164612</v>
+        <v>3.39219164848328</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G358" t="n">
-        <v>3.31163787841797</v>
+        <v>3.31163811683655</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G359" t="n">
-        <v>3.31163787841797</v>
+        <v>3.31163811683655</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G360" t="n">
-        <v>3.31163787841797</v>
+        <v>3.31163811683655</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G361" t="n">
-        <v>3.34744000434875</v>
+        <v>3.34743976593018</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G363" t="n">
-        <v>3.31163787841797</v>
+        <v>3.31163811683655</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G364" t="n">
-        <v>3.20423364639282</v>
+        <v>3.20423340797424</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G367" t="n">
-        <v>3.09682893753052</v>
+        <v>3.09682941436768</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G369" t="n">
-        <v>3.20423364639282</v>
+        <v>3.20423340797424</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G374" t="n">
-        <v>2.85516881942749</v>
+        <v>2.85516929626465</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G375" t="n">
-        <v>2.82831788063049</v>
+        <v>2.82831811904907</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G377" t="n">
-        <v>2.95362329483032</v>
+        <v>2.95362305641174</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>3.25</v>
       </c>
       <c r="G379" t="n">
-        <v>2.90887141227722</v>
+        <v>2.90887117385864</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>3.25</v>
       </c>
       <c r="G381" t="n">
-        <v>2.90887141227722</v>
+        <v>2.90887117385864</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G382" t="n">
-        <v>2.95362329483032</v>
+        <v>2.95362305641174</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G383" t="n">
-        <v>2.95362329483032</v>
+        <v>2.95362305641174</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G384" t="n">
-        <v>3.0073254108429</v>
+        <v>3.00732493400574</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G385" t="n">
-        <v>2.95362329483032</v>
+        <v>2.95362305641174</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>3.25</v>
       </c>
       <c r="G387" t="n">
-        <v>2.90887141227722</v>
+        <v>2.90887117385864</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G388" t="n">
-        <v>2.82831788063049</v>
+        <v>2.82831811904907</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G390" t="n">
-        <v>2.81041741371155</v>
+        <v>2.81041765213013</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G394" t="n">
-        <v>2.94467258453369</v>
+        <v>2.94467282295227</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G395" t="n">
-        <v>3.06102752685547</v>
+        <v>3.06102800369263</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G396" t="n">
-        <v>3.06997776031494</v>
+        <v>3.06997799873352</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G397" t="n">
-        <v>3.17738246917725</v>
+        <v>3.17738223075867</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G398" t="n">
-        <v>3.17738246917725</v>
+        <v>3.17738223075867</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G399" t="n">
-        <v>3.26688647270203</v>
+        <v>3.26688671112061</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G401" t="n">
-        <v>3.26688647270203</v>
+        <v>3.26688671112061</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G402" t="n">
-        <v>3.26688647270203</v>
+        <v>3.26688671112061</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G403" t="n">
-        <v>3.31163787841797</v>
+        <v>3.31163811683655</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>3.75</v>
       </c>
       <c r="G404" t="n">
-        <v>3.35638999938965</v>
+        <v>3.35638976097107</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G405" t="n">
-        <v>3.39219117164612</v>
+        <v>3.39219164848328</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G406" t="n">
-        <v>3.499596118927</v>
+        <v>3.49959588050842</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G408" t="n">
-        <v>3.66965246200562</v>
+        <v>3.66965317726135</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4</v>
       </c>
       <c r="G412" t="n">
-        <v>3.58014893531799</v>
+        <v>3.58014917373657</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G415" t="n">
-        <v>3.66070318222046</v>
+        <v>3.66070246696472</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G417" t="n">
-        <v>3.49064540863037</v>
+        <v>3.49064564704895</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G418" t="n">
-        <v>3.53539776802063</v>
+        <v>3.53539752960205</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G419" t="n">
-        <v>3.66965246200562</v>
+        <v>3.66965317726135</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>4</v>
       </c>
       <c r="G420" t="n">
-        <v>3.58014893531799</v>
+        <v>3.58014917373657</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G421" t="n">
-        <v>3.66965246200562</v>
+        <v>3.66965317726135</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G422" t="n">
-        <v>3.66965246200562</v>
+        <v>3.66965317726135</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G425" t="n">
-        <v>3.62490153312683</v>
+        <v>3.62490105628967</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>4</v>
       </c>
       <c r="G427" t="n">
-        <v>3.58014893531799</v>
+        <v>3.58014917373657</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G430" t="n">
-        <v>3.69650459289551</v>
+        <v>3.69650435447693</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G431" t="n">
-        <v>3.75020599365234</v>
+        <v>3.75020623207092</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G432" t="n">
-        <v>3.78600788116455</v>
+        <v>3.78600835800171</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G433" t="n">
-        <v>3.90236306190491</v>
+        <v>3.90236258506775</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G436" t="n">
-        <v>4.09927082061768</v>
+        <v>4.09927129745483</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G437" t="n">
-        <v>4.09927082061768</v>
+        <v>4.09927129745483</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>4.75</v>
       </c>
       <c r="G438" t="n">
-        <v>4.25142765045166</v>
+        <v>4.2514271736145</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>4.43043422698975</v>
+        <v>4.4304347038269</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>4.29617977142334</v>
+        <v>4.29617929458618</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G443" t="n">
-        <v>4.23352670669556</v>
+        <v>4.2335262298584</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G446" t="n">
-        <v>3.90236306190491</v>
+        <v>3.90236258506775</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G447" t="n">
-        <v>3.92026376724243</v>
+        <v>3.92026352882385</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G448" t="n">
-        <v>3.76810717582703</v>
+        <v>3.76810765266418</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G449" t="n">
-        <v>3.7770574092865</v>
+        <v>3.77705669403076</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G450" t="n">
-        <v>3.66965246200562</v>
+        <v>3.66965317726135</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G451" t="n">
-        <v>3.7054545879364</v>
+        <v>3.70545434951782</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G452" t="n">
-        <v>3.9292140007019</v>
+        <v>3.92921376228333</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G453" t="n">
-        <v>4.00976657867432</v>
+        <v>4.00976800918579</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G455" t="n">
-        <v>4.13507270812988</v>
+        <v>4.13507175445557</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G456" t="n">
-        <v>4.05451965332031</v>
+        <v>4.05451917648315</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G458" t="n">
-        <v>4.29617977142334</v>
+        <v>4.29617929458618</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G460" t="n">
-        <v>4.34093046188354</v>
+        <v>4.34093141555786</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G461" t="n">
-        <v>4.40358352661133</v>
+        <v>4.40358304977417</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G463" t="n">
-        <v>4.3230299949646</v>
+        <v>4.32302951812744</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G466" t="n">
-        <v>4.38568305969238</v>
+        <v>4.38568353652954</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G468" t="n">
-        <v>4.29617977142334</v>
+        <v>4.29617929458618</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G469" t="n">
-        <v>4.21562576293945</v>
+        <v>4.21562671661377</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G472" t="n">
-        <v>4.38917779922485</v>
+        <v>4.3891773223877</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G473" t="n">
-        <v>4.2888011932373</v>
+        <v>4.28880023956299</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G476" t="n">
-        <v>4.2888011932373</v>
+        <v>4.28880023956299</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G481" t="n">
-        <v>4.27055072784424</v>
+        <v>4.27055168151855</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G482" t="n">
-        <v>4.26142597198486</v>
+        <v>4.26142644882202</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G483" t="n">
-        <v>4.2888011932373</v>
+        <v>4.28880023956299</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G484" t="n">
-        <v>4.21580076217651</v>
+        <v>4.2157998085022</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G485" t="n">
-        <v>4.2888011932373</v>
+        <v>4.28880023956299</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G486" t="n">
-        <v>4.35267639160156</v>
+        <v>4.35267734527588</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G487" t="n">
-        <v>4.3618016242981</v>
+        <v>4.36180257797241</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G488" t="n">
-        <v>4.3618016242981</v>
+        <v>4.36180257797241</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G490" t="n">
-        <v>4.2888011932373</v>
+        <v>4.28880023956299</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G491" t="n">
-        <v>4.2888011932373</v>
+        <v>4.28880023956299</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>4.75</v>
       </c>
       <c r="G492" t="n">
-        <v>4.33442735671997</v>
+        <v>4.33442687988281</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>4.75</v>
       </c>
       <c r="G493" t="n">
-        <v>4.33442735671997</v>
+        <v>4.33442687988281</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G495" t="n">
-        <v>4.38005304336548</v>
+        <v>4.38005256652832</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G497" t="n">
-        <v>4.38005304336548</v>
+        <v>4.38005256652832</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>4.75</v>
       </c>
       <c r="G498" t="n">
-        <v>4.33442735671997</v>
+        <v>4.33442687988281</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>4.75</v>
       </c>
       <c r="G499" t="n">
-        <v>4.33442735671997</v>
+        <v>4.33442687988281</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G500" t="n">
-        <v>4.38005304336548</v>
+        <v>4.38005256652832</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>4.75</v>
       </c>
       <c r="G503" t="n">
-        <v>4.33442735671997</v>
+        <v>4.33442687988281</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G504" t="n">
-        <v>4.29792642593384</v>
+        <v>4.297926902771</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G505" t="n">
-        <v>4.29792642593384</v>
+        <v>4.297926902771</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G506" t="n">
-        <v>4.29792642593384</v>
+        <v>4.297926902771</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G507" t="n">
-        <v>4.38005304336548</v>
+        <v>4.38005256652832</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G508" t="n">
-        <v>4.38005304336548</v>
+        <v>4.38005256652832</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G509" t="n">
-        <v>4.3161768913269</v>
+        <v>4.31617641448975</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G510" t="n">
-        <v>4.32530212402344</v>
+        <v>4.32530164718628</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G511" t="n">
-        <v>4.3161768913269</v>
+        <v>4.31617641448975</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G512" t="n">
-        <v>4.32530212402344</v>
+        <v>4.32530164718628</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>4.75</v>
       </c>
       <c r="G514" t="n">
-        <v>4.33442735671997</v>
+        <v>4.33442687988281</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G516" t="n">
-        <v>4.2888011932373</v>
+        <v>4.28880023956299</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G518" t="n">
-        <v>4.61730623245239</v>
+        <v>4.61730527877808</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>5</v>
       </c>
       <c r="G520" t="n">
-        <v>4.56255531311035</v>
+        <v>4.56255483627319</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G522" t="n">
-        <v>4.48042917251587</v>
+        <v>4.48042869567871</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G523" t="n">
-        <v>4.61730623245239</v>
+        <v>4.61730527877808</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G525" t="n">
-        <v>4.726806640625</v>
+        <v>4.72680711746216</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G526" t="n">
-        <v>4.79980802536011</v>
+        <v>4.79980754852295</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>4.9275598526001</v>
+        <v>4.92755889892578</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G534" t="n">
-        <v>5.1648120880127</v>
+        <v>5.16481161117554</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G535" t="n">
-        <v>5.20131206512451</v>
+        <v>5.20131254196167</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G536" t="n">
-        <v>5.27431344985962</v>
+        <v>5.27431392669678</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G537" t="n">
-        <v>5.1830620765686</v>
+        <v>5.18306159973145</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G538" t="n">
-        <v>5.1648120880127</v>
+        <v>5.16481161117554</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G539" t="n">
-        <v>5.1648120880127</v>
+        <v>5.16481161117554</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G541" t="n">
-        <v>5.00056028366089</v>
+        <v>5.00055980682373</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G545" t="n">
-        <v>5.05531024932861</v>
+        <v>5.05531072616577</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G546" t="n">
-        <v>5.14656162261963</v>
+        <v>5.14656114578247</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G547" t="n">
-        <v>5.14656162261963</v>
+        <v>5.14656114578247</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G548" t="n">
-        <v>5.20131206512451</v>
+        <v>5.20131254196167</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G549" t="n">
-        <v>5.1648120880127</v>
+        <v>5.16481161117554</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G551" t="n">
-        <v>5.1830620765686</v>
+        <v>5.18306159973145</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G552" t="n">
-        <v>5.1648120880127</v>
+        <v>5.16481161117554</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G555" t="n">
-        <v>5.25606346130371</v>
+        <v>5.25606298446655</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G556" t="n">
-        <v>5.3290638923645</v>
+        <v>5.32906436920166</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G557" t="n">
-        <v>5.42031526565552</v>
+        <v>5.42031478881836</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>6</v>
       </c>
       <c r="G558" t="n">
-        <v>5.47506666183472</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G560" t="n">
-        <v>5.73056936264038</v>
+        <v>5.73056888580322</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G561" t="n">
-        <v>5.49331569671631</v>
+        <v>5.49331521987915</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>6</v>
       </c>
       <c r="G563" t="n">
-        <v>5.47506666183472</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G564" t="n">
-        <v>5.42031526565552</v>
+        <v>5.42031478881836</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G565" t="n">
-        <v>5.3290638923645</v>
+        <v>5.32906436920166</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G568" t="n">
-        <v>5.27431344985962</v>
+        <v>5.27431392669678</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G569" t="n">
-        <v>5.25606346130371</v>
+        <v>5.25606298446655</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G571" t="n">
-        <v>5.3290638923645</v>
+        <v>5.32906436920166</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>6</v>
       </c>
       <c r="G572" t="n">
-        <v>5.47506666183472</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>6</v>
       </c>
       <c r="G573" t="n">
-        <v>5.47506666183472</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G574" t="n">
-        <v>5.42031526565552</v>
+        <v>5.42031478881836</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G578" t="n">
-        <v>5.36556434631348</v>
+        <v>5.36556482315063</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G579" t="n">
-        <v>5.34731435775757</v>
+        <v>5.34731388092041</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G580" t="n">
-        <v>5.42031526565552</v>
+        <v>5.42031478881836</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G581" t="n">
-        <v>5.45681524276733</v>
+        <v>5.45681571960449</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G582" t="n">
-        <v>5.49331569671631</v>
+        <v>5.49331521987915</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G583" t="n">
-        <v>5.43856525421143</v>
+        <v>5.43856573104858</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G584" t="n">
-        <v>5.43856525421143</v>
+        <v>5.43856573104858</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G585" t="n">
-        <v>5.43856525421143</v>
+        <v>5.43856573104858</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G586" t="n">
-        <v>5.42031526565552</v>
+        <v>5.42031478881836</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>6</v>
       </c>
       <c r="G587" t="n">
-        <v>5.47506666183472</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>6</v>
       </c>
       <c r="G588" t="n">
-        <v>5.47506666183472</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G589" t="n">
-        <v>5.43856525421143</v>
+        <v>5.43856573104858</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G590" t="n">
-        <v>5.43856525421143</v>
+        <v>5.43856573104858</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>6</v>
       </c>
       <c r="G591" t="n">
-        <v>5.47506666183472</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>6</v>
       </c>
       <c r="G592" t="n">
-        <v>5.47506666183472</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>6</v>
       </c>
       <c r="G593" t="n">
-        <v>5.47506666183472</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G594" t="n">
-        <v>5.43856525421143</v>
+        <v>5.43856573104858</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>6</v>
       </c>
       <c r="G595" t="n">
-        <v>5.47506666183472</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>6</v>
       </c>
       <c r="G596" t="n">
-        <v>5.47506666183472</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>6</v>
       </c>
       <c r="G597" t="n">
-        <v>5.47506666183472</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G598" t="n">
-        <v>5.45681524276733</v>
+        <v>5.45681571960449</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G600" t="n">
-        <v>5.49331569671631</v>
+        <v>5.49331521987915</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>6</v>
       </c>
       <c r="G601" t="n">
-        <v>5.47506666183472</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>6</v>
       </c>
       <c r="G602" t="n">
-        <v>5.47506666183472</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>6</v>
       </c>
       <c r="G604" t="n">
-        <v>5.47506666183472</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G607" t="n">
-        <v>5.80357027053833</v>
+        <v>5.80356931686401</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G611" t="n">
-        <v>6.40582656860352</v>
+        <v>6.40582704544067</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G612" t="n">
-        <v>6.49707794189453</v>
+        <v>6.49707746505737</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G613" t="n">
-        <v>6.51532888412476</v>
+        <v>6.51532793045044</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G614" t="n">
-        <v>6.49707794189453</v>
+        <v>6.49707746505737</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G615" t="n">
-        <v>6.47882747650146</v>
+        <v>6.47882699966431</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G616" t="n">
-        <v>6.49707794189453</v>
+        <v>6.49707746505737</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G618" t="n">
-        <v>6.69783067703247</v>
+        <v>6.69783020019531</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G619" t="n">
-        <v>7.00808429718018</v>
+        <v>7.00808382034302</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G620" t="n">
-        <v>6.916832447052</v>
+        <v>6.91683292388916</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G621" t="n">
-        <v>7.13583612442017</v>
+        <v>7.13583564758301</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>8</v>
       </c>
       <c r="G622" t="n">
-        <v>7.30008697509766</v>
+        <v>7.30008840560913</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G623" t="n">
-        <v>7.39133930206299</v>
+        <v>7.39133882522583</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G624" t="n">
-        <v>7.62859201431274</v>
+        <v>7.62859153747559</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>8.5</v>
       </c>
       <c r="G625" t="n">
-        <v>7.75634384155273</v>
+        <v>7.75634336471558</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G626" t="n">
-        <v>7.73809289932251</v>
+        <v>7.73809337615967</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G627" t="n">
-        <v>7.84759426116943</v>
+        <v>7.84759521484375</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G629" t="n">
-        <v>7.84759426116943</v>
+        <v>7.84759521484375</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G630" t="n">
-        <v>7.93884468078613</v>
+        <v>7.93884515762329</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>8.5</v>
       </c>
       <c r="G631" t="n">
-        <v>7.75634384155273</v>
+        <v>7.75634336471558</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G632" t="n">
-        <v>7.93884468078613</v>
+        <v>7.93884515762329</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G633" t="n">
-        <v>7.97534561157227</v>
+        <v>7.97534608840942</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G634" t="n">
-        <v>8.43160152435303</v>
+        <v>8.43159961700439</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G635" t="n">
-        <v>8.57760238647461</v>
+        <v>8.57760047912598</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G636" t="n">
-        <v>8.65060424804688</v>
+        <v>8.65060329437256</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G637" t="n">
-        <v>8.63235378265381</v>
+        <v>8.63235282897949</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G638" t="n">
-        <v>8.65060424804688</v>
+        <v>8.65060329437256</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G639" t="n">
-        <v>8.26735019683838</v>
+        <v>8.26734924316406</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G640" t="n">
-        <v>8.26735019683838</v>
+        <v>8.26734924316406</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G641" t="n">
-        <v>8.55935287475586</v>
+        <v>8.55935192108154</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G643" t="n">
-        <v>8.57760238647461</v>
+        <v>8.57760047912598</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G644" t="n">
-        <v>8.43160152435303</v>
+        <v>8.43159961700439</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G645" t="n">
-        <v>8.37685012817383</v>
+        <v>8.37685203552246</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G647" t="n">
-        <v>8.13959980010986</v>
+        <v>8.13959789276123</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G648" t="n">
-        <v>8.30385112762451</v>
+        <v>8.30384826660156</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G649" t="n">
-        <v>8.52285194396973</v>
+        <v>8.52285289764404</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G650" t="n">
-        <v>8.37685012817383</v>
+        <v>8.37685203552246</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G651" t="n">
-        <v>8.55935287475586</v>
+        <v>8.55935192108154</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G652" t="n">
-        <v>8.54110145568848</v>
+        <v>8.54110336303711</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G653" t="n">
-        <v>8.54110145568848</v>
+        <v>8.54110336303711</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G655" t="n">
-        <v>9.08860969543457</v>
+        <v>9.08860874176025</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G656" t="n">
-        <v>9.17073631286621</v>
+        <v>9.17073535919189</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>10</v>
       </c>
       <c r="G672" t="n">
-        <v>9.1251106262207</v>
+        <v>9.12510967254639</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G673" t="n">
-        <v>9.03385734558105</v>
+        <v>9.03385925292969</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G674" t="n">
-        <v>9.30761241912842</v>
+        <v>9.3076114654541</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>9.49011421203613</v>
+        <v>9.49011325836182</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G677" t="n">
-        <v>9.94636821746826</v>
+        <v>9.94636917114258</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G688" t="n">
-        <v>8.90610885620117</v>
+        <v>8.90610599517822</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G689" t="n">
-        <v>9.26198673248291</v>
+        <v>9.26198577880859</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G691" t="n">
-        <v>9.10685920715332</v>
+        <v>9.106858253479</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G692" t="n">
-        <v>8.99735832214355</v>
+        <v>8.99735736846924</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G693" t="n">
-        <v>8.77835559844971</v>
+        <v>8.77835464477539</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G694" t="n">
-        <v>8.97910785675049</v>
+        <v>8.97910690307617</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G696" t="n">
-        <v>8.55935287475586</v>
+        <v>8.55935192108154</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G697" t="n">
-        <v>7.84759426116943</v>
+        <v>7.84759521484375</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G698" t="n">
-        <v>7.61034202575684</v>
+        <v>7.61034250259399</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G699" t="n">
-        <v>7.11758518218994</v>
+        <v>7.1175856590271</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>8</v>
       </c>
       <c r="G700" t="n">
-        <v>7.30008697509766</v>
+        <v>7.30008840560913</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G702" t="n">
-        <v>7.26358699798584</v>
+        <v>7.263587474823</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G705" t="n">
-        <v>6.916832447052</v>
+        <v>6.91683292388916</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G707" t="n">
-        <v>7.50084018707275</v>
+        <v>7.50084066390991</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G708" t="n">
-        <v>7.51909017562866</v>
+        <v>7.5190896987915</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G709" t="n">
-        <v>7.62859201431274</v>
+        <v>7.62859153747559</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G710" t="n">
-        <v>8.03009700775146</v>
+        <v>8.03009605407715</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G711" t="n">
-        <v>7.64684104919434</v>
+        <v>7.64684247970581</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G712" t="n">
-        <v>7.77459335327148</v>
+        <v>7.7745943069458</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>8.5</v>
       </c>
       <c r="G713" t="n">
-        <v>7.75634384155273</v>
+        <v>7.75634336471558</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G715" t="n">
-        <v>8.0483455657959</v>
+        <v>8.04834651947021</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G717" t="n">
-        <v>8.30385112762451</v>
+        <v>8.30384826660156</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G719" t="n">
-        <v>8.76010608673096</v>
+        <v>8.76010513305664</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G720" t="n">
-        <v>9.03385734558105</v>
+        <v>9.03385925292969</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G722" t="n">
-        <v>9.21636199951172</v>
+        <v>9.21636009216309</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G723" t="n">
-        <v>8.92435741424561</v>
+        <v>8.92435550689697</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G725" t="n">
-        <v>9.08860969543457</v>
+        <v>9.08860874176025</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G726" t="n">
-        <v>9.08860969543457</v>
+        <v>9.08860874176025</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G730" t="n">
-        <v>9.49011421203613</v>
+        <v>9.49011325836182</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G733" t="n">
-        <v>10.2201223373413</v>
+        <v>10.220121383667</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G734" t="n">
-        <v>10.402624130249</v>
+        <v>10.4026250839233</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G737" t="n">
-        <v>10.2176895141602</v>
+        <v>10.2176904678345</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G738" t="n">
-        <v>10.3101558685303</v>
+        <v>10.3101568222046</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>11</v>
       </c>
       <c r="G739" t="n">
-        <v>10.1714572906494</v>
+        <v>10.1714563369751</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G740" t="n">
-        <v>10.4950933456421</v>
+        <v>10.4950923919678</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G741" t="n">
-        <v>10.3101558685303</v>
+        <v>10.3101568222046</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>10.25</v>
       </c>
       <c r="G747" t="n">
-        <v>9.47794723510742</v>
+        <v>9.47794818878174</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G755" t="n">
-        <v>10.078987121582</v>
+        <v>10.0789880752563</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G757" t="n">
-        <v>10.3101558685303</v>
+        <v>10.3101568222046</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G759" t="n">
-        <v>10.4950933456421</v>
+        <v>10.4950923919678</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>11</v>
       </c>
       <c r="G764" t="n">
-        <v>10.1714572906494</v>
+        <v>10.1714563369751</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G765" t="n">
-        <v>10.078987121582</v>
+        <v>10.0789880752563</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G766" t="n">
-        <v>10.5413255691528</v>
+        <v>10.5413265228271</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G767" t="n">
-        <v>10.5413255691528</v>
+        <v>10.5413265228271</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G768" t="n">
-        <v>11.0036659240723</v>
+        <v>11.0036649703979</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G769" t="n">
-        <v>11.6047067642212</v>
+        <v>11.6047058105469</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G770" t="n">
-        <v>11.9745779037476</v>
+        <v>11.9745769500732</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>13</v>
       </c>
       <c r="G772" t="n">
-        <v>12.0208101272583</v>
+        <v>12.0208110809326</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>13</v>
       </c>
       <c r="G776" t="n">
-        <v>12.0208101272583</v>
+        <v>12.0208110809326</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G777" t="n">
-        <v>12.1595125198364</v>
+        <v>12.1595115661621</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G778" t="n">
-        <v>11.9745779037476</v>
+        <v>11.9745769500732</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G780" t="n">
-        <v>12.0670442581177</v>
+        <v>12.067045211792</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>13</v>
       </c>
       <c r="G781" t="n">
-        <v>12.0208101272583</v>
+        <v>12.0208110809326</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G783" t="n">
-        <v>11.9283428192139</v>
+        <v>11.9283418655396</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G784" t="n">
-        <v>11.8358764648438</v>
+        <v>11.8358755111694</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G785" t="n">
-        <v>11.9745779037476</v>
+        <v>11.9745769500732</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>13</v>
       </c>
       <c r="G789" t="n">
-        <v>12.0208101272583</v>
+        <v>12.0208110809326</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G790" t="n">
-        <v>11.9283428192139</v>
+        <v>11.9283418655396</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G791" t="n">
-        <v>11.7434072494507</v>
+        <v>11.743408203125</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G792" t="n">
-        <v>11.6509408950806</v>
+        <v>11.6509399414062</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G793" t="n">
-        <v>11.5122385025024</v>
+        <v>11.5122375488281</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G794" t="n">
-        <v>11.6509408950806</v>
+        <v>11.6509399414062</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G795" t="n">
-        <v>11.4660034179688</v>
+        <v>11.4660043716431</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G797" t="n">
-        <v>11.6971731185913</v>
+        <v>11.6971740722656</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G798" t="n">
-        <v>11.4197702407837</v>
+        <v>11.419771194458</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G800" t="n">
-        <v>11.3735389709473</v>
+        <v>11.37353515625</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G801" t="n">
-        <v>11.1423664093018</v>
+        <v>11.1423683166504</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G802" t="n">
-        <v>10.8187294006348</v>
+        <v>10.8187303543091</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G803" t="n">
-        <v>11.1423664093018</v>
+        <v>11.1423683166504</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G808" t="n">
-        <v>11.3735389709473</v>
+        <v>11.37353515625</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G810" t="n">
-        <v>11.4197702407837</v>
+        <v>11.419771194458</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G812" t="n">
-        <v>11.8358764648438</v>
+        <v>11.8358755111694</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G814" t="n">
-        <v>11.6509408950806</v>
+        <v>11.6509399414062</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G815" t="n">
-        <v>11.6509408950806</v>
+        <v>11.6509399414062</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G817" t="n">
-        <v>11.6509408950806</v>
+        <v>11.6509399414062</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G818" t="n">
-        <v>11.6509408950806</v>
+        <v>11.6509399414062</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G819" t="n">
-        <v>11.6971731185913</v>
+        <v>11.6971740722656</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G820" t="n">
-        <v>11.4660034179688</v>
+        <v>11.4660043716431</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G824" t="n">
-        <v>11.6509408950806</v>
+        <v>11.6509399414062</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G825" t="n">
-        <v>11.9745779037476</v>
+        <v>11.9745769500732</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G826" t="n">
-        <v>12.0670442581177</v>
+        <v>12.067045211792</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G829" t="n">
-        <v>13.130425453186</v>
+        <v>13.1304235458374</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G830" t="n">
-        <v>13.454062461853</v>
+        <v>13.4540605545044</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G831" t="n">
-        <v>13.731466293335</v>
+        <v>13.7314643859863</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G832" t="n">
-        <v>14.1938047409058</v>
+        <v>14.1938037872314</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>14.1938047409058</v>
+        <v>14.1938037872314</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>16.25</v>
       </c>
       <c r="G836" t="n">
-        <v>15.0260133743286</v>
+        <v>15.0260143280029</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G838" t="n">
-        <v>16.4592628479004</v>
+        <v>16.459264755249</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G839" t="n">
-        <v>16.2743282318115</v>
+        <v>16.2743301391602</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G840" t="n">
-        <v>16.2280960083008</v>
+        <v>16.2280941009521</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G841" t="n">
-        <v>16.2280960083008</v>
+        <v>16.2280941009521</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>17</v>
       </c>
       <c r="G843" t="n">
-        <v>15.7195234298706</v>
+        <v>15.7195224761963</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G846" t="n">
-        <v>14.9335460662842</v>
+        <v>14.9335451126099</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G847" t="n">
-        <v>14.6561422348022</v>
+        <v>14.6561431884766</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>16.5</v>
       </c>
       <c r="G848" t="n">
-        <v>15.2571840286255</v>
+        <v>15.2571849822998</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G853" t="n">
-        <v>15.8119916915894</v>
+        <v>15.8119897842407</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G854" t="n">
-        <v>15.3958835601807</v>
+        <v>15.3958854675293</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G858" t="n">
-        <v>14.4249725341797</v>
+        <v>14.424973487854</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G860" t="n">
-        <v>13.5465288162231</v>
+        <v>13.5465297698975</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G861" t="n">
-        <v>13.3615942001343</v>
+        <v>13.3615951538086</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G863" t="n">
-        <v>13.0379581451416</v>
+        <v>13.0379571914673</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G864" t="n">
-        <v>13.130425453186</v>
+        <v>13.1304235458374</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G865" t="n">
-        <v>13.3615942001343</v>
+        <v>13.3615951538086</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>16.5</v>
       </c>
       <c r="G869" t="n">
-        <v>15.2571840286255</v>
+        <v>15.2571849822998</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G872" t="n">
-        <v>15.072247505188</v>
+        <v>15.0722465515137</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G877" t="n">
-        <v>14.2862710952759</v>
+        <v>14.2862720489502</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G878" t="n">
-        <v>14.3787393569946</v>
+        <v>14.3787384033203</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G879" t="n">
-        <v>14.7023763656616</v>
+        <v>14.7023773193359</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G882" t="n">
-        <v>14.1938047409058</v>
+        <v>14.1938037872314</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>13.5465288162231</v>
+        <v>13.5465297698975</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G887" t="n">
-        <v>13.454062461853</v>
+        <v>13.4540605545044</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G888" t="n">
-        <v>13.3153610229492</v>
+        <v>13.3153591156006</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G889" t="n">
-        <v>13.2228918075562</v>
+        <v>13.2228927612305</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>14.75</v>
       </c>
       <c r="G890" t="n">
-        <v>13.6389980316162</v>
+        <v>13.6389970779419</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23613,7 +23613,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G894" t="n">
-        <v>14.6561422348022</v>
+        <v>14.6561431884766</v>
       </c>
       <c r="H894" t="s">
         <v>8</v>
@@ -23691,7 +23691,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G897" t="n">
-        <v>14.6561422348022</v>
+        <v>14.6561431884766</v>
       </c>
       <c r="H897" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G900" t="n">
-        <v>14.8873109817505</v>
+        <v>14.8873128890991</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G902" t="n">
-        <v>15.072247505188</v>
+        <v>15.0722465515137</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G903" t="n">
-        <v>14.9335460662842</v>
+        <v>14.9335451126099</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G905" t="n">
-        <v>15.072247505188</v>
+        <v>15.0722465515137</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G906" t="n">
-        <v>15.5345849990845</v>
+        <v>15.5345859527588</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G908" t="n">
-        <v>15.1184816360474</v>
+        <v>15.1184825897217</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G909" t="n">
-        <v>14.9335460662842</v>
+        <v>14.9335451126099</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G912" t="n">
-        <v>14.6561422348022</v>
+        <v>14.6561431884766</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G913" t="n">
-        <v>14.2400379180908</v>
+        <v>14.2400369644165</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G914" t="n">
-        <v>14.4249725341797</v>
+        <v>14.424973487854</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G915" t="n">
-        <v>13.9626350402832</v>
+        <v>13.9626340866089</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G926" t="n">
-        <v>14.2862710952759</v>
+        <v>14.2862720489502</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G927" t="n">
-        <v>14.0551013946533</v>
+        <v>14.0551023483276</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G928" t="n">
-        <v>14.3787393569946</v>
+        <v>14.3787384033203</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G930" t="n">
-        <v>14.4249725341797</v>
+        <v>14.424973487854</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G931" t="n">
-        <v>15.072247505188</v>
+        <v>15.0722465515137</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G932" t="n">
-        <v>14.8873109817505</v>
+        <v>14.8873128890991</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G935" t="n">
-        <v>14.7023763656616</v>
+        <v>14.7023773193359</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24731,7 +24731,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G937" t="n">
-        <v>14.6561422348022</v>
+        <v>14.6561431884766</v>
       </c>
       <c r="H937" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G940" t="n">
-        <v>14.7023763656616</v>
+        <v>14.7023773193359</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G942" t="n">
-        <v>14.2862710952759</v>
+        <v>14.2862720489502</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G943" t="n">
-        <v>14.7023763656616</v>
+        <v>14.7023773193359</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G944" t="n">
-        <v>14.6561422348022</v>
+        <v>14.6561431884766</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G945" t="n">
-        <v>14.3787393569946</v>
+        <v>14.3787384033203</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G946" t="n">
-        <v>14.6561422348022</v>
+        <v>14.6561431884766</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G947" t="n">
-        <v>14.6099081039429</v>
+        <v>14.6099090576172</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G948" t="n">
-        <v>14.4249725341797</v>
+        <v>14.424973487854</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G949" t="n">
-        <v>14.4249725341797</v>
+        <v>14.424973487854</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G951" t="n">
-        <v>13.5465288162231</v>
+        <v>13.5465297698975</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G956" t="n">
-        <v>14.0551013946533</v>
+        <v>14.0551023483276</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G957" t="n">
-        <v>14.0551013946533</v>
+        <v>14.0551023483276</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G958" t="n">
-        <v>14.1938047409058</v>
+        <v>14.1938037872314</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G960" t="n">
-        <v>13.9626350402832</v>
+        <v>13.9626340866089</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G961" t="n">
-        <v>13.5465288162231</v>
+        <v>13.5465297698975</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G962" t="n">
-        <v>13.3615942001343</v>
+        <v>13.3615951538086</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G964" t="n">
-        <v>13.454062461853</v>
+        <v>13.4540605545044</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G968" t="n">
-        <v>14.2862710952759</v>
+        <v>14.2862720489502</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G969" t="n">
-        <v>14.2770233154297</v>
+        <v>14.2770252227783</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>15.5</v>
       </c>
       <c r="G970" t="n">
-        <v>14.3325061798096</v>
+        <v>14.3325052261353</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G971" t="n">
-        <v>14.6099081039429</v>
+        <v>14.6099090576172</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G975" t="n">
-        <v>14.3509998321533</v>
+        <v>14.350998878479</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G977" t="n">
-        <v>14.7023763656616</v>
+        <v>14.7023773193359</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G981" t="n">
-        <v>14.6653890609741</v>
+        <v>14.6653881072998</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G982" t="n">
-        <v>14.7763500213623</v>
+        <v>14.7763509750366</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G983" t="n">
-        <v>14.924298286438</v>
+        <v>14.9243001937866</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G984" t="n">
-        <v>15.2017030715942</v>
+        <v>15.2017040252686</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G986" t="n">
-        <v>15.0352611541748</v>
+        <v>15.0352602005005</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G987" t="n">
-        <v>14.9982719421387</v>
+        <v>14.998272895813</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G989" t="n">
-        <v>15.072247505188</v>
+        <v>15.0722465515137</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G991" t="n">
-        <v>14.7023763656616</v>
+        <v>14.7023773193359</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G992" t="n">
-        <v>14.9612855911255</v>
+        <v>14.9612865447998</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G993" t="n">
-        <v>14.9612855911255</v>
+        <v>14.9612865447998</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G995" t="n">
-        <v>14.8728675842285</v>
+        <v>14.8728685379028</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G996" t="n">
-        <v>14.5191955566406</v>
+        <v>14.5191965103149</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G998" t="n">
-        <v>14.9845533370972</v>
+        <v>14.9845552444458</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G999" t="n">
-        <v>15.133469581604</v>
+        <v>15.1334686279297</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1001" t="n">
-        <v>15.2265434265137</v>
+        <v>15.226541519165</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1003" t="n">
-        <v>14.9845533370972</v>
+        <v>14.9845552444458</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>16.4699993133545</v>
       </c>
       <c r="G1004" t="n">
-        <v>15.3289194107056</v>
+        <v>15.3289213180542</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>17.3120002746582</v>
       </c>
       <c r="G1005" t="n">
-        <v>16.112585067749</v>
+        <v>16.1125831604004</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>17.75</v>
       </c>
       <c r="G1006" t="n">
-        <v>16.5202407836914</v>
+        <v>16.5202388763428</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1008" t="n">
-        <v>17.9628486633301</v>
+        <v>17.9628524780273</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1009" t="n">
-        <v>17.9814643859863</v>
+        <v>17.981466293335</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1010" t="n">
-        <v>17.9628486633301</v>
+        <v>17.9628524780273</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G1011" t="n">
-        <v>17.4602642059326</v>
+        <v>17.460262298584</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1012" t="n">
-        <v>17.2741203308105</v>
+        <v>17.2741222381592</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1013" t="n">
-        <v>17.4044208526611</v>
+        <v>17.4044227600098</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1014" t="n">
-        <v>18.0559215545654</v>
+        <v>18.0559234619141</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1015" t="n">
-        <v>16.6040058135986</v>
+        <v>16.60400390625</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G1016" t="n">
-        <v>16.5295448303223</v>
+        <v>16.5295467376709</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1020" t="n">
-        <v>16.492317199707</v>
+        <v>16.4923152923584</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1027" t="n">
-        <v>17.9814643859863</v>
+        <v>17.981466293335</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G1028" t="n">
-        <v>17.7208633422852</v>
+        <v>17.7208652496338</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G1034" t="n">
-        <v>17.7580909729004</v>
+        <v>17.7580947875977</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1036" t="n">
-        <v>18.297908782959</v>
+        <v>18.2979106903076</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1042" t="n">
-        <v>18.297908782959</v>
+        <v>18.2979106903076</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1044" t="n">
-        <v>17.571949005127</v>
+        <v>17.5719470977783</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G1046" t="n">
-        <v>17.348575592041</v>
+        <v>17.3485774993896</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1049" t="n">
-        <v>17.7394771575928</v>
+        <v>17.7394790649414</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G1051" t="n">
-        <v>17.9442386627197</v>
+        <v>17.9442367553711</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1052" t="n">
-        <v>17.9814643859863</v>
+        <v>17.981466293335</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1053" t="n">
-        <v>18.2420692443848</v>
+        <v>18.2420654296875</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1054" t="n">
-        <v>18.5212821960449</v>
+        <v>18.5212802886963</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>20.25</v>
       </c>
       <c r="G1055" t="n">
-        <v>18.8470325469971</v>
+        <v>18.8470344543457</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>21.1000003814697</v>
       </c>
       <c r="G1056" t="n">
-        <v>19.6381416320801</v>
+        <v>19.6381435394287</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G1057" t="n">
-        <v>20.1500377655029</v>
+        <v>20.1500358581543</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1058" t="n">
-        <v>20.6153984069824</v>
+        <v>20.6153964996338</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1059" t="n">
-        <v>20.5688610076904</v>
+        <v>20.5688629150391</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1061" t="n">
-        <v>21.4995765686035</v>
+        <v>21.4995784759521</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>23</v>
       </c>
       <c r="G1062" t="n">
-        <v>21.4065074920654</v>
+        <v>21.4065036773682</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1063" t="n">
-        <v>21.4995765686035</v>
+        <v>21.4995784759521</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1065" t="n">
-        <v>22.0580081939697</v>
+        <v>22.058012008667</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G1068" t="n">
-        <v>22.2255401611328</v>
+        <v>22.2255382537842</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>23.9799995422363</v>
       </c>
       <c r="G1074" t="n">
-        <v>22.3186092376709</v>
+        <v>22.3186111450195</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>24.2399997711182</v>
       </c>
       <c r="G1075" t="n">
-        <v>22.5605983734131</v>
+        <v>22.5605945587158</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>25.2199993133545</v>
       </c>
       <c r="G1076" t="n">
-        <v>23.4727001190186</v>
+        <v>23.4726982116699</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>26.4599990844727</v>
       </c>
       <c r="G1079" t="n">
-        <v>24.6267890930176</v>
+        <v>24.6267871856689</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>25.6200008392334</v>
       </c>
       <c r="G1080" t="n">
-        <v>23.8449878692627</v>
+        <v>23.8449859619141</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G1081" t="n">
-        <v>25.2969055175781</v>
+        <v>25.2969074249268</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G1087" t="n">
-        <v>24.4034175872803</v>
+        <v>24.4034194946289</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G1088" t="n">
-        <v>24.4034175872803</v>
+        <v>24.4034194946289</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>27.2199993133545</v>
       </c>
       <c r="G1091" t="n">
-        <v>25.334135055542</v>
+        <v>25.3341331481934</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>26.5599994659424</v>
       </c>
       <c r="G1092" t="n">
-        <v>24.7198600769043</v>
+        <v>24.7198619842529</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1094" t="n">
-        <v>24.0125160217285</v>
+        <v>24.0125141143799</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>24.5200004577637</v>
       </c>
       <c r="G1095" t="n">
-        <v>22.8211994171143</v>
+        <v>22.8211975097656</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G1099" t="n">
-        <v>22.8770408630371</v>
+        <v>22.8770389556885</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>25.2399997711182</v>
       </c>
       <c r="G1102" t="n">
-        <v>23.4913139343262</v>
+        <v>23.4913158416748</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1103" t="n">
-        <v>23.6402282714844</v>
+        <v>23.640230178833</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1105" t="n">
-        <v>24.1055889129639</v>
+        <v>24.1055870056152</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>26.5400009155273</v>
       </c>
       <c r="G1106" t="n">
-        <v>24.7012481689453</v>
+        <v>24.7012462615967</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>26.5</v>
       </c>
       <c r="G1107" t="n">
-        <v>24.6640186309814</v>
+        <v>24.6640205383301</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>26.5799999237061</v>
       </c>
       <c r="G1108" t="n">
-        <v>24.7384738922119</v>
+        <v>24.7384757995605</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1109" t="n">
-        <v>26.8046703338623</v>
+        <v>26.8046684265137</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1111" t="n">
-        <v>26.8046703338623</v>
+        <v>26.8046684265137</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>32.3800010681152</v>
       </c>
       <c r="G1113" t="n">
-        <v>30.1366405487061</v>
+        <v>30.1366386413574</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G1114" t="n">
-        <v>29.6898937225342</v>
+        <v>29.6898918151855</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>30.5200004577637</v>
       </c>
       <c r="G1118" t="n">
-        <v>28.4055042266846</v>
+        <v>28.4055023193359</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>30.8400001525879</v>
       </c>
       <c r="G1119" t="n">
-        <v>28.703332901001</v>
+        <v>28.7033348083496</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>31.7199993133545</v>
       </c>
       <c r="G1120" t="n">
-        <v>29.5223636627197</v>
+        <v>29.5223617553711</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>32.6199989318848</v>
       </c>
       <c r="G1122" t="n">
-        <v>30.3600082397461</v>
+        <v>30.3600101470947</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>32.439998626709</v>
       </c>
       <c r="G1123" t="n">
-        <v>30.1924781799316</v>
+        <v>30.1924800872803</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>33.7200012207031</v>
       </c>
       <c r="G1124" t="n">
-        <v>31.3838043212891</v>
+        <v>31.3837985992432</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>33.5400009155273</v>
       </c>
       <c r="G1127" t="n">
-        <v>31.2162704467773</v>
+        <v>31.216272354126</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>33.5</v>
       </c>
       <c r="G1129" t="n">
-        <v>31.1790390014648</v>
+        <v>31.1790428161621</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1131" t="n">
-        <v>31.8305492401123</v>
+        <v>31.8305435180664</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>32.9599990844727</v>
       </c>
       <c r="G1132" t="n">
-        <v>30.6764545440674</v>
+        <v>30.6764526367188</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1135" t="n">
-        <v>28.9453201293945</v>
+        <v>28.9453182220459</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>32.4799995422363</v>
       </c>
       <c r="G1138" t="n">
-        <v>30.2297115325928</v>
+        <v>30.2297096252441</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>33.7200012207031</v>
       </c>
       <c r="G1142" t="n">
-        <v>31.3838043212891</v>
+        <v>31.3837985992432</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>33.4599990844727</v>
       </c>
       <c r="G1143" t="n">
-        <v>31.1418113708496</v>
+        <v>31.1418132781982</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>34.439998626709</v>
       </c>
       <c r="G1144" t="n">
-        <v>32.0539169311523</v>
+        <v>32.0539131164551</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>35.2599983215332</v>
       </c>
       <c r="G1146" t="n">
-        <v>32.8171081542969</v>
+        <v>32.8171043395996</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G1147" t="n">
-        <v>32.7612609863281</v>
+        <v>32.7612648010254</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>36</v>
       </c>
       <c r="G1148" t="n">
-        <v>33.5058364868164</v>
+        <v>33.5058403015137</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>33.6199989318848</v>
       </c>
       <c r="G1152" t="n">
-        <v>31.2907276153564</v>
+        <v>31.2907314300537</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>33.9199981689453</v>
       </c>
       <c r="G1153" t="n">
-        <v>31.5699424743652</v>
+        <v>31.5699443817139</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>35.7400016784668</v>
       </c>
       <c r="G1159" t="n">
-        <v>33.2638549804688</v>
+        <v>33.2638511657715</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>35.6800003051758</v>
       </c>
       <c r="G1160" t="n">
-        <v>33.2080116271973</v>
+        <v>33.2080078125</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>35.8400001525879</v>
       </c>
       <c r="G1161" t="n">
-        <v>33.3569221496582</v>
+        <v>33.3569259643555</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>37.9799995422363</v>
       </c>
       <c r="G1163" t="n">
-        <v>35.3486557006836</v>
+        <v>35.3486595153809</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>38.060001373291</v>
       </c>
       <c r="G1165" t="n">
-        <v>35.4231147766113</v>
+        <v>35.4231185913086</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>36</v>
       </c>
       <c r="G1166" t="n">
-        <v>33.5058364868164</v>
+        <v>33.5058403015137</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>33.5400009155273</v>
       </c>
       <c r="G1167" t="n">
-        <v>31.2162704467773</v>
+        <v>31.216272354126</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>34</v>
       </c>
       <c r="G1168" t="n">
-        <v>31.6444034576416</v>
+        <v>31.644401550293</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>35.5</v>
       </c>
       <c r="G1170" t="n">
-        <v>33.0404815673828</v>
+        <v>33.0404777526855</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>33.439998626709</v>
       </c>
       <c r="G1173" t="n">
-        <v>31.1231994628906</v>
+        <v>31.123197555542</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>30.8400001525879</v>
       </c>
       <c r="G1177" t="n">
-        <v>28.703332901001</v>
+        <v>28.7033348083496</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>30.1800003051758</v>
       </c>
       <c r="G1179" t="n">
-        <v>28.0890579223633</v>
+        <v>28.0890598297119</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>30.0599994659424</v>
       </c>
       <c r="G1181" t="n">
-        <v>27.9773731231689</v>
+        <v>27.9773712158203</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>31.1800003051758</v>
       </c>
       <c r="G1182" t="n">
-        <v>29.0197772979736</v>
+        <v>29.0197792053223</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>32.9799995422363</v>
       </c>
       <c r="G1183" t="n">
-        <v>30.6950664520264</v>
+        <v>30.695068359375</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>32.5400009155273</v>
       </c>
       <c r="G1184" t="n">
-        <v>30.2855567932129</v>
+        <v>30.2855529785156</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>30.7199993133545</v>
       </c>
       <c r="G1186" t="n">
-        <v>28.591646194458</v>
+        <v>28.5916481018066</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1187" t="n">
-        <v>27.7353858947754</v>
+        <v>27.735387802124</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>30.1399993896484</v>
       </c>
       <c r="G1189" t="n">
-        <v>28.0518283843994</v>
+        <v>28.051830291748</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>30.1800003051758</v>
       </c>
       <c r="G1193" t="n">
-        <v>28.0890579223633</v>
+        <v>28.0890598297119</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>29.9799995422363</v>
       </c>
       <c r="G1194" t="n">
-        <v>27.9029159545898</v>
+        <v>27.9029178619385</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1198" t="n">
-        <v>26.897741317749</v>
+        <v>26.8977432250977</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>28.8799991607666</v>
       </c>
       <c r="G1201" t="n">
-        <v>26.8791255950928</v>
+        <v>26.8791275024414</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>28.8799991607666</v>
       </c>
       <c r="G1203" t="n">
-        <v>26.8791255950928</v>
+        <v>26.8791275024414</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>28.5</v>
       </c>
       <c r="G1204" t="n">
-        <v>26.5254554748535</v>
+        <v>26.5254535675049</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G1205" t="n">
-        <v>25.2969055175781</v>
+        <v>25.2969074249268</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>25.7800006866455</v>
       </c>
       <c r="G1207" t="n">
-        <v>23.9939041137695</v>
+        <v>23.9939022064209</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>26</v>
       </c>
       <c r="G1208" t="n">
-        <v>24.198657989502</v>
+        <v>24.1986598968506</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>27.1200008392334</v>
       </c>
       <c r="G1210" t="n">
-        <v>25.2410640716553</v>
+        <v>25.2410659790039</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>28.4799995422363</v>
       </c>
       <c r="G1212" t="n">
-        <v>26.5068397521973</v>
+        <v>26.5068378448486</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>29.8799991607666</v>
       </c>
       <c r="G1215" t="n">
-        <v>27.8098449707031</v>
+        <v>27.8098430633545</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>29.3199996948242</v>
       </c>
       <c r="G1216" t="n">
-        <v>27.2886409759521</v>
+        <v>27.2886428833008</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>28.8400001525879</v>
       </c>
       <c r="G1217" t="n">
-        <v>26.8418979644775</v>
+        <v>26.8418998718262</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1218" t="n">
-        <v>27.6423168182373</v>
+        <v>27.6423149108887</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1219" t="n">
-        <v>27.7353858947754</v>
+        <v>27.735387802124</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>29.5</v>
       </c>
       <c r="G1220" t="n">
-        <v>27.4561729431152</v>
+        <v>27.4561710357666</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1221" t="n">
-        <v>28.293815612793</v>
+        <v>28.2938175201416</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>30.9200000762939</v>
       </c>
       <c r="G1224" t="n">
-        <v>28.7777900695801</v>
+        <v>28.7777919769287</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>29.9599990844727</v>
       </c>
       <c r="G1225" t="n">
-        <v>27.8843021392822</v>
+        <v>27.8843002319336</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>28.9799995422363</v>
       </c>
       <c r="G1228" t="n">
-        <v>26.9721984863281</v>
+        <v>26.9721965789795</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>27.7399997711182</v>
       </c>
       <c r="G1230" t="n">
-        <v>25.8181076049805</v>
+        <v>25.8181095123291</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>28.4400005340576</v>
       </c>
       <c r="G1232" t="n">
-        <v>26.4696102142334</v>
+        <v>26.469612121582</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1234" t="n">
-        <v>26.4323844909668</v>
+        <v>26.4323806762695</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1235" t="n">
-        <v>25.873950958252</v>
+        <v>25.8739528656006</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G1238" t="n">
-        <v>25.2969055175781</v>
+        <v>25.2969074249268</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>26.7600002288818</v>
       </c>
       <c r="G1239" t="n">
-        <v>24.906005859375</v>
+        <v>24.9060039520264</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G1241" t="n">
-        <v>23.9647331237793</v>
+        <v>23.9647350311279</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>24.9799995422363</v>
       </c>
       <c r="G1245" t="n">
-        <v>23.5129261016846</v>
+        <v>23.5129241943359</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1251" t="n">
-        <v>20.5196838378906</v>
+        <v>20.5196876525879</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>21.1800003051758</v>
       </c>
       <c r="G1252" t="n">
-        <v>19.9360980987549</v>
+        <v>19.9361000061035</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1256" t="n">
-        <v>19.9549236297607</v>
+        <v>19.9549255371094</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>21.1599998474121</v>
       </c>
       <c r="G1260" t="n">
-        <v>19.9172706604004</v>
+        <v>19.917272567749</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G1262" t="n">
-        <v>19.7854957580566</v>
+        <v>19.7854976654053</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1263" t="n">
-        <v>19.6725444793701</v>
+        <v>19.6725425720215</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>22</v>
       </c>
       <c r="G1266" t="n">
-        <v>20.7079429626465</v>
+        <v>20.7079410552979</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>22.3600006103516</v>
       </c>
       <c r="G1267" t="n">
-        <v>21.0468006134033</v>
+        <v>21.0467967987061</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>21</v>
       </c>
       <c r="G1269" t="n">
-        <v>19.7666721343994</v>
+        <v>19.7666702270508</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>21.0599994659424</v>
       </c>
       <c r="G1272" t="n">
-        <v>19.8231449127197</v>
+        <v>19.8231468200684</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G1273" t="n">
-        <v>19.7478466033936</v>
+        <v>19.7478427886963</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1276" t="n">
-        <v>17.74294090271</v>
+        <v>17.7429389953613</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1278" t="n">
-        <v>18.0159072875977</v>
+        <v>18.0159091949463</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1279" t="n">
-        <v>18.2041606903076</v>
+        <v>18.2041625976562</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1281" t="n">
-        <v>17.7147026062012</v>
+        <v>17.7146987915039</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G1283" t="n">
-        <v>17.9217834472656</v>
+        <v>17.921781539917</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1285" t="n">
-        <v>17.5264472961426</v>
+        <v>17.5264492034912</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G1289" t="n">
-        <v>16.293384552002</v>
+        <v>16.2933826446533</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1290" t="n">
-        <v>16.020414352417</v>
+        <v>16.0204162597656</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1291" t="n">
-        <v>16.0957183837891</v>
+        <v>16.0957164764404</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G1293" t="n">
-        <v>17.3852558135986</v>
+        <v>17.3852577209473</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1294" t="n">
-        <v>18.0723838806152</v>
+        <v>18.0723857879639</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>19.3099994659424</v>
       </c>
       <c r="G1295" t="n">
-        <v>18.1759243011475</v>
+        <v>18.1759223937988</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G1296" t="n">
-        <v>17.8088302612305</v>
+        <v>17.8088283538818</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34117,7 +34117,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G1298" t="n">
-        <v>16.8016681671143</v>
+        <v>16.8016700744629</v>
       </c>
       <c r="H1298" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1300" t="n">
-        <v>16.4533977508545</v>
+        <v>16.4533996582031</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1301" t="n">
-        <v>17.8370666503906</v>
+        <v>17.8370685577393</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G1303" t="n">
-        <v>17.5829238891602</v>
+        <v>17.5829257965088</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G1304" t="n">
-        <v>17.6770534515381</v>
+        <v>17.6770515441895</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>18.8299999237061</v>
       </c>
       <c r="G1305" t="n">
-        <v>17.7241134643555</v>
+        <v>17.7241153717041</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>18.75</v>
       </c>
       <c r="G1306" t="n">
-        <v>17.648811340332</v>
+        <v>17.6488151550293</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1307" t="n">
-        <v>17.2252407073975</v>
+        <v>17.2252388000488</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>20</v>
       </c>
       <c r="G1309" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>19.7900009155273</v>
       </c>
       <c r="G1310" t="n">
-        <v>18.6277351379395</v>
+        <v>18.6277332305908</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>20</v>
       </c>
       <c r="G1311" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>20</v>
       </c>
       <c r="G1312" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G1318" t="n">
-        <v>18.3830032348633</v>
+        <v>18.3830051422119</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G1319" t="n">
-        <v>18.6089115142822</v>
+        <v>18.608907699585</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G1320" t="n">
-        <v>18.2982902526855</v>
+        <v>18.2982883453369</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G1321" t="n">
-        <v>18.0347347259521</v>
+        <v>18.0347328186035</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1322" t="n">
-        <v>17.5264472961426</v>
+        <v>17.5264492034912</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1324" t="n">
-        <v>17.4887943267822</v>
+        <v>17.4887981414795</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G1325" t="n">
-        <v>16.7169551849365</v>
+        <v>16.7169570922852</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G1327" t="n">
-        <v>16.7263679504395</v>
+        <v>16.7263660430908</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1330" t="n">
-        <v>16.2839698791504</v>
+        <v>16.283971786499</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G1331" t="n">
-        <v>16.7263679504395</v>
+        <v>16.7263660430908</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1335" t="n">
-        <v>16.6134166717529</v>
+        <v>16.6134147644043</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1336" t="n">
-        <v>16.6134166717529</v>
+        <v>16.6134147644043</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1338" t="n">
-        <v>17.244068145752</v>
+        <v>17.2440662384033</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G1339" t="n">
-        <v>17.6205730438232</v>
+        <v>17.6205768585205</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1341" t="n">
-        <v>16.6793041229248</v>
+        <v>16.6793022155762</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G1342" t="n">
-        <v>16.4910488128662</v>
+        <v>16.4910507202148</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>16</v>
       </c>
       <c r="G1344" t="n">
-        <v>15.0603199005127</v>
+        <v>15.060320854187</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1347" t="n">
-        <v>13.6954793930054</v>
+        <v>13.6954784393311</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G1348" t="n">
-        <v>13.4695749282837</v>
+        <v>13.4695739746094</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G1350" t="n">
-        <v>12.9989395141602</v>
+        <v>12.9989385604858</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1351" t="n">
-        <v>13.0271768569946</v>
+        <v>13.0271759033203</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>13.2700004577637</v>
       </c>
       <c r="G1352" t="n">
-        <v>12.4906539916992</v>
+        <v>12.4906530380249</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1356" t="n">
-        <v>13.6954793930054</v>
+        <v>13.6954784393311</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G1357" t="n">
-        <v>13.7801933288574</v>
+        <v>13.7801923751831</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G1358" t="n">
-        <v>13.337797164917</v>
+        <v>13.3377952575684</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>13.8900003433228</v>
       </c>
       <c r="G1360" t="n">
-        <v>13.074239730835</v>
+        <v>13.0742406845093</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>14.0699996948242</v>
       </c>
       <c r="G1361" t="n">
-        <v>13.2436676025391</v>
+        <v>13.2436685562134</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G1362" t="n">
-        <v>13.4413347244263</v>
+        <v>13.4413356781006</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G1363" t="n">
-        <v>13.3472099304199</v>
+        <v>13.3472089767456</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G1366" t="n">
-        <v>13.300145149231</v>
+        <v>13.3001461029053</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>15.5699996948242</v>
       </c>
       <c r="G1373" t="n">
-        <v>14.6555738449097</v>
+        <v>14.6555728912354</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1377" t="n">
-        <v>14.2131776809692</v>
+        <v>14.2131767272949</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1378" t="n">
-        <v>14.4484958648682</v>
+        <v>14.4484949111938</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1382" t="n">
-        <v>16.331033706665</v>
+        <v>16.3310356140137</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>17.5</v>
       </c>
       <c r="G1386" t="n">
-        <v>16.472225189209</v>
+        <v>16.4722232818604</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="G1388" t="n">
-        <v>16.3122100830078</v>
+        <v>16.3122081756592</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1393" t="n">
-        <v>17.2252407073975</v>
+        <v>17.2252388000488</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>17.5100002288818</v>
       </c>
       <c r="G1395" t="n">
-        <v>16.4816379547119</v>
+        <v>16.4816398620605</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1397" t="n">
-        <v>17.1122894287109</v>
+        <v>17.1122875213623</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1398" t="n">
-        <v>17.601749420166</v>
+        <v>17.6017513275146</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>18.6100006103516</v>
       </c>
       <c r="G1399" t="n">
-        <v>17.5170345306396</v>
+        <v>17.5170364379883</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G1402" t="n">
-        <v>16.9240341186523</v>
+        <v>16.924036026001</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>17.8700008392334</v>
       </c>
       <c r="G1403" t="n">
-        <v>16.8204936981201</v>
+        <v>16.8204956054688</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G1404" t="n">
-        <v>16.9052104949951</v>
+        <v>16.9052085876465</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1406" t="n">
-        <v>17.36643409729</v>
+        <v>17.3664321899414</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1407" t="n">
-        <v>17.0181617736816</v>
+        <v>17.018159866333</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1408" t="n">
-        <v>16.5475292205811</v>
+        <v>16.5475273132324</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>17.5</v>
       </c>
       <c r="G1412" t="n">
-        <v>16.472225189209</v>
+        <v>16.4722232818604</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G1413" t="n">
-        <v>16.5381164550781</v>
+        <v>16.5381145477295</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1414" t="n">
-        <v>16.2651462554932</v>
+        <v>16.2651481628418</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1416" t="n">
-        <v>16.6134166717529</v>
+        <v>16.6134147644043</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1424" t="n">
-        <v>18.1665115356445</v>
+        <v>18.1665134429932</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1425" t="n">
-        <v>18.2794666290283</v>
+        <v>18.2794628143311</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G1426" t="n">
-        <v>18.3924179077148</v>
+        <v>18.3924160003662</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G1428" t="n">
-        <v>18.9760055541992</v>
+        <v>18.9760036468506</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>21.5</v>
       </c>
       <c r="G1436" t="n">
-        <v>20.2373065948486</v>
+        <v>20.2373046875</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1437" t="n">
-        <v>20.1431770324707</v>
+        <v>20.1431789398193</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>21.1800003051758</v>
       </c>
       <c r="G1438" t="n">
-        <v>19.9360980987549</v>
+        <v>19.9361000061035</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G1442" t="n">
-        <v>20.7455921173096</v>
+        <v>20.7455940246582</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>21.9599990844727</v>
       </c>
       <c r="G1443" t="n">
-        <v>20.6702880859375</v>
+        <v>20.6702899932861</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>21.7199993133545</v>
       </c>
       <c r="G1445" t="n">
-        <v>20.4443855285645</v>
+        <v>20.4443836212158</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>21.2600002288818</v>
       </c>
       <c r="G1451" t="n">
-        <v>20.0114040374756</v>
+        <v>20.0114002227783</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>20.8199996948242</v>
       </c>
       <c r="G1452" t="n">
-        <v>19.597240447998</v>
+        <v>19.5972385406494</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G1456" t="n">
-        <v>19.2772102355957</v>
+        <v>19.2772083282471</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>20</v>
       </c>
       <c r="G1457" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G1458" t="n">
-        <v>18.9948291778564</v>
+        <v>18.9948272705078</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1460" t="n">
-        <v>19.0136566162109</v>
+        <v>19.0136528015137</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38355,7 +38355,7 @@
         <v>20.5</v>
       </c>
       <c r="G1461" t="n">
-        <v>19.2960338592529</v>
+        <v>19.2960357666016</v>
       </c>
       <c r="H1461" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G1462" t="n">
-        <v>19.7101955413818</v>
+        <v>19.7101936340332</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G1463" t="n">
-        <v>19.7854957580566</v>
+        <v>19.7854976654053</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38433,7 +38433,7 @@
         <v>20.5</v>
       </c>
       <c r="G1464" t="n">
-        <v>19.2960338592529</v>
+        <v>19.2960357666016</v>
       </c>
       <c r="H1464" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G1465" t="n">
-        <v>19.4466381072998</v>
+        <v>19.4466400146484</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>19.5699996948242</v>
       </c>
       <c r="G1467" t="n">
-        <v>18.4206523895264</v>
+        <v>18.420654296875</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G1468" t="n">
-        <v>18.0347347259521</v>
+        <v>18.0347328186035</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>20</v>
       </c>
       <c r="G1470" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>19.7099990844727</v>
       </c>
       <c r="G1471" t="n">
-        <v>18.5524291992188</v>
+        <v>18.5524311065674</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1472" t="n">
-        <v>18.2794666290283</v>
+        <v>18.2794628143311</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G1474" t="n">
-        <v>18.9760055541992</v>
+        <v>18.9760036468506</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>20</v>
       </c>
       <c r="G1477" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1478" t="n">
-        <v>18.731273651123</v>
+        <v>18.7312717437744</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1483" t="n">
-        <v>18.8724613189697</v>
+        <v>18.8724632263184</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>20</v>
       </c>
       <c r="G1484" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>20</v>
       </c>
       <c r="G1487" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>20</v>
       </c>
       <c r="G1488" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>20</v>
       </c>
       <c r="G1489" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>20</v>
       </c>
       <c r="G1493" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>20</v>
       </c>
       <c r="G1494" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1498" t="n">
-        <v>18.731273651123</v>
+        <v>18.7312717437744</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1504" t="n">
-        <v>18.9665927886963</v>
+        <v>18.966588973999</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1509" t="n">
-        <v>18.3455181121826</v>
+        <v>18.3455200195312</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1510" t="n">
-        <v>18.2881870269775</v>
+        <v>18.2881889343262</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1511" t="n">
-        <v>18.0015411376953</v>
+        <v>18.0015392303467</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>19</v>
       </c>
       <c r="G1513" t="n">
-        <v>18.1544208526611</v>
+        <v>18.1544189453125</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1514" t="n">
-        <v>18.3455181121826</v>
+        <v>18.3455200195312</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>19.5</v>
       </c>
       <c r="G1515" t="n">
-        <v>18.6321678161621</v>
+        <v>18.6321659088135</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1518" t="n">
-        <v>18.2881870269775</v>
+        <v>18.2881889343262</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G1520" t="n">
-        <v>18.670389175415</v>
+        <v>18.6703872680664</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>20</v>
       </c>
       <c r="G1523" t="n">
-        <v>19.1099166870117</v>
+        <v>19.1099147796631</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1526" t="n">
-        <v>19.2532405853271</v>
+        <v>19.2532386779785</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>20</v>
       </c>
       <c r="G1527" t="n">
-        <v>19.1099166870117</v>
+        <v>19.1099147796631</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1529" t="n">
-        <v>19.492115020752</v>
+        <v>19.4921131134033</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>21</v>
       </c>
       <c r="G1530" t="n">
-        <v>20.0654106140137</v>
+        <v>20.0654125213623</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1538" t="n">
-        <v>20.2087326049805</v>
+        <v>20.2087364196777</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1545" t="n">
-        <v>19.2532405853271</v>
+        <v>19.2532386779785</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1546" t="n">
-        <v>19.2532405853271</v>
+        <v>19.2532386779785</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>20</v>
       </c>
       <c r="G1551" t="n">
-        <v>19.1099166870117</v>
+        <v>19.1099147796631</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1553" t="n">
-        <v>18.976146697998</v>
+        <v>18.9761486053467</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1557" t="n">
-        <v>19.1576881408691</v>
+        <v>19.1576900482178</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G1559" t="n">
-        <v>18.5175075531006</v>
+        <v>18.517505645752</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1561" t="n">
-        <v>18.0588684082031</v>
+        <v>18.0588703155518</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1562" t="n">
-        <v>18.0588684082031</v>
+        <v>18.0588703155518</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G1564" t="n">
-        <v>18.4983978271484</v>
+        <v>18.4983997344971</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1565" t="n">
-        <v>18.441068649292</v>
+        <v>18.4410667419434</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1566" t="n">
-        <v>18.4792881011963</v>
+        <v>18.4792861938477</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>19</v>
       </c>
       <c r="G1567" t="n">
-        <v>18.1544208526611</v>
+        <v>18.1544189453125</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1568" t="n">
-        <v>16.6638469696045</v>
+        <v>16.6638450622559</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1569" t="n">
-        <v>15.8039016723633</v>
+        <v>15.8038997650146</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G1577" t="n">
-        <v>16.3580875396729</v>
+        <v>16.3580894470215</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1580" t="n">
-        <v>16.4918556213379</v>
+        <v>16.4918575286865</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1582" t="n">
-        <v>16.4154167175293</v>
+        <v>16.4154186248779</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G1583" t="n">
-        <v>16.3580875396729</v>
+        <v>16.3580894470215</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G1584" t="n">
-        <v>16.4727458953857</v>
+        <v>16.4727478027344</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1585" t="n">
-        <v>16.549186706543</v>
+        <v>16.5491847991943</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1591" t="n">
-        <v>16.4154167175293</v>
+        <v>16.4154186248779</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1595" t="n">
-        <v>15.9567813873291</v>
+        <v>15.9567794799805</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1596" t="n">
-        <v>15.2497129440308</v>
+        <v>15.2497119903564</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G1604" t="n">
-        <v>14.5426464080811</v>
+        <v>14.5426454544067</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G1605" t="n">
-        <v>14.3897657394409</v>
+        <v>14.3897666931152</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G1606" t="n">
-        <v>14.179557800293</v>
+        <v>14.1795568466187</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1608" t="n">
-        <v>14.4662055969238</v>
+        <v>14.4662065505981</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G1610" t="n">
-        <v>13.7209186553955</v>
+        <v>13.7209196090698</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G1611" t="n">
-        <v>13.5489311218262</v>
+        <v>13.5489301681519</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G1612" t="n">
-        <v>13.4533796310425</v>
+        <v>13.4533805847168</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1613" t="n">
-        <v>13.434271812439</v>
+        <v>13.4342708587646</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1615" t="n">
-        <v>13.434271812439</v>
+        <v>13.4342708587646</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1618" t="n">
-        <v>13.2813901901245</v>
+        <v>13.2813911437988</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G1620" t="n">
-        <v>13.9311285018921</v>
+        <v>13.9311275482178</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1624" t="n">
-        <v>13.7591381072998</v>
+        <v>13.7591390609741</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G1625" t="n">
-        <v>13.9311285018921</v>
+        <v>13.9311275482178</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G1630" t="n">
-        <v>14.1222267150879</v>
+        <v>14.1222276687622</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G1631" t="n">
-        <v>14.5999755859375</v>
+        <v>14.5999746322632</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G1634" t="n">
-        <v>15.0777235031128</v>
+        <v>15.0777225494385</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G1636" t="n">
-        <v>15.6510190963745</v>
+        <v>15.6510200500488</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1640" t="n">
-        <v>16.9313831329346</v>
+        <v>16.9313850402832</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>17.5</v>
       </c>
       <c r="G1642" t="n">
-        <v>16.7211742401123</v>
+        <v>16.7211761474609</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1643" t="n">
-        <v>17.0078239440918</v>
+        <v>17.0078258514404</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1647" t="n">
-        <v>16.4154167175293</v>
+        <v>16.4154186248779</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1648" t="n">
-        <v>16.7976150512695</v>
+        <v>16.7976169586182</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1650" t="n">
-        <v>16.6638469696045</v>
+        <v>16.6638450622559</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>18</v>
       </c>
       <c r="G1651" t="n">
-        <v>17.1989231109619</v>
+        <v>17.1989250183105</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1652" t="n">
-        <v>17.2371444702148</v>
+        <v>17.2371463775635</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1655" t="n">
-        <v>16.7785053253174</v>
+        <v>16.7785034179688</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1656" t="n">
-        <v>16.9887161254883</v>
+        <v>16.9887142181396</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G1659" t="n">
-        <v>17.2180347442627</v>
+        <v>17.2180328369141</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1660" t="n">
-        <v>17.2753639221191</v>
+        <v>17.2753620147705</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G1664" t="n">
-        <v>18.1353073120117</v>
+        <v>18.1353092193604</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1665" t="n">
-        <v>18.3455181121826</v>
+        <v>18.3455200195312</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1666" t="n">
-        <v>18.3455181121826</v>
+        <v>18.3455200195312</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>19.5</v>
       </c>
       <c r="G1667" t="n">
-        <v>18.6321678161621</v>
+        <v>18.6321659088135</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>19.5</v>
       </c>
       <c r="G1671" t="n">
-        <v>18.6321678161621</v>
+        <v>18.6321659088135</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G1674" t="n">
-        <v>17.8868789672852</v>
+        <v>17.8868808746338</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>19</v>
       </c>
       <c r="G1676" t="n">
-        <v>18.1544208526611</v>
+        <v>18.1544189453125</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G1677" t="n">
-        <v>18.0970916748047</v>
+        <v>18.0970897674561</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1680" t="n">
-        <v>18.039758682251</v>
+        <v>18.0397567749023</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1683" t="n">
-        <v>16.8740539550781</v>
+        <v>16.8740558624268</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G1684" t="n">
-        <v>17.0842628479004</v>
+        <v>17.084264755249</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1688" t="n">
-        <v>17.3326930999756</v>
+        <v>17.332691192627</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1690" t="n">
-        <v>18.0015411376953</v>
+        <v>18.0015392303467</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1700" t="n">
-        <v>17.3900241851807</v>
+        <v>17.390022277832</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>19.5</v>
       </c>
       <c r="G1706" t="n">
-        <v>18.6321678161621</v>
+        <v>18.6321659088135</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1708" t="n">
-        <v>18.039758682251</v>
+        <v>18.0397567749023</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G1711" t="n">
-        <v>18.307300567627</v>
+        <v>18.3072986602783</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G1714" t="n">
-        <v>17.5237922668457</v>
+        <v>17.5237941741943</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G1719" t="n">
-        <v>17.8868789672852</v>
+        <v>17.8868808746338</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1726" t="n">
-        <v>17.0078239440918</v>
+        <v>17.0078258514404</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1727" t="n">
-        <v>16.7976150512695</v>
+        <v>16.7976169586182</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1729" t="n">
-        <v>16.8167266845703</v>
+        <v>16.8167247772217</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>18</v>
       </c>
       <c r="G1733" t="n">
-        <v>17.1989231109619</v>
+        <v>17.1989250183105</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>17.5</v>
       </c>
       <c r="G1735" t="n">
-        <v>16.7211742401123</v>
+        <v>16.7211761474609</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1736" t="n">
-        <v>16.8740539550781</v>
+        <v>16.8740558624268</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1739" t="n">
-        <v>16.4918556213379</v>
+        <v>16.4918575286865</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1740" t="n">
-        <v>15.8994483947754</v>
+        <v>15.8994493484497</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1741" t="n">
-        <v>15.7847890853882</v>
+        <v>15.7847900390625</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G1744" t="n">
-        <v>15.6510190963745</v>
+        <v>15.6510200500488</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G1749" t="n">
-        <v>14.8675136566162</v>
+        <v>14.8675146102905</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G1753" t="n">
-        <v>15.5554714202881</v>
+        <v>15.5554723739624</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G1754" t="n">
-        <v>15.5936908721924</v>
+        <v>15.5936918258667</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1756" t="n">
-        <v>15.6319122314453</v>
+        <v>15.6319103240967</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1758" t="n">
-        <v>15.7847890853882</v>
+        <v>15.7847900390625</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1760" t="n">
-        <v>15.8994483947754</v>
+        <v>15.8994493484497</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1761" t="n">
-        <v>15.9185590744019</v>
+        <v>15.9185600280762</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1763" t="n">
-        <v>15.9185590744019</v>
+        <v>15.9185600280762</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1764" t="n">
-        <v>16.4536380767822</v>
+        <v>16.4536361694336</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1765" t="n">
-        <v>16.6447353363037</v>
+        <v>16.6447372436523</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1766" t="n">
-        <v>16.8740539550781</v>
+        <v>16.8740558624268</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1767" t="n">
-        <v>16.8167266845703</v>
+        <v>16.8167247772217</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1772" t="n">
-        <v>16.7389602661133</v>
+        <v>16.7389583587646</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46493,7 +46493,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1774" t="n">
-        <v>17.3610820770264</v>
+        <v>17.361083984375</v>
       </c>
       <c r="H1774" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G1775" t="n">
-        <v>17.1472263336182</v>
+        <v>17.1472282409668</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>18</v>
       </c>
       <c r="G1777" t="n">
-        <v>17.4971694946289</v>
+        <v>17.4971714019775</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G1778" t="n">
-        <v>17.7110233306885</v>
+        <v>17.7110252380371</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G1786" t="n">
-        <v>17.4388484954834</v>
+        <v>17.4388465881348</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1787" t="n">
-        <v>16.9528160095215</v>
+        <v>16.9528141021729</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>18</v>
       </c>
       <c r="G1788" t="n">
-        <v>17.4971694946289</v>
+        <v>17.4971714019775</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G1792" t="n">
-        <v>19.3829765319824</v>
+        <v>19.3829784393311</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1794" t="n">
-        <v>20.5591735839844</v>
+        <v>20.559175491333</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>22.25</v>
       </c>
       <c r="G1796" t="n">
-        <v>21.6284484863281</v>
+        <v>21.6284465789795</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1801" t="n">
-        <v>22.0658779144287</v>
+        <v>22.0658760070801</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1804" t="n">
-        <v>22.2602882385254</v>
+        <v>22.260290145874</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47299,7 +47299,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1805" t="n">
-        <v>22.2116870880127</v>
+        <v>22.2116851806641</v>
       </c>
       <c r="H1805" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1806" t="n">
-        <v>22.454704284668</v>
+        <v>22.4547023773193</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1808" t="n">
-        <v>22.0658779144287</v>
+        <v>22.0658760070801</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>22.5</v>
       </c>
       <c r="G1816" t="n">
-        <v>21.8714618682861</v>
+        <v>21.8714637756348</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>22.5</v>
       </c>
       <c r="G1820" t="n">
-        <v>21.8714618682861</v>
+        <v>21.8714637756348</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1822" t="n">
-        <v>20.5591735839844</v>
+        <v>20.559175491333</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47949,7 +47949,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1830" t="n">
-        <v>19.8301277160645</v>
+        <v>19.8301258087158</v>
       </c>
       <c r="H1830" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1831" t="n">
-        <v>19.8301277160645</v>
+        <v>19.8301258087158</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1832" t="n">
-        <v>19.8301277160645</v>
+        <v>19.8301258087158</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G1841" t="n">
-        <v>20.4619674682617</v>
+        <v>20.4619693756104</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48313,7 +48313,7 @@
         <v>21.25</v>
       </c>
       <c r="G1844" t="n">
-        <v>20.6563835144043</v>
+        <v>20.6563816070557</v>
       </c>
       <c r="H1844" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>22.5</v>
       </c>
       <c r="G1850" t="n">
-        <v>21.8714618682861</v>
+        <v>21.8714637756348</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1851" t="n">
-        <v>22.0658779144287</v>
+        <v>22.0658760070801</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>22.5</v>
       </c>
       <c r="G1857" t="n">
-        <v>21.8714618682861</v>
+        <v>21.8714637756348</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>21.75</v>
       </c>
       <c r="G1858" t="n">
-        <v>21.1424160003662</v>
+        <v>21.1424140930176</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48703,7 +48703,7 @@
         <v>21.75</v>
       </c>
       <c r="G1859" t="n">
-        <v>21.1424160003662</v>
+        <v>21.1424140930176</v>
       </c>
       <c r="H1859" t="s">
         <v>8</v>
@@ -48885,7 +48885,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1866" t="n">
-        <v>22.0658779144287</v>
+        <v>22.0658760070801</v>
       </c>
       <c r="H1866" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1870" t="n">
-        <v>22.0658779144287</v>
+        <v>22.0658760070801</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>22.5</v>
       </c>
       <c r="G1871" t="n">
-        <v>21.8714618682861</v>
+        <v>21.8714637756348</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1874" t="n">
-        <v>22.0658779144287</v>
+        <v>22.0658760070801</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49119,7 +49119,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1875" t="n">
-        <v>22.2116870880127</v>
+        <v>22.2116851806641</v>
       </c>
       <c r="H1875" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1876" t="n">
-        <v>21.9686717987061</v>
+        <v>21.9686698913574</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1884" t="n">
-        <v>20.9479999542236</v>
+        <v>20.9480018615723</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49431,7 +49431,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1887" t="n">
-        <v>19.8301277160645</v>
+        <v>19.8301258087158</v>
       </c>
       <c r="H1887" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1888" t="n">
-        <v>19.8301277160645</v>
+        <v>19.8301258087158</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49587,7 +49587,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1893" t="n">
-        <v>19.8301277160645</v>
+        <v>19.8301258087158</v>
       </c>
       <c r="H1893" t="s">
         <v>8</v>
@@ -49795,7 +49795,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1901" t="n">
-        <v>18.9163837432861</v>
+        <v>18.9163856506348</v>
       </c>
       <c r="H1901" t="s">
         <v>8</v>
@@ -49821,7 +49821,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1902" t="n">
-        <v>19.305212020874</v>
+        <v>19.3052139282227</v>
       </c>
       <c r="H1902" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1906" t="n">
-        <v>20.5591735839844</v>
+        <v>20.559175491333</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -49951,7 +49951,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G1907" t="n">
-        <v>20.4619674682617</v>
+        <v>20.4619693756104</v>
       </c>
       <c r="H1907" t="s">
         <v>8</v>
@@ -49977,7 +49977,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G1908" t="n">
-        <v>20.4619674682617</v>
+        <v>20.4619693756104</v>
       </c>
       <c r="H1908" t="s">
         <v>8</v>
@@ -50055,7 +50055,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1911" t="n">
-        <v>20.267557144165</v>
+        <v>20.2675552368164</v>
       </c>
       <c r="H1911" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1914" t="n">
-        <v>19.8301277160645</v>
+        <v>19.8301258087158</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G1919" t="n">
-        <v>19.0913562774658</v>
+        <v>19.0913581848145</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50289,7 +50289,7 @@
         <v>19</v>
       </c>
       <c r="G1920" t="n">
-        <v>18.4692363739014</v>
+        <v>18.4692344665527</v>
       </c>
       <c r="H1920" t="s">
         <v>8</v>
@@ -50419,7 +50419,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1925" t="n">
-        <v>19.305212020874</v>
+        <v>19.3052139282227</v>
       </c>
       <c r="H1925" t="s">
         <v>8</v>
@@ -50497,7 +50497,7 @@
         <v>19.5</v>
       </c>
       <c r="G1928" t="n">
-        <v>18.9552688598633</v>
+        <v>18.9552669525146</v>
       </c>
       <c r="H1928" t="s">
         <v>8</v>
@@ -50575,7 +50575,7 @@
         <v>19</v>
       </c>
       <c r="G1931" t="n">
-        <v>18.4692363739014</v>
+        <v>18.4692344665527</v>
       </c>
       <c r="H1931" t="s">
         <v>8</v>
@@ -50653,7 +50653,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1934" t="n">
-        <v>18.022087097168</v>
+        <v>18.0220851898193</v>
       </c>
       <c r="H1934" t="s">
         <v>8</v>
@@ -50705,7 +50705,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1936" t="n">
-        <v>18.3720283508301</v>
+        <v>18.3720302581787</v>
       </c>
       <c r="H1936" t="s">
         <v>8</v>
@@ -50913,7 +50913,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G1944" t="n">
-        <v>17.8665542602539</v>
+        <v>17.8665561676025</v>
       </c>
       <c r="H1944" t="s">
         <v>8</v>
@@ -51017,7 +51017,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G1948" t="n">
-        <v>17.7110233306885</v>
+        <v>17.7110252380371</v>
       </c>
       <c r="H1948" t="s">
         <v>8</v>
@@ -51069,7 +51069,7 @@
         <v>18</v>
       </c>
       <c r="G1950" t="n">
-        <v>17.4971694946289</v>
+        <v>17.4971714019775</v>
       </c>
       <c r="H1950" t="s">
         <v>8</v>
@@ -51095,7 +51095,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G1951" t="n">
-        <v>17.5166130065918</v>
+        <v>17.5166110992432</v>
       </c>
       <c r="H1951" t="s">
         <v>8</v>
@@ -51121,7 +51121,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1952" t="n">
-        <v>17.6527004241943</v>
+        <v>17.652702331543</v>
       </c>
       <c r="H1952" t="s">
         <v>8</v>
@@ -51147,7 +51147,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G1953" t="n">
-        <v>17.7110233306885</v>
+        <v>17.7110252380371</v>
       </c>
       <c r="H1953" t="s">
         <v>8</v>
@@ -51329,7 +51329,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1960" t="n">
-        <v>16.7389602661133</v>
+        <v>16.7389583587646</v>
       </c>
       <c r="H1960" t="s">
         <v>8</v>
@@ -51511,7 +51511,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1967" t="n">
-        <v>16.7778415679932</v>
+        <v>16.7778434753418</v>
       </c>
       <c r="H1967" t="s">
         <v>8</v>
@@ -51563,7 +51563,7 @@
         <v>16.5</v>
       </c>
       <c r="G1969" t="n">
-        <v>16.0390720367432</v>
+        <v>16.0390739440918</v>
       </c>
       <c r="H1969" t="s">
         <v>8</v>
@@ -51667,7 +51667,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1973" t="n">
-        <v>15.241979598999</v>
+        <v>15.2419805526733</v>
       </c>
       <c r="H1973" t="s">
         <v>8</v>
@@ -51693,7 +51693,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G1974" t="n">
-        <v>15.8252191543579</v>
+        <v>15.8252201080322</v>
       </c>
       <c r="H1974" t="s">
         <v>8</v>
@@ -51797,7 +51797,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G1978" t="n">
-        <v>15.7280130386353</v>
+        <v>15.7280120849609</v>
       </c>
       <c r="H1978" t="s">
         <v>8</v>
@@ -51849,7 +51849,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1980" t="n">
-        <v>15.2225389480591</v>
+        <v>15.2225379943848</v>
       </c>
       <c r="H1980" t="s">
         <v>8</v>
@@ -51953,7 +51953,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G1984" t="n">
-        <v>14.4254455566406</v>
+        <v>14.4254446029663</v>
       </c>
       <c r="H1984" t="s">
         <v>8</v>
@@ -52109,7 +52109,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1990" t="n">
-        <v>13.5117034912109</v>
+        <v>13.5117044448853</v>
       </c>
       <c r="H1990" t="s">
         <v>8</v>
@@ -52239,7 +52239,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1995" t="n">
-        <v>13.8033227920532</v>
+        <v>13.8033237457275</v>
       </c>
       <c r="H1995" t="s">
         <v>8</v>
@@ -52343,7 +52343,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G1999" t="n">
-        <v>14.2504739761353</v>
+        <v>14.2504730224609</v>
       </c>
       <c r="H1999" t="s">
         <v>8</v>
@@ -52369,7 +52369,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G2000" t="n">
-        <v>13.8810882568359</v>
+        <v>13.8810892105103</v>
       </c>
       <c r="H2000" t="s">
         <v>8</v>
@@ -52447,7 +52447,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G2003" t="n">
-        <v>15.3197450637817</v>
+        <v>15.3197460174561</v>
       </c>
       <c r="H2003" t="s">
         <v>8</v>
@@ -52499,7 +52499,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2005" t="n">
-        <v>15.3586273193359</v>
+        <v>15.3586282730103</v>
       </c>
       <c r="H2005" t="s">
         <v>8</v>
@@ -52525,7 +52525,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G2006" t="n">
-        <v>15.241979598999</v>
+        <v>15.2419805526733</v>
       </c>
       <c r="H2006" t="s">
         <v>8</v>
@@ -52551,7 +52551,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2007" t="n">
-        <v>14.969801902771</v>
+        <v>14.9698009490967</v>
       </c>
       <c r="H2007" t="s">
         <v>8</v>
@@ -52577,7 +52577,7 @@
         <v>16.5</v>
       </c>
       <c r="G2008" t="n">
-        <v>16.0390720367432</v>
+        <v>16.0390739440918</v>
       </c>
       <c r="H2008" t="s">
         <v>8</v>
@@ -61758,6 +61758,32 @@
         <v>30.0499992370605</v>
       </c>
       <c r="H2361" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2362">
+      <c r="A2362" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B2362" t="n">
+        <v>21417</v>
+      </c>
+      <c r="C2362" t="n">
+        <v>30.7000007629395</v>
+      </c>
+      <c r="D2362" t="n">
+        <v>29.6499996185303</v>
+      </c>
+      <c r="E2362" t="n">
+        <v>30.1000003814697</v>
+      </c>
+      <c r="F2362" t="n">
+        <v>30.2000007629395</v>
+      </c>
+      <c r="G2362" t="n">
+        <v>30.2000007629395</v>
+      </c>
+      <c r="H2362" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/WIIT.MI.xlsx
+++ b/data/WIIT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2" t="n">
-        <v>4.49076509475708</v>
+        <v>4.49076461791992</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G3" t="n">
-        <v>4.49076509475708</v>
+        <v>4.49076461791992</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>5.125</v>
       </c>
       <c r="G4" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>5.125</v>
       </c>
       <c r="G5" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>5.125</v>
       </c>
       <c r="G6" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>5.125</v>
       </c>
       <c r="G7" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>5.125</v>
       </c>
       <c r="G8" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>5.125</v>
       </c>
       <c r="G9" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>5.125</v>
       </c>
       <c r="G10" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>5.125</v>
       </c>
       <c r="G11" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>5.125</v>
       </c>
       <c r="G12" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>5.125</v>
       </c>
       <c r="G13" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>5.125</v>
       </c>
       <c r="G14" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>5.125</v>
       </c>
       <c r="G15" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>5.125</v>
       </c>
       <c r="G16" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>5.125</v>
       </c>
       <c r="G17" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>5.125</v>
       </c>
       <c r="G18" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>5.125</v>
       </c>
       <c r="G19" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>5.125</v>
       </c>
       <c r="G20" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>5.125</v>
       </c>
       <c r="G21" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>5.125</v>
       </c>
       <c r="G22" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>5.125</v>
       </c>
       <c r="G23" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>5.125</v>
       </c>
       <c r="G24" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>5.125</v>
       </c>
       <c r="G25" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>5.125</v>
       </c>
       <c r="G26" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>5.125</v>
       </c>
       <c r="G27" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>5.125</v>
       </c>
       <c r="G28" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>5.125</v>
       </c>
       <c r="G29" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>5.125</v>
       </c>
       <c r="G30" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>5.125</v>
       </c>
       <c r="G31" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>5.125</v>
       </c>
       <c r="G32" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>5.125</v>
       </c>
       <c r="G33" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>5.125</v>
       </c>
       <c r="G34" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>5.125</v>
       </c>
       <c r="G35" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>5.125</v>
       </c>
       <c r="G36" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>5.125</v>
       </c>
       <c r="G37" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>5.125</v>
       </c>
       <c r="G38" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>5.125</v>
       </c>
       <c r="G39" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>5.125</v>
       </c>
       <c r="G40" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>5.125</v>
       </c>
       <c r="G41" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>5.125</v>
       </c>
       <c r="G42" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>5.125</v>
       </c>
       <c r="G43" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>5.125</v>
       </c>
       <c r="G44" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>5.125</v>
       </c>
       <c r="G45" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>5.125</v>
       </c>
       <c r="G46" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>5.125</v>
       </c>
       <c r="G47" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>5.125</v>
       </c>
       <c r="G48" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>5.125</v>
       </c>
       <c r="G49" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>5.125</v>
       </c>
       <c r="G50" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>5.125</v>
       </c>
       <c r="G51" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>5.125</v>
       </c>
       <c r="G52" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>5.125</v>
       </c>
       <c r="G53" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>5.125</v>
       </c>
       <c r="G54" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>5.125</v>
       </c>
       <c r="G55" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>5.125</v>
       </c>
       <c r="G56" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>5.125</v>
       </c>
       <c r="G57" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>5.125</v>
       </c>
       <c r="G58" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>5.125</v>
       </c>
       <c r="G59" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>5.125</v>
       </c>
       <c r="G60" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>5.125</v>
       </c>
       <c r="G61" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>5.125</v>
       </c>
       <c r="G62" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>5.125</v>
       </c>
       <c r="G63" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>5.125</v>
       </c>
       <c r="G64" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>5.125</v>
       </c>
       <c r="G65" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>5.125</v>
       </c>
       <c r="G66" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>5.125</v>
       </c>
       <c r="G67" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>5.125</v>
       </c>
       <c r="G68" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>5.125</v>
       </c>
       <c r="G69" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>5.125</v>
       </c>
       <c r="G70" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5.125</v>
       </c>
       <c r="G71" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>5.125</v>
       </c>
       <c r="G72" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>5.125</v>
       </c>
       <c r="G73" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>5.125</v>
       </c>
       <c r="G74" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>5.125</v>
       </c>
       <c r="G75" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>5.125</v>
       </c>
       <c r="G76" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>5.125</v>
       </c>
       <c r="G77" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>5.125</v>
       </c>
       <c r="G78" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>5.125</v>
       </c>
       <c r="G79" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>5.125</v>
       </c>
       <c r="G80" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>5.125</v>
       </c>
       <c r="G81" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>5.125</v>
       </c>
       <c r="G82" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>5.125</v>
       </c>
       <c r="G83" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>5.125</v>
       </c>
       <c r="G84" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>5.125</v>
       </c>
       <c r="G85" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>5.125</v>
       </c>
       <c r="G86" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>5.125</v>
       </c>
       <c r="G87" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>5.125</v>
       </c>
       <c r="G88" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>5.125</v>
       </c>
       <c r="G89" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>5.125</v>
       </c>
       <c r="G90" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>5.125</v>
       </c>
       <c r="G91" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>5.125</v>
       </c>
       <c r="G92" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>5.125</v>
       </c>
       <c r="G93" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>5.125</v>
       </c>
       <c r="G94" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>5.125</v>
       </c>
       <c r="G95" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>5.125</v>
       </c>
       <c r="G96" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>5.125</v>
       </c>
       <c r="G97" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>5.125</v>
       </c>
       <c r="G98" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>5.125</v>
       </c>
       <c r="G99" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>5.125</v>
       </c>
       <c r="G100" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>5.125</v>
       </c>
       <c r="G101" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>5.125</v>
       </c>
       <c r="G102" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>5.125</v>
       </c>
       <c r="G103" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>5.125</v>
       </c>
       <c r="G104" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>5.125</v>
       </c>
       <c r="G105" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>5.125</v>
       </c>
       <c r="G106" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>5.125</v>
       </c>
       <c r="G107" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>5.125</v>
       </c>
       <c r="G108" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>5.125</v>
       </c>
       <c r="G109" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>5.125</v>
       </c>
       <c r="G110" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>5.125</v>
       </c>
       <c r="G111" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>5.125</v>
       </c>
       <c r="G112" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>5.125</v>
       </c>
       <c r="G113" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>5.125</v>
       </c>
       <c r="G114" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>5.125</v>
       </c>
       <c r="G115" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>5.125</v>
       </c>
       <c r="G116" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>5.125</v>
       </c>
       <c r="G117" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>5.125</v>
       </c>
       <c r="G118" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>5.125</v>
       </c>
       <c r="G119" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>5.125</v>
       </c>
       <c r="G120" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>5.125</v>
       </c>
       <c r="G121" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>5.125</v>
       </c>
       <c r="G122" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>5.125</v>
       </c>
       <c r="G123" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>5.125</v>
       </c>
       <c r="G124" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>5.125</v>
       </c>
       <c r="G125" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>5.125</v>
       </c>
       <c r="G126" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.125</v>
       </c>
       <c r="G127" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>5.125</v>
       </c>
       <c r="G128" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>5.125</v>
       </c>
       <c r="G129" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>5.125</v>
       </c>
       <c r="G130" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>5.125</v>
       </c>
       <c r="G131" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>5.125</v>
       </c>
       <c r="G132" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>5.125</v>
       </c>
       <c r="G133" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>5.125</v>
       </c>
       <c r="G134" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>5.125</v>
       </c>
       <c r="G135" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>5.125</v>
       </c>
       <c r="G136" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>5.125</v>
       </c>
       <c r="G137" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>5.125</v>
       </c>
       <c r="G138" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>5.125</v>
       </c>
       <c r="G139" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>5.125</v>
       </c>
       <c r="G140" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>5.125</v>
       </c>
       <c r="G141" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>5.125</v>
       </c>
       <c r="G142" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>5.125</v>
       </c>
       <c r="G143" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>5.125</v>
       </c>
       <c r="G144" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>5.125</v>
       </c>
       <c r="G145" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>5.125</v>
       </c>
       <c r="G146" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>5.125</v>
       </c>
       <c r="G147" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>5.125</v>
       </c>
       <c r="G148" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>5.125</v>
       </c>
       <c r="G149" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>5.125</v>
       </c>
       <c r="G150" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>5.125</v>
       </c>
       <c r="G151" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>5.125</v>
       </c>
       <c r="G152" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>5.125</v>
       </c>
       <c r="G153" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>5.125</v>
       </c>
       <c r="G154" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>5.125</v>
       </c>
       <c r="G155" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>5.125</v>
       </c>
       <c r="G156" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>5.125</v>
       </c>
       <c r="G157" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>5.125</v>
       </c>
       <c r="G158" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>5.125</v>
       </c>
       <c r="G159" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>5.125</v>
       </c>
       <c r="G160" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>5.125</v>
       </c>
       <c r="G161" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>5.125</v>
       </c>
       <c r="G162" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>5.125</v>
       </c>
       <c r="G163" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>5.125</v>
       </c>
       <c r="G164" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>5.125</v>
       </c>
       <c r="G165" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>5.125</v>
       </c>
       <c r="G166" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>5.125</v>
       </c>
       <c r="G167" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>5.125</v>
       </c>
       <c r="G168" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>5.125</v>
       </c>
       <c r="G169" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>5.125</v>
       </c>
       <c r="G170" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>5.125</v>
       </c>
       <c r="G171" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>5.125</v>
       </c>
       <c r="G172" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>5.125</v>
       </c>
       <c r="G173" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>5.125</v>
       </c>
       <c r="G174" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>5.125</v>
       </c>
       <c r="G175" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>5.125</v>
       </c>
       <c r="G176" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>5.125</v>
       </c>
       <c r="G177" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>5.125</v>
       </c>
       <c r="G178" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>5.125</v>
       </c>
       <c r="G179" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>5.125</v>
       </c>
       <c r="G180" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>5.125</v>
       </c>
       <c r="G181" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>5.125</v>
       </c>
       <c r="G182" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>5.125</v>
       </c>
       <c r="G183" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>5.125</v>
       </c>
       <c r="G184" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>5.125</v>
       </c>
       <c r="G185" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>5.125</v>
       </c>
       <c r="G186" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>5.125</v>
       </c>
       <c r="G187" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>5.125</v>
       </c>
       <c r="G188" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>5.125</v>
       </c>
       <c r="G189" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>5.125</v>
       </c>
       <c r="G190" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>5.125</v>
       </c>
       <c r="G191" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>5.125</v>
       </c>
       <c r="G192" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>5.125</v>
       </c>
       <c r="G193" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>5.125</v>
       </c>
       <c r="G194" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>5.125</v>
       </c>
       <c r="G195" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>5.125</v>
       </c>
       <c r="G196" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>5.125</v>
       </c>
       <c r="G197" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>5.125</v>
       </c>
       <c r="G198" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>5.125</v>
       </c>
       <c r="G199" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>5.125</v>
       </c>
       <c r="G200" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>5.125</v>
       </c>
       <c r="G201" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>5.125</v>
       </c>
       <c r="G202" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>5.125</v>
       </c>
       <c r="G203" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>5.125</v>
       </c>
       <c r="G204" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>5.125</v>
       </c>
       <c r="G205" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>5.125</v>
       </c>
       <c r="G206" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>5.125</v>
       </c>
       <c r="G207" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>5.125</v>
       </c>
       <c r="G208" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>5.125</v>
       </c>
       <c r="G209" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>5.125</v>
       </c>
       <c r="G210" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>5.125</v>
       </c>
       <c r="G211" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>5.125</v>
       </c>
       <c r="G212" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>5.125</v>
       </c>
       <c r="G213" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>5.125</v>
       </c>
       <c r="G214" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>5.125</v>
       </c>
       <c r="G215" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>5.125</v>
       </c>
       <c r="G216" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>5.125</v>
       </c>
       <c r="G217" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>5.125</v>
       </c>
       <c r="G218" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>5.125</v>
       </c>
       <c r="G219" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>5.125</v>
       </c>
       <c r="G220" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>5.125</v>
       </c>
       <c r="G221" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>5.125</v>
       </c>
       <c r="G222" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>5.125</v>
       </c>
       <c r="G223" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>5.125</v>
       </c>
       <c r="G224" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>5.125</v>
       </c>
       <c r="G225" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>5.125</v>
       </c>
       <c r="G226" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>5.125</v>
       </c>
       <c r="G227" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>5.125</v>
       </c>
       <c r="G228" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>5.125</v>
       </c>
       <c r="G229" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>5.125</v>
       </c>
       <c r="G230" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>5.125</v>
       </c>
       <c r="G231" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>5.125</v>
       </c>
       <c r="G232" t="n">
-        <v>4.51277780532837</v>
+        <v>4.51277828216553</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G275" t="n">
-        <v>4.4125337600708</v>
+        <v>4.41253328323364</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G276" t="n">
-        <v>4.52888870239258</v>
+        <v>4.52888822555542</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G277" t="n">
-        <v>4.49308729171753</v>
+        <v>4.49308824539185</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G278" t="n">
-        <v>4.44833564758301</v>
+        <v>4.44833517074585</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>5</v>
       </c>
       <c r="G279" t="n">
-        <v>4.47518634796143</v>
+        <v>4.47518682479858</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>5</v>
       </c>
       <c r="G280" t="n">
-        <v>4.47518634796143</v>
+        <v>4.47518682479858</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>5</v>
       </c>
       <c r="G281" t="n">
-        <v>4.47518634796143</v>
+        <v>4.47518682479858</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G282" t="n">
-        <v>4.49308729171753</v>
+        <v>4.49308824539185</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G283" t="n">
-        <v>4.43938541412354</v>
+        <v>4.43938493728638</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G284" t="n">
-        <v>4.49308729171753</v>
+        <v>4.49308824539185</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>5</v>
       </c>
       <c r="G285" t="n">
-        <v>4.47518634796143</v>
+        <v>4.47518682479858</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G286" t="n">
-        <v>4.44833564758301</v>
+        <v>4.44833517074585</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G287" t="n">
-        <v>4.44833564758301</v>
+        <v>4.44833517074585</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G288" t="n">
-        <v>4.44833564758301</v>
+        <v>4.44833517074585</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G289" t="n">
-        <v>4.44833564758301</v>
+        <v>4.44833517074585</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>5</v>
       </c>
       <c r="G290" t="n">
-        <v>4.47518634796143</v>
+        <v>4.47518682479858</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G294" t="n">
-        <v>4.58259105682373</v>
+        <v>4.58259010314941</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G297" t="n">
-        <v>4.52888870239258</v>
+        <v>4.52888822555542</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G300" t="n">
-        <v>4.49308729171753</v>
+        <v>4.49308824539185</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G301" t="n">
-        <v>4.49308729171753</v>
+        <v>4.49308824539185</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>4.49308729171753</v>
+        <v>4.49308824539185</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G303" t="n">
-        <v>4.4304347038269</v>
+        <v>4.43043422698975</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G304" t="n">
-        <v>4.4304347038269</v>
+        <v>4.43043422698975</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G305" t="n">
-        <v>4.38568353652954</v>
+        <v>4.38568305969238</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G306" t="n">
-        <v>4.34093141555786</v>
+        <v>4.3409309387207</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G309" t="n">
-        <v>4.33198070526123</v>
+        <v>4.33198022842407</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G310" t="n">
-        <v>4.33198070526123</v>
+        <v>4.33198022842407</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G311" t="n">
-        <v>4.27827882766724</v>
+        <v>4.27827930450439</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G312" t="n">
-        <v>4.27827882766724</v>
+        <v>4.27827930450439</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>4.45728588104248</v>
+        <v>4.45728635787964</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>4.43938541412354</v>
+        <v>4.43938493728638</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G315" t="n">
-        <v>4.36778211593628</v>
+        <v>4.36778163909912</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G316" t="n">
-        <v>4.33198070526123</v>
+        <v>4.33198022842407</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G317" t="n">
-        <v>4.32302951812744</v>
+        <v>4.3230299949646</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G318" t="n">
-        <v>4.32302951812744</v>
+        <v>4.3230299949646</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G319" t="n">
-        <v>4.35883140563965</v>
+        <v>4.35883188247681</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G320" t="n">
-        <v>4.14402294158936</v>
+        <v>4.14402341842651</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G322" t="n">
-        <v>4.32302951812744</v>
+        <v>4.3230299949646</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G325" t="n">
-        <v>4.1798243522644</v>
+        <v>4.17982387542725</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G326" t="n">
-        <v>4.0903205871582</v>
+        <v>4.09032106399536</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G327" t="n">
-        <v>4.04556846618652</v>
+        <v>4.04556894302368</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G328" t="n">
-        <v>3.90236258506775</v>
+        <v>3.90236282348633</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G330" t="n">
-        <v>4.14402294158936</v>
+        <v>4.14402341842651</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G331" t="n">
-        <v>4.08137083053589</v>
+        <v>4.08136940002441</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G332" t="n">
-        <v>4.13507175445557</v>
+        <v>4.13507270812988</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G333" t="n">
-        <v>4.1798243522644</v>
+        <v>4.17982387542725</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G334" t="n">
-        <v>4.14402294158936</v>
+        <v>4.14402341842651</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G335" t="n">
-        <v>4.11717176437378</v>
+        <v>4.11717128753662</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>4.5</v>
       </c>
       <c r="G337" t="n">
-        <v>4.02766752243042</v>
+        <v>4.02766799926758</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G339" t="n">
-        <v>3.8844621181488</v>
+        <v>3.88446187973022</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G340" t="n">
-        <v>3.90236258506775</v>
+        <v>3.90236282348633</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G341" t="n">
-        <v>3.86656141281128</v>
+        <v>3.86656093597412</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>3.76810765266418</v>
+        <v>3.76810693740845</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G343" t="n">
-        <v>3.84866070747375</v>
+        <v>3.8486602306366</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G344" t="n">
-        <v>3.78600835800171</v>
+        <v>3.78600788116455</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G346" t="n">
-        <v>3.66965317726135</v>
+        <v>3.66965270042419</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G347" t="n">
-        <v>3.60700082778931</v>
+        <v>3.60700058937073</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G350" t="n">
-        <v>3.57119941711426</v>
+        <v>3.5711989402771</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G353" t="n">
-        <v>3.43694353103638</v>
+        <v>3.4369432926178</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G355" t="n">
-        <v>3.44589376449585</v>
+        <v>3.44589352607727</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G357" t="n">
-        <v>3.39219164848328</v>
+        <v>3.3921914100647</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G365" t="n">
-        <v>3.08787894248962</v>
+        <v>3.08787870407104</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G366" t="n">
-        <v>3.07892847061157</v>
+        <v>3.07892870903015</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G367" t="n">
-        <v>3.09682941436768</v>
+        <v>3.09682893753052</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G368" t="n">
-        <v>3.10577940940857</v>
+        <v>3.10577964782715</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G371" t="n">
-        <v>3.22213435173035</v>
+        <v>3.22213411331177</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G372" t="n">
-        <v>3.22213435173035</v>
+        <v>3.22213411331177</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G373" t="n">
-        <v>2.93572235107422</v>
+        <v>2.9357225894928</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G374" t="n">
-        <v>2.85516929626465</v>
+        <v>2.85516905784607</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G377" t="n">
-        <v>2.95362305641174</v>
+        <v>2.95362329483032</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>3.25</v>
       </c>
       <c r="G379" t="n">
-        <v>2.90887117385864</v>
+        <v>2.90887141227722</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>3.25</v>
       </c>
       <c r="G381" t="n">
-        <v>2.90887117385864</v>
+        <v>2.90887141227722</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G382" t="n">
-        <v>2.95362305641174</v>
+        <v>2.95362329483032</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G383" t="n">
-        <v>2.95362305641174</v>
+        <v>2.95362329483032</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G384" t="n">
-        <v>3.00732493400574</v>
+        <v>3.00732517242432</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G385" t="n">
-        <v>2.95362305641174</v>
+        <v>2.95362329483032</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>3.25</v>
       </c>
       <c r="G387" t="n">
-        <v>2.90887117385864</v>
+        <v>2.90887141227722</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G390" t="n">
-        <v>2.81041765213013</v>
+        <v>2.81041741371155</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G391" t="n">
-        <v>2.84621906280518</v>
+        <v>2.8462188243866</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G393" t="n">
-        <v>2.89992094039917</v>
+        <v>2.89992117881775</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G394" t="n">
-        <v>2.94467282295227</v>
+        <v>2.94467306137085</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G397" t="n">
-        <v>3.17738223075867</v>
+        <v>3.17738270759583</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G398" t="n">
-        <v>3.17738223075867</v>
+        <v>3.17738270759583</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G399" t="n">
-        <v>3.26688671112061</v>
+        <v>3.26688647270203</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>3.22213435173035</v>
+        <v>3.22213411331177</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G401" t="n">
-        <v>3.26688671112061</v>
+        <v>3.26688647270203</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G402" t="n">
-        <v>3.26688671112061</v>
+        <v>3.26688647270203</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>3.75</v>
       </c>
       <c r="G404" t="n">
-        <v>3.35638976097107</v>
+        <v>3.35638999938965</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G405" t="n">
-        <v>3.39219164848328</v>
+        <v>3.3921914100647</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G408" t="n">
-        <v>3.66965317726135</v>
+        <v>3.66965270042419</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G413" t="n">
-        <v>3.5890998840332</v>
+        <v>3.58909964561462</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G414" t="n">
-        <v>3.63385152816772</v>
+        <v>3.6338517665863</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G415" t="n">
-        <v>3.66070246696472</v>
+        <v>3.6607027053833</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G416" t="n">
-        <v>3.63385152816772</v>
+        <v>3.6338517665863</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G417" t="n">
-        <v>3.49064564704895</v>
+        <v>3.49064588546753</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G419" t="n">
-        <v>3.66965317726135</v>
+        <v>3.66965270042419</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G421" t="n">
-        <v>3.66965317726135</v>
+        <v>3.66965270042419</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G422" t="n">
-        <v>3.66965317726135</v>
+        <v>3.66965270042419</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G423" t="n">
-        <v>3.5890998840332</v>
+        <v>3.58909964561462</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G424" t="n">
-        <v>3.63385152816772</v>
+        <v>3.6338517665863</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G425" t="n">
-        <v>3.62490105628967</v>
+        <v>3.62490153312683</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G426" t="n">
-        <v>3.63385152816772</v>
+        <v>3.6338517665863</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G428" t="n">
-        <v>3.63385152816772</v>
+        <v>3.6338517665863</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G429" t="n">
-        <v>3.5890998840332</v>
+        <v>3.58909964561462</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G430" t="n">
-        <v>3.69650435447693</v>
+        <v>3.69650459289551</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G432" t="n">
-        <v>3.78600835800171</v>
+        <v>3.78600788116455</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G433" t="n">
-        <v>3.90236258506775</v>
+        <v>3.90236282348633</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G434" t="n">
-        <v>4.0903205871582</v>
+        <v>4.09032106399536</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G435" t="n">
-        <v>4.14402294158936</v>
+        <v>4.14402341842651</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G436" t="n">
-        <v>4.09927129745483</v>
+        <v>4.09927082061768</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G437" t="n">
-        <v>4.09927129745483</v>
+        <v>4.09927082061768</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>4.75</v>
       </c>
       <c r="G438" t="n">
-        <v>4.2514271736145</v>
+        <v>4.25142621994019</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G439" t="n">
-        <v>4.11717176437378</v>
+        <v>4.11717128753662</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>4.4304347038269</v>
+        <v>4.43043422698975</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G444" t="n">
-        <v>4.14402294158936</v>
+        <v>4.14402341842651</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>4.5</v>
       </c>
       <c r="G445" t="n">
-        <v>4.02766752243042</v>
+        <v>4.02766799926758</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G446" t="n">
-        <v>3.90236258506775</v>
+        <v>3.90236282348633</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G447" t="n">
-        <v>3.92026352882385</v>
+        <v>3.92026329040527</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G448" t="n">
-        <v>3.76810765266418</v>
+        <v>3.76810693740845</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G449" t="n">
-        <v>3.77705669403076</v>
+        <v>3.7770574092865</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G450" t="n">
-        <v>3.66965317726135</v>
+        <v>3.66965270042419</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G452" t="n">
-        <v>3.92921376228333</v>
+        <v>3.9292140007019</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G453" t="n">
-        <v>4.00976800918579</v>
+        <v>4.00976753234863</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G454" t="n">
-        <v>4.14402294158936</v>
+        <v>4.14402341842651</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G455" t="n">
-        <v>4.13507175445557</v>
+        <v>4.13507270812988</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G456" t="n">
-        <v>4.05451917648315</v>
+        <v>4.05451965332031</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G457" t="n">
-        <v>4.20667505264282</v>
+        <v>4.20667552947998</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G459" t="n">
-        <v>4.26037788391113</v>
+        <v>4.26037836074829</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G460" t="n">
-        <v>4.34093141555786</v>
+        <v>4.3409309387207</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G461" t="n">
-        <v>4.40358304977417</v>
+        <v>4.40358352661133</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G462" t="n">
-        <v>4.44833564758301</v>
+        <v>4.44833517074585</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G463" t="n">
-        <v>4.32302951812744</v>
+        <v>4.3230299949646</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G466" t="n">
-        <v>4.38568353652954</v>
+        <v>4.38568305969238</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G469" t="n">
-        <v>4.21562671661377</v>
+        <v>4.21562576293945</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G470" t="n">
-        <v>4.22457551956177</v>
+        <v>4.22457599639893</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G471" t="n">
-        <v>4.20667505264282</v>
+        <v>4.20667552947998</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G472" t="n">
-        <v>4.3891773223877</v>
+        <v>4.38917779922485</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G473" t="n">
-        <v>4.28880023956299</v>
+        <v>4.2888011932373</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G474" t="n">
-        <v>4.37092733383179</v>
+        <v>4.37092685699463</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G476" t="n">
-        <v>4.28880023956299</v>
+        <v>4.2888011932373</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G481" t="n">
-        <v>4.27055168151855</v>
+        <v>4.27055072784424</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G482" t="n">
-        <v>4.26142644882202</v>
+        <v>4.26142597198486</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G483" t="n">
-        <v>4.28880023956299</v>
+        <v>4.2888011932373</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G484" t="n">
-        <v>4.2157998085022</v>
+        <v>4.21580028533936</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G485" t="n">
-        <v>4.28880023956299</v>
+        <v>4.2888011932373</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G486" t="n">
-        <v>4.35267734527588</v>
+        <v>4.35267686843872</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G487" t="n">
-        <v>4.36180257797241</v>
+        <v>4.36180305480957</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G488" t="n">
-        <v>4.36180257797241</v>
+        <v>4.36180305480957</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G490" t="n">
-        <v>4.28880023956299</v>
+        <v>4.2888011932373</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G491" t="n">
-        <v>4.28880023956299</v>
+        <v>4.2888011932373</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>4.75</v>
       </c>
       <c r="G492" t="n">
-        <v>4.33442687988281</v>
+        <v>4.3344259262085</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>4.75</v>
       </c>
       <c r="G493" t="n">
-        <v>4.33442687988281</v>
+        <v>4.3344259262085</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>4.75</v>
       </c>
       <c r="G498" t="n">
-        <v>4.33442687988281</v>
+        <v>4.3344259262085</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>4.75</v>
       </c>
       <c r="G499" t="n">
-        <v>4.33442687988281</v>
+        <v>4.3344259262085</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G501" t="n">
-        <v>4.37092733383179</v>
+        <v>4.37092685699463</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>4.75</v>
       </c>
       <c r="G503" t="n">
-        <v>4.33442687988281</v>
+        <v>4.3344259262085</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G504" t="n">
-        <v>4.297926902771</v>
+        <v>4.29792642593384</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G505" t="n">
-        <v>4.297926902771</v>
+        <v>4.29792642593384</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G506" t="n">
-        <v>4.297926902771</v>
+        <v>4.29792642593384</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G510" t="n">
-        <v>4.32530164718628</v>
+        <v>4.32530212402344</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G512" t="n">
-        <v>4.32530164718628</v>
+        <v>4.32530212402344</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>4.75</v>
       </c>
       <c r="G514" t="n">
-        <v>4.33442687988281</v>
+        <v>4.3344259262085</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G516" t="n">
-        <v>4.28880023956299</v>
+        <v>4.2888011932373</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G519" t="n">
-        <v>4.59905481338501</v>
+        <v>4.59905529022217</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G522" t="n">
-        <v>4.48042869567871</v>
+        <v>4.48042917251587</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G524" t="n">
-        <v>4.63555574417114</v>
+        <v>4.63555526733398</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>4.92755889892578</v>
+        <v>4.92755842208862</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G531" t="n">
-        <v>4.94580936431885</v>
+        <v>4.94580888748169</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G535" t="n">
-        <v>5.20131254196167</v>
+        <v>5.20131206512451</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G536" t="n">
-        <v>5.27431392669678</v>
+        <v>5.27431344985962</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G537" t="n">
-        <v>5.18306159973145</v>
+        <v>5.1830620765686</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G541" t="n">
-        <v>5.00055980682373</v>
+        <v>5.00056028366089</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G545" t="n">
-        <v>5.05531072616577</v>
+        <v>5.05531120300293</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G546" t="n">
-        <v>5.14656114578247</v>
+        <v>5.14656162261963</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G547" t="n">
-        <v>5.14656114578247</v>
+        <v>5.14656162261963</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G548" t="n">
-        <v>5.20131254196167</v>
+        <v>5.20131206512451</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G550" t="n">
-        <v>5.12831115722656</v>
+        <v>5.1283106803894</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G551" t="n">
-        <v>5.18306159973145</v>
+        <v>5.1830620765686</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G556" t="n">
-        <v>5.32906436920166</v>
+        <v>5.3290638923645</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G559" t="n">
-        <v>5.60281753540039</v>
+        <v>5.60281705856323</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G561" t="n">
-        <v>5.49331521987915</v>
+        <v>5.49331569671631</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G565" t="n">
-        <v>5.32906436920166</v>
+        <v>5.3290638923645</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G568" t="n">
-        <v>5.27431392669678</v>
+        <v>5.27431344985962</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G571" t="n">
-        <v>5.32906436920166</v>
+        <v>5.3290638923645</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G575" t="n">
-        <v>5.40206480026245</v>
+        <v>5.40206432342529</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G576" t="n">
-        <v>5.31081342697144</v>
+        <v>5.31081390380859</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G578" t="n">
-        <v>5.36556482315063</v>
+        <v>5.36556386947632</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G581" t="n">
-        <v>5.45681571960449</v>
+        <v>5.45681524276733</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G582" t="n">
-        <v>5.49331521987915</v>
+        <v>5.49331569671631</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G583" t="n">
-        <v>5.43856573104858</v>
+        <v>5.43856525421143</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G584" t="n">
-        <v>5.43856573104858</v>
+        <v>5.43856525421143</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G585" t="n">
-        <v>5.43856573104858</v>
+        <v>5.43856525421143</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G589" t="n">
-        <v>5.43856573104858</v>
+        <v>5.43856525421143</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G590" t="n">
-        <v>5.43856573104858</v>
+        <v>5.43856525421143</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G594" t="n">
-        <v>5.43856573104858</v>
+        <v>5.43856525421143</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G598" t="n">
-        <v>5.45681571960449</v>
+        <v>5.45681524276733</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G599" t="n">
-        <v>5.51156616210938</v>
+        <v>5.51156663894653</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G600" t="n">
-        <v>5.49331521987915</v>
+        <v>5.49331569671631</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G603" t="n">
-        <v>5.51156616210938</v>
+        <v>5.51156663894653</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G605" t="n">
-        <v>5.51156616210938</v>
+        <v>5.51156663894653</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G606" t="n">
-        <v>5.69406795501709</v>
+        <v>5.69406843185425</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G609" t="n">
-        <v>6.29632568359375</v>
+        <v>6.29632520675659</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G610" t="n">
-        <v>6.27807569503784</v>
+        <v>6.27807521820068</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G611" t="n">
-        <v>6.40582704544067</v>
+        <v>6.40582656860352</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G612" t="n">
-        <v>6.49707746505737</v>
+        <v>6.49707794189453</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G614" t="n">
-        <v>6.49707746505737</v>
+        <v>6.49707794189453</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G615" t="n">
-        <v>6.47882699966431</v>
+        <v>6.47882747650146</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G616" t="n">
-        <v>6.49707746505737</v>
+        <v>6.49707794189453</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G618" t="n">
-        <v>6.69783020019531</v>
+        <v>6.69783115386963</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G619" t="n">
-        <v>7.00808382034302</v>
+        <v>7.00808334350586</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>8</v>
       </c>
       <c r="G622" t="n">
-        <v>7.30008840560913</v>
+        <v>7.30008745193481</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G623" t="n">
-        <v>7.39133882522583</v>
+        <v>7.39133977890015</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G624" t="n">
-        <v>7.62859153747559</v>
+        <v>7.62859201431274</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>8.5</v>
       </c>
       <c r="G625" t="n">
-        <v>7.75634336471558</v>
+        <v>7.75634384155273</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G627" t="n">
-        <v>7.84759521484375</v>
+        <v>7.84759378433228</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G628" t="n">
-        <v>7.88409566879272</v>
+        <v>7.88409376144409</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G629" t="n">
-        <v>7.84759521484375</v>
+        <v>7.84759378433228</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G630" t="n">
-        <v>7.93884515762329</v>
+        <v>7.93884611129761</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>8.5</v>
       </c>
       <c r="G631" t="n">
-        <v>7.75634336471558</v>
+        <v>7.75634384155273</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G632" t="n">
-        <v>7.93884515762329</v>
+        <v>7.93884611129761</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G634" t="n">
-        <v>8.43159961700439</v>
+        <v>8.43160057067871</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G635" t="n">
-        <v>8.57760047912598</v>
+        <v>8.57760238647461</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G636" t="n">
-        <v>8.65060329437256</v>
+        <v>8.65060424804688</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G638" t="n">
-        <v>8.65060329437256</v>
+        <v>8.65060424804688</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G639" t="n">
-        <v>8.26734924316406</v>
+        <v>8.26735019683838</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G640" t="n">
-        <v>8.26734924316406</v>
+        <v>8.26735019683838</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G641" t="n">
-        <v>8.55935192108154</v>
+        <v>8.55935096740723</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G643" t="n">
-        <v>8.57760047912598</v>
+        <v>8.57760238647461</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G644" t="n">
-        <v>8.43159961700439</v>
+        <v>8.43160057067871</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G645" t="n">
-        <v>8.37685203552246</v>
+        <v>8.37685108184814</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G646" t="n">
-        <v>8.41335105895996</v>
+        <v>8.41335201263428</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G647" t="n">
-        <v>8.13959789276123</v>
+        <v>8.13959693908691</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G648" t="n">
-        <v>8.30384826660156</v>
+        <v>8.3038501739502</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G649" t="n">
-        <v>8.52285289764404</v>
+        <v>8.52285194396973</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G650" t="n">
-        <v>8.37685203552246</v>
+        <v>8.37685108184814</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G651" t="n">
-        <v>8.55935192108154</v>
+        <v>8.55935096740723</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G652" t="n">
-        <v>8.54110336303711</v>
+        <v>8.54110145568848</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G653" t="n">
-        <v>8.54110336303711</v>
+        <v>8.54110145568848</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G654" t="n">
-        <v>8.86960601806641</v>
+        <v>8.86960506439209</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G655" t="n">
-        <v>9.08860874176025</v>
+        <v>9.08860969543457</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G656" t="n">
-        <v>9.17073535919189</v>
+        <v>9.17073440551758</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G662" t="n">
-        <v>9.67261600494385</v>
+        <v>9.67261695861816</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G663" t="n">
-        <v>9.53573894500732</v>
+        <v>9.53573989868164</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G665" t="n">
-        <v>9.53573894500732</v>
+        <v>9.53573989868164</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G666" t="n">
-        <v>9.62699127197266</v>
+        <v>9.62699031829834</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>10.75</v>
       </c>
       <c r="G667" t="n">
-        <v>9.80949211120605</v>
+        <v>9.80949401855469</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G669" t="n">
-        <v>9.53573894500732</v>
+        <v>9.53573989868164</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G673" t="n">
-        <v>9.03385925292969</v>
+        <v>9.03385734558105</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G676" t="n">
-        <v>9.67261600494385</v>
+        <v>9.67261695861816</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G683" t="n">
-        <v>9.67261600494385</v>
+        <v>9.67261695861816</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G684" t="n">
-        <v>9.67261600494385</v>
+        <v>9.67261695861816</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G685" t="n">
-        <v>9.67261600494385</v>
+        <v>9.67261695861816</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>10.75</v>
       </c>
       <c r="G686" t="n">
-        <v>9.80949211120605</v>
+        <v>9.80949401855469</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G687" t="n">
-        <v>9.71824169158936</v>
+        <v>9.71824073791504</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G688" t="n">
-        <v>8.90610599517822</v>
+        <v>8.90610694885254</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G689" t="n">
-        <v>9.26198577880859</v>
+        <v>9.26198673248291</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G690" t="n">
-        <v>9.62699127197266</v>
+        <v>9.62699031829834</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G692" t="n">
-        <v>8.99735736846924</v>
+        <v>8.99735641479492</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G693" t="n">
-        <v>8.77835464477539</v>
+        <v>8.77835559844971</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G694" t="n">
-        <v>8.97910690307617</v>
+        <v>8.97910785675049</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G696" t="n">
-        <v>8.55935192108154</v>
+        <v>8.55935096740723</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G697" t="n">
-        <v>7.84759521484375</v>
+        <v>7.84759378433228</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G698" t="n">
-        <v>7.61034250259399</v>
+        <v>7.61034107208252</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>8</v>
       </c>
       <c r="G700" t="n">
-        <v>7.30008840560913</v>
+        <v>7.30008745193481</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>7.5</v>
       </c>
       <c r="G701" t="n">
-        <v>6.84383201599121</v>
+        <v>6.84383153915405</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G702" t="n">
-        <v>7.263587474823</v>
+        <v>7.26358699798584</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G707" t="n">
-        <v>7.50084066390991</v>
+        <v>7.50084018707275</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G709" t="n">
-        <v>7.62859153747559</v>
+        <v>7.62859201431274</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G711" t="n">
-        <v>7.64684247970581</v>
+        <v>7.64684152603149</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G712" t="n">
-        <v>7.7745943069458</v>
+        <v>7.77459478378296</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>8.5</v>
       </c>
       <c r="G713" t="n">
-        <v>7.75634336471558</v>
+        <v>7.75634384155273</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G714" t="n">
-        <v>7.88409566879272</v>
+        <v>7.88409376144409</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G716" t="n">
-        <v>8.32209968566895</v>
+        <v>8.32209873199463</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G717" t="n">
-        <v>8.30384826660156</v>
+        <v>8.3038501739502</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G720" t="n">
-        <v>9.03385925292969</v>
+        <v>9.03385734558105</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G721" t="n">
-        <v>9.05210781097412</v>
+        <v>9.05210876464844</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G723" t="n">
-        <v>8.92435550689697</v>
+        <v>8.92435741424561</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>9.05210781097412</v>
+        <v>9.05210876464844</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G725" t="n">
-        <v>9.08860874176025</v>
+        <v>9.08860969543457</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G726" t="n">
-        <v>9.08860874176025</v>
+        <v>9.08860969543457</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G728" t="n">
-        <v>9.53573894500732</v>
+        <v>9.53573989868164</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G729" t="n">
-        <v>9.53573894500732</v>
+        <v>9.53573989868164</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>9.67261600494385</v>
+        <v>9.67261695861816</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G732" t="n">
-        <v>9.67261600494385</v>
+        <v>9.67261695861816</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G734" t="n">
-        <v>10.4026250839233</v>
+        <v>10.402624130249</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G735" t="n">
-        <v>10.356390953064</v>
+        <v>10.3563899993896</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G737" t="n">
-        <v>10.2176904678345</v>
+        <v>10.2176885604858</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G738" t="n">
-        <v>10.3101568222046</v>
+        <v>10.3101577758789</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>11</v>
       </c>
       <c r="G739" t="n">
-        <v>10.1714563369751</v>
+        <v>10.1714553833008</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G741" t="n">
-        <v>10.3101568222046</v>
+        <v>10.3101577758789</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G742" t="n">
-        <v>9.9865198135376</v>
+        <v>9.98651885986328</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G744" t="n">
-        <v>9.9865198135376</v>
+        <v>9.98651885986328</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>10.25</v>
       </c>
       <c r="G747" t="n">
-        <v>9.47794818878174</v>
+        <v>9.47794723510742</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G748" t="n">
-        <v>9.80158519744873</v>
+        <v>9.80158615112305</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G749" t="n">
-        <v>9.9865198135376</v>
+        <v>9.98651885986328</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G750" t="n">
-        <v>9.80158519744873</v>
+        <v>9.80158615112305</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G751" t="n">
-        <v>9.80158519744873</v>
+        <v>9.80158615112305</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G752" t="n">
-        <v>9.61664867401123</v>
+        <v>9.61664962768555</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G753" t="n">
-        <v>9.80158519744873</v>
+        <v>9.80158615112305</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G754" t="n">
-        <v>9.9865198135376</v>
+        <v>9.98651885986328</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G756" t="n">
-        <v>10.356390953064</v>
+        <v>10.3563899993896</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G757" t="n">
-        <v>10.3101568222046</v>
+        <v>10.3101577758789</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G761" t="n">
-        <v>10.356390953064</v>
+        <v>10.3563899993896</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G762" t="n">
-        <v>10.356390953064</v>
+        <v>10.3563899993896</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>11</v>
       </c>
       <c r="G764" t="n">
-        <v>10.1714563369751</v>
+        <v>10.1714553833008</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G766" t="n">
-        <v>10.5413265228271</v>
+        <v>10.5413255691528</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G767" t="n">
-        <v>10.5413265228271</v>
+        <v>10.5413255691528</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G768" t="n">
-        <v>11.0036649703979</v>
+        <v>11.0036668777466</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G770" t="n">
-        <v>11.9745769500732</v>
+        <v>11.9745759963989</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G771" t="n">
-        <v>12.7605533599854</v>
+        <v>12.760552406311</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>13.25</v>
       </c>
       <c r="G774" t="n">
-        <v>12.2519817352295</v>
+        <v>12.2519798278809</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G775" t="n">
-        <v>12.1132793426514</v>
+        <v>12.1132783889771</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G777" t="n">
-        <v>12.1595115661621</v>
+        <v>12.1595125198364</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G778" t="n">
-        <v>11.9745769500732</v>
+        <v>11.9745759963989</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G779" t="n">
-        <v>11.8821096420288</v>
+        <v>11.8821105957031</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G782" t="n">
-        <v>11.8821096420288</v>
+        <v>11.8821105957031</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G783" t="n">
-        <v>11.9283418655396</v>
+        <v>11.9283437728882</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G785" t="n">
-        <v>11.9745769500732</v>
+        <v>11.9745759963989</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>11.8821096420288</v>
+        <v>11.8821105957031</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G790" t="n">
-        <v>11.9283418655396</v>
+        <v>11.9283437728882</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G791" t="n">
-        <v>11.743408203125</v>
+        <v>11.7434072494507</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G792" t="n">
-        <v>11.6509399414062</v>
+        <v>11.6509408950806</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G793" t="n">
-        <v>11.5122375488281</v>
+        <v>11.5122385025024</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G794" t="n">
-        <v>11.6509399414062</v>
+        <v>11.6509408950806</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G795" t="n">
-        <v>11.4660043716431</v>
+        <v>11.4660034179688</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G798" t="n">
-        <v>11.419771194458</v>
+        <v>11.4197702407837</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G800" t="n">
-        <v>11.37353515625</v>
+        <v>11.3735361099243</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G801" t="n">
-        <v>11.1423683166504</v>
+        <v>11.1423692703247</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G803" t="n">
-        <v>11.1423683166504</v>
+        <v>11.1423692703247</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G808" t="n">
-        <v>11.37353515625</v>
+        <v>11.3735361099243</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G810" t="n">
-        <v>11.419771194458</v>
+        <v>11.4197702407837</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>12.5</v>
       </c>
       <c r="G811" t="n">
-        <v>11.5584726333618</v>
+        <v>11.5584716796875</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>12.5</v>
       </c>
       <c r="G813" t="n">
-        <v>11.5584726333618</v>
+        <v>11.5584716796875</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G814" t="n">
-        <v>11.6509399414062</v>
+        <v>11.6509408950806</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G815" t="n">
-        <v>11.6509399414062</v>
+        <v>11.6509408950806</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G817" t="n">
-        <v>11.6509399414062</v>
+        <v>11.6509408950806</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G818" t="n">
-        <v>11.6509399414062</v>
+        <v>11.6509408950806</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G820" t="n">
-        <v>11.4660043716431</v>
+        <v>11.4660034179688</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G824" t="n">
-        <v>11.6509399414062</v>
+        <v>11.6509408950806</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G825" t="n">
-        <v>11.9745769500732</v>
+        <v>11.9745759963989</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G829" t="n">
-        <v>13.1304235458374</v>
+        <v>13.1304244995117</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G830" t="n">
-        <v>13.4540605545044</v>
+        <v>13.4540615081787</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G831" t="n">
-        <v>13.7314643859863</v>
+        <v>13.7314653396606</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G832" t="n">
-        <v>14.1938037872314</v>
+        <v>14.1938047409058</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>14.1938037872314</v>
+        <v>14.1938047409058</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G835" t="n">
-        <v>15.3496503829956</v>
+        <v>15.3496513366699</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>16.25</v>
       </c>
       <c r="G836" t="n">
-        <v>15.0260143280029</v>
+        <v>15.0260133743286</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G837" t="n">
-        <v>16.3667964935303</v>
+        <v>16.3667984008789</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G839" t="n">
-        <v>16.2743301391602</v>
+        <v>16.2743282318115</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G842" t="n">
-        <v>16.0431613922119</v>
+        <v>16.0431594848633</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>17</v>
       </c>
       <c r="G843" t="n">
-        <v>15.7195224761963</v>
+        <v>15.7195234298706</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G844" t="n">
-        <v>15.3496503829956</v>
+        <v>15.3496513366699</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G849" t="n">
-        <v>15.2109498977661</v>
+        <v>15.2109489440918</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G850" t="n">
-        <v>15.6270542144775</v>
+        <v>15.6270523071289</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G853" t="n">
-        <v>15.8119897842407</v>
+        <v>15.811990737915</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>14.9797801971436</v>
+        <v>14.9797821044922</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G857" t="n">
-        <v>14.7486095428467</v>
+        <v>14.748610496521</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G860" t="n">
-        <v>13.5465297698975</v>
+        <v>13.5465288162231</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G861" t="n">
-        <v>13.3615951538086</v>
+        <v>13.3615942001343</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G863" t="n">
-        <v>13.0379571914673</v>
+        <v>13.0379552841187</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G864" t="n">
-        <v>13.1304235458374</v>
+        <v>13.1304244995117</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G865" t="n">
-        <v>13.3615951538086</v>
+        <v>13.3615942001343</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>14.5</v>
       </c>
       <c r="G866" t="n">
-        <v>13.4078283309937</v>
+        <v>13.407829284668</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G867" t="n">
-        <v>15.3496503829956</v>
+        <v>15.3496513366699</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G870" t="n">
-        <v>15.3496503829956</v>
+        <v>15.3496513366699</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G871" t="n">
-        <v>14.9797801971436</v>
+        <v>14.9797821044922</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G872" t="n">
-        <v>15.0722465515137</v>
+        <v>15.0722455978394</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G873" t="n">
-        <v>14.7486095428467</v>
+        <v>14.748610496521</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G874" t="n">
-        <v>14.5174417495728</v>
+        <v>14.5174407958984</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>16</v>
       </c>
       <c r="G875" t="n">
-        <v>14.7948446273804</v>
+        <v>14.7948436737061</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G877" t="n">
-        <v>14.2862720489502</v>
+        <v>14.2862710952759</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G880" t="n">
-        <v>14.4712066650391</v>
+        <v>14.4712085723877</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G882" t="n">
-        <v>14.1938037872314</v>
+        <v>14.1938047409058</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>13.5465297698975</v>
+        <v>13.5465288162231</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G886" t="n">
-        <v>13.8239316940308</v>
+        <v>13.8239307403564</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G887" t="n">
-        <v>13.4540605545044</v>
+        <v>13.4540615081787</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G888" t="n">
-        <v>13.3153591156006</v>
+        <v>13.3153581619263</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>13.5927639007568</v>
+        <v>13.5927629470825</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G892" t="n">
-        <v>13.5002956390381</v>
+        <v>13.5002965927124</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>16</v>
       </c>
       <c r="G895" t="n">
-        <v>14.7948446273804</v>
+        <v>14.7948436737061</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G896" t="n">
-        <v>14.5174417495728</v>
+        <v>14.5174407958984</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>16</v>
       </c>
       <c r="G898" t="n">
-        <v>14.7948446273804</v>
+        <v>14.7948436737061</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G900" t="n">
-        <v>14.8873128890991</v>
+        <v>14.8873119354248</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G902" t="n">
-        <v>15.0722465515137</v>
+        <v>15.0722455978394</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G904" t="n">
-        <v>15.2109498977661</v>
+        <v>15.2109489440918</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G905" t="n">
-        <v>15.0722465515137</v>
+        <v>15.0722455978394</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G906" t="n">
-        <v>15.5345859527588</v>
+        <v>15.5345878601074</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G907" t="n">
-        <v>15.3496503829956</v>
+        <v>15.3496513366699</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G908" t="n">
-        <v>15.1184825897217</v>
+        <v>15.118483543396</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>16</v>
       </c>
       <c r="G910" t="n">
-        <v>14.7948446273804</v>
+        <v>14.7948436737061</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G911" t="n">
-        <v>14.7486095428467</v>
+        <v>14.748610496521</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G919" t="n">
-        <v>14.5174417495728</v>
+        <v>14.5174407958984</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G923" t="n">
-        <v>13.5927639007568</v>
+        <v>13.5927629470825</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G926" t="n">
-        <v>14.2862720489502</v>
+        <v>14.2862710952759</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G931" t="n">
-        <v>15.0722465515137</v>
+        <v>15.0722455978394</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G932" t="n">
-        <v>14.8873128890991</v>
+        <v>14.8873119354248</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>16</v>
       </c>
       <c r="G934" t="n">
-        <v>14.7948446273804</v>
+        <v>14.7948436737061</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G936" t="n">
-        <v>14.9797801971436</v>
+        <v>14.9797821044922</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G938" t="n">
-        <v>14.7486095428467</v>
+        <v>14.748610496521</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G939" t="n">
-        <v>14.5174417495728</v>
+        <v>14.5174407958984</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G942" t="n">
-        <v>14.2862720489502</v>
+        <v>14.2862710952759</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G947" t="n">
-        <v>14.6099090576172</v>
+        <v>14.6099100112915</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G951" t="n">
-        <v>13.5465297698975</v>
+        <v>13.5465288162231</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G958" t="n">
-        <v>14.1938037872314</v>
+        <v>14.1938047409058</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G961" t="n">
-        <v>13.5465297698975</v>
+        <v>13.5465288162231</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G962" t="n">
-        <v>13.3615951538086</v>
+        <v>13.3615942001343</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G963" t="n">
-        <v>13.2691259384155</v>
+        <v>13.2691268920898</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G964" t="n">
-        <v>13.4540605545044</v>
+        <v>13.4540615081787</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G967" t="n">
-        <v>14.4712066650391</v>
+        <v>14.4712085723877</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G968" t="n">
-        <v>14.2862720489502</v>
+        <v>14.2862710952759</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G969" t="n">
-        <v>14.2770252227783</v>
+        <v>14.277024269104</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G971" t="n">
-        <v>14.6099090576172</v>
+        <v>14.6099100112915</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G974" t="n">
-        <v>14.4804534912109</v>
+        <v>14.4804544448853</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G976" t="n">
-        <v>14.5359344482422</v>
+        <v>14.5359354019165</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>16</v>
       </c>
       <c r="G978" t="n">
-        <v>14.7948446273804</v>
+        <v>14.7948436737061</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>16</v>
       </c>
       <c r="G979" t="n">
-        <v>14.7948446273804</v>
+        <v>14.7948436737061</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G980" t="n">
-        <v>14.5174417495728</v>
+        <v>14.5174407958984</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>15.8599996566772</v>
       </c>
       <c r="G981" t="n">
-        <v>14.6653881072998</v>
+        <v>14.6653900146484</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G983" t="n">
-        <v>14.9243001937866</v>
+        <v>14.924298286438</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G984" t="n">
-        <v>15.2017040252686</v>
+        <v>15.2017030715942</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>16</v>
       </c>
       <c r="G985" t="n">
-        <v>14.7948446273804</v>
+        <v>14.7948436737061</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G989" t="n">
-        <v>15.0722465515137</v>
+        <v>15.0722455978394</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G990" t="n">
-        <v>14.5359344482422</v>
+        <v>14.5359354019165</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G992" t="n">
-        <v>14.9612865447998</v>
+        <v>14.9612855911255</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G993" t="n">
-        <v>14.9612865447998</v>
+        <v>14.9612855911255</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G998" t="n">
-        <v>14.9845552444458</v>
+        <v>14.9845542907715</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1000" t="n">
-        <v>15.1706972122192</v>
+        <v>15.1706962585449</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1003" t="n">
-        <v>14.9845552444458</v>
+        <v>14.9845542907715</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>16.4699993133545</v>
       </c>
       <c r="G1004" t="n">
-        <v>15.3289213180542</v>
+        <v>15.3289184570312</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>17.3120002746582</v>
       </c>
       <c r="G1005" t="n">
-        <v>16.1125831604004</v>
+        <v>16.112585067749</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26577,7 +26577,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1008" t="n">
-        <v>17.9628524780273</v>
+        <v>17.9628505706787</v>
       </c>
       <c r="H1008" t="s">
         <v>8</v>
@@ -26629,7 +26629,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1010" t="n">
-        <v>17.9628524780273</v>
+        <v>17.9628505706787</v>
       </c>
       <c r="H1010" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1012" t="n">
-        <v>17.2741222381592</v>
+        <v>17.2741203308105</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1013" t="n">
-        <v>17.4044227600098</v>
+        <v>17.4044189453125</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1017" t="n">
-        <v>16.2503299713135</v>
+        <v>16.2503318786621</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1018" t="n">
-        <v>16.4737033843994</v>
+        <v>16.473705291748</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G1021" t="n">
-        <v>16.7715320587158</v>
+        <v>16.7715301513672</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G1022" t="n">
-        <v>17.1624336242676</v>
+        <v>17.1624355316162</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1023" t="n">
-        <v>17.5905628204346</v>
+        <v>17.5905666351318</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1024" t="n">
-        <v>17.4974899291992</v>
+        <v>17.4974918365479</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1025" t="n">
-        <v>17.4974899291992</v>
+        <v>17.4974918365479</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1026" t="n">
-        <v>17.4974899291992</v>
+        <v>17.4974918365479</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1029" t="n">
-        <v>17.7767066955566</v>
+        <v>17.7767086029053</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1030" t="n">
-        <v>17.7767066955566</v>
+        <v>17.7767086029053</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G1031" t="n">
-        <v>17.6650199890137</v>
+        <v>17.665018081665</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1032" t="n">
-        <v>17.7953224182129</v>
+        <v>17.7953243255615</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1033" t="n">
-        <v>17.7767066955566</v>
+        <v>17.7767086029053</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G1034" t="n">
-        <v>17.7580947875977</v>
+        <v>17.758092880249</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1036" t="n">
-        <v>18.2979106903076</v>
+        <v>18.297908782959</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1037" t="n">
-        <v>17.7953224182129</v>
+        <v>17.7953243255615</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1040" t="n">
-        <v>18.3351402282715</v>
+        <v>18.3351421356201</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1042" t="n">
-        <v>18.2979106903076</v>
+        <v>18.297908782959</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1043" t="n">
-        <v>17.4416484832764</v>
+        <v>17.441650390625</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1044" t="n">
-        <v>17.5719470977783</v>
+        <v>17.571949005127</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G1046" t="n">
-        <v>17.3485774993896</v>
+        <v>17.348575592041</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1047" t="n">
-        <v>17.5905628204346</v>
+        <v>17.5905666351318</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1048" t="n">
-        <v>17.5905628204346</v>
+        <v>17.5905666351318</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1049" t="n">
-        <v>17.7394790649414</v>
+        <v>17.7394771575928</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>18.9599990844727</v>
       </c>
       <c r="G1050" t="n">
-        <v>17.6464061737061</v>
+        <v>17.6464080810547</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1053" t="n">
-        <v>18.2420654296875</v>
+        <v>18.2420673370361</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>20.25</v>
       </c>
       <c r="G1055" t="n">
-        <v>18.8470344543457</v>
+        <v>18.8470325469971</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G1057" t="n">
-        <v>20.1500358581543</v>
+        <v>20.1500377655029</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1059" t="n">
-        <v>20.5688629150391</v>
+        <v>20.5688591003418</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1060" t="n">
-        <v>20.8480758666992</v>
+        <v>20.8480739593506</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1061" t="n">
-        <v>21.4995784759521</v>
+        <v>21.4995765686035</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>23</v>
       </c>
       <c r="G1062" t="n">
-        <v>21.4065036773682</v>
+        <v>21.4065055847168</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1063" t="n">
-        <v>21.4995784759521</v>
+        <v>21.4995765686035</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>23.2800006866455</v>
       </c>
       <c r="G1064" t="n">
-        <v>21.667106628418</v>
+        <v>21.6671085357666</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1065" t="n">
-        <v>22.058012008667</v>
+        <v>22.0580101013184</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>23.9599990844727</v>
       </c>
       <c r="G1067" t="n">
-        <v>22.2999935150146</v>
+        <v>22.299991607666</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G1068" t="n">
-        <v>22.2255382537842</v>
+        <v>22.2255363464355</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>23.9599990844727</v>
       </c>
       <c r="G1069" t="n">
-        <v>22.2999935150146</v>
+        <v>22.299991607666</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>23.2800006866455</v>
       </c>
       <c r="G1071" t="n">
-        <v>21.667106628418</v>
+        <v>21.6671085357666</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>23.5</v>
       </c>
       <c r="G1072" t="n">
-        <v>21.8718643188477</v>
+        <v>21.8718662261963</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>23.9799995422363</v>
       </c>
       <c r="G1074" t="n">
-        <v>22.3186111450195</v>
+        <v>22.3186092376709</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>24.2399997711182</v>
       </c>
       <c r="G1075" t="n">
-        <v>22.5605945587158</v>
+        <v>22.5605964660645</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>25.2199993133545</v>
       </c>
       <c r="G1076" t="n">
-        <v>23.4726982116699</v>
+        <v>23.4726963043213</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>26.4599990844727</v>
       </c>
       <c r="G1079" t="n">
-        <v>24.6267871856689</v>
+        <v>24.6267910003662</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>25.6200008392334</v>
       </c>
       <c r="G1080" t="n">
-        <v>23.8449859619141</v>
+        <v>23.8449878692627</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>27.0599994659424</v>
       </c>
       <c r="G1082" t="n">
-        <v>25.1852207183838</v>
+        <v>25.1852226257324</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1083" t="n">
-        <v>24.3848037719727</v>
+        <v>24.384801864624</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>26.9200000762939</v>
       </c>
       <c r="G1085" t="n">
-        <v>25.0549182891846</v>
+        <v>25.0549201965332</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>26.2399997711182</v>
       </c>
       <c r="G1086" t="n">
-        <v>24.4220294952393</v>
+        <v>24.4220314025879</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G1087" t="n">
-        <v>24.4034194946289</v>
+        <v>24.4034175872803</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28657,7 +28657,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G1088" t="n">
-        <v>24.4034194946289</v>
+        <v>24.4034175872803</v>
       </c>
       <c r="H1088" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>27.2199993133545</v>
       </c>
       <c r="G1091" t="n">
-        <v>25.3341331481934</v>
+        <v>25.3341369628906</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>26.5599994659424</v>
       </c>
       <c r="G1092" t="n">
-        <v>24.7198619842529</v>
+        <v>24.7198600769043</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1094" t="n">
-        <v>24.0125141143799</v>
+        <v>24.0125179290771</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>24.5200004577637</v>
       </c>
       <c r="G1095" t="n">
-        <v>22.8211975097656</v>
+        <v>22.8211994171143</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>24.5400009155273</v>
       </c>
       <c r="G1097" t="n">
-        <v>22.8398113250732</v>
+        <v>22.8398132324219</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>25</v>
       </c>
       <c r="G1098" t="n">
-        <v>23.2679424285889</v>
+        <v>23.2679405212402</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G1099" t="n">
-        <v>22.8770389556885</v>
+        <v>22.8770408630371</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>25.2399997711182</v>
       </c>
       <c r="G1102" t="n">
-        <v>23.4913158416748</v>
+        <v>23.4913139343262</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1103" t="n">
-        <v>23.640230178833</v>
+        <v>23.6402282714844</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>25.6399993896484</v>
       </c>
       <c r="G1104" t="n">
-        <v>23.8636016845703</v>
+        <v>23.8636035919189</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1105" t="n">
-        <v>24.1055870056152</v>
+        <v>24.1055850982666</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>26.5400009155273</v>
       </c>
       <c r="G1106" t="n">
-        <v>24.7012462615967</v>
+        <v>24.7012481689453</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>26.5</v>
       </c>
       <c r="G1107" t="n">
-        <v>24.6640205383301</v>
+        <v>24.6640167236328</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>26.5799999237061</v>
       </c>
       <c r="G1108" t="n">
-        <v>24.7384757995605</v>
+        <v>24.7384738922119</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1109" t="n">
-        <v>26.8046684265137</v>
+        <v>26.804666519165</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>29</v>
       </c>
       <c r="G1110" t="n">
-        <v>26.9908142089844</v>
+        <v>26.990816116333</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1111" t="n">
-        <v>26.8046684265137</v>
+        <v>26.804666519165</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>31.4400005340576</v>
       </c>
       <c r="G1112" t="n">
-        <v>29.2617626190186</v>
+        <v>29.2617645263672</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>32.3800010681152</v>
       </c>
       <c r="G1113" t="n">
-        <v>30.1366386413574</v>
+        <v>30.1366405487061</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G1114" t="n">
-        <v>29.6898918151855</v>
+        <v>29.6898937225342</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>30.9799995422363</v>
       </c>
       <c r="G1116" t="n">
-        <v>28.8336334228516</v>
+        <v>28.8336353302002</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>30.6599998474121</v>
       </c>
       <c r="G1117" t="n">
-        <v>28.5358047485352</v>
+        <v>28.5358028411865</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>30.5200004577637</v>
       </c>
       <c r="G1118" t="n">
-        <v>28.4055023193359</v>
+        <v>28.4055042266846</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>31.7199993133545</v>
       </c>
       <c r="G1120" t="n">
-        <v>29.5223617553711</v>
+        <v>29.5223655700684</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>33.7200012207031</v>
       </c>
       <c r="G1124" t="n">
-        <v>31.3837985992432</v>
+        <v>31.3838005065918</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>33.5400009155273</v>
       </c>
       <c r="G1127" t="n">
-        <v>31.216272354126</v>
+        <v>31.2162704467773</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G1128" t="n">
-        <v>34.3434829711914</v>
+        <v>34.3434867858887</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>33.5</v>
       </c>
       <c r="G1129" t="n">
-        <v>31.1790428161621</v>
+        <v>31.1790409088135</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>33.6599998474121</v>
       </c>
       <c r="G1130" t="n">
-        <v>31.3279552459717</v>
+        <v>31.327953338623</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1131" t="n">
-        <v>31.8305435180664</v>
+        <v>31.830545425415</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>32.9599990844727</v>
       </c>
       <c r="G1132" t="n">
-        <v>30.6764526367188</v>
+        <v>30.6764507293701</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>31.6200008392334</v>
       </c>
       <c r="G1134" t="n">
-        <v>29.4292945861816</v>
+        <v>29.429292678833</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>32.4199981689453</v>
       </c>
       <c r="G1136" t="n">
-        <v>30.1738662719727</v>
+        <v>30.1738681793213</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>32.6399993896484</v>
       </c>
       <c r="G1137" t="n">
-        <v>30.378625869751</v>
+        <v>30.3786277770996</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>32.4799995422363</v>
       </c>
       <c r="G1138" t="n">
-        <v>30.2297096252441</v>
+        <v>30.2297115325928</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>33.7200012207031</v>
       </c>
       <c r="G1142" t="n">
-        <v>31.3837985992432</v>
+        <v>31.3838005065918</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>35.2599983215332</v>
       </c>
       <c r="G1146" t="n">
-        <v>32.8171043395996</v>
+        <v>32.8171081542969</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G1147" t="n">
-        <v>32.7612648010254</v>
+        <v>32.7612609863281</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>36.1399993896484</v>
       </c>
       <c r="G1149" t="n">
-        <v>33.6361351013184</v>
+        <v>33.6361389160156</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>33.6199989318848</v>
       </c>
       <c r="G1152" t="n">
-        <v>31.2907314300537</v>
+        <v>31.2907295227051</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>33.9199981689453</v>
       </c>
       <c r="G1153" t="n">
-        <v>31.5699443817139</v>
+        <v>31.5699462890625</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>35.7799987792969</v>
       </c>
       <c r="G1157" t="n">
-        <v>33.3010787963867</v>
+        <v>33.3010749816895</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>36.2799987792969</v>
       </c>
       <c r="G1158" t="n">
-        <v>33.7664337158203</v>
+        <v>33.7664375305176</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>35.7400016784668</v>
       </c>
       <c r="G1159" t="n">
-        <v>33.2638511657715</v>
+        <v>33.2638473510742</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>36.0200004577637</v>
       </c>
       <c r="G1162" t="n">
-        <v>33.5244522094727</v>
+        <v>33.5244560241699</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>37.9799995422363</v>
       </c>
       <c r="G1163" t="n">
-        <v>35.3486595153809</v>
+        <v>35.3486518859863</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>33.5400009155273</v>
       </c>
       <c r="G1167" t="n">
-        <v>31.216272354126</v>
+        <v>31.2162704467773</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>34</v>
       </c>
       <c r="G1168" t="n">
-        <v>31.644401550293</v>
+        <v>31.6444034576416</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>33.439998626709</v>
       </c>
       <c r="G1173" t="n">
-        <v>31.123197555542</v>
+        <v>31.1231994628906</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>33.3800010681152</v>
       </c>
       <c r="G1174" t="n">
-        <v>31.0673580169678</v>
+        <v>31.0673561096191</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1176" t="n">
-        <v>30.8998260498047</v>
+        <v>30.8998279571533</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>29.9200000762939</v>
       </c>
       <c r="G1178" t="n">
-        <v>27.847074508667</v>
+        <v>27.8470726013184</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>30.1800003051758</v>
       </c>
       <c r="G1179" t="n">
-        <v>28.0890598297119</v>
+        <v>28.0890617370605</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>30.2399997711182</v>
       </c>
       <c r="G1180" t="n">
-        <v>28.1449031829834</v>
+        <v>28.1449012756348</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>31.1800003051758</v>
       </c>
       <c r="G1182" t="n">
-        <v>29.0197792053223</v>
+        <v>29.0197772979736</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>31.0200004577637</v>
       </c>
       <c r="G1185" t="n">
-        <v>28.8708629608154</v>
+        <v>28.8708610534668</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31205,7 +31205,7 @@
         <v>30.7199993133545</v>
       </c>
       <c r="G1186" t="n">
-        <v>28.5916481018066</v>
+        <v>28.591646194458</v>
       </c>
       <c r="H1186" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>30.1399993896484</v>
       </c>
       <c r="G1189" t="n">
-        <v>28.051830291748</v>
+        <v>28.0518283843994</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>29</v>
       </c>
       <c r="G1190" t="n">
-        <v>26.9908142089844</v>
+        <v>26.990816116333</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>28.7800006866455</v>
       </c>
       <c r="G1192" t="n">
-        <v>26.7860565185547</v>
+        <v>26.7860546112061</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>30.1800003051758</v>
       </c>
       <c r="G1193" t="n">
-        <v>28.0890598297119</v>
+        <v>28.0890617370605</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>29.9799995422363</v>
       </c>
       <c r="G1194" t="n">
-        <v>27.9029178619385</v>
+        <v>27.9029140472412</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>30.2800006866455</v>
       </c>
       <c r="G1195" t="n">
-        <v>28.1821327209473</v>
+        <v>28.1821308135986</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G1197" t="n">
-        <v>26.3579254150391</v>
+        <v>26.3579273223877</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1198" t="n">
-        <v>26.8977432250977</v>
+        <v>26.897741317749</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G1199" t="n">
-        <v>26.1903953552246</v>
+        <v>26.190393447876</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>28.8799991607666</v>
       </c>
       <c r="G1201" t="n">
-        <v>26.8791275024414</v>
+        <v>26.8791236877441</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>28.8799991607666</v>
       </c>
       <c r="G1203" t="n">
-        <v>26.8791275024414</v>
+        <v>26.8791236877441</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>26.0400009155273</v>
       </c>
       <c r="G1206" t="n">
-        <v>24.2358913421631</v>
+        <v>24.2358894348145</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>28.2199993133545</v>
       </c>
       <c r="G1209" t="n">
-        <v>26.2648544311523</v>
+        <v>26.2648525238037</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G1211" t="n">
-        <v>26.1903953552246</v>
+        <v>26.190393447876</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>28.4799995422363</v>
       </c>
       <c r="G1212" t="n">
-        <v>26.5068378448486</v>
+        <v>26.5068397521973</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1214" t="n">
-        <v>27.2141857147217</v>
+        <v>27.214183807373</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>29.8799991607666</v>
       </c>
       <c r="G1215" t="n">
-        <v>27.8098430633545</v>
+        <v>27.8098449707031</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>29.3199996948242</v>
       </c>
       <c r="G1216" t="n">
-        <v>27.2886428833008</v>
+        <v>27.2886409759521</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1218" t="n">
-        <v>27.6423149108887</v>
+        <v>27.6423168182373</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>29.9599990844727</v>
       </c>
       <c r="G1225" t="n">
-        <v>27.8843002319336</v>
+        <v>27.8843021392822</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>28.9799995422363</v>
       </c>
       <c r="G1228" t="n">
-        <v>26.9721965789795</v>
+        <v>26.9721984863281</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1231" t="n">
-        <v>26.2462406158447</v>
+        <v>26.2462368011475</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>28.4400005340576</v>
       </c>
       <c r="G1232" t="n">
-        <v>26.469612121582</v>
+        <v>26.4696102142334</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1234" t="n">
-        <v>26.4323806762695</v>
+        <v>26.4323825836182</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>26.7600002288818</v>
       </c>
       <c r="G1239" t="n">
-        <v>24.9060039520264</v>
+        <v>24.906005859375</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G1241" t="n">
-        <v>23.9647350311279</v>
+        <v>23.9647331237793</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>24.9799995422363</v>
       </c>
       <c r="G1245" t="n">
-        <v>23.5129241943359</v>
+        <v>23.5129261016846</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G1248" t="n">
-        <v>21.6680355072021</v>
+        <v>21.6680374145508</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G1254" t="n">
-        <v>19.6537170410156</v>
+        <v>19.653715133667</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1255" t="n">
-        <v>19.2019081115723</v>
+        <v>19.2019062042236</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G1262" t="n">
-        <v>19.7854976654053</v>
+        <v>19.7854957580566</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>21</v>
       </c>
       <c r="G1269" t="n">
-        <v>19.7666702270508</v>
+        <v>19.7666721343994</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>21.0599994659424</v>
       </c>
       <c r="G1272" t="n">
-        <v>19.8231468200684</v>
+        <v>19.8231449127197</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G1273" t="n">
-        <v>19.7478427886963</v>
+        <v>19.7478446960449</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>20.0200004577637</v>
       </c>
       <c r="G1274" t="n">
-        <v>18.8442268371582</v>
+        <v>18.8442249298096</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G1275" t="n">
-        <v>18.2888774871826</v>
+        <v>18.288875579834</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1278" t="n">
-        <v>18.0159091949463</v>
+        <v>18.0159072875977</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1279" t="n">
-        <v>18.2041625976562</v>
+        <v>18.2041606903076</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1281" t="n">
-        <v>17.7146987915039</v>
+        <v>17.7147006988525</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G1283" t="n">
-        <v>17.921781539917</v>
+        <v>17.9217834472656</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G1287" t="n">
-        <v>16.8863849639893</v>
+        <v>16.8863830566406</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1288" t="n">
-        <v>16.3780975341797</v>
+        <v>16.3780994415283</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33935,7 +33935,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1291" t="n">
-        <v>16.0957164764404</v>
+        <v>16.0957183837891</v>
       </c>
       <c r="H1291" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1300" t="n">
-        <v>16.4533996582031</v>
+        <v>16.4534015655518</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G1302" t="n">
-        <v>17.4982089996338</v>
+        <v>17.4982109069824</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34247,7 +34247,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G1303" t="n">
-        <v>17.5829257965088</v>
+        <v>17.5829238891602</v>
       </c>
       <c r="H1303" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>18.75</v>
       </c>
       <c r="G1306" t="n">
-        <v>17.6488151550293</v>
+        <v>17.6488132476807</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34351,7 +34351,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1307" t="n">
-        <v>17.2252388000488</v>
+        <v>17.2252407073975</v>
       </c>
       <c r="H1307" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>20</v>
       </c>
       <c r="G1309" t="n">
-        <v>18.8254013061523</v>
+        <v>18.8253993988037</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>19.7900009155273</v>
       </c>
       <c r="G1310" t="n">
-        <v>18.6277332305908</v>
+        <v>18.6277351379395</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>20</v>
       </c>
       <c r="G1311" t="n">
-        <v>18.8254013061523</v>
+        <v>18.8253993988037</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>20</v>
       </c>
       <c r="G1312" t="n">
-        <v>18.8254013061523</v>
+        <v>18.8253993988037</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G1316" t="n">
-        <v>18.2888774871826</v>
+        <v>18.288875579834</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1317" t="n">
-        <v>18.4488906860352</v>
+        <v>18.4488925933838</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G1318" t="n">
-        <v>18.3830051422119</v>
+        <v>18.3830032348633</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G1319" t="n">
-        <v>18.608907699585</v>
+        <v>18.6089096069336</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G1320" t="n">
-        <v>18.2982883453369</v>
+        <v>18.2982902526855</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>18.1700000762939</v>
       </c>
       <c r="G1323" t="n">
-        <v>17.102876663208</v>
+        <v>17.1028747558594</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1324" t="n">
-        <v>17.4887981414795</v>
+        <v>17.4887962341309</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G1327" t="n">
-        <v>16.7263660430908</v>
+        <v>16.7263679504395</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1330" t="n">
-        <v>16.283971786499</v>
+        <v>16.2839698791504</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G1331" t="n">
-        <v>16.7263660430908</v>
+        <v>16.7263679504395</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G1339" t="n">
-        <v>17.6205768585205</v>
+        <v>17.6205749511719</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1343" t="n">
-        <v>15.6815586090088</v>
+        <v>15.6815595626831</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>16</v>
       </c>
       <c r="G1344" t="n">
-        <v>15.060320854187</v>
+        <v>15.0603199005127</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G1346" t="n">
-        <v>14.3920183181763</v>
+        <v>14.392017364502</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G1348" t="n">
-        <v>13.4695739746094</v>
+        <v>13.4695749282837</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1351" t="n">
-        <v>13.0271759033203</v>
+        <v>13.0271768569946</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35521,7 +35521,7 @@
         <v>13.2700004577637</v>
       </c>
       <c r="G1352" t="n">
-        <v>12.4906530380249</v>
+        <v>12.4906539916992</v>
       </c>
       <c r="H1352" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G1357" t="n">
-        <v>13.7801923751831</v>
+        <v>13.7801933288574</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G1358" t="n">
-        <v>13.3377952575684</v>
+        <v>13.3377962112427</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>14.0699996948242</v>
       </c>
       <c r="G1361" t="n">
-        <v>13.2436685562134</v>
+        <v>13.2436676025391</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G1362" t="n">
-        <v>13.4413356781006</v>
+        <v>13.4413366317749</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1364" t="n">
-        <v>13.3660335540771</v>
+        <v>13.3660345077515</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1365" t="n">
-        <v>13.3660335540771</v>
+        <v>13.3660345077515</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G1367" t="n">
-        <v>13.516637802124</v>
+        <v>13.5166368484497</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>15.5699996948242</v>
       </c>
       <c r="G1373" t="n">
-        <v>14.6555728912354</v>
+        <v>14.6555738449097</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>15.3900003433228</v>
       </c>
       <c r="G1374" t="n">
-        <v>14.4861459732056</v>
+        <v>14.4861469268799</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G1376" t="n">
-        <v>14.1567010879517</v>
+        <v>14.1567001342773</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1378" t="n">
-        <v>14.4484949111938</v>
+        <v>14.4484958648682</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1382" t="n">
-        <v>16.3310356140137</v>
+        <v>16.331033706665</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>17.5</v>
       </c>
       <c r="G1386" t="n">
-        <v>16.4722232818604</v>
+        <v>16.472225189209</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1387" t="n">
-        <v>16.1898460388184</v>
+        <v>16.1898441314697</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="G1388" t="n">
-        <v>16.3122081756592</v>
+        <v>16.3122100830078</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1391" t="n">
-        <v>16.1898460388184</v>
+        <v>16.1898441314697</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1393" t="n">
-        <v>17.2252388000488</v>
+        <v>17.2252407073975</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G1394" t="n">
-        <v>16.9710998535156</v>
+        <v>16.971097946167</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>17.5100002288818</v>
       </c>
       <c r="G1395" t="n">
-        <v>16.4816398620605</v>
+        <v>16.4816379547119</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1398" t="n">
-        <v>17.6017513275146</v>
+        <v>17.601749420166</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>18.6100006103516</v>
       </c>
       <c r="G1399" t="n">
-        <v>17.5170364379883</v>
+        <v>17.5170345306396</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>18.3899993896484</v>
       </c>
       <c r="G1400" t="n">
-        <v>17.3099555969238</v>
+        <v>17.3099536895752</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1401" t="n">
-        <v>16.8110828399658</v>
+        <v>16.8110847473145</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>17.8700008392334</v>
       </c>
       <c r="G1403" t="n">
-        <v>16.8204956054688</v>
+        <v>16.8204936981201</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G1404" t="n">
-        <v>16.9052085876465</v>
+        <v>16.9052066802979</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36951,7 +36951,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1407" t="n">
-        <v>17.018159866333</v>
+        <v>17.0181617736816</v>
       </c>
       <c r="H1407" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>17.5</v>
       </c>
       <c r="G1412" t="n">
-        <v>16.4722232818604</v>
+        <v>16.472225189209</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1414" t="n">
-        <v>16.2651481628418</v>
+        <v>16.2651443481445</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1419" t="n">
-        <v>16.9805126190186</v>
+        <v>16.9805107116699</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1424" t="n">
-        <v>18.1665134429932</v>
+        <v>18.1665115356445</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37419,7 +37419,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1425" t="n">
-        <v>18.2794628143311</v>
+        <v>18.2794647216797</v>
       </c>
       <c r="H1425" t="s">
         <v>8</v>
@@ -37445,7 +37445,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G1426" t="n">
-        <v>18.3924160003662</v>
+        <v>18.3924179077148</v>
       </c>
       <c r="H1426" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1427" t="n">
-        <v>18.4488906860352</v>
+        <v>18.4488925933838</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>20.6200008392334</v>
       </c>
       <c r="G1431" t="n">
-        <v>19.4089889526367</v>
+        <v>19.4089870452881</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>21.5</v>
       </c>
       <c r="G1436" t="n">
-        <v>20.2373046875</v>
+        <v>20.2373065948486</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>21.1399993896484</v>
       </c>
       <c r="G1439" t="n">
-        <v>19.8984470367432</v>
+        <v>19.8984451293945</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37835,7 +37835,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G1441" t="n">
-        <v>20.915018081665</v>
+        <v>20.9150199890137</v>
       </c>
       <c r="H1441" t="s">
         <v>8</v>
@@ -37861,7 +37861,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G1442" t="n">
-        <v>20.7455940246582</v>
+        <v>20.7455921173096</v>
       </c>
       <c r="H1442" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>21.9599990844727</v>
       </c>
       <c r="G1443" t="n">
-        <v>20.6702899932861</v>
+        <v>20.6702880859375</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>21.7199993133545</v>
       </c>
       <c r="G1445" t="n">
-        <v>20.4443836212158</v>
+        <v>20.4443855285645</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G1447" t="n">
-        <v>20.4067344665527</v>
+        <v>20.4067325592041</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G1449" t="n">
-        <v>20.1055297851562</v>
+        <v>20.1055278778076</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>21.2600002288818</v>
       </c>
       <c r="G1451" t="n">
-        <v>20.0114002227783</v>
+        <v>20.011402130127</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>20.8199996948242</v>
       </c>
       <c r="G1452" t="n">
-        <v>19.5972385406494</v>
+        <v>19.5972423553467</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>20.6399993896484</v>
       </c>
       <c r="G1454" t="n">
-        <v>19.4278125762939</v>
+        <v>19.4278106689453</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1455" t="n">
-        <v>18.919527053833</v>
+        <v>18.9195289611816</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>20</v>
       </c>
       <c r="G1457" t="n">
-        <v>18.8254013061523</v>
+        <v>18.8253993988037</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38277,7 +38277,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G1458" t="n">
-        <v>18.9948272705078</v>
+        <v>18.9948291778564</v>
       </c>
       <c r="H1458" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1460" t="n">
-        <v>19.0136528015137</v>
+        <v>19.0136547088623</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G1463" t="n">
-        <v>19.7854976654053</v>
+        <v>19.7854957580566</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1466" t="n">
-        <v>18.919527053833</v>
+        <v>18.9195289611816</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>20</v>
       </c>
       <c r="G1470" t="n">
-        <v>18.8254013061523</v>
+        <v>18.8253993988037</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38641,7 +38641,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1472" t="n">
-        <v>18.2794628143311</v>
+        <v>18.2794647216797</v>
       </c>
       <c r="H1472" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1475" t="n">
-        <v>18.919527053833</v>
+        <v>18.9195289611816</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>20</v>
       </c>
       <c r="G1477" t="n">
-        <v>18.8254013061523</v>
+        <v>18.8253993988037</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>19.5</v>
       </c>
       <c r="G1479" t="n">
-        <v>18.3547649383545</v>
+        <v>18.3547630310059</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1480" t="n">
-        <v>18.4488906860352</v>
+        <v>18.4488925933838</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1483" t="n">
-        <v>18.8724632263184</v>
+        <v>18.8724613189697</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>20</v>
       </c>
       <c r="G1484" t="n">
-        <v>18.8254013061523</v>
+        <v>18.8253993988037</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1486" t="n">
-        <v>18.919527053833</v>
+        <v>18.9195289611816</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>20</v>
       </c>
       <c r="G1487" t="n">
-        <v>18.8254013061523</v>
+        <v>18.8253993988037</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>20</v>
       </c>
       <c r="G1488" t="n">
-        <v>18.8254013061523</v>
+        <v>18.8253993988037</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>20</v>
       </c>
       <c r="G1489" t="n">
-        <v>18.8254013061523</v>
+        <v>18.8253993988037</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1490" t="n">
-        <v>19.2019081115723</v>
+        <v>19.2019062042236</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>20</v>
       </c>
       <c r="G1493" t="n">
-        <v>18.8254013061523</v>
+        <v>18.8253993988037</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>20</v>
       </c>
       <c r="G1494" t="n">
-        <v>18.8254013061523</v>
+        <v>18.8253993988037</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1495" t="n">
-        <v>18.4488906860352</v>
+        <v>18.4488925933838</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G1503" t="n">
-        <v>18.5241928100586</v>
+        <v>18.5241947174072</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1504" t="n">
-        <v>18.966588973999</v>
+        <v>18.9665908813477</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1507" t="n">
-        <v>18.7850475311279</v>
+        <v>18.7850456237793</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39629,7 +39629,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1510" t="n">
-        <v>18.2881889343262</v>
+        <v>18.2881870269775</v>
       </c>
       <c r="H1510" t="s">
         <v>8</v>
@@ -39655,7 +39655,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1511" t="n">
-        <v>18.0015392303467</v>
+        <v>18.0015411376953</v>
       </c>
       <c r="H1511" t="s">
         <v>8</v>
@@ -39837,7 +39837,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1518" t="n">
-        <v>18.2881889343262</v>
+        <v>18.2881870269775</v>
       </c>
       <c r="H1518" t="s">
         <v>8</v>
@@ -39889,7 +39889,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G1520" t="n">
-        <v>18.6703872680664</v>
+        <v>18.670389175415</v>
       </c>
       <c r="H1520" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>19.7399997711182</v>
       </c>
       <c r="G1522" t="n">
-        <v>18.8614864349365</v>
+        <v>18.8614845275879</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>20</v>
       </c>
       <c r="G1523" t="n">
-        <v>19.1099147796631</v>
+        <v>19.1099166870117</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1526" t="n">
-        <v>19.2532386779785</v>
+        <v>19.2532405853271</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>20</v>
       </c>
       <c r="G1527" t="n">
-        <v>19.1099147796631</v>
+        <v>19.1099166870117</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40149,7 +40149,7 @@
         <v>21</v>
       </c>
       <c r="G1530" t="n">
-        <v>20.0654125213623</v>
+        <v>20.0654106140137</v>
       </c>
       <c r="H1530" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G1531" t="n">
-        <v>20.1131839752197</v>
+        <v>20.1131858825684</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1532" t="n">
-        <v>20.4476089477539</v>
+        <v>20.4476108551025</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1533" t="n">
-        <v>20.4476089477539</v>
+        <v>20.4476108551025</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1534" t="n">
-        <v>20.5909328460693</v>
+        <v>20.590934753418</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1538" t="n">
-        <v>20.2087364196777</v>
+        <v>20.2087345123291</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1545" t="n">
-        <v>19.2532386779785</v>
+        <v>19.2532405853271</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1546" t="n">
-        <v>19.2532386779785</v>
+        <v>19.2532405853271</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1547" t="n">
-        <v>19.0143661499023</v>
+        <v>19.0143642425537</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1548" t="n">
-        <v>18.8423748016357</v>
+        <v>18.8423767089844</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1549" t="n">
-        <v>19.0143661499023</v>
+        <v>19.0143642425537</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>20</v>
       </c>
       <c r="G1551" t="n">
-        <v>19.1099147796631</v>
+        <v>19.1099166870117</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1555" t="n">
-        <v>19.0143661499023</v>
+        <v>19.0143642425537</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1556" t="n">
-        <v>19.0143661499023</v>
+        <v>19.0143642425537</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40851,7 +40851,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1557" t="n">
-        <v>19.1576900482178</v>
+        <v>19.1576881408691</v>
       </c>
       <c r="H1557" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1558" t="n">
-        <v>19.0143661499023</v>
+        <v>19.0143642425537</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G1559" t="n">
-        <v>18.517505645752</v>
+        <v>18.5175075531006</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G1563" t="n">
-        <v>18.4219589233398</v>
+        <v>18.4219570159912</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G1564" t="n">
-        <v>18.4983997344971</v>
+        <v>18.4983978271484</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1565" t="n">
-        <v>18.4410667419434</v>
+        <v>18.441068649292</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41085,7 +41085,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1566" t="n">
-        <v>18.4792861938477</v>
+        <v>18.4792881011963</v>
       </c>
       <c r="H1566" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1573" t="n">
-        <v>16.4345283508301</v>
+        <v>16.4345264434814</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1574" t="n">
-        <v>16.4345283508301</v>
+        <v>16.4345264434814</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1585" t="n">
-        <v>16.5491847991943</v>
+        <v>16.549186706543</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1586" t="n">
-        <v>16.5109672546387</v>
+        <v>16.51096534729</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1596" t="n">
-        <v>15.2497119903564</v>
+        <v>15.2497129440308</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G1604" t="n">
-        <v>14.5426454544067</v>
+        <v>14.5426464080811</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42177,7 +42177,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1608" t="n">
-        <v>14.4662065505981</v>
+        <v>14.4662055969238</v>
       </c>
       <c r="H1608" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G1610" t="n">
-        <v>13.7209196090698</v>
+        <v>13.7209186553955</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>14.5</v>
       </c>
       <c r="G1622" t="n">
-        <v>13.8546886444092</v>
+        <v>13.8546895980835</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1624" t="n">
-        <v>13.7591390609741</v>
+        <v>13.7591381072998</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G1630" t="n">
-        <v>14.1222276687622</v>
+        <v>14.1222267150879</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42775,7 +42775,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G1631" t="n">
-        <v>14.5999746322632</v>
+        <v>14.5999755859375</v>
       </c>
       <c r="H1631" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G1636" t="n">
-        <v>15.6510200500488</v>
+        <v>15.6510210037231</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1640" t="n">
-        <v>16.9313850402832</v>
+        <v>16.9313831329346</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>17.5</v>
       </c>
       <c r="G1642" t="n">
-        <v>16.7211761474609</v>
+        <v>16.7211742401123</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1643" t="n">
-        <v>17.0078258514404</v>
+        <v>17.0078239440918</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43217,7 +43217,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1648" t="n">
-        <v>16.7976169586182</v>
+        <v>16.7976150512695</v>
       </c>
       <c r="H1648" t="s">
         <v>8</v>
@@ -43321,7 +43321,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1652" t="n">
-        <v>17.2371463775635</v>
+        <v>17.2371444702148</v>
       </c>
       <c r="H1652" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1654" t="n">
-        <v>16.7020645141602</v>
+        <v>16.7020664215088</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43399,7 +43399,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1655" t="n">
-        <v>16.7785034179688</v>
+        <v>16.7785053253174</v>
       </c>
       <c r="H1655" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1656" t="n">
-        <v>16.9887142181396</v>
+        <v>16.9887161254883</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43529,7 +43529,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1660" t="n">
-        <v>17.2753620147705</v>
+        <v>17.2753639221191</v>
       </c>
       <c r="H1660" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1663" t="n">
-        <v>18.5939464569092</v>
+        <v>18.5939483642578</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G1664" t="n">
-        <v>18.1353092193604</v>
+        <v>18.1353073120117</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1668" t="n">
-        <v>18.5939464569092</v>
+        <v>18.5939483642578</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -44049,7 +44049,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1680" t="n">
-        <v>18.0397567749023</v>
+        <v>18.039758682251</v>
       </c>
       <c r="H1680" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1682" t="n">
-        <v>17.3518028259277</v>
+        <v>17.3518047332764</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1683" t="n">
-        <v>16.8740558624268</v>
+        <v>16.8740539550781</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G1684" t="n">
-        <v>17.084264755249</v>
+        <v>17.0842628479004</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1687" t="n">
-        <v>17.0651550292969</v>
+        <v>17.0651569366455</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1688" t="n">
-        <v>17.332691192627</v>
+        <v>17.3326930999756</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44309,7 +44309,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1690" t="n">
-        <v>18.0015392303467</v>
+        <v>18.0015411376953</v>
       </c>
       <c r="H1690" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G1698" t="n">
-        <v>17.4091320037842</v>
+        <v>17.4091339111328</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G1702" t="n">
-        <v>17.4091320037842</v>
+        <v>17.4091339111328</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44777,7 +44777,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1708" t="n">
-        <v>18.0397567749023</v>
+        <v>18.039758682251</v>
       </c>
       <c r="H1708" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G1714" t="n">
-        <v>17.5237941741943</v>
+        <v>17.5237922668457</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1726" t="n">
-        <v>17.0078258514404</v>
+        <v>17.0078239440918</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45271,7 +45271,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1727" t="n">
-        <v>16.7976169586182</v>
+        <v>16.7976150512695</v>
       </c>
       <c r="H1727" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1729" t="n">
-        <v>16.8167247772217</v>
+        <v>16.8167266845703</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>17.5</v>
       </c>
       <c r="G1735" t="n">
-        <v>16.7211761474609</v>
+        <v>16.7211742401123</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1736" t="n">
-        <v>16.8740558624268</v>
+        <v>16.8740539550781</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1740" t="n">
-        <v>15.8994493484497</v>
+        <v>15.8994483947754</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1741" t="n">
-        <v>15.7847900390625</v>
+        <v>15.7847909927368</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G1744" t="n">
-        <v>15.6510200500488</v>
+        <v>15.6510210037231</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G1745" t="n">
-        <v>15.459921836853</v>
+        <v>15.4599208831787</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1756" t="n">
-        <v>15.6319103240967</v>
+        <v>15.631911277771</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1758" t="n">
-        <v>15.7847900390625</v>
+        <v>15.7847909927368</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1760" t="n">
-        <v>15.8994493484497</v>
+        <v>15.8994483947754</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1761" t="n">
-        <v>15.9185600280762</v>
+        <v>15.9185609817505</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1763" t="n">
-        <v>15.9185600280762</v>
+        <v>15.9185609817505</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1765" t="n">
-        <v>16.6447372436523</v>
+        <v>16.6447353363037</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1766" t="n">
-        <v>16.8740558624268</v>
+        <v>16.8740539550781</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1767" t="n">
-        <v>16.8167247772217</v>
+        <v>16.8167266845703</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -61784,6 +61784,32 @@
         <v>30.2000007629395</v>
       </c>
       <c r="H2362" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2363">
+      <c r="A2363" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B2363" t="n">
+        <v>21679</v>
+      </c>
+      <c r="C2363" t="n">
+        <v>30</v>
+      </c>
+      <c r="D2363" t="n">
+        <v>29.2000007629395</v>
+      </c>
+      <c r="E2363" t="n">
+        <v>29.8500003814697</v>
+      </c>
+      <c r="F2363" t="n">
+        <v>29.7999992370605</v>
+      </c>
+      <c r="G2363" t="n">
+        <v>29.7999992370605</v>
+      </c>
+      <c r="H2363" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/WIIT.MI.xlsx
+++ b/data/WIIT.MI.xlsx
@@ -7493,7 +7493,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G274" t="n">
-        <v>4.51098823547363</v>
+        <v>4.51098871231079</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G276" t="n">
-        <v>4.52888822555542</v>
+        <v>4.52888870239258</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G277" t="n">
-        <v>4.49308824539185</v>
+        <v>4.49308776855469</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G278" t="n">
-        <v>4.44833517074585</v>
+        <v>4.44833564758301</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G282" t="n">
-        <v>4.49308824539185</v>
+        <v>4.49308776855469</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G284" t="n">
-        <v>4.49308824539185</v>
+        <v>4.49308776855469</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G286" t="n">
-        <v>4.44833517074585</v>
+        <v>4.44833564758301</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G287" t="n">
-        <v>4.44833517074585</v>
+        <v>4.44833564758301</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G288" t="n">
-        <v>4.44833517074585</v>
+        <v>4.44833564758301</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G289" t="n">
-        <v>4.44833517074585</v>
+        <v>4.44833564758301</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G291" t="n">
-        <v>4.54678916931152</v>
+        <v>4.54678964614868</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G292" t="n">
-        <v>4.54678916931152</v>
+        <v>4.54678964614868</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G293" t="n">
-        <v>4.54678916931152</v>
+        <v>4.54678964614868</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G294" t="n">
-        <v>4.58259010314941</v>
+        <v>4.58259105682373</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G295" t="n">
-        <v>4.54678916931152</v>
+        <v>4.54678964614868</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G296" t="n">
-        <v>4.51098823547363</v>
+        <v>4.51098871231079</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G297" t="n">
-        <v>4.52888822555542</v>
+        <v>4.52888870239258</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G298" t="n">
-        <v>4.51098823547363</v>
+        <v>4.51098871231079</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>4.51098823547363</v>
+        <v>4.51098871231079</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G300" t="n">
-        <v>4.49308824539185</v>
+        <v>4.49308776855469</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G301" t="n">
-        <v>4.49308824539185</v>
+        <v>4.49308776855469</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>4.49308824539185</v>
+        <v>4.49308776855469</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G303" t="n">
-        <v>4.43043422698975</v>
+        <v>4.4304347038269</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G304" t="n">
-        <v>4.43043422698975</v>
+        <v>4.4304347038269</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G306" t="n">
-        <v>4.3409309387207</v>
+        <v>4.34093046188354</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G307" t="n">
-        <v>4.30513000488281</v>
+        <v>4.30512952804565</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G309" t="n">
-        <v>4.33198022842407</v>
+        <v>4.33198070526123</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G310" t="n">
-        <v>4.33198022842407</v>
+        <v>4.33198070526123</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G311" t="n">
-        <v>4.27827930450439</v>
+        <v>4.27827835083008</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G312" t="n">
-        <v>4.27827930450439</v>
+        <v>4.27827835083008</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G315" t="n">
-        <v>4.36778163909912</v>
+        <v>4.36778259277344</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G316" t="n">
-        <v>4.33198022842407</v>
+        <v>4.33198070526123</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G317" t="n">
-        <v>4.3230299949646</v>
+        <v>4.32303047180176</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G318" t="n">
-        <v>4.3230299949646</v>
+        <v>4.32303047180176</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G320" t="n">
-        <v>4.14402341842651</v>
+        <v>4.14402198791504</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G322" t="n">
-        <v>4.3230299949646</v>
+        <v>4.32303047180176</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G323" t="n">
-        <v>4.34988164901733</v>
+        <v>4.34988212585449</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>4.28722858428955</v>
+        <v>4.28722906112671</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G325" t="n">
-        <v>4.17982387542725</v>
+        <v>4.1798243522644</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8871,7 +8871,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G327" t="n">
-        <v>4.04556894302368</v>
+        <v>4.04556798934937</v>
       </c>
       <c r="H327" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G328" t="n">
-        <v>3.90236282348633</v>
+        <v>3.90236330032349</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G329" t="n">
-        <v>3.99186658859253</v>
+        <v>3.99186635017395</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G330" t="n">
-        <v>4.14402341842651</v>
+        <v>4.14402198791504</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G331" t="n">
-        <v>4.08136940002441</v>
+        <v>4.08136987686157</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G333" t="n">
-        <v>4.17982387542725</v>
+        <v>4.1798243522644</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G334" t="n">
-        <v>4.14402341842651</v>
+        <v>4.14402198791504</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G335" t="n">
-        <v>4.11717128753662</v>
+        <v>4.11717176437378</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G336" t="n">
-        <v>3.99186658859253</v>
+        <v>3.99186635017395</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G338" t="n">
-        <v>3.93816447257996</v>
+        <v>3.93816471099854</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G339" t="n">
-        <v>3.88446187973022</v>
+        <v>3.8844621181488</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G340" t="n">
-        <v>3.90236282348633</v>
+        <v>3.90236330032349</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G341" t="n">
-        <v>3.86656093597412</v>
+        <v>3.86656069755554</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>3.76810693740845</v>
+        <v>3.76810717582703</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G343" t="n">
-        <v>3.8486602306366</v>
+        <v>3.84866094589233</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G344" t="n">
-        <v>3.78600788116455</v>
+        <v>3.78600764274597</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G345" t="n">
-        <v>3.70545434951782</v>
+        <v>3.7054545879364</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G346" t="n">
-        <v>3.66965270042419</v>
+        <v>3.66965293884277</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G347" t="n">
-        <v>3.60700058937073</v>
+        <v>3.60700035095215</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>4</v>
       </c>
       <c r="G352" t="n">
-        <v>3.58014917373657</v>
+        <v>3.58014941215515</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G353" t="n">
-        <v>3.4369432926178</v>
+        <v>3.43694305419922</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G355" t="n">
-        <v>3.44589352607727</v>
+        <v>3.44589376449585</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G356" t="n">
-        <v>3.41009211540222</v>
+        <v>3.4100923538208</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G358" t="n">
-        <v>3.31163811683655</v>
+        <v>3.31163787841797</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G359" t="n">
-        <v>3.31163811683655</v>
+        <v>3.31163787841797</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G360" t="n">
-        <v>3.31163811683655</v>
+        <v>3.31163787841797</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G361" t="n">
-        <v>3.34743976593018</v>
+        <v>3.3474395275116</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G362" t="n">
-        <v>3.36534023284912</v>
+        <v>3.36534070968628</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G363" t="n">
-        <v>3.31163811683655</v>
+        <v>3.31163787841797</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G364" t="n">
-        <v>3.20423340797424</v>
+        <v>3.20423316955566</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G365" t="n">
-        <v>3.08787870407104</v>
+        <v>3.08787894248962</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G366" t="n">
-        <v>3.07892870903015</v>
+        <v>3.07892823219299</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G367" t="n">
-        <v>3.09682893753052</v>
+        <v>3.0968291759491</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G368" t="n">
-        <v>3.10577964782715</v>
+        <v>3.10577940940857</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G369" t="n">
-        <v>3.20423340797424</v>
+        <v>3.20423316955566</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G371" t="n">
-        <v>3.22213411331177</v>
+        <v>3.22213459014893</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G372" t="n">
-        <v>3.22213411331177</v>
+        <v>3.22213459014893</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G373" t="n">
-        <v>2.9357225894928</v>
+        <v>2.93572235107422</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G376" t="n">
-        <v>2.91782164573669</v>
+        <v>2.91782140731812</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G377" t="n">
-        <v>2.95362329483032</v>
+        <v>2.9536235332489</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G378" t="n">
-        <v>2.91782164573669</v>
+        <v>2.91782140731812</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G382" t="n">
-        <v>2.95362329483032</v>
+        <v>2.9536235332489</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G383" t="n">
-        <v>2.95362329483032</v>
+        <v>2.9536235332489</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G384" t="n">
-        <v>3.00732517242432</v>
+        <v>3.0073254108429</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G385" t="n">
-        <v>2.95362329483032</v>
+        <v>2.9536235332489</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G386" t="n">
-        <v>2.91782164573669</v>
+        <v>2.91782140731812</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G390" t="n">
-        <v>2.81041741371155</v>
+        <v>2.81041765213013</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G393" t="n">
-        <v>2.89992117881775</v>
+        <v>2.89992094039917</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G395" t="n">
-        <v>3.06102800369263</v>
+        <v>3.06102776527405</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G397" t="n">
-        <v>3.17738270759583</v>
+        <v>3.17738246917725</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G398" t="n">
-        <v>3.17738270759583</v>
+        <v>3.17738246917725</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>3.22213411331177</v>
+        <v>3.22213459014893</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G403" t="n">
-        <v>3.31163811683655</v>
+        <v>3.31163787841797</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G406" t="n">
-        <v>3.49959588050842</v>
+        <v>3.49959635734558</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G407" t="n">
-        <v>3.50854635238647</v>
+        <v>3.5085461139679</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G408" t="n">
-        <v>3.66965270042419</v>
+        <v>3.66965293884277</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4</v>
       </c>
       <c r="G412" t="n">
-        <v>3.58014917373657</v>
+        <v>3.58014941215515</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G413" t="n">
-        <v>3.58909964561462</v>
+        <v>3.58910012245178</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G415" t="n">
-        <v>3.6607027053833</v>
+        <v>3.66070294380188</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G417" t="n">
-        <v>3.49064588546753</v>
+        <v>3.49064564704895</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G419" t="n">
-        <v>3.66965270042419</v>
+        <v>3.66965293884277</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>4</v>
       </c>
       <c r="G420" t="n">
-        <v>3.58014917373657</v>
+        <v>3.58014941215515</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G421" t="n">
-        <v>3.66965270042419</v>
+        <v>3.66965293884277</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G422" t="n">
-        <v>3.66965270042419</v>
+        <v>3.66965293884277</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G423" t="n">
-        <v>3.58909964561462</v>
+        <v>3.58910012245178</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G425" t="n">
-        <v>3.62490153312683</v>
+        <v>3.62490129470825</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>4</v>
       </c>
       <c r="G427" t="n">
-        <v>3.58014917373657</v>
+        <v>3.58014941215515</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G429" t="n">
-        <v>3.58909964561462</v>
+        <v>3.58910012245178</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G430" t="n">
-        <v>3.69650459289551</v>
+        <v>3.69650363922119</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G431" t="n">
-        <v>3.75020623207092</v>
+        <v>3.75020718574524</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G432" t="n">
-        <v>3.78600788116455</v>
+        <v>3.78600764274597</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G433" t="n">
-        <v>3.90236282348633</v>
+        <v>3.90236330032349</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G435" t="n">
-        <v>4.14402341842651</v>
+        <v>4.14402198791504</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>4.75</v>
       </c>
       <c r="G438" t="n">
-        <v>4.25142621994019</v>
+        <v>4.25142669677734</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G439" t="n">
-        <v>4.11717128753662</v>
+        <v>4.11717176437378</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G440" t="n">
-        <v>4.37673282623291</v>
+        <v>4.37673234939575</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>4.43043422698975</v>
+        <v>4.4304347038269</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G444" t="n">
-        <v>4.14402341842651</v>
+        <v>4.14402198791504</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G446" t="n">
-        <v>3.90236282348633</v>
+        <v>3.90236330032349</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G447" t="n">
-        <v>3.92026329040527</v>
+        <v>3.92026352882385</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G448" t="n">
-        <v>3.76810693740845</v>
+        <v>3.76810717582703</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G450" t="n">
-        <v>3.66965270042419</v>
+        <v>3.66965293884277</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G451" t="n">
-        <v>3.70545434951782</v>
+        <v>3.7054545879364</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G452" t="n">
-        <v>3.9292140007019</v>
+        <v>3.92921376228333</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G454" t="n">
-        <v>4.14402341842651</v>
+        <v>4.14402198791504</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G456" t="n">
-        <v>4.05451965332031</v>
+        <v>4.05451917648315</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G457" t="n">
-        <v>4.20667552947998</v>
+        <v>4.20667600631714</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G459" t="n">
-        <v>4.26037836074829</v>
+        <v>4.26037788391113</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G460" t="n">
-        <v>4.3409309387207</v>
+        <v>4.34093046188354</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G462" t="n">
-        <v>4.44833517074585</v>
+        <v>4.44833564758301</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G463" t="n">
-        <v>4.3230299949646</v>
+        <v>4.32303047180176</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G464" t="n">
-        <v>4.42148494720459</v>
+        <v>4.42148399353027</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G465" t="n">
-        <v>4.37673282623291</v>
+        <v>4.37673234939575</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G467" t="n">
-        <v>4.37673282623291</v>
+        <v>4.37673234939575</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G471" t="n">
-        <v>4.20667552947998</v>
+        <v>4.20667600631714</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G472" t="n">
-        <v>4.38917779922485</v>
+        <v>4.3891773223877</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G473" t="n">
-        <v>4.2888011932373</v>
+        <v>4.28880214691162</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G474" t="n">
-        <v>4.37092685699463</v>
+        <v>4.37092733383179</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G476" t="n">
-        <v>4.2888011932373</v>
+        <v>4.28880214691162</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G477" t="n">
-        <v>4.34355211257935</v>
+        <v>4.3435525894165</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G478" t="n">
-        <v>4.34355211257935</v>
+        <v>4.3435525894165</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G479" t="n">
-        <v>4.34355211257935</v>
+        <v>4.3435525894165</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G480" t="n">
-        <v>4.34355211257935</v>
+        <v>4.3435525894165</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G481" t="n">
-        <v>4.27055072784424</v>
+        <v>4.2705512046814</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G482" t="n">
-        <v>4.26142597198486</v>
+        <v>4.26142644882202</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G483" t="n">
-        <v>4.2888011932373</v>
+        <v>4.28880214691162</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G484" t="n">
-        <v>4.21580028533936</v>
+        <v>4.21580076217651</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G485" t="n">
-        <v>4.2888011932373</v>
+        <v>4.28880214691162</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G486" t="n">
-        <v>4.35267686843872</v>
+        <v>4.35267734527588</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G487" t="n">
-        <v>4.36180305480957</v>
+        <v>4.36180257797241</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G488" t="n">
-        <v>4.36180305480957</v>
+        <v>4.36180257797241</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G489" t="n">
-        <v>4.34355211257935</v>
+        <v>4.3435525894165</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G490" t="n">
-        <v>4.2888011932373</v>
+        <v>4.28880214691162</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G491" t="n">
-        <v>4.2888011932373</v>
+        <v>4.28880214691162</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>4.75</v>
       </c>
       <c r="G492" t="n">
-        <v>4.3344259262085</v>
+        <v>4.33442640304565</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>4.75</v>
       </c>
       <c r="G493" t="n">
-        <v>4.3344259262085</v>
+        <v>4.33442640304565</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G494" t="n">
-        <v>4.2431755065918</v>
+        <v>4.24317646026611</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G495" t="n">
-        <v>4.38005256652832</v>
+        <v>4.38005304336548</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G496" t="n">
-        <v>4.34355211257935</v>
+        <v>4.3435525894165</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G497" t="n">
-        <v>4.38005256652832</v>
+        <v>4.38005304336548</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>4.75</v>
       </c>
       <c r="G498" t="n">
-        <v>4.3344259262085</v>
+        <v>4.33442640304565</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>4.75</v>
       </c>
       <c r="G499" t="n">
-        <v>4.3344259262085</v>
+        <v>4.33442640304565</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G500" t="n">
-        <v>4.38005256652832</v>
+        <v>4.38005304336548</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G501" t="n">
-        <v>4.37092685699463</v>
+        <v>4.37092733383179</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G502" t="n">
-        <v>4.34355211257935</v>
+        <v>4.3435525894165</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>4.75</v>
       </c>
       <c r="G503" t="n">
-        <v>4.3344259262085</v>
+        <v>4.33442640304565</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G507" t="n">
-        <v>4.38005256652832</v>
+        <v>4.38005304336548</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G508" t="n">
-        <v>4.38005256652832</v>
+        <v>4.38005304336548</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G510" t="n">
-        <v>4.32530212402344</v>
+        <v>4.32530164718628</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G512" t="n">
-        <v>4.32530212402344</v>
+        <v>4.32530164718628</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G513" t="n">
-        <v>4.30705118179321</v>
+        <v>4.30705165863037</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>4.75</v>
       </c>
       <c r="G514" t="n">
-        <v>4.3344259262085</v>
+        <v>4.33442640304565</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G515" t="n">
-        <v>4.30705118179321</v>
+        <v>4.30705165863037</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G516" t="n">
-        <v>4.2888011932373</v>
+        <v>4.28880214691162</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G517" t="n">
-        <v>4.30705118179321</v>
+        <v>4.30705165863037</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G519" t="n">
-        <v>4.59905529022217</v>
+        <v>4.59905576705933</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G524" t="n">
-        <v>4.63555526733398</v>
+        <v>4.63555574417114</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G525" t="n">
-        <v>4.72680711746216</v>
+        <v>4.72680616378784</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G527" t="n">
-        <v>4.90930891036987</v>
+        <v>4.90930938720703</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G528" t="n">
-        <v>4.90930891036987</v>
+        <v>4.90930938720703</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>4.92755842208862</v>
+        <v>4.9275598526001</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G531" t="n">
-        <v>4.94580888748169</v>
+        <v>4.94580936431885</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G534" t="n">
-        <v>5.16481161117554</v>
+        <v>5.1648120880127</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G535" t="n">
-        <v>5.20131206512451</v>
+        <v>5.20131254196167</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G537" t="n">
-        <v>5.1830620765686</v>
+        <v>5.18306255340576</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G538" t="n">
-        <v>5.16481161117554</v>
+        <v>5.1648120880127</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G539" t="n">
-        <v>5.16481161117554</v>
+        <v>5.1648120880127</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G541" t="n">
-        <v>5.00056028366089</v>
+        <v>5.00055980682373</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G545" t="n">
-        <v>5.05531120300293</v>
+        <v>5.05531024932861</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G546" t="n">
-        <v>5.14656162261963</v>
+        <v>5.14656209945679</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G547" t="n">
-        <v>5.14656162261963</v>
+        <v>5.14656209945679</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G548" t="n">
-        <v>5.20131206512451</v>
+        <v>5.20131254196167</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G549" t="n">
-        <v>5.16481161117554</v>
+        <v>5.1648120880127</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G550" t="n">
-        <v>5.1283106803894</v>
+        <v>5.12831115722656</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G551" t="n">
-        <v>5.1830620765686</v>
+        <v>5.18306255340576</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G552" t="n">
-        <v>5.16481161117554</v>
+        <v>5.1648120880127</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G555" t="n">
-        <v>5.25606298446655</v>
+        <v>5.25606346130371</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G556" t="n">
-        <v>5.3290638923645</v>
+        <v>5.32906341552734</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G557" t="n">
-        <v>5.42031478881836</v>
+        <v>5.42031526565552</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>6</v>
       </c>
       <c r="G558" t="n">
-        <v>5.4750657081604</v>
+        <v>5.47506618499756</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G559" t="n">
-        <v>5.60281705856323</v>
+        <v>5.60281658172607</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G560" t="n">
-        <v>5.73056888580322</v>
+        <v>5.73056936264038</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G561" t="n">
-        <v>5.49331569671631</v>
+        <v>5.49331617355347</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>6</v>
       </c>
       <c r="G563" t="n">
-        <v>5.4750657081604</v>
+        <v>5.47506618499756</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G564" t="n">
-        <v>5.42031478881836</v>
+        <v>5.42031526565552</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G565" t="n">
-        <v>5.3290638923645</v>
+        <v>5.32906341552734</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G569" t="n">
-        <v>5.25606298446655</v>
+        <v>5.25606346130371</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G571" t="n">
-        <v>5.3290638923645</v>
+        <v>5.32906341552734</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>6</v>
       </c>
       <c r="G572" t="n">
-        <v>5.4750657081604</v>
+        <v>5.47506618499756</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>6</v>
       </c>
       <c r="G573" t="n">
-        <v>5.4750657081604</v>
+        <v>5.47506618499756</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G574" t="n">
-        <v>5.42031478881836</v>
+        <v>5.42031526565552</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G575" t="n">
-        <v>5.40206432342529</v>
+        <v>5.40206527709961</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G576" t="n">
-        <v>5.31081390380859</v>
+        <v>5.31081485748291</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G578" t="n">
-        <v>5.36556386947632</v>
+        <v>5.36556434631348</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G579" t="n">
-        <v>5.34731388092041</v>
+        <v>5.34731435775757</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G580" t="n">
-        <v>5.42031478881836</v>
+        <v>5.42031526565552</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G581" t="n">
-        <v>5.45681524276733</v>
+        <v>5.45681571960449</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G582" t="n">
-        <v>5.49331569671631</v>
+        <v>5.49331617355347</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G586" t="n">
-        <v>5.42031478881836</v>
+        <v>5.42031526565552</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>6</v>
       </c>
       <c r="G587" t="n">
-        <v>5.4750657081604</v>
+        <v>5.47506618499756</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>6</v>
       </c>
       <c r="G588" t="n">
-        <v>5.4750657081604</v>
+        <v>5.47506618499756</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>6</v>
       </c>
       <c r="G591" t="n">
-        <v>5.4750657081604</v>
+        <v>5.47506618499756</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>6</v>
       </c>
       <c r="G592" t="n">
-        <v>5.4750657081604</v>
+        <v>5.47506618499756</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>6</v>
       </c>
       <c r="G593" t="n">
-        <v>5.4750657081604</v>
+        <v>5.47506618499756</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>6</v>
       </c>
       <c r="G595" t="n">
-        <v>5.4750657081604</v>
+        <v>5.47506618499756</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>6</v>
       </c>
       <c r="G596" t="n">
-        <v>5.4750657081604</v>
+        <v>5.47506618499756</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>6</v>
       </c>
       <c r="G597" t="n">
-        <v>5.4750657081604</v>
+        <v>5.47506618499756</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G598" t="n">
-        <v>5.45681524276733</v>
+        <v>5.45681571960449</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G599" t="n">
-        <v>5.51156663894653</v>
+        <v>5.51156616210938</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G600" t="n">
-        <v>5.49331569671631</v>
+        <v>5.49331617355347</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>6</v>
       </c>
       <c r="G601" t="n">
-        <v>5.4750657081604</v>
+        <v>5.47506618499756</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>6</v>
       </c>
       <c r="G602" t="n">
-        <v>5.4750657081604</v>
+        <v>5.47506618499756</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G603" t="n">
-        <v>5.51156663894653</v>
+        <v>5.51156616210938</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>6</v>
       </c>
       <c r="G604" t="n">
-        <v>5.4750657081604</v>
+        <v>5.47506618499756</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G605" t="n">
-        <v>5.51156663894653</v>
+        <v>5.51156616210938</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G607" t="n">
-        <v>5.80356931686401</v>
+        <v>5.80356979370117</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G608" t="n">
-        <v>6.07732248306274</v>
+        <v>6.0773229598999</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G609" t="n">
-        <v>6.29632520675659</v>
+        <v>6.29632568359375</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G610" t="n">
-        <v>6.27807521820068</v>
+        <v>6.27807474136353</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G611" t="n">
-        <v>6.40582656860352</v>
+        <v>6.40582752227783</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G612" t="n">
-        <v>6.49707794189453</v>
+        <v>6.49707841873169</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G613" t="n">
-        <v>6.51532793045044</v>
+        <v>6.51532745361328</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G614" t="n">
-        <v>6.49707794189453</v>
+        <v>6.49707841873169</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G616" t="n">
-        <v>6.49707794189453</v>
+        <v>6.49707841873169</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G617" t="n">
-        <v>6.55182838439941</v>
+        <v>6.55182790756226</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G618" t="n">
-        <v>6.69783115386963</v>
+        <v>6.69783067703247</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G621" t="n">
-        <v>7.13583564758301</v>
+        <v>7.13583612442017</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>8</v>
       </c>
       <c r="G622" t="n">
-        <v>7.30008745193481</v>
+        <v>7.30008792877197</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G623" t="n">
-        <v>7.39133977890015</v>
+        <v>7.39133882522583</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G624" t="n">
-        <v>7.62859201431274</v>
+        <v>7.62859153747559</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G626" t="n">
-        <v>7.73809337615967</v>
+        <v>7.73809242248535</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G627" t="n">
-        <v>7.84759378433228</v>
+        <v>7.84759521484375</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G628" t="n">
-        <v>7.88409376144409</v>
+        <v>7.88409328460693</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G629" t="n">
-        <v>7.84759378433228</v>
+        <v>7.84759521484375</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G630" t="n">
-        <v>7.93884611129761</v>
+        <v>7.93884468078613</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G632" t="n">
-        <v>7.93884611129761</v>
+        <v>7.93884468078613</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G634" t="n">
-        <v>8.43160057067871</v>
+        <v>8.43160152435303</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G635" t="n">
-        <v>8.57760238647461</v>
+        <v>8.57760429382324</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G636" t="n">
-        <v>8.65060424804688</v>
+        <v>8.65060329437256</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G638" t="n">
-        <v>8.65060424804688</v>
+        <v>8.65060329437256</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G639" t="n">
-        <v>8.26735019683838</v>
+        <v>8.26734924316406</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G640" t="n">
-        <v>8.26735019683838</v>
+        <v>8.26734924316406</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G641" t="n">
-        <v>8.55935096740723</v>
+        <v>8.55935287475586</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G642" t="n">
-        <v>8.61410236358643</v>
+        <v>8.61410331726074</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G643" t="n">
-        <v>8.57760238647461</v>
+        <v>8.57760429382324</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G644" t="n">
-        <v>8.43160057067871</v>
+        <v>8.43160152435303</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G646" t="n">
-        <v>8.41335201263428</v>
+        <v>8.41335105895996</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G647" t="n">
-        <v>8.13959693908691</v>
+        <v>8.13959789276123</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G648" t="n">
-        <v>8.3038501739502</v>
+        <v>8.30385112762451</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G649" t="n">
-        <v>8.52285194396973</v>
+        <v>8.52285289764404</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G651" t="n">
-        <v>8.55935096740723</v>
+        <v>8.55935287475586</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G652" t="n">
-        <v>8.54110145568848</v>
+        <v>8.54110240936279</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G653" t="n">
-        <v>8.54110145568848</v>
+        <v>8.54110240936279</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G654" t="n">
-        <v>8.86960506439209</v>
+        <v>8.86960697174072</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G655" t="n">
-        <v>9.08860969543457</v>
+        <v>9.08861064910889</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G656" t="n">
-        <v>9.17073440551758</v>
+        <v>9.17073535919189</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G659" t="n">
-        <v>9.99199485778809</v>
+        <v>9.99199390411377</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G662" t="n">
-        <v>9.67261695861816</v>
+        <v>9.67261791229248</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>10.75</v>
       </c>
       <c r="G667" t="n">
-        <v>9.80949401855469</v>
+        <v>9.80949306488037</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G673" t="n">
-        <v>9.03385734558105</v>
+        <v>9.03385829925537</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G674" t="n">
-        <v>9.3076114654541</v>
+        <v>9.30761241912842</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G676" t="n">
-        <v>9.67261695861816</v>
+        <v>9.67261791229248</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G677" t="n">
-        <v>9.94636917114258</v>
+        <v>9.94637012481689</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G678" t="n">
-        <v>9.99199485778809</v>
+        <v>9.99199390411377</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G679" t="n">
-        <v>9.99199485778809</v>
+        <v>9.99199390411377</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G680" t="n">
-        <v>9.99199485778809</v>
+        <v>9.99199390411377</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G681" t="n">
-        <v>9.99199485778809</v>
+        <v>9.99199390411377</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G682" t="n">
-        <v>9.99199485778809</v>
+        <v>9.99199390411377</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G683" t="n">
-        <v>9.67261695861816</v>
+        <v>9.67261791229248</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G684" t="n">
-        <v>9.67261695861816</v>
+        <v>9.67261791229248</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G685" t="n">
-        <v>9.67261695861816</v>
+        <v>9.67261791229248</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>10.75</v>
       </c>
       <c r="G686" t="n">
-        <v>9.80949401855469</v>
+        <v>9.80949306488037</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G688" t="n">
-        <v>8.90610694885254</v>
+        <v>8.90610790252686</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G689" t="n">
-        <v>9.26198673248291</v>
+        <v>9.26198482513428</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G691" t="n">
-        <v>9.106858253479</v>
+        <v>9.10685920715332</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G692" t="n">
-        <v>8.99735641479492</v>
+        <v>8.99735736846924</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G693" t="n">
-        <v>8.77835559844971</v>
+        <v>8.77835464477539</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G694" t="n">
-        <v>8.97910785675049</v>
+        <v>8.97910690307617</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G695" t="n">
-        <v>8.68710422515869</v>
+        <v>8.68710517883301</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G696" t="n">
-        <v>8.55935096740723</v>
+        <v>8.55935287475586</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G697" t="n">
-        <v>7.84759378433228</v>
+        <v>7.84759521484375</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G698" t="n">
-        <v>7.61034107208252</v>
+        <v>7.61034202575684</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>8</v>
       </c>
       <c r="G700" t="n">
-        <v>7.30008745193481</v>
+        <v>7.30008792877197</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>7.5</v>
       </c>
       <c r="G701" t="n">
-        <v>6.84383153915405</v>
+        <v>6.84383201599121</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G702" t="n">
-        <v>7.26358699798584</v>
+        <v>7.263587474823</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G703" t="n">
-        <v>7.02633380889893</v>
+        <v>7.02633428573608</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G704" t="n">
-        <v>7.02633380889893</v>
+        <v>7.02633428573608</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G706" t="n">
-        <v>7.02633380889893</v>
+        <v>7.02633428573608</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G707" t="n">
-        <v>7.50084018707275</v>
+        <v>7.50084066390991</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G708" t="n">
-        <v>7.5190896987915</v>
+        <v>7.51909017562866</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G709" t="n">
-        <v>7.62859201431274</v>
+        <v>7.62859153747559</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G710" t="n">
-        <v>8.03009605407715</v>
+        <v>8.03009700775146</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G711" t="n">
-        <v>7.64684152603149</v>
+        <v>7.64684343338013</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G712" t="n">
-        <v>7.77459478378296</v>
+        <v>7.77459335327148</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G714" t="n">
-        <v>7.88409376144409</v>
+        <v>7.88409328460693</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G716" t="n">
-        <v>8.32209873199463</v>
+        <v>8.32209968566895</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G717" t="n">
-        <v>8.3038501739502</v>
+        <v>8.30385112762451</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G719" t="n">
-        <v>8.76010513305664</v>
+        <v>8.76010608673096</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G720" t="n">
-        <v>9.03385734558105</v>
+        <v>9.03385829925537</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G721" t="n">
-        <v>9.05210876464844</v>
+        <v>9.05210781097412</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G723" t="n">
-        <v>8.92435741424561</v>
+        <v>8.92435646057129</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>9.05210876464844</v>
+        <v>9.05210781097412</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G725" t="n">
-        <v>9.08860969543457</v>
+        <v>9.08861064910889</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G726" t="n">
-        <v>9.08860969543457</v>
+        <v>9.08861064910889</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>9.67261695861816</v>
+        <v>9.67261791229248</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G732" t="n">
-        <v>9.67261695861816</v>
+        <v>9.67261791229248</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G733" t="n">
-        <v>10.220121383667</v>
+        <v>10.2201232910156</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G734" t="n">
-        <v>10.402624130249</v>
+        <v>10.4026250839233</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G735" t="n">
-        <v>10.3563899993896</v>
+        <v>10.3563919067383</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G737" t="n">
-        <v>10.2176885604858</v>
+        <v>10.2176895141602</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G738" t="n">
-        <v>10.3101577758789</v>
+        <v>10.3101558685303</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G740" t="n">
-        <v>10.4950923919678</v>
+        <v>10.4950933456421</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G741" t="n">
-        <v>10.3101577758789</v>
+        <v>10.3101558685303</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G742" t="n">
-        <v>9.98651885986328</v>
+        <v>9.98652076721191</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G744" t="n">
-        <v>9.98651885986328</v>
+        <v>9.98652076721191</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>10.25</v>
       </c>
       <c r="G747" t="n">
-        <v>9.47794723510742</v>
+        <v>9.47794818878174</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G748" t="n">
-        <v>9.80158615112305</v>
+        <v>9.80158519744873</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G749" t="n">
-        <v>9.98651885986328</v>
+        <v>9.98652076721191</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G750" t="n">
-        <v>9.80158615112305</v>
+        <v>9.80158519744873</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G751" t="n">
-        <v>9.80158615112305</v>
+        <v>9.80158519744873</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G752" t="n">
-        <v>9.61664962768555</v>
+        <v>9.61664867401123</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G753" t="n">
-        <v>9.80158615112305</v>
+        <v>9.80158519744873</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G754" t="n">
-        <v>9.98651885986328</v>
+        <v>9.98652076721191</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G756" t="n">
-        <v>10.3563899993896</v>
+        <v>10.3563919067383</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G757" t="n">
-        <v>10.3101577758789</v>
+        <v>10.3101558685303</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G758" t="n">
-        <v>10.4488592147827</v>
+        <v>10.4488582611084</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G759" t="n">
-        <v>10.4950923919678</v>
+        <v>10.4950933456421</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G760" t="n">
-        <v>10.4488592147827</v>
+        <v>10.4488582611084</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G761" t="n">
-        <v>10.3563899993896</v>
+        <v>10.3563919067383</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G762" t="n">
-        <v>10.3563899993896</v>
+        <v>10.3563919067383</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G763" t="n">
-        <v>10.4488592147827</v>
+        <v>10.4488582611084</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G766" t="n">
-        <v>10.5413255691528</v>
+        <v>10.5413274765015</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G767" t="n">
-        <v>10.5413255691528</v>
+        <v>10.5413274765015</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G768" t="n">
-        <v>11.0036668777466</v>
+        <v>11.0036640167236</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G769" t="n">
-        <v>11.6047058105469</v>
+        <v>11.6047067642212</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G770" t="n">
-        <v>11.9745759963989</v>
+        <v>11.9745779037476</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G771" t="n">
-        <v>12.760552406311</v>
+        <v>12.7605543136597</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>13</v>
       </c>
       <c r="G772" t="n">
-        <v>12.0208110809326</v>
+        <v>12.0208101272583</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G773" t="n">
-        <v>12.2982139587402</v>
+        <v>12.2982149124146</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G775" t="n">
-        <v>12.1132783889771</v>
+        <v>12.1132802963257</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>13</v>
       </c>
       <c r="G776" t="n">
-        <v>12.0208110809326</v>
+        <v>12.0208101272583</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G777" t="n">
-        <v>12.1595125198364</v>
+        <v>12.1595134735107</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G778" t="n">
-        <v>11.9745759963989</v>
+        <v>11.9745779037476</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G779" t="n">
-        <v>11.8821105957031</v>
+        <v>11.8821096420288</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G780" t="n">
-        <v>12.067045211792</v>
+        <v>12.0670442581177</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>13</v>
       </c>
       <c r="G781" t="n">
-        <v>12.0208110809326</v>
+        <v>12.0208101272583</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G782" t="n">
-        <v>11.8821105957031</v>
+        <v>11.8821096420288</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G783" t="n">
-        <v>11.9283437728882</v>
+        <v>11.9283428192139</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G785" t="n">
-        <v>11.9745759963989</v>
+        <v>11.9745779037476</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>12.75</v>
       </c>
       <c r="G786" t="n">
-        <v>11.7896413803101</v>
+        <v>11.7896423339844</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>12.75</v>
       </c>
       <c r="G787" t="n">
-        <v>11.7896413803101</v>
+        <v>11.7896423339844</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>11.8821105957031</v>
+        <v>11.8821096420288</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>13</v>
       </c>
       <c r="G789" t="n">
-        <v>12.0208110809326</v>
+        <v>12.0208101272583</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G790" t="n">
-        <v>11.9283437728882</v>
+        <v>11.9283428192139</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G792" t="n">
-        <v>11.6509408950806</v>
+        <v>11.6509399414062</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G794" t="n">
-        <v>11.6509408950806</v>
+        <v>11.6509399414062</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>12.75</v>
       </c>
       <c r="G796" t="n">
-        <v>11.7896413803101</v>
+        <v>11.7896423339844</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G798" t="n">
-        <v>11.4197702407837</v>
+        <v>11.419771194458</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>12.25</v>
       </c>
       <c r="G799" t="n">
-        <v>11.3273029327393</v>
+        <v>11.3273019790649</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G800" t="n">
-        <v>11.3735361099243</v>
+        <v>11.3735370635986</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G801" t="n">
-        <v>11.1423692703247</v>
+        <v>11.1423673629761</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G802" t="n">
-        <v>10.8187303543091</v>
+        <v>10.8187294006348</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G803" t="n">
-        <v>11.1423692703247</v>
+        <v>11.1423673629761</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>12.25</v>
       </c>
       <c r="G804" t="n">
-        <v>11.3273029327393</v>
+        <v>11.3273019790649</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>12.25</v>
       </c>
       <c r="G805" t="n">
-        <v>11.3273029327393</v>
+        <v>11.3273019790649</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>12.25</v>
       </c>
       <c r="G806" t="n">
-        <v>11.3273029327393</v>
+        <v>11.3273019790649</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G807" t="n">
-        <v>11.2810688018799</v>
+        <v>11.2810697555542</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G808" t="n">
-        <v>11.3735361099243</v>
+        <v>11.3735370635986</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G809" t="n">
-        <v>11.2810688018799</v>
+        <v>11.2810697555542</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G810" t="n">
-        <v>11.4197702407837</v>
+        <v>11.419771194458</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>12.5</v>
       </c>
       <c r="G811" t="n">
-        <v>11.5584716796875</v>
+        <v>11.5584726333618</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>12.5</v>
       </c>
       <c r="G813" t="n">
-        <v>11.5584716796875</v>
+        <v>11.5584726333618</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G814" t="n">
-        <v>11.6509408950806</v>
+        <v>11.6509399414062</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G815" t="n">
-        <v>11.6509408950806</v>
+        <v>11.6509399414062</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>12.75</v>
       </c>
       <c r="G816" t="n">
-        <v>11.7896413803101</v>
+        <v>11.7896423339844</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G817" t="n">
-        <v>11.6509408950806</v>
+        <v>11.6509399414062</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G818" t="n">
-        <v>11.6509408950806</v>
+        <v>11.6509399414062</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G821" t="n">
-        <v>11.2810688018799</v>
+        <v>11.2810697555542</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>12.25</v>
       </c>
       <c r="G822" t="n">
-        <v>11.3273029327393</v>
+        <v>11.3273019790649</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G823" t="n">
-        <v>11.2810688018799</v>
+        <v>11.2810697555542</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G824" t="n">
-        <v>11.6509408950806</v>
+        <v>11.6509399414062</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G825" t="n">
-        <v>11.9745759963989</v>
+        <v>11.9745779037476</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G826" t="n">
-        <v>12.067045211792</v>
+        <v>12.0670442581177</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>12.3444480895996</v>
+        <v>12.3444499969482</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G828" t="n">
-        <v>12.8992538452148</v>
+        <v>12.8992557525635</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G829" t="n">
-        <v>13.1304244995117</v>
+        <v>13.1304235458374</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G835" t="n">
-        <v>15.3496513366699</v>
+        <v>15.3496522903442</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G837" t="n">
-        <v>16.3667984008789</v>
+        <v>16.3667964935303</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G838" t="n">
-        <v>16.459264755249</v>
+        <v>16.4592628479004</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G839" t="n">
-        <v>16.2743282318115</v>
+        <v>16.2743301391602</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G842" t="n">
-        <v>16.0431594848633</v>
+        <v>16.0431613922119</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G844" t="n">
-        <v>15.3496513366699</v>
+        <v>15.3496522903442</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G845" t="n">
-        <v>15.1647148132324</v>
+        <v>15.1647157669067</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G846" t="n">
-        <v>14.9335451126099</v>
+        <v>14.9335470199585</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>16.5</v>
       </c>
       <c r="G848" t="n">
-        <v>15.2571849822998</v>
+        <v>15.2571830749512</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G850" t="n">
-        <v>15.6270523071289</v>
+        <v>15.6270551681519</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G851" t="n">
-        <v>15.9969253540039</v>
+        <v>15.9969263076782</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G852" t="n">
-        <v>15.9969253540039</v>
+        <v>15.9969263076782</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G854" t="n">
-        <v>15.3958854675293</v>
+        <v>15.395884513855</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G855" t="n">
-        <v>15.1647148132324</v>
+        <v>15.1647157669067</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>14.9797821044922</v>
+        <v>14.9797811508179</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G862" t="n">
-        <v>12.4369163513184</v>
+        <v>12.436915397644</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G863" t="n">
-        <v>13.0379552841187</v>
+        <v>13.0379571914673</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G864" t="n">
-        <v>13.1304244995117</v>
+        <v>13.1304235458374</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>14.5</v>
       </c>
       <c r="G866" t="n">
-        <v>13.407829284668</v>
+        <v>13.4078273773193</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G867" t="n">
-        <v>15.3496513366699</v>
+        <v>15.3496522903442</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G868" t="n">
-        <v>15.6732902526855</v>
+        <v>15.6732892990112</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>16.5</v>
       </c>
       <c r="G869" t="n">
-        <v>15.2571849822998</v>
+        <v>15.2571830749512</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G870" t="n">
-        <v>15.3496513366699</v>
+        <v>15.3496522903442</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G871" t="n">
-        <v>14.9797821044922</v>
+        <v>14.9797811508179</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>16</v>
       </c>
       <c r="G875" t="n">
-        <v>14.7948436737061</v>
+        <v>14.7948455810547</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G876" t="n">
-        <v>14.1475696563721</v>
+        <v>14.1475687026978</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G878" t="n">
-        <v>14.3787384033203</v>
+        <v>14.3787403106689</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G879" t="n">
-        <v>14.7023773193359</v>
+        <v>14.702374458313</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G880" t="n">
-        <v>14.4712085723877</v>
+        <v>14.4712066650391</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G886" t="n">
-        <v>13.8239307403564</v>
+        <v>13.8239326477051</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G888" t="n">
-        <v>13.3153581619263</v>
+        <v>13.3153610229492</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G893" t="n">
-        <v>13.6852312088013</v>
+        <v>13.685230255127</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>16</v>
       </c>
       <c r="G895" t="n">
-        <v>14.7948436737061</v>
+        <v>14.7948455810547</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>16</v>
       </c>
       <c r="G898" t="n">
-        <v>14.7948436737061</v>
+        <v>14.7948455810547</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G899" t="n">
-        <v>15.6732902526855</v>
+        <v>15.6732892990112</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G901" t="n">
-        <v>15.1647148132324</v>
+        <v>15.1647157669067</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G903" t="n">
-        <v>14.9335451126099</v>
+        <v>14.9335470199585</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G906" t="n">
-        <v>15.5345878601074</v>
+        <v>15.5345859527588</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G907" t="n">
-        <v>15.3496513366699</v>
+        <v>15.3496522903442</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G908" t="n">
-        <v>15.118483543396</v>
+        <v>15.1184825897217</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G909" t="n">
-        <v>14.9335451126099</v>
+        <v>14.9335470199585</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>16</v>
       </c>
       <c r="G910" t="n">
-        <v>14.7948436737061</v>
+        <v>14.7948455810547</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G913" t="n">
-        <v>14.2400369644165</v>
+        <v>14.2400379180908</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G917" t="n">
-        <v>14.1475696563721</v>
+        <v>14.1475687026978</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G920" t="n">
-        <v>14.1475696563721</v>
+        <v>14.1475687026978</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G928" t="n">
-        <v>14.3787384033203</v>
+        <v>14.3787403106689</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G933" t="n">
-        <v>15.1647148132324</v>
+        <v>15.1647157669067</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>16</v>
       </c>
       <c r="G934" t="n">
-        <v>14.7948436737061</v>
+        <v>14.7948455810547</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G935" t="n">
-        <v>14.7023773193359</v>
+        <v>14.702374458313</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G936" t="n">
-        <v>14.9797821044922</v>
+        <v>14.9797811508179</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G940" t="n">
-        <v>14.7023773193359</v>
+        <v>14.702374458313</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G943" t="n">
-        <v>14.7023773193359</v>
+        <v>14.702374458313</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G945" t="n">
-        <v>14.3787384033203</v>
+        <v>14.3787403106689</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G947" t="n">
-        <v>14.6099100112915</v>
+        <v>14.6099090576172</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G950" t="n">
-        <v>13.6852312088013</v>
+        <v>13.685230255127</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G959" t="n">
-        <v>14.1475696563721</v>
+        <v>14.1475687026978</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G963" t="n">
-        <v>13.2691268920898</v>
+        <v>13.2691259384155</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G966" t="n">
-        <v>14.1475696563721</v>
+        <v>14.1475687026978</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G967" t="n">
-        <v>14.4712085723877</v>
+        <v>14.4712066650391</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>15.5</v>
       </c>
       <c r="G970" t="n">
-        <v>14.3325052261353</v>
+        <v>14.3325061798096</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G971" t="n">
-        <v>14.6099100112915</v>
+        <v>14.6099090576172</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G974" t="n">
-        <v>14.4804544448853</v>
+        <v>14.4804534912109</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G975" t="n">
-        <v>14.350998878479</v>
+        <v>14.3509998321533</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G976" t="n">
-        <v>14.5359354019165</v>
+        <v>14.5359344482422</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G977" t="n">
-        <v>14.7023773193359</v>
+        <v>14.702374458313</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>16</v>
       </c>
       <c r="G978" t="n">
-        <v>14.7948436737061</v>
+        <v>14.7948455810547</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>16</v>
       </c>
       <c r="G979" t="n">
-        <v>14.7948436737061</v>
+        <v>14.7948455810547</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G982" t="n">
-        <v>14.7763509750366</v>
+        <v>14.7763500213623</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>16</v>
       </c>
       <c r="G985" t="n">
-        <v>14.7948436737061</v>
+        <v>14.7948455810547</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G987" t="n">
-        <v>14.998272895813</v>
+        <v>14.9982738494873</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G990" t="n">
-        <v>14.5359354019165</v>
+        <v>14.5359344482422</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G991" t="n">
-        <v>14.7023773193359</v>
+        <v>14.702374458313</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G992" t="n">
-        <v>14.9612855911255</v>
+        <v>14.9612865447998</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G993" t="n">
-        <v>14.9612855911255</v>
+        <v>14.9612865447998</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G994" t="n">
-        <v>15.2637691497803</v>
+        <v>15.2637701034546</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G995" t="n">
-        <v>14.8728685379028</v>
+        <v>14.8728675842285</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G996" t="n">
-        <v>14.5191965103149</v>
+        <v>14.5191955566406</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G998" t="n">
-        <v>14.9845542907715</v>
+        <v>14.9845552444458</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G999" t="n">
-        <v>15.1334686279297</v>
+        <v>15.133469581604</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1000" t="n">
-        <v>15.1706962585449</v>
+        <v>15.1706972122192</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1003" t="n">
-        <v>14.9845542907715</v>
+        <v>14.9845552444458</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>17.75</v>
       </c>
       <c r="G1006" t="n">
-        <v>16.5202388763428</v>
+        <v>16.5202407836914</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1009" t="n">
-        <v>17.981466293335</v>
+        <v>17.9814643859863</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G1011" t="n">
-        <v>17.460262298584</v>
+        <v>17.4602642059326</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1012" t="n">
-        <v>17.2741203308105</v>
+        <v>17.2741184234619</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1013" t="n">
-        <v>17.4044189453125</v>
+        <v>17.4044208526611</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G1016" t="n">
-        <v>16.5295467376709</v>
+        <v>16.5295448303223</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1017" t="n">
-        <v>16.2503318786621</v>
+        <v>16.2503299713135</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1018" t="n">
-        <v>16.473705291748</v>
+        <v>16.4737033843994</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1020" t="n">
-        <v>16.4923152923584</v>
+        <v>16.492317199707</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G1021" t="n">
-        <v>16.7715301513672</v>
+        <v>16.7715339660645</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G1022" t="n">
-        <v>17.1624355316162</v>
+        <v>17.1624336242676</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1023" t="n">
-        <v>17.5905666351318</v>
+        <v>17.5905647277832</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1024" t="n">
-        <v>17.4974918365479</v>
+        <v>17.4974937438965</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1025" t="n">
-        <v>17.4974918365479</v>
+        <v>17.4974937438965</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1026" t="n">
-        <v>17.4974918365479</v>
+        <v>17.4974937438965</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1027" t="n">
-        <v>17.981466293335</v>
+        <v>17.9814643859863</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G1028" t="n">
-        <v>17.7208652496338</v>
+        <v>17.7208671569824</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1029" t="n">
-        <v>17.7767086029053</v>
+        <v>17.7767066955566</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1030" t="n">
-        <v>17.7767086029053</v>
+        <v>17.7767066955566</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G1031" t="n">
-        <v>17.665018081665</v>
+        <v>17.6650218963623</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1033" t="n">
-        <v>17.7767086029053</v>
+        <v>17.7767066955566</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1040" t="n">
-        <v>18.3351421356201</v>
+        <v>18.3351402282715</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G1041" t="n">
-        <v>18.4095973968506</v>
+        <v>18.4095993041992</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1043" t="n">
-        <v>17.441650390625</v>
+        <v>17.4416484832764</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1045" t="n">
-        <v>17.5347213745117</v>
+        <v>17.5347194671631</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G1046" t="n">
-        <v>17.348575592041</v>
+        <v>17.3485774993896</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1047" t="n">
-        <v>17.5905666351318</v>
+        <v>17.5905647277832</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1048" t="n">
-        <v>17.5905666351318</v>
+        <v>17.5905647277832</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1049" t="n">
-        <v>17.7394771575928</v>
+        <v>17.7394790649414</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1052" t="n">
-        <v>17.981466293335</v>
+        <v>17.9814643859863</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1054" t="n">
-        <v>18.5212802886963</v>
+        <v>18.5212783813477</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1058" t="n">
-        <v>20.6153964996338</v>
+        <v>20.6153984069824</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1059" t="n">
-        <v>20.5688591003418</v>
+        <v>20.5688610076904</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1060" t="n">
-        <v>20.8480739593506</v>
+        <v>20.8480758666992</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1061" t="n">
-        <v>21.4995765686035</v>
+        <v>21.4995784759521</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1063" t="n">
-        <v>21.4995765686035</v>
+        <v>21.4995784759521</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>24.5</v>
       </c>
       <c r="G1066" t="n">
-        <v>22.802583694458</v>
+        <v>22.8025817871094</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>23.9599990844727</v>
       </c>
       <c r="G1067" t="n">
-        <v>22.299991607666</v>
+        <v>22.2999954223633</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G1068" t="n">
-        <v>22.2255363464355</v>
+        <v>22.2255382537842</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>23.9599990844727</v>
       </c>
       <c r="G1069" t="n">
-        <v>22.299991607666</v>
+        <v>22.2999954223633</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>23.5</v>
       </c>
       <c r="G1072" t="n">
-        <v>21.8718662261963</v>
+        <v>21.871862411499</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>23.7600002288818</v>
       </c>
       <c r="G1073" t="n">
-        <v>22.1138534545898</v>
+        <v>22.1138515472412</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>25.2199993133545</v>
       </c>
       <c r="G1076" t="n">
-        <v>23.4726963043213</v>
+        <v>23.4727001190186</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>25.5</v>
       </c>
       <c r="G1078" t="n">
-        <v>23.7333011627197</v>
+        <v>23.7333030700684</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>26.4599990844727</v>
       </c>
       <c r="G1079" t="n">
-        <v>24.6267910003662</v>
+        <v>24.6267890930176</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>25.6200008392334</v>
       </c>
       <c r="G1080" t="n">
-        <v>23.8449878692627</v>
+        <v>23.8449859619141</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>27.0599994659424</v>
       </c>
       <c r="G1082" t="n">
-        <v>25.1852226257324</v>
+        <v>25.1852207183838</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1083" t="n">
-        <v>24.384801864624</v>
+        <v>24.3848037719727</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>26.9200000762939</v>
       </c>
       <c r="G1085" t="n">
-        <v>25.0549201965332</v>
+        <v>25.0549221038818</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>26.1599998474121</v>
       </c>
       <c r="G1089" t="n">
-        <v>24.3475742340088</v>
+        <v>24.3475723266602</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>27.3199996948242</v>
       </c>
       <c r="G1090" t="n">
-        <v>25.4272060394287</v>
+        <v>25.4272079467773</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>27.2199993133545</v>
       </c>
       <c r="G1091" t="n">
-        <v>25.3341369628906</v>
+        <v>25.334135055542</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>26.5599994659424</v>
       </c>
       <c r="G1092" t="n">
-        <v>24.7198600769043</v>
+        <v>24.7198619842529</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1094" t="n">
-        <v>24.0125179290771</v>
+        <v>24.0125160217285</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>24.5200004577637</v>
       </c>
       <c r="G1095" t="n">
-        <v>22.8211994171143</v>
+        <v>22.8211975097656</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>24.5</v>
       </c>
       <c r="G1096" t="n">
-        <v>22.802583694458</v>
+        <v>22.8025817871094</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>24.5400009155273</v>
       </c>
       <c r="G1097" t="n">
-        <v>22.8398132324219</v>
+        <v>22.8398151397705</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G1099" t="n">
-        <v>22.8770408630371</v>
+        <v>22.8770389556885</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1103" t="n">
-        <v>23.6402282714844</v>
+        <v>23.6402263641357</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1105" t="n">
-        <v>24.1055850982666</v>
+        <v>24.1055870056152</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1109" t="n">
-        <v>26.804666519165</v>
+        <v>26.8046703338623</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>29</v>
       </c>
       <c r="G1110" t="n">
-        <v>26.990816116333</v>
+        <v>26.9908103942871</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1111" t="n">
-        <v>26.804666519165</v>
+        <v>26.8046703338623</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>32.3800010681152</v>
       </c>
       <c r="G1113" t="n">
-        <v>30.1366405487061</v>
+        <v>30.1366424560547</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G1114" t="n">
-        <v>29.6898937225342</v>
+        <v>29.6898956298828</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>31.8600006103516</v>
       </c>
       <c r="G1115" t="n">
-        <v>29.6526660919189</v>
+        <v>29.6526641845703</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>30.9799995422363</v>
       </c>
       <c r="G1116" t="n">
-        <v>28.8336353302002</v>
+        <v>28.8336315155029</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>32.1199989318848</v>
       </c>
       <c r="G1121" t="n">
-        <v>29.8946514129639</v>
+        <v>29.8946533203125</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>33.7200012207031</v>
       </c>
       <c r="G1124" t="n">
-        <v>31.3838005065918</v>
+        <v>31.3838024139404</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>33.5800018310547</v>
       </c>
       <c r="G1125" t="n">
-        <v>31.2535018920898</v>
+        <v>31.2534980773926</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>33</v>
       </c>
       <c r="G1126" t="n">
-        <v>30.7136859893799</v>
+        <v>30.7136840820312</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>33.5400009155273</v>
       </c>
       <c r="G1127" t="n">
-        <v>31.2162704467773</v>
+        <v>31.2162685394287</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>33.5</v>
       </c>
       <c r="G1129" t="n">
-        <v>31.1790409088135</v>
+        <v>31.1790428161621</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>33.6599998474121</v>
       </c>
       <c r="G1130" t="n">
-        <v>31.327953338623</v>
+        <v>31.3279571533203</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1131" t="n">
-        <v>31.830545425415</v>
+        <v>31.8305435180664</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>32.9599990844727</v>
       </c>
       <c r="G1132" t="n">
-        <v>30.6764507293701</v>
+        <v>30.6764526367188</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1133" t="n">
-        <v>30.5275382995605</v>
+        <v>30.5275402069092</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1135" t="n">
-        <v>28.9453182220459</v>
+        <v>28.9453201293945</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>32.4199981689453</v>
       </c>
       <c r="G1136" t="n">
-        <v>30.1738681793213</v>
+        <v>30.173864364624</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>32.6399993896484</v>
       </c>
       <c r="G1137" t="n">
-        <v>30.3786277770996</v>
+        <v>30.378625869751</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>32.4799995422363</v>
       </c>
       <c r="G1138" t="n">
-        <v>30.2297115325928</v>
+        <v>30.2297096252441</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>33</v>
       </c>
       <c r="G1139" t="n">
-        <v>30.7136859893799</v>
+        <v>30.7136840820312</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>32.8199996948242</v>
       </c>
       <c r="G1140" t="n">
-        <v>30.5461559295654</v>
+        <v>30.5461540222168</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>33.7200012207031</v>
       </c>
       <c r="G1142" t="n">
-        <v>31.3838005065918</v>
+        <v>31.3838024139404</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>34.439998626709</v>
       </c>
       <c r="G1144" t="n">
-        <v>32.0539131164551</v>
+        <v>32.0539207458496</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>36.1199989318848</v>
       </c>
       <c r="G1145" t="n">
-        <v>33.6175231933594</v>
+        <v>33.6175193786621</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>35.2599983215332</v>
       </c>
       <c r="G1146" t="n">
-        <v>32.8171081542969</v>
+        <v>32.8171043395996</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G1147" t="n">
-        <v>32.7612609863281</v>
+        <v>32.7612648010254</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>36</v>
       </c>
       <c r="G1148" t="n">
-        <v>33.5058403015137</v>
+        <v>33.5058364868164</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>36.1399993896484</v>
       </c>
       <c r="G1149" t="n">
-        <v>33.6361389160156</v>
+        <v>33.6361351013184</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>33.9199981689453</v>
       </c>
       <c r="G1153" t="n">
-        <v>31.5699462890625</v>
+        <v>31.5699443817139</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>34.1800003051758</v>
       </c>
       <c r="G1154" t="n">
-        <v>31.8119316101074</v>
+        <v>31.8119297027588</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1155" t="n">
-        <v>32.2028312683105</v>
+        <v>32.2028350830078</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>35.7400016784668</v>
       </c>
       <c r="G1159" t="n">
-        <v>33.2638473510742</v>
+        <v>33.2638511657715</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>35.8400001525879</v>
       </c>
       <c r="G1161" t="n">
-        <v>33.3569259643555</v>
+        <v>33.3569221496582</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>37.9799995422363</v>
       </c>
       <c r="G1163" t="n">
-        <v>35.3486518859863</v>
+        <v>35.3486595153809</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>38.060001373291</v>
       </c>
       <c r="G1165" t="n">
-        <v>35.4231185913086</v>
+        <v>35.4231147766113</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>36</v>
       </c>
       <c r="G1166" t="n">
-        <v>33.5058403015137</v>
+        <v>33.5058364868164</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>33.5400009155273</v>
       </c>
       <c r="G1167" t="n">
-        <v>31.2162704467773</v>
+        <v>31.2162685394287</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>34</v>
       </c>
       <c r="G1168" t="n">
-        <v>31.6444034576416</v>
+        <v>31.644401550293</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G1169" t="n">
-        <v>32.4820518493652</v>
+        <v>32.4820442199707</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>35.5</v>
       </c>
       <c r="G1170" t="n">
-        <v>33.0404777526855</v>
+        <v>33.0404815673828</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G1171" t="n">
-        <v>32.4820518493652</v>
+        <v>32.4820442199707</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1172" t="n">
-        <v>32.2028312683105</v>
+        <v>32.2028350830078</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>33.439998626709</v>
       </c>
       <c r="G1173" t="n">
-        <v>31.1231994628906</v>
+        <v>31.1232013702393</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>33.3800010681152</v>
       </c>
       <c r="G1174" t="n">
-        <v>31.0673561096191</v>
+        <v>31.0673542022705</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>34.7400016784668</v>
       </c>
       <c r="G1175" t="n">
-        <v>32.3331336975098</v>
+        <v>32.3331298828125</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1176" t="n">
-        <v>30.8998279571533</v>
+        <v>30.8998260498047</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>30.0599994659424</v>
       </c>
       <c r="G1181" t="n">
-        <v>27.9773712158203</v>
+        <v>27.9773731231689</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>32.9799995422363</v>
       </c>
       <c r="G1183" t="n">
-        <v>30.695068359375</v>
+        <v>30.6950740814209</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>32.5400009155273</v>
       </c>
       <c r="G1184" t="n">
-        <v>30.2855529785156</v>
+        <v>30.2855548858643</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31179,7 +31179,7 @@
         <v>31.0200004577637</v>
       </c>
       <c r="G1185" t="n">
-        <v>28.8708610534668</v>
+        <v>28.8708629608154</v>
       </c>
       <c r="H1185" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1187" t="n">
-        <v>27.735387802124</v>
+        <v>27.7353858947754</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>30.1399993896484</v>
       </c>
       <c r="G1189" t="n">
-        <v>28.0518283843994</v>
+        <v>28.051830291748</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>29</v>
       </c>
       <c r="G1190" t="n">
-        <v>26.990816116333</v>
+        <v>26.9908103942871</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>28.7800006866455</v>
       </c>
       <c r="G1192" t="n">
-        <v>26.7860546112061</v>
+        <v>26.7860527038574</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>29.9799995422363</v>
       </c>
       <c r="G1194" t="n">
-        <v>27.9029140472412</v>
+        <v>27.9029159545898</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G1197" t="n">
-        <v>26.3579273223877</v>
+        <v>26.3579235076904</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G1199" t="n">
-        <v>26.190393447876</v>
+        <v>26.1903972625732</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>28.8799991607666</v>
       </c>
       <c r="G1201" t="n">
-        <v>26.8791236877441</v>
+        <v>26.8791275024414</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>28.5599994659424</v>
       </c>
       <c r="G1202" t="n">
-        <v>26.5812969207764</v>
+        <v>26.5812950134277</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>28.8799991607666</v>
       </c>
       <c r="G1203" t="n">
-        <v>26.8791236877441</v>
+        <v>26.8791275024414</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>28.5</v>
       </c>
       <c r="G1204" t="n">
-        <v>26.5254535675049</v>
+        <v>26.5254554748535</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>26.0400009155273</v>
       </c>
       <c r="G1206" t="n">
-        <v>24.2358894348145</v>
+        <v>24.2358913421631</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31803,7 +31803,7 @@
         <v>28.2199993133545</v>
       </c>
       <c r="G1209" t="n">
-        <v>26.2648525238037</v>
+        <v>26.2648544311523</v>
       </c>
       <c r="H1209" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>27.1200008392334</v>
       </c>
       <c r="G1210" t="n">
-        <v>25.2410659790039</v>
+        <v>25.2410640716553</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G1211" t="n">
-        <v>26.190393447876</v>
+        <v>26.1903972625732</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>28.2399997711182</v>
       </c>
       <c r="G1213" t="n">
-        <v>26.28346824646</v>
+        <v>26.2834663391113</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>29.8799991607666</v>
       </c>
       <c r="G1215" t="n">
-        <v>27.8098449707031</v>
+        <v>27.8098430633545</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>28.8400001525879</v>
       </c>
       <c r="G1217" t="n">
-        <v>26.8418998718262</v>
+        <v>26.8418979644775</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1218" t="n">
-        <v>27.6423168182373</v>
+        <v>27.6423149108887</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1219" t="n">
-        <v>27.735387802124</v>
+        <v>27.7353858947754</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1221" t="n">
-        <v>28.2938175201416</v>
+        <v>28.2938194274902</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>29.6399993896484</v>
       </c>
       <c r="G1227" t="n">
-        <v>27.5864715576172</v>
+        <v>27.5864734649658</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1229" t="n">
-        <v>25.9670219421387</v>
+        <v>25.9670238494873</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>27.7399997711182</v>
       </c>
       <c r="G1230" t="n">
-        <v>25.8181095123291</v>
+        <v>25.8181056976318</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1231" t="n">
-        <v>26.2462368011475</v>
+        <v>26.2462406158447</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32401,7 +32401,7 @@
         <v>28.4400005340576</v>
       </c>
       <c r="G1232" t="n">
-        <v>26.4696102142334</v>
+        <v>26.469612121582</v>
       </c>
       <c r="H1232" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1233" t="n">
-        <v>26.6185264587402</v>
+        <v>26.6185245513916</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1235" t="n">
-        <v>25.8739528656006</v>
+        <v>25.873950958252</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32505,7 +32505,7 @@
         <v>27.7000007629395</v>
       </c>
       <c r="G1236" t="n">
-        <v>25.7808799743652</v>
+        <v>25.7808818817139</v>
       </c>
       <c r="H1236" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>26.7600002288818</v>
       </c>
       <c r="G1239" t="n">
-        <v>24.906005859375</v>
+        <v>24.9060039520264</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G1241" t="n">
-        <v>23.9647331237793</v>
+        <v>23.9647350311279</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>25</v>
       </c>
       <c r="G1242" t="n">
-        <v>23.5317516326904</v>
+        <v>23.5317497253418</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>24.9799995422363</v>
       </c>
       <c r="G1245" t="n">
-        <v>23.5129261016846</v>
+        <v>23.5129241943359</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>25.2600002288818</v>
       </c>
       <c r="G1246" t="n">
-        <v>23.776481628418</v>
+        <v>23.7764797210693</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>23.8199996948242</v>
       </c>
       <c r="G1247" t="n">
-        <v>22.4210510253906</v>
+        <v>22.421049118042</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G1248" t="n">
-        <v>21.6680374145508</v>
+        <v>21.6680355072021</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>22.5200004577637</v>
       </c>
       <c r="G1249" t="n">
-        <v>21.1974010467529</v>
+        <v>21.1974029541016</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G1250" t="n">
-        <v>20.2749557495117</v>
+        <v>20.2749576568604</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1251" t="n">
-        <v>20.5196876525879</v>
+        <v>20.5196857452393</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G1253" t="n">
-        <v>19.371337890625</v>
+        <v>19.3713359832764</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G1254" t="n">
-        <v>19.653715133667</v>
+        <v>19.6537170410156</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1255" t="n">
-        <v>19.2019062042236</v>
+        <v>19.2019081115723</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G1259" t="n">
-        <v>19.6913681030273</v>
+        <v>19.691370010376</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>21.1599998474121</v>
       </c>
       <c r="G1260" t="n">
-        <v>19.917272567749</v>
+        <v>19.9172744750977</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G1261" t="n">
-        <v>20.2749557495117</v>
+        <v>20.2749576568604</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1263" t="n">
-        <v>19.6725425720215</v>
+        <v>19.6725444793701</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G1265" t="n">
-        <v>21.0279712677002</v>
+        <v>21.0279731750488</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>22.3600006103516</v>
       </c>
       <c r="G1267" t="n">
-        <v>21.0467967987061</v>
+        <v>21.0467987060547</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>21</v>
       </c>
       <c r="G1269" t="n">
-        <v>19.7666721343994</v>
+        <v>19.7666702270508</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>21.0599994659424</v>
       </c>
       <c r="G1272" t="n">
-        <v>19.8231449127197</v>
+        <v>19.823148727417</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>20.0200004577637</v>
       </c>
       <c r="G1274" t="n">
-        <v>18.8442249298096</v>
+        <v>18.8442268371582</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G1275" t="n">
-        <v>18.288875579834</v>
+        <v>18.2888774871826</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1276" t="n">
-        <v>17.7429389953613</v>
+        <v>17.74294090271</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1279" t="n">
-        <v>18.2041606903076</v>
+        <v>18.2041625976562</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G1283" t="n">
-        <v>17.9217834472656</v>
+        <v>17.921781539917</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1285" t="n">
-        <v>17.5264492034912</v>
+        <v>17.5264472961426</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G1286" t="n">
-        <v>17.3758430480957</v>
+        <v>17.3758411407471</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G1287" t="n">
-        <v>16.8863830566406</v>
+        <v>16.8863849639893</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1290" t="n">
-        <v>16.0204162597656</v>
+        <v>16.020414352417</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G1293" t="n">
-        <v>17.3852577209473</v>
+        <v>17.3852558135986</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1299" t="n">
-        <v>16.4157485961914</v>
+        <v>16.41575050354</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1300" t="n">
-        <v>16.4534015655518</v>
+        <v>16.4533977508545</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1301" t="n">
-        <v>17.8370685577393</v>
+        <v>17.8370666503906</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G1302" t="n">
-        <v>17.4982109069824</v>
+        <v>17.4982089996338</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G1308" t="n">
-        <v>18.0253200531006</v>
+        <v>18.0253219604492</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>20</v>
       </c>
       <c r="G1309" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>19.7900009155273</v>
       </c>
       <c r="G1310" t="n">
-        <v>18.6277351379395</v>
+        <v>18.6277332305908</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>20</v>
       </c>
       <c r="G1311" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>20</v>
       </c>
       <c r="G1312" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1313" t="n">
-        <v>19.107780456543</v>
+        <v>19.1077823638916</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G1316" t="n">
-        <v>18.288875579834</v>
+        <v>18.2888774871826</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1317" t="n">
-        <v>18.4488925933838</v>
+        <v>18.4488906860352</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G1320" t="n">
-        <v>18.2982902526855</v>
+        <v>18.2982883453369</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1322" t="n">
-        <v>17.5264492034912</v>
+        <v>17.5264472961426</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>18.1700000762939</v>
       </c>
       <c r="G1323" t="n">
-        <v>17.1028747558594</v>
+        <v>17.102876663208</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1324" t="n">
-        <v>17.4887962341309</v>
+        <v>17.4887981414795</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>18</v>
       </c>
       <c r="G1326" t="n">
-        <v>16.9428615570068</v>
+        <v>16.9428596496582</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G1327" t="n">
-        <v>16.7263679504395</v>
+        <v>16.7263698577881</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>18</v>
       </c>
       <c r="G1328" t="n">
-        <v>16.9428615570068</v>
+        <v>16.9428596496582</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G1331" t="n">
-        <v>16.7263679504395</v>
+        <v>16.7263698577881</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>17.1299991607666</v>
       </c>
       <c r="G1333" t="n">
-        <v>16.1239528656006</v>
+        <v>16.1239547729492</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1334" t="n">
-        <v>16.6228275299072</v>
+        <v>16.6228294372559</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1335" t="n">
-        <v>16.6134147644043</v>
+        <v>16.6134166717529</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1336" t="n">
-        <v>16.6134147644043</v>
+        <v>16.6134166717529</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>18</v>
       </c>
       <c r="G1337" t="n">
-        <v>16.9428615570068</v>
+        <v>16.9428596496582</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G1339" t="n">
-        <v>17.6205749511719</v>
+        <v>17.6205730438232</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G1340" t="n">
-        <v>17.3946685791016</v>
+        <v>17.3946704864502</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1341" t="n">
-        <v>16.6793022155762</v>
+        <v>16.6793041229248</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1343" t="n">
-        <v>15.6815595626831</v>
+        <v>15.6815576553345</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>16</v>
       </c>
       <c r="G1344" t="n">
-        <v>15.0603199005127</v>
+        <v>15.060320854187</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G1345" t="n">
-        <v>14.3355417251587</v>
+        <v>14.335542678833</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G1346" t="n">
-        <v>14.392017364502</v>
+        <v>14.3920183181763</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G1348" t="n">
-        <v>13.4695749282837</v>
+        <v>13.4695739746094</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1349" t="n">
-        <v>13.4601612091064</v>
+        <v>13.4601621627808</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G1350" t="n">
-        <v>12.9989385604858</v>
+        <v>12.9989395141602</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1351" t="n">
-        <v>13.0271768569946</v>
+        <v>13.0271787643433</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>14.2700004577637</v>
       </c>
       <c r="G1354" t="n">
-        <v>13.4319229125977</v>
+        <v>13.431923866272</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>14.710000038147</v>
       </c>
       <c r="G1355" t="n">
-        <v>13.8460817337036</v>
+        <v>13.8460826873779</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G1359" t="n">
-        <v>13.3095579147339</v>
+        <v>13.3095588684082</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>13.8900003433228</v>
       </c>
       <c r="G1360" t="n">
-        <v>13.0742406845093</v>
+        <v>13.0742416381836</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>14.0699996948242</v>
       </c>
       <c r="G1361" t="n">
-        <v>13.2436676025391</v>
+        <v>13.2436695098877</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G1362" t="n">
-        <v>13.4413366317749</v>
+        <v>13.4413347244263</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G1366" t="n">
-        <v>13.3001461029053</v>
+        <v>13.300145149231</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G1367" t="n">
-        <v>13.5166368484497</v>
+        <v>13.5166358947754</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G1368" t="n">
-        <v>13.526050567627</v>
+        <v>13.5260496139526</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1369" t="n">
-        <v>13.93079662323</v>
+        <v>13.9307956695557</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>15.3900003433228</v>
       </c>
       <c r="G1374" t="n">
-        <v>14.4861469268799</v>
+        <v>14.4861450195312</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G1375" t="n">
-        <v>14.1284627914429</v>
+        <v>14.1284637451172</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G1376" t="n">
-        <v>14.1567001342773</v>
+        <v>14.1567010879517</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1377" t="n">
-        <v>14.2131767272949</v>
+        <v>14.2131776809692</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1378" t="n">
-        <v>14.4484958648682</v>
+        <v>14.4484949111938</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>15.710000038147</v>
       </c>
       <c r="G1379" t="n">
-        <v>14.7873525619507</v>
+        <v>14.7873516082764</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1382" t="n">
-        <v>16.331033706665</v>
+        <v>16.3310375213623</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>18</v>
       </c>
       <c r="G1385" t="n">
-        <v>16.9428615570068</v>
+        <v>16.9428596496582</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="G1388" t="n">
-        <v>16.3122100830078</v>
+        <v>16.3122081756592</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G1394" t="n">
-        <v>16.971097946167</v>
+        <v>16.9710998535156</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1396" t="n">
-        <v>16.3027973175049</v>
+        <v>16.3027954101562</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>18.6100006103516</v>
       </c>
       <c r="G1399" t="n">
-        <v>17.5170345306396</v>
+        <v>17.5170364379883</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>18.3899993896484</v>
       </c>
       <c r="G1400" t="n">
-        <v>17.3099536895752</v>
+        <v>17.3099555969238</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1401" t="n">
-        <v>16.8110847473145</v>
+        <v>16.8110828399658</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>17.8700008392334</v>
       </c>
       <c r="G1403" t="n">
-        <v>16.8204936981201</v>
+        <v>16.8204956054688</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G1404" t="n">
-        <v>16.9052066802979</v>
+        <v>16.9052104949951</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>18.4899997711182</v>
       </c>
       <c r="G1405" t="n">
-        <v>17.4040813446045</v>
+        <v>17.4040832519531</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1408" t="n">
-        <v>16.5475273132324</v>
+        <v>16.5475254058838</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G1413" t="n">
-        <v>16.5381145477295</v>
+        <v>16.5381126403809</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1416" t="n">
-        <v>16.6134147644043</v>
+        <v>16.6134166717529</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>18</v>
       </c>
       <c r="G1417" t="n">
-        <v>16.9428615570068</v>
+        <v>16.9428596496582</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1418" t="n">
-        <v>17.0369873046875</v>
+        <v>17.0369853973389</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1419" t="n">
-        <v>16.9805107116699</v>
+        <v>16.9805126190186</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G1421" t="n">
-        <v>17.3758430480957</v>
+        <v>17.3758411407471</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G1422" t="n">
-        <v>17.3946685791016</v>
+        <v>17.3946704864502</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1424" t="n">
-        <v>18.1665115356445</v>
+        <v>18.1665096282959</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1427" t="n">
-        <v>18.4488925933838</v>
+        <v>18.4488906860352</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G1428" t="n">
-        <v>18.9760036468506</v>
+        <v>18.976001739502</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1429" t="n">
-        <v>19.107780456543</v>
+        <v>19.1077823638916</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>20.6200008392334</v>
       </c>
       <c r="G1431" t="n">
-        <v>19.4089870452881</v>
+        <v>19.4089889526367</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>21.0400009155273</v>
       </c>
       <c r="G1432" t="n">
-        <v>19.8043212890625</v>
+        <v>19.8043193817139</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G1433" t="n">
-        <v>20.2749557495117</v>
+        <v>20.2749576568604</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>21.3199996948242</v>
       </c>
       <c r="G1435" t="n">
-        <v>20.0678768157959</v>
+        <v>20.0678749084473</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>21.5</v>
       </c>
       <c r="G1436" t="n">
-        <v>20.2373065948486</v>
+        <v>20.2373046875</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1437" t="n">
-        <v>20.1431789398193</v>
+        <v>20.1431770324707</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>21.1399993896484</v>
       </c>
       <c r="G1439" t="n">
-        <v>19.8984451293945</v>
+        <v>19.8984470367432</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>21.9599990844727</v>
       </c>
       <c r="G1443" t="n">
-        <v>20.6702880859375</v>
+        <v>20.6702899932861</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>21.7199993133545</v>
       </c>
       <c r="G1445" t="n">
-        <v>20.4443855285645</v>
+        <v>20.4443836212158</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G1447" t="n">
-        <v>20.4067325592041</v>
+        <v>20.4067344665527</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G1449" t="n">
-        <v>20.1055278778076</v>
+        <v>20.1055297851562</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>21.0400009155273</v>
       </c>
       <c r="G1450" t="n">
-        <v>19.8043212890625</v>
+        <v>19.8043193817139</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>21.2600002288818</v>
       </c>
       <c r="G1451" t="n">
-        <v>20.011402130127</v>
+        <v>20.0114002227783</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G1453" t="n">
-        <v>19.6913681030273</v>
+        <v>19.691370010376</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>20.6399993896484</v>
       </c>
       <c r="G1454" t="n">
-        <v>19.4278106689453</v>
+        <v>19.4278125762939</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1455" t="n">
-        <v>18.9195289611816</v>
+        <v>18.919527053833</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>20</v>
       </c>
       <c r="G1457" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1460" t="n">
-        <v>19.0136547088623</v>
+        <v>19.0136566162109</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G1465" t="n">
-        <v>19.4466400146484</v>
+        <v>19.4466381072998</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1466" t="n">
-        <v>18.9195289611816</v>
+        <v>18.919527053833</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>19.5699996948242</v>
       </c>
       <c r="G1467" t="n">
-        <v>18.420654296875</v>
+        <v>18.4206523895264</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>20</v>
       </c>
       <c r="G1470" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G1473" t="n">
-        <v>18.8818759918213</v>
+        <v>18.8818740844727</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G1474" t="n">
-        <v>18.9760036468506</v>
+        <v>18.976001739502</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1475" t="n">
-        <v>18.9195289611816</v>
+        <v>18.919527053833</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1476" t="n">
-        <v>19.107780456543</v>
+        <v>19.1077823638916</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>20</v>
       </c>
       <c r="G1477" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>19.5</v>
       </c>
       <c r="G1479" t="n">
-        <v>18.3547630310059</v>
+        <v>18.3547649383545</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1480" t="n">
-        <v>18.4488925933838</v>
+        <v>18.4488906860352</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G1482" t="n">
-        <v>18.8818759918213</v>
+        <v>18.8818740844727</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1483" t="n">
-        <v>18.8724613189697</v>
+        <v>18.8724632263184</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>20</v>
       </c>
       <c r="G1484" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1486" t="n">
-        <v>18.9195289611816</v>
+        <v>18.919527053833</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>20</v>
       </c>
       <c r="G1487" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>20</v>
       </c>
       <c r="G1488" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>20</v>
       </c>
       <c r="G1489" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1490" t="n">
-        <v>19.2019062042236</v>
+        <v>19.2019081115723</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1491" t="n">
-        <v>19.107780456543</v>
+        <v>19.1077823638916</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1492" t="n">
-        <v>19.107780456543</v>
+        <v>19.1077823638916</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>20</v>
       </c>
       <c r="G1493" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>20</v>
       </c>
       <c r="G1494" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1495" t="n">
-        <v>18.4488925933838</v>
+        <v>18.4488906860352</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1504" t="n">
-        <v>18.9665908813477</v>
+        <v>18.966588973999</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1505" t="n">
-        <v>19.3965625762939</v>
+        <v>19.3965644836426</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1508" t="n">
-        <v>18.4601783752441</v>
+        <v>18.4601802825928</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>19.5</v>
       </c>
       <c r="G1515" t="n">
-        <v>18.6321659088135</v>
+        <v>18.6321678161621</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G1516" t="n">
-        <v>18.61305809021</v>
+        <v>18.6130561828613</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G1517" t="n">
-        <v>17.8295516967773</v>
+        <v>17.8295497894287</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1521" t="n">
-        <v>18.5366191864014</v>
+        <v>18.5366172790527</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>20</v>
       </c>
       <c r="G1523" t="n">
-        <v>19.1099166870117</v>
+        <v>19.1099147796631</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1524" t="n">
-        <v>19.3010139465332</v>
+        <v>19.3010158538818</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1526" t="n">
-        <v>19.2532405853271</v>
+        <v>19.2532386779785</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>20</v>
       </c>
       <c r="G1527" t="n">
-        <v>19.1099166870117</v>
+        <v>19.1099147796631</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1529" t="n">
-        <v>19.4921131134033</v>
+        <v>19.492115020752</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1532" t="n">
-        <v>20.4476108551025</v>
+        <v>20.4476089477539</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1533" t="n">
-        <v>20.4476108551025</v>
+        <v>20.4476089477539</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1534" t="n">
-        <v>20.590934753418</v>
+        <v>20.5909328460693</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1541" t="n">
-        <v>19.3965625762939</v>
+        <v>19.3965644836426</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1542" t="n">
-        <v>19.3965625762939</v>
+        <v>19.3965644836426</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1545" t="n">
-        <v>19.2532405853271</v>
+        <v>19.2532386779785</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1546" t="n">
-        <v>19.2532405853271</v>
+        <v>19.2532386779785</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>20</v>
       </c>
       <c r="G1551" t="n">
-        <v>19.1099166870117</v>
+        <v>19.1099147796631</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1553" t="n">
-        <v>18.9761486053467</v>
+        <v>18.976146697998</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G1559" t="n">
-        <v>18.5175075531006</v>
+        <v>18.517505645752</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1560" t="n">
-        <v>17.9633197784424</v>
+        <v>17.963321685791</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G1563" t="n">
-        <v>18.4219570159912</v>
+        <v>18.4219589233398</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G1564" t="n">
-        <v>18.4983978271484</v>
+        <v>18.4983997344971</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1565" t="n">
-        <v>18.441068649292</v>
+        <v>18.4410667419434</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1568" t="n">
-        <v>16.6638450622559</v>
+        <v>16.6638469696045</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1569" t="n">
-        <v>15.8038997650146</v>
+        <v>15.803900718689</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1573" t="n">
-        <v>16.4345264434814</v>
+        <v>16.4345283508301</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1574" t="n">
-        <v>16.4345264434814</v>
+        <v>16.4345283508301</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G1577" t="n">
-        <v>16.3580894470215</v>
+        <v>16.3580875396729</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1578" t="n">
-        <v>16.205207824707</v>
+        <v>16.2052059173584</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1579" t="n">
-        <v>16.205207824707</v>
+        <v>16.2052059173584</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1580" t="n">
-        <v>16.4918575286865</v>
+        <v>16.4918556213379</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1581" t="n">
-        <v>16.5874061584473</v>
+        <v>16.5874080657959</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1582" t="n">
-        <v>16.4154186248779</v>
+        <v>16.4154167175293</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G1583" t="n">
-        <v>16.3580894470215</v>
+        <v>16.3580875396729</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1585" t="n">
-        <v>16.549186706543</v>
+        <v>16.5491847991943</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1586" t="n">
-        <v>16.51096534729</v>
+        <v>16.5109672546387</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1590" t="n">
-        <v>16.5874061584473</v>
+        <v>16.5874080657959</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1591" t="n">
-        <v>16.4154186248779</v>
+        <v>16.4154167175293</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1592" t="n">
-        <v>16.3007583618164</v>
+        <v>16.3007564544678</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1596" t="n">
-        <v>15.2497129440308</v>
+        <v>15.2497119903564</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1600" t="n">
-        <v>15.2306022644043</v>
+        <v>15.23060131073</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G1604" t="n">
-        <v>14.5426464080811</v>
+        <v>14.5426454544067</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G1606" t="n">
-        <v>14.1795568466187</v>
+        <v>14.179557800293</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G1610" t="n">
-        <v>13.7209186553955</v>
+        <v>13.7209177017212</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1614" t="n">
-        <v>12.994743347168</v>
+        <v>12.9947423934937</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1618" t="n">
-        <v>13.2813911437988</v>
+        <v>13.2813901901245</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G1619" t="n">
-        <v>13.7973575592041</v>
+        <v>13.7973585128784</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G1620" t="n">
-        <v>13.9311275482178</v>
+        <v>13.9311285018921</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>14.5</v>
       </c>
       <c r="G1622" t="n">
-        <v>13.8546895980835</v>
+        <v>13.8546886444092</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1624" t="n">
-        <v>13.7591381072998</v>
+        <v>13.7591390609741</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G1625" t="n">
-        <v>13.9311275482178</v>
+        <v>13.9311285018921</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1626" t="n">
-        <v>13.8737983703613</v>
+        <v>13.8737993240356</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G1627" t="n">
-        <v>13.8355779647827</v>
+        <v>13.835578918457</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1628" t="n">
-        <v>13.8737983703613</v>
+        <v>13.8737993240356</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G1629" t="n">
-        <v>13.8355779647827</v>
+        <v>13.835578918457</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G1630" t="n">
-        <v>14.1222267150879</v>
+        <v>14.1222276687622</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1640" t="n">
-        <v>16.9313831329346</v>
+        <v>16.9313850402832</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G1641" t="n">
-        <v>17.122486114502</v>
+        <v>17.1224842071533</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>17.5</v>
       </c>
       <c r="G1642" t="n">
-        <v>16.7211742401123</v>
+        <v>16.7211761474609</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1644" t="n">
-        <v>17.0460453033447</v>
+        <v>17.0460433959961</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1647" t="n">
-        <v>16.4154186248779</v>
+        <v>16.4154167175293</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1650" t="n">
-        <v>16.6638450622559</v>
+        <v>16.6638469696045</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>18</v>
       </c>
       <c r="G1651" t="n">
-        <v>17.1989250183105</v>
+        <v>17.1989231109619</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G1653" t="n">
-        <v>17.0269336700439</v>
+        <v>17.0269355773926</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1654" t="n">
-        <v>16.7020664215088</v>
+        <v>16.7020645141602</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1656" t="n">
-        <v>16.9887161254883</v>
+        <v>16.9887142181396</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1657" t="n">
-        <v>17.1033725738525</v>
+        <v>17.1033744812012</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1658" t="n">
-        <v>17.2562522888184</v>
+        <v>17.256254196167</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G1659" t="n">
-        <v>17.2180328369141</v>
+        <v>17.2180347442627</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1661" t="n">
-        <v>17.1033725738525</v>
+        <v>17.1033744812012</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G1662" t="n">
-        <v>18.3264102935791</v>
+        <v>18.3264083862305</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1663" t="n">
-        <v>18.5939483642578</v>
+        <v>18.5939464569092</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G1664" t="n">
-        <v>18.1353073120117</v>
+        <v>18.1353092193604</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>19.5</v>
       </c>
       <c r="G1667" t="n">
-        <v>18.6321659088135</v>
+        <v>18.6321678161621</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1668" t="n">
-        <v>18.5939483642578</v>
+        <v>18.5939464569092</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G1670" t="n">
-        <v>18.8041553497314</v>
+        <v>18.8041572570801</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>19.5</v>
       </c>
       <c r="G1671" t="n">
-        <v>18.6321659088135</v>
+        <v>18.6321678161621</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1675" t="n">
-        <v>17.7722206115723</v>
+        <v>17.7722225189209</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G1677" t="n">
-        <v>18.0970897674561</v>
+        <v>18.0970916748047</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G1678" t="n">
-        <v>17.8104400634766</v>
+        <v>17.8104419708252</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1679" t="n">
-        <v>17.4855728149414</v>
+        <v>17.4855709075928</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1682" t="n">
-        <v>17.3518047332764</v>
+        <v>17.3518028259277</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1683" t="n">
-        <v>16.8740539550781</v>
+        <v>16.8740558624268</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G1684" t="n">
-        <v>17.0842628479004</v>
+        <v>17.0842609405518</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G1686" t="n">
-        <v>17.0269336700439</v>
+        <v>17.0269355773926</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1687" t="n">
-        <v>17.0651569366455</v>
+        <v>17.0651550292969</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1688" t="n">
-        <v>17.3326930999756</v>
+        <v>17.332691192627</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G1691" t="n">
-        <v>18.0206508636475</v>
+        <v>18.0206489562988</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G1692" t="n">
-        <v>18.0206508636475</v>
+        <v>18.0206489562988</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1696" t="n">
-        <v>17.4855728149414</v>
+        <v>17.4855709075928</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G1698" t="n">
-        <v>17.4091339111328</v>
+        <v>17.4091320037842</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1700" t="n">
-        <v>17.390022277832</v>
+        <v>17.3900241851807</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1701" t="n">
-        <v>17.7531108856201</v>
+        <v>17.7531127929688</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G1702" t="n">
-        <v>17.4091339111328</v>
+        <v>17.4091320037842</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G1704" t="n">
-        <v>17.8104400634766</v>
+        <v>17.8104419708252</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G1705" t="n">
-        <v>18.0206508636475</v>
+        <v>18.0206489562988</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>19.5</v>
       </c>
       <c r="G1706" t="n">
-        <v>18.6321659088135</v>
+        <v>18.6321678161621</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1707" t="n">
-        <v>17.9633197784424</v>
+        <v>17.963321685791</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G1710" t="n">
-        <v>18.3646259307861</v>
+        <v>18.3646278381348</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G1712" t="n">
-        <v>18.3646259307861</v>
+        <v>18.3646278381348</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1713" t="n">
-        <v>17.7531108856201</v>
+        <v>17.7531127929688</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G1714" t="n">
-        <v>17.5237922668457</v>
+        <v>17.5237941741943</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1715" t="n">
-        <v>17.791332244873</v>
+        <v>17.7913303375244</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1716" t="n">
-        <v>17.7531108856201</v>
+        <v>17.7531127929688</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1717" t="n">
-        <v>17.2944736480713</v>
+        <v>17.2944717407227</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1718" t="n">
-        <v>17.7531108856201</v>
+        <v>17.7531127929688</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1720" t="n">
-        <v>17.791332244873</v>
+        <v>17.7913303375244</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1724" t="n">
-        <v>17.1033725738525</v>
+        <v>17.1033744812012</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1725" t="n">
-        <v>16.5874061584473</v>
+        <v>16.5874080657959</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1731" t="n">
-        <v>16.9504928588867</v>
+        <v>16.9504947662354</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1732" t="n">
-        <v>17.1033725738525</v>
+        <v>17.1033744812012</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>18</v>
       </c>
       <c r="G1733" t="n">
-        <v>17.1989250183105</v>
+        <v>17.1989231109619</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1734" t="n">
-        <v>17.2562522888184</v>
+        <v>17.256254196167</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>17.5</v>
       </c>
       <c r="G1735" t="n">
-        <v>16.7211742401123</v>
+        <v>16.7211761474609</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1736" t="n">
-        <v>16.8740539550781</v>
+        <v>16.8740558624268</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1739" t="n">
-        <v>16.4918575286865</v>
+        <v>16.4918556213379</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1740" t="n">
-        <v>15.8994483947754</v>
+        <v>15.899450302124</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1741" t="n">
-        <v>15.7847909927368</v>
+        <v>15.7847900390625</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G1742" t="n">
-        <v>15.9758892059326</v>
+        <v>15.9758882522583</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1743" t="n">
-        <v>15.670129776001</v>
+        <v>15.6701307296753</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G1745" t="n">
-        <v>15.4599208831787</v>
+        <v>15.459921836853</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1746" t="n">
-        <v>15.3834819793701</v>
+        <v>15.3834829330444</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1751" t="n">
-        <v>15.4790325164795</v>
+        <v>15.4790315628052</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G1753" t="n">
-        <v>15.5554723739624</v>
+        <v>15.5554714202881</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G1754" t="n">
-        <v>15.5936918258667</v>
+        <v>15.5936908721924</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1755" t="n">
-        <v>15.3834819793701</v>
+        <v>15.3834829330444</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1757" t="n">
-        <v>15.8803405761719</v>
+        <v>15.8803415298462</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1758" t="n">
-        <v>15.7847909927368</v>
+        <v>15.7847900390625</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1760" t="n">
-        <v>15.8994483947754</v>
+        <v>15.899450302124</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1761" t="n">
-        <v>15.9185609817505</v>
+        <v>15.9185590744019</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1762" t="n">
-        <v>15.8803405761719</v>
+        <v>15.8803415298462</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1763" t="n">
-        <v>15.9185609817505</v>
+        <v>15.9185590744019</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1766" t="n">
-        <v>16.8740539550781</v>
+        <v>16.8740558624268</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1772" t="n">
-        <v>16.7389583587646</v>
+        <v>16.7389602661133</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46493,7 +46493,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1774" t="n">
-        <v>17.361083984375</v>
+        <v>17.3610820770264</v>
       </c>
       <c r="H1774" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G1775" t="n">
-        <v>17.1472282409668</v>
+        <v>17.1472263336182</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>18</v>
       </c>
       <c r="G1777" t="n">
-        <v>17.4971714019775</v>
+        <v>17.4971694946289</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G1778" t="n">
-        <v>17.7110252380371</v>
+        <v>17.7110233306885</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G1786" t="n">
-        <v>17.4388465881348</v>
+        <v>17.4388484954834</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1787" t="n">
-        <v>16.9528141021729</v>
+        <v>16.9528160095215</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>18</v>
       </c>
       <c r="G1788" t="n">
-        <v>17.4971714019775</v>
+        <v>17.4971694946289</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G1792" t="n">
-        <v>19.3829784393311</v>
+        <v>19.3829765319824</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1794" t="n">
-        <v>20.559175491333</v>
+        <v>20.5591735839844</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>22.25</v>
       </c>
       <c r="G1796" t="n">
-        <v>21.6284465789795</v>
+        <v>21.6284484863281</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1801" t="n">
-        <v>22.0658760070801</v>
+        <v>22.0658779144287</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1804" t="n">
-        <v>22.260290145874</v>
+        <v>22.2602882385254</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47299,7 +47299,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1805" t="n">
-        <v>22.2116851806641</v>
+        <v>22.2116870880127</v>
       </c>
       <c r="H1805" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1806" t="n">
-        <v>22.4547023773193</v>
+        <v>22.454704284668</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1808" t="n">
-        <v>22.0658760070801</v>
+        <v>22.0658779144287</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>22.5</v>
       </c>
       <c r="G1816" t="n">
-        <v>21.8714637756348</v>
+        <v>21.8714618682861</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>22.5</v>
       </c>
       <c r="G1820" t="n">
-        <v>21.8714637756348</v>
+        <v>21.8714618682861</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1822" t="n">
-        <v>20.559175491333</v>
+        <v>20.5591735839844</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47949,7 +47949,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1830" t="n">
-        <v>19.8301258087158</v>
+        <v>19.8301277160645</v>
       </c>
       <c r="H1830" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1831" t="n">
-        <v>19.8301258087158</v>
+        <v>19.8301277160645</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1832" t="n">
-        <v>19.8301258087158</v>
+        <v>19.8301277160645</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G1841" t="n">
-        <v>20.4619693756104</v>
+        <v>20.4619674682617</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48313,7 +48313,7 @@
         <v>21.25</v>
       </c>
       <c r="G1844" t="n">
-        <v>20.6563816070557</v>
+        <v>20.6563835144043</v>
       </c>
       <c r="H1844" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>22.5</v>
       </c>
       <c r="G1850" t="n">
-        <v>21.8714637756348</v>
+        <v>21.8714618682861</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1851" t="n">
-        <v>22.0658760070801</v>
+        <v>22.0658779144287</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>22.5</v>
       </c>
       <c r="G1857" t="n">
-        <v>21.8714637756348</v>
+        <v>21.8714618682861</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>21.75</v>
       </c>
       <c r="G1858" t="n">
-        <v>21.1424140930176</v>
+        <v>21.1424160003662</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48703,7 +48703,7 @@
         <v>21.75</v>
       </c>
       <c r="G1859" t="n">
-        <v>21.1424140930176</v>
+        <v>21.1424160003662</v>
       </c>
       <c r="H1859" t="s">
         <v>8</v>
@@ -48885,7 +48885,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1866" t="n">
-        <v>22.0658760070801</v>
+        <v>22.0658779144287</v>
       </c>
       <c r="H1866" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1870" t="n">
-        <v>22.0658760070801</v>
+        <v>22.0658779144287</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>22.5</v>
       </c>
       <c r="G1871" t="n">
-        <v>21.8714637756348</v>
+        <v>21.8714618682861</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1874" t="n">
-        <v>22.0658760070801</v>
+        <v>22.0658779144287</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49119,7 +49119,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1875" t="n">
-        <v>22.2116851806641</v>
+        <v>22.2116870880127</v>
       </c>
       <c r="H1875" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1876" t="n">
-        <v>21.9686698913574</v>
+        <v>21.9686717987061</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1884" t="n">
-        <v>20.9480018615723</v>
+        <v>20.9479999542236</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49431,7 +49431,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1887" t="n">
-        <v>19.8301258087158</v>
+        <v>19.8301277160645</v>
       </c>
       <c r="H1887" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1888" t="n">
-        <v>19.8301258087158</v>
+        <v>19.8301277160645</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49587,7 +49587,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1893" t="n">
-        <v>19.8301258087158</v>
+        <v>19.8301277160645</v>
       </c>
       <c r="H1893" t="s">
         <v>8</v>
@@ -49795,7 +49795,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1901" t="n">
-        <v>18.9163856506348</v>
+        <v>18.9163837432861</v>
       </c>
       <c r="H1901" t="s">
         <v>8</v>
@@ -49821,7 +49821,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1902" t="n">
-        <v>19.3052139282227</v>
+        <v>19.305212020874</v>
       </c>
       <c r="H1902" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1906" t="n">
-        <v>20.559175491333</v>
+        <v>20.5591735839844</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -49951,7 +49951,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G1907" t="n">
-        <v>20.4619693756104</v>
+        <v>20.4619674682617</v>
       </c>
       <c r="H1907" t="s">
         <v>8</v>
@@ -49977,7 +49977,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G1908" t="n">
-        <v>20.4619693756104</v>
+        <v>20.4619674682617</v>
       </c>
       <c r="H1908" t="s">
         <v>8</v>
@@ -50055,7 +50055,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1911" t="n">
-        <v>20.2675552368164</v>
+        <v>20.267557144165</v>
       </c>
       <c r="H1911" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1914" t="n">
-        <v>19.8301258087158</v>
+        <v>19.8301277160645</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G1919" t="n">
-        <v>19.0913581848145</v>
+        <v>19.0913562774658</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50289,7 +50289,7 @@
         <v>19</v>
       </c>
       <c r="G1920" t="n">
-        <v>18.4692344665527</v>
+        <v>18.4692363739014</v>
       </c>
       <c r="H1920" t="s">
         <v>8</v>
@@ -50419,7 +50419,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1925" t="n">
-        <v>19.3052139282227</v>
+        <v>19.305212020874</v>
       </c>
       <c r="H1925" t="s">
         <v>8</v>
@@ -50497,7 +50497,7 @@
         <v>19.5</v>
       </c>
       <c r="G1928" t="n">
-        <v>18.9552669525146</v>
+        <v>18.9552688598633</v>
       </c>
       <c r="H1928" t="s">
         <v>8</v>
@@ -50575,7 +50575,7 @@
         <v>19</v>
       </c>
       <c r="G1931" t="n">
-        <v>18.4692344665527</v>
+        <v>18.4692363739014</v>
       </c>
       <c r="H1931" t="s">
         <v>8</v>
@@ -50653,7 +50653,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1934" t="n">
-        <v>18.0220851898193</v>
+        <v>18.022087097168</v>
       </c>
       <c r="H1934" t="s">
         <v>8</v>
@@ -50705,7 +50705,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1936" t="n">
-        <v>18.3720302581787</v>
+        <v>18.3720283508301</v>
       </c>
       <c r="H1936" t="s">
         <v>8</v>
@@ -50913,7 +50913,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G1944" t="n">
-        <v>17.8665561676025</v>
+        <v>17.8665542602539</v>
       </c>
       <c r="H1944" t="s">
         <v>8</v>
@@ -51017,7 +51017,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G1948" t="n">
-        <v>17.7110252380371</v>
+        <v>17.7110233306885</v>
       </c>
       <c r="H1948" t="s">
         <v>8</v>
@@ -51069,7 +51069,7 @@
         <v>18</v>
       </c>
       <c r="G1950" t="n">
-        <v>17.4971714019775</v>
+        <v>17.4971694946289</v>
       </c>
       <c r="H1950" t="s">
         <v>8</v>
@@ -51095,7 +51095,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G1951" t="n">
-        <v>17.5166110992432</v>
+        <v>17.5166130065918</v>
       </c>
       <c r="H1951" t="s">
         <v>8</v>
@@ -51121,7 +51121,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1952" t="n">
-        <v>17.652702331543</v>
+        <v>17.6527004241943</v>
       </c>
       <c r="H1952" t="s">
         <v>8</v>
@@ -51147,7 +51147,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G1953" t="n">
-        <v>17.7110252380371</v>
+        <v>17.7110233306885</v>
       </c>
       <c r="H1953" t="s">
         <v>8</v>
@@ -51329,7 +51329,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1960" t="n">
-        <v>16.7389583587646</v>
+        <v>16.7389602661133</v>
       </c>
       <c r="H1960" t="s">
         <v>8</v>
@@ -51511,7 +51511,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1967" t="n">
-        <v>16.7778434753418</v>
+        <v>16.7778415679932</v>
       </c>
       <c r="H1967" t="s">
         <v>8</v>
@@ -51563,7 +51563,7 @@
         <v>16.5</v>
       </c>
       <c r="G1969" t="n">
-        <v>16.0390739440918</v>
+        <v>16.0390720367432</v>
       </c>
       <c r="H1969" t="s">
         <v>8</v>
@@ -51667,7 +51667,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1973" t="n">
-        <v>15.2419805526733</v>
+        <v>15.241979598999</v>
       </c>
       <c r="H1973" t="s">
         <v>8</v>
@@ -51693,7 +51693,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G1974" t="n">
-        <v>15.8252201080322</v>
+        <v>15.8252191543579</v>
       </c>
       <c r="H1974" t="s">
         <v>8</v>
@@ -51797,7 +51797,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G1978" t="n">
-        <v>15.7280120849609</v>
+        <v>15.7280130386353</v>
       </c>
       <c r="H1978" t="s">
         <v>8</v>
@@ -51849,7 +51849,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1980" t="n">
-        <v>15.2225379943848</v>
+        <v>15.2225389480591</v>
       </c>
       <c r="H1980" t="s">
         <v>8</v>
@@ -51953,7 +51953,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G1984" t="n">
-        <v>14.4254446029663</v>
+        <v>14.4254455566406</v>
       </c>
       <c r="H1984" t="s">
         <v>8</v>
@@ -52109,7 +52109,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1990" t="n">
-        <v>13.5117044448853</v>
+        <v>13.5117034912109</v>
       </c>
       <c r="H1990" t="s">
         <v>8</v>
@@ -52239,7 +52239,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1995" t="n">
-        <v>13.8033237457275</v>
+        <v>13.8033227920532</v>
       </c>
       <c r="H1995" t="s">
         <v>8</v>
@@ -52343,7 +52343,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G1999" t="n">
-        <v>14.2504730224609</v>
+        <v>14.2504739761353</v>
       </c>
       <c r="H1999" t="s">
         <v>8</v>
@@ -52369,7 +52369,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G2000" t="n">
-        <v>13.8810892105103</v>
+        <v>13.8810882568359</v>
       </c>
       <c r="H2000" t="s">
         <v>8</v>
@@ -52447,7 +52447,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G2003" t="n">
-        <v>15.3197460174561</v>
+        <v>15.3197450637817</v>
       </c>
       <c r="H2003" t="s">
         <v>8</v>
@@ -52499,7 +52499,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2005" t="n">
-        <v>15.3586282730103</v>
+        <v>15.3586273193359</v>
       </c>
       <c r="H2005" t="s">
         <v>8</v>
@@ -52525,7 +52525,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G2006" t="n">
-        <v>15.2419805526733</v>
+        <v>15.241979598999</v>
       </c>
       <c r="H2006" t="s">
         <v>8</v>
@@ -52551,7 +52551,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2007" t="n">
-        <v>14.9698009490967</v>
+        <v>14.969801902771</v>
       </c>
       <c r="H2007" t="s">
         <v>8</v>
@@ -52577,7 +52577,7 @@
         <v>16.5</v>
       </c>
       <c r="G2008" t="n">
-        <v>16.0390739440918</v>
+        <v>16.0390720367432</v>
       </c>
       <c r="H2008" t="s">
         <v>8</v>
@@ -61810,6 +61810,32 @@
         <v>29.7999992370605</v>
       </c>
       <c r="H2363" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2364">
+      <c r="A2364" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B2364" t="n">
+        <v>17977</v>
+      </c>
+      <c r="C2364" t="n">
+        <v>30.1499996185303</v>
+      </c>
+      <c r="D2364" t="n">
+        <v>29.1499996185303</v>
+      </c>
+      <c r="E2364" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="F2364" t="n">
+        <v>29.4500007629395</v>
+      </c>
+      <c r="G2364" t="n">
+        <v>29.4500007629395</v>
+      </c>
+      <c r="H2364" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/WIIT.MI.xlsx
+++ b/data/WIIT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2" t="n">
-        <v>4.49076509475708</v>
+        <v>4.49076461791992</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G3" t="n">
-        <v>4.49076509475708</v>
+        <v>4.49076461791992</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>5.125</v>
       </c>
       <c r="G4" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>5.125</v>
       </c>
       <c r="G5" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>5.125</v>
       </c>
       <c r="G6" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>5.125</v>
       </c>
       <c r="G7" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>5.125</v>
       </c>
       <c r="G8" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>5.125</v>
       </c>
       <c r="G9" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>5.125</v>
       </c>
       <c r="G10" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>5.125</v>
       </c>
       <c r="G11" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>5.125</v>
       </c>
       <c r="G12" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>5.125</v>
       </c>
       <c r="G13" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>5.125</v>
       </c>
       <c r="G14" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>5.125</v>
       </c>
       <c r="G15" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>5.125</v>
       </c>
       <c r="G16" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>5.125</v>
       </c>
       <c r="G17" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>5.125</v>
       </c>
       <c r="G18" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>5.125</v>
       </c>
       <c r="G19" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>5.125</v>
       </c>
       <c r="G20" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>5.125</v>
       </c>
       <c r="G21" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>5.125</v>
       </c>
       <c r="G22" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>5.125</v>
       </c>
       <c r="G23" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>5.125</v>
       </c>
       <c r="G24" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>5.125</v>
       </c>
       <c r="G25" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>5.125</v>
       </c>
       <c r="G26" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>5.125</v>
       </c>
       <c r="G27" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>5.125</v>
       </c>
       <c r="G28" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>5.125</v>
       </c>
       <c r="G29" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>5.125</v>
       </c>
       <c r="G30" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>5.125</v>
       </c>
       <c r="G31" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>5.125</v>
       </c>
       <c r="G32" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>5.125</v>
       </c>
       <c r="G33" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>5.125</v>
       </c>
       <c r="G34" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>5.125</v>
       </c>
       <c r="G35" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>5.125</v>
       </c>
       <c r="G36" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>5.125</v>
       </c>
       <c r="G37" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>5.125</v>
       </c>
       <c r="G38" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>5.125</v>
       </c>
       <c r="G39" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>5.125</v>
       </c>
       <c r="G40" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>5.125</v>
       </c>
       <c r="G41" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>5.125</v>
       </c>
       <c r="G42" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>5.125</v>
       </c>
       <c r="G43" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>5.125</v>
       </c>
       <c r="G44" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>5.125</v>
       </c>
       <c r="G45" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>5.125</v>
       </c>
       <c r="G46" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>5.125</v>
       </c>
       <c r="G47" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>5.125</v>
       </c>
       <c r="G48" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>5.125</v>
       </c>
       <c r="G49" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>5.125</v>
       </c>
       <c r="G50" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>5.125</v>
       </c>
       <c r="G51" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>5.125</v>
       </c>
       <c r="G52" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>5.125</v>
       </c>
       <c r="G53" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>5.125</v>
       </c>
       <c r="G54" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>5.125</v>
       </c>
       <c r="G55" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>5.125</v>
       </c>
       <c r="G56" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>5.125</v>
       </c>
       <c r="G57" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>5.125</v>
       </c>
       <c r="G58" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>5.125</v>
       </c>
       <c r="G59" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>5.125</v>
       </c>
       <c r="G60" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>5.125</v>
       </c>
       <c r="G61" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>5.125</v>
       </c>
       <c r="G62" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>5.125</v>
       </c>
       <c r="G63" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>5.125</v>
       </c>
       <c r="G64" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>5.125</v>
       </c>
       <c r="G65" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>5.125</v>
       </c>
       <c r="G66" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>5.125</v>
       </c>
       <c r="G67" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>5.125</v>
       </c>
       <c r="G68" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>5.125</v>
       </c>
       <c r="G69" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>5.125</v>
       </c>
       <c r="G70" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5.125</v>
       </c>
       <c r="G71" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>5.125</v>
       </c>
       <c r="G72" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>5.125</v>
       </c>
       <c r="G73" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>5.125</v>
       </c>
       <c r="G74" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>5.125</v>
       </c>
       <c r="G75" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>5.125</v>
       </c>
       <c r="G76" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>5.125</v>
       </c>
       <c r="G77" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>5.125</v>
       </c>
       <c r="G78" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>5.125</v>
       </c>
       <c r="G79" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>5.125</v>
       </c>
       <c r="G80" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>5.125</v>
       </c>
       <c r="G81" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>5.125</v>
       </c>
       <c r="G82" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>5.125</v>
       </c>
       <c r="G83" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>5.125</v>
       </c>
       <c r="G84" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>5.125</v>
       </c>
       <c r="G85" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>5.125</v>
       </c>
       <c r="G86" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>5.125</v>
       </c>
       <c r="G87" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>5.125</v>
       </c>
       <c r="G88" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>5.125</v>
       </c>
       <c r="G89" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>5.125</v>
       </c>
       <c r="G90" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>5.125</v>
       </c>
       <c r="G91" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>5.125</v>
       </c>
       <c r="G92" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>5.125</v>
       </c>
       <c r="G93" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>5.125</v>
       </c>
       <c r="G94" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>5.125</v>
       </c>
       <c r="G95" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>5.125</v>
       </c>
       <c r="G96" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>5.125</v>
       </c>
       <c r="G97" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>5.125</v>
       </c>
       <c r="G98" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>5.125</v>
       </c>
       <c r="G99" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>5.125</v>
       </c>
       <c r="G100" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>5.125</v>
       </c>
       <c r="G101" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>5.125</v>
       </c>
       <c r="G102" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>5.125</v>
       </c>
       <c r="G103" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>5.125</v>
       </c>
       <c r="G104" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>5.125</v>
       </c>
       <c r="G105" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>5.125</v>
       </c>
       <c r="G106" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>5.125</v>
       </c>
       <c r="G107" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>5.125</v>
       </c>
       <c r="G108" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>5.125</v>
       </c>
       <c r="G109" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>5.125</v>
       </c>
       <c r="G110" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>5.125</v>
       </c>
       <c r="G111" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>5.125</v>
       </c>
       <c r="G112" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>5.125</v>
       </c>
       <c r="G113" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>5.125</v>
       </c>
       <c r="G114" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>5.125</v>
       </c>
       <c r="G115" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>5.125</v>
       </c>
       <c r="G116" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>5.125</v>
       </c>
       <c r="G117" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>5.125</v>
       </c>
       <c r="G118" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>5.125</v>
       </c>
       <c r="G119" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>5.125</v>
       </c>
       <c r="G120" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>5.125</v>
       </c>
       <c r="G121" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>5.125</v>
       </c>
       <c r="G122" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>5.125</v>
       </c>
       <c r="G123" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>5.125</v>
       </c>
       <c r="G124" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>5.125</v>
       </c>
       <c r="G125" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>5.125</v>
       </c>
       <c r="G126" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.125</v>
       </c>
       <c r="G127" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>5.125</v>
       </c>
       <c r="G128" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>5.125</v>
       </c>
       <c r="G129" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>5.125</v>
       </c>
       <c r="G130" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>5.125</v>
       </c>
       <c r="G131" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>5.125</v>
       </c>
       <c r="G132" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>5.125</v>
       </c>
       <c r="G133" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>5.125</v>
       </c>
       <c r="G134" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>5.125</v>
       </c>
       <c r="G135" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>5.125</v>
       </c>
       <c r="G136" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>5.125</v>
       </c>
       <c r="G137" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>5.125</v>
       </c>
       <c r="G138" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>5.125</v>
       </c>
       <c r="G139" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>5.125</v>
       </c>
       <c r="G140" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>5.125</v>
       </c>
       <c r="G141" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>5.125</v>
       </c>
       <c r="G142" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>5.125</v>
       </c>
       <c r="G143" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>5.125</v>
       </c>
       <c r="G144" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>5.125</v>
       </c>
       <c r="G145" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>5.125</v>
       </c>
       <c r="G146" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>5.125</v>
       </c>
       <c r="G147" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>5.125</v>
       </c>
       <c r="G148" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>5.125</v>
       </c>
       <c r="G149" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>5.125</v>
       </c>
       <c r="G150" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>5.125</v>
       </c>
       <c r="G151" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>5.125</v>
       </c>
       <c r="G152" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>5.125</v>
       </c>
       <c r="G153" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>5.125</v>
       </c>
       <c r="G154" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>5.125</v>
       </c>
       <c r="G155" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>5.125</v>
       </c>
       <c r="G156" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>5.125</v>
       </c>
       <c r="G157" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>5.125</v>
       </c>
       <c r="G158" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>5.125</v>
       </c>
       <c r="G159" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>5.125</v>
       </c>
       <c r="G160" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>5.125</v>
       </c>
       <c r="G161" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>5.125</v>
       </c>
       <c r="G162" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>5.125</v>
       </c>
       <c r="G163" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>5.125</v>
       </c>
       <c r="G164" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>5.125</v>
       </c>
       <c r="G165" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>5.125</v>
       </c>
       <c r="G166" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>5.125</v>
       </c>
       <c r="G167" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>5.125</v>
       </c>
       <c r="G168" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>5.125</v>
       </c>
       <c r="G169" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>5.125</v>
       </c>
       <c r="G170" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>5.125</v>
       </c>
       <c r="G171" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>5.125</v>
       </c>
       <c r="G172" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>5.125</v>
       </c>
       <c r="G173" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>5.125</v>
       </c>
       <c r="G174" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>5.125</v>
       </c>
       <c r="G175" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>5.125</v>
       </c>
       <c r="G176" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>5.125</v>
       </c>
       <c r="G177" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>5.125</v>
       </c>
       <c r="G178" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>5.125</v>
       </c>
       <c r="G179" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>5.125</v>
       </c>
       <c r="G180" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>5.125</v>
       </c>
       <c r="G181" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>5.125</v>
       </c>
       <c r="G182" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>5.125</v>
       </c>
       <c r="G183" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>5.125</v>
       </c>
       <c r="G184" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>5.125</v>
       </c>
       <c r="G185" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>5.125</v>
       </c>
       <c r="G186" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>5.125</v>
       </c>
       <c r="G187" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>5.125</v>
       </c>
       <c r="G188" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>5.125</v>
       </c>
       <c r="G189" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>5.125</v>
       </c>
       <c r="G190" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>5.125</v>
       </c>
       <c r="G191" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>5.125</v>
       </c>
       <c r="G192" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>5.125</v>
       </c>
       <c r="G193" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>5.125</v>
       </c>
       <c r="G194" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>5.125</v>
       </c>
       <c r="G195" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>5.125</v>
       </c>
       <c r="G196" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>5.125</v>
       </c>
       <c r="G197" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>5.125</v>
       </c>
       <c r="G198" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>5.125</v>
       </c>
       <c r="G199" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>5.125</v>
       </c>
       <c r="G200" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>5.125</v>
       </c>
       <c r="G201" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>5.125</v>
       </c>
       <c r="G202" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>5.125</v>
       </c>
       <c r="G203" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>5.125</v>
       </c>
       <c r="G204" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>5.125</v>
       </c>
       <c r="G205" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>5.125</v>
       </c>
       <c r="G206" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>5.125</v>
       </c>
       <c r="G207" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>5.125</v>
       </c>
       <c r="G208" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>5.125</v>
       </c>
       <c r="G209" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>5.125</v>
       </c>
       <c r="G210" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>5.125</v>
       </c>
       <c r="G211" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>5.125</v>
       </c>
       <c r="G212" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>5.125</v>
       </c>
       <c r="G213" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>5.125</v>
       </c>
       <c r="G214" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>5.125</v>
       </c>
       <c r="G215" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>5.125</v>
       </c>
       <c r="G216" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>5.125</v>
       </c>
       <c r="G217" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>5.125</v>
       </c>
       <c r="G218" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>5.125</v>
       </c>
       <c r="G219" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>5.125</v>
       </c>
       <c r="G220" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>5.125</v>
       </c>
       <c r="G221" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>5.125</v>
       </c>
       <c r="G222" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>5.125</v>
       </c>
       <c r="G223" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>5.125</v>
       </c>
       <c r="G224" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>5.125</v>
       </c>
       <c r="G225" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>5.125</v>
       </c>
       <c r="G226" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>5.125</v>
       </c>
       <c r="G227" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>5.125</v>
       </c>
       <c r="G228" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>5.125</v>
       </c>
       <c r="G229" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>5.125</v>
       </c>
       <c r="G230" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>5.125</v>
       </c>
       <c r="G231" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>5.125</v>
       </c>
       <c r="G232" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>5.125</v>
       </c>
       <c r="G233" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>5.125</v>
       </c>
       <c r="G234" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>5.125</v>
       </c>
       <c r="G235" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>5.125</v>
       </c>
       <c r="G236" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>5.125</v>
       </c>
       <c r="G237" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>5.125</v>
       </c>
       <c r="G238" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>5.125</v>
       </c>
       <c r="G239" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>5.125</v>
       </c>
       <c r="G240" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>5.125</v>
       </c>
       <c r="G241" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>5.125</v>
       </c>
       <c r="G242" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>5.125</v>
       </c>
       <c r="G243" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>5.125</v>
       </c>
       <c r="G244" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>5.125</v>
       </c>
       <c r="G245" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>5.125</v>
       </c>
       <c r="G246" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>5.125</v>
       </c>
       <c r="G247" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>5.125</v>
       </c>
       <c r="G248" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>5.125</v>
       </c>
       <c r="G249" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>5.125</v>
       </c>
       <c r="G250" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>5.125</v>
       </c>
       <c r="G251" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>5.125</v>
       </c>
       <c r="G252" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>5.125</v>
       </c>
       <c r="G253" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>5.125</v>
       </c>
       <c r="G254" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>5.125</v>
       </c>
       <c r="G255" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>5.125</v>
       </c>
       <c r="G256" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>5.125</v>
       </c>
       <c r="G257" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>5.125</v>
       </c>
       <c r="G258" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>5.125</v>
       </c>
       <c r="G259" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>5.125</v>
       </c>
       <c r="G260" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>5.125</v>
       </c>
       <c r="G261" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>5.125</v>
       </c>
       <c r="G262" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>5.125</v>
       </c>
       <c r="G263" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>5.125</v>
       </c>
       <c r="G264" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>5.125</v>
       </c>
       <c r="G265" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>5.125</v>
       </c>
       <c r="G266" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>5.125</v>
       </c>
       <c r="G267" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>5.125</v>
       </c>
       <c r="G268" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>5.125</v>
       </c>
       <c r="G269" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>5.125</v>
       </c>
       <c r="G270" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>5.125</v>
       </c>
       <c r="G271" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>5.125</v>
       </c>
       <c r="G272" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>5.125</v>
       </c>
       <c r="G273" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706569671631</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G274" t="n">
-        <v>4.51098823547363</v>
+        <v>4.51098871231079</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G276" t="n">
-        <v>4.52888870239258</v>
+        <v>4.52888917922974</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G277" t="n">
-        <v>4.49308776855469</v>
+        <v>4.49308729171753</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G278" t="n">
-        <v>4.44833564758301</v>
+        <v>4.44833517074585</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>5</v>
       </c>
       <c r="G279" t="n">
-        <v>4.47518682479858</v>
+        <v>4.47518634796143</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>5</v>
       </c>
       <c r="G280" t="n">
-        <v>4.47518682479858</v>
+        <v>4.47518634796143</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>5</v>
       </c>
       <c r="G281" t="n">
-        <v>4.47518682479858</v>
+        <v>4.47518634796143</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G282" t="n">
-        <v>4.49308776855469</v>
+        <v>4.49308729171753</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G283" t="n">
-        <v>4.43938541412354</v>
+        <v>4.43938493728638</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G284" t="n">
-        <v>4.49308776855469</v>
+        <v>4.49308729171753</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>5</v>
       </c>
       <c r="G285" t="n">
-        <v>4.47518682479858</v>
+        <v>4.47518634796143</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G286" t="n">
-        <v>4.44833564758301</v>
+        <v>4.44833517074585</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G287" t="n">
-        <v>4.44833564758301</v>
+        <v>4.44833517074585</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G288" t="n">
-        <v>4.44833564758301</v>
+        <v>4.44833517074585</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G289" t="n">
-        <v>4.44833564758301</v>
+        <v>4.44833517074585</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>5</v>
       </c>
       <c r="G290" t="n">
-        <v>4.47518682479858</v>
+        <v>4.47518634796143</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G296" t="n">
-        <v>4.51098823547363</v>
+        <v>4.51098871231079</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G297" t="n">
-        <v>4.52888870239258</v>
+        <v>4.52888917922974</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G298" t="n">
-        <v>4.51098823547363</v>
+        <v>4.51098871231079</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>4.51098823547363</v>
+        <v>4.51098871231079</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G300" t="n">
-        <v>4.49308776855469</v>
+        <v>4.49308729171753</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G301" t="n">
-        <v>4.49308776855469</v>
+        <v>4.49308729171753</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>4.49308776855469</v>
+        <v>4.49308729171753</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G303" t="n">
-        <v>4.4304347038269</v>
+        <v>4.43043422698975</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G304" t="n">
-        <v>4.4304347038269</v>
+        <v>4.43043422698975</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G305" t="n">
-        <v>4.38568305969238</v>
+        <v>4.38568258285522</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G306" t="n">
-        <v>4.3409309387207</v>
+        <v>4.34093141555786</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G308" t="n">
-        <v>4.29617881774902</v>
+        <v>4.29617929458618</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G309" t="n">
-        <v>4.33198022842407</v>
+        <v>4.33198118209839</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G310" t="n">
-        <v>4.33198022842407</v>
+        <v>4.33198118209839</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>4.45728635787964</v>
+        <v>4.45728588104248</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>4.43938541412354</v>
+        <v>4.43938493728638</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G315" t="n">
-        <v>4.36778163909912</v>
+        <v>4.36778211593628</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G316" t="n">
-        <v>4.33198022842407</v>
+        <v>4.33198118209839</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G317" t="n">
-        <v>4.32302951812744</v>
+        <v>4.3230299949646</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G318" t="n">
-        <v>4.32302951812744</v>
+        <v>4.3230299949646</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G321" t="n">
-        <v>4.23352670669556</v>
+        <v>4.2335262298584</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G322" t="n">
-        <v>4.32302951812744</v>
+        <v>4.3230299949646</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>4.28722858428955</v>
+        <v>4.28722906112671</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G326" t="n">
-        <v>4.0903205871582</v>
+        <v>4.09032106399536</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G329" t="n">
-        <v>3.99186611175537</v>
+        <v>3.99186682701111</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G331" t="n">
-        <v>4.08137035369873</v>
+        <v>4.08136940002441</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G332" t="n">
-        <v>4.13507223129272</v>
+        <v>4.13507270812988</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G335" t="n">
-        <v>4.11717176437378</v>
+        <v>4.11717224121094</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G336" t="n">
-        <v>3.99186611175537</v>
+        <v>3.99186682701111</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>4.5</v>
       </c>
       <c r="G337" t="n">
-        <v>4.02766752243042</v>
+        <v>4.02766799926758</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G338" t="n">
-        <v>3.93816447257996</v>
+        <v>3.93816471099854</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G339" t="n">
-        <v>3.8844621181488</v>
+        <v>3.88446259498596</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G341" t="n">
-        <v>3.86656141281128</v>
+        <v>3.86656165122986</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>3.76810765266418</v>
+        <v>3.76810741424561</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G343" t="n">
-        <v>3.84866118431091</v>
+        <v>3.8486602306366</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G344" t="n">
-        <v>3.78600788116455</v>
+        <v>3.78600764274597</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G345" t="n">
-        <v>3.70545387268066</v>
+        <v>3.70545411109924</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G347" t="n">
-        <v>3.60700058937073</v>
+        <v>3.60700035095215</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G348" t="n">
-        <v>3.59805011749268</v>
+        <v>3.5980498790741</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G349" t="n">
-        <v>3.59805011749268</v>
+        <v>3.5980498790741</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G350" t="n">
-        <v>3.57119917869568</v>
+        <v>3.57119870185852</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G351" t="n">
-        <v>3.53539705276489</v>
+        <v>3.53539776802063</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>4</v>
       </c>
       <c r="G352" t="n">
-        <v>3.58014917373657</v>
+        <v>3.58014941215515</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G353" t="n">
-        <v>3.4369432926178</v>
+        <v>3.43694353103638</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G354" t="n">
-        <v>3.47274518013</v>
+        <v>3.47274470329285</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G356" t="n">
-        <v>3.41009211540222</v>
+        <v>3.4100923538208</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G358" t="n">
-        <v>3.31163835525513</v>
+        <v>3.31163811683655</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G359" t="n">
-        <v>3.31163835525513</v>
+        <v>3.31163811683655</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G360" t="n">
-        <v>3.31163835525513</v>
+        <v>3.31163811683655</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G362" t="n">
-        <v>3.36534023284912</v>
+        <v>3.3653404712677</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G363" t="n">
-        <v>3.31163835525513</v>
+        <v>3.31163811683655</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G365" t="n">
-        <v>3.0878791809082</v>
+        <v>3.08787870407104</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G368" t="n">
-        <v>3.10577940940857</v>
+        <v>3.10577964782715</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G370" t="n">
-        <v>3.21318387985229</v>
+        <v>3.21318364143372</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G371" t="n">
-        <v>3.22213459014893</v>
+        <v>3.2221348285675</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G372" t="n">
-        <v>3.22213459014893</v>
+        <v>3.2221348285675</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G375" t="n">
-        <v>2.82831835746765</v>
+        <v>2.82831811904907</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G377" t="n">
-        <v>2.95362281799316</v>
+        <v>2.95362305641174</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G382" t="n">
-        <v>2.95362281799316</v>
+        <v>2.95362305641174</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G383" t="n">
-        <v>2.95362281799316</v>
+        <v>2.95362305641174</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G384" t="n">
-        <v>3.0073254108429</v>
+        <v>3.00732517242432</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G385" t="n">
-        <v>2.95362281799316</v>
+        <v>2.95362305641174</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G388" t="n">
-        <v>2.82831835746765</v>
+        <v>2.82831811904907</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G390" t="n">
-        <v>2.81041717529297</v>
+        <v>2.81041741371155</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G391" t="n">
-        <v>2.84621906280518</v>
+        <v>2.8462188243866</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G394" t="n">
-        <v>2.94467258453369</v>
+        <v>2.94467282295227</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G396" t="n">
-        <v>3.0699782371521</v>
+        <v>3.06997799873352</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G397" t="n">
-        <v>3.17738270759583</v>
+        <v>3.17738246917725</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G398" t="n">
-        <v>3.17738270759583</v>
+        <v>3.17738246917725</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G399" t="n">
-        <v>3.26688671112061</v>
+        <v>3.26688647270203</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>3.22213459014893</v>
+        <v>3.2221348285675</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G401" t="n">
-        <v>3.26688671112061</v>
+        <v>3.26688647270203</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G402" t="n">
-        <v>3.26688671112061</v>
+        <v>3.26688647270203</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G403" t="n">
-        <v>3.31163835525513</v>
+        <v>3.31163811683655</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>3.75</v>
       </c>
       <c r="G404" t="n">
-        <v>3.35638976097107</v>
+        <v>3.35638999938965</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G407" t="n">
-        <v>3.50854635238647</v>
+        <v>3.50854587554932</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G409" t="n">
-        <v>3.59805011749268</v>
+        <v>3.5980498790741</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G411" t="n">
-        <v>3.59805011749268</v>
+        <v>3.5980498790741</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4</v>
       </c>
       <c r="G412" t="n">
-        <v>3.58014917373657</v>
+        <v>3.58014941215515</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G413" t="n">
-        <v>3.58909964561462</v>
+        <v>3.58910012245178</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G415" t="n">
-        <v>3.66070294380188</v>
+        <v>3.6607027053833</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G417" t="n">
-        <v>3.49064588546753</v>
+        <v>3.49064564704895</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G418" t="n">
-        <v>3.53539705276489</v>
+        <v>3.53539776802063</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>4</v>
       </c>
       <c r="G420" t="n">
-        <v>3.58014917373657</v>
+        <v>3.58014941215515</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G423" t="n">
-        <v>3.58909964561462</v>
+        <v>3.58910012245178</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G425" t="n">
-        <v>3.62490105628967</v>
+        <v>3.62490129470825</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>4</v>
       </c>
       <c r="G427" t="n">
-        <v>3.58014917373657</v>
+        <v>3.58014941215515</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G429" t="n">
-        <v>3.58909964561462</v>
+        <v>3.58910012245178</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G430" t="n">
-        <v>3.69650411605835</v>
+        <v>3.69650387763977</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G431" t="n">
-        <v>3.75020599365234</v>
+        <v>3.75020670890808</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G432" t="n">
-        <v>3.78600788116455</v>
+        <v>3.78600764274597</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G434" t="n">
-        <v>4.0903205871582</v>
+        <v>4.09032106399536</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G436" t="n">
-        <v>4.09927129745483</v>
+        <v>4.09927034378052</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G437" t="n">
-        <v>4.09927129745483</v>
+        <v>4.09927034378052</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>4.75</v>
       </c>
       <c r="G438" t="n">
-        <v>4.25142669677734</v>
+        <v>4.25142765045166</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G439" t="n">
-        <v>4.11717176437378</v>
+        <v>4.11717224121094</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>4.4304347038269</v>
+        <v>4.43043422698975</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>4.29617881774902</v>
+        <v>4.29617929458618</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G443" t="n">
-        <v>4.23352670669556</v>
+        <v>4.2335262298584</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>4.5</v>
       </c>
       <c r="G445" t="n">
-        <v>4.02766752243042</v>
+        <v>4.02766799926758</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G447" t="n">
-        <v>3.92026352882385</v>
+        <v>3.92026400566101</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G448" t="n">
-        <v>3.76810765266418</v>
+        <v>3.76810741424561</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G449" t="n">
-        <v>3.77705717086792</v>
+        <v>3.77705788612366</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G451" t="n">
-        <v>3.70545387268066</v>
+        <v>3.70545411109924</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G455" t="n">
-        <v>4.13507223129272</v>
+        <v>4.13507270812988</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G458" t="n">
-        <v>4.29617881774902</v>
+        <v>4.29617929458618</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G459" t="n">
-        <v>4.26037836074829</v>
+        <v>4.26037788391113</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G460" t="n">
-        <v>4.3409309387207</v>
+        <v>4.34093141555786</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G462" t="n">
-        <v>4.44833564758301</v>
+        <v>4.44833517074585</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G463" t="n">
-        <v>4.32302951812744</v>
+        <v>4.3230299949646</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G466" t="n">
-        <v>4.38568305969238</v>
+        <v>4.38568258285522</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G468" t="n">
-        <v>4.29617881774902</v>
+        <v>4.29617929458618</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G469" t="n">
-        <v>4.21562623977661</v>
+        <v>4.21562576293945</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G472" t="n">
-        <v>4.3891773223877</v>
+        <v>4.38917779922485</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G473" t="n">
-        <v>4.28880071640015</v>
+        <v>4.28880167007446</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G474" t="n">
-        <v>4.37092733383179</v>
+        <v>4.37092781066895</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G475" t="n">
-        <v>4.44392824172974</v>
+        <v>4.44392871856689</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G476" t="n">
-        <v>4.28880071640015</v>
+        <v>4.28880167007446</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G482" t="n">
-        <v>4.26142597198486</v>
+        <v>4.26142644882202</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G483" t="n">
-        <v>4.28880071640015</v>
+        <v>4.28880167007446</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G484" t="n">
-        <v>4.2157998085022</v>
+        <v>4.21580076217651</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G485" t="n">
-        <v>4.28880071640015</v>
+        <v>4.28880167007446</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G490" t="n">
-        <v>4.28880071640015</v>
+        <v>4.28880167007446</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G491" t="n">
-        <v>4.28880071640015</v>
+        <v>4.28880167007446</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>4.75</v>
       </c>
       <c r="G492" t="n">
-        <v>4.33442640304565</v>
+        <v>4.33442735671997</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>4.75</v>
       </c>
       <c r="G493" t="n">
-        <v>4.33442640304565</v>
+        <v>4.33442735671997</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G494" t="n">
-        <v>4.2431755065918</v>
+        <v>4.24317646026611</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G495" t="n">
-        <v>4.38005256652832</v>
+        <v>4.38005304336548</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G497" t="n">
-        <v>4.38005256652832</v>
+        <v>4.38005304336548</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>4.75</v>
       </c>
       <c r="G498" t="n">
-        <v>4.33442640304565</v>
+        <v>4.33442735671997</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>4.75</v>
       </c>
       <c r="G499" t="n">
-        <v>4.33442640304565</v>
+        <v>4.33442735671997</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G500" t="n">
-        <v>4.38005256652832</v>
+        <v>4.38005304336548</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G501" t="n">
-        <v>4.37092733383179</v>
+        <v>4.37092781066895</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>4.75</v>
       </c>
       <c r="G503" t="n">
-        <v>4.33442640304565</v>
+        <v>4.33442735671997</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G507" t="n">
-        <v>4.38005256652832</v>
+        <v>4.38005304336548</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G508" t="n">
-        <v>4.38005256652832</v>
+        <v>4.38005304336548</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G509" t="n">
-        <v>4.3161768913269</v>
+        <v>4.31617641448975</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G510" t="n">
-        <v>4.32530212402344</v>
+        <v>4.32530164718628</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G511" t="n">
-        <v>4.3161768913269</v>
+        <v>4.31617641448975</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G512" t="n">
-        <v>4.32530212402344</v>
+        <v>4.32530164718628</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>4.75</v>
       </c>
       <c r="G514" t="n">
-        <v>4.33442640304565</v>
+        <v>4.33442735671997</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G516" t="n">
-        <v>4.28880071640015</v>
+        <v>4.28880167007446</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G518" t="n">
-        <v>4.61730480194092</v>
+        <v>4.61730575561523</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G519" t="n">
-        <v>4.59905481338501</v>
+        <v>4.59905576705933</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G522" t="n">
-        <v>4.48042869567871</v>
+        <v>4.48042917251587</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G523" t="n">
-        <v>4.61730480194092</v>
+        <v>4.61730575561523</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G524" t="n">
-        <v>4.63555574417114</v>
+        <v>4.63555526733398</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G525" t="n">
-        <v>4.726806640625</v>
+        <v>4.72680616378784</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G527" t="n">
-        <v>4.90930843353271</v>
+        <v>4.90930986404419</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G528" t="n">
-        <v>4.90930843353271</v>
+        <v>4.90930986404419</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G531" t="n">
-        <v>4.94580936431885</v>
+        <v>4.94580984115601</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>5.5</v>
       </c>
       <c r="G533" t="n">
-        <v>5.0188102722168</v>
+        <v>5.01881074905396</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G534" t="n">
-        <v>5.16481161117554</v>
+        <v>5.1648120880127</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G535" t="n">
-        <v>5.20131206512451</v>
+        <v>5.20131254196167</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G537" t="n">
-        <v>5.18306159973145</v>
+        <v>5.1830620765686</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G538" t="n">
-        <v>5.16481161117554</v>
+        <v>5.1648120880127</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G539" t="n">
-        <v>5.16481161117554</v>
+        <v>5.1648120880127</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G541" t="n">
-        <v>5.00055980682373</v>
+        <v>5.00056028366089</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>5.5</v>
       </c>
       <c r="G542" t="n">
-        <v>5.0188102722168</v>
+        <v>5.01881074905396</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>5.5</v>
       </c>
       <c r="G544" t="n">
-        <v>5.0188102722168</v>
+        <v>5.01881074905396</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G546" t="n">
-        <v>5.14656114578247</v>
+        <v>5.14656257629395</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G547" t="n">
-        <v>5.14656114578247</v>
+        <v>5.14656257629395</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G548" t="n">
-        <v>5.20131206512451</v>
+        <v>5.20131254196167</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G549" t="n">
-        <v>5.16481161117554</v>
+        <v>5.1648120880127</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G550" t="n">
-        <v>5.12831163406372</v>
+        <v>5.12831115722656</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G551" t="n">
-        <v>5.18306159973145</v>
+        <v>5.1830620765686</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G552" t="n">
-        <v>5.16481161117554</v>
+        <v>5.1648120880127</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G553" t="n">
-        <v>5.29256391525269</v>
+        <v>5.29256343841553</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G554" t="n">
-        <v>5.29256391525269</v>
+        <v>5.29256343841553</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G555" t="n">
-        <v>5.25606298446655</v>
+        <v>5.25606346130371</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G556" t="n">
-        <v>5.32906341552734</v>
+        <v>5.3290638923645</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G557" t="n">
-        <v>5.42031478881836</v>
+        <v>5.42031574249268</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>6</v>
       </c>
       <c r="G558" t="n">
-        <v>5.47506523132324</v>
+        <v>5.47506618499756</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G562" t="n">
-        <v>5.56631660461426</v>
+        <v>5.56631708145142</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>6</v>
       </c>
       <c r="G563" t="n">
-        <v>5.47506523132324</v>
+        <v>5.47506618499756</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G564" t="n">
-        <v>5.42031478881836</v>
+        <v>5.42031574249268</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G565" t="n">
-        <v>5.32906341552734</v>
+        <v>5.3290638923645</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G566" t="n">
-        <v>5.29256391525269</v>
+        <v>5.29256343841553</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G567" t="n">
-        <v>5.29256391525269</v>
+        <v>5.29256343841553</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G569" t="n">
-        <v>5.25606298446655</v>
+        <v>5.25606346130371</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G570" t="n">
-        <v>5.29256391525269</v>
+        <v>5.29256343841553</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G571" t="n">
-        <v>5.32906341552734</v>
+        <v>5.3290638923645</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>6</v>
       </c>
       <c r="G572" t="n">
-        <v>5.47506523132324</v>
+        <v>5.47506618499756</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>6</v>
       </c>
       <c r="G573" t="n">
-        <v>5.47506523132324</v>
+        <v>5.47506618499756</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G574" t="n">
-        <v>5.42031478881836</v>
+        <v>5.42031574249268</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G575" t="n">
-        <v>5.40206480026245</v>
+        <v>5.40206527709961</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G576" t="n">
-        <v>5.31081390380859</v>
+        <v>5.31081438064575</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G577" t="n">
-        <v>5.29256391525269</v>
+        <v>5.29256343841553</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G578" t="n">
-        <v>5.36556482315063</v>
+        <v>5.36556434631348</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G579" t="n">
-        <v>5.34731388092041</v>
+        <v>5.34731435775757</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G580" t="n">
-        <v>5.42031478881836</v>
+        <v>5.42031574249268</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G581" t="n">
-        <v>5.45681524276733</v>
+        <v>5.45681571960449</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G583" t="n">
-        <v>5.43856573104858</v>
+        <v>5.43856525421143</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G584" t="n">
-        <v>5.43856573104858</v>
+        <v>5.43856525421143</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G585" t="n">
-        <v>5.43856573104858</v>
+        <v>5.43856525421143</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G586" t="n">
-        <v>5.42031478881836</v>
+        <v>5.42031574249268</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>6</v>
       </c>
       <c r="G587" t="n">
-        <v>5.47506523132324</v>
+        <v>5.47506618499756</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>6</v>
       </c>
       <c r="G588" t="n">
-        <v>5.47506523132324</v>
+        <v>5.47506618499756</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G589" t="n">
-        <v>5.43856573104858</v>
+        <v>5.43856525421143</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G590" t="n">
-        <v>5.43856573104858</v>
+        <v>5.43856525421143</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>6</v>
       </c>
       <c r="G591" t="n">
-        <v>5.47506523132324</v>
+        <v>5.47506618499756</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>6</v>
       </c>
       <c r="G592" t="n">
-        <v>5.47506523132324</v>
+        <v>5.47506618499756</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>6</v>
       </c>
       <c r="G593" t="n">
-        <v>5.47506523132324</v>
+        <v>5.47506618499756</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G594" t="n">
-        <v>5.43856573104858</v>
+        <v>5.43856525421143</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15839,7 +15839,7 @@
         <v>6</v>
       </c>
       <c r="G595" t="n">
-        <v>5.47506523132324</v>
+        <v>5.47506618499756</v>
       </c>
       <c r="H595" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>6</v>
       </c>
       <c r="G596" t="n">
-        <v>5.47506523132324</v>
+        <v>5.47506618499756</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>6</v>
       </c>
       <c r="G597" t="n">
-        <v>5.47506523132324</v>
+        <v>5.47506618499756</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G598" t="n">
-        <v>5.45681524276733</v>
+        <v>5.45681571960449</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G599" t="n">
-        <v>5.51156568527222</v>
+        <v>5.51156616210938</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>6</v>
       </c>
       <c r="G601" t="n">
-        <v>5.47506523132324</v>
+        <v>5.47506618499756</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>6</v>
       </c>
       <c r="G602" t="n">
-        <v>5.47506523132324</v>
+        <v>5.47506618499756</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G603" t="n">
-        <v>5.51156568527222</v>
+        <v>5.51156616210938</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>6</v>
       </c>
       <c r="G604" t="n">
-        <v>5.47506523132324</v>
+        <v>5.47506618499756</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G605" t="n">
-        <v>5.51156568527222</v>
+        <v>5.51156616210938</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G606" t="n">
-        <v>5.69406747817993</v>
+        <v>5.69406843185425</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G608" t="n">
-        <v>6.07732248306274</v>
+        <v>6.0773229598999</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G609" t="n">
-        <v>6.29632616043091</v>
+        <v>6.29632568359375</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G610" t="n">
-        <v>6.27807569503784</v>
+        <v>6.27807521820068</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G611" t="n">
-        <v>6.40582704544067</v>
+        <v>6.40582752227783</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G612" t="n">
-        <v>6.49707841873169</v>
+        <v>6.49707746505737</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G614" t="n">
-        <v>6.49707841873169</v>
+        <v>6.49707746505737</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G615" t="n">
-        <v>6.47882747650146</v>
+        <v>6.47882795333862</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G616" t="n">
-        <v>6.49707841873169</v>
+        <v>6.49707746505737</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G619" t="n">
-        <v>7.00808334350586</v>
+        <v>7.00808429718018</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G620" t="n">
-        <v>6.91683292388916</v>
+        <v>6.91683340072632</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G621" t="n">
-        <v>7.13583612442017</v>
+        <v>7.13583564758301</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G623" t="n">
-        <v>7.39133930206299</v>
+        <v>7.39133882522583</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G624" t="n">
-        <v>7.62859201431274</v>
+        <v>7.62859106063843</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>8.5</v>
       </c>
       <c r="G625" t="n">
-        <v>7.75634241104126</v>
+        <v>7.75634384155273</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G626" t="n">
-        <v>7.73809289932251</v>
+        <v>7.73809242248535</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G628" t="n">
-        <v>7.88409471511841</v>
+        <v>7.88409423828125</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G630" t="n">
-        <v>7.93884611129761</v>
+        <v>7.93884563446045</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>8.5</v>
       </c>
       <c r="G631" t="n">
-        <v>7.75634241104126</v>
+        <v>7.75634384155273</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G632" t="n">
-        <v>7.93884611129761</v>
+        <v>7.93884563446045</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G633" t="n">
-        <v>7.97534513473511</v>
+        <v>7.97534608840942</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G634" t="n">
-        <v>8.43159961700439</v>
+        <v>8.43160152435303</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G635" t="n">
-        <v>8.57760143280029</v>
+        <v>8.57760334014893</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G636" t="n">
-        <v>8.65060424804688</v>
+        <v>8.65060329437256</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G637" t="n">
-        <v>8.63235378265381</v>
+        <v>8.63235282897949</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G638" t="n">
-        <v>8.65060424804688</v>
+        <v>8.65060329437256</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G639" t="n">
-        <v>8.26734924316406</v>
+        <v>8.26735019683838</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G640" t="n">
-        <v>8.26734924316406</v>
+        <v>8.26735019683838</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G643" t="n">
-        <v>8.57760143280029</v>
+        <v>8.57760334014893</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G644" t="n">
-        <v>8.43159961700439</v>
+        <v>8.43160152435303</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G649" t="n">
-        <v>8.52285194396973</v>
+        <v>8.52285289764404</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G655" t="n">
-        <v>9.08860874176025</v>
+        <v>9.08860969543457</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>10.25</v>
       </c>
       <c r="G657" t="n">
-        <v>9.35323810577393</v>
+        <v>9.35323715209961</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G659" t="n">
-        <v>9.99199485778809</v>
+        <v>9.9919958114624</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G662" t="n">
-        <v>9.67261505126953</v>
+        <v>9.67261695861816</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G664" t="n">
-        <v>9.3988618850708</v>
+        <v>9.39886283874512</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>10.75</v>
       </c>
       <c r="G667" t="n">
-        <v>9.80949211120605</v>
+        <v>9.80949306488037</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>10.25</v>
       </c>
       <c r="G668" t="n">
-        <v>9.35323810577393</v>
+        <v>9.35323715209961</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G670" t="n">
-        <v>9.3988618850708</v>
+        <v>9.39886283874512</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G671" t="n">
-        <v>9.3988618850708</v>
+        <v>9.39886283874512</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G673" t="n">
-        <v>9.03385829925537</v>
+        <v>9.03385734558105</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>9.49011421203613</v>
+        <v>9.49011325836182</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G676" t="n">
-        <v>9.67261505126953</v>
+        <v>9.67261695861816</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G677" t="n">
-        <v>9.94636821746826</v>
+        <v>9.94636917114258</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G678" t="n">
-        <v>9.99199485778809</v>
+        <v>9.9919958114624</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G679" t="n">
-        <v>9.99199485778809</v>
+        <v>9.9919958114624</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G680" t="n">
-        <v>9.99199485778809</v>
+        <v>9.9919958114624</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G681" t="n">
-        <v>9.99199485778809</v>
+        <v>9.9919958114624</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G682" t="n">
-        <v>9.99199485778809</v>
+        <v>9.9919958114624</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G683" t="n">
-        <v>9.67261505126953</v>
+        <v>9.67261695861816</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G684" t="n">
-        <v>9.67261505126953</v>
+        <v>9.67261695861816</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G685" t="n">
-        <v>9.67261505126953</v>
+        <v>9.67261695861816</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18205,7 +18205,7 @@
         <v>10.75</v>
       </c>
       <c r="G686" t="n">
-        <v>9.80949211120605</v>
+        <v>9.80949306488037</v>
       </c>
       <c r="H686" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G687" t="n">
-        <v>9.71824073791504</v>
+        <v>9.71824169158936</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G688" t="n">
-        <v>8.90610694885254</v>
+        <v>8.90610790252686</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G691" t="n">
-        <v>9.10685729980469</v>
+        <v>9.106858253479</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G693" t="n">
-        <v>8.77835464477539</v>
+        <v>8.77835559844971</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G698" t="n">
-        <v>7.61034202575684</v>
+        <v>7.61034250259399</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G702" t="n">
-        <v>7.263587474823</v>
+        <v>7.26358795166016</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G703" t="n">
-        <v>7.02633380889893</v>
+        <v>7.02633428573608</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G704" t="n">
-        <v>7.02633380889893</v>
+        <v>7.02633428573608</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G705" t="n">
-        <v>6.91683292388916</v>
+        <v>6.91683340072632</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G706" t="n">
-        <v>7.02633380889893</v>
+        <v>7.02633428573608</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G707" t="n">
-        <v>7.50084114074707</v>
+        <v>7.50084018707275</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G708" t="n">
-        <v>7.51909112930298</v>
+        <v>7.51909065246582</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G709" t="n">
-        <v>7.62859201431274</v>
+        <v>7.62859106063843</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G710" t="n">
-        <v>8.03009605407715</v>
+        <v>8.03009700775146</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G711" t="n">
-        <v>7.64684200286865</v>
+        <v>7.64684247970581</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G712" t="n">
-        <v>7.77459526062012</v>
+        <v>7.77459335327148</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>8.5</v>
       </c>
       <c r="G713" t="n">
-        <v>7.75634241104126</v>
+        <v>7.75634384155273</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G714" t="n">
-        <v>7.88409471511841</v>
+        <v>7.88409423828125</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G715" t="n">
-        <v>8.0483455657959</v>
+        <v>8.04834651947021</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G716" t="n">
-        <v>8.32209968566895</v>
+        <v>8.32209873199463</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G718" t="n">
-        <v>8.39510059356689</v>
+        <v>8.39509963989258</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G719" t="n">
-        <v>8.76010513305664</v>
+        <v>8.76010608673096</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G720" t="n">
-        <v>9.03385829925537</v>
+        <v>9.03385734558105</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G721" t="n">
-        <v>9.05210781097412</v>
+        <v>9.05210876464844</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G722" t="n">
-        <v>9.21636199951172</v>
+        <v>9.2163610458374</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G723" t="n">
-        <v>8.92435646057129</v>
+        <v>8.92435741424561</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>9.05210781097412</v>
+        <v>9.05210876464844</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G725" t="n">
-        <v>9.08860874176025</v>
+        <v>9.08860969543457</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G726" t="n">
-        <v>9.08860874176025</v>
+        <v>9.08860969543457</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G730" t="n">
-        <v>9.49011421203613</v>
+        <v>9.49011325836182</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>9.67261505126953</v>
+        <v>9.67261695861816</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G732" t="n">
-        <v>9.67261505126953</v>
+        <v>9.67261695861816</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G733" t="n">
-        <v>10.220121383667</v>
+        <v>10.2201232910156</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G734" t="n">
-        <v>10.402624130249</v>
+        <v>10.4026250839233</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G735" t="n">
-        <v>10.356390953064</v>
+        <v>10.3563919067383</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G736" t="n">
-        <v>10.1252212524414</v>
+        <v>10.1252222061157</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G737" t="n">
-        <v>10.2176904678345</v>
+        <v>10.2176895141602</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G738" t="n">
-        <v>10.3101558685303</v>
+        <v>10.3101568222046</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G741" t="n">
-        <v>10.3101558685303</v>
+        <v>10.3101568222046</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G742" t="n">
-        <v>9.98652076721191</v>
+        <v>9.9865198135376</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G743" t="n">
-        <v>10.0327548980713</v>
+        <v>10.032753944397</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G744" t="n">
-        <v>9.98652076721191</v>
+        <v>9.9865198135376</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G745" t="n">
-        <v>10.0327548980713</v>
+        <v>10.032753944397</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>10.25</v>
       </c>
       <c r="G747" t="n">
-        <v>9.47794818878174</v>
+        <v>9.47794723510742</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G749" t="n">
-        <v>9.98652076721191</v>
+        <v>9.9865198135376</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G752" t="n">
-        <v>9.61664962768555</v>
+        <v>9.61664867401123</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G754" t="n">
-        <v>9.98652076721191</v>
+        <v>9.9865198135376</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G755" t="n">
-        <v>10.078987121582</v>
+        <v>10.0789880752563</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G756" t="n">
-        <v>10.356390953064</v>
+        <v>10.3563919067383</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G757" t="n">
-        <v>10.3101558685303</v>
+        <v>10.3101568222046</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G758" t="n">
-        <v>10.448860168457</v>
+        <v>10.4488582611084</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G760" t="n">
-        <v>10.448860168457</v>
+        <v>10.4488582611084</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G761" t="n">
-        <v>10.356390953064</v>
+        <v>10.3563919067383</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G762" t="n">
-        <v>10.356390953064</v>
+        <v>10.3563919067383</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G763" t="n">
-        <v>10.448860168457</v>
+        <v>10.4488582611084</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G765" t="n">
-        <v>10.078987121582</v>
+        <v>10.0789880752563</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G766" t="n">
-        <v>10.5413255691528</v>
+        <v>10.5413274765015</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G767" t="n">
-        <v>10.5413255691528</v>
+        <v>10.5413274765015</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G769" t="n">
-        <v>11.6047058105469</v>
+        <v>11.6047067642212</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G770" t="n">
-        <v>11.9745779037476</v>
+        <v>11.9745769500732</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G771" t="n">
-        <v>12.7605543136597</v>
+        <v>12.7605533599854</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>13</v>
       </c>
       <c r="G772" t="n">
-        <v>12.0208110809326</v>
+        <v>12.0208101272583</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G773" t="n">
-        <v>12.2982149124146</v>
+        <v>12.2982139587402</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>13.25</v>
       </c>
       <c r="G774" t="n">
-        <v>12.2519807815552</v>
+        <v>12.2519798278809</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G775" t="n">
-        <v>12.1132793426514</v>
+        <v>12.1132802963257</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>13</v>
       </c>
       <c r="G776" t="n">
-        <v>12.0208110809326</v>
+        <v>12.0208101272583</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G777" t="n">
-        <v>12.1595115661621</v>
+        <v>12.1595125198364</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G778" t="n">
-        <v>11.9745779037476</v>
+        <v>11.9745769500732</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G779" t="n">
-        <v>11.8821086883545</v>
+        <v>11.8821096420288</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>13</v>
       </c>
       <c r="G781" t="n">
-        <v>12.0208110809326</v>
+        <v>12.0208101272583</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G782" t="n">
-        <v>11.8821086883545</v>
+        <v>11.8821096420288</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G783" t="n">
-        <v>11.9283428192139</v>
+        <v>11.9283437728882</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G784" t="n">
-        <v>11.8358755111694</v>
+        <v>11.8358745574951</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G785" t="n">
-        <v>11.9745779037476</v>
+        <v>11.9745769500732</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>12.75</v>
       </c>
       <c r="G786" t="n">
-        <v>11.7896413803101</v>
+        <v>11.7896423339844</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>12.75</v>
       </c>
       <c r="G787" t="n">
-        <v>11.7896413803101</v>
+        <v>11.7896423339844</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>11.8821086883545</v>
+        <v>11.8821096420288</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>13</v>
       </c>
       <c r="G789" t="n">
-        <v>12.0208110809326</v>
+        <v>12.0208101272583</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G790" t="n">
-        <v>11.9283428192139</v>
+        <v>11.9283437728882</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G791" t="n">
-        <v>11.7434072494507</v>
+        <v>11.743408203125</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G792" t="n">
-        <v>11.6509389877319</v>
+        <v>11.6509399414062</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G794" t="n">
-        <v>11.6509389877319</v>
+        <v>11.6509399414062</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G795" t="n">
-        <v>11.4660043716431</v>
+        <v>11.4660034179688</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>12.75</v>
       </c>
       <c r="G796" t="n">
-        <v>11.7896413803101</v>
+        <v>11.7896423339844</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G797" t="n">
-        <v>11.6971750259399</v>
+        <v>11.6971740722656</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G798" t="n">
-        <v>11.419771194458</v>
+        <v>11.4197702407837</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G800" t="n">
-        <v>11.37353515625</v>
+        <v>11.3735370635986</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G807" t="n">
-        <v>11.2810688018799</v>
+        <v>11.2810697555542</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G808" t="n">
-        <v>11.37353515625</v>
+        <v>11.3735370635986</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G809" t="n">
-        <v>11.2810688018799</v>
+        <v>11.2810697555542</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G810" t="n">
-        <v>11.419771194458</v>
+        <v>11.4197702407837</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>12.5</v>
       </c>
       <c r="G811" t="n">
-        <v>11.5584726333618</v>
+        <v>11.5584716796875</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G812" t="n">
-        <v>11.8358755111694</v>
+        <v>11.8358745574951</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>12.5</v>
       </c>
       <c r="G813" t="n">
-        <v>11.5584726333618</v>
+        <v>11.5584716796875</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G814" t="n">
-        <v>11.6509389877319</v>
+        <v>11.6509399414062</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G815" t="n">
-        <v>11.6509389877319</v>
+        <v>11.6509399414062</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>12.75</v>
       </c>
       <c r="G816" t="n">
-        <v>11.7896413803101</v>
+        <v>11.7896423339844</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G817" t="n">
-        <v>11.6509389877319</v>
+        <v>11.6509399414062</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G818" t="n">
-        <v>11.6509389877319</v>
+        <v>11.6509399414062</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G819" t="n">
-        <v>11.6971750259399</v>
+        <v>11.6971740722656</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G820" t="n">
-        <v>11.4660043716431</v>
+        <v>11.4660034179688</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G821" t="n">
-        <v>11.2810688018799</v>
+        <v>11.2810697555542</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G823" t="n">
-        <v>11.2810688018799</v>
+        <v>11.2810697555542</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G824" t="n">
-        <v>11.6509389877319</v>
+        <v>11.6509399414062</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G825" t="n">
-        <v>11.9745779037476</v>
+        <v>11.9745769500732</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>12.3444480895996</v>
+        <v>12.3444499969482</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G828" t="n">
-        <v>12.8992538452148</v>
+        <v>12.8992557525635</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G831" t="n">
-        <v>13.7314643859863</v>
+        <v>13.7314653396606</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>15.75</v>
       </c>
       <c r="G834" t="n">
-        <v>14.5636739730835</v>
+        <v>14.5636758804321</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>16.25</v>
       </c>
       <c r="G836" t="n">
-        <v>15.0260124206543</v>
+        <v>15.0260133743286</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G837" t="n">
-        <v>16.3667964935303</v>
+        <v>16.3667984008789</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G840" t="n">
-        <v>16.2280921936035</v>
+        <v>16.2280941009521</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G841" t="n">
-        <v>16.2280921936035</v>
+        <v>16.2280941009521</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>17</v>
       </c>
       <c r="G843" t="n">
-        <v>15.7195205688477</v>
+        <v>15.7195234298706</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G845" t="n">
-        <v>15.1647148132324</v>
+        <v>15.1647157669067</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G846" t="n">
-        <v>14.9335451126099</v>
+        <v>14.9335470199585</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>16.5</v>
       </c>
       <c r="G848" t="n">
-        <v>15.2571830749512</v>
+        <v>15.2571821212769</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G850" t="n">
-        <v>15.6270542144775</v>
+        <v>15.6270513534546</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G851" t="n">
-        <v>15.9969234466553</v>
+        <v>15.9969263076782</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G852" t="n">
-        <v>15.9969234466553</v>
+        <v>15.9969263076782</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G853" t="n">
-        <v>15.8119916915894</v>
+        <v>15.811990737915</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G855" t="n">
-        <v>15.1647148132324</v>
+        <v>15.1647157669067</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>14.9797811508179</v>
+        <v>14.9797801971436</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G857" t="n">
-        <v>14.748610496521</v>
+        <v>14.7486114501953</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G859" t="n">
-        <v>13.9164009094238</v>
+        <v>13.9164018630981</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G860" t="n">
-        <v>13.5465297698975</v>
+        <v>13.5465288162231</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G861" t="n">
-        <v>13.36159324646</v>
+        <v>13.3615951538086</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G862" t="n">
-        <v>12.4369163513184</v>
+        <v>12.436915397644</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G865" t="n">
-        <v>13.36159324646</v>
+        <v>13.3615951538086</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>16.5</v>
       </c>
       <c r="G869" t="n">
-        <v>15.2571830749512</v>
+        <v>15.2571821212769</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G871" t="n">
-        <v>14.9797811508179</v>
+        <v>14.9797801971436</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G872" t="n">
-        <v>15.072247505188</v>
+        <v>15.0722455978394</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G873" t="n">
-        <v>14.748610496521</v>
+        <v>14.7486114501953</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>16</v>
       </c>
       <c r="G875" t="n">
-        <v>14.7948436737061</v>
+        <v>14.7948446273804</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G876" t="n">
-        <v>14.1475696563721</v>
+        <v>14.1475706100464</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G879" t="n">
-        <v>14.7023773193359</v>
+        <v>14.7023754119873</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G880" t="n">
-        <v>14.4712076187134</v>
+        <v>14.4712066650391</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G884" t="n">
-        <v>13.9164009094238</v>
+        <v>13.9164018630981</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>13.5465297698975</v>
+        <v>13.5465288162231</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G886" t="n">
-        <v>13.8239316940308</v>
+        <v>13.8239326477051</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G888" t="n">
-        <v>13.3153591156006</v>
+        <v>13.3153610229492</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G893" t="n">
-        <v>13.6852312088013</v>
+        <v>13.685230255127</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>16</v>
       </c>
       <c r="G895" t="n">
-        <v>14.7948436737061</v>
+        <v>14.7948446273804</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>16</v>
       </c>
       <c r="G898" t="n">
-        <v>14.7948436737061</v>
+        <v>14.7948446273804</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G901" t="n">
-        <v>15.1647148132324</v>
+        <v>15.1647157669067</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G902" t="n">
-        <v>15.072247505188</v>
+        <v>15.0722455978394</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G903" t="n">
-        <v>14.9335451126099</v>
+        <v>14.9335470199585</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G905" t="n">
-        <v>15.072247505188</v>
+        <v>15.0722455978394</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G906" t="n">
-        <v>15.5345878601074</v>
+        <v>15.5345859527588</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G908" t="n">
-        <v>15.118483543396</v>
+        <v>15.1184816360474</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G909" t="n">
-        <v>14.9335451126099</v>
+        <v>14.9335470199585</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>16</v>
       </c>
       <c r="G910" t="n">
-        <v>14.7948436737061</v>
+        <v>14.7948446273804</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G911" t="n">
-        <v>14.748610496521</v>
+        <v>14.7486114501953</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24211,7 +24211,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G917" t="n">
-        <v>14.1475696563721</v>
+        <v>14.1475706100464</v>
       </c>
       <c r="H917" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G920" t="n">
-        <v>14.1475696563721</v>
+        <v>14.1475706100464</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G927" t="n">
-        <v>14.0551013946533</v>
+        <v>14.0551023483276</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G931" t="n">
-        <v>15.072247505188</v>
+        <v>15.0722455978394</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G933" t="n">
-        <v>15.1647148132324</v>
+        <v>15.1647157669067</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>16</v>
       </c>
       <c r="G934" t="n">
-        <v>14.7948436737061</v>
+        <v>14.7948446273804</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G935" t="n">
-        <v>14.7023773193359</v>
+        <v>14.7023754119873</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G936" t="n">
-        <v>14.9797811508179</v>
+        <v>14.9797801971436</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G938" t="n">
-        <v>14.748610496521</v>
+        <v>14.7486114501953</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G940" t="n">
-        <v>14.7023773193359</v>
+        <v>14.7023754119873</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>15.75</v>
       </c>
       <c r="G941" t="n">
-        <v>14.5636739730835</v>
+        <v>14.5636758804321</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G943" t="n">
-        <v>14.7023773193359</v>
+        <v>14.7023754119873</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G947" t="n">
-        <v>14.6099090576172</v>
+        <v>14.6099100112915</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G950" t="n">
-        <v>13.6852312088013</v>
+        <v>13.685230255127</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G951" t="n">
-        <v>13.5465297698975</v>
+        <v>13.5465288162231</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G952" t="n">
-        <v>13.9164009094238</v>
+        <v>13.9164018630981</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G956" t="n">
-        <v>14.0551013946533</v>
+        <v>14.0551023483276</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G957" t="n">
-        <v>14.0551013946533</v>
+        <v>14.0551023483276</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25303,7 +25303,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G959" t="n">
-        <v>14.1475696563721</v>
+        <v>14.1475706100464</v>
       </c>
       <c r="H959" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G961" t="n">
-        <v>13.5465297698975</v>
+        <v>13.5465288162231</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G962" t="n">
-        <v>13.36159324646</v>
+        <v>13.3615951538086</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25485,7 +25485,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G966" t="n">
-        <v>14.1475696563721</v>
+        <v>14.1475706100464</v>
       </c>
       <c r="H966" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G967" t="n">
-        <v>14.4712076187134</v>
+        <v>14.4712066650391</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>15.5</v>
       </c>
       <c r="G970" t="n">
-        <v>14.3325061798096</v>
+        <v>14.3325052261353</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G971" t="n">
-        <v>14.6099090576172</v>
+        <v>14.6099100112915</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G972" t="n">
-        <v>14.2585306167603</v>
+        <v>14.2585315704346</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G973" t="n">
-        <v>14.498948097229</v>
+        <v>14.4989471435547</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G975" t="n">
-        <v>14.350998878479</v>
+        <v>14.3509998321533</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G977" t="n">
-        <v>14.7023773193359</v>
+        <v>14.7023754119873</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>16</v>
       </c>
       <c r="G978" t="n">
-        <v>14.7948436737061</v>
+        <v>14.7948446273804</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>16</v>
       </c>
       <c r="G979" t="n">
-        <v>14.7948436737061</v>
+        <v>14.7948446273804</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G983" t="n">
-        <v>14.9242992401123</v>
+        <v>14.924298286438</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G984" t="n">
-        <v>15.2017049789429</v>
+        <v>15.2017021179199</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>16</v>
       </c>
       <c r="G985" t="n">
-        <v>14.7948436737061</v>
+        <v>14.7948446273804</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G986" t="n">
-        <v>15.0352611541748</v>
+        <v>15.0352602005005</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G987" t="n">
-        <v>14.9982738494873</v>
+        <v>14.998272895813</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G989" t="n">
-        <v>15.072247505188</v>
+        <v>15.0722455978394</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G991" t="n">
-        <v>14.7023773193359</v>
+        <v>14.7023754119873</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G992" t="n">
-        <v>14.9612865447998</v>
+        <v>14.9612874984741</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G993" t="n">
-        <v>14.9612865447998</v>
+        <v>14.9612874984741</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G996" t="n">
-        <v>14.5191965103149</v>
+        <v>14.5191955566406</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G998" t="n">
-        <v>14.9845552444458</v>
+        <v>14.9845561981201</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1000" t="n">
-        <v>15.1706981658936</v>
+        <v>15.1706972122192</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1001" t="n">
-        <v>15.2265434265137</v>
+        <v>15.226541519165</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1002" t="n">
-        <v>15.2079267501831</v>
+        <v>15.2079277038574</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1003" t="n">
-        <v>14.9845552444458</v>
+        <v>14.9845561981201</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>16.4699993133545</v>
       </c>
       <c r="G1004" t="n">
-        <v>15.3289203643799</v>
+        <v>15.3289194107056</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>17.75</v>
       </c>
       <c r="G1006" t="n">
-        <v>16.5202388763428</v>
+        <v>16.5202407836914</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1007" t="n">
-        <v>16.5667724609375</v>
+        <v>16.5667743682861</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1009" t="n">
-        <v>17.9814643859863</v>
+        <v>17.981466293335</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G1011" t="n">
-        <v>17.4602642059326</v>
+        <v>17.460262298584</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26681,7 +26681,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1012" t="n">
-        <v>17.2741222381592</v>
+        <v>17.2741184234619</v>
       </c>
       <c r="H1012" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1013" t="n">
-        <v>17.4044208526611</v>
+        <v>17.4044227600098</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1014" t="n">
-        <v>18.0559215545654</v>
+        <v>18.0559253692627</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1019" t="n">
-        <v>16.3992443084717</v>
+        <v>16.3992462158203</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G1022" t="n">
-        <v>17.1624336242676</v>
+        <v>17.1624355316162</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1023" t="n">
-        <v>17.5905628204346</v>
+        <v>17.5905666351318</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1024" t="n">
-        <v>17.4974918365479</v>
+        <v>17.4974937438965</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1025" t="n">
-        <v>17.4974918365479</v>
+        <v>17.4974937438965</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1026" t="n">
-        <v>17.4974918365479</v>
+        <v>17.4974937438965</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1027" t="n">
-        <v>17.9814643859863</v>
+        <v>17.981466293335</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G1028" t="n">
-        <v>17.7208652496338</v>
+        <v>17.7208671569824</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G1031" t="n">
-        <v>17.6650199890137</v>
+        <v>17.6650218963623</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1036" t="n">
-        <v>18.2979106903076</v>
+        <v>18.297908782959</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G1039" t="n">
-        <v>18.2234516143799</v>
+        <v>18.2234535217285</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1040" t="n">
-        <v>18.3351402282715</v>
+        <v>18.3351383209229</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G1041" t="n">
-        <v>18.409595489502</v>
+        <v>18.4095993041992</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1042" t="n">
-        <v>18.2979106903076</v>
+        <v>18.297908782959</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1047" t="n">
-        <v>17.5905628204346</v>
+        <v>17.5905666351318</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1048" t="n">
-        <v>17.5905628204346</v>
+        <v>17.5905666351318</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27695,7 +27695,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G1051" t="n">
-        <v>17.9442386627197</v>
+        <v>17.9442367553711</v>
       </c>
       <c r="H1051" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1052" t="n">
-        <v>17.9814643859863</v>
+        <v>17.981466293335</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1054" t="n">
-        <v>18.5212821960449</v>
+        <v>18.5212783813477</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>20.25</v>
       </c>
       <c r="G1055" t="n">
-        <v>18.8470344543457</v>
+        <v>18.8470325469971</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G1057" t="n">
-        <v>20.1500377655029</v>
+        <v>20.1500358581543</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1058" t="n">
-        <v>20.6153945922852</v>
+        <v>20.6153984069824</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1059" t="n">
-        <v>20.5688629150391</v>
+        <v>20.5688610076904</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>23</v>
       </c>
       <c r="G1062" t="n">
-        <v>21.4065036773682</v>
+        <v>21.4065055847168</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1065" t="n">
-        <v>22.058012008667</v>
+        <v>22.0580101013184</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28085,7 +28085,7 @@
         <v>24.5</v>
       </c>
       <c r="G1066" t="n">
-        <v>22.802583694458</v>
+        <v>22.8025817871094</v>
       </c>
       <c r="H1066" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>24.2399997711182</v>
       </c>
       <c r="G1075" t="n">
-        <v>22.5605945587158</v>
+        <v>22.5605964660645</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>25.2199993133545</v>
       </c>
       <c r="G1076" t="n">
-        <v>23.4726982116699</v>
+        <v>23.4727001190186</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>26.3600006103516</v>
       </c>
       <c r="G1077" t="n">
-        <v>24.5337200164795</v>
+        <v>24.5337181091309</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>25.5</v>
       </c>
       <c r="G1078" t="n">
-        <v>23.7333011627197</v>
+        <v>23.7333030700684</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>25.6200008392334</v>
       </c>
       <c r="G1080" t="n">
-        <v>23.8449878692627</v>
+        <v>23.8449859619141</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G1081" t="n">
-        <v>25.2969055175781</v>
+        <v>25.2969074249268</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>26.9200000762939</v>
       </c>
       <c r="G1085" t="n">
-        <v>25.0549201965332</v>
+        <v>25.0549221038818</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>26.1599998474121</v>
       </c>
       <c r="G1089" t="n">
-        <v>24.3475761413574</v>
+        <v>24.3475742340088</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>27.3199996948242</v>
       </c>
       <c r="G1090" t="n">
-        <v>25.4272060394287</v>
+        <v>25.4272079467773</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>27.2199993133545</v>
       </c>
       <c r="G1091" t="n">
-        <v>25.3341331481934</v>
+        <v>25.334135055542</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>26.5599994659424</v>
       </c>
       <c r="G1092" t="n">
-        <v>24.7198600769043</v>
+        <v>24.7198619842529</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>24.5200004577637</v>
       </c>
       <c r="G1095" t="n">
-        <v>22.8211975097656</v>
+        <v>22.8211994171143</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>24.5</v>
       </c>
       <c r="G1096" t="n">
-        <v>22.802583694458</v>
+        <v>22.8025817871094</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>24.5400009155273</v>
       </c>
       <c r="G1097" t="n">
-        <v>22.8398113250732</v>
+        <v>22.8398132324219</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>25</v>
       </c>
       <c r="G1098" t="n">
-        <v>23.2679424285889</v>
+        <v>23.2679405212402</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1100" t="n">
-        <v>23.5471591949463</v>
+        <v>23.5471572875977</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1101" t="n">
-        <v>23.5471591949463</v>
+        <v>23.5471572875977</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1105" t="n">
-        <v>24.1055889129639</v>
+        <v>24.1055870056152</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>26.5</v>
       </c>
       <c r="G1107" t="n">
-        <v>24.6640186309814</v>
+        <v>24.6640167236328</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1109" t="n">
-        <v>26.8046684265137</v>
+        <v>26.8046703338623</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1111" t="n">
-        <v>26.8046684265137</v>
+        <v>26.8046703338623</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>31.4400005340576</v>
       </c>
       <c r="G1112" t="n">
-        <v>29.2617645263672</v>
+        <v>29.2617664337158</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G1114" t="n">
-        <v>29.6898937225342</v>
+        <v>29.6898956298828</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>30.6599998474121</v>
       </c>
       <c r="G1117" t="n">
-        <v>28.5358047485352</v>
+        <v>28.5358028411865</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>30.8400001525879</v>
       </c>
       <c r="G1119" t="n">
-        <v>28.703332901001</v>
+        <v>28.7033348083496</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>32.1199989318848</v>
       </c>
       <c r="G1121" t="n">
-        <v>29.8946495056152</v>
+        <v>29.8946514129639</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>32.439998626709</v>
       </c>
       <c r="G1123" t="n">
-        <v>30.1924819946289</v>
+        <v>30.1924800872803</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>33.7200012207031</v>
       </c>
       <c r="G1124" t="n">
-        <v>31.3838005065918</v>
+        <v>31.3838024139404</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>33.5800018310547</v>
       </c>
       <c r="G1125" t="n">
-        <v>31.2535037994385</v>
+        <v>31.2535018920898</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>33.5</v>
       </c>
       <c r="G1129" t="n">
-        <v>31.1790409088135</v>
+        <v>31.1790428161621</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>32.9599990844727</v>
       </c>
       <c r="G1132" t="n">
-        <v>30.6764583587646</v>
+        <v>30.6764545440674</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>31.6200008392334</v>
       </c>
       <c r="G1134" t="n">
-        <v>29.4292945861816</v>
+        <v>29.429292678833</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>32.6399993896484</v>
       </c>
       <c r="G1137" t="n">
-        <v>30.3786239624023</v>
+        <v>30.378625869751</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29957,7 +29957,7 @@
         <v>32.4799995422363</v>
       </c>
       <c r="G1138" t="n">
-        <v>30.2297115325928</v>
+        <v>30.2297096252441</v>
       </c>
       <c r="H1138" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>32.8199996948242</v>
       </c>
       <c r="G1140" t="n">
-        <v>30.5461559295654</v>
+        <v>30.5461540222168</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>33.560001373291</v>
       </c>
       <c r="G1141" t="n">
-        <v>31.2348861694336</v>
+        <v>31.2348880767822</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>33.7200012207031</v>
       </c>
       <c r="G1142" t="n">
-        <v>31.3838005065918</v>
+        <v>31.3838024139404</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>33.4599990844727</v>
       </c>
       <c r="G1143" t="n">
-        <v>31.1418170928955</v>
+        <v>31.1418132781982</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>34.439998626709</v>
       </c>
       <c r="G1144" t="n">
-        <v>32.0539207458496</v>
+        <v>32.0539169311523</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>36.1199989318848</v>
       </c>
       <c r="G1145" t="n">
-        <v>33.6175231933594</v>
+        <v>33.6175193786621</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30243,7 +30243,7 @@
         <v>36.1399993896484</v>
       </c>
       <c r="G1149" t="n">
-        <v>33.6361389160156</v>
+        <v>33.6361351013184</v>
       </c>
       <c r="H1149" t="s">
         <v>8</v>
@@ -30269,7 +30269,7 @@
         <v>34.5800018310547</v>
       </c>
       <c r="G1150" t="n">
-        <v>32.1842231750488</v>
+        <v>32.1842193603516</v>
       </c>
       <c r="H1150" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G1151" t="n">
-        <v>31.5513305664062</v>
+        <v>31.5513324737549</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>33.6199989318848</v>
       </c>
       <c r="G1152" t="n">
-        <v>31.2907257080078</v>
+        <v>31.2907295227051</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>33.9199981689453</v>
       </c>
       <c r="G1153" t="n">
-        <v>31.5699424743652</v>
+        <v>31.5699443817139</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>34.1800003051758</v>
       </c>
       <c r="G1154" t="n">
-        <v>31.8119316101074</v>
+        <v>31.8119297027588</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1155" t="n">
-        <v>32.2028274536133</v>
+        <v>32.2028350830078</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G1156" t="n">
-        <v>33.7850494384766</v>
+        <v>33.7850532531738</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>35.7799987792969</v>
       </c>
       <c r="G1157" t="n">
-        <v>33.3010787963867</v>
+        <v>33.3010749816895</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>36.2799987792969</v>
       </c>
       <c r="G1158" t="n">
-        <v>33.7664375305176</v>
+        <v>33.7664337158203</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>35.7400016784668</v>
       </c>
       <c r="G1159" t="n">
-        <v>33.2638473510742</v>
+        <v>33.2638511657715</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>35.8400001525879</v>
       </c>
       <c r="G1161" t="n">
-        <v>33.3569183349609</v>
+        <v>33.3569221496582</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>36.0200004577637</v>
       </c>
       <c r="G1162" t="n">
-        <v>33.5244483947754</v>
+        <v>33.5244522094727</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>39.7000007629395</v>
       </c>
       <c r="G1164" t="n">
-        <v>36.9494934082031</v>
+        <v>36.9494895935059</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>34</v>
       </c>
       <c r="G1168" t="n">
-        <v>31.6443977355957</v>
+        <v>31.6444053649902</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G1169" t="n">
-        <v>32.4820518493652</v>
+        <v>32.482048034668</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>35.5</v>
       </c>
       <c r="G1170" t="n">
-        <v>33.0404777526855</v>
+        <v>33.0404815673828</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G1171" t="n">
-        <v>32.4820518493652</v>
+        <v>32.482048034668</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1172" t="n">
-        <v>32.2028274536133</v>
+        <v>32.2028350830078</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30867,7 +30867,7 @@
         <v>33.439998626709</v>
       </c>
       <c r="G1173" t="n">
-        <v>31.1231994628906</v>
+        <v>31.123197555542</v>
       </c>
       <c r="H1173" t="s">
         <v>8</v>
@@ -30893,7 +30893,7 @@
         <v>33.3800010681152</v>
       </c>
       <c r="G1174" t="n">
-        <v>31.0673561096191</v>
+        <v>31.0673580169678</v>
       </c>
       <c r="H1174" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1176" t="n">
-        <v>30.8998279571533</v>
+        <v>30.8998241424561</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>30.8400001525879</v>
       </c>
       <c r="G1177" t="n">
-        <v>28.703332901001</v>
+        <v>28.7033348083496</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>29.9200000762939</v>
       </c>
       <c r="G1178" t="n">
-        <v>27.847074508667</v>
+        <v>27.8470726013184</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31023,7 +31023,7 @@
         <v>30.1800003051758</v>
       </c>
       <c r="G1179" t="n">
-        <v>28.0890598297119</v>
+        <v>28.0890617370605</v>
       </c>
       <c r="H1179" t="s">
         <v>8</v>
@@ -31049,7 +31049,7 @@
         <v>30.2399997711182</v>
       </c>
       <c r="G1180" t="n">
-        <v>28.1449012756348</v>
+        <v>28.1449031829834</v>
       </c>
       <c r="H1180" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>30.0599994659424</v>
       </c>
       <c r="G1181" t="n">
-        <v>27.9773731231689</v>
+        <v>27.9773712158203</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>31.1800003051758</v>
       </c>
       <c r="G1182" t="n">
-        <v>29.0197792053223</v>
+        <v>29.0197772979736</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>32.9799995422363</v>
       </c>
       <c r="G1183" t="n">
-        <v>30.695068359375</v>
+        <v>30.6950702667236</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>32.5400009155273</v>
       </c>
       <c r="G1184" t="n">
-        <v>30.2855529785156</v>
+        <v>30.2855548858643</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>28.7800006866455</v>
       </c>
       <c r="G1192" t="n">
-        <v>26.7860546112061</v>
+        <v>26.7860527038574</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>30.1800003051758</v>
       </c>
       <c r="G1193" t="n">
-        <v>28.0890598297119</v>
+        <v>28.0890617370605</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>29.9799995422363</v>
       </c>
       <c r="G1194" t="n">
-        <v>27.9029140472412</v>
+        <v>27.9029159545898</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>30.2800006866455</v>
       </c>
       <c r="G1195" t="n">
-        <v>28.1821327209473</v>
+        <v>28.1821308135986</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G1197" t="n">
-        <v>26.3579254150391</v>
+        <v>26.3579235076904</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1198" t="n">
-        <v>26.8977394104004</v>
+        <v>26.897741317749</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G1199" t="n">
-        <v>26.1903953552246</v>
+        <v>26.1903972625732</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>27.6399993896484</v>
       </c>
       <c r="G1200" t="n">
-        <v>25.7250366210938</v>
+        <v>25.7250347137451</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31673,7 +31673,7 @@
         <v>28.5</v>
       </c>
       <c r="G1204" t="n">
-        <v>26.5254554748535</v>
+        <v>26.5254573822021</v>
       </c>
       <c r="H1204" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G1205" t="n">
-        <v>25.2969055175781</v>
+        <v>25.2969074249268</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>26.0400009155273</v>
       </c>
       <c r="G1206" t="n">
-        <v>24.2358913421631</v>
+        <v>24.2358894348145</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>25.7800006866455</v>
       </c>
       <c r="G1207" t="n">
-        <v>23.9939022064209</v>
+        <v>23.9939002990723</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G1211" t="n">
-        <v>26.1903953552246</v>
+        <v>26.1903972625732</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>28.4799995422363</v>
       </c>
       <c r="G1212" t="n">
-        <v>26.5068397521973</v>
+        <v>26.5068378448486</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>28.2399997711182</v>
       </c>
       <c r="G1213" t="n">
-        <v>26.2834663391113</v>
+        <v>26.28346824646</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1214" t="n">
-        <v>27.2141857147217</v>
+        <v>27.214183807373</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>29.3199996948242</v>
       </c>
       <c r="G1216" t="n">
-        <v>27.2886428833008</v>
+        <v>27.2886409759521</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>28.8400001525879</v>
       </c>
       <c r="G1217" t="n">
-        <v>26.8418998718262</v>
+        <v>26.8418979644775</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32115,7 +32115,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1221" t="n">
-        <v>28.293815612793</v>
+        <v>28.2938194274902</v>
       </c>
       <c r="H1221" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>29.9599990844727</v>
       </c>
       <c r="G1225" t="n">
-        <v>27.8843002319336</v>
+        <v>27.8843021392822</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>29.6399993896484</v>
       </c>
       <c r="G1227" t="n">
-        <v>27.5864696502686</v>
+        <v>27.5864734649658</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>28.9799995422363</v>
       </c>
       <c r="G1228" t="n">
-        <v>26.9721984863281</v>
+        <v>26.9721965789795</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>27.7399997711182</v>
       </c>
       <c r="G1230" t="n">
-        <v>25.8181095123291</v>
+        <v>25.8181056976318</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>27.2800006866455</v>
       </c>
       <c r="G1237" t="n">
-        <v>25.3899784088135</v>
+        <v>25.3899765014648</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G1238" t="n">
-        <v>25.2969055175781</v>
+        <v>25.2969074249268</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G1241" t="n">
-        <v>23.9647331237793</v>
+        <v>23.9647350311279</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>25</v>
       </c>
       <c r="G1242" t="n">
-        <v>23.5317516326904</v>
+        <v>23.5317497253418</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>25.5599994659424</v>
       </c>
       <c r="G1243" t="n">
-        <v>24.0588626861572</v>
+        <v>24.0588607788086</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32791,7 +32791,7 @@
         <v>23.8199996948242</v>
       </c>
       <c r="G1247" t="n">
-        <v>22.4210510253906</v>
+        <v>22.421049118042</v>
       </c>
       <c r="H1247" t="s">
         <v>8</v>
@@ -32843,7 +32843,7 @@
         <v>22.5200004577637</v>
       </c>
       <c r="G1249" t="n">
-        <v>21.1974010467529</v>
+        <v>21.1974029541016</v>
       </c>
       <c r="H1249" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1256" t="n">
-        <v>19.9549236297607</v>
+        <v>19.9549255371094</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G1259" t="n">
-        <v>19.6913681030273</v>
+        <v>19.691370010376</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33129,7 +33129,7 @@
         <v>21.1599998474121</v>
       </c>
       <c r="G1260" t="n">
-        <v>19.917272567749</v>
+        <v>19.9172744750977</v>
       </c>
       <c r="H1260" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1268" t="n">
-        <v>20.3314342498779</v>
+        <v>20.3314323425293</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>21</v>
       </c>
       <c r="G1269" t="n">
-        <v>19.7666721343994</v>
+        <v>19.7666702270508</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>21.0599994659424</v>
       </c>
       <c r="G1272" t="n">
-        <v>19.8231468200684</v>
+        <v>19.823148727417</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G1273" t="n">
-        <v>19.7478466033936</v>
+        <v>19.7478446960449</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33545,7 +33545,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1276" t="n">
-        <v>17.7429389953613</v>
+        <v>17.74294090271</v>
       </c>
       <c r="H1276" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1279" t="n">
-        <v>18.2041606903076</v>
+        <v>18.2041625976562</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1281" t="n">
-        <v>17.7147026062012</v>
+        <v>17.7147006988525</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1284" t="n">
-        <v>17.9029579162598</v>
+        <v>17.9029560089111</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33805,7 +33805,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G1286" t="n">
-        <v>17.3758430480957</v>
+        <v>17.3758411407471</v>
       </c>
       <c r="H1286" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>19.3099994659424</v>
       </c>
       <c r="G1295" t="n">
-        <v>18.1759243011475</v>
+        <v>18.1759223937988</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G1296" t="n">
-        <v>17.8088302612305</v>
+        <v>17.8088283538818</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1299" t="n">
-        <v>16.4157485961914</v>
+        <v>16.41575050354</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G1304" t="n">
-        <v>17.6770534515381</v>
+        <v>17.6770515441895</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>18.8299999237061</v>
       </c>
       <c r="G1305" t="n">
-        <v>17.7241134643555</v>
+        <v>17.7241153717041</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>18.75</v>
       </c>
       <c r="G1306" t="n">
-        <v>17.648811340332</v>
+        <v>17.6488132476807</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>19.7900009155273</v>
       </c>
       <c r="G1310" t="n">
-        <v>18.6277351379395</v>
+        <v>18.6277332305908</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -34507,7 +34507,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1313" t="n">
-        <v>19.107780456543</v>
+        <v>19.1077823638916</v>
       </c>
       <c r="H1313" t="s">
         <v>8</v>
@@ -34793,7 +34793,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1324" t="n">
-        <v>17.4887962341309</v>
+        <v>17.4887981414795</v>
       </c>
       <c r="H1324" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G1325" t="n">
-        <v>16.7169551849365</v>
+        <v>16.7169570922852</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34871,7 +34871,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G1327" t="n">
-        <v>16.7263679504395</v>
+        <v>16.7263698577881</v>
       </c>
       <c r="H1327" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1329" t="n">
-        <v>16.0392436981201</v>
+        <v>16.0392417907715</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34975,7 +34975,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G1331" t="n">
-        <v>16.7263679504395</v>
+        <v>16.7263698577881</v>
       </c>
       <c r="H1331" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1332" t="n">
-        <v>16.5851764678955</v>
+        <v>16.5851783752441</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35027,7 +35027,7 @@
         <v>17.1299991607666</v>
       </c>
       <c r="G1333" t="n">
-        <v>16.1239528656006</v>
+        <v>16.1239547729492</v>
       </c>
       <c r="H1333" t="s">
         <v>8</v>
@@ -35053,7 +35053,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1334" t="n">
-        <v>16.6228275299072</v>
+        <v>16.6228294372559</v>
       </c>
       <c r="H1334" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1338" t="n">
-        <v>17.244068145752</v>
+        <v>17.2440662384033</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G1340" t="n">
-        <v>17.3946685791016</v>
+        <v>17.3946704864502</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1343" t="n">
-        <v>15.6815595626831</v>
+        <v>15.6815576553345</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>16</v>
       </c>
       <c r="G1344" t="n">
-        <v>15.0603199005127</v>
+        <v>15.060320854187</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35417,7 +35417,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G1348" t="n">
-        <v>13.4695749282837</v>
+        <v>13.4695739746094</v>
       </c>
       <c r="H1348" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1349" t="n">
-        <v>13.4601612091064</v>
+        <v>13.4601621627808</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1351" t="n">
-        <v>13.0271768569946</v>
+        <v>13.0271787643433</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G1353" t="n">
-        <v>13.1213045120239</v>
+        <v>13.1213035583496</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>14.2700004577637</v>
       </c>
       <c r="G1354" t="n">
-        <v>13.4319229125977</v>
+        <v>13.431923866272</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35599,7 +35599,7 @@
         <v>14.710000038147</v>
       </c>
       <c r="G1355" t="n">
-        <v>13.8460817337036</v>
+        <v>13.8460826873779</v>
       </c>
       <c r="H1355" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G1357" t="n">
-        <v>13.7801923751831</v>
+        <v>13.7801933288574</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G1358" t="n">
-        <v>13.337797164917</v>
+        <v>13.3377962112427</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G1359" t="n">
-        <v>13.3095579147339</v>
+        <v>13.3095588684082</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35729,7 +35729,7 @@
         <v>13.8900003433228</v>
       </c>
       <c r="G1360" t="n">
-        <v>13.0742406845093</v>
+        <v>13.0742416381836</v>
       </c>
       <c r="H1360" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>14.0699996948242</v>
       </c>
       <c r="G1361" t="n">
-        <v>13.2436685562134</v>
+        <v>13.2436695098877</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35885,7 +35885,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G1366" t="n">
-        <v>13.3001461029053</v>
+        <v>13.300145149231</v>
       </c>
       <c r="H1366" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G1367" t="n">
-        <v>13.5166368484497</v>
+        <v>13.5166358947754</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1369" t="n">
-        <v>13.93079662323</v>
+        <v>13.9307956695557</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G1371" t="n">
-        <v>15.1356229782104</v>
+        <v>15.1356220245361</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>15.3900003433228</v>
       </c>
       <c r="G1374" t="n">
-        <v>14.4861459732056</v>
+        <v>14.4861450195312</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>15.0100002288818</v>
       </c>
       <c r="G1375" t="n">
-        <v>14.1284627914429</v>
+        <v>14.1284637451172</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>15.710000038147</v>
       </c>
       <c r="G1379" t="n">
-        <v>14.7873525619507</v>
+        <v>14.7873516082764</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1380" t="n">
-        <v>15.3897666931152</v>
+        <v>15.3897657394409</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1381" t="n">
-        <v>15.342700958252</v>
+        <v>15.3427000045776</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1382" t="n">
-        <v>16.3310356140137</v>
+        <v>16.3310375213623</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>17.3299999237061</v>
       </c>
       <c r="G1388" t="n">
-        <v>16.3122100830078</v>
+        <v>16.3122081756592</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1390" t="n">
-        <v>15.8133373260498</v>
+        <v>15.8133354187012</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1396" t="n">
-        <v>16.3027973175049</v>
+        <v>16.3027954101562</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1397" t="n">
-        <v>17.1122894287109</v>
+        <v>17.1122875213623</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36743,7 +36743,7 @@
         <v>18.6100006103516</v>
       </c>
       <c r="G1399" t="n">
-        <v>17.5170345306396</v>
+        <v>17.5170364379883</v>
       </c>
       <c r="H1399" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G1402" t="n">
-        <v>16.9240341186523</v>
+        <v>16.924036026001</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>17.8700008392334</v>
       </c>
       <c r="G1403" t="n">
-        <v>16.8204936981201</v>
+        <v>16.8204956054688</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36899,7 +36899,7 @@
         <v>18.4899997711182</v>
       </c>
       <c r="G1405" t="n">
-        <v>17.4040813446045</v>
+        <v>17.4040832519531</v>
       </c>
       <c r="H1405" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1406" t="n">
-        <v>17.36643409729</v>
+        <v>17.3664321899414</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1408" t="n">
-        <v>16.5475292205811</v>
+        <v>16.5475254058838</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37107,7 +37107,7 @@
         <v>17.5699996948242</v>
       </c>
       <c r="G1413" t="n">
-        <v>16.5381145477295</v>
+        <v>16.5381126403809</v>
       </c>
       <c r="H1413" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1414" t="n">
-        <v>16.2651462554932</v>
+        <v>16.2651443481445</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1415" t="n">
-        <v>16.3969249725342</v>
+        <v>16.3969230651855</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37237,7 +37237,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1418" t="n">
-        <v>17.0369873046875</v>
+        <v>17.0369853973389</v>
       </c>
       <c r="H1418" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1419" t="n">
-        <v>16.9805145263672</v>
+        <v>16.9805126190186</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1420" t="n">
-        <v>17.4511451721191</v>
+        <v>17.4511470794678</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37315,7 +37315,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G1421" t="n">
-        <v>17.3758430480957</v>
+        <v>17.3758411407471</v>
       </c>
       <c r="H1421" t="s">
         <v>8</v>
@@ -37341,7 +37341,7 @@
         <v>18.4799995422363</v>
       </c>
       <c r="G1422" t="n">
-        <v>17.3946685791016</v>
+        <v>17.3946704864502</v>
       </c>
       <c r="H1422" t="s">
         <v>8</v>
@@ -37393,7 +37393,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1424" t="n">
-        <v>18.1665115356445</v>
+        <v>18.1665096282959</v>
       </c>
       <c r="H1424" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G1428" t="n">
-        <v>18.9760036468506</v>
+        <v>18.976001739502</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37523,7 +37523,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1429" t="n">
-        <v>19.107780456543</v>
+        <v>19.1077823638916</v>
       </c>
       <c r="H1429" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>20.6200008392334</v>
       </c>
       <c r="G1431" t="n">
-        <v>19.4089908599854</v>
+        <v>19.4089889526367</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37601,7 +37601,7 @@
         <v>21.0400009155273</v>
       </c>
       <c r="G1432" t="n">
-        <v>19.8043212890625</v>
+        <v>19.8043193817139</v>
       </c>
       <c r="H1432" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1434" t="n">
-        <v>20.3314342498779</v>
+        <v>20.3314323425293</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>20.3314342498779</v>
+        <v>20.3314323425293</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37939,7 +37939,7 @@
         <v>21.7199993133545</v>
       </c>
       <c r="G1445" t="n">
-        <v>20.4443855285645</v>
+        <v>20.4443836212158</v>
       </c>
       <c r="H1445" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1448" t="n">
-        <v>20.3314342498779</v>
+        <v>20.3314323425293</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38069,7 +38069,7 @@
         <v>21.0400009155273</v>
       </c>
       <c r="G1450" t="n">
-        <v>19.8043212890625</v>
+        <v>19.8043193817139</v>
       </c>
       <c r="H1450" t="s">
         <v>8</v>
@@ -38095,7 +38095,7 @@
         <v>21.2600002288818</v>
       </c>
       <c r="G1451" t="n">
-        <v>20.011402130127</v>
+        <v>20.0114002227783</v>
       </c>
       <c r="H1451" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>20.8199996948242</v>
       </c>
       <c r="G1452" t="n">
-        <v>19.597240447998</v>
+        <v>19.5972423553467</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G1453" t="n">
-        <v>19.6913681030273</v>
+        <v>19.691370010376</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G1456" t="n">
-        <v>19.2772102355957</v>
+        <v>19.2772083282471</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G1462" t="n">
-        <v>19.7101955413818</v>
+        <v>19.7101936340332</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>19.7099990844727</v>
       </c>
       <c r="G1471" t="n">
-        <v>18.5524291992188</v>
+        <v>18.5524311065674</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38667,7 +38667,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G1473" t="n">
-        <v>18.8818759918213</v>
+        <v>18.8818740844727</v>
       </c>
       <c r="H1473" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G1474" t="n">
-        <v>18.9760036468506</v>
+        <v>18.976001739502</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38745,7 +38745,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1476" t="n">
-        <v>19.107780456543</v>
+        <v>19.1077823638916</v>
       </c>
       <c r="H1476" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1478" t="n">
-        <v>18.731273651123</v>
+        <v>18.7312717437744</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G1481" t="n">
-        <v>18.6183204650879</v>
+        <v>18.6183223724365</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38901,7 +38901,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G1482" t="n">
-        <v>18.8818759918213</v>
+        <v>18.8818740844727</v>
       </c>
       <c r="H1482" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G1485" t="n">
-        <v>18.7877464294434</v>
+        <v>18.787748336792</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39135,7 +39135,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1491" t="n">
-        <v>19.107780456543</v>
+        <v>19.1077823638916</v>
       </c>
       <c r="H1491" t="s">
         <v>8</v>
@@ -39161,7 +39161,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1492" t="n">
-        <v>19.107780456543</v>
+        <v>19.1077823638916</v>
       </c>
       <c r="H1492" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G1496" t="n">
-        <v>18.7877464294434</v>
+        <v>18.787748336792</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1498" t="n">
-        <v>18.731273651123</v>
+        <v>18.7312717437744</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G1500" t="n">
-        <v>18.6183204650879</v>
+        <v>18.6183223724365</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G1503" t="n">
-        <v>18.5241928100586</v>
+        <v>18.5241947174072</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39473,7 +39473,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1504" t="n">
-        <v>18.9665908813477</v>
+        <v>18.966588973999</v>
       </c>
       <c r="H1504" t="s">
         <v>8</v>
@@ -39499,7 +39499,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1505" t="n">
-        <v>19.3965625762939</v>
+        <v>19.3965644836426</v>
       </c>
       <c r="H1505" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G1506" t="n">
-        <v>18.8805980682373</v>
+        <v>18.8805961608887</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39577,7 +39577,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1508" t="n">
-        <v>18.4601783752441</v>
+        <v>18.4601802825928</v>
       </c>
       <c r="H1508" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1509" t="n">
-        <v>18.3455181121826</v>
+        <v>18.3455200195312</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1514" t="n">
-        <v>18.3455181121826</v>
+        <v>18.3455200195312</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G1519" t="n">
-        <v>18.8805980682373</v>
+        <v>18.8805961608887</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>19.7399997711182</v>
       </c>
       <c r="G1522" t="n">
-        <v>18.8614864349365</v>
+        <v>18.8614845275879</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -40045,7 +40045,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1526" t="n">
-        <v>19.2532405853271</v>
+        <v>19.2532386779785</v>
       </c>
       <c r="H1526" t="s">
         <v>8</v>
@@ -40435,7 +40435,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1541" t="n">
-        <v>19.3965625762939</v>
+        <v>19.3965644836426</v>
       </c>
       <c r="H1541" t="s">
         <v>8</v>
@@ -40461,7 +40461,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1542" t="n">
-        <v>19.3965625762939</v>
+        <v>19.3965644836426</v>
       </c>
       <c r="H1542" t="s">
         <v>8</v>
@@ -40539,7 +40539,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1545" t="n">
-        <v>19.2532405853271</v>
+        <v>19.2532386779785</v>
       </c>
       <c r="H1545" t="s">
         <v>8</v>
@@ -40565,7 +40565,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1546" t="n">
-        <v>19.2532405853271</v>
+        <v>19.2532386779785</v>
       </c>
       <c r="H1546" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1547" t="n">
-        <v>19.0143661499023</v>
+        <v>19.0143642425537</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1549" t="n">
-        <v>19.0143661499023</v>
+        <v>19.0143642425537</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1555" t="n">
-        <v>19.0143661499023</v>
+        <v>19.0143642425537</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1556" t="n">
-        <v>19.0143661499023</v>
+        <v>19.0143642425537</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1558" t="n">
-        <v>19.0143661499023</v>
+        <v>19.0143642425537</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40903,7 +40903,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G1559" t="n">
-        <v>18.5175075531006</v>
+        <v>18.517505645752</v>
       </c>
       <c r="H1559" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G1563" t="n">
-        <v>18.4219608306885</v>
+        <v>18.4219589233398</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41059,7 +41059,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1565" t="n">
-        <v>18.441068649292</v>
+        <v>18.4410667419434</v>
       </c>
       <c r="H1565" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G1575" t="n">
-        <v>16.3771953582764</v>
+        <v>16.377197265625</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41397,7 +41397,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1578" t="n">
-        <v>16.205207824707</v>
+        <v>16.2052059173584</v>
       </c>
       <c r="H1578" t="s">
         <v>8</v>
@@ -41423,7 +41423,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1579" t="n">
-        <v>16.205207824707</v>
+        <v>16.2052059173584</v>
       </c>
       <c r="H1579" t="s">
         <v>8</v>
@@ -41475,7 +41475,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1581" t="n">
-        <v>16.5874061584473</v>
+        <v>16.5874080657959</v>
       </c>
       <c r="H1581" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G1584" t="n">
-        <v>16.4727458953857</v>
+        <v>16.4727478027344</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41579,7 +41579,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1585" t="n">
-        <v>16.549186706543</v>
+        <v>16.5491847991943</v>
       </c>
       <c r="H1585" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1586" t="n">
-        <v>16.5109691619873</v>
+        <v>16.5109672546387</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41709,7 +41709,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1590" t="n">
-        <v>16.5874061584473</v>
+        <v>16.5874080657959</v>
       </c>
       <c r="H1590" t="s">
         <v>8</v>
@@ -41865,7 +41865,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1596" t="n">
-        <v>15.2497129440308</v>
+        <v>15.2497119903564</v>
       </c>
       <c r="H1596" t="s">
         <v>8</v>
@@ -41969,7 +41969,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1600" t="n">
-        <v>15.2306022644043</v>
+        <v>15.23060131073</v>
       </c>
       <c r="H1600" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1602" t="n">
-        <v>14.9057350158691</v>
+        <v>14.9057340621948</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42073,7 +42073,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G1604" t="n">
-        <v>14.5426464080811</v>
+        <v>14.5426454544067</v>
       </c>
       <c r="H1604" t="s">
         <v>8</v>
@@ -42229,7 +42229,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G1610" t="n">
-        <v>13.7209186553955</v>
+        <v>13.7209177017212</v>
       </c>
       <c r="H1610" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1613" t="n">
-        <v>13.434271812439</v>
+        <v>13.4342708587646</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1615" t="n">
-        <v>13.434271812439</v>
+        <v>13.4342708587646</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42463,7 +42463,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G1619" t="n">
-        <v>13.7973575592041</v>
+        <v>13.7973585128784</v>
       </c>
       <c r="H1619" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G1623" t="n">
-        <v>13.7400283813477</v>
+        <v>13.740029335022</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42593,7 +42593,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1624" t="n">
-        <v>13.7591381072998</v>
+        <v>13.7591390609741</v>
       </c>
       <c r="H1624" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G1632" t="n">
-        <v>14.6955242156982</v>
+        <v>14.6955251693726</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G1634" t="n">
-        <v>15.0777235031128</v>
+        <v>15.0777225494385</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G1636" t="n">
-        <v>15.6510190963745</v>
+        <v>15.6510210037231</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1638" t="n">
-        <v>16.071439743042</v>
+        <v>16.0714378356934</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -43009,7 +43009,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1640" t="n">
-        <v>16.9313831329346</v>
+        <v>16.9313850402832</v>
       </c>
       <c r="H1640" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1643" t="n">
-        <v>17.0078258514404</v>
+        <v>17.0078239440918</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43425,7 +43425,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1656" t="n">
-        <v>16.9887161254883</v>
+        <v>16.9887142181396</v>
       </c>
       <c r="H1656" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1665" t="n">
-        <v>18.3455181121826</v>
+        <v>18.3455200195312</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1666" t="n">
-        <v>18.3455181121826</v>
+        <v>18.3455200195312</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G1669" t="n">
-        <v>18.8805980682373</v>
+        <v>18.8805961608887</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43789,7 +43789,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G1670" t="n">
-        <v>18.8041553497314</v>
+        <v>18.8041572570801</v>
       </c>
       <c r="H1670" t="s">
         <v>8</v>
@@ -43919,7 +43919,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1675" t="n">
-        <v>17.7722206115723</v>
+        <v>17.7722225189209</v>
       </c>
       <c r="H1675" t="s">
         <v>8</v>
@@ -43997,7 +43997,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G1678" t="n">
-        <v>17.8104400634766</v>
+        <v>17.8104419708252</v>
       </c>
       <c r="H1678" t="s">
         <v>8</v>
@@ -44023,7 +44023,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1679" t="n">
-        <v>17.4855728149414</v>
+        <v>17.4855709075928</v>
       </c>
       <c r="H1679" t="s">
         <v>8</v>
@@ -44127,7 +44127,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1683" t="n">
-        <v>16.8740539550781</v>
+        <v>16.8740558624268</v>
       </c>
       <c r="H1683" t="s">
         <v>8</v>
@@ -44153,7 +44153,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G1684" t="n">
-        <v>17.0842628479004</v>
+        <v>17.0842609405518</v>
       </c>
       <c r="H1684" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1689" t="n">
-        <v>17.9824314117432</v>
+        <v>17.9824295043945</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44335,7 +44335,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G1691" t="n">
-        <v>18.0206508636475</v>
+        <v>18.0206489562988</v>
       </c>
       <c r="H1691" t="s">
         <v>8</v>
@@ -44361,7 +44361,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G1692" t="n">
-        <v>18.0206508636475</v>
+        <v>18.0206489562988</v>
       </c>
       <c r="H1692" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1694" t="n">
-        <v>17.867769241333</v>
+        <v>17.8677711486816</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44465,7 +44465,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1696" t="n">
-        <v>17.4855728149414</v>
+        <v>17.4855709075928</v>
       </c>
       <c r="H1696" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G1698" t="n">
-        <v>17.4091300964355</v>
+        <v>17.4091320037842</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44595,7 +44595,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1701" t="n">
-        <v>17.7531108856201</v>
+        <v>17.7531127929688</v>
       </c>
       <c r="H1701" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G1702" t="n">
-        <v>17.4091300964355</v>
+        <v>17.4091320037842</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44673,7 +44673,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G1704" t="n">
-        <v>17.8104400634766</v>
+        <v>17.8104419708252</v>
       </c>
       <c r="H1704" t="s">
         <v>8</v>
@@ -44699,7 +44699,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G1705" t="n">
-        <v>18.0206508636475</v>
+        <v>18.0206489562988</v>
       </c>
       <c r="H1705" t="s">
         <v>8</v>
@@ -44907,7 +44907,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1713" t="n">
-        <v>17.7531108856201</v>
+        <v>17.7531127929688</v>
       </c>
       <c r="H1713" t="s">
         <v>8</v>
@@ -44933,7 +44933,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G1714" t="n">
-        <v>17.5237922668457</v>
+        <v>17.5237941741943</v>
       </c>
       <c r="H1714" t="s">
         <v>8</v>
@@ -44985,7 +44985,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1716" t="n">
-        <v>17.7531108856201</v>
+        <v>17.7531127929688</v>
       </c>
       <c r="H1716" t="s">
         <v>8</v>
@@ -45037,7 +45037,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1718" t="n">
-        <v>17.7531108856201</v>
+        <v>17.7531127929688</v>
       </c>
       <c r="H1718" t="s">
         <v>8</v>
@@ -45219,7 +45219,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1725" t="n">
-        <v>16.5874061584473</v>
+        <v>16.5874080657959</v>
       </c>
       <c r="H1725" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1726" t="n">
-        <v>17.0078258514404</v>
+        <v>17.0078239440918</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1728" t="n">
-        <v>16.5682983398438</v>
+        <v>16.5682964324951</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1729" t="n">
-        <v>16.8167247772217</v>
+        <v>16.8167266845703</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1730" t="n">
-        <v>16.8358345031738</v>
+        <v>16.8358364105225</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45375,7 +45375,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1731" t="n">
-        <v>16.9504928588867</v>
+        <v>16.9504947662354</v>
       </c>
       <c r="H1731" t="s">
         <v>8</v>
@@ -45505,7 +45505,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1736" t="n">
-        <v>16.8740539550781</v>
+        <v>16.8740558624268</v>
       </c>
       <c r="H1736" t="s">
         <v>8</v>
@@ -45609,7 +45609,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1740" t="n">
-        <v>15.8994483947754</v>
+        <v>15.899450302124</v>
       </c>
       <c r="H1740" t="s">
         <v>8</v>
@@ -45687,7 +45687,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1743" t="n">
-        <v>15.670129776001</v>
+        <v>15.6701307296753</v>
       </c>
       <c r="H1743" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G1744" t="n">
-        <v>15.6510190963745</v>
+        <v>15.6510210037231</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45765,7 +45765,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1746" t="n">
-        <v>15.3834819793701</v>
+        <v>15.3834829330444</v>
       </c>
       <c r="H1746" t="s">
         <v>8</v>
@@ -45895,7 +45895,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1751" t="n">
-        <v>15.4790325164795</v>
+        <v>15.4790315628052</v>
       </c>
       <c r="H1751" t="s">
         <v>8</v>
@@ -45999,7 +45999,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1755" t="n">
-        <v>15.3834819793701</v>
+        <v>15.3834829330444</v>
       </c>
       <c r="H1755" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1756" t="n">
-        <v>15.6319122314453</v>
+        <v>15.631911277771</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1757" t="n">
-        <v>15.8803396224976</v>
+        <v>15.8803415298462</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46129,7 +46129,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1760" t="n">
-        <v>15.8994483947754</v>
+        <v>15.899450302124</v>
       </c>
       <c r="H1760" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1762" t="n">
-        <v>15.8803396224976</v>
+        <v>15.8803415298462</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1765" t="n">
-        <v>16.6447372436523</v>
+        <v>16.6447353363037</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46285,7 +46285,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1766" t="n">
-        <v>16.8740539550781</v>
+        <v>16.8740558624268</v>
       </c>
       <c r="H1766" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1767" t="n">
-        <v>16.8167247772217</v>
+        <v>16.8167266845703</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -61888,6 +61888,32 @@
         <v>29.5</v>
       </c>
       <c r="H2366" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2367">
+      <c r="A2367" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B2367" t="n">
+        <v>20863</v>
+      </c>
+      <c r="C2367" t="n">
+        <v>29.5</v>
+      </c>
+      <c r="D2367" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="E2367" t="n">
+        <v>29.2999992370605</v>
+      </c>
+      <c r="F2367" t="n">
+        <v>29.1499996185303</v>
+      </c>
+      <c r="G2367" t="n">
+        <v>29.1499996185303</v>
+      </c>
+      <c r="H2367" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/WIIT.MI.xlsx
+++ b/data/WIIT.MI.xlsx
@@ -54875,8 +54875,31 @@
       <c r="E2370" t="n">
         <v>29.2000007629395</v>
       </c>
-      <c r="F2370"/>
+      <c r="F2370" t="n">
+        <v>29.7000007629395</v>
+      </c>
       <c r="G2370" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2371">
+      <c r="A2371" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B2371" t="n">
+        <v>20593</v>
+      </c>
+      <c r="C2371" t="n">
+        <v>30.25</v>
+      </c>
+      <c r="D2371" t="n">
+        <v>29.6499996185303</v>
+      </c>
+      <c r="E2371" t="n">
+        <v>30</v>
+      </c>
+      <c r="F2371"/>
+      <c r="G2371" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/WIIT.MI.xlsx
+++ b/data/WIIT.MI.xlsx
@@ -54898,8 +54898,31 @@
       <c r="E2371" t="n">
         <v>30</v>
       </c>
-      <c r="F2371"/>
+      <c r="F2371" t="n">
+        <v>29.7999992370605</v>
+      </c>
       <c r="G2371" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2372">
+      <c r="A2372" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B2372" t="n">
+        <v>13182</v>
+      </c>
+      <c r="C2372" t="n">
+        <v>29.7000007629395</v>
+      </c>
+      <c r="D2372" t="n">
+        <v>29.1000003814697</v>
+      </c>
+      <c r="E2372" t="n">
+        <v>29.6000003814697</v>
+      </c>
+      <c r="F2372"/>
+      <c r="G2372" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/WIIT.MI.xlsx
+++ b/data/WIIT.MI.xlsx
@@ -54916,13 +54916,36 @@
         <v>29.7000007629395</v>
       </c>
       <c r="D2372" t="n">
-        <v>29.1000003814697</v>
+        <v>29.0499992370605</v>
       </c>
       <c r="E2372" t="n">
         <v>29.6000003814697</v>
       </c>
-      <c r="F2372"/>
+      <c r="F2372" t="n">
+        <v>29.0499992370605</v>
+      </c>
       <c r="G2372" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2373">
+      <c r="A2373" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B2373" t="n">
+        <v>27752</v>
+      </c>
+      <c r="C2373" t="n">
+        <v>29.8500003814697</v>
+      </c>
+      <c r="D2373" t="n">
+        <v>28.8500003814697</v>
+      </c>
+      <c r="E2373" t="n">
+        <v>29.1000003814697</v>
+      </c>
+      <c r="F2373"/>
+      <c r="G2373" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/WIIT.MI.xlsx
+++ b/data/WIIT.MI.xlsx
@@ -54944,8 +54944,31 @@
       <c r="E2373" t="n">
         <v>29.1000003814697</v>
       </c>
-      <c r="F2373"/>
+      <c r="F2373" t="n">
+        <v>29.2000007629395</v>
+      </c>
       <c r="G2373" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2374">
+      <c r="A2374" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B2374" t="n">
+        <v>17787</v>
+      </c>
+      <c r="C2374" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="D2374" t="n">
+        <v>28.6000003814697</v>
+      </c>
+      <c r="E2374" t="n">
+        <v>29.5499992370605</v>
+      </c>
+      <c r="F2374"/>
+      <c r="G2374" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/WIIT.MI.xlsx
+++ b/data/WIIT.MI.xlsx
@@ -54974,6 +54974,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="2375">
+      <c r="A2375" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B2375" t="n">
+        <v>20044</v>
+      </c>
+      <c r="C2375" t="n">
+        <v>29.5499992370605</v>
+      </c>
+      <c r="D2375" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="E2375" t="n">
+        <v>29</v>
+      </c>
+      <c r="F2375" t="n">
+        <v>29.2000007629395</v>
+      </c>
+      <c r="G2375" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/WIIT.MI.xlsx
+++ b/data/WIIT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2" t="n">
-        <v>4.49076414108276</v>
+        <v>4.49076461791992</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G3" t="n">
-        <v>4.49076414108276</v>
+        <v>4.49076461791992</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>5.125</v>
       </c>
       <c r="G233" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>5.125</v>
       </c>
       <c r="G234" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>5.125</v>
       </c>
       <c r="G235" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>5.125</v>
       </c>
       <c r="G236" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>5.125</v>
       </c>
       <c r="G237" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6557,7 +6557,7 @@
         <v>5.125</v>
       </c>
       <c r="G238" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H238" t="s">
         <v>8</v>
@@ -6583,7 +6583,7 @@
         <v>5.125</v>
       </c>
       <c r="G239" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H239" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>5.125</v>
       </c>
       <c r="G240" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>5.125</v>
       </c>
       <c r="G241" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6661,7 +6661,7 @@
         <v>5.125</v>
       </c>
       <c r="G242" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H242" t="s">
         <v>8</v>
@@ -6687,7 +6687,7 @@
         <v>5.125</v>
       </c>
       <c r="G243" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H243" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>5.125</v>
       </c>
       <c r="G244" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>5.125</v>
       </c>
       <c r="G245" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>5.125</v>
       </c>
       <c r="G246" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>5.125</v>
       </c>
       <c r="G247" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6817,7 +6817,7 @@
         <v>5.125</v>
       </c>
       <c r="G248" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H248" t="s">
         <v>8</v>
@@ -6843,7 +6843,7 @@
         <v>5.125</v>
       </c>
       <c r="G249" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H249" t="s">
         <v>8</v>
@@ -6869,7 +6869,7 @@
         <v>5.125</v>
       </c>
       <c r="G250" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H250" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>5.125</v>
       </c>
       <c r="G251" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>5.125</v>
       </c>
       <c r="G252" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>5.125</v>
       </c>
       <c r="G253" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>5.125</v>
       </c>
       <c r="G254" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>5.125</v>
       </c>
       <c r="G255" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7025,7 +7025,7 @@
         <v>5.125</v>
       </c>
       <c r="G256" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H256" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>5.125</v>
       </c>
       <c r="G257" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>5.125</v>
       </c>
       <c r="G258" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>5.125</v>
       </c>
       <c r="G259" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>5.125</v>
       </c>
       <c r="G260" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>5.125</v>
       </c>
       <c r="G261" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>5.125</v>
       </c>
       <c r="G262" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>5.125</v>
       </c>
       <c r="G263" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>5.125</v>
       </c>
       <c r="G264" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>5.125</v>
       </c>
       <c r="G265" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>5.125</v>
       </c>
       <c r="G266" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>5.125</v>
       </c>
       <c r="G267" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>5.125</v>
       </c>
       <c r="G268" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7363,7 +7363,7 @@
         <v>5.125</v>
       </c>
       <c r="G269" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H269" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>5.125</v>
       </c>
       <c r="G270" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>5.125</v>
       </c>
       <c r="G271" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>5.125</v>
       </c>
       <c r="G272" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>5.125</v>
       </c>
       <c r="G273" t="n">
-        <v>4.58706617355347</v>
+        <v>4.58706665039062</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G274" t="n">
-        <v>4.51098871231079</v>
+        <v>4.51098823547363</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G275" t="n">
-        <v>4.4125337600708</v>
+        <v>4.41253423690796</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G276" t="n">
-        <v>4.52888917922974</v>
+        <v>4.52888870239258</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G277" t="n">
-        <v>4.49308681488037</v>
+        <v>4.49308729171753</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G278" t="n">
-        <v>4.44833564758301</v>
+        <v>4.44833612442017</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>5</v>
       </c>
       <c r="G279" t="n">
-        <v>4.47518682479858</v>
+        <v>4.47518634796143</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>5</v>
       </c>
       <c r="G280" t="n">
-        <v>4.47518682479858</v>
+        <v>4.47518634796143</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>5</v>
       </c>
       <c r="G281" t="n">
-        <v>4.47518682479858</v>
+        <v>4.47518634796143</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G282" t="n">
-        <v>4.49308681488037</v>
+        <v>4.49308729171753</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G283" t="n">
-        <v>4.43938541412354</v>
+        <v>4.43938589096069</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G284" t="n">
-        <v>4.49308681488037</v>
+        <v>4.49308729171753</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>5</v>
       </c>
       <c r="G285" t="n">
-        <v>4.47518682479858</v>
+        <v>4.47518634796143</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G286" t="n">
-        <v>4.44833564758301</v>
+        <v>4.44833612442017</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G287" t="n">
-        <v>4.44833564758301</v>
+        <v>4.44833612442017</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G288" t="n">
-        <v>4.44833564758301</v>
+        <v>4.44833612442017</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G289" t="n">
-        <v>4.44833564758301</v>
+        <v>4.44833612442017</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>5</v>
       </c>
       <c r="G290" t="n">
-        <v>4.47518682479858</v>
+        <v>4.47518634796143</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G291" t="n">
-        <v>4.54678916931152</v>
+        <v>4.54678869247437</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G292" t="n">
-        <v>4.54678916931152</v>
+        <v>4.54678869247437</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G293" t="n">
-        <v>4.54678916931152</v>
+        <v>4.54678869247437</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G294" t="n">
-        <v>4.58259105682373</v>
+        <v>4.58259057998657</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G295" t="n">
-        <v>4.54678916931152</v>
+        <v>4.54678869247437</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G296" t="n">
-        <v>4.51098871231079</v>
+        <v>4.51098823547363</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G297" t="n">
-        <v>4.52888917922974</v>
+        <v>4.52888870239258</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G298" t="n">
-        <v>4.51098871231079</v>
+        <v>4.51098823547363</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>4.51098871231079</v>
+        <v>4.51098823547363</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G300" t="n">
-        <v>4.49308681488037</v>
+        <v>4.49308729171753</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G301" t="n">
-        <v>4.49308681488037</v>
+        <v>4.49308729171753</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>4.49308681488037</v>
+        <v>4.49308729171753</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G305" t="n">
-        <v>4.38568353652954</v>
+        <v>4.38568258285522</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G307" t="n">
-        <v>4.30512952804565</v>
+        <v>4.30513000488281</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G308" t="n">
-        <v>4.29617977142334</v>
+        <v>4.29617929458618</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G309" t="n">
-        <v>4.33198118209839</v>
+        <v>4.33198070526123</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G310" t="n">
-        <v>4.33198118209839</v>
+        <v>4.33198070526123</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G311" t="n">
-        <v>4.27827882766724</v>
+        <v>4.27827835083008</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G312" t="n">
-        <v>4.27827882766724</v>
+        <v>4.27827835083008</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>4.45728540420532</v>
+        <v>4.45728635787964</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>4.43938541412354</v>
+        <v>4.43938589096069</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G316" t="n">
-        <v>4.33198118209839</v>
+        <v>4.33198070526123</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G317" t="n">
-        <v>4.32303047180176</v>
+        <v>4.3230299949646</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G318" t="n">
-        <v>4.32303047180176</v>
+        <v>4.3230299949646</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G320" t="n">
-        <v>4.14402341842651</v>
+        <v>4.14402294158936</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G322" t="n">
-        <v>4.32303047180176</v>
+        <v>4.3230299949646</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8767,7 +8767,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G323" t="n">
-        <v>4.34988117218018</v>
+        <v>4.34988164901733</v>
       </c>
       <c r="H323" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>4.28722953796387</v>
+        <v>4.28722906112671</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G325" t="n">
-        <v>4.1798243522644</v>
+        <v>4.17982482910156</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G328" t="n">
-        <v>3.90236306190491</v>
+        <v>3.90236258506775</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G329" t="n">
-        <v>3.99186635017395</v>
+        <v>3.99186682701111</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G330" t="n">
-        <v>4.14402341842651</v>
+        <v>4.14402294158936</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G331" t="n">
-        <v>4.08137035369873</v>
+        <v>4.08136987686157</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G332" t="n">
-        <v>4.13507223129272</v>
+        <v>4.13507270812988</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G333" t="n">
-        <v>4.1798243522644</v>
+        <v>4.17982482910156</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G334" t="n">
-        <v>4.14402341842651</v>
+        <v>4.14402294158936</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G335" t="n">
-        <v>4.11717128753662</v>
+        <v>4.11717176437378</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G336" t="n">
-        <v>3.99186635017395</v>
+        <v>3.99186682701111</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>4.5</v>
       </c>
       <c r="G337" t="n">
-        <v>4.02766752243042</v>
+        <v>4.02766847610474</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G338" t="n">
-        <v>3.93816494941711</v>
+        <v>3.93816423416138</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G340" t="n">
-        <v>3.90236306190491</v>
+        <v>3.90236258506775</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>3.76810693740845</v>
+        <v>3.76810717582703</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G343" t="n">
-        <v>3.84866094589233</v>
+        <v>3.8486602306366</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G344" t="n">
-        <v>3.78600811958313</v>
+        <v>3.78600764274597</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G345" t="n">
-        <v>3.70545434951782</v>
+        <v>3.7054545879364</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G347" t="n">
-        <v>3.60700058937073</v>
+        <v>3.60700082778931</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G348" t="n">
-        <v>3.59805011749268</v>
+        <v>3.5980498790741</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G349" t="n">
-        <v>3.59805011749268</v>
+        <v>3.5980498790741</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G351" t="n">
-        <v>3.53539729118347</v>
+        <v>3.53539752960205</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>4</v>
       </c>
       <c r="G352" t="n">
-        <v>3.58014917373657</v>
+        <v>3.58014965057373</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G353" t="n">
-        <v>3.43694353103638</v>
+        <v>3.4369432926178</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G354" t="n">
-        <v>3.47274494171143</v>
+        <v>3.47274470329285</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G355" t="n">
-        <v>3.44589352607727</v>
+        <v>3.44589400291443</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G356" t="n">
-        <v>3.4100923538208</v>
+        <v>3.41009259223938</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G357" t="n">
-        <v>3.39219164848328</v>
+        <v>3.3921914100647</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G361" t="n">
-        <v>3.34743976593018</v>
+        <v>3.34744000434875</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G362" t="n">
-        <v>3.36534023284912</v>
+        <v>3.3653404712677</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G365" t="n">
-        <v>3.08787894248962</v>
+        <v>3.08787870407104</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G367" t="n">
-        <v>3.09682893753052</v>
+        <v>3.09682869911194</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G368" t="n">
-        <v>3.10577988624573</v>
+        <v>3.10577964782715</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G370" t="n">
-        <v>3.21318387985229</v>
+        <v>3.21318411827087</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G371" t="n">
-        <v>3.22213411331177</v>
+        <v>3.22213435173035</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G372" t="n">
-        <v>3.22213411331177</v>
+        <v>3.22213435173035</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G373" t="n">
-        <v>2.93572282791138</v>
+        <v>2.93572235107422</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G377" t="n">
-        <v>2.95362305641174</v>
+        <v>2.95362329483032</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>3.25</v>
       </c>
       <c r="G379" t="n">
-        <v>2.90887141227722</v>
+        <v>2.90887117385864</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>3.25</v>
       </c>
       <c r="G381" t="n">
-        <v>2.90887141227722</v>
+        <v>2.90887117385864</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G382" t="n">
-        <v>2.95362305641174</v>
+        <v>2.95362329483032</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G383" t="n">
-        <v>2.95362305641174</v>
+        <v>2.95362329483032</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G384" t="n">
-        <v>3.0073254108429</v>
+        <v>3.00732564926147</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G385" t="n">
-        <v>2.95362305641174</v>
+        <v>2.95362329483032</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>3.25</v>
       </c>
       <c r="G387" t="n">
-        <v>2.90887141227722</v>
+        <v>2.90887117385864</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G390" t="n">
-        <v>2.81041717529297</v>
+        <v>2.81041741371155</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G391" t="n">
-        <v>2.84621858596802</v>
+        <v>2.84621906280518</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G393" t="n">
-        <v>2.89992117881775</v>
+        <v>2.89992070198059</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G394" t="n">
-        <v>2.94467282295227</v>
+        <v>2.94467306137085</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G396" t="n">
-        <v>3.06997799873352</v>
+        <v>3.06997776031494</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G397" t="n">
-        <v>3.1773829460144</v>
+        <v>3.17738270759583</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G398" t="n">
-        <v>3.1773829460144</v>
+        <v>3.17738270759583</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G399" t="n">
-        <v>3.26688623428345</v>
+        <v>3.26688647270203</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>3.22213411331177</v>
+        <v>3.22213435173035</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G401" t="n">
-        <v>3.26688623428345</v>
+        <v>3.26688647270203</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G402" t="n">
-        <v>3.26688623428345</v>
+        <v>3.26688647270203</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>3.75</v>
       </c>
       <c r="G404" t="n">
-        <v>3.35638999938965</v>
+        <v>3.35639023780823</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G405" t="n">
-        <v>3.39219164848328</v>
+        <v>3.3921914100647</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G409" t="n">
-        <v>3.59805011749268</v>
+        <v>3.5980498790741</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G410" t="n">
-        <v>3.56224870681763</v>
+        <v>3.56224822998047</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G411" t="n">
-        <v>3.59805011749268</v>
+        <v>3.5980498790741</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4</v>
       </c>
       <c r="G412" t="n">
-        <v>3.58014917373657</v>
+        <v>3.58014965057373</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G413" t="n">
-        <v>3.5890998840332</v>
+        <v>3.58910012245178</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G414" t="n">
-        <v>3.6338517665863</v>
+        <v>3.63385128974915</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G415" t="n">
-        <v>3.66070294380188</v>
+        <v>3.6607027053833</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G416" t="n">
-        <v>3.6338517665863</v>
+        <v>3.63385128974915</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G417" t="n">
-        <v>3.49064588546753</v>
+        <v>3.49064564704895</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G418" t="n">
-        <v>3.53539729118347</v>
+        <v>3.53539752960205</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>4</v>
       </c>
       <c r="G420" t="n">
-        <v>3.58014917373657</v>
+        <v>3.58014965057373</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G423" t="n">
-        <v>3.5890998840332</v>
+        <v>3.58910012245178</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G424" t="n">
-        <v>3.6338517665863</v>
+        <v>3.63385128974915</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G425" t="n">
-        <v>3.62490129470825</v>
+        <v>3.62490153312683</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G426" t="n">
-        <v>3.6338517665863</v>
+        <v>3.63385128974915</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>4</v>
       </c>
       <c r="G427" t="n">
-        <v>3.58014917373657</v>
+        <v>3.58014965057373</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G428" t="n">
-        <v>3.6338517665863</v>
+        <v>3.63385128974915</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G429" t="n">
-        <v>3.5890998840332</v>
+        <v>3.58910012245178</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G430" t="n">
-        <v>3.69650411605835</v>
+        <v>3.69650435447693</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G431" t="n">
-        <v>3.75020670890808</v>
+        <v>3.75020623207092</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G432" t="n">
-        <v>3.78600811958313</v>
+        <v>3.78600764274597</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G433" t="n">
-        <v>3.90236306190491</v>
+        <v>3.90236258506775</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G435" t="n">
-        <v>4.14402341842651</v>
+        <v>4.14402294158936</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G436" t="n">
-        <v>4.09927129745483</v>
+        <v>4.09927082061768</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G437" t="n">
-        <v>4.09927129745483</v>
+        <v>4.09927082061768</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>4.75</v>
       </c>
       <c r="G438" t="n">
-        <v>4.2514271736145</v>
+        <v>4.25142765045166</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G439" t="n">
-        <v>4.11717128753662</v>
+        <v>4.11717176437378</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>4.29617977142334</v>
+        <v>4.29617929458618</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G444" t="n">
-        <v>4.14402341842651</v>
+        <v>4.14402294158936</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>4.5</v>
       </c>
       <c r="G445" t="n">
-        <v>4.02766752243042</v>
+        <v>4.02766847610474</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G446" t="n">
-        <v>3.90236306190491</v>
+        <v>3.90236258506775</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G447" t="n">
-        <v>3.92026352882385</v>
+        <v>3.92026305198669</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G448" t="n">
-        <v>3.76810693740845</v>
+        <v>3.76810717582703</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G451" t="n">
-        <v>3.70545434951782</v>
+        <v>3.7054545879364</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G454" t="n">
-        <v>4.14402341842651</v>
+        <v>4.14402294158936</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G455" t="n">
-        <v>4.13507223129272</v>
+        <v>4.13507270812988</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G457" t="n">
-        <v>4.20667505264282</v>
+        <v>4.20667457580566</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G458" t="n">
-        <v>4.29617977142334</v>
+        <v>4.29617929458618</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G461" t="n">
-        <v>4.40358352661133</v>
+        <v>4.40358400344849</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G462" t="n">
-        <v>4.44833564758301</v>
+        <v>4.44833612442017</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G463" t="n">
-        <v>4.32303047180176</v>
+        <v>4.3230299949646</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G464" t="n">
-        <v>4.42148494720459</v>
+        <v>4.42148542404175</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G466" t="n">
-        <v>4.38568353652954</v>
+        <v>4.38568258285522</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G468" t="n">
-        <v>4.29617977142334</v>
+        <v>4.29617929458618</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G470" t="n">
-        <v>4.22457551956177</v>
+        <v>4.22457599639893</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G471" t="n">
-        <v>4.20667505264282</v>
+        <v>4.20667457580566</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G473" t="n">
-        <v>4.2888011932373</v>
+        <v>4.28880167007446</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G475" t="n">
-        <v>4.44392824172974</v>
+        <v>4.44392871856689</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G476" t="n">
-        <v>4.2888011932373</v>
+        <v>4.28880167007446</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G477" t="n">
-        <v>4.3435525894165</v>
+        <v>4.34355211257935</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G478" t="n">
-        <v>4.3435525894165</v>
+        <v>4.34355211257935</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G479" t="n">
-        <v>4.3435525894165</v>
+        <v>4.34355211257935</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G480" t="n">
-        <v>4.3435525894165</v>
+        <v>4.34355211257935</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G481" t="n">
-        <v>4.27055072784424</v>
+        <v>4.2705512046814</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G483" t="n">
-        <v>4.2888011932373</v>
+        <v>4.28880167007446</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G484" t="n">
-        <v>4.21580076217651</v>
+        <v>4.21580123901367</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G485" t="n">
-        <v>4.2888011932373</v>
+        <v>4.28880167007446</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G486" t="n">
-        <v>4.35267734527588</v>
+        <v>4.35267686843872</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G489" t="n">
-        <v>4.3435525894165</v>
+        <v>4.34355211257935</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G490" t="n">
-        <v>4.2888011932373</v>
+        <v>4.28880167007446</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G491" t="n">
-        <v>4.2888011932373</v>
+        <v>4.28880167007446</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>4.75</v>
       </c>
       <c r="G492" t="n">
-        <v>4.33442783355713</v>
+        <v>4.33442687988281</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>4.75</v>
       </c>
       <c r="G493" t="n">
-        <v>4.33442783355713</v>
+        <v>4.33442687988281</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G494" t="n">
-        <v>4.2431755065918</v>
+        <v>4.24317646026611</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G495" t="n">
-        <v>4.38005304336548</v>
+        <v>4.38005256652832</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G496" t="n">
-        <v>4.3435525894165</v>
+        <v>4.34355211257935</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G497" t="n">
-        <v>4.38005304336548</v>
+        <v>4.38005256652832</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>4.75</v>
       </c>
       <c r="G498" t="n">
-        <v>4.33442783355713</v>
+        <v>4.33442687988281</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>4.75</v>
       </c>
       <c r="G499" t="n">
-        <v>4.33442783355713</v>
+        <v>4.33442687988281</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G500" t="n">
-        <v>4.38005304336548</v>
+        <v>4.38005256652832</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G502" t="n">
-        <v>4.3435525894165</v>
+        <v>4.34355211257935</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>4.75</v>
       </c>
       <c r="G503" t="n">
-        <v>4.33442783355713</v>
+        <v>4.33442687988281</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G504" t="n">
-        <v>4.297926902771</v>
+        <v>4.29792642593384</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G505" t="n">
-        <v>4.297926902771</v>
+        <v>4.29792642593384</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G506" t="n">
-        <v>4.297926902771</v>
+        <v>4.29792642593384</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G507" t="n">
-        <v>4.38005304336548</v>
+        <v>4.38005256652832</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G508" t="n">
-        <v>4.38005304336548</v>
+        <v>4.38005256652832</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G509" t="n">
-        <v>4.3161768913269</v>
+        <v>4.31617641448975</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G511" t="n">
-        <v>4.3161768913269</v>
+        <v>4.31617641448975</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G513" t="n">
-        <v>4.30705118179321</v>
+        <v>4.30705165863037</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>4.75</v>
       </c>
       <c r="G514" t="n">
-        <v>4.33442783355713</v>
+        <v>4.33442687988281</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G515" t="n">
-        <v>4.30705118179321</v>
+        <v>4.30705165863037</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G516" t="n">
-        <v>4.2888011932373</v>
+        <v>4.28880167007446</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G517" t="n">
-        <v>4.30705118179321</v>
+        <v>4.30705165863037</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G518" t="n">
-        <v>4.61730527877808</v>
+        <v>4.61730575561523</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G519" t="n">
-        <v>4.59905529022217</v>
+        <v>4.59905576705933</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>5</v>
       </c>
       <c r="G520" t="n">
-        <v>4.56255435943604</v>
+        <v>4.56255483627319</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G521" t="n">
-        <v>4.5808048248291</v>
+        <v>4.58080434799194</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G523" t="n">
-        <v>4.61730527877808</v>
+        <v>4.61730575561523</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G524" t="n">
-        <v>4.6355562210083</v>
+        <v>4.63555574417114</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G525" t="n">
-        <v>4.72680616378784</v>
+        <v>4.726806640625</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G526" t="n">
-        <v>4.79980707168579</v>
+        <v>4.79980802536011</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G527" t="n">
-        <v>4.90930891036987</v>
+        <v>4.90930986404419</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G528" t="n">
-        <v>4.90930891036987</v>
+        <v>4.90930986404419</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G531" t="n">
-        <v>4.94581031799316</v>
+        <v>4.94580984115601</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>5.5</v>
       </c>
       <c r="G533" t="n">
-        <v>5.0188102722168</v>
+        <v>5.01881074905396</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G534" t="n">
-        <v>5.16481113433838</v>
+        <v>5.1648120880127</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G537" t="n">
-        <v>5.18306159973145</v>
+        <v>5.1830620765686</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14357,7 +14357,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G538" t="n">
-        <v>5.16481113433838</v>
+        <v>5.1648120880127</v>
       </c>
       <c r="H538" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G539" t="n">
-        <v>5.16481113433838</v>
+        <v>5.1648120880127</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>5.5</v>
       </c>
       <c r="G542" t="n">
-        <v>5.0188102722168</v>
+        <v>5.01881074905396</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>5.5</v>
       </c>
       <c r="G544" t="n">
-        <v>5.0188102722168</v>
+        <v>5.01881074905396</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G545" t="n">
-        <v>5.05531072616577</v>
+        <v>5.05531024932861</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G546" t="n">
-        <v>5.14656114578247</v>
+        <v>5.14656162261963</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G547" t="n">
-        <v>5.14656114578247</v>
+        <v>5.14656162261963</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G549" t="n">
-        <v>5.16481113433838</v>
+        <v>5.1648120880127</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G550" t="n">
-        <v>5.12831163406372</v>
+        <v>5.12831115722656</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G551" t="n">
-        <v>5.18306159973145</v>
+        <v>5.1830620765686</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G552" t="n">
-        <v>5.16481113433838</v>
+        <v>5.1648120880127</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G553" t="n">
-        <v>5.29256391525269</v>
+        <v>5.29256343841553</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G554" t="n">
-        <v>5.29256391525269</v>
+        <v>5.29256343841553</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G555" t="n">
-        <v>5.25606393814087</v>
+        <v>5.25606298446655</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G556" t="n">
-        <v>5.3290638923645</v>
+        <v>5.32906436920166</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G557" t="n">
-        <v>5.42031526565552</v>
+        <v>5.42031478881836</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G559" t="n">
-        <v>5.60281753540039</v>
+        <v>5.60281705856323</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G561" t="n">
-        <v>5.49331569671631</v>
+        <v>5.49331521987915</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G564" t="n">
-        <v>5.42031526565552</v>
+        <v>5.42031478881836</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G565" t="n">
-        <v>5.3290638923645</v>
+        <v>5.32906436920166</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G566" t="n">
-        <v>5.29256391525269</v>
+        <v>5.29256343841553</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G567" t="n">
-        <v>5.29256391525269</v>
+        <v>5.29256343841553</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G569" t="n">
-        <v>5.25606393814087</v>
+        <v>5.25606298446655</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G570" t="n">
-        <v>5.29256391525269</v>
+        <v>5.29256343841553</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G571" t="n">
-        <v>5.3290638923645</v>
+        <v>5.32906436920166</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G574" t="n">
-        <v>5.42031526565552</v>
+        <v>5.42031478881836</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G576" t="n">
-        <v>5.31081342697144</v>
+        <v>5.31081438064575</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G577" t="n">
-        <v>5.29256391525269</v>
+        <v>5.29256343841553</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G578" t="n">
-        <v>5.36556482315063</v>
+        <v>5.36556386947632</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G579" t="n">
-        <v>5.34731435775757</v>
+        <v>5.34731388092041</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G580" t="n">
-        <v>5.42031526565552</v>
+        <v>5.42031478881836</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G582" t="n">
-        <v>5.49331569671631</v>
+        <v>5.49331521987915</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G583" t="n">
-        <v>5.43856525421143</v>
+        <v>5.43856430053711</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G584" t="n">
-        <v>5.43856525421143</v>
+        <v>5.43856430053711</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G585" t="n">
-        <v>5.43856525421143</v>
+        <v>5.43856430053711</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G586" t="n">
-        <v>5.42031526565552</v>
+        <v>5.42031478881836</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G589" t="n">
-        <v>5.43856525421143</v>
+        <v>5.43856430053711</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G590" t="n">
-        <v>5.43856525421143</v>
+        <v>5.43856430053711</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G594" t="n">
-        <v>5.43856525421143</v>
+        <v>5.43856430053711</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G599" t="n">
-        <v>5.51156568527222</v>
+        <v>5.51156616210938</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G600" t="n">
-        <v>5.49331569671631</v>
+        <v>5.49331521987915</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G603" t="n">
-        <v>5.51156568527222</v>
+        <v>5.51156616210938</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G605" t="n">
-        <v>5.51156568527222</v>
+        <v>5.51156616210938</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G606" t="n">
-        <v>5.69406747817993</v>
+        <v>5.69406843185425</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G607" t="n">
-        <v>5.80356931686401</v>
+        <v>5.80356979370117</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G610" t="n">
-        <v>6.27807521820068</v>
+        <v>6.27807569503784</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G612" t="n">
-        <v>6.49707841873169</v>
+        <v>6.49707794189453</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G613" t="n">
-        <v>6.5153284072876</v>
+        <v>6.51532745361328</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G614" t="n">
-        <v>6.49707841873169</v>
+        <v>6.49707794189453</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G616" t="n">
-        <v>6.49707841873169</v>
+        <v>6.49707794189453</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G617" t="n">
-        <v>6.55182838439941</v>
+        <v>6.55182790756226</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G618" t="n">
-        <v>6.69782972335815</v>
+        <v>6.69783067703247</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G620" t="n">
-        <v>6.91683340072632</v>
+        <v>6.91683292388916</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>8</v>
       </c>
       <c r="G622" t="n">
-        <v>7.30008745193481</v>
+        <v>7.30008792877197</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G623" t="n">
-        <v>7.39133930206299</v>
+        <v>7.39133977890015</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G624" t="n">
-        <v>7.62859201431274</v>
+        <v>7.62859153747559</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>8.5</v>
       </c>
       <c r="G625" t="n">
-        <v>7.75634336471558</v>
+        <v>7.75634288787842</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G627" t="n">
-        <v>7.84759378433228</v>
+        <v>7.84759426116943</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G628" t="n">
-        <v>7.88409423828125</v>
+        <v>7.88409519195557</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G629" t="n">
-        <v>7.84759378433228</v>
+        <v>7.84759426116943</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G630" t="n">
-        <v>7.93884515762329</v>
+        <v>7.93884468078613</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>8.5</v>
       </c>
       <c r="G631" t="n">
-        <v>7.75634336471558</v>
+        <v>7.75634288787842</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G632" t="n">
-        <v>7.93884515762329</v>
+        <v>7.93884468078613</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G633" t="n">
-        <v>7.97534608840942</v>
+        <v>7.97534513473511</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G634" t="n">
-        <v>8.43160152435303</v>
+        <v>8.43160247802734</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G635" t="n">
-        <v>8.57760238647461</v>
+        <v>8.57760334014893</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G637" t="n">
-        <v>8.63235378265381</v>
+        <v>8.63235282897949</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G641" t="n">
-        <v>8.55935287475586</v>
+        <v>8.55935192108154</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G642" t="n">
-        <v>8.61410236358643</v>
+        <v>8.61410331726074</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G643" t="n">
-        <v>8.57760238647461</v>
+        <v>8.57760334014893</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G644" t="n">
-        <v>8.43160152435303</v>
+        <v>8.43160247802734</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G648" t="n">
-        <v>8.30385112762451</v>
+        <v>8.3038501739502</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G651" t="n">
-        <v>8.55935287475586</v>
+        <v>8.55935192108154</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G652" t="n">
-        <v>8.54110145568848</v>
+        <v>8.54110240936279</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G653" t="n">
-        <v>8.54110145568848</v>
+        <v>8.54110240936279</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G654" t="n">
-        <v>8.86960697174072</v>
+        <v>8.86960601806641</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G655" t="n">
-        <v>9.08860874176025</v>
+        <v>9.08860969543457</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G656" t="n">
-        <v>9.17073535919189</v>
+        <v>9.17073440551758</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>10.25</v>
       </c>
       <c r="G657" t="n">
-        <v>9.35323619842529</v>
+        <v>9.35323715209961</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G658" t="n">
-        <v>9.76386642456055</v>
+        <v>9.76386737823486</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G659" t="n">
-        <v>9.99199485778809</v>
+        <v>9.9919958114624</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G662" t="n">
-        <v>9.67261600494385</v>
+        <v>9.67261791229248</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G666" t="n">
-        <v>9.62699222564697</v>
+        <v>9.62699127197266</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>10.25</v>
       </c>
       <c r="G668" t="n">
-        <v>9.35323619842529</v>
+        <v>9.35323715209961</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>10</v>
       </c>
       <c r="G672" t="n">
-        <v>9.12510871887207</v>
+        <v>9.12510967254639</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G673" t="n">
-        <v>9.03385829925537</v>
+        <v>9.03385734558105</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>9.49011421203613</v>
+        <v>9.49011325836182</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G676" t="n">
-        <v>9.67261600494385</v>
+        <v>9.67261791229248</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G677" t="n">
-        <v>9.94636917114258</v>
+        <v>9.94636821746826</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G678" t="n">
-        <v>9.99199485778809</v>
+        <v>9.9919958114624</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G679" t="n">
-        <v>9.99199485778809</v>
+        <v>9.9919958114624</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G680" t="n">
-        <v>9.99199485778809</v>
+        <v>9.9919958114624</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G681" t="n">
-        <v>9.99199485778809</v>
+        <v>9.9919958114624</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G682" t="n">
-        <v>9.99199485778809</v>
+        <v>9.9919958114624</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G683" t="n">
-        <v>9.67261600494385</v>
+        <v>9.67261791229248</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G684" t="n">
-        <v>9.67261600494385</v>
+        <v>9.67261791229248</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G685" t="n">
-        <v>9.67261600494385</v>
+        <v>9.67261791229248</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G688" t="n">
-        <v>8.90610790252686</v>
+        <v>8.90610885620117</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G690" t="n">
-        <v>9.62699222564697</v>
+        <v>9.62699127197266</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G691" t="n">
-        <v>9.106858253479</v>
+        <v>9.10685920715332</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G695" t="n">
-        <v>8.68710517883301</v>
+        <v>8.68710422515869</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G696" t="n">
-        <v>8.55935287475586</v>
+        <v>8.55935192108154</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G697" t="n">
-        <v>7.84759378433228</v>
+        <v>7.84759426116943</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G698" t="n">
-        <v>7.61034154891968</v>
+        <v>7.61034250259399</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>8</v>
       </c>
       <c r="G700" t="n">
-        <v>7.30008745193481</v>
+        <v>7.30008792877197</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G702" t="n">
-        <v>7.263587474823</v>
+        <v>7.26358699798584</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G703" t="n">
-        <v>7.02633476257324</v>
+        <v>7.02633428573608</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G704" t="n">
-        <v>7.02633476257324</v>
+        <v>7.02633428573608</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G705" t="n">
-        <v>6.91683340072632</v>
+        <v>6.91683292388916</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G706" t="n">
-        <v>7.02633476257324</v>
+        <v>7.02633428573608</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G707" t="n">
-        <v>7.50084018707275</v>
+        <v>7.50084114074707</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G708" t="n">
-        <v>7.51909017562866</v>
+        <v>7.51909065246582</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G709" t="n">
-        <v>7.62859201431274</v>
+        <v>7.62859153747559</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G710" t="n">
-        <v>8.03009605407715</v>
+        <v>8.03009700775146</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G712" t="n">
-        <v>7.77459383010864</v>
+        <v>7.7745943069458</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>8.5</v>
       </c>
       <c r="G713" t="n">
-        <v>7.75634336471558</v>
+        <v>7.75634288787842</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G714" t="n">
-        <v>7.88409423828125</v>
+        <v>7.88409519195557</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G716" t="n">
-        <v>8.32209968566895</v>
+        <v>8.32210063934326</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G717" t="n">
-        <v>8.30385112762451</v>
+        <v>8.3038501739502</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G718" t="n">
-        <v>8.39510059356689</v>
+        <v>8.39509963989258</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G719" t="n">
-        <v>8.76010608673096</v>
+        <v>8.76010513305664</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>9.89999961853027</v>
       </c>
       <c r="G720" t="n">
-        <v>9.03385829925537</v>
+        <v>9.03385734558105</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G721" t="n">
-        <v>9.05210876464844</v>
+        <v>9.05210971832275</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G722" t="n">
-        <v>9.21636009216309</v>
+        <v>9.2163610458374</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>9.05210876464844</v>
+        <v>9.05210971832275</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G725" t="n">
-        <v>9.08860874176025</v>
+        <v>9.08860969543457</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G726" t="n">
-        <v>9.08860874176025</v>
+        <v>9.08860969543457</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G730" t="n">
-        <v>9.49011421203613</v>
+        <v>9.49011325836182</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>9.67261600494385</v>
+        <v>9.67261791229248</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G732" t="n">
-        <v>9.67261600494385</v>
+        <v>9.67261791229248</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G733" t="n">
-        <v>10.2201242446899</v>
+        <v>10.2201223373413</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G736" t="n">
-        <v>10.1252202987671</v>
+        <v>10.1252222061157</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G737" t="n">
-        <v>10.2176885604858</v>
+        <v>10.2176904678345</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G738" t="n">
-        <v>10.3101577758789</v>
+        <v>10.3101568222046</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G740" t="n">
-        <v>10.4950923919678</v>
+        <v>10.4950933456421</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G741" t="n">
-        <v>10.3101577758789</v>
+        <v>10.3101568222046</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G742" t="n">
-        <v>9.9865198135376</v>
+        <v>9.98652076721191</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G743" t="n">
-        <v>10.0327548980713</v>
+        <v>10.0327520370483</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G744" t="n">
-        <v>9.9865198135376</v>
+        <v>9.98652076721191</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G745" t="n">
-        <v>10.0327548980713</v>
+        <v>10.0327520370483</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>10.5</v>
       </c>
       <c r="G746" t="n">
-        <v>9.70911693572998</v>
+        <v>9.70911598205566</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>10.25</v>
       </c>
       <c r="G747" t="n">
-        <v>9.47794818878174</v>
+        <v>9.47794723510742</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G749" t="n">
-        <v>9.9865198135376</v>
+        <v>9.98652076721191</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G754" t="n">
-        <v>9.9865198135376</v>
+        <v>9.98652076721191</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G755" t="n">
-        <v>10.0789880752563</v>
+        <v>10.078987121582</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G757" t="n">
-        <v>10.3101577758789</v>
+        <v>10.3101568222046</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G758" t="n">
-        <v>10.4488582611084</v>
+        <v>10.4488592147827</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G759" t="n">
-        <v>10.4950923919678</v>
+        <v>10.4950933456421</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G760" t="n">
-        <v>10.4488582611084</v>
+        <v>10.4488592147827</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G763" t="n">
-        <v>10.4488582611084</v>
+        <v>10.4488592147827</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G765" t="n">
-        <v>10.0789880752563</v>
+        <v>10.078987121582</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G768" t="n">
-        <v>11.0036668777466</v>
+        <v>11.0036640167236</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G769" t="n">
-        <v>11.6047058105469</v>
+        <v>11.6047067642212</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G770" t="n">
-        <v>11.9745759963989</v>
+        <v>11.9745769500732</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>13</v>
       </c>
       <c r="G772" t="n">
-        <v>12.0208101272583</v>
+        <v>12.0208110809326</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G773" t="n">
-        <v>12.2982139587402</v>
+        <v>12.2982158660889</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G775" t="n">
-        <v>12.1132783889771</v>
+        <v>12.1132802963257</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>13</v>
       </c>
       <c r="G776" t="n">
-        <v>12.0208101272583</v>
+        <v>12.0208110809326</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G777" t="n">
-        <v>12.1595125198364</v>
+        <v>12.1595115661621</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G778" t="n">
-        <v>11.9745759963989</v>
+        <v>11.9745769500732</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G780" t="n">
-        <v>12.0670461654663</v>
+        <v>12.067045211792</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>13</v>
       </c>
       <c r="G781" t="n">
-        <v>12.0208101272583</v>
+        <v>12.0208110809326</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G784" t="n">
-        <v>11.8358755111694</v>
+        <v>11.8358745574951</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G785" t="n">
-        <v>11.9745759963989</v>
+        <v>11.9745769500732</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>13</v>
       </c>
       <c r="G789" t="n">
-        <v>12.0208101272583</v>
+        <v>12.0208110809326</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G791" t="n">
-        <v>11.7434072494507</v>
+        <v>11.743408203125</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G792" t="n">
-        <v>11.6509408950806</v>
+        <v>11.6509389877319</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G794" t="n">
-        <v>11.6509408950806</v>
+        <v>11.6509389877319</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G795" t="n">
-        <v>11.4660034179688</v>
+        <v>11.4660043716431</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G797" t="n">
-        <v>11.6971731185913</v>
+        <v>11.6971740722656</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>12.25</v>
       </c>
       <c r="G799" t="n">
-        <v>11.3273019790649</v>
+        <v>11.3273029327393</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G800" t="n">
-        <v>11.3735370635986</v>
+        <v>11.3735380172729</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G801" t="n">
-        <v>11.1423673629761</v>
+        <v>11.1423683166504</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G802" t="n">
-        <v>10.8187303543091</v>
+        <v>10.8187294006348</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G803" t="n">
-        <v>11.1423673629761</v>
+        <v>11.1423683166504</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>12.25</v>
       </c>
       <c r="G804" t="n">
-        <v>11.3273019790649</v>
+        <v>11.3273029327393</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>12.25</v>
       </c>
       <c r="G805" t="n">
-        <v>11.3273019790649</v>
+        <v>11.3273029327393</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>12.25</v>
       </c>
       <c r="G806" t="n">
-        <v>11.3273019790649</v>
+        <v>11.3273029327393</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G808" t="n">
-        <v>11.3735370635986</v>
+        <v>11.3735380172729</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G812" t="n">
-        <v>11.8358755111694</v>
+        <v>11.8358745574951</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G814" t="n">
-        <v>11.6509408950806</v>
+        <v>11.6509389877319</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G815" t="n">
-        <v>11.6509408950806</v>
+        <v>11.6509389877319</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G817" t="n">
-        <v>11.6509408950806</v>
+        <v>11.6509389877319</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G818" t="n">
-        <v>11.6509408950806</v>
+        <v>11.6509389877319</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G819" t="n">
-        <v>11.6971731185913</v>
+        <v>11.6971740722656</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G820" t="n">
-        <v>11.4660034179688</v>
+        <v>11.4660043716431</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>12.25</v>
       </c>
       <c r="G822" t="n">
-        <v>11.3273019790649</v>
+        <v>11.3273029327393</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G824" t="n">
-        <v>11.6509408950806</v>
+        <v>11.6509389877319</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G825" t="n">
-        <v>11.9745759963989</v>
+        <v>11.9745769500732</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G826" t="n">
-        <v>12.0670461654663</v>
+        <v>12.067045211792</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>12.3444480895996</v>
+        <v>12.3444490432739</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G829" t="n">
-        <v>13.130425453186</v>
+        <v>13.1304244995117</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G830" t="n">
-        <v>13.4540615081787</v>
+        <v>13.4540605545044</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>15.75</v>
       </c>
       <c r="G834" t="n">
-        <v>14.5636749267578</v>
+        <v>14.5636758804321</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G835" t="n">
-        <v>15.3496503829956</v>
+        <v>15.3496532440186</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G837" t="n">
-        <v>16.3667984008789</v>
+        <v>16.3667964935303</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G838" t="n">
-        <v>16.459264755249</v>
+        <v>16.4592628479004</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G842" t="n">
-        <v>16.0431594848633</v>
+        <v>16.0431613922119</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>17</v>
       </c>
       <c r="G843" t="n">
-        <v>15.7195224761963</v>
+        <v>15.719521522522</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G844" t="n">
-        <v>15.3496503829956</v>
+        <v>15.3496532440186</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G845" t="n">
-        <v>15.1647157669067</v>
+        <v>15.1647167205811</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G846" t="n">
-        <v>14.9335451126099</v>
+        <v>14.9335460662842</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>16.5</v>
       </c>
       <c r="G848" t="n">
-        <v>15.2571840286255</v>
+        <v>15.2571830749512</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G849" t="n">
-        <v>15.2109498977661</v>
+        <v>15.2109508514404</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G851" t="n">
-        <v>15.9969244003296</v>
+        <v>15.9969263076782</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G852" t="n">
-        <v>15.9969244003296</v>
+        <v>15.9969263076782</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G853" t="n">
-        <v>15.8119916915894</v>
+        <v>15.8119888305664</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G854" t="n">
-        <v>15.3958854675293</v>
+        <v>15.395884513855</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G855" t="n">
-        <v>15.1647157669067</v>
+        <v>15.1647167205811</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>14.9797811508179</v>
+        <v>14.9797821044922</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G858" t="n">
-        <v>14.4249725341797</v>
+        <v>14.424973487854</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G860" t="n">
-        <v>13.5465297698975</v>
+        <v>13.5465288162231</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G861" t="n">
-        <v>13.36159324646</v>
+        <v>13.3615942001343</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G862" t="n">
-        <v>12.4369173049927</v>
+        <v>12.4369163513184</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G863" t="n">
-        <v>13.037956237793</v>
+        <v>13.0379571914673</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G864" t="n">
-        <v>13.130425453186</v>
+        <v>13.1304244995117</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G865" t="n">
-        <v>13.36159324646</v>
+        <v>13.3615942001343</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G867" t="n">
-        <v>15.3496503829956</v>
+        <v>15.3496532440186</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G868" t="n">
-        <v>15.6732902526855</v>
+        <v>15.6732883453369</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>16.5</v>
       </c>
       <c r="G869" t="n">
-        <v>15.2571840286255</v>
+        <v>15.2571830749512</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G870" t="n">
-        <v>15.3496503829956</v>
+        <v>15.3496532440186</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G871" t="n">
-        <v>14.9797811508179</v>
+        <v>14.9797821044922</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G874" t="n">
-        <v>14.5174417495728</v>
+        <v>14.5174407958984</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>16</v>
       </c>
       <c r="G875" t="n">
-        <v>14.7948436737061</v>
+        <v>14.7948455810547</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23197,7 +23197,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G878" t="n">
-        <v>14.3787393569946</v>
+        <v>14.3787384033203</v>
       </c>
       <c r="H878" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G879" t="n">
-        <v>14.7023763656616</v>
+        <v>14.702374458313</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>15.25</v>
       </c>
       <c r="G881" t="n">
-        <v>14.1013355255127</v>
+        <v>14.101336479187</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>13.5465297698975</v>
+        <v>13.5465288162231</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G886" t="n">
-        <v>13.8239316940308</v>
+        <v>13.8239326477051</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G887" t="n">
-        <v>13.4540615081787</v>
+        <v>13.4540605545044</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G889" t="n">
-        <v>13.2228908538818</v>
+        <v>13.2228918075562</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>14.75</v>
       </c>
       <c r="G890" t="n">
-        <v>13.6389980316162</v>
+        <v>13.6389970779419</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>13.5927629470825</v>
+        <v>13.5927639007568</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G892" t="n">
-        <v>13.5002956390381</v>
+        <v>13.5002965927124</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G893" t="n">
-        <v>13.6852321624756</v>
+        <v>13.685230255127</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>16</v>
       </c>
       <c r="G895" t="n">
-        <v>14.7948436737061</v>
+        <v>14.7948455810547</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G896" t="n">
-        <v>14.5174417495728</v>
+        <v>14.5174407958984</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>16</v>
       </c>
       <c r="G898" t="n">
-        <v>14.7948436737061</v>
+        <v>14.7948455810547</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G899" t="n">
-        <v>15.6732902526855</v>
+        <v>15.6732883453369</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G901" t="n">
-        <v>15.1647157669067</v>
+        <v>15.1647167205811</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G903" t="n">
-        <v>14.9335451126099</v>
+        <v>14.9335460662842</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G904" t="n">
-        <v>15.2109498977661</v>
+        <v>15.2109508514404</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G907" t="n">
-        <v>15.3496503829956</v>
+        <v>15.3496532440186</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G908" t="n">
-        <v>15.1184825897217</v>
+        <v>15.118480682373</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G909" t="n">
-        <v>14.9335451126099</v>
+        <v>14.9335460662842</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>16</v>
       </c>
       <c r="G910" t="n">
-        <v>14.7948436737061</v>
+        <v>14.7948455810547</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24107,7 +24107,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G913" t="n">
-        <v>14.2400369644165</v>
+        <v>14.2400379180908</v>
       </c>
       <c r="H913" t="s">
         <v>8</v>
@@ -24133,7 +24133,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G914" t="n">
-        <v>14.4249725341797</v>
+        <v>14.424973487854</v>
       </c>
       <c r="H914" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G915" t="n">
-        <v>13.9626350402832</v>
+        <v>13.9626340866089</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>15.25</v>
       </c>
       <c r="G916" t="n">
-        <v>14.1013355255127</v>
+        <v>14.101336479187</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>15.25</v>
       </c>
       <c r="G918" t="n">
-        <v>14.1013355255127</v>
+        <v>14.101336479187</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G919" t="n">
-        <v>14.5174417495728</v>
+        <v>14.5174407958984</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>15.25</v>
       </c>
       <c r="G922" t="n">
-        <v>14.1013355255127</v>
+        <v>14.101336479187</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G923" t="n">
-        <v>13.5927629470825</v>
+        <v>13.5927639007568</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>15</v>
       </c>
       <c r="G924" t="n">
-        <v>13.8701658248901</v>
+        <v>13.8701667785645</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G928" t="n">
-        <v>14.3787393569946</v>
+        <v>14.3787384033203</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>15.25</v>
       </c>
       <c r="G929" t="n">
-        <v>14.1013355255127</v>
+        <v>14.101336479187</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G930" t="n">
-        <v>14.4249725341797</v>
+        <v>14.424973487854</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G933" t="n">
-        <v>15.1647157669067</v>
+        <v>15.1647167205811</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>16</v>
       </c>
       <c r="G934" t="n">
-        <v>14.7948436737061</v>
+        <v>14.7948455810547</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G935" t="n">
-        <v>14.7023763656616</v>
+        <v>14.702374458313</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G936" t="n">
-        <v>14.9797811508179</v>
+        <v>14.9797821044922</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G939" t="n">
-        <v>14.5174417495728</v>
+        <v>14.5174407958984</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G940" t="n">
-        <v>14.7023763656616</v>
+        <v>14.702374458313</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>15.75</v>
       </c>
       <c r="G941" t="n">
-        <v>14.5636749267578</v>
+        <v>14.5636758804321</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G943" t="n">
-        <v>14.7023763656616</v>
+        <v>14.702374458313</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G945" t="n">
-        <v>14.3787393569946</v>
+        <v>14.3787384033203</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G947" t="n">
-        <v>14.6099090576172</v>
+        <v>14.6099081039429</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G948" t="n">
-        <v>14.4249725341797</v>
+        <v>14.424973487854</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G949" t="n">
-        <v>14.4249725341797</v>
+        <v>14.424973487854</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G950" t="n">
-        <v>13.6852321624756</v>
+        <v>13.685230255127</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G951" t="n">
-        <v>13.5465297698975</v>
+        <v>13.5465288162231</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>15.25</v>
       </c>
       <c r="G953" t="n">
-        <v>14.1013355255127</v>
+        <v>14.101336479187</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>15.25</v>
       </c>
       <c r="G954" t="n">
-        <v>14.1013355255127</v>
+        <v>14.101336479187</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>15</v>
       </c>
       <c r="G955" t="n">
-        <v>13.8701658248901</v>
+        <v>13.8701667785645</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G960" t="n">
-        <v>13.9626350402832</v>
+        <v>13.9626340866089</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G961" t="n">
-        <v>13.5465297698975</v>
+        <v>13.5465288162231</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25381,7 +25381,7 @@
         <v>14.4499998092651</v>
       </c>
       <c r="G962" t="n">
-        <v>13.36159324646</v>
+        <v>13.3615942001343</v>
       </c>
       <c r="H962" t="s">
         <v>8</v>
@@ -25407,7 +25407,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G963" t="n">
-        <v>13.2691268920898</v>
+        <v>13.2691259384155</v>
       </c>
       <c r="H963" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G964" t="n">
-        <v>13.4540615081787</v>
+        <v>13.4540605545044</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>15</v>
       </c>
       <c r="G965" t="n">
-        <v>13.8701658248901</v>
+        <v>13.8701667785645</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G969" t="n">
-        <v>14.277024269104</v>
+        <v>14.2770252227783</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>15.5</v>
       </c>
       <c r="G970" t="n">
-        <v>14.3325061798096</v>
+        <v>14.3325052261353</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G971" t="n">
-        <v>14.6099090576172</v>
+        <v>14.6099081039429</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G972" t="n">
-        <v>14.2585315704346</v>
+        <v>14.2585306167603</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G973" t="n">
-        <v>14.498948097229</v>
+        <v>14.4989490509033</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G975" t="n">
-        <v>14.350998878479</v>
+        <v>14.3509998321533</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G976" t="n">
-        <v>14.5359354019165</v>
+        <v>14.5359334945679</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G977" t="n">
-        <v>14.7023763656616</v>
+        <v>14.702374458313</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>16</v>
       </c>
       <c r="G978" t="n">
-        <v>14.7948436737061</v>
+        <v>14.7948455810547</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>16</v>
       </c>
       <c r="G979" t="n">
-        <v>14.7948436737061</v>
+        <v>14.7948455810547</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G980" t="n">
-        <v>14.5174417495728</v>
+        <v>14.5174407958984</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G982" t="n">
-        <v>14.7763509750366</v>
+        <v>14.7763500213623</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G983" t="n">
-        <v>14.924298286438</v>
+        <v>14.9242992401123</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>16</v>
       </c>
       <c r="G985" t="n">
-        <v>14.7948436737061</v>
+        <v>14.7948455810547</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G986" t="n">
-        <v>15.0352602005005</v>
+        <v>15.0352592468262</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G987" t="n">
-        <v>14.9982738494873</v>
+        <v>14.9982719421387</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G990" t="n">
-        <v>14.5359354019165</v>
+        <v>14.5359334945679</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G991" t="n">
-        <v>14.7023763656616</v>
+        <v>14.702374458313</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G992" t="n">
-        <v>14.9612865447998</v>
+        <v>14.9612874984741</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G993" t="n">
-        <v>14.9612865447998</v>
+        <v>14.9612874984741</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G994" t="n">
-        <v>15.2637691497803</v>
+        <v>15.263768196106</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G995" t="n">
-        <v>14.8728685379028</v>
+        <v>14.8728675842285</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>15.5</v>
       </c>
       <c r="G997" t="n">
-        <v>14.4261236190796</v>
+        <v>14.4261245727539</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G998" t="n">
-        <v>14.9845552444458</v>
+        <v>14.9845542907715</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G999" t="n">
-        <v>15.1334686279297</v>
+        <v>15.1334676742554</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1000" t="n">
-        <v>15.1706972122192</v>
+        <v>15.1706981658936</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1001" t="n">
-        <v>15.2265424728394</v>
+        <v>15.2265434265137</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1002" t="n">
-        <v>15.2079267501831</v>
+        <v>15.2079277038574</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1003" t="n">
-        <v>14.9845552444458</v>
+        <v>14.9845542907715</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>16.4699993133545</v>
       </c>
       <c r="G1004" t="n">
-        <v>15.3289194107056</v>
+        <v>15.3289213180542</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>17.3120002746582</v>
       </c>
       <c r="G1005" t="n">
-        <v>16.1125831604004</v>
+        <v>16.112585067749</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>17.75</v>
       </c>
       <c r="G1006" t="n">
-        <v>16.5202388763428</v>
+        <v>16.5202407836914</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1007" t="n">
-        <v>16.5667724609375</v>
+        <v>16.5667762756348</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1009" t="n">
-        <v>17.981466293335</v>
+        <v>17.9814643859863</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26655,7 +26655,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G1011" t="n">
-        <v>17.460262298584</v>
+        <v>17.4602661132812</v>
       </c>
       <c r="H1011" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1015" t="n">
-        <v>16.60400390625</v>
+        <v>16.6040019989014</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G1016" t="n">
-        <v>16.5295467376709</v>
+        <v>16.5295448303223</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1017" t="n">
-        <v>16.2503299713135</v>
+        <v>16.2503318786621</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1018" t="n">
-        <v>16.4737033843994</v>
+        <v>16.473705291748</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1019" t="n">
-        <v>16.3992462158203</v>
+        <v>16.3992443084717</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1020" t="n">
-        <v>16.4923152923584</v>
+        <v>16.492317199707</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G1021" t="n">
-        <v>16.7715320587158</v>
+        <v>16.7715339660645</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G1022" t="n">
-        <v>17.1624336242676</v>
+        <v>17.1624355316162</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26993,7 +26993,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1024" t="n">
-        <v>17.4974937438965</v>
+        <v>17.4974918365479</v>
       </c>
       <c r="H1024" t="s">
         <v>8</v>
@@ -27019,7 +27019,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1025" t="n">
-        <v>17.4974937438965</v>
+        <v>17.4974918365479</v>
       </c>
       <c r="H1025" t="s">
         <v>8</v>
@@ -27045,7 +27045,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1026" t="n">
-        <v>17.4974937438965</v>
+        <v>17.4974918365479</v>
       </c>
       <c r="H1026" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1027" t="n">
-        <v>17.981466293335</v>
+        <v>17.9814643859863</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G1034" t="n">
-        <v>17.758092880249</v>
+        <v>17.7580909729004</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G1035" t="n">
-        <v>17.8325500488281</v>
+        <v>17.8325519561768</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G1038" t="n">
-        <v>18.1303806304932</v>
+        <v>18.1303825378418</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1040" t="n">
-        <v>18.3351402282715</v>
+        <v>18.3351383209229</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1043" t="n">
-        <v>17.441650390625</v>
+        <v>17.4416484832764</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1045" t="n">
-        <v>17.5347194671631</v>
+        <v>17.5347213745117</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>18.9599990844727</v>
       </c>
       <c r="G1050" t="n">
-        <v>17.6464080810547</v>
+        <v>17.6464061737061</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1052" t="n">
-        <v>17.981466293335</v>
+        <v>17.9814643859863</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1053" t="n">
-        <v>18.2420673370361</v>
+        <v>18.2420654296875</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1054" t="n">
-        <v>18.5212802886963</v>
+        <v>18.5212821960449</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1060" t="n">
-        <v>20.8480758666992</v>
+        <v>20.8480739593506</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1061" t="n">
-        <v>21.4995784759521</v>
+        <v>21.4995803833008</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>23</v>
       </c>
       <c r="G1062" t="n">
-        <v>21.4065036773682</v>
+        <v>21.4065074920654</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1063" t="n">
-        <v>21.4995784759521</v>
+        <v>21.4995803833008</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>23.2800006866455</v>
       </c>
       <c r="G1064" t="n">
-        <v>21.6671085357666</v>
+        <v>21.667106628418</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28059,7 +28059,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1065" t="n">
-        <v>22.058012008667</v>
+        <v>22.0580101013184</v>
       </c>
       <c r="H1065" t="s">
         <v>8</v>
@@ -28111,7 +28111,7 @@
         <v>23.9599990844727</v>
       </c>
       <c r="G1067" t="n">
-        <v>22.2999935150146</v>
+        <v>22.2999954223633</v>
       </c>
       <c r="H1067" t="s">
         <v>8</v>
@@ -28163,7 +28163,7 @@
         <v>23.9599990844727</v>
       </c>
       <c r="G1069" t="n">
-        <v>22.2999935150146</v>
+        <v>22.2999954223633</v>
       </c>
       <c r="H1069" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1070" t="n">
-        <v>22.0393943786621</v>
+        <v>22.0393962860107</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>23.2800006866455</v>
       </c>
       <c r="G1071" t="n">
-        <v>21.6671085357666</v>
+        <v>21.667106628418</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>23.5</v>
       </c>
       <c r="G1072" t="n">
-        <v>21.8718643188477</v>
+        <v>21.871862411499</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>23.9799995422363</v>
       </c>
       <c r="G1074" t="n">
-        <v>22.3186111450195</v>
+        <v>22.3186073303223</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>24.2399997711182</v>
       </c>
       <c r="G1075" t="n">
-        <v>22.5605945587158</v>
+        <v>22.5605983734131</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>25.2199993133545</v>
       </c>
       <c r="G1076" t="n">
-        <v>23.4726982116699</v>
+        <v>23.4727001190186</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>26.3600006103516</v>
       </c>
       <c r="G1077" t="n">
-        <v>24.5337181091309</v>
+        <v>24.5337162017822</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G1081" t="n">
-        <v>25.2969093322754</v>
+        <v>25.2969055175781</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>27.0599994659424</v>
       </c>
       <c r="G1082" t="n">
-        <v>25.1852226257324</v>
+        <v>25.1852188110352</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1083" t="n">
-        <v>24.3848037719727</v>
+        <v>24.384801864624</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>26.1800003051758</v>
       </c>
       <c r="G1084" t="n">
-        <v>24.3661880493164</v>
+        <v>24.366189956665</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>26.9200000762939</v>
       </c>
       <c r="G1085" t="n">
-        <v>25.0549201965332</v>
+        <v>25.0549182891846</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>27.3199996948242</v>
       </c>
       <c r="G1090" t="n">
-        <v>25.4272060394287</v>
+        <v>25.4272079467773</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>27.2199993133545</v>
       </c>
       <c r="G1091" t="n">
-        <v>25.3341331481934</v>
+        <v>25.3341369628906</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>26.5599994659424</v>
       </c>
       <c r="G1092" t="n">
-        <v>24.7198619842529</v>
+        <v>24.7198600769043</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>26.1800003051758</v>
       </c>
       <c r="G1093" t="n">
-        <v>24.3661880493164</v>
+        <v>24.366189956665</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1094" t="n">
-        <v>24.0125160217285</v>
+        <v>24.0125179290771</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>24.5400009155273</v>
       </c>
       <c r="G1097" t="n">
-        <v>22.8398113250732</v>
+        <v>22.8398132324219</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G1099" t="n">
-        <v>22.8770408630371</v>
+        <v>22.8770389556885</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1100" t="n">
-        <v>23.5471572875977</v>
+        <v>23.547155380249</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1101" t="n">
-        <v>23.5471572875977</v>
+        <v>23.547155380249</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29021,7 +29021,7 @@
         <v>25.2399997711182</v>
       </c>
       <c r="G1102" t="n">
-        <v>23.4913158416748</v>
+        <v>23.4913139343262</v>
       </c>
       <c r="H1102" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1103" t="n">
-        <v>23.640230178833</v>
+        <v>23.6402282714844</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29073,7 +29073,7 @@
         <v>25.6399993896484</v>
       </c>
       <c r="G1104" t="n">
-        <v>23.8636035919189</v>
+        <v>23.8636016845703</v>
       </c>
       <c r="H1104" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>25.8999996185303</v>
       </c>
       <c r="G1105" t="n">
-        <v>24.1055870056152</v>
+        <v>24.1055889129639</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>26.5400009155273</v>
       </c>
       <c r="G1106" t="n">
-        <v>24.7012481689453</v>
+        <v>24.7012500762939</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1109" t="n">
-        <v>26.804666519165</v>
+        <v>26.8046684265137</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>29</v>
       </c>
       <c r="G1110" t="n">
-        <v>26.990816116333</v>
+        <v>26.9908123016357</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1111" t="n">
-        <v>26.804666519165</v>
+        <v>26.8046684265137</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29359,7 +29359,7 @@
         <v>31.8600006103516</v>
       </c>
       <c r="G1115" t="n">
-        <v>29.6526679992676</v>
+        <v>29.6526660919189</v>
       </c>
       <c r="H1115" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>30.5200004577637</v>
       </c>
       <c r="G1118" t="n">
-        <v>28.4055042266846</v>
+        <v>28.4055023193359</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>30.8400001525879</v>
       </c>
       <c r="G1119" t="n">
-        <v>28.703332901001</v>
+        <v>28.7033348083496</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>33.5800018310547</v>
       </c>
       <c r="G1125" t="n">
-        <v>31.2534999847412</v>
+        <v>31.2535018920898</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>33</v>
       </c>
       <c r="G1126" t="n">
-        <v>30.7136859893799</v>
+        <v>30.7136821746826</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>33.5400009155273</v>
       </c>
       <c r="G1127" t="n">
-        <v>31.216272354126</v>
+        <v>31.2162704467773</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>33.5</v>
       </c>
       <c r="G1129" t="n">
-        <v>31.1790447235107</v>
+        <v>31.1790390014648</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>33.6599998474121</v>
       </c>
       <c r="G1130" t="n">
-        <v>31.3279571533203</v>
+        <v>31.3279590606689</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1133" t="n">
-        <v>30.5275382995605</v>
+        <v>30.5275363922119</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>31.6200008392334</v>
       </c>
       <c r="G1134" t="n">
-        <v>29.429292678833</v>
+        <v>29.4292945861816</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1135" t="n">
-        <v>28.9453182220459</v>
+        <v>28.9453201293945</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>32.4199981689453</v>
       </c>
       <c r="G1136" t="n">
-        <v>30.1738662719727</v>
+        <v>30.173864364624</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>32.6399993896484</v>
       </c>
       <c r="G1137" t="n">
-        <v>30.378625869751</v>
+        <v>30.3786239624023</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -29983,7 +29983,7 @@
         <v>33</v>
       </c>
       <c r="G1139" t="n">
-        <v>30.7136859893799</v>
+        <v>30.7136821746826</v>
       </c>
       <c r="H1139" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>33.4599990844727</v>
       </c>
       <c r="G1143" t="n">
-        <v>31.1418113708496</v>
+        <v>31.1418151855469</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>34.439998626709</v>
       </c>
       <c r="G1144" t="n">
-        <v>32.0539131164551</v>
+        <v>32.0539169311523</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G1147" t="n">
-        <v>32.7612648010254</v>
+        <v>32.7612609863281</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>36</v>
       </c>
       <c r="G1148" t="n">
-        <v>33.5058403015137</v>
+        <v>33.5058326721191</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G1151" t="n">
-        <v>31.5513324737549</v>
+        <v>31.5513286590576</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>33.6199989318848</v>
       </c>
       <c r="G1152" t="n">
-        <v>31.2907295227051</v>
+        <v>31.2907276153564</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>33.9199981689453</v>
       </c>
       <c r="G1153" t="n">
-        <v>31.5699443817139</v>
+        <v>31.5699405670166</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>34.1800003051758</v>
       </c>
       <c r="G1154" t="n">
-        <v>31.8119316101074</v>
+        <v>31.8119335174561</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30399,7 +30399,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1155" t="n">
-        <v>32.2028274536133</v>
+        <v>32.2028312683105</v>
       </c>
       <c r="H1155" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G1156" t="n">
-        <v>33.7850532531738</v>
+        <v>33.7850494384766</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30451,7 +30451,7 @@
         <v>35.7799987792969</v>
       </c>
       <c r="G1157" t="n">
-        <v>33.3010787963867</v>
+        <v>33.3010749816895</v>
       </c>
       <c r="H1157" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>36.2799987792969</v>
       </c>
       <c r="G1158" t="n">
-        <v>33.7664375305176</v>
+        <v>33.766429901123</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30503,7 +30503,7 @@
         <v>35.7400016784668</v>
       </c>
       <c r="G1159" t="n">
-        <v>33.2638473510742</v>
+        <v>33.2638511657715</v>
       </c>
       <c r="H1159" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>35.6800003051758</v>
       </c>
       <c r="G1160" t="n">
-        <v>33.2080078125</v>
+        <v>33.2080039978027</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30555,7 +30555,7 @@
         <v>35.8400001525879</v>
       </c>
       <c r="G1161" t="n">
-        <v>33.3569221496582</v>
+        <v>33.3569259643555</v>
       </c>
       <c r="H1161" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>37.9799995422363</v>
       </c>
       <c r="G1163" t="n">
-        <v>35.3486595153809</v>
+        <v>35.3486557006836</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>39.7000007629395</v>
       </c>
       <c r="G1164" t="n">
-        <v>36.9494972229004</v>
+        <v>36.9494934082031</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>38.060001373291</v>
       </c>
       <c r="G1165" t="n">
-        <v>35.4231185913086</v>
+        <v>35.4231147766113</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>36</v>
       </c>
       <c r="G1166" t="n">
-        <v>33.5058403015137</v>
+        <v>33.5058326721191</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>33.5400009155273</v>
       </c>
       <c r="G1167" t="n">
-        <v>31.216272354126</v>
+        <v>31.2162704467773</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G1169" t="n">
-        <v>32.4820518493652</v>
+        <v>32.482048034668</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>35.5</v>
       </c>
       <c r="G1170" t="n">
-        <v>33.0404777526855</v>
+        <v>33.0404815673828</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G1171" t="n">
-        <v>32.4820518493652</v>
+        <v>32.482048034668</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30841,7 +30841,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1172" t="n">
-        <v>32.2028274536133</v>
+        <v>32.2028312683105</v>
       </c>
       <c r="H1172" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1176" t="n">
-        <v>30.8998260498047</v>
+        <v>30.8998279571533</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>30.8400001525879</v>
       </c>
       <c r="G1177" t="n">
-        <v>28.703332901001</v>
+        <v>28.7033348083496</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>29.9200000762939</v>
       </c>
       <c r="G1178" t="n">
-        <v>27.847074508667</v>
+        <v>27.8470726013184</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>30.0599994659424</v>
       </c>
       <c r="G1181" t="n">
-        <v>27.9773712158203</v>
+        <v>27.9773731231689</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31101,7 +31101,7 @@
         <v>31.1800003051758</v>
       </c>
       <c r="G1182" t="n">
-        <v>29.0197792053223</v>
+        <v>29.0197772979736</v>
       </c>
       <c r="H1182" t="s">
         <v>8</v>
@@ -31127,7 +31127,7 @@
         <v>32.9799995422363</v>
       </c>
       <c r="G1183" t="n">
-        <v>30.695068359375</v>
+        <v>30.6950702667236</v>
       </c>
       <c r="H1183" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1187" t="n">
-        <v>27.735387802124</v>
+        <v>27.7353858947754</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>29.0400009155273</v>
       </c>
       <c r="G1188" t="n">
-        <v>27.028039932251</v>
+        <v>27.0280418395996</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>29</v>
       </c>
       <c r="G1190" t="n">
-        <v>26.990816116333</v>
+        <v>26.9908123016357</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>28.7800006866455</v>
       </c>
       <c r="G1192" t="n">
-        <v>26.7860565185547</v>
+        <v>26.7860546112061</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>29.9799995422363</v>
       </c>
       <c r="G1194" t="n">
-        <v>27.9029159545898</v>
+        <v>27.9029140472412</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>29.0400009155273</v>
       </c>
       <c r="G1196" t="n">
-        <v>27.028039932251</v>
+        <v>27.0280418395996</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G1197" t="n">
-        <v>26.3579273223877</v>
+        <v>26.3579235076904</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1198" t="n">
-        <v>26.897741317749</v>
+        <v>26.8977394104004</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G1199" t="n">
-        <v>26.190393447876</v>
+        <v>26.1903953552246</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>28.8799991607666</v>
       </c>
       <c r="G1201" t="n">
-        <v>26.8791255950928</v>
+        <v>26.8791275024414</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>28.5599994659424</v>
       </c>
       <c r="G1202" t="n">
-        <v>26.581298828125</v>
+        <v>26.5812969207764</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>28.8799991607666</v>
       </c>
       <c r="G1203" t="n">
-        <v>26.8791255950928</v>
+        <v>26.8791275024414</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G1205" t="n">
-        <v>25.2969093322754</v>
+        <v>25.2969055175781</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>26.0400009155273</v>
       </c>
       <c r="G1206" t="n">
-        <v>24.2358913421631</v>
+        <v>24.2358894348145</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>25.7800006866455</v>
       </c>
       <c r="G1207" t="n">
-        <v>23.9939022064209</v>
+        <v>23.9939041137695</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>27.1200008392334</v>
       </c>
       <c r="G1210" t="n">
-        <v>25.2410659790039</v>
+        <v>25.2410640716553</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31855,7 +31855,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G1211" t="n">
-        <v>26.190393447876</v>
+        <v>26.1903953552246</v>
       </c>
       <c r="H1211" t="s">
         <v>8</v>
@@ -31881,7 +31881,7 @@
         <v>28.4799995422363</v>
       </c>
       <c r="G1212" t="n">
-        <v>26.5068397521973</v>
+        <v>26.5068378448486</v>
       </c>
       <c r="H1212" t="s">
         <v>8</v>
@@ -31933,7 +31933,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1214" t="n">
-        <v>27.2141857147217</v>
+        <v>27.2141876220703</v>
       </c>
       <c r="H1214" t="s">
         <v>8</v>
@@ -31959,7 +31959,7 @@
         <v>29.8799991607666</v>
       </c>
       <c r="G1215" t="n">
-        <v>27.8098449707031</v>
+        <v>27.8098411560059</v>
       </c>
       <c r="H1215" t="s">
         <v>8</v>
@@ -31985,7 +31985,7 @@
         <v>29.3199996948242</v>
       </c>
       <c r="G1216" t="n">
-        <v>27.2886409759521</v>
+        <v>27.2886428833008</v>
       </c>
       <c r="H1216" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>28.8400001525879</v>
       </c>
       <c r="G1217" t="n">
-        <v>26.8418998718262</v>
+        <v>26.8418979644775</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32037,7 +32037,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1218" t="n">
-        <v>27.6423149108887</v>
+        <v>27.6423168182373</v>
       </c>
       <c r="H1218" t="s">
         <v>8</v>
@@ -32063,7 +32063,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1219" t="n">
-        <v>27.735387802124</v>
+        <v>27.7353858947754</v>
       </c>
       <c r="H1219" t="s">
         <v>8</v>
@@ -32193,7 +32193,7 @@
         <v>30.9200000762939</v>
       </c>
       <c r="G1224" t="n">
-        <v>28.7777900695801</v>
+        <v>28.7777919769287</v>
       </c>
       <c r="H1224" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>29.9599990844727</v>
       </c>
       <c r="G1225" t="n">
-        <v>27.8843002319336</v>
+        <v>27.8843040466309</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32245,7 +32245,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1226" t="n">
-        <v>27.549243927002</v>
+        <v>27.5492458343506</v>
       </c>
       <c r="H1226" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>29.6399993896484</v>
       </c>
       <c r="G1227" t="n">
-        <v>27.5864734649658</v>
+        <v>27.5864715576172</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32375,7 +32375,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1231" t="n">
-        <v>26.2462387084961</v>
+        <v>26.2462406158447</v>
       </c>
       <c r="H1231" t="s">
         <v>8</v>
@@ -32479,7 +32479,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1235" t="n">
-        <v>25.8739528656006</v>
+        <v>25.873950958252</v>
       </c>
       <c r="H1235" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>27.2800006866455</v>
       </c>
       <c r="G1237" t="n">
-        <v>25.3899784088135</v>
+        <v>25.3899765014648</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32557,7 +32557,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G1238" t="n">
-        <v>25.2969093322754</v>
+        <v>25.2969055175781</v>
       </c>
       <c r="H1238" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>26.7600002288818</v>
       </c>
       <c r="G1239" t="n">
-        <v>24.9060039520264</v>
+        <v>24.906005859375</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32687,7 +32687,7 @@
         <v>25.5599994659424</v>
       </c>
       <c r="G1243" t="n">
-        <v>24.0588607788086</v>
+        <v>24.0588626861572</v>
       </c>
       <c r="H1243" t="s">
         <v>8</v>
@@ -32739,7 +32739,7 @@
         <v>24.9799995422363</v>
       </c>
       <c r="G1245" t="n">
-        <v>23.5129261016846</v>
+        <v>23.5129241943359</v>
       </c>
       <c r="H1245" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>25.2600002288818</v>
       </c>
       <c r="G1246" t="n">
-        <v>23.776481628418</v>
+        <v>23.7764797210693</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G1248" t="n">
-        <v>21.6680374145508</v>
+        <v>21.6680355072021</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G1250" t="n">
-        <v>20.2749557495117</v>
+        <v>20.2749576568604</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32895,7 +32895,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1251" t="n">
-        <v>20.5196876525879</v>
+        <v>20.5196857452393</v>
       </c>
       <c r="H1251" t="s">
         <v>8</v>
@@ -32947,7 +32947,7 @@
         <v>20.5799999237061</v>
       </c>
       <c r="G1253" t="n">
-        <v>19.371337890625</v>
+        <v>19.3713359832764</v>
       </c>
       <c r="H1253" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G1254" t="n">
-        <v>19.653715133667</v>
+        <v>19.6537170410156</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1255" t="n">
-        <v>19.2019062042236</v>
+        <v>19.2019081115723</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1256" t="n">
-        <v>19.9549255371094</v>
+        <v>19.9549236297607</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G1261" t="n">
-        <v>20.2749557495117</v>
+        <v>20.2749576568604</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>20.8999996185303</v>
       </c>
       <c r="G1263" t="n">
-        <v>19.6725425720215</v>
+        <v>19.6725444793701</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33259,7 +33259,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G1265" t="n">
-        <v>21.0279712677002</v>
+        <v>21.0279731750488</v>
       </c>
       <c r="H1265" t="s">
         <v>8</v>
@@ -33311,7 +33311,7 @@
         <v>22.3600006103516</v>
       </c>
       <c r="G1267" t="n">
-        <v>21.0467967987061</v>
+        <v>21.0467987060547</v>
       </c>
       <c r="H1267" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1268" t="n">
-        <v>20.3314323425293</v>
+        <v>20.3314342498779</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>21.0599994659424</v>
       </c>
       <c r="G1272" t="n">
-        <v>19.8231449127197</v>
+        <v>19.8231468200684</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G1273" t="n">
-        <v>19.7478446960449</v>
+        <v>19.7478466033936</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33493,7 +33493,7 @@
         <v>20.0200004577637</v>
       </c>
       <c r="G1274" t="n">
-        <v>18.8442249298096</v>
+        <v>18.8442268371582</v>
       </c>
       <c r="H1274" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G1275" t="n">
-        <v>18.288875579834</v>
+        <v>18.2888774871826</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1281" t="n">
-        <v>17.7147006988525</v>
+        <v>17.7147026062012</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G1283" t="n">
-        <v>17.9217834472656</v>
+        <v>17.921781539917</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1284" t="n">
-        <v>17.9029560089111</v>
+        <v>17.9029579162598</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1285" t="n">
-        <v>17.5264492034912</v>
+        <v>17.5264472961426</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33831,7 +33831,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G1287" t="n">
-        <v>16.8863830566406</v>
+        <v>16.8863849639893</v>
       </c>
       <c r="H1287" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1290" t="n">
-        <v>16.0204162597656</v>
+        <v>16.020414352417</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G1293" t="n">
-        <v>17.3852577209473</v>
+        <v>17.3852558135986</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34039,7 +34039,7 @@
         <v>19.3099994659424</v>
       </c>
       <c r="G1295" t="n">
-        <v>18.1759223937988</v>
+        <v>18.1759243011475</v>
       </c>
       <c r="H1295" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G1296" t="n">
-        <v>17.8088283538818</v>
+        <v>17.8088302612305</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1300" t="n">
-        <v>16.4534015655518</v>
+        <v>16.4533977508545</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1301" t="n">
-        <v>17.8370685577393</v>
+        <v>17.8370666503906</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G1302" t="n">
-        <v>17.4982109069824</v>
+        <v>17.4982089996338</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G1304" t="n">
-        <v>17.6770515441895</v>
+        <v>17.6770534515381</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34299,7 +34299,7 @@
         <v>18.8299999237061</v>
       </c>
       <c r="G1305" t="n">
-        <v>17.7241153717041</v>
+        <v>17.7241134643555</v>
       </c>
       <c r="H1305" t="s">
         <v>8</v>
@@ -34325,7 +34325,7 @@
         <v>18.75</v>
       </c>
       <c r="G1306" t="n">
-        <v>17.6488132476807</v>
+        <v>17.648811340332</v>
       </c>
       <c r="H1306" t="s">
         <v>8</v>
@@ -34377,7 +34377,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G1308" t="n">
-        <v>18.0253200531006</v>
+        <v>18.0253219604492</v>
       </c>
       <c r="H1308" t="s">
         <v>8</v>
@@ -34403,7 +34403,7 @@
         <v>20</v>
       </c>
       <c r="G1309" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1309" t="s">
         <v>8</v>
@@ -34455,7 +34455,7 @@
         <v>20</v>
       </c>
       <c r="G1311" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1311" t="s">
         <v>8</v>
@@ -34481,7 +34481,7 @@
         <v>20</v>
       </c>
       <c r="G1312" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1312" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G1316" t="n">
-        <v>18.288875579834</v>
+        <v>18.2888774871826</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1317" t="n">
-        <v>18.4488925933838</v>
+        <v>18.4488906860352</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34689,7 +34689,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G1320" t="n">
-        <v>18.2982902526855</v>
+        <v>18.2982883453369</v>
       </c>
       <c r="H1320" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1322" t="n">
-        <v>17.5264492034912</v>
+        <v>17.5264472961426</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34767,7 +34767,7 @@
         <v>18.1700000762939</v>
       </c>
       <c r="G1323" t="n">
-        <v>17.1028747558594</v>
+        <v>17.102876663208</v>
       </c>
       <c r="H1323" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G1325" t="n">
-        <v>16.7169570922852</v>
+        <v>16.7169551849365</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34845,7 +34845,7 @@
         <v>18</v>
       </c>
       <c r="G1326" t="n">
-        <v>16.9428615570068</v>
+        <v>16.9428596496582</v>
       </c>
       <c r="H1326" t="s">
         <v>8</v>
@@ -34897,7 +34897,7 @@
         <v>18</v>
       </c>
       <c r="G1328" t="n">
-        <v>16.9428615570068</v>
+        <v>16.9428596496582</v>
       </c>
       <c r="H1328" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1329" t="n">
-        <v>16.0392417907715</v>
+        <v>16.0392436981201</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1332" t="n">
-        <v>16.5851783752441</v>
+        <v>16.5851764678955</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1335" t="n">
-        <v>16.6134147644043</v>
+        <v>16.6134166717529</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1336" t="n">
-        <v>16.6134147644043</v>
+        <v>16.6134166717529</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35131,7 +35131,7 @@
         <v>18</v>
       </c>
       <c r="G1337" t="n">
-        <v>16.9428615570068</v>
+        <v>16.9428596496582</v>
       </c>
       <c r="H1337" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1338" t="n">
-        <v>17.2440662384033</v>
+        <v>17.244068145752</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35183,7 +35183,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G1339" t="n">
-        <v>17.6205749511719</v>
+        <v>17.6205730438232</v>
       </c>
       <c r="H1339" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1341" t="n">
-        <v>16.6793022155762</v>
+        <v>16.6793041229248</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G1345" t="n">
-        <v>14.3355417251587</v>
+        <v>14.335542678833</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G1346" t="n">
-        <v>14.392017364502</v>
+        <v>14.3920183181763</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35469,7 +35469,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G1350" t="n">
-        <v>12.9989385604858</v>
+        <v>12.9989395141602</v>
       </c>
       <c r="H1350" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G1353" t="n">
-        <v>13.1213035583496</v>
+        <v>13.1213045120239</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G1357" t="n">
-        <v>13.7801933288574</v>
+        <v>13.7801923751831</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G1358" t="n">
-        <v>13.3377962112427</v>
+        <v>13.337797164917</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35755,7 +35755,7 @@
         <v>14.0699996948242</v>
       </c>
       <c r="G1361" t="n">
-        <v>13.2436676025391</v>
+        <v>13.2436685562134</v>
       </c>
       <c r="H1361" t="s">
         <v>8</v>
@@ -35781,7 +35781,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G1362" t="n">
-        <v>13.4413366317749</v>
+        <v>13.4413347244263</v>
       </c>
       <c r="H1362" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G1368" t="n">
-        <v>13.526050567627</v>
+        <v>13.5260496139526</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G1371" t="n">
-        <v>15.1356220245361</v>
+        <v>15.1356229782104</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36093,7 +36093,7 @@
         <v>15.3900003433228</v>
       </c>
       <c r="G1374" t="n">
-        <v>14.4861469268799</v>
+        <v>14.4861459732056</v>
       </c>
       <c r="H1374" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G1376" t="n">
-        <v>14.1567001342773</v>
+        <v>14.1567010879517</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36171,7 +36171,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1377" t="n">
-        <v>14.2131767272949</v>
+        <v>14.2131776809692</v>
       </c>
       <c r="H1377" t="s">
         <v>8</v>
@@ -36197,7 +36197,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1378" t="n">
-        <v>14.4484958648682</v>
+        <v>14.4484949111938</v>
       </c>
       <c r="H1378" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1380" t="n">
-        <v>15.3897657394409</v>
+        <v>15.3897666931152</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1381" t="n">
-        <v>15.3427000045776</v>
+        <v>15.342700958252</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1382" t="n">
-        <v>16.331033706665</v>
+        <v>16.3310356140137</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36379,7 +36379,7 @@
         <v>18</v>
       </c>
       <c r="G1385" t="n">
-        <v>16.9428615570068</v>
+        <v>16.9428596496582</v>
       </c>
       <c r="H1385" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1390" t="n">
-        <v>15.8133354187012</v>
+        <v>15.8133373260498</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G1394" t="n">
-        <v>16.971097946167</v>
+        <v>16.9710998535156</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36691,7 +36691,7 @@
         <v>18.1800003051758</v>
       </c>
       <c r="G1397" t="n">
-        <v>17.1122875213623</v>
+        <v>17.1122894287109</v>
       </c>
       <c r="H1397" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>18.3899993896484</v>
       </c>
       <c r="G1400" t="n">
-        <v>17.3099536895752</v>
+        <v>17.3099555969238</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36795,7 +36795,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1401" t="n">
-        <v>16.8110847473145</v>
+        <v>16.8110828399658</v>
       </c>
       <c r="H1401" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G1402" t="n">
-        <v>16.924036026001</v>
+        <v>16.9240341186523</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G1404" t="n">
-        <v>16.9052066802979</v>
+        <v>16.9052104949951</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36925,7 +36925,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1406" t="n">
-        <v>17.3664321899414</v>
+        <v>17.36643409729</v>
       </c>
       <c r="H1406" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1408" t="n">
-        <v>16.5475273132324</v>
+        <v>16.5475292205811</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37133,7 +37133,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1414" t="n">
-        <v>16.2651443481445</v>
+        <v>16.2651462554932</v>
       </c>
       <c r="H1414" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1415" t="n">
-        <v>16.3969230651855</v>
+        <v>16.3969249725342</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1416" t="n">
-        <v>16.6134147644043</v>
+        <v>16.6134166717529</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37211,7 +37211,7 @@
         <v>18</v>
       </c>
       <c r="G1417" t="n">
-        <v>16.9428615570068</v>
+        <v>16.9428596496582</v>
       </c>
       <c r="H1417" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1419" t="n">
-        <v>16.9805107116699</v>
+        <v>16.9805145263672</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1420" t="n">
-        <v>17.4511470794678</v>
+        <v>17.4511451721191</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1427" t="n">
-        <v>18.4488925933838</v>
+        <v>18.4488906860352</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>20.6200008392334</v>
       </c>
       <c r="G1431" t="n">
-        <v>19.4089870452881</v>
+        <v>19.4089908599854</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G1433" t="n">
-        <v>20.2749557495117</v>
+        <v>20.2749576568604</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1434" t="n">
-        <v>20.3314323425293</v>
+        <v>20.3314342498779</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>21.3199996948242</v>
       </c>
       <c r="G1435" t="n">
-        <v>20.0678768157959</v>
+        <v>20.0678749084473</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>21.5</v>
       </c>
       <c r="G1436" t="n">
-        <v>20.2373065948486</v>
+        <v>20.2373046875</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37731,7 +37731,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1437" t="n">
-        <v>20.1431789398193</v>
+        <v>20.1431770324707</v>
       </c>
       <c r="H1437" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>21.1399993896484</v>
       </c>
       <c r="G1439" t="n">
-        <v>19.8984451293945</v>
+        <v>19.8984470367432</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>20.3314323425293</v>
+        <v>20.3314342498779</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37887,7 +37887,7 @@
         <v>21.9599990844727</v>
       </c>
       <c r="G1443" t="n">
-        <v>20.6702880859375</v>
+        <v>20.6702899932861</v>
       </c>
       <c r="H1443" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G1447" t="n">
-        <v>20.4067325592041</v>
+        <v>20.4067344665527</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1448" t="n">
-        <v>20.3314323425293</v>
+        <v>20.3314342498779</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G1449" t="n">
-        <v>20.1055278778076</v>
+        <v>20.1055297851562</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38121,7 +38121,7 @@
         <v>20.8199996948242</v>
       </c>
       <c r="G1452" t="n">
-        <v>19.5972423553467</v>
+        <v>19.597240447998</v>
       </c>
       <c r="H1452" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>20.6399993896484</v>
       </c>
       <c r="G1454" t="n">
-        <v>19.4278106689453</v>
+        <v>19.4278125762939</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38199,7 +38199,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1455" t="n">
-        <v>18.9195289611816</v>
+        <v>18.919527053833</v>
       </c>
       <c r="H1455" t="s">
         <v>8</v>
@@ -38225,7 +38225,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G1456" t="n">
-        <v>19.2772083282471</v>
+        <v>19.2772102355957</v>
       </c>
       <c r="H1456" t="s">
         <v>8</v>
@@ -38251,7 +38251,7 @@
         <v>20</v>
       </c>
       <c r="G1457" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1457" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1460" t="n">
-        <v>19.0136547088623</v>
+        <v>19.0136566162109</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G1462" t="n">
-        <v>19.7101936340332</v>
+        <v>19.7101955413818</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38459,7 +38459,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G1465" t="n">
-        <v>19.4466400146484</v>
+        <v>19.4466381072998</v>
       </c>
       <c r="H1465" t="s">
         <v>8</v>
@@ -38485,7 +38485,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1466" t="n">
-        <v>18.9195289611816</v>
+        <v>18.919527053833</v>
       </c>
       <c r="H1466" t="s">
         <v>8</v>
@@ -38511,7 +38511,7 @@
         <v>19.5699996948242</v>
       </c>
       <c r="G1467" t="n">
-        <v>18.420654296875</v>
+        <v>18.4206523895264</v>
       </c>
       <c r="H1467" t="s">
         <v>8</v>
@@ -38589,7 +38589,7 @@
         <v>20</v>
       </c>
       <c r="G1470" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1470" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>19.7099990844727</v>
       </c>
       <c r="G1471" t="n">
-        <v>18.5524311065674</v>
+        <v>18.5524291992188</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38719,7 +38719,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1475" t="n">
-        <v>18.9195289611816</v>
+        <v>18.919527053833</v>
       </c>
       <c r="H1475" t="s">
         <v>8</v>
@@ -38771,7 +38771,7 @@
         <v>20</v>
       </c>
       <c r="G1477" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1477" t="s">
         <v>8</v>
@@ -38797,7 +38797,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1478" t="n">
-        <v>18.7312717437744</v>
+        <v>18.731273651123</v>
       </c>
       <c r="H1478" t="s">
         <v>8</v>
@@ -38823,7 +38823,7 @@
         <v>19.5</v>
       </c>
       <c r="G1479" t="n">
-        <v>18.3547630310059</v>
+        <v>18.3547649383545</v>
       </c>
       <c r="H1479" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1480" t="n">
-        <v>18.4488925933838</v>
+        <v>18.4488906860352</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G1481" t="n">
-        <v>18.6183223724365</v>
+        <v>18.6183204650879</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1483" t="n">
-        <v>18.8724613189697</v>
+        <v>18.8724632263184</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38953,7 +38953,7 @@
         <v>20</v>
       </c>
       <c r="G1484" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1484" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G1485" t="n">
-        <v>18.787748336792</v>
+        <v>18.7877464294434</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39005,7 +39005,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1486" t="n">
-        <v>18.9195289611816</v>
+        <v>18.919527053833</v>
       </c>
       <c r="H1486" t="s">
         <v>8</v>
@@ -39031,7 +39031,7 @@
         <v>20</v>
       </c>
       <c r="G1487" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1487" t="s">
         <v>8</v>
@@ -39057,7 +39057,7 @@
         <v>20</v>
       </c>
       <c r="G1488" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1488" t="s">
         <v>8</v>
@@ -39083,7 +39083,7 @@
         <v>20</v>
       </c>
       <c r="G1489" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1489" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1490" t="n">
-        <v>19.2019062042236</v>
+        <v>19.2019081115723</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39187,7 +39187,7 @@
         <v>20</v>
       </c>
       <c r="G1493" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1493" t="s">
         <v>8</v>
@@ -39213,7 +39213,7 @@
         <v>20</v>
       </c>
       <c r="G1494" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1494" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1495" t="n">
-        <v>18.4488925933838</v>
+        <v>18.4488906860352</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G1496" t="n">
-        <v>18.787748336792</v>
+        <v>18.7877464294434</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39317,7 +39317,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1498" t="n">
-        <v>18.7312717437744</v>
+        <v>18.731273651123</v>
       </c>
       <c r="H1498" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G1500" t="n">
-        <v>18.6183223724365</v>
+        <v>18.6183204650879</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39447,7 +39447,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G1503" t="n">
-        <v>18.5241947174072</v>
+        <v>18.5241928100586</v>
       </c>
       <c r="H1503" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G1506" t="n">
-        <v>18.8805961608887</v>
+        <v>18.8805980682373</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39603,7 +39603,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1509" t="n">
-        <v>18.3455200195312</v>
+        <v>18.3455181121826</v>
       </c>
       <c r="H1509" t="s">
         <v>8</v>
@@ -39733,7 +39733,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1514" t="n">
-        <v>18.3455200195312</v>
+        <v>18.3455181121826</v>
       </c>
       <c r="H1514" t="s">
         <v>8</v>
@@ -39759,7 +39759,7 @@
         <v>19.5</v>
       </c>
       <c r="G1515" t="n">
-        <v>18.6321659088135</v>
+        <v>18.6321678161621</v>
       </c>
       <c r="H1515" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G1516" t="n">
-        <v>18.61305809021</v>
+        <v>18.6130561828613</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G1517" t="n">
-        <v>17.8295516967773</v>
+        <v>17.8295497894287</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G1519" t="n">
-        <v>18.8805961608887</v>
+        <v>18.8805980682373</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1521" t="n">
-        <v>18.5366191864014</v>
+        <v>18.5366172790527</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39941,7 +39941,7 @@
         <v>19.7399997711182</v>
       </c>
       <c r="G1522" t="n">
-        <v>18.8614845275879</v>
+        <v>18.8614864349365</v>
       </c>
       <c r="H1522" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>20</v>
       </c>
       <c r="G1523" t="n">
-        <v>19.1099166870117</v>
+        <v>19.1099147796631</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1524" t="n">
-        <v>19.3010139465332</v>
+        <v>19.3010158538818</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>20</v>
       </c>
       <c r="G1527" t="n">
-        <v>19.1099166870117</v>
+        <v>19.1099147796631</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40123,7 +40123,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1529" t="n">
-        <v>19.4921131134033</v>
+        <v>19.492115020752</v>
       </c>
       <c r="H1529" t="s">
         <v>8</v>
@@ -40201,7 +40201,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1532" t="n">
-        <v>20.4476108551025</v>
+        <v>20.4476089477539</v>
       </c>
       <c r="H1532" t="s">
         <v>8</v>
@@ -40227,7 +40227,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1533" t="n">
-        <v>20.4476108551025</v>
+        <v>20.4476089477539</v>
       </c>
       <c r="H1533" t="s">
         <v>8</v>
@@ -40253,7 +40253,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1534" t="n">
-        <v>20.590934753418</v>
+        <v>20.5909328460693</v>
       </c>
       <c r="H1534" t="s">
         <v>8</v>
@@ -40591,7 +40591,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1547" t="n">
-        <v>19.0143642425537</v>
+        <v>19.0143661499023</v>
       </c>
       <c r="H1547" t="s">
         <v>8</v>
@@ -40643,7 +40643,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1549" t="n">
-        <v>19.0143642425537</v>
+        <v>19.0143661499023</v>
       </c>
       <c r="H1549" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>20</v>
       </c>
       <c r="G1551" t="n">
-        <v>19.1099166870117</v>
+        <v>19.1099147796631</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40747,7 +40747,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1553" t="n">
-        <v>18.9761486053467</v>
+        <v>18.976146697998</v>
       </c>
       <c r="H1553" t="s">
         <v>8</v>
@@ -40799,7 +40799,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1555" t="n">
-        <v>19.0143642425537</v>
+        <v>19.0143661499023</v>
       </c>
       <c r="H1555" t="s">
         <v>8</v>
@@ -40825,7 +40825,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1556" t="n">
-        <v>19.0143642425537</v>
+        <v>19.0143661499023</v>
       </c>
       <c r="H1556" t="s">
         <v>8</v>
@@ -40877,7 +40877,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1558" t="n">
-        <v>19.0143642425537</v>
+        <v>19.0143661499023</v>
       </c>
       <c r="H1558" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1560" t="n">
-        <v>17.9633197784424</v>
+        <v>17.963321685791</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G1563" t="n">
-        <v>18.4219570159912</v>
+        <v>18.4219608306885</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G1564" t="n">
-        <v>18.4983978271484</v>
+        <v>18.4983997344971</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41137,7 +41137,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1568" t="n">
-        <v>16.6638450622559</v>
+        <v>16.6638469696045</v>
       </c>
       <c r="H1568" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1569" t="n">
-        <v>15.8038997650146</v>
+        <v>15.803900718689</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41267,7 +41267,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1573" t="n">
-        <v>16.4345264434814</v>
+        <v>16.4345283508301</v>
       </c>
       <c r="H1573" t="s">
         <v>8</v>
@@ -41293,7 +41293,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1574" t="n">
-        <v>16.4345264434814</v>
+        <v>16.4345283508301</v>
       </c>
       <c r="H1574" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G1575" t="n">
-        <v>16.377197265625</v>
+        <v>16.3771953582764</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41371,7 +41371,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G1577" t="n">
-        <v>16.3580894470215</v>
+        <v>16.3580875396729</v>
       </c>
       <c r="H1577" t="s">
         <v>8</v>
@@ -41449,7 +41449,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1580" t="n">
-        <v>16.4918575286865</v>
+        <v>16.4918556213379</v>
       </c>
       <c r="H1580" t="s">
         <v>8</v>
@@ -41501,7 +41501,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1582" t="n">
-        <v>16.4154186248779</v>
+        <v>16.4154167175293</v>
       </c>
       <c r="H1582" t="s">
         <v>8</v>
@@ -41527,7 +41527,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G1583" t="n">
-        <v>16.3580894470215</v>
+        <v>16.3580875396729</v>
       </c>
       <c r="H1583" t="s">
         <v>8</v>
@@ -41553,7 +41553,7 @@
         <v>17.2399997711182</v>
       </c>
       <c r="G1584" t="n">
-        <v>16.4727478027344</v>
+        <v>16.4727458953857</v>
       </c>
       <c r="H1584" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1586" t="n">
-        <v>16.51096534729</v>
+        <v>16.5109691619873</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41735,7 +41735,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1591" t="n">
-        <v>16.4154186248779</v>
+        <v>16.4154167175293</v>
       </c>
       <c r="H1591" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1592" t="n">
-        <v>16.3007583618164</v>
+        <v>16.3007564544678</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1602" t="n">
-        <v>14.9057340621948</v>
+        <v>14.9057350158691</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42125,7 +42125,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G1606" t="n">
-        <v>14.1795568466187</v>
+        <v>14.179557800293</v>
       </c>
       <c r="H1606" t="s">
         <v>8</v>
@@ -42307,7 +42307,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1613" t="n">
-        <v>13.4342708587646</v>
+        <v>13.434271812439</v>
       </c>
       <c r="H1613" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1614" t="n">
-        <v>12.994743347168</v>
+        <v>12.9947423934937</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42359,7 +42359,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1615" t="n">
-        <v>13.4342708587646</v>
+        <v>13.434271812439</v>
       </c>
       <c r="H1615" t="s">
         <v>8</v>
@@ -42437,7 +42437,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1618" t="n">
-        <v>13.2813911437988</v>
+        <v>13.2813901901245</v>
       </c>
       <c r="H1618" t="s">
         <v>8</v>
@@ -42489,7 +42489,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G1620" t="n">
-        <v>13.9311275482178</v>
+        <v>13.9311285018921</v>
       </c>
       <c r="H1620" t="s">
         <v>8</v>
@@ -42541,7 +42541,7 @@
         <v>14.5</v>
       </c>
       <c r="G1622" t="n">
-        <v>13.8546895980835</v>
+        <v>13.8546886444092</v>
       </c>
       <c r="H1622" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G1623" t="n">
-        <v>13.740029335022</v>
+        <v>13.7400283813477</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42619,7 +42619,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G1625" t="n">
-        <v>13.9311275482178</v>
+        <v>13.9311285018921</v>
       </c>
       <c r="H1625" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1626" t="n">
-        <v>13.8737983703613</v>
+        <v>13.8737993240356</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G1627" t="n">
-        <v>13.8355779647827</v>
+        <v>13.835578918457</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1628" t="n">
-        <v>13.8737983703613</v>
+        <v>13.8737993240356</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G1629" t="n">
-        <v>13.8355779647827</v>
+        <v>13.835578918457</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G1630" t="n">
-        <v>14.1222267150879</v>
+        <v>14.1222276687622</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G1632" t="n">
-        <v>14.6955251693726</v>
+        <v>14.6955242156982</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42853,7 +42853,7 @@
         <v>15.7799997329712</v>
       </c>
       <c r="G1634" t="n">
-        <v>15.0777225494385</v>
+        <v>15.0777235031128</v>
       </c>
       <c r="H1634" t="s">
         <v>8</v>
@@ -42905,7 +42905,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G1636" t="n">
-        <v>15.6510210037231</v>
+        <v>15.6510190963745</v>
       </c>
       <c r="H1636" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1638" t="n">
-        <v>16.0714378356934</v>
+        <v>16.071439743042</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G1641" t="n">
-        <v>17.122486114502</v>
+        <v>17.1224842071533</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>17.5</v>
       </c>
       <c r="G1642" t="n">
-        <v>16.7211742401123</v>
+        <v>16.7211761474609</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1643" t="n">
-        <v>17.0078239440918</v>
+        <v>17.0078258514404</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1644" t="n">
-        <v>17.0460453033447</v>
+        <v>17.0460433959961</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43191,7 +43191,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1647" t="n">
-        <v>16.4154186248779</v>
+        <v>16.4154167175293</v>
       </c>
       <c r="H1647" t="s">
         <v>8</v>
@@ -43269,7 +43269,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1650" t="n">
-        <v>16.6638450622559</v>
+        <v>16.6638469696045</v>
       </c>
       <c r="H1650" t="s">
         <v>8</v>
@@ -43295,7 +43295,7 @@
         <v>18</v>
       </c>
       <c r="G1651" t="n">
-        <v>17.1989250183105</v>
+        <v>17.1989231109619</v>
       </c>
       <c r="H1651" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G1653" t="n">
-        <v>17.0269336700439</v>
+        <v>17.0269355773926</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43373,7 +43373,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1654" t="n">
-        <v>16.7020664215088</v>
+        <v>16.7020645141602</v>
       </c>
       <c r="H1654" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1657" t="n">
-        <v>17.1033725738525</v>
+        <v>17.1033744812012</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1658" t="n">
-        <v>17.2562522888184</v>
+        <v>17.256254196167</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43503,7 +43503,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G1659" t="n">
-        <v>17.2180328369141</v>
+        <v>17.2180347442627</v>
       </c>
       <c r="H1659" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1661" t="n">
-        <v>17.1033725738525</v>
+        <v>17.1033744812012</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G1662" t="n">
-        <v>18.3264102935791</v>
+        <v>18.3264083862305</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43607,7 +43607,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1663" t="n">
-        <v>18.5939483642578</v>
+        <v>18.5939464569092</v>
       </c>
       <c r="H1663" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G1664" t="n">
-        <v>18.1353073120117</v>
+        <v>18.1353092193604</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43659,7 +43659,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1665" t="n">
-        <v>18.3455200195312</v>
+        <v>18.3455181121826</v>
       </c>
       <c r="H1665" t="s">
         <v>8</v>
@@ -43685,7 +43685,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1666" t="n">
-        <v>18.3455200195312</v>
+        <v>18.3455181121826</v>
       </c>
       <c r="H1666" t="s">
         <v>8</v>
@@ -43711,7 +43711,7 @@
         <v>19.5</v>
       </c>
       <c r="G1667" t="n">
-        <v>18.6321659088135</v>
+        <v>18.6321678161621</v>
       </c>
       <c r="H1667" t="s">
         <v>8</v>
@@ -43737,7 +43737,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1668" t="n">
-        <v>18.5939483642578</v>
+        <v>18.5939464569092</v>
       </c>
       <c r="H1668" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G1669" t="n">
-        <v>18.8805961608887</v>
+        <v>18.8805980682373</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43815,7 +43815,7 @@
         <v>19.5</v>
       </c>
       <c r="G1671" t="n">
-        <v>18.6321659088135</v>
+        <v>18.6321678161621</v>
       </c>
       <c r="H1671" t="s">
         <v>8</v>
@@ -43971,7 +43971,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G1677" t="n">
-        <v>18.0970897674561</v>
+        <v>18.0970916748047</v>
       </c>
       <c r="H1677" t="s">
         <v>8</v>
@@ -44101,7 +44101,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1682" t="n">
-        <v>17.3518047332764</v>
+        <v>17.3518028259277</v>
       </c>
       <c r="H1682" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G1686" t="n">
-        <v>17.0269336700439</v>
+        <v>17.0269355773926</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44231,7 +44231,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1687" t="n">
-        <v>17.0651569366455</v>
+        <v>17.0651550292969</v>
       </c>
       <c r="H1687" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1688" t="n">
-        <v>17.3326930999756</v>
+        <v>17.332691192627</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1689" t="n">
-        <v>17.9824295043945</v>
+        <v>17.9824314117432</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1694" t="n">
-        <v>17.8677711486816</v>
+        <v>17.867769241333</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G1698" t="n">
-        <v>17.4091339111328</v>
+        <v>17.4091300964355</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44569,7 +44569,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1700" t="n">
-        <v>17.390022277832</v>
+        <v>17.3900241851807</v>
       </c>
       <c r="H1700" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G1702" t="n">
-        <v>17.4091339111328</v>
+        <v>17.4091300964355</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44725,7 +44725,7 @@
         <v>19.5</v>
       </c>
       <c r="G1706" t="n">
-        <v>18.6321659088135</v>
+        <v>18.6321678161621</v>
       </c>
       <c r="H1706" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1707" t="n">
-        <v>17.9633197784424</v>
+        <v>17.963321685791</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G1710" t="n">
-        <v>18.3646259307861</v>
+        <v>18.3646278381348</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G1712" t="n">
-        <v>18.3646259307861</v>
+        <v>18.3646278381348</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1715" t="n">
-        <v>17.791332244873</v>
+        <v>17.7913303375244</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1717" t="n">
-        <v>17.2944736480713</v>
+        <v>17.2944717407227</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1720" t="n">
-        <v>17.791332244873</v>
+        <v>17.7913303375244</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1724" t="n">
-        <v>17.1033725738525</v>
+        <v>17.1033744812012</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1726" t="n">
-        <v>17.0078239440918</v>
+        <v>17.0078258514404</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1728" t="n">
-        <v>16.5682964324951</v>
+        <v>16.5682983398438</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1729" t="n">
-        <v>16.8167266845703</v>
+        <v>16.8167247772217</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1730" t="n">
-        <v>16.8358364105225</v>
+        <v>16.8358345031738</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1732" t="n">
-        <v>17.1033725738525</v>
+        <v>17.1033744812012</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45427,7 +45427,7 @@
         <v>18</v>
       </c>
       <c r="G1733" t="n">
-        <v>17.1989250183105</v>
+        <v>17.1989231109619</v>
       </c>
       <c r="H1733" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1734" t="n">
-        <v>17.2562522888184</v>
+        <v>17.256254196167</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>17.5</v>
       </c>
       <c r="G1735" t="n">
-        <v>16.7211742401123</v>
+        <v>16.7211761474609</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45583,7 +45583,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1739" t="n">
-        <v>16.4918575286865</v>
+        <v>16.4918556213379</v>
       </c>
       <c r="H1739" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1741" t="n">
-        <v>15.7847909927368</v>
+        <v>15.7847900390625</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G1742" t="n">
-        <v>15.9758892059326</v>
+        <v>15.9758882522583</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45713,7 +45713,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G1744" t="n">
-        <v>15.6510210037231</v>
+        <v>15.6510190963745</v>
       </c>
       <c r="H1744" t="s">
         <v>8</v>
@@ -45739,7 +45739,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G1745" t="n">
-        <v>15.4599208831787</v>
+        <v>15.459921836853</v>
       </c>
       <c r="H1745" t="s">
         <v>8</v>
@@ -45947,7 +45947,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G1753" t="n">
-        <v>15.5554723739624</v>
+        <v>15.5554714202881</v>
       </c>
       <c r="H1753" t="s">
         <v>8</v>
@@ -45973,7 +45973,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G1754" t="n">
-        <v>15.5936918258667</v>
+        <v>15.5936908721924</v>
       </c>
       <c r="H1754" t="s">
         <v>8</v>
@@ -46025,7 +46025,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1756" t="n">
-        <v>15.631911277771</v>
+        <v>15.6319122314453</v>
       </c>
       <c r="H1756" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1757" t="n">
-        <v>15.8803405761719</v>
+        <v>15.8803396224976</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1758" t="n">
-        <v>15.7847909927368</v>
+        <v>15.7847900390625</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46155,7 +46155,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1761" t="n">
-        <v>15.9185609817505</v>
+        <v>15.9185590744019</v>
       </c>
       <c r="H1761" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1762" t="n">
-        <v>15.8803405761719</v>
+        <v>15.8803396224976</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46207,7 +46207,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1763" t="n">
-        <v>15.9185609817505</v>
+        <v>15.9185590744019</v>
       </c>
       <c r="H1763" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1765" t="n">
-        <v>16.6447353363037</v>
+        <v>16.6447372436523</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1767" t="n">
-        <v>16.8167266845703</v>
+        <v>16.8167247772217</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -46441,7 +46441,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1772" t="n">
-        <v>16.7389583587646</v>
+        <v>16.7389602661133</v>
       </c>
       <c r="H1772" t="s">
         <v>8</v>
@@ -46493,7 +46493,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1774" t="n">
-        <v>17.361083984375</v>
+        <v>17.3610820770264</v>
       </c>
       <c r="H1774" t="s">
         <v>8</v>
@@ -46519,7 +46519,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G1775" t="n">
-        <v>17.1472282409668</v>
+        <v>17.1472263336182</v>
       </c>
       <c r="H1775" t="s">
         <v>8</v>
@@ -46571,7 +46571,7 @@
         <v>18</v>
       </c>
       <c r="G1777" t="n">
-        <v>17.4971714019775</v>
+        <v>17.4971694946289</v>
       </c>
       <c r="H1777" t="s">
         <v>8</v>
@@ -46597,7 +46597,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G1778" t="n">
-        <v>17.7110252380371</v>
+        <v>17.7110233306885</v>
       </c>
       <c r="H1778" t="s">
         <v>8</v>
@@ -46805,7 +46805,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G1786" t="n">
-        <v>17.4388465881348</v>
+        <v>17.4388484954834</v>
       </c>
       <c r="H1786" t="s">
         <v>8</v>
@@ -46831,7 +46831,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1787" t="n">
-        <v>16.9528141021729</v>
+        <v>16.9528160095215</v>
       </c>
       <c r="H1787" t="s">
         <v>8</v>
@@ -46857,7 +46857,7 @@
         <v>18</v>
       </c>
       <c r="G1788" t="n">
-        <v>17.4971714019775</v>
+        <v>17.4971694946289</v>
       </c>
       <c r="H1788" t="s">
         <v>8</v>
@@ -46961,7 +46961,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G1792" t="n">
-        <v>19.3829784393311</v>
+        <v>19.3829765319824</v>
       </c>
       <c r="H1792" t="s">
         <v>8</v>
@@ -47013,7 +47013,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1794" t="n">
-        <v>20.559175491333</v>
+        <v>20.5591735839844</v>
       </c>
       <c r="H1794" t="s">
         <v>8</v>
@@ -47065,7 +47065,7 @@
         <v>22.25</v>
       </c>
       <c r="G1796" t="n">
-        <v>21.6284465789795</v>
+        <v>21.6284484863281</v>
       </c>
       <c r="H1796" t="s">
         <v>8</v>
@@ -47195,7 +47195,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1801" t="n">
-        <v>22.0658760070801</v>
+        <v>22.0658779144287</v>
       </c>
       <c r="H1801" t="s">
         <v>8</v>
@@ -47273,7 +47273,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1804" t="n">
-        <v>22.260290145874</v>
+        <v>22.2602882385254</v>
       </c>
       <c r="H1804" t="s">
         <v>8</v>
@@ -47299,7 +47299,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1805" t="n">
-        <v>22.2116851806641</v>
+        <v>22.2116870880127</v>
       </c>
       <c r="H1805" t="s">
         <v>8</v>
@@ -47325,7 +47325,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1806" t="n">
-        <v>22.4547023773193</v>
+        <v>22.454704284668</v>
       </c>
       <c r="H1806" t="s">
         <v>8</v>
@@ -47377,7 +47377,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1808" t="n">
-        <v>22.0658760070801</v>
+        <v>22.0658779144287</v>
       </c>
       <c r="H1808" t="s">
         <v>8</v>
@@ -47585,7 +47585,7 @@
         <v>22.5</v>
       </c>
       <c r="G1816" t="n">
-        <v>21.8714637756348</v>
+        <v>21.8714618682861</v>
       </c>
       <c r="H1816" t="s">
         <v>8</v>
@@ -47689,7 +47689,7 @@
         <v>22.5</v>
       </c>
       <c r="G1820" t="n">
-        <v>21.8714637756348</v>
+        <v>21.8714618682861</v>
       </c>
       <c r="H1820" t="s">
         <v>8</v>
@@ -47741,7 +47741,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1822" t="n">
-        <v>20.559175491333</v>
+        <v>20.5591735839844</v>
       </c>
       <c r="H1822" t="s">
         <v>8</v>
@@ -47949,7 +47949,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1830" t="n">
-        <v>19.8301258087158</v>
+        <v>19.8301277160645</v>
       </c>
       <c r="H1830" t="s">
         <v>8</v>
@@ -47975,7 +47975,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1831" t="n">
-        <v>19.8301258087158</v>
+        <v>19.8301277160645</v>
       </c>
       <c r="H1831" t="s">
         <v>8</v>
@@ -48001,7 +48001,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1832" t="n">
-        <v>19.8301258087158</v>
+        <v>19.8301277160645</v>
       </c>
       <c r="H1832" t="s">
         <v>8</v>
@@ -48235,7 +48235,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G1841" t="n">
-        <v>20.4619693756104</v>
+        <v>20.4619674682617</v>
       </c>
       <c r="H1841" t="s">
         <v>8</v>
@@ -48313,7 +48313,7 @@
         <v>21.25</v>
       </c>
       <c r="G1844" t="n">
-        <v>20.6563816070557</v>
+        <v>20.6563835144043</v>
       </c>
       <c r="H1844" t="s">
         <v>8</v>
@@ -48469,7 +48469,7 @@
         <v>22.5</v>
       </c>
       <c r="G1850" t="n">
-        <v>21.8714637756348</v>
+        <v>21.8714618682861</v>
       </c>
       <c r="H1850" t="s">
         <v>8</v>
@@ -48495,7 +48495,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1851" t="n">
-        <v>22.0658760070801</v>
+        <v>22.0658779144287</v>
       </c>
       <c r="H1851" t="s">
         <v>8</v>
@@ -48651,7 +48651,7 @@
         <v>22.5</v>
       </c>
       <c r="G1857" t="n">
-        <v>21.8714637756348</v>
+        <v>21.8714618682861</v>
       </c>
       <c r="H1857" t="s">
         <v>8</v>
@@ -48677,7 +48677,7 @@
         <v>21.75</v>
       </c>
       <c r="G1858" t="n">
-        <v>21.1424140930176</v>
+        <v>21.1424160003662</v>
       </c>
       <c r="H1858" t="s">
         <v>8</v>
@@ -48703,7 +48703,7 @@
         <v>21.75</v>
       </c>
       <c r="G1859" t="n">
-        <v>21.1424140930176</v>
+        <v>21.1424160003662</v>
       </c>
       <c r="H1859" t="s">
         <v>8</v>
@@ -48885,7 +48885,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1866" t="n">
-        <v>22.0658760070801</v>
+        <v>22.0658779144287</v>
       </c>
       <c r="H1866" t="s">
         <v>8</v>
@@ -48989,7 +48989,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1870" t="n">
-        <v>22.0658760070801</v>
+        <v>22.0658779144287</v>
       </c>
       <c r="H1870" t="s">
         <v>8</v>
@@ -49015,7 +49015,7 @@
         <v>22.5</v>
       </c>
       <c r="G1871" t="n">
-        <v>21.8714637756348</v>
+        <v>21.8714618682861</v>
       </c>
       <c r="H1871" t="s">
         <v>8</v>
@@ -49093,7 +49093,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1874" t="n">
-        <v>22.0658760070801</v>
+        <v>22.0658779144287</v>
       </c>
       <c r="H1874" t="s">
         <v>8</v>
@@ -49119,7 +49119,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1875" t="n">
-        <v>22.2116851806641</v>
+        <v>22.2116870880127</v>
       </c>
       <c r="H1875" t="s">
         <v>8</v>
@@ -49145,7 +49145,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1876" t="n">
-        <v>21.9686698913574</v>
+        <v>21.9686717987061</v>
       </c>
       <c r="H1876" t="s">
         <v>8</v>
@@ -49353,7 +49353,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1884" t="n">
-        <v>20.9480018615723</v>
+        <v>20.9479999542236</v>
       </c>
       <c r="H1884" t="s">
         <v>8</v>
@@ -49431,7 +49431,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1887" t="n">
-        <v>19.8301258087158</v>
+        <v>19.8301277160645</v>
       </c>
       <c r="H1887" t="s">
         <v>8</v>
@@ -49457,7 +49457,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1888" t="n">
-        <v>19.8301258087158</v>
+        <v>19.8301277160645</v>
       </c>
       <c r="H1888" t="s">
         <v>8</v>
@@ -49587,7 +49587,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1893" t="n">
-        <v>19.8301258087158</v>
+        <v>19.8301277160645</v>
       </c>
       <c r="H1893" t="s">
         <v>8</v>
@@ -49795,7 +49795,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1901" t="n">
-        <v>18.9163856506348</v>
+        <v>18.9163837432861</v>
       </c>
       <c r="H1901" t="s">
         <v>8</v>
@@ -49821,7 +49821,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1902" t="n">
-        <v>19.3052139282227</v>
+        <v>19.305212020874</v>
       </c>
       <c r="H1902" t="s">
         <v>8</v>
@@ -49925,7 +49925,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1906" t="n">
-        <v>20.559175491333</v>
+        <v>20.5591735839844</v>
       </c>
       <c r="H1906" t="s">
         <v>8</v>
@@ -49951,7 +49951,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G1907" t="n">
-        <v>20.4619693756104</v>
+        <v>20.4619674682617</v>
       </c>
       <c r="H1907" t="s">
         <v>8</v>
@@ -49977,7 +49977,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G1908" t="n">
-        <v>20.4619693756104</v>
+        <v>20.4619674682617</v>
       </c>
       <c r="H1908" t="s">
         <v>8</v>
@@ -50055,7 +50055,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1911" t="n">
-        <v>20.2675552368164</v>
+        <v>20.267557144165</v>
       </c>
       <c r="H1911" t="s">
         <v>8</v>
@@ -50133,7 +50133,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1914" t="n">
-        <v>19.8301258087158</v>
+        <v>19.8301277160645</v>
       </c>
       <c r="H1914" t="s">
         <v>8</v>
@@ -50263,7 +50263,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G1919" t="n">
-        <v>19.0913581848145</v>
+        <v>19.0913562774658</v>
       </c>
       <c r="H1919" t="s">
         <v>8</v>
@@ -50289,7 +50289,7 @@
         <v>19</v>
       </c>
       <c r="G1920" t="n">
-        <v>18.4692344665527</v>
+        <v>18.4692363739014</v>
       </c>
       <c r="H1920" t="s">
         <v>8</v>
@@ -50419,7 +50419,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1925" t="n">
-        <v>19.3052139282227</v>
+        <v>19.305212020874</v>
       </c>
       <c r="H1925" t="s">
         <v>8</v>
@@ -50497,7 +50497,7 @@
         <v>19.5</v>
       </c>
       <c r="G1928" t="n">
-        <v>18.9552669525146</v>
+        <v>18.9552688598633</v>
       </c>
       <c r="H1928" t="s">
         <v>8</v>
@@ -50575,7 +50575,7 @@
         <v>19</v>
       </c>
       <c r="G1931" t="n">
-        <v>18.4692344665527</v>
+        <v>18.4692363739014</v>
       </c>
       <c r="H1931" t="s">
         <v>8</v>
@@ -50653,7 +50653,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1934" t="n">
-        <v>18.0220851898193</v>
+        <v>18.022087097168</v>
       </c>
       <c r="H1934" t="s">
         <v>8</v>
@@ -50705,7 +50705,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1936" t="n">
-        <v>18.3720302581787</v>
+        <v>18.3720283508301</v>
       </c>
       <c r="H1936" t="s">
         <v>8</v>
@@ -50913,7 +50913,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G1944" t="n">
-        <v>17.8665561676025</v>
+        <v>17.8665542602539</v>
       </c>
       <c r="H1944" t="s">
         <v>8</v>
@@ -51017,7 +51017,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G1948" t="n">
-        <v>17.7110252380371</v>
+        <v>17.7110233306885</v>
       </c>
       <c r="H1948" t="s">
         <v>8</v>
@@ -51069,7 +51069,7 @@
         <v>18</v>
       </c>
       <c r="G1950" t="n">
-        <v>17.4971714019775</v>
+        <v>17.4971694946289</v>
       </c>
       <c r="H1950" t="s">
         <v>8</v>
@@ -51095,7 +51095,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G1951" t="n">
-        <v>17.5166110992432</v>
+        <v>17.5166130065918</v>
       </c>
       <c r="H1951" t="s">
         <v>8</v>
@@ -51121,7 +51121,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1952" t="n">
-        <v>17.652702331543</v>
+        <v>17.6527004241943</v>
       </c>
       <c r="H1952" t="s">
         <v>8</v>
@@ -51147,7 +51147,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G1953" t="n">
-        <v>17.7110252380371</v>
+        <v>17.7110233306885</v>
       </c>
       <c r="H1953" t="s">
         <v>8</v>
@@ -51329,7 +51329,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1960" t="n">
-        <v>16.7389583587646</v>
+        <v>16.7389602661133</v>
       </c>
       <c r="H1960" t="s">
         <v>8</v>
@@ -51511,7 +51511,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1967" t="n">
-        <v>16.7778434753418</v>
+        <v>16.7778415679932</v>
       </c>
       <c r="H1967" t="s">
         <v>8</v>
@@ -51563,7 +51563,7 @@
         <v>16.5</v>
       </c>
       <c r="G1969" t="n">
-        <v>16.0390739440918</v>
+        <v>16.0390720367432</v>
       </c>
       <c r="H1969" t="s">
         <v>8</v>
@@ -51667,7 +51667,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1973" t="n">
-        <v>15.2419805526733</v>
+        <v>15.241979598999</v>
       </c>
       <c r="H1973" t="s">
         <v>8</v>
@@ -51693,7 +51693,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G1974" t="n">
-        <v>15.8252201080322</v>
+        <v>15.8252191543579</v>
       </c>
       <c r="H1974" t="s">
         <v>8</v>
@@ -51797,7 +51797,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G1978" t="n">
-        <v>15.7280120849609</v>
+        <v>15.7280130386353</v>
       </c>
       <c r="H1978" t="s">
         <v>8</v>
@@ -51849,7 +51849,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1980" t="n">
-        <v>15.2225379943848</v>
+        <v>15.2225389480591</v>
       </c>
       <c r="H1980" t="s">
         <v>8</v>
@@ -51953,7 +51953,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G1984" t="n">
-        <v>14.4254446029663</v>
+        <v>14.4254455566406</v>
       </c>
       <c r="H1984" t="s">
         <v>8</v>
@@ -52109,7 +52109,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1990" t="n">
-        <v>13.5117044448853</v>
+        <v>13.5117034912109</v>
       </c>
       <c r="H1990" t="s">
         <v>8</v>
@@ -52239,7 +52239,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1995" t="n">
-        <v>13.8033237457275</v>
+        <v>13.8033227920532</v>
       </c>
       <c r="H1995" t="s">
         <v>8</v>
@@ -52343,7 +52343,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G1999" t="n">
-        <v>14.2504730224609</v>
+        <v>14.2504739761353</v>
       </c>
       <c r="H1999" t="s">
         <v>8</v>
@@ -52369,7 +52369,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G2000" t="n">
-        <v>13.8810892105103</v>
+        <v>13.8810882568359</v>
       </c>
       <c r="H2000" t="s">
         <v>8</v>
@@ -52447,7 +52447,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G2003" t="n">
-        <v>15.3197460174561</v>
+        <v>15.3197450637817</v>
       </c>
       <c r="H2003" t="s">
         <v>8</v>
@@ -52499,7 +52499,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2005" t="n">
-        <v>15.3586282730103</v>
+        <v>15.3586273193359</v>
       </c>
       <c r="H2005" t="s">
         <v>8</v>
@@ -52525,7 +52525,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G2006" t="n">
-        <v>15.2419805526733</v>
+        <v>15.241979598999</v>
       </c>
       <c r="H2006" t="s">
         <v>8</v>
@@ -52551,7 +52551,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2007" t="n">
-        <v>14.9698009490967</v>
+        <v>14.969801902771</v>
       </c>
       <c r="H2007" t="s">
         <v>8</v>
@@ -52577,7 +52577,7 @@
         <v>16.5</v>
       </c>
       <c r="G2008" t="n">
-        <v>16.0390739440918</v>
+        <v>16.0390720367432</v>
       </c>
       <c r="H2008" t="s">
         <v>8</v>
@@ -62174,6 +62174,32 @@
         <v>28.3500003814697</v>
       </c>
       <c r="H2377" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2378">
+      <c r="A2378" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B2378" t="n">
+        <v>42461</v>
+      </c>
+      <c r="C2378" t="n">
+        <v>28.9500007629395</v>
+      </c>
+      <c r="D2378" t="n">
+        <v>27.6499996185303</v>
+      </c>
+      <c r="E2378" t="n">
+        <v>28.2999992370605</v>
+      </c>
+      <c r="F2378" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="G2378" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="H2378" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/WIIT.MI.xlsx
+++ b/data/WIIT.MI.xlsx
@@ -421,7 +421,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2" t="n">
-        <v>4.49076461791992</v>
+        <v>4.49076509475708</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G3" t="n">
-        <v>4.49076461791992</v>
+        <v>4.49076509475708</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>5.125</v>
       </c>
       <c r="G4" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>5.125</v>
       </c>
       <c r="G5" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>5.125</v>
       </c>
       <c r="G6" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>5.125</v>
       </c>
       <c r="G7" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>5.125</v>
       </c>
       <c r="G8" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>5.125</v>
       </c>
       <c r="G9" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>5.125</v>
       </c>
       <c r="G10" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>5.125</v>
       </c>
       <c r="G11" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>5.125</v>
       </c>
       <c r="G12" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>5.125</v>
       </c>
       <c r="G13" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>5.125</v>
       </c>
       <c r="G14" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>5.125</v>
       </c>
       <c r="G15" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>5.125</v>
       </c>
       <c r="G16" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>5.125</v>
       </c>
       <c r="G17" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>5.125</v>
       </c>
       <c r="G18" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>5.125</v>
       </c>
       <c r="G19" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>5.125</v>
       </c>
       <c r="G20" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>5.125</v>
       </c>
       <c r="G21" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>5.125</v>
       </c>
       <c r="G22" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>5.125</v>
       </c>
       <c r="G23" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>5.125</v>
       </c>
       <c r="G24" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>5.125</v>
       </c>
       <c r="G25" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>5.125</v>
       </c>
       <c r="G26" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>5.125</v>
       </c>
       <c r="G27" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>5.125</v>
       </c>
       <c r="G28" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>5.125</v>
       </c>
       <c r="G29" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>5.125</v>
       </c>
       <c r="G30" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>5.125</v>
       </c>
       <c r="G31" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>5.125</v>
       </c>
       <c r="G32" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>5.125</v>
       </c>
       <c r="G33" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>5.125</v>
       </c>
       <c r="G34" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>5.125</v>
       </c>
       <c r="G35" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>5.125</v>
       </c>
       <c r="G36" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>5.125</v>
       </c>
       <c r="G37" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>5.125</v>
       </c>
       <c r="G38" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>5.125</v>
       </c>
       <c r="G39" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>5.125</v>
       </c>
       <c r="G40" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>5.125</v>
       </c>
       <c r="G41" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>5.125</v>
       </c>
       <c r="G42" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>5.125</v>
       </c>
       <c r="G43" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>5.125</v>
       </c>
       <c r="G44" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>5.125</v>
       </c>
       <c r="G45" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>5.125</v>
       </c>
       <c r="G46" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>5.125</v>
       </c>
       <c r="G47" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>5.125</v>
       </c>
       <c r="G48" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>5.125</v>
       </c>
       <c r="G49" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>5.125</v>
       </c>
       <c r="G50" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>5.125</v>
       </c>
       <c r="G51" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>5.125</v>
       </c>
       <c r="G52" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>5.125</v>
       </c>
       <c r="G53" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>5.125</v>
       </c>
       <c r="G54" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>5.125</v>
       </c>
       <c r="G55" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>5.125</v>
       </c>
       <c r="G56" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>5.125</v>
       </c>
       <c r="G57" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>5.125</v>
       </c>
       <c r="G58" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>5.125</v>
       </c>
       <c r="G59" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>5.125</v>
       </c>
       <c r="G60" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>5.125</v>
       </c>
       <c r="G61" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>5.125</v>
       </c>
       <c r="G62" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>5.125</v>
       </c>
       <c r="G63" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>5.125</v>
       </c>
       <c r="G64" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>5.125</v>
       </c>
       <c r="G65" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>5.125</v>
       </c>
       <c r="G66" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>5.125</v>
       </c>
       <c r="G67" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>5.125</v>
       </c>
       <c r="G68" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>5.125</v>
       </c>
       <c r="G69" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>5.125</v>
       </c>
       <c r="G70" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>5.125</v>
       </c>
       <c r="G71" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>5.125</v>
       </c>
       <c r="G72" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>5.125</v>
       </c>
       <c r="G73" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>5.125</v>
       </c>
       <c r="G74" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>5.125</v>
       </c>
       <c r="G75" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>5.125</v>
       </c>
       <c r="G76" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>5.125</v>
       </c>
       <c r="G77" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>5.125</v>
       </c>
       <c r="G78" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>5.125</v>
       </c>
       <c r="G79" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>5.125</v>
       </c>
       <c r="G80" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>5.125</v>
       </c>
       <c r="G81" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>5.125</v>
       </c>
       <c r="G82" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>5.125</v>
       </c>
       <c r="G83" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>5.125</v>
       </c>
       <c r="G84" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>5.125</v>
       </c>
       <c r="G85" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>5.125</v>
       </c>
       <c r="G86" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>5.125</v>
       </c>
       <c r="G87" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>5.125</v>
       </c>
       <c r="G88" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>5.125</v>
       </c>
       <c r="G89" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>5.125</v>
       </c>
       <c r="G90" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>5.125</v>
       </c>
       <c r="G91" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>5.125</v>
       </c>
       <c r="G92" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>5.125</v>
       </c>
       <c r="G93" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>5.125</v>
       </c>
       <c r="G94" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>5.125</v>
       </c>
       <c r="G95" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>5.125</v>
       </c>
       <c r="G96" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>5.125</v>
       </c>
       <c r="G97" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>5.125</v>
       </c>
       <c r="G98" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>5.125</v>
       </c>
       <c r="G99" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>5.125</v>
       </c>
       <c r="G100" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>5.125</v>
       </c>
       <c r="G101" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>5.125</v>
       </c>
       <c r="G102" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>5.125</v>
       </c>
       <c r="G103" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>5.125</v>
       </c>
       <c r="G104" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>5.125</v>
       </c>
       <c r="G105" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>5.125</v>
       </c>
       <c r="G106" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>5.125</v>
       </c>
       <c r="G107" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>5.125</v>
       </c>
       <c r="G108" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>5.125</v>
       </c>
       <c r="G109" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>5.125</v>
       </c>
       <c r="G110" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>5.125</v>
       </c>
       <c r="G111" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>5.125</v>
       </c>
       <c r="G112" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>5.125</v>
       </c>
       <c r="G113" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>5.125</v>
       </c>
       <c r="G114" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>5.125</v>
       </c>
       <c r="G115" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>5.125</v>
       </c>
       <c r="G116" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>5.125</v>
       </c>
       <c r="G117" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>5.125</v>
       </c>
       <c r="G118" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>5.125</v>
       </c>
       <c r="G119" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>5.125</v>
       </c>
       <c r="G120" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3515,7 +3515,7 @@
         <v>5.125</v>
       </c>
       <c r="G121" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H121" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>5.125</v>
       </c>
       <c r="G122" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>5.125</v>
       </c>
       <c r="G123" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>5.125</v>
       </c>
       <c r="G124" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>5.125</v>
       </c>
       <c r="G125" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>5.125</v>
       </c>
       <c r="G126" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>5.125</v>
       </c>
       <c r="G127" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>5.125</v>
       </c>
       <c r="G128" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>5.125</v>
       </c>
       <c r="G129" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>5.125</v>
       </c>
       <c r="G130" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>5.125</v>
       </c>
       <c r="G131" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>5.125</v>
       </c>
       <c r="G132" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>5.125</v>
       </c>
       <c r="G133" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>5.125</v>
       </c>
       <c r="G134" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>5.125</v>
       </c>
       <c r="G135" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>5.125</v>
       </c>
       <c r="G136" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>5.125</v>
       </c>
       <c r="G137" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>5.125</v>
       </c>
       <c r="G138" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>5.125</v>
       </c>
       <c r="G139" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>5.125</v>
       </c>
       <c r="G140" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>5.125</v>
       </c>
       <c r="G141" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>5.125</v>
       </c>
       <c r="G142" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>5.125</v>
       </c>
       <c r="G143" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>5.125</v>
       </c>
       <c r="G144" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>5.125</v>
       </c>
       <c r="G145" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>5.125</v>
       </c>
       <c r="G146" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>5.125</v>
       </c>
       <c r="G147" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>5.125</v>
       </c>
       <c r="G148" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4243,7 +4243,7 @@
         <v>5.125</v>
       </c>
       <c r="G149" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H149" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>5.125</v>
       </c>
       <c r="G150" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>5.125</v>
       </c>
       <c r="G151" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>5.125</v>
       </c>
       <c r="G152" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>5.125</v>
       </c>
       <c r="G153" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>5.125</v>
       </c>
       <c r="G154" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>5.125</v>
       </c>
       <c r="G155" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4425,7 +4425,7 @@
         <v>5.125</v>
       </c>
       <c r="G156" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H156" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>5.125</v>
       </c>
       <c r="G157" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>5.125</v>
       </c>
       <c r="G158" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>5.125</v>
       </c>
       <c r="G159" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>5.125</v>
       </c>
       <c r="G160" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>5.125</v>
       </c>
       <c r="G161" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>5.125</v>
       </c>
       <c r="G162" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4607,7 +4607,7 @@
         <v>5.125</v>
       </c>
       <c r="G163" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H163" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>5.125</v>
       </c>
       <c r="G164" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>5.125</v>
       </c>
       <c r="G165" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>5.125</v>
       </c>
       <c r="G166" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>5.125</v>
       </c>
       <c r="G167" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>5.125</v>
       </c>
       <c r="G168" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>5.125</v>
       </c>
       <c r="G169" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>5.125</v>
       </c>
       <c r="G170" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>5.125</v>
       </c>
       <c r="G171" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>5.125</v>
       </c>
       <c r="G172" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>5.125</v>
       </c>
       <c r="G173" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>5.125</v>
       </c>
       <c r="G174" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>5.125</v>
       </c>
       <c r="G175" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>5.125</v>
       </c>
       <c r="G176" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>5.125</v>
       </c>
       <c r="G177" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>5.125</v>
       </c>
       <c r="G178" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>5.125</v>
       </c>
       <c r="G179" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>5.125</v>
       </c>
       <c r="G180" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>5.125</v>
       </c>
       <c r="G181" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>5.125</v>
       </c>
       <c r="G182" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>5.125</v>
       </c>
       <c r="G183" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>5.125</v>
       </c>
       <c r="G184" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>5.125</v>
       </c>
       <c r="G185" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>5.125</v>
       </c>
       <c r="G186" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>5.125</v>
       </c>
       <c r="G187" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>5.125</v>
       </c>
       <c r="G188" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>5.125</v>
       </c>
       <c r="G189" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>5.125</v>
       </c>
       <c r="G190" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5335,7 +5335,7 @@
         <v>5.125</v>
       </c>
       <c r="G191" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H191" t="s">
         <v>8</v>
@@ -5361,7 +5361,7 @@
         <v>5.125</v>
       </c>
       <c r="G192" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H192" t="s">
         <v>8</v>
@@ -5387,7 +5387,7 @@
         <v>5.125</v>
       </c>
       <c r="G193" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H193" t="s">
         <v>8</v>
@@ -5413,7 +5413,7 @@
         <v>5.125</v>
       </c>
       <c r="G194" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H194" t="s">
         <v>8</v>
@@ -5439,7 +5439,7 @@
         <v>5.125</v>
       </c>
       <c r="G195" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H195" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>5.125</v>
       </c>
       <c r="G196" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>5.125</v>
       </c>
       <c r="G197" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>5.125</v>
       </c>
       <c r="G198" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>5.125</v>
       </c>
       <c r="G199" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>5.125</v>
       </c>
       <c r="G200" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>5.125</v>
       </c>
       <c r="G201" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>5.125</v>
       </c>
       <c r="G202" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>5.125</v>
       </c>
       <c r="G203" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>5.125</v>
       </c>
       <c r="G204" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>5.125</v>
       </c>
       <c r="G205" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>5.125</v>
       </c>
       <c r="G206" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>5.125</v>
       </c>
       <c r="G207" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>5.125</v>
       </c>
       <c r="G208" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>5.125</v>
       </c>
       <c r="G209" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>5.125</v>
       </c>
       <c r="G210" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>5.125</v>
       </c>
       <c r="G211" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>5.125</v>
       </c>
       <c r="G212" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>5.125</v>
       </c>
       <c r="G213" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>5.125</v>
       </c>
       <c r="G214" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>5.125</v>
       </c>
       <c r="G215" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>5.125</v>
       </c>
       <c r="G216" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>5.125</v>
       </c>
       <c r="G217" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>5.125</v>
       </c>
       <c r="G218" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>5.125</v>
       </c>
       <c r="G219" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>5.125</v>
       </c>
       <c r="G220" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>5.125</v>
       </c>
       <c r="G221" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>5.125</v>
       </c>
       <c r="G222" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>5.125</v>
       </c>
       <c r="G223" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>5.125</v>
       </c>
       <c r="G224" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>5.125</v>
       </c>
       <c r="G225" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>5.125</v>
       </c>
       <c r="G226" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>5.125</v>
       </c>
       <c r="G227" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>5.125</v>
       </c>
       <c r="G228" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>5.125</v>
       </c>
       <c r="G229" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>5.125</v>
       </c>
       <c r="G230" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>5.125</v>
       </c>
       <c r="G231" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>5.125</v>
       </c>
       <c r="G232" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G275" t="n">
-        <v>4.41253423690796</v>
+        <v>4.4125337600708</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G276" t="n">
-        <v>4.52888870239258</v>
+        <v>4.52888822555542</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G277" t="n">
-        <v>4.49308729171753</v>
+        <v>4.49308681488037</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G278" t="n">
-        <v>4.44833612442017</v>
+        <v>4.44833469390869</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>5</v>
       </c>
       <c r="G279" t="n">
-        <v>4.47518634796143</v>
+        <v>4.47518682479858</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>5</v>
       </c>
       <c r="G280" t="n">
-        <v>4.47518634796143</v>
+        <v>4.47518682479858</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>5</v>
       </c>
       <c r="G281" t="n">
-        <v>4.47518634796143</v>
+        <v>4.47518682479858</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G282" t="n">
-        <v>4.49308729171753</v>
+        <v>4.49308681488037</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G283" t="n">
-        <v>4.43938589096069</v>
+        <v>4.43938541412354</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G284" t="n">
-        <v>4.49308729171753</v>
+        <v>4.49308681488037</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>5</v>
       </c>
       <c r="G285" t="n">
-        <v>4.47518634796143</v>
+        <v>4.47518682479858</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G286" t="n">
-        <v>4.44833612442017</v>
+        <v>4.44833469390869</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G287" t="n">
-        <v>4.44833612442017</v>
+        <v>4.44833469390869</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G288" t="n">
-        <v>4.44833612442017</v>
+        <v>4.44833469390869</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G289" t="n">
-        <v>4.44833612442017</v>
+        <v>4.44833469390869</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>5</v>
       </c>
       <c r="G290" t="n">
-        <v>4.47518634796143</v>
+        <v>4.47518682479858</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G291" t="n">
-        <v>4.54678869247437</v>
+        <v>4.54678964614868</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G292" t="n">
-        <v>4.54678869247437</v>
+        <v>4.54678964614868</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G293" t="n">
-        <v>4.54678869247437</v>
+        <v>4.54678964614868</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G294" t="n">
-        <v>4.58259057998657</v>
+        <v>4.58259105682373</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G295" t="n">
-        <v>4.54678869247437</v>
+        <v>4.54678964614868</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G297" t="n">
-        <v>4.52888870239258</v>
+        <v>4.52888822555542</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G300" t="n">
-        <v>4.49308729171753</v>
+        <v>4.49308681488037</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G301" t="n">
-        <v>4.49308729171753</v>
+        <v>4.49308681488037</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>4.49308729171753</v>
+        <v>4.49308681488037</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G303" t="n">
-        <v>4.43043518066406</v>
+        <v>4.43043422698975</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G304" t="n">
-        <v>4.43043518066406</v>
+        <v>4.43043422698975</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G305" t="n">
-        <v>4.38568258285522</v>
+        <v>4.38568305969238</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G306" t="n">
-        <v>4.3409309387207</v>
+        <v>4.34093046188354</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G309" t="n">
-        <v>4.33198070526123</v>
+        <v>4.33198022842407</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G310" t="n">
-        <v>4.33198070526123</v>
+        <v>4.33198022842407</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>4.45728635787964</v>
+        <v>4.45728588104248</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>4.43938589096069</v>
+        <v>4.43938541412354</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G316" t="n">
-        <v>4.33198070526123</v>
+        <v>4.33198022842407</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G317" t="n">
-        <v>4.3230299949646</v>
+        <v>4.32302951812744</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G318" t="n">
-        <v>4.3230299949646</v>
+        <v>4.32302951812744</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G319" t="n">
-        <v>4.35883188247681</v>
+        <v>4.35883140563965</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G321" t="n">
-        <v>4.23352670669556</v>
+        <v>4.2335262298584</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G322" t="n">
-        <v>4.3230299949646</v>
+        <v>4.32302951812744</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>4.28722906112671</v>
+        <v>4.28722953796387</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G325" t="n">
-        <v>4.17982482910156</v>
+        <v>4.17982387542725</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G326" t="n">
-        <v>4.09032154083252</v>
+        <v>4.09032106399536</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G328" t="n">
-        <v>3.90236258506775</v>
+        <v>3.90236282348633</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G329" t="n">
-        <v>3.99186682701111</v>
+        <v>3.99186658859253</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G331" t="n">
-        <v>4.08136987686157</v>
+        <v>4.08137035369873</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G332" t="n">
-        <v>4.13507270812988</v>
+        <v>4.13507223129272</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G333" t="n">
-        <v>4.17982482910156</v>
+        <v>4.17982387542725</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G335" t="n">
-        <v>4.11717176437378</v>
+        <v>4.11717128753662</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G336" t="n">
-        <v>3.99186682701111</v>
+        <v>3.99186658859253</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>4.5</v>
       </c>
       <c r="G337" t="n">
-        <v>4.02766847610474</v>
+        <v>4.02766752243042</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G338" t="n">
-        <v>3.93816423416138</v>
+        <v>3.93816447257996</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9209,7 +9209,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G340" t="n">
-        <v>3.90236258506775</v>
+        <v>3.90236282348633</v>
       </c>
       <c r="H340" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G341" t="n">
-        <v>3.86656141281128</v>
+        <v>3.86656165122986</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>3.76810717582703</v>
+        <v>3.76810789108276</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G344" t="n">
-        <v>3.78600764274597</v>
+        <v>3.78600788116455</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G345" t="n">
-        <v>3.7054545879364</v>
+        <v>3.70545411109924</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G346" t="n">
-        <v>3.66965293884277</v>
+        <v>3.66965270042419</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G347" t="n">
-        <v>3.60700082778931</v>
+        <v>3.60700058937073</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G348" t="n">
-        <v>3.5980498790741</v>
+        <v>3.59805011749268</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G349" t="n">
-        <v>3.5980498790741</v>
+        <v>3.59805011749268</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G350" t="n">
-        <v>3.5711989402771</v>
+        <v>3.57119917869568</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G351" t="n">
-        <v>3.53539752960205</v>
+        <v>3.53539729118347</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>4</v>
       </c>
       <c r="G352" t="n">
-        <v>3.58014965057373</v>
+        <v>3.58014917373657</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G353" t="n">
-        <v>3.4369432926178</v>
+        <v>3.43694353103638</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G354" t="n">
-        <v>3.47274470329285</v>
+        <v>3.47274494171143</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G355" t="n">
-        <v>3.44589400291443</v>
+        <v>3.44589352607727</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G356" t="n">
-        <v>3.41009259223938</v>
+        <v>3.41009211540222</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G357" t="n">
-        <v>3.3921914100647</v>
+        <v>3.39219164848328</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G358" t="n">
-        <v>3.31163811683655</v>
+        <v>3.31163787841797</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G359" t="n">
-        <v>3.31163811683655</v>
+        <v>3.31163787841797</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G360" t="n">
-        <v>3.31163811683655</v>
+        <v>3.31163787841797</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G361" t="n">
-        <v>3.34744000434875</v>
+        <v>3.3474395275116</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G362" t="n">
-        <v>3.3653404712677</v>
+        <v>3.36534023284912</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G363" t="n">
-        <v>3.31163811683655</v>
+        <v>3.31163787841797</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G365" t="n">
-        <v>3.08787870407104</v>
+        <v>3.08787894248962</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G366" t="n">
-        <v>3.07892847061157</v>
+        <v>3.07892823219299</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G367" t="n">
-        <v>3.09682869911194</v>
+        <v>3.0968291759491</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G371" t="n">
-        <v>3.22213435173035</v>
+        <v>3.22213459014893</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G372" t="n">
-        <v>3.22213435173035</v>
+        <v>3.22213459014893</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G373" t="n">
-        <v>2.93572235107422</v>
+        <v>2.9357225894928</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G375" t="n">
-        <v>2.82831788063049</v>
+        <v>2.82831811904907</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G377" t="n">
-        <v>2.95362329483032</v>
+        <v>2.95362305641174</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G382" t="n">
-        <v>2.95362329483032</v>
+        <v>2.95362305641174</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G383" t="n">
-        <v>2.95362329483032</v>
+        <v>2.95362305641174</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G384" t="n">
-        <v>3.00732564926147</v>
+        <v>3.00732517242432</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G385" t="n">
-        <v>2.95362329483032</v>
+        <v>2.95362305641174</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G388" t="n">
-        <v>2.82831788063049</v>
+        <v>2.82831811904907</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G391" t="n">
-        <v>2.84621906280518</v>
+        <v>2.8462188243866</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G393" t="n">
-        <v>2.89992070198059</v>
+        <v>2.89992094039917</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G394" t="n">
-        <v>2.94467306137085</v>
+        <v>2.94467258453369</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G395" t="n">
-        <v>3.06102752685547</v>
+        <v>3.06102776527405</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G396" t="n">
-        <v>3.06997776031494</v>
+        <v>3.0699782371521</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G399" t="n">
-        <v>3.26688647270203</v>
+        <v>3.26688671112061</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>3.22213435173035</v>
+        <v>3.22213459014893</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G401" t="n">
-        <v>3.26688647270203</v>
+        <v>3.26688671112061</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G402" t="n">
-        <v>3.26688647270203</v>
+        <v>3.26688671112061</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G403" t="n">
-        <v>3.31163811683655</v>
+        <v>3.31163787841797</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>3.75</v>
       </c>
       <c r="G404" t="n">
-        <v>3.35639023780823</v>
+        <v>3.35638976097107</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G405" t="n">
-        <v>3.3921914100647</v>
+        <v>3.39219164848328</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G406" t="n">
-        <v>3.499596118927</v>
+        <v>3.49959588050842</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G407" t="n">
-        <v>3.50854635238647</v>
+        <v>3.5085461139679</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G408" t="n">
-        <v>3.66965293884277</v>
+        <v>3.66965270042419</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G409" t="n">
-        <v>3.5980498790741</v>
+        <v>3.59805011749268</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G410" t="n">
-        <v>3.56224822998047</v>
+        <v>3.56224870681763</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G411" t="n">
-        <v>3.5980498790741</v>
+        <v>3.59805011749268</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4</v>
       </c>
       <c r="G412" t="n">
-        <v>3.58014965057373</v>
+        <v>3.58014917373657</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G414" t="n">
-        <v>3.63385128974915</v>
+        <v>3.63385152816772</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G415" t="n">
-        <v>3.6607027053833</v>
+        <v>3.66070246696472</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G416" t="n">
-        <v>3.63385128974915</v>
+        <v>3.63385152816772</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G417" t="n">
-        <v>3.49064564704895</v>
+        <v>3.49064588546753</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G418" t="n">
-        <v>3.53539752960205</v>
+        <v>3.53539729118347</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G419" t="n">
-        <v>3.66965293884277</v>
+        <v>3.66965270042419</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>4</v>
       </c>
       <c r="G420" t="n">
-        <v>3.58014965057373</v>
+        <v>3.58014917373657</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G421" t="n">
-        <v>3.66965293884277</v>
+        <v>3.66965270042419</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G422" t="n">
-        <v>3.66965293884277</v>
+        <v>3.66965270042419</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G424" t="n">
-        <v>3.63385128974915</v>
+        <v>3.63385152816772</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G426" t="n">
-        <v>3.63385128974915</v>
+        <v>3.63385152816772</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>4</v>
       </c>
       <c r="G427" t="n">
-        <v>3.58014965057373</v>
+        <v>3.58014917373657</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G428" t="n">
-        <v>3.63385128974915</v>
+        <v>3.63385152816772</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G430" t="n">
-        <v>3.69650435447693</v>
+        <v>3.69650411605835</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G431" t="n">
-        <v>3.75020623207092</v>
+        <v>3.75020670890808</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G432" t="n">
-        <v>3.78600764274597</v>
+        <v>3.78600788116455</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G433" t="n">
-        <v>3.90236258506775</v>
+        <v>3.90236282348633</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G434" t="n">
-        <v>4.09032154083252</v>
+        <v>4.09032106399536</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>4.75</v>
       </c>
       <c r="G438" t="n">
-        <v>4.25142765045166</v>
+        <v>4.2514271736145</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G439" t="n">
-        <v>4.11717176437378</v>
+        <v>4.11717128753662</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>4.43043518066406</v>
+        <v>4.43043422698975</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G443" t="n">
-        <v>4.23352670669556</v>
+        <v>4.2335262298584</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>4.5</v>
       </c>
       <c r="G445" t="n">
-        <v>4.02766847610474</v>
+        <v>4.02766752243042</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G446" t="n">
-        <v>3.90236258506775</v>
+        <v>3.90236282348633</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G447" t="n">
-        <v>3.92026305198669</v>
+        <v>3.92026352882385</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G448" t="n">
-        <v>3.76810717582703</v>
+        <v>3.76810789108276</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G450" t="n">
-        <v>3.66965293884277</v>
+        <v>3.66965270042419</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G451" t="n">
-        <v>3.7054545879364</v>
+        <v>3.70545411109924</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G453" t="n">
-        <v>4.00976657867432</v>
+        <v>4.00976705551147</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G455" t="n">
-        <v>4.13507270812988</v>
+        <v>4.13507223129272</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G457" t="n">
-        <v>4.20667457580566</v>
+        <v>4.20667552947998</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G459" t="n">
-        <v>4.26037788391113</v>
+        <v>4.26037836074829</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G460" t="n">
-        <v>4.3409309387207</v>
+        <v>4.34093046188354</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>4.92000007629395</v>
       </c>
       <c r="G461" t="n">
-        <v>4.40358400344849</v>
+        <v>4.40358352661133</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G462" t="n">
-        <v>4.44833612442017</v>
+        <v>4.44833469390869</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G463" t="n">
-        <v>4.3230299949646</v>
+        <v>4.32302951812744</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G464" t="n">
-        <v>4.42148542404175</v>
+        <v>4.42148447036743</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G466" t="n">
-        <v>4.38568258285522</v>
+        <v>4.38568305969238</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G469" t="n">
-        <v>4.21562576293945</v>
+        <v>4.21562623977661</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G471" t="n">
-        <v>4.20667457580566</v>
+        <v>4.20667552947998</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G472" t="n">
-        <v>4.3891773223877</v>
+        <v>4.38917779922485</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G473" t="n">
-        <v>4.28880167007446</v>
+        <v>4.2888011932373</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G474" t="n">
-        <v>4.37092685699463</v>
+        <v>4.37092781066895</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G475" t="n">
-        <v>4.44392871856689</v>
+        <v>4.44392824172974</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G476" t="n">
-        <v>4.28880167007446</v>
+        <v>4.2888011932373</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G481" t="n">
-        <v>4.2705512046814</v>
+        <v>4.27055072784424</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G482" t="n">
-        <v>4.26142597198486</v>
+        <v>4.26142549514771</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G483" t="n">
-        <v>4.28880167007446</v>
+        <v>4.2888011932373</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G484" t="n">
-        <v>4.21580123901367</v>
+        <v>4.21580028533936</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G485" t="n">
-        <v>4.28880167007446</v>
+        <v>4.2888011932373</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G486" t="n">
-        <v>4.35267686843872</v>
+        <v>4.35267734527588</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G487" t="n">
-        <v>4.36180305480957</v>
+        <v>4.36180210113525</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G488" t="n">
-        <v>4.36180305480957</v>
+        <v>4.36180210113525</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G490" t="n">
-        <v>4.28880167007446</v>
+        <v>4.2888011932373</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G491" t="n">
-        <v>4.28880167007446</v>
+        <v>4.2888011932373</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>4.75</v>
       </c>
       <c r="G492" t="n">
-        <v>4.33442687988281</v>
+        <v>4.33442640304565</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>4.75</v>
       </c>
       <c r="G493" t="n">
-        <v>4.33442687988281</v>
+        <v>4.33442640304565</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G494" t="n">
-        <v>4.24317646026611</v>
+        <v>4.24317598342896</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G495" t="n">
-        <v>4.38005256652832</v>
+        <v>4.38005208969116</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G497" t="n">
-        <v>4.38005256652832</v>
+        <v>4.38005208969116</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>4.75</v>
       </c>
       <c r="G498" t="n">
-        <v>4.33442687988281</v>
+        <v>4.33442640304565</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>4.75</v>
       </c>
       <c r="G499" t="n">
-        <v>4.33442687988281</v>
+        <v>4.33442640304565</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G500" t="n">
-        <v>4.38005256652832</v>
+        <v>4.38005208969116</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G501" t="n">
-        <v>4.37092685699463</v>
+        <v>4.37092781066895</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>4.75</v>
       </c>
       <c r="G503" t="n">
-        <v>4.33442687988281</v>
+        <v>4.33442640304565</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G507" t="n">
-        <v>4.38005256652832</v>
+        <v>4.38005208969116</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G508" t="n">
-        <v>4.38005256652832</v>
+        <v>4.38005208969116</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G510" t="n">
-        <v>4.32530164718628</v>
+        <v>4.32530212402344</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G512" t="n">
-        <v>4.32530164718628</v>
+        <v>4.32530212402344</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>4.75</v>
       </c>
       <c r="G514" t="n">
-        <v>4.33442687988281</v>
+        <v>4.33442640304565</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G516" t="n">
-        <v>4.28880167007446</v>
+        <v>4.2888011932373</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G518" t="n">
-        <v>4.61730575561523</v>
+        <v>4.61730480194092</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G519" t="n">
-        <v>4.59905576705933</v>
+        <v>4.59905481338501</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G523" t="n">
-        <v>4.61730575561523</v>
+        <v>4.61730480194092</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G526" t="n">
-        <v>4.79980802536011</v>
+        <v>4.79980754852295</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G527" t="n">
-        <v>4.90930986404419</v>
+        <v>4.90930891036987</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G528" t="n">
-        <v>4.90930986404419</v>
+        <v>4.90930891036987</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>4.9275598526001</v>
+        <v>4.92755937576294</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G530" t="n">
-        <v>4.96405935287476</v>
+        <v>4.96406030654907</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G531" t="n">
-        <v>4.94580984115601</v>
+        <v>4.94580936431885</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>5.5</v>
       </c>
       <c r="G533" t="n">
-        <v>5.01881074905396</v>
+        <v>5.01880931854248</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G535" t="n">
-        <v>5.20131206512451</v>
+        <v>5.20131158828735</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G536" t="n">
-        <v>5.27431344985962</v>
+        <v>5.27431392669678</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14331,7 +14331,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G537" t="n">
-        <v>5.1830620765686</v>
+        <v>5.18306159973145</v>
       </c>
       <c r="H537" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G541" t="n">
-        <v>5.00056028366089</v>
+        <v>5.00055932998657</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>5.5</v>
       </c>
       <c r="G542" t="n">
-        <v>5.01881074905396</v>
+        <v>5.01880931854248</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>5.5</v>
       </c>
       <c r="G544" t="n">
-        <v>5.01881074905396</v>
+        <v>5.01880931854248</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G545" t="n">
-        <v>5.05531024932861</v>
+        <v>5.05531072616577</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G548" t="n">
-        <v>5.20131206512451</v>
+        <v>5.20131158828735</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G551" t="n">
-        <v>5.1830620765686</v>
+        <v>5.18306159973145</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G553" t="n">
-        <v>5.29256343841553</v>
+        <v>5.29256391525269</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G554" t="n">
-        <v>5.29256343841553</v>
+        <v>5.29256391525269</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G556" t="n">
-        <v>5.32906436920166</v>
+        <v>5.32906341552734</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G557" t="n">
-        <v>5.42031478881836</v>
+        <v>5.4203143119812</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G561" t="n">
-        <v>5.49331521987915</v>
+        <v>5.49331569671631</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G564" t="n">
-        <v>5.42031478881836</v>
+        <v>5.4203143119812</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15059,7 +15059,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G565" t="n">
-        <v>5.32906436920166</v>
+        <v>5.32906341552734</v>
       </c>
       <c r="H565" t="s">
         <v>8</v>
@@ -15085,7 +15085,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G566" t="n">
-        <v>5.29256343841553</v>
+        <v>5.29256391525269</v>
       </c>
       <c r="H566" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G567" t="n">
-        <v>5.29256343841553</v>
+        <v>5.29256391525269</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G568" t="n">
-        <v>5.27431344985962</v>
+        <v>5.27431392669678</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G570" t="n">
-        <v>5.29256343841553</v>
+        <v>5.29256391525269</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G571" t="n">
-        <v>5.32906436920166</v>
+        <v>5.32906341552734</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G574" t="n">
-        <v>5.42031478881836</v>
+        <v>5.4203143119812</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G576" t="n">
-        <v>5.31081438064575</v>
+        <v>5.31081342697144</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G577" t="n">
-        <v>5.29256343841553</v>
+        <v>5.29256391525269</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G578" t="n">
-        <v>5.36556386947632</v>
+        <v>5.36556482315063</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G580" t="n">
-        <v>5.42031478881836</v>
+        <v>5.4203143119812</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G582" t="n">
-        <v>5.49331521987915</v>
+        <v>5.49331569671631</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G583" t="n">
-        <v>5.43856430053711</v>
+        <v>5.43856525421143</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G584" t="n">
-        <v>5.43856430053711</v>
+        <v>5.43856525421143</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G585" t="n">
-        <v>5.43856430053711</v>
+        <v>5.43856525421143</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G586" t="n">
-        <v>5.42031478881836</v>
+        <v>5.4203143119812</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G589" t="n">
-        <v>5.43856430053711</v>
+        <v>5.43856525421143</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G590" t="n">
-        <v>5.43856430053711</v>
+        <v>5.43856525421143</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G594" t="n">
-        <v>5.43856430053711</v>
+        <v>5.43856525421143</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G599" t="n">
-        <v>5.51156616210938</v>
+        <v>5.51156568527222</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G600" t="n">
-        <v>5.49331521987915</v>
+        <v>5.49331569671631</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G603" t="n">
-        <v>5.51156616210938</v>
+        <v>5.51156568527222</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G605" t="n">
-        <v>5.51156616210938</v>
+        <v>5.51156568527222</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G607" t="n">
-        <v>5.80356979370117</v>
+        <v>5.80356931686401</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G608" t="n">
-        <v>6.0773229598999</v>
+        <v>6.07732248306274</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G610" t="n">
-        <v>6.27807569503784</v>
+        <v>6.27807474136353</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G613" t="n">
-        <v>6.51532745361328</v>
+        <v>6.51532793045044</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>7.09999990463257</v>
       </c>
       <c r="G615" t="n">
-        <v>6.47882795333862</v>
+        <v>6.47882747650146</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G617" t="n">
-        <v>6.55182790756226</v>
+        <v>6.55182838439941</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G621" t="n">
-        <v>7.13583612442017</v>
+        <v>7.13583564758301</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>8.5</v>
       </c>
       <c r="G625" t="n">
-        <v>7.75634288787842</v>
+        <v>7.75634241104126</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G627" t="n">
-        <v>7.84759426116943</v>
+        <v>7.84759378433228</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G628" t="n">
-        <v>7.88409519195557</v>
+        <v>7.88409566879272</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G629" t="n">
-        <v>7.84759426116943</v>
+        <v>7.84759378433228</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G630" t="n">
-        <v>7.93884468078613</v>
+        <v>7.93884611129761</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>8.5</v>
       </c>
       <c r="G631" t="n">
-        <v>7.75634288787842</v>
+        <v>7.75634241104126</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G632" t="n">
-        <v>7.93884468078613</v>
+        <v>7.93884611129761</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G633" t="n">
-        <v>7.97534513473511</v>
+        <v>7.97534608840942</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G634" t="n">
-        <v>8.43160247802734</v>
+        <v>8.43160057067871</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G635" t="n">
-        <v>8.57760334014893</v>
+        <v>8.57760238647461</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G636" t="n">
-        <v>8.65060329437256</v>
+        <v>8.65060424804688</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G638" t="n">
-        <v>8.65060329437256</v>
+        <v>8.65060424804688</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G639" t="n">
-        <v>8.26735019683838</v>
+        <v>8.26734924316406</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G640" t="n">
-        <v>8.26735019683838</v>
+        <v>8.26734924316406</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G641" t="n">
-        <v>8.55935192108154</v>
+        <v>8.55935382843018</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G643" t="n">
-        <v>8.57760334014893</v>
+        <v>8.57760238647461</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G644" t="n">
-        <v>8.43160247802734</v>
+        <v>8.43160057067871</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G646" t="n">
-        <v>8.41335010528564</v>
+        <v>8.41335105895996</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G647" t="n">
-        <v>8.13959884643555</v>
+        <v>8.13959789276123</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G649" t="n">
-        <v>8.52285194396973</v>
+        <v>8.52285099029541</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G651" t="n">
-        <v>8.55935192108154</v>
+        <v>8.55935382843018</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G652" t="n">
-        <v>8.54110240936279</v>
+        <v>8.54110145568848</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G653" t="n">
-        <v>8.54110240936279</v>
+        <v>8.54110145568848</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G654" t="n">
-        <v>8.86960601806641</v>
+        <v>8.86960697174072</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G655" t="n">
-        <v>9.08860969543457</v>
+        <v>9.08860874176025</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G656" t="n">
-        <v>9.17073440551758</v>
+        <v>9.17073535919189</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>10.25</v>
       </c>
       <c r="G657" t="n">
-        <v>9.35323715209961</v>
+        <v>9.35323810577393</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G658" t="n">
-        <v>9.76386737823486</v>
+        <v>9.76386642456055</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G659" t="n">
-        <v>9.9919958114624</v>
+        <v>9.99199390411377</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>10.5</v>
       </c>
       <c r="G660" t="n">
-        <v>9.58136463165283</v>
+        <v>9.58136558532715</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>10.5</v>
       </c>
       <c r="G661" t="n">
-        <v>9.58136463165283</v>
+        <v>9.58136558532715</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G662" t="n">
-        <v>9.67261791229248</v>
+        <v>9.67261600494385</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G663" t="n">
-        <v>9.53573894500732</v>
+        <v>9.53573989868164</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G665" t="n">
-        <v>9.53573894500732</v>
+        <v>9.53573989868164</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G666" t="n">
-        <v>9.62699127197266</v>
+        <v>9.62699222564697</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>10.25</v>
       </c>
       <c r="G668" t="n">
-        <v>9.35323715209961</v>
+        <v>9.35323810577393</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G669" t="n">
-        <v>9.53573894500732</v>
+        <v>9.53573989868164</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G674" t="n">
-        <v>9.3076114654541</v>
+        <v>9.30761241912842</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>9.49011325836182</v>
+        <v>9.49011421203613</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G676" t="n">
-        <v>9.67261791229248</v>
+        <v>9.67261600494385</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G678" t="n">
-        <v>9.9919958114624</v>
+        <v>9.99199390411377</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G679" t="n">
-        <v>9.9919958114624</v>
+        <v>9.99199390411377</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G680" t="n">
-        <v>9.9919958114624</v>
+        <v>9.99199390411377</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G681" t="n">
-        <v>9.9919958114624</v>
+        <v>9.99199390411377</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G682" t="n">
-        <v>9.9919958114624</v>
+        <v>9.99199390411377</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G683" t="n">
-        <v>9.67261791229248</v>
+        <v>9.67261600494385</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G684" t="n">
-        <v>9.67261791229248</v>
+        <v>9.67261600494385</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G685" t="n">
-        <v>9.67261791229248</v>
+        <v>9.67261600494385</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G687" t="n">
-        <v>9.71824073791504</v>
+        <v>9.71824169158936</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G688" t="n">
-        <v>8.90610885620117</v>
+        <v>8.90610694885254</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G689" t="n">
-        <v>9.26198577880859</v>
+        <v>9.26198673248291</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G690" t="n">
-        <v>9.62699127197266</v>
+        <v>9.62699222564697</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G691" t="n">
-        <v>9.10685920715332</v>
+        <v>9.106858253479</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G692" t="n">
-        <v>8.99735832214355</v>
+        <v>8.99735736846924</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G693" t="n">
-        <v>8.77835464477539</v>
+        <v>8.77835559844971</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G696" t="n">
-        <v>8.55935192108154</v>
+        <v>8.55935382843018</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G697" t="n">
-        <v>7.84759426116943</v>
+        <v>7.84759378433228</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G698" t="n">
-        <v>7.61034250259399</v>
+        <v>7.61034154891968</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>7.5</v>
       </c>
       <c r="G701" t="n">
-        <v>6.84383249282837</v>
+        <v>6.84383153915405</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G702" t="n">
-        <v>7.26358699798584</v>
+        <v>7.263587474823</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G703" t="n">
-        <v>7.02633428573608</v>
+        <v>7.02633380889893</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G704" t="n">
-        <v>7.02633428573608</v>
+        <v>7.02633380889893</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G706" t="n">
-        <v>7.02633428573608</v>
+        <v>7.02633380889893</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>8.22000026702881</v>
       </c>
       <c r="G707" t="n">
-        <v>7.50084114074707</v>
+        <v>7.50084066390991</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G708" t="n">
-        <v>7.51909065246582</v>
+        <v>7.51909017562866</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G711" t="n">
-        <v>7.64684200286865</v>
+        <v>7.64684295654297</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G712" t="n">
-        <v>7.7745943069458</v>
+        <v>7.77459478378296</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>8.5</v>
       </c>
       <c r="G713" t="n">
-        <v>7.75634288787842</v>
+        <v>7.75634241104126</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G714" t="n">
-        <v>7.88409519195557</v>
+        <v>7.88409566879272</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G716" t="n">
-        <v>8.32210063934326</v>
+        <v>8.32209968566895</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G719" t="n">
-        <v>8.76010513305664</v>
+        <v>8.76010417938232</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G721" t="n">
-        <v>9.05210971832275</v>
+        <v>9.05210876464844</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G722" t="n">
-        <v>9.2163610458374</v>
+        <v>9.21636199951172</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>9.05210971832275</v>
+        <v>9.05210876464844</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G725" t="n">
-        <v>9.08860969543457</v>
+        <v>9.08860874176025</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G726" t="n">
-        <v>9.08860969543457</v>
+        <v>9.08860874176025</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G727" t="n">
-        <v>9.44448852539062</v>
+        <v>9.44448947906494</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G728" t="n">
-        <v>9.53573894500732</v>
+        <v>9.53573989868164</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G729" t="n">
-        <v>9.53573894500732</v>
+        <v>9.53573989868164</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19349,7 +19349,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G730" t="n">
-        <v>9.49011325836182</v>
+        <v>9.49011421203613</v>
       </c>
       <c r="H730" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>9.67261791229248</v>
+        <v>9.67261600494385</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G732" t="n">
-        <v>9.67261791229248</v>
+        <v>9.67261600494385</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G733" t="n">
-        <v>10.2201223373413</v>
+        <v>10.220121383667</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G734" t="n">
-        <v>10.402624130249</v>
+        <v>10.4026231765747</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G736" t="n">
-        <v>10.1252222061157</v>
+        <v>10.1252202987671</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>11</v>
       </c>
       <c r="G739" t="n">
-        <v>10.1714563369751</v>
+        <v>10.1714553833008</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G742" t="n">
-        <v>9.98652076721191</v>
+        <v>9.9865198135376</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G743" t="n">
-        <v>10.0327520370483</v>
+        <v>10.0327558517456</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G744" t="n">
-        <v>9.98652076721191</v>
+        <v>9.9865198135376</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19739,7 +19739,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G745" t="n">
-        <v>10.0327520370483</v>
+        <v>10.0327558517456</v>
       </c>
       <c r="H745" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>10.25</v>
       </c>
       <c r="G747" t="n">
-        <v>9.47794723510742</v>
+        <v>9.47794818878174</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G748" t="n">
-        <v>9.80158519744873</v>
+        <v>9.80158424377441</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G749" t="n">
-        <v>9.98652076721191</v>
+        <v>9.9865198135376</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G750" t="n">
-        <v>9.80158519744873</v>
+        <v>9.80158424377441</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G751" t="n">
-        <v>9.80158519744873</v>
+        <v>9.80158424377441</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G753" t="n">
-        <v>9.80158519744873</v>
+        <v>9.80158424377441</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G754" t="n">
-        <v>9.98652076721191</v>
+        <v>9.9865198135376</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>11</v>
       </c>
       <c r="G764" t="n">
-        <v>10.1714563369751</v>
+        <v>10.1714553833008</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G768" t="n">
-        <v>11.0036640167236</v>
+        <v>11.0036649703979</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20363,7 +20363,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G769" t="n">
-        <v>11.6047067642212</v>
+        <v>11.6047048568726</v>
       </c>
       <c r="H769" t="s">
         <v>8</v>
@@ -20389,7 +20389,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G770" t="n">
-        <v>11.9745769500732</v>
+        <v>11.9745779037476</v>
       </c>
       <c r="H770" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G773" t="n">
-        <v>12.2982158660889</v>
+        <v>12.2982149124146</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>13.25</v>
       </c>
       <c r="G774" t="n">
-        <v>12.2519807815552</v>
+        <v>12.2519817352295</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G775" t="n">
-        <v>12.1132802963257</v>
+        <v>12.1132793426514</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G778" t="n">
-        <v>11.9745769500732</v>
+        <v>11.9745779037476</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G779" t="n">
-        <v>11.8821096420288</v>
+        <v>11.8821086883545</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G780" t="n">
-        <v>12.067045211792</v>
+        <v>12.0670442581177</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G782" t="n">
-        <v>11.8821096420288</v>
+        <v>11.8821086883545</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G784" t="n">
-        <v>11.8358745574951</v>
+        <v>11.8358755111694</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G785" t="n">
-        <v>11.9745769500732</v>
+        <v>11.9745779037476</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>12.75</v>
       </c>
       <c r="G786" t="n">
-        <v>11.7896423339844</v>
+        <v>11.7896413803101</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>12.75</v>
       </c>
       <c r="G787" t="n">
-        <v>11.7896423339844</v>
+        <v>11.7896413803101</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>11.8821096420288</v>
+        <v>11.8821086883545</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G791" t="n">
-        <v>11.743408203125</v>
+        <v>11.7434072494507</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G792" t="n">
-        <v>11.6509389877319</v>
+        <v>11.6509399414062</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G794" t="n">
-        <v>11.6509389877319</v>
+        <v>11.6509399414062</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>12.75</v>
       </c>
       <c r="G796" t="n">
-        <v>11.7896423339844</v>
+        <v>11.7896413803101</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G797" t="n">
-        <v>11.6971740722656</v>
+        <v>11.6971750259399</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G798" t="n">
-        <v>11.4197702407837</v>
+        <v>11.419771194458</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G800" t="n">
-        <v>11.3735380172729</v>
+        <v>11.3735361099243</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G808" t="n">
-        <v>11.3735380172729</v>
+        <v>11.3735361099243</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G810" t="n">
-        <v>11.4197702407837</v>
+        <v>11.419771194458</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>12.5</v>
       </c>
       <c r="G811" t="n">
-        <v>11.5584726333618</v>
+        <v>11.5584716796875</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>12.8000001907349</v>
       </c>
       <c r="G812" t="n">
-        <v>11.8358745574951</v>
+        <v>11.8358755111694</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>12.5</v>
       </c>
       <c r="G813" t="n">
-        <v>11.5584726333618</v>
+        <v>11.5584716796875</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G814" t="n">
-        <v>11.6509389877319</v>
+        <v>11.6509399414062</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G815" t="n">
-        <v>11.6509389877319</v>
+        <v>11.6509399414062</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>12.75</v>
       </c>
       <c r="G816" t="n">
-        <v>11.7896423339844</v>
+        <v>11.7896413803101</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G817" t="n">
-        <v>11.6509389877319</v>
+        <v>11.6509399414062</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G818" t="n">
-        <v>11.6509389877319</v>
+        <v>11.6509399414062</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G819" t="n">
-        <v>11.6971740722656</v>
+        <v>11.6971750259399</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G824" t="n">
-        <v>11.6509389877319</v>
+        <v>11.6509399414062</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G825" t="n">
-        <v>11.9745769500732</v>
+        <v>11.9745779037476</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G826" t="n">
-        <v>12.067045211792</v>
+        <v>12.0670442581177</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>12.3444490432739</v>
+        <v>12.3444480895996</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G828" t="n">
-        <v>12.8992547988892</v>
+        <v>12.8992538452148</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G829" t="n">
-        <v>13.1304244995117</v>
+        <v>13.1304235458374</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G830" t="n">
-        <v>13.4540605545044</v>
+        <v>13.4540615081787</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>15.75</v>
       </c>
       <c r="G834" t="n">
-        <v>14.5636758804321</v>
+        <v>14.5636749267578</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G835" t="n">
-        <v>15.3496532440186</v>
+        <v>15.3496503829956</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>16.25</v>
       </c>
       <c r="G836" t="n">
-        <v>15.0260133743286</v>
+        <v>15.0260124206543</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G838" t="n">
-        <v>16.4592628479004</v>
+        <v>16.459264755249</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G842" t="n">
-        <v>16.0431613922119</v>
+        <v>16.0431594848633</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>17</v>
       </c>
       <c r="G843" t="n">
-        <v>15.719521522522</v>
+        <v>15.7195205688477</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G844" t="n">
-        <v>15.3496532440186</v>
+        <v>15.3496503829956</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G845" t="n">
-        <v>15.1647167205811</v>
+        <v>15.1647148132324</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G849" t="n">
-        <v>15.2109508514404</v>
+        <v>15.2109498977661</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G850" t="n">
-        <v>15.6270542144775</v>
+        <v>15.6270523071289</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G851" t="n">
-        <v>15.9969263076782</v>
+        <v>15.9969253540039</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G852" t="n">
-        <v>15.9969263076782</v>
+        <v>15.9969253540039</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G853" t="n">
-        <v>15.8119888305664</v>
+        <v>15.8119916915894</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G854" t="n">
-        <v>15.395884513855</v>
+        <v>15.3958864212036</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G855" t="n">
-        <v>15.1647167205811</v>
+        <v>15.1647148132324</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>14.9797821044922</v>
+        <v>14.9797811508179</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G857" t="n">
-        <v>14.748610496521</v>
+        <v>14.7486095428467</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G859" t="n">
-        <v>13.9164018630981</v>
+        <v>13.9163999557495</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G864" t="n">
-        <v>13.1304244995117</v>
+        <v>13.1304235458374</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G867" t="n">
-        <v>15.3496532440186</v>
+        <v>15.3496503829956</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G868" t="n">
-        <v>15.6732883453369</v>
+        <v>15.6732902526855</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G870" t="n">
-        <v>15.3496532440186</v>
+        <v>15.3496503829956</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G871" t="n">
-        <v>14.9797821044922</v>
+        <v>14.9797811508179</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G872" t="n">
-        <v>15.0722455978394</v>
+        <v>15.0722465515137</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G873" t="n">
-        <v>14.748610496521</v>
+        <v>14.7486095428467</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G874" t="n">
-        <v>14.5174407958984</v>
+        <v>14.5174417495728</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23119,7 +23119,7 @@
         <v>16</v>
       </c>
       <c r="G875" t="n">
-        <v>14.7948455810547</v>
+        <v>14.7948436737061</v>
       </c>
       <c r="H875" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G877" t="n">
-        <v>14.2862720489502</v>
+        <v>14.2862710952759</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G879" t="n">
-        <v>14.702374458313</v>
+        <v>14.7023773193359</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>15.25</v>
       </c>
       <c r="G881" t="n">
-        <v>14.101336479187</v>
+        <v>14.1013355255127</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G884" t="n">
-        <v>13.9164018630981</v>
+        <v>13.9163999557495</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23431,7 +23431,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G887" t="n">
-        <v>13.4540605545044</v>
+        <v>13.4540615081787</v>
       </c>
       <c r="H887" t="s">
         <v>8</v>
@@ -23457,7 +23457,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G888" t="n">
-        <v>13.3153600692749</v>
+        <v>13.3153581619263</v>
       </c>
       <c r="H888" t="s">
         <v>8</v>
@@ -23483,7 +23483,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G889" t="n">
-        <v>13.2228918075562</v>
+        <v>13.2228937149048</v>
       </c>
       <c r="H889" t="s">
         <v>8</v>
@@ -23509,7 +23509,7 @@
         <v>14.75</v>
       </c>
       <c r="G890" t="n">
-        <v>13.6389970779419</v>
+        <v>13.6389961242676</v>
       </c>
       <c r="H890" t="s">
         <v>8</v>
@@ -23535,7 +23535,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>13.5927639007568</v>
+        <v>13.5927629470825</v>
       </c>
       <c r="H891" t="s">
         <v>8</v>
@@ -23561,7 +23561,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G892" t="n">
-        <v>13.5002965927124</v>
+        <v>13.5002956390381</v>
       </c>
       <c r="H892" t="s">
         <v>8</v>
@@ -23587,7 +23587,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G893" t="n">
-        <v>13.685230255127</v>
+        <v>13.6852321624756</v>
       </c>
       <c r="H893" t="s">
         <v>8</v>
@@ -23639,7 +23639,7 @@
         <v>16</v>
       </c>
       <c r="G895" t="n">
-        <v>14.7948455810547</v>
+        <v>14.7948436737061</v>
       </c>
       <c r="H895" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G896" t="n">
-        <v>14.5174407958984</v>
+        <v>14.5174417495728</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>16</v>
       </c>
       <c r="G898" t="n">
-        <v>14.7948455810547</v>
+        <v>14.7948436737061</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23743,7 +23743,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G899" t="n">
-        <v>15.6732883453369</v>
+        <v>15.6732902526855</v>
       </c>
       <c r="H899" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G901" t="n">
-        <v>15.1647167205811</v>
+        <v>15.1647148132324</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23821,7 +23821,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G902" t="n">
-        <v>15.0722455978394</v>
+        <v>15.0722465515137</v>
       </c>
       <c r="H902" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G904" t="n">
-        <v>15.2109508514404</v>
+        <v>15.2109498977661</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G905" t="n">
-        <v>15.0722455978394</v>
+        <v>15.0722465515137</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G906" t="n">
-        <v>15.5345869064331</v>
+        <v>15.5345859527588</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G907" t="n">
-        <v>15.3496532440186</v>
+        <v>15.3496503829956</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G908" t="n">
-        <v>15.118480682373</v>
+        <v>15.118483543396</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24029,7 +24029,7 @@
         <v>16</v>
       </c>
       <c r="G910" t="n">
-        <v>14.7948455810547</v>
+        <v>14.7948436737061</v>
       </c>
       <c r="H910" t="s">
         <v>8</v>
@@ -24055,7 +24055,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G911" t="n">
-        <v>14.748610496521</v>
+        <v>14.7486095428467</v>
       </c>
       <c r="H911" t="s">
         <v>8</v>
@@ -24159,7 +24159,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G915" t="n">
-        <v>13.9626340866089</v>
+        <v>13.9626350402832</v>
       </c>
       <c r="H915" t="s">
         <v>8</v>
@@ -24185,7 +24185,7 @@
         <v>15.25</v>
       </c>
       <c r="G916" t="n">
-        <v>14.101336479187</v>
+        <v>14.1013355255127</v>
       </c>
       <c r="H916" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>15.25</v>
       </c>
       <c r="G918" t="n">
-        <v>14.101336479187</v>
+        <v>14.1013355255127</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G919" t="n">
-        <v>14.5174407958984</v>
+        <v>14.5174417495728</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>15.25</v>
       </c>
       <c r="G922" t="n">
-        <v>14.101336479187</v>
+        <v>14.1013355255127</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24367,7 +24367,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G923" t="n">
-        <v>13.5927639007568</v>
+        <v>13.5927629470825</v>
       </c>
       <c r="H923" t="s">
         <v>8</v>
@@ -24393,7 +24393,7 @@
         <v>15</v>
       </c>
       <c r="G924" t="n">
-        <v>13.8701667785645</v>
+        <v>13.8701658248901</v>
       </c>
       <c r="H924" t="s">
         <v>8</v>
@@ -24445,7 +24445,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G926" t="n">
-        <v>14.2862720489502</v>
+        <v>14.2862710952759</v>
       </c>
       <c r="H926" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>15.25</v>
       </c>
       <c r="G929" t="n">
-        <v>14.101336479187</v>
+        <v>14.1013355255127</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G931" t="n">
-        <v>15.0722455978394</v>
+        <v>15.0722465515137</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G933" t="n">
-        <v>15.1647167205811</v>
+        <v>15.1647148132324</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>16</v>
       </c>
       <c r="G934" t="n">
-        <v>14.7948455810547</v>
+        <v>14.7948436737061</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G935" t="n">
-        <v>14.702374458313</v>
+        <v>14.7023773193359</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24705,7 +24705,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G936" t="n">
-        <v>14.9797821044922</v>
+        <v>14.9797811508179</v>
       </c>
       <c r="H936" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G938" t="n">
-        <v>14.748610496521</v>
+        <v>14.7486095428467</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G939" t="n">
-        <v>14.5174407958984</v>
+        <v>14.5174417495728</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G940" t="n">
-        <v>14.702374458313</v>
+        <v>14.7023773193359</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24835,7 +24835,7 @@
         <v>15.75</v>
       </c>
       <c r="G941" t="n">
-        <v>14.5636758804321</v>
+        <v>14.5636749267578</v>
       </c>
       <c r="H941" t="s">
         <v>8</v>
@@ -24861,7 +24861,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G942" t="n">
-        <v>14.2862720489502</v>
+        <v>14.2862710952759</v>
       </c>
       <c r="H942" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G943" t="n">
-        <v>14.702374458313</v>
+        <v>14.7023773193359</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G947" t="n">
-        <v>14.6099081039429</v>
+        <v>14.6099090576172</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25069,7 +25069,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G950" t="n">
-        <v>13.685230255127</v>
+        <v>13.6852321624756</v>
       </c>
       <c r="H950" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G952" t="n">
-        <v>13.9164018630981</v>
+        <v>13.9163999557495</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>15.25</v>
       </c>
       <c r="G953" t="n">
-        <v>14.101336479187</v>
+        <v>14.1013355255127</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>15.25</v>
       </c>
       <c r="G954" t="n">
-        <v>14.101336479187</v>
+        <v>14.1013355255127</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>15</v>
       </c>
       <c r="G955" t="n">
-        <v>13.8701667785645</v>
+        <v>13.8701658248901</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G960" t="n">
-        <v>13.9626340866089</v>
+        <v>13.9626350402832</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G964" t="n">
-        <v>13.4540605545044</v>
+        <v>13.4540615081787</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>15</v>
       </c>
       <c r="G965" t="n">
-        <v>13.8701667785645</v>
+        <v>13.8701658248901</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G968" t="n">
-        <v>14.2862720489502</v>
+        <v>14.2862710952759</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>15.5</v>
       </c>
       <c r="G970" t="n">
-        <v>14.3325052261353</v>
+        <v>14.3325061798096</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G971" t="n">
-        <v>14.6099081039429</v>
+        <v>14.6099090576172</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G973" t="n">
-        <v>14.4989490509033</v>
+        <v>14.4989471435547</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G974" t="n">
-        <v>14.4804534912109</v>
+        <v>14.4804544448853</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G975" t="n">
-        <v>14.3509998321533</v>
+        <v>14.350998878479</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G976" t="n">
-        <v>14.5359334945679</v>
+        <v>14.5359344482422</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G977" t="n">
-        <v>14.702374458313</v>
+        <v>14.7023773193359</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>16</v>
       </c>
       <c r="G978" t="n">
-        <v>14.7948455810547</v>
+        <v>14.7948436737061</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>16</v>
       </c>
       <c r="G979" t="n">
-        <v>14.7948455810547</v>
+        <v>14.7948436737061</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G980" t="n">
-        <v>14.5174407958984</v>
+        <v>14.5174417495728</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G982" t="n">
-        <v>14.7763500213623</v>
+        <v>14.7763509750366</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>16</v>
       </c>
       <c r="G985" t="n">
-        <v>14.7948455810547</v>
+        <v>14.7948436737061</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G986" t="n">
-        <v>15.0352592468262</v>
+        <v>15.0352602005005</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G987" t="n">
-        <v>14.9982719421387</v>
+        <v>14.9982738494873</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G988" t="n">
-        <v>15.1092338562012</v>
+        <v>15.1092348098755</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G989" t="n">
-        <v>15.0722455978394</v>
+        <v>15.0722465515137</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26109,7 +26109,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G990" t="n">
-        <v>14.5359334945679</v>
+        <v>14.5359344482422</v>
       </c>
       <c r="H990" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G991" t="n">
-        <v>14.702374458313</v>
+        <v>14.7023773193359</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26161,7 +26161,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G992" t="n">
-        <v>14.9612874984741</v>
+        <v>14.9612865447998</v>
       </c>
       <c r="H992" t="s">
         <v>8</v>
@@ -26187,7 +26187,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G993" t="n">
-        <v>14.9612874984741</v>
+        <v>14.9612865447998</v>
       </c>
       <c r="H993" t="s">
         <v>8</v>
@@ -26213,7 +26213,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G994" t="n">
-        <v>15.263768196106</v>
+        <v>15.2637691497803</v>
       </c>
       <c r="H994" t="s">
         <v>8</v>
@@ -26239,7 +26239,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G995" t="n">
-        <v>14.8728675842285</v>
+        <v>14.8728685379028</v>
       </c>
       <c r="H995" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G996" t="n">
-        <v>14.5191965103149</v>
+        <v>14.5191955566406</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G998" t="n">
-        <v>14.9845542907715</v>
+        <v>14.9845552444458</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G999" t="n">
-        <v>15.1334676742554</v>
+        <v>15.1334686279297</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1000" t="n">
-        <v>15.1706981658936</v>
+        <v>15.1706972122192</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26395,7 +26395,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1001" t="n">
-        <v>15.2265434265137</v>
+        <v>15.2265424728394</v>
       </c>
       <c r="H1001" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1002" t="n">
-        <v>15.2079277038574</v>
+        <v>15.2079267501831</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1003" t="n">
-        <v>14.9845542907715</v>
+        <v>14.9845552444458</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>16.4699993133545</v>
       </c>
       <c r="G1004" t="n">
-        <v>15.3289213180542</v>
+        <v>15.3289203643799</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26499,7 +26499,7 @@
         <v>17.3120002746582</v>
       </c>
       <c r="G1005" t="n">
-        <v>16.112585067749</v>
+        <v>16.1125831604004</v>
       </c>
       <c r="H1005" t="s">
         <v>8</v>
@@ -26525,7 +26525,7 @@
         <v>17.75</v>
       </c>
       <c r="G1006" t="n">
-        <v>16.5202407836914</v>
+        <v>16.5202388763428</v>
       </c>
       <c r="H1006" t="s">
         <v>8</v>
@@ -26551,7 +26551,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1007" t="n">
-        <v>16.5667762756348</v>
+        <v>16.5667743682861</v>
       </c>
       <c r="H1007" t="s">
         <v>8</v>
@@ -26603,7 +26603,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1009" t="n">
-        <v>17.9814643859863</v>
+        <v>17.981466293335</v>
       </c>
       <c r="H1009" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1015" t="n">
-        <v>16.6040019989014</v>
+        <v>16.60400390625</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26785,7 +26785,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G1016" t="n">
-        <v>16.5295448303223</v>
+        <v>16.5295467376709</v>
       </c>
       <c r="H1016" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1017" t="n">
-        <v>16.2503318786621</v>
+        <v>16.2503299713135</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1018" t="n">
-        <v>16.473705291748</v>
+        <v>16.4737033843994</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26863,7 +26863,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1019" t="n">
-        <v>16.3992443084717</v>
+        <v>16.3992462158203</v>
       </c>
       <c r="H1019" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1020" t="n">
-        <v>16.492317199707</v>
+        <v>16.4923152923584</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G1022" t="n">
-        <v>17.1624355316162</v>
+        <v>17.1624336242676</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -26967,7 +26967,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1023" t="n">
-        <v>17.5905647277832</v>
+        <v>17.5905609130859</v>
       </c>
       <c r="H1023" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1027" t="n">
-        <v>17.9814643859863</v>
+        <v>17.981466293335</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27097,7 +27097,7 @@
         <v>19.0400009155273</v>
       </c>
       <c r="G1028" t="n">
-        <v>17.7208671569824</v>
+        <v>17.7208652496338</v>
       </c>
       <c r="H1028" t="s">
         <v>8</v>
@@ -27123,7 +27123,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1029" t="n">
-        <v>17.7767066955566</v>
+        <v>17.7767086029053</v>
       </c>
       <c r="H1029" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1030" t="n">
-        <v>17.7767066955566</v>
+        <v>17.7767086029053</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1032" t="n">
-        <v>17.7953243255615</v>
+        <v>17.7953224182129</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1033" t="n">
-        <v>17.7767066955566</v>
+        <v>17.7767086029053</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G1034" t="n">
-        <v>17.7580909729004</v>
+        <v>17.7580947875977</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27305,7 +27305,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1036" t="n">
-        <v>18.297908782959</v>
+        <v>18.2979106903076</v>
       </c>
       <c r="H1036" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1037" t="n">
-        <v>17.7953243255615</v>
+        <v>17.7953224182129</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>19.7000007629395</v>
       </c>
       <c r="G1040" t="n">
-        <v>18.3351383209229</v>
+        <v>18.3351402282715</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1042" t="n">
-        <v>18.297908782959</v>
+        <v>18.2979106903076</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1043" t="n">
-        <v>17.4416484832764</v>
+        <v>17.441650390625</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27591,7 +27591,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1047" t="n">
-        <v>17.5905647277832</v>
+        <v>17.5905609130859</v>
       </c>
       <c r="H1047" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1048" t="n">
-        <v>17.5905647277832</v>
+        <v>17.5905609130859</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>19.0599994659424</v>
       </c>
       <c r="G1049" t="n">
-        <v>17.7394790649414</v>
+        <v>17.7394771575928</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27721,7 +27721,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1052" t="n">
-        <v>17.9814643859863</v>
+        <v>17.981466293335</v>
       </c>
       <c r="H1052" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1053" t="n">
-        <v>18.2420654296875</v>
+        <v>18.2420673370361</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1059" t="n">
-        <v>20.5688610076904</v>
+        <v>20.5688629150391</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1060" t="n">
-        <v>20.8480739593506</v>
+        <v>20.8480758666992</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>23</v>
       </c>
       <c r="G1062" t="n">
-        <v>21.4065074920654</v>
+        <v>21.4065036773682</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>23.2800006866455</v>
       </c>
       <c r="G1064" t="n">
-        <v>21.667106628418</v>
+        <v>21.6671085357666</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28189,7 +28189,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1070" t="n">
-        <v>22.0393962860107</v>
+        <v>22.0393943786621</v>
       </c>
       <c r="H1070" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>23.2800006866455</v>
       </c>
       <c r="G1071" t="n">
-        <v>21.667106628418</v>
+        <v>21.6671085357666</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28241,7 +28241,7 @@
         <v>23.5</v>
       </c>
       <c r="G1072" t="n">
-        <v>21.871862411499</v>
+        <v>21.8718662261963</v>
       </c>
       <c r="H1072" t="s">
         <v>8</v>
@@ -28293,7 +28293,7 @@
         <v>23.9799995422363</v>
       </c>
       <c r="G1074" t="n">
-        <v>22.3186073303223</v>
+        <v>22.3186092376709</v>
       </c>
       <c r="H1074" t="s">
         <v>8</v>
@@ -28319,7 +28319,7 @@
         <v>24.2399997711182</v>
       </c>
       <c r="G1075" t="n">
-        <v>22.5605983734131</v>
+        <v>22.5605964660645</v>
       </c>
       <c r="H1075" t="s">
         <v>8</v>
@@ -28345,7 +28345,7 @@
         <v>25.2199993133545</v>
       </c>
       <c r="G1076" t="n">
-        <v>23.4727001190186</v>
+        <v>23.4726982116699</v>
       </c>
       <c r="H1076" t="s">
         <v>8</v>
@@ -28371,7 +28371,7 @@
         <v>26.3600006103516</v>
       </c>
       <c r="G1077" t="n">
-        <v>24.5337162017822</v>
+        <v>24.5337181091309</v>
       </c>
       <c r="H1077" t="s">
         <v>8</v>
@@ -28501,7 +28501,7 @@
         <v>27.0599994659424</v>
       </c>
       <c r="G1082" t="n">
-        <v>25.1852188110352</v>
+        <v>25.1852207183838</v>
       </c>
       <c r="H1082" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1083" t="n">
-        <v>24.384801864624</v>
+        <v>24.3848037719727</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>26.1800003051758</v>
       </c>
       <c r="G1084" t="n">
-        <v>24.366189956665</v>
+        <v>24.3661861419678</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>26.1599998474121</v>
       </c>
       <c r="G1089" t="n">
-        <v>24.3475761413574</v>
+        <v>24.3475742340088</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>27.3199996948242</v>
       </c>
       <c r="G1090" t="n">
-        <v>25.4272079467773</v>
+        <v>25.4272060394287</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>27.2199993133545</v>
       </c>
       <c r="G1091" t="n">
-        <v>25.3341369628906</v>
+        <v>25.334135055542</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>26.1800003051758</v>
       </c>
       <c r="G1093" t="n">
-        <v>24.366189956665</v>
+        <v>24.3661861419678</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>24.5400009155273</v>
       </c>
       <c r="G1097" t="n">
-        <v>22.8398132324219</v>
+        <v>22.8398113250732</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>25</v>
       </c>
       <c r="G1098" t="n">
-        <v>23.2679424285889</v>
+        <v>23.2679405212402</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -28943,7 +28943,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G1099" t="n">
-        <v>22.8770389556885</v>
+        <v>22.8770427703857</v>
       </c>
       <c r="H1099" t="s">
         <v>8</v>
@@ -28969,7 +28969,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1100" t="n">
-        <v>23.547155380249</v>
+        <v>23.5471591949463</v>
       </c>
       <c r="H1100" t="s">
         <v>8</v>
@@ -28995,7 +28995,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1101" t="n">
-        <v>23.547155380249</v>
+        <v>23.5471591949463</v>
       </c>
       <c r="H1101" t="s">
         <v>8</v>
@@ -29125,7 +29125,7 @@
         <v>26.5400009155273</v>
       </c>
       <c r="G1106" t="n">
-        <v>24.7012500762939</v>
+        <v>24.7012481689453</v>
       </c>
       <c r="H1106" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>26.5</v>
       </c>
       <c r="G1107" t="n">
-        <v>24.6640186309814</v>
+        <v>24.6640205383301</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29177,7 +29177,7 @@
         <v>26.5799999237061</v>
       </c>
       <c r="G1108" t="n">
-        <v>24.7384738922119</v>
+        <v>24.7384757995605</v>
       </c>
       <c r="H1108" t="s">
         <v>8</v>
@@ -29203,7 +29203,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1109" t="n">
-        <v>26.8046684265137</v>
+        <v>26.804666519165</v>
       </c>
       <c r="H1109" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>29</v>
       </c>
       <c r="G1110" t="n">
-        <v>26.9908123016357</v>
+        <v>26.9908142089844</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1111" t="n">
-        <v>26.8046684265137</v>
+        <v>26.804666519165</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>31.4400005340576</v>
       </c>
       <c r="G1112" t="n">
-        <v>29.2617645263672</v>
+        <v>29.2617626190186</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29333,7 +29333,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G1114" t="n">
-        <v>29.6898937225342</v>
+        <v>29.6898918151855</v>
       </c>
       <c r="H1114" t="s">
         <v>8</v>
@@ -29385,7 +29385,7 @@
         <v>30.9799995422363</v>
       </c>
       <c r="G1116" t="n">
-        <v>28.8336315155029</v>
+        <v>28.8336334228516</v>
       </c>
       <c r="H1116" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>30.5200004577637</v>
       </c>
       <c r="G1118" t="n">
-        <v>28.4055023193359</v>
+        <v>28.4055042266846</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>30.8400001525879</v>
       </c>
       <c r="G1119" t="n">
-        <v>28.7033348083496</v>
+        <v>28.703332901001</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>32.1199989318848</v>
       </c>
       <c r="G1121" t="n">
-        <v>29.8946514129639</v>
+        <v>29.8946495056152</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>32.439998626709</v>
       </c>
       <c r="G1123" t="n">
-        <v>30.1924800872803</v>
+        <v>30.1924819946289</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>33.5800018310547</v>
       </c>
       <c r="G1125" t="n">
-        <v>31.2535018920898</v>
+        <v>31.2534999847412</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>33.5400009155273</v>
       </c>
       <c r="G1127" t="n">
-        <v>31.2162704467773</v>
+        <v>31.216272354126</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>36.9000015258789</v>
       </c>
       <c r="G1128" t="n">
-        <v>34.3434829711914</v>
+        <v>34.3434867858887</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>33.5</v>
       </c>
       <c r="G1129" t="n">
-        <v>31.1790390014648</v>
+        <v>31.1790447235107</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>33.6599998474121</v>
       </c>
       <c r="G1130" t="n">
-        <v>31.3279590606689</v>
+        <v>31.3279609680176</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29801,7 +29801,7 @@
         <v>32.9599990844727</v>
       </c>
       <c r="G1132" t="n">
-        <v>30.6764526367188</v>
+        <v>30.6764545440674</v>
       </c>
       <c r="H1132" t="s">
         <v>8</v>
@@ -29827,7 +29827,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1133" t="n">
-        <v>30.5275363922119</v>
+        <v>30.5275382995605</v>
       </c>
       <c r="H1133" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>31.6200008392334</v>
       </c>
       <c r="G1134" t="n">
-        <v>29.4292945861816</v>
+        <v>29.4292964935303</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1135" t="n">
-        <v>28.9453201293945</v>
+        <v>28.9453182220459</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>32.4199981689453</v>
       </c>
       <c r="G1136" t="n">
-        <v>30.173864364624</v>
+        <v>30.1738662719727</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>32.8199996948242</v>
       </c>
       <c r="G1140" t="n">
-        <v>30.5461559295654</v>
+        <v>30.5461540222168</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>33.4599990844727</v>
       </c>
       <c r="G1143" t="n">
-        <v>31.1418151855469</v>
+        <v>31.1418132781982</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30113,7 +30113,7 @@
         <v>34.439998626709</v>
       </c>
       <c r="G1144" t="n">
-        <v>32.0539169311523</v>
+        <v>32.0539207458496</v>
       </c>
       <c r="H1144" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>36.1199989318848</v>
       </c>
       <c r="G1145" t="n">
-        <v>33.6175231933594</v>
+        <v>33.6175193786621</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G1147" t="n">
-        <v>32.7612609863281</v>
+        <v>32.7612648010254</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>36</v>
       </c>
       <c r="G1148" t="n">
-        <v>33.5058326721191</v>
+        <v>33.5058364868164</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G1151" t="n">
-        <v>31.5513286590576</v>
+        <v>31.5513324737549</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>33.6199989318848</v>
       </c>
       <c r="G1152" t="n">
-        <v>31.2907276153564</v>
+        <v>31.2907257080078</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -30347,7 +30347,7 @@
         <v>33.9199981689453</v>
       </c>
       <c r="G1153" t="n">
-        <v>31.5699405670166</v>
+        <v>31.5699424743652</v>
       </c>
       <c r="H1153" t="s">
         <v>8</v>
@@ -30373,7 +30373,7 @@
         <v>34.1800003051758</v>
       </c>
       <c r="G1154" t="n">
-        <v>31.8119335174561</v>
+        <v>31.8119316101074</v>
       </c>
       <c r="H1154" t="s">
         <v>8</v>
@@ -30425,7 +30425,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G1156" t="n">
-        <v>33.7850494384766</v>
+        <v>33.7850532531738</v>
       </c>
       <c r="H1156" t="s">
         <v>8</v>
@@ -30477,7 +30477,7 @@
         <v>36.2799987792969</v>
       </c>
       <c r="G1158" t="n">
-        <v>33.766429901123</v>
+        <v>33.7664375305176</v>
       </c>
       <c r="H1158" t="s">
         <v>8</v>
@@ -30529,7 +30529,7 @@
         <v>35.6800003051758</v>
       </c>
       <c r="G1160" t="n">
-        <v>33.2080039978027</v>
+        <v>33.2080078125</v>
       </c>
       <c r="H1160" t="s">
         <v>8</v>
@@ -30581,7 +30581,7 @@
         <v>36.0200004577637</v>
       </c>
       <c r="G1162" t="n">
-        <v>33.5244522094727</v>
+        <v>33.5244483947754</v>
       </c>
       <c r="H1162" t="s">
         <v>8</v>
@@ -30607,7 +30607,7 @@
         <v>37.9799995422363</v>
       </c>
       <c r="G1163" t="n">
-        <v>35.3486557006836</v>
+        <v>35.3486595153809</v>
       </c>
       <c r="H1163" t="s">
         <v>8</v>
@@ -30633,7 +30633,7 @@
         <v>39.7000007629395</v>
       </c>
       <c r="G1164" t="n">
-        <v>36.9494934082031</v>
+        <v>36.9494972229004</v>
       </c>
       <c r="H1164" t="s">
         <v>8</v>
@@ -30659,7 +30659,7 @@
         <v>38.060001373291</v>
       </c>
       <c r="G1165" t="n">
-        <v>35.4231147766113</v>
+        <v>35.4231185913086</v>
       </c>
       <c r="H1165" t="s">
         <v>8</v>
@@ -30685,7 +30685,7 @@
         <v>36</v>
       </c>
       <c r="G1166" t="n">
-        <v>33.5058326721191</v>
+        <v>33.5058364868164</v>
       </c>
       <c r="H1166" t="s">
         <v>8</v>
@@ -30711,7 +30711,7 @@
         <v>33.5400009155273</v>
       </c>
       <c r="G1167" t="n">
-        <v>31.2162704467773</v>
+        <v>31.216272354126</v>
       </c>
       <c r="H1167" t="s">
         <v>8</v>
@@ -30737,7 +30737,7 @@
         <v>34</v>
       </c>
       <c r="G1168" t="n">
-        <v>31.644401550293</v>
+        <v>31.6443977355957</v>
       </c>
       <c r="H1168" t="s">
         <v>8</v>
@@ -30763,7 +30763,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G1169" t="n">
-        <v>32.482048034668</v>
+        <v>32.4820518493652</v>
       </c>
       <c r="H1169" t="s">
         <v>8</v>
@@ -30789,7 +30789,7 @@
         <v>35.5</v>
       </c>
       <c r="G1170" t="n">
-        <v>33.0404815673828</v>
+        <v>33.0404777526855</v>
       </c>
       <c r="H1170" t="s">
         <v>8</v>
@@ -30815,7 +30815,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G1171" t="n">
-        <v>32.482048034668</v>
+        <v>32.4820518493652</v>
       </c>
       <c r="H1171" t="s">
         <v>8</v>
@@ -30919,7 +30919,7 @@
         <v>34.7400016784668</v>
       </c>
       <c r="G1175" t="n">
-        <v>32.3331298828125</v>
+        <v>32.3331336975098</v>
       </c>
       <c r="H1175" t="s">
         <v>8</v>
@@ -30945,7 +30945,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1176" t="n">
-        <v>30.8998279571533</v>
+        <v>30.8998260498047</v>
       </c>
       <c r="H1176" t="s">
         <v>8</v>
@@ -30971,7 +30971,7 @@
         <v>30.8400001525879</v>
       </c>
       <c r="G1177" t="n">
-        <v>28.7033348083496</v>
+        <v>28.703332901001</v>
       </c>
       <c r="H1177" t="s">
         <v>8</v>
@@ -30997,7 +30997,7 @@
         <v>29.9200000762939</v>
       </c>
       <c r="G1178" t="n">
-        <v>27.8470726013184</v>
+        <v>27.847074508667</v>
       </c>
       <c r="H1178" t="s">
         <v>8</v>
@@ -31075,7 +31075,7 @@
         <v>30.0599994659424</v>
       </c>
       <c r="G1181" t="n">
-        <v>27.9773731231689</v>
+        <v>27.9773750305176</v>
       </c>
       <c r="H1181" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>32.5400009155273</v>
       </c>
       <c r="G1184" t="n">
-        <v>30.2855529785156</v>
+        <v>30.2855548858643</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31257,7 +31257,7 @@
         <v>29.0400009155273</v>
       </c>
       <c r="G1188" t="n">
-        <v>27.0280418395996</v>
+        <v>27.028039932251</v>
       </c>
       <c r="H1188" t="s">
         <v>8</v>
@@ -31283,7 +31283,7 @@
         <v>30.1399993896484</v>
       </c>
       <c r="G1189" t="n">
-        <v>28.051830291748</v>
+        <v>28.0518321990967</v>
       </c>
       <c r="H1189" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>29</v>
       </c>
       <c r="G1190" t="n">
-        <v>26.9908123016357</v>
+        <v>26.9908142089844</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>28.7800006866455</v>
       </c>
       <c r="G1192" t="n">
-        <v>26.7860546112061</v>
+        <v>26.7860565185547</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>29.9799995422363</v>
       </c>
       <c r="G1194" t="n">
-        <v>27.9029140472412</v>
+        <v>27.9029159545898</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>30.2800006866455</v>
       </c>
       <c r="G1195" t="n">
-        <v>28.1821327209473</v>
+        <v>28.1821308135986</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>29.0400009155273</v>
       </c>
       <c r="G1196" t="n">
-        <v>27.0280418395996</v>
+        <v>27.028039932251</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1198" t="n">
-        <v>26.8977394104004</v>
+        <v>26.897741317749</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>28.8799991607666</v>
       </c>
       <c r="G1201" t="n">
-        <v>26.8791275024414</v>
+        <v>26.8791255950928</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>28.5599994659424</v>
       </c>
       <c r="G1202" t="n">
-        <v>26.5812969207764</v>
+        <v>26.5812950134277</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>28.8799991607666</v>
       </c>
       <c r="G1203" t="n">
-        <v>26.8791275024414</v>
+        <v>26.8791255950928</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>26.0400009155273</v>
       </c>
       <c r="G1206" t="n">
-        <v>24.2358894348145</v>
+        <v>24.2358913421631</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>25.7800006866455</v>
       </c>
       <c r="G1207" t="n">
-        <v>23.9939041137695</v>
+        <v>23.9939022064209</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31829,7 +31829,7 @@
         <v>27.1200008392334</v>
       </c>
       <c r="G1210" t="n">
-        <v>25.2410640716553</v>
+        <v>25.2410659790039</v>
       </c>
       <c r="H1210" t="s">
         <v>8</v>
@@ -31907,7 +31907,7 @@
         <v>28.2399997711182</v>
       </c>
       <c r="G1213" t="n">
-        <v>26.28346824646</v>
+        <v>26.2834663391113</v>
       </c>
       <c r="H1213" t="s">
         <v>8</v>
@@ -32011,7 +32011,7 @@
         <v>28.8400001525879</v>
       </c>
       <c r="G1217" t="n">
-        <v>26.8418979644775</v>
+        <v>26.8418998718262</v>
       </c>
       <c r="H1217" t="s">
         <v>8</v>
@@ -32089,7 +32089,7 @@
         <v>29.5</v>
       </c>
       <c r="G1220" t="n">
-        <v>27.4561710357666</v>
+        <v>27.456169128418</v>
       </c>
       <c r="H1220" t="s">
         <v>8</v>
@@ -32141,7 +32141,7 @@
         <v>30.1200008392334</v>
       </c>
       <c r="G1222" t="n">
-        <v>28.0332183837891</v>
+        <v>28.0332145690918</v>
       </c>
       <c r="H1222" t="s">
         <v>8</v>
@@ -32219,7 +32219,7 @@
         <v>29.9599990844727</v>
       </c>
       <c r="G1225" t="n">
-        <v>27.8843040466309</v>
+        <v>27.8843002319336</v>
       </c>
       <c r="H1225" t="s">
         <v>8</v>
@@ -32271,7 +32271,7 @@
         <v>29.6399993896484</v>
       </c>
       <c r="G1227" t="n">
-        <v>27.5864715576172</v>
+        <v>27.5864696502686</v>
       </c>
       <c r="H1227" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1229" t="n">
-        <v>25.96702003479</v>
+        <v>25.9670219421387</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32349,7 +32349,7 @@
         <v>27.7399997711182</v>
       </c>
       <c r="G1230" t="n">
-        <v>25.8181076049805</v>
+        <v>25.8181095123291</v>
       </c>
       <c r="H1230" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1233" t="n">
-        <v>26.6185264587402</v>
+        <v>26.6185283660889</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1234" t="n">
-        <v>26.4323825836182</v>
+        <v>26.4323806762695</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32531,7 +32531,7 @@
         <v>27.2800006866455</v>
       </c>
       <c r="G1237" t="n">
-        <v>25.3899765014648</v>
+        <v>25.3899784088135</v>
       </c>
       <c r="H1237" t="s">
         <v>8</v>
@@ -32583,7 +32583,7 @@
         <v>26.7600002288818</v>
       </c>
       <c r="G1239" t="n">
-        <v>24.906005859375</v>
+        <v>24.9060039520264</v>
       </c>
       <c r="H1239" t="s">
         <v>8</v>
@@ -32635,7 +32635,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G1241" t="n">
-        <v>23.9647331237793</v>
+        <v>23.9647312164307</v>
       </c>
       <c r="H1241" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>25</v>
       </c>
       <c r="G1242" t="n">
-        <v>23.5317516326904</v>
+        <v>23.5317497253418</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32765,7 +32765,7 @@
         <v>25.2600002288818</v>
       </c>
       <c r="G1246" t="n">
-        <v>23.7764797210693</v>
+        <v>23.776481628418</v>
       </c>
       <c r="H1246" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G1248" t="n">
-        <v>21.6680355072021</v>
+        <v>21.6680374145508</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32869,7 +32869,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G1250" t="n">
-        <v>20.2749576568604</v>
+        <v>20.2749557495117</v>
       </c>
       <c r="H1250" t="s">
         <v>8</v>
@@ -32921,7 +32921,7 @@
         <v>21.1800003051758</v>
       </c>
       <c r="G1252" t="n">
-        <v>19.9361000061035</v>
+        <v>19.9360980987549</v>
       </c>
       <c r="H1252" t="s">
         <v>8</v>
@@ -32973,7 +32973,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="G1254" t="n">
-        <v>19.6537170410156</v>
+        <v>19.6537189483643</v>
       </c>
       <c r="H1254" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1255" t="n">
-        <v>19.2019081115723</v>
+        <v>19.2019100189209</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33103,7 +33103,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G1259" t="n">
-        <v>19.6913681030273</v>
+        <v>19.6913661956787</v>
       </c>
       <c r="H1259" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G1261" t="n">
-        <v>20.2749576568604</v>
+        <v>20.2749557495117</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33181,7 +33181,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G1262" t="n">
-        <v>19.7854957580566</v>
+        <v>19.7854976654053</v>
       </c>
       <c r="H1262" t="s">
         <v>8</v>
@@ -33233,7 +33233,7 @@
         <v>21.7000007629395</v>
       </c>
       <c r="G1264" t="n">
-        <v>20.4255599975586</v>
+        <v>20.4255619049072</v>
       </c>
       <c r="H1264" t="s">
         <v>8</v>
@@ -33285,7 +33285,7 @@
         <v>22</v>
       </c>
       <c r="G1266" t="n">
-        <v>20.7079410552979</v>
+        <v>20.7079391479492</v>
       </c>
       <c r="H1266" t="s">
         <v>8</v>
@@ -33337,7 +33337,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1268" t="n">
-        <v>20.3314342498779</v>
+        <v>20.3314323425293</v>
       </c>
       <c r="H1268" t="s">
         <v>8</v>
@@ -33363,7 +33363,7 @@
         <v>21</v>
       </c>
       <c r="G1269" t="n">
-        <v>19.7666721343994</v>
+        <v>19.7666702270508</v>
       </c>
       <c r="H1269" t="s">
         <v>8</v>
@@ -33441,7 +33441,7 @@
         <v>21.0599994659424</v>
       </c>
       <c r="G1272" t="n">
-        <v>19.8231468200684</v>
+        <v>19.8231449127197</v>
       </c>
       <c r="H1272" t="s">
         <v>8</v>
@@ -33467,7 +33467,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G1273" t="n">
-        <v>19.7478466033936</v>
+        <v>19.7478446960449</v>
       </c>
       <c r="H1273" t="s">
         <v>8</v>
@@ -33519,7 +33519,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G1275" t="n">
-        <v>18.2888774871826</v>
+        <v>18.288875579834</v>
       </c>
       <c r="H1275" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1278" t="n">
-        <v>18.0159072875977</v>
+        <v>18.015905380249</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33623,7 +33623,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1279" t="n">
-        <v>18.2041606903076</v>
+        <v>18.2041625976562</v>
       </c>
       <c r="H1279" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1281" t="n">
-        <v>17.7147026062012</v>
+        <v>17.7147006988525</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33701,7 +33701,7 @@
         <v>19.2900009155273</v>
       </c>
       <c r="G1282" t="n">
-        <v>18.1570987701416</v>
+        <v>18.1571006774902</v>
       </c>
       <c r="H1282" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>19.0200004577637</v>
       </c>
       <c r="G1284" t="n">
-        <v>17.9029579162598</v>
+        <v>17.9029560089111</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33779,7 +33779,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1285" t="n">
-        <v>17.5264472961426</v>
+        <v>17.5264492034912</v>
       </c>
       <c r="H1285" t="s">
         <v>8</v>
@@ -33857,7 +33857,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1288" t="n">
-        <v>16.3780994415283</v>
+        <v>16.3780975341797</v>
       </c>
       <c r="H1288" t="s">
         <v>8</v>
@@ -33883,7 +33883,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G1289" t="n">
-        <v>16.2933826446533</v>
+        <v>16.293384552002</v>
       </c>
       <c r="H1289" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1290" t="n">
-        <v>16.020414352417</v>
+        <v>16.0204162597656</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G1293" t="n">
-        <v>17.3852558135986</v>
+        <v>17.3852577209473</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1294" t="n">
-        <v>18.0723857879639</v>
+        <v>18.0723838806152</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1299" t="n">
-        <v>16.4157485961914</v>
+        <v>16.41575050354</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34273,7 +34273,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G1304" t="n">
-        <v>17.6770534515381</v>
+        <v>17.6770515441895</v>
       </c>
       <c r="H1304" t="s">
         <v>8</v>
@@ -34585,7 +34585,7 @@
         <v>19.4300003051758</v>
       </c>
       <c r="G1316" t="n">
-        <v>18.2888774871826</v>
+        <v>18.288875579834</v>
       </c>
       <c r="H1316" t="s">
         <v>8</v>
@@ -34611,7 +34611,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1317" t="n">
-        <v>18.4488906860352</v>
+        <v>18.4488925933838</v>
       </c>
       <c r="H1317" t="s">
         <v>8</v>
@@ -34637,7 +34637,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G1318" t="n">
-        <v>18.3830032348633</v>
+        <v>18.3830051422119</v>
       </c>
       <c r="H1318" t="s">
         <v>8</v>
@@ -34663,7 +34663,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G1319" t="n">
-        <v>18.6089096069336</v>
+        <v>18.6089115142822</v>
       </c>
       <c r="H1319" t="s">
         <v>8</v>
@@ -34715,7 +34715,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G1321" t="n">
-        <v>18.0347328186035</v>
+        <v>18.0347347259521</v>
       </c>
       <c r="H1321" t="s">
         <v>8</v>
@@ -34741,7 +34741,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1322" t="n">
-        <v>17.5264472961426</v>
+        <v>17.5264492034912</v>
       </c>
       <c r="H1322" t="s">
         <v>8</v>
@@ -34819,7 +34819,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G1325" t="n">
-        <v>16.7169551849365</v>
+        <v>16.7169570922852</v>
       </c>
       <c r="H1325" t="s">
         <v>8</v>
@@ -34923,7 +34923,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1329" t="n">
-        <v>16.0392436981201</v>
+        <v>16.0392417907715</v>
       </c>
       <c r="H1329" t="s">
         <v>8</v>
@@ -34949,7 +34949,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1330" t="n">
-        <v>16.2839698791504</v>
+        <v>16.283971786499</v>
       </c>
       <c r="H1330" t="s">
         <v>8</v>
@@ -35001,7 +35001,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1332" t="n">
-        <v>16.5851764678955</v>
+        <v>16.5851783752441</v>
       </c>
       <c r="H1332" t="s">
         <v>8</v>
@@ -35079,7 +35079,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1335" t="n">
-        <v>16.6134166717529</v>
+        <v>16.6134147644043</v>
       </c>
       <c r="H1335" t="s">
         <v>8</v>
@@ -35105,7 +35105,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1336" t="n">
-        <v>16.6134166717529</v>
+        <v>16.6134147644043</v>
       </c>
       <c r="H1336" t="s">
         <v>8</v>
@@ -35157,7 +35157,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1338" t="n">
-        <v>17.244068145752</v>
+        <v>17.2440662384033</v>
       </c>
       <c r="H1338" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1341" t="n">
-        <v>16.6793041229248</v>
+        <v>16.6793022155762</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1343" t="n">
-        <v>15.6815595626831</v>
+        <v>15.6815576553345</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35339,7 +35339,7 @@
         <v>15.2299995422363</v>
       </c>
       <c r="G1345" t="n">
-        <v>14.335542678833</v>
+        <v>14.3355417251587</v>
       </c>
       <c r="H1345" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1347" t="n">
-        <v>13.6954784393311</v>
+        <v>13.6954793930054</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35443,7 +35443,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1349" t="n">
-        <v>13.4601612091064</v>
+        <v>13.4601621627808</v>
       </c>
       <c r="H1349" t="s">
         <v>8</v>
@@ -35495,7 +35495,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1351" t="n">
-        <v>13.0271768569946</v>
+        <v>13.0271778106689</v>
       </c>
       <c r="H1351" t="s">
         <v>8</v>
@@ -35547,7 +35547,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G1353" t="n">
-        <v>13.1213045120239</v>
+        <v>13.1213035583496</v>
       </c>
       <c r="H1353" t="s">
         <v>8</v>
@@ -35573,7 +35573,7 @@
         <v>14.2700004577637</v>
       </c>
       <c r="G1354" t="n">
-        <v>13.4319229125977</v>
+        <v>13.431923866272</v>
       </c>
       <c r="H1354" t="s">
         <v>8</v>
@@ -35625,7 +35625,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1356" t="n">
-        <v>13.6954784393311</v>
+        <v>13.6954793930054</v>
       </c>
       <c r="H1356" t="s">
         <v>8</v>
@@ -35651,7 +35651,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G1357" t="n">
-        <v>13.7801923751831</v>
+        <v>13.7801933288574</v>
       </c>
       <c r="H1357" t="s">
         <v>8</v>
@@ -35677,7 +35677,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G1358" t="n">
-        <v>13.337797164917</v>
+        <v>13.3377962112427</v>
       </c>
       <c r="H1358" t="s">
         <v>8</v>
@@ -35703,7 +35703,7 @@
         <v>14.1400003433228</v>
       </c>
       <c r="G1359" t="n">
-        <v>13.3095579147339</v>
+        <v>13.3095588684082</v>
       </c>
       <c r="H1359" t="s">
         <v>8</v>
@@ -35807,7 +35807,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G1363" t="n">
-        <v>13.3472089767456</v>
+        <v>13.3472099304199</v>
       </c>
       <c r="H1363" t="s">
         <v>8</v>
@@ -35833,7 +35833,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1364" t="n">
-        <v>13.3660345077515</v>
+        <v>13.3660335540771</v>
       </c>
       <c r="H1364" t="s">
         <v>8</v>
@@ -35859,7 +35859,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1365" t="n">
-        <v>13.3660345077515</v>
+        <v>13.3660335540771</v>
       </c>
       <c r="H1365" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>14.3699998855591</v>
       </c>
       <c r="G1368" t="n">
-        <v>13.5260496139526</v>
+        <v>13.526050567627</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1369" t="n">
-        <v>13.93079662323</v>
+        <v>13.9307975769043</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1370" t="n">
-        <v>14.4955577850342</v>
+        <v>14.4955587387085</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G1371" t="n">
-        <v>15.1356229782104</v>
+        <v>15.1356220245361</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36041,7 +36041,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G1372" t="n">
-        <v>14.4955577850342</v>
+        <v>14.4955587387085</v>
       </c>
       <c r="H1372" t="s">
         <v>8</v>
@@ -36067,7 +36067,7 @@
         <v>15.5699996948242</v>
       </c>
       <c r="G1373" t="n">
-        <v>14.6555738449097</v>
+        <v>14.655574798584</v>
       </c>
       <c r="H1373" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G1376" t="n">
-        <v>14.1567010879517</v>
+        <v>14.156702041626</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>15.710000038147</v>
       </c>
       <c r="G1379" t="n">
-        <v>14.7873525619507</v>
+        <v>14.7873516082764</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1381" t="n">
-        <v>15.342700958252</v>
+        <v>15.3427000045776</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1382" t="n">
-        <v>16.3310356140137</v>
+        <v>16.331033706665</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G1383" t="n">
-        <v>16.7734317779541</v>
+        <v>16.7734298706055</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>17.5</v>
       </c>
       <c r="G1386" t="n">
-        <v>16.472225189209</v>
+        <v>16.4722232818604</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1387" t="n">
-        <v>16.1898441314697</v>
+        <v>16.1898460388184</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1389" t="n">
-        <v>16.1427803039551</v>
+        <v>16.1427822113037</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G1390" t="n">
-        <v>15.8133373260498</v>
+        <v>15.8133354187012</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1391" t="n">
-        <v>16.1898441314697</v>
+        <v>16.1898460388184</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1392" t="n">
-        <v>16.9993362426758</v>
+        <v>16.9993343353271</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>18.0300006866455</v>
       </c>
       <c r="G1394" t="n">
-        <v>16.9710998535156</v>
+        <v>16.971097946167</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G1402" t="n">
-        <v>16.9240341186523</v>
+        <v>16.9240322113037</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -36847,7 +36847,7 @@
         <v>17.8700008392334</v>
       </c>
       <c r="G1403" t="n">
-        <v>16.8204936981201</v>
+        <v>16.8204956054688</v>
       </c>
       <c r="H1403" t="s">
         <v>8</v>
@@ -36873,7 +36873,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G1404" t="n">
-        <v>16.9052104949951</v>
+        <v>16.9052085876465</v>
       </c>
       <c r="H1404" t="s">
         <v>8</v>
@@ -36977,7 +36977,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1408" t="n">
-        <v>16.5475292205811</v>
+        <v>16.5475254058838</v>
       </c>
       <c r="H1408" t="s">
         <v>8</v>
@@ -37029,7 +37029,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1410" t="n">
-        <v>16.1427803039551</v>
+        <v>16.1427822113037</v>
       </c>
       <c r="H1410" t="s">
         <v>8</v>
@@ -37081,7 +37081,7 @@
         <v>17.5</v>
       </c>
       <c r="G1412" t="n">
-        <v>16.472225189209</v>
+        <v>16.4722232818604</v>
       </c>
       <c r="H1412" t="s">
         <v>8</v>
@@ -37159,7 +37159,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1415" t="n">
-        <v>16.3969249725342</v>
+        <v>16.3969230651855</v>
       </c>
       <c r="H1415" t="s">
         <v>8</v>
@@ -37185,7 +37185,7 @@
         <v>17.6499996185303</v>
       </c>
       <c r="G1416" t="n">
-        <v>16.6134166717529</v>
+        <v>16.6134147644043</v>
       </c>
       <c r="H1416" t="s">
         <v>8</v>
@@ -37263,7 +37263,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1419" t="n">
-        <v>16.9805145263672</v>
+        <v>16.9805126190186</v>
       </c>
       <c r="H1419" t="s">
         <v>8</v>
@@ -37289,7 +37289,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1420" t="n">
-        <v>17.4511451721191</v>
+        <v>17.4511470794678</v>
       </c>
       <c r="H1420" t="s">
         <v>8</v>
@@ -37471,7 +37471,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1427" t="n">
-        <v>18.4488906860352</v>
+        <v>18.4488925933838</v>
       </c>
       <c r="H1427" t="s">
         <v>8</v>
@@ -37497,7 +37497,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G1428" t="n">
-        <v>18.9760036468506</v>
+        <v>18.9760055541992</v>
       </c>
       <c r="H1428" t="s">
         <v>8</v>
@@ -37575,7 +37575,7 @@
         <v>20.6200008392334</v>
       </c>
       <c r="G1431" t="n">
-        <v>19.4089908599854</v>
+        <v>19.4089889526367</v>
       </c>
       <c r="H1431" t="s">
         <v>8</v>
@@ -37627,7 +37627,7 @@
         <v>21.5400009155273</v>
       </c>
       <c r="G1433" t="n">
-        <v>20.2749576568604</v>
+        <v>20.2749557495117</v>
       </c>
       <c r="H1433" t="s">
         <v>8</v>
@@ -37653,7 +37653,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1434" t="n">
-        <v>20.3314342498779</v>
+        <v>20.3314323425293</v>
       </c>
       <c r="H1434" t="s">
         <v>8</v>
@@ -37679,7 +37679,7 @@
         <v>21.3199996948242</v>
       </c>
       <c r="G1435" t="n">
-        <v>20.0678749084473</v>
+        <v>20.0678768157959</v>
       </c>
       <c r="H1435" t="s">
         <v>8</v>
@@ -37705,7 +37705,7 @@
         <v>21.5</v>
       </c>
       <c r="G1436" t="n">
-        <v>20.2373046875</v>
+        <v>20.2373065948486</v>
       </c>
       <c r="H1436" t="s">
         <v>8</v>
@@ -37757,7 +37757,7 @@
         <v>21.1800003051758</v>
       </c>
       <c r="G1438" t="n">
-        <v>19.9361000061035</v>
+        <v>19.9360980987549</v>
       </c>
       <c r="H1438" t="s">
         <v>8</v>
@@ -37783,7 +37783,7 @@
         <v>21.1399993896484</v>
       </c>
       <c r="G1439" t="n">
-        <v>19.8984470367432</v>
+        <v>19.8984489440918</v>
       </c>
       <c r="H1439" t="s">
         <v>8</v>
@@ -37809,7 +37809,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>20.3314342498779</v>
+        <v>20.3314323425293</v>
       </c>
       <c r="H1440" t="s">
         <v>8</v>
@@ -37913,7 +37913,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1444" t="n">
-        <v>20.6138134002686</v>
+        <v>20.6138114929199</v>
       </c>
       <c r="H1444" t="s">
         <v>8</v>
@@ -37991,7 +37991,7 @@
         <v>21.6800003051758</v>
       </c>
       <c r="G1447" t="n">
-        <v>20.4067344665527</v>
+        <v>20.4067325592041</v>
       </c>
       <c r="H1447" t="s">
         <v>8</v>
@@ -38017,7 +38017,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1448" t="n">
-        <v>20.3314342498779</v>
+        <v>20.3314323425293</v>
       </c>
       <c r="H1448" t="s">
         <v>8</v>
@@ -38043,7 +38043,7 @@
         <v>21.3600006103516</v>
       </c>
       <c r="G1449" t="n">
-        <v>20.1055297851562</v>
+        <v>20.1055278778076</v>
       </c>
       <c r="H1449" t="s">
         <v>8</v>
@@ -38147,7 +38147,7 @@
         <v>20.9200000762939</v>
       </c>
       <c r="G1453" t="n">
-        <v>19.6913681030273</v>
+        <v>19.6913661956787</v>
       </c>
       <c r="H1453" t="s">
         <v>8</v>
@@ -38173,7 +38173,7 @@
         <v>20.6399993896484</v>
       </c>
       <c r="G1454" t="n">
-        <v>19.4278125762939</v>
+        <v>19.4278144836426</v>
       </c>
       <c r="H1454" t="s">
         <v>8</v>
@@ -38329,7 +38329,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1460" t="n">
-        <v>19.0136566162109</v>
+        <v>19.0136547088623</v>
       </c>
       <c r="H1460" t="s">
         <v>8</v>
@@ -38381,7 +38381,7 @@
         <v>20.9400005340576</v>
       </c>
       <c r="G1462" t="n">
-        <v>19.7101955413818</v>
+        <v>19.7101936340332</v>
       </c>
       <c r="H1462" t="s">
         <v>8</v>
@@ -38407,7 +38407,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G1463" t="n">
-        <v>19.7854957580566</v>
+        <v>19.7854976654053</v>
       </c>
       <c r="H1463" t="s">
         <v>8</v>
@@ -38537,7 +38537,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G1468" t="n">
-        <v>18.0347328186035</v>
+        <v>18.0347347259521</v>
       </c>
       <c r="H1468" t="s">
         <v>8</v>
@@ -38615,7 +38615,7 @@
         <v>19.7099990844727</v>
       </c>
       <c r="G1471" t="n">
-        <v>18.5524291992188</v>
+        <v>18.5524311065674</v>
       </c>
       <c r="H1471" t="s">
         <v>8</v>
@@ -38693,7 +38693,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G1474" t="n">
-        <v>18.9760036468506</v>
+        <v>18.9760055541992</v>
       </c>
       <c r="H1474" t="s">
         <v>8</v>
@@ -38849,7 +38849,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1480" t="n">
-        <v>18.4488906860352</v>
+        <v>18.4488925933838</v>
       </c>
       <c r="H1480" t="s">
         <v>8</v>
@@ -38875,7 +38875,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G1481" t="n">
-        <v>18.6183204650879</v>
+        <v>18.6183223724365</v>
       </c>
       <c r="H1481" t="s">
         <v>8</v>
@@ -38927,7 +38927,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1483" t="n">
-        <v>18.8724632263184</v>
+        <v>18.8724613189697</v>
       </c>
       <c r="H1483" t="s">
         <v>8</v>
@@ -38979,7 +38979,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G1485" t="n">
-        <v>18.7877464294434</v>
+        <v>18.787748336792</v>
       </c>
       <c r="H1485" t="s">
         <v>8</v>
@@ -39109,7 +39109,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1490" t="n">
-        <v>19.2019081115723</v>
+        <v>19.2019100189209</v>
       </c>
       <c r="H1490" t="s">
         <v>8</v>
@@ -39239,7 +39239,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1495" t="n">
-        <v>18.4488906860352</v>
+        <v>18.4488925933838</v>
       </c>
       <c r="H1495" t="s">
         <v>8</v>
@@ -39265,7 +39265,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G1496" t="n">
-        <v>18.7877464294434</v>
+        <v>18.787748336792</v>
       </c>
       <c r="H1496" t="s">
         <v>8</v>
@@ -39343,7 +39343,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G1499" t="n">
-        <v>18.3359394073486</v>
+        <v>18.3359413146973</v>
       </c>
       <c r="H1499" t="s">
         <v>8</v>
@@ -39369,7 +39369,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G1500" t="n">
-        <v>18.6183204650879</v>
+        <v>18.6183223724365</v>
       </c>
       <c r="H1500" t="s">
         <v>8</v>
@@ -39525,7 +39525,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G1506" t="n">
-        <v>18.8805980682373</v>
+        <v>18.8805961608887</v>
       </c>
       <c r="H1506" t="s">
         <v>8</v>
@@ -39551,7 +39551,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1507" t="n">
-        <v>18.7850456237793</v>
+        <v>18.7850475311279</v>
       </c>
       <c r="H1507" t="s">
         <v>8</v>
@@ -39707,7 +39707,7 @@
         <v>19</v>
       </c>
       <c r="G1513" t="n">
-        <v>18.1544189453125</v>
+        <v>18.1544208526611</v>
       </c>
       <c r="H1513" t="s">
         <v>8</v>
@@ -39785,7 +39785,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G1516" t="n">
-        <v>18.6130561828613</v>
+        <v>18.61305809021</v>
       </c>
       <c r="H1516" t="s">
         <v>8</v>
@@ -39811,7 +39811,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G1517" t="n">
-        <v>17.8295497894287</v>
+        <v>17.8295516967773</v>
       </c>
       <c r="H1517" t="s">
         <v>8</v>
@@ -39863,7 +39863,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G1519" t="n">
-        <v>18.8805980682373</v>
+        <v>18.8805961608887</v>
       </c>
       <c r="H1519" t="s">
         <v>8</v>
@@ -39915,7 +39915,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1521" t="n">
-        <v>18.5366172790527</v>
+        <v>18.5366191864014</v>
       </c>
       <c r="H1521" t="s">
         <v>8</v>
@@ -39967,7 +39967,7 @@
         <v>20</v>
       </c>
       <c r="G1523" t="n">
-        <v>19.1099147796631</v>
+        <v>19.1099166870117</v>
       </c>
       <c r="H1523" t="s">
         <v>8</v>
@@ -39993,7 +39993,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1524" t="n">
-        <v>19.3010158538818</v>
+        <v>19.3010139465332</v>
       </c>
       <c r="H1524" t="s">
         <v>8</v>
@@ -40071,7 +40071,7 @@
         <v>20</v>
       </c>
       <c r="G1527" t="n">
-        <v>19.1099147796631</v>
+        <v>19.1099166870117</v>
       </c>
       <c r="H1527" t="s">
         <v>8</v>
@@ -40175,7 +40175,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G1531" t="n">
-        <v>20.1131858825684</v>
+        <v>20.1131839752197</v>
       </c>
       <c r="H1531" t="s">
         <v>8</v>
@@ -40357,7 +40357,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1538" t="n">
-        <v>20.2087345123291</v>
+        <v>20.2087326049805</v>
       </c>
       <c r="H1538" t="s">
         <v>8</v>
@@ -40617,7 +40617,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1548" t="n">
-        <v>18.8423767089844</v>
+        <v>18.8423748016357</v>
       </c>
       <c r="H1548" t="s">
         <v>8</v>
@@ -40695,7 +40695,7 @@
         <v>20</v>
       </c>
       <c r="G1551" t="n">
-        <v>19.1099147796631</v>
+        <v>19.1099166870117</v>
       </c>
       <c r="H1551" t="s">
         <v>8</v>
@@ -40929,7 +40929,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1560" t="n">
-        <v>17.963321685791</v>
+        <v>17.9633197784424</v>
       </c>
       <c r="H1560" t="s">
         <v>8</v>
@@ -40955,7 +40955,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1561" t="n">
-        <v>18.0588703155518</v>
+        <v>18.0588684082031</v>
       </c>
       <c r="H1561" t="s">
         <v>8</v>
@@ -40981,7 +40981,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1562" t="n">
-        <v>18.0588703155518</v>
+        <v>18.0588684082031</v>
       </c>
       <c r="H1562" t="s">
         <v>8</v>
@@ -41007,7 +41007,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G1563" t="n">
-        <v>18.4219608306885</v>
+        <v>18.4219589233398</v>
       </c>
       <c r="H1563" t="s">
         <v>8</v>
@@ -41033,7 +41033,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G1564" t="n">
-        <v>18.4983997344971</v>
+        <v>18.4983978271484</v>
       </c>
       <c r="H1564" t="s">
         <v>8</v>
@@ -41111,7 +41111,7 @@
         <v>19</v>
       </c>
       <c r="G1567" t="n">
-        <v>18.1544189453125</v>
+        <v>18.1544208526611</v>
       </c>
       <c r="H1567" t="s">
         <v>8</v>
@@ -41163,7 +41163,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1569" t="n">
-        <v>15.803900718689</v>
+        <v>15.8039016723633</v>
       </c>
       <c r="H1569" t="s">
         <v>8</v>
@@ -41319,7 +41319,7 @@
         <v>17.1399993896484</v>
       </c>
       <c r="G1575" t="n">
-        <v>16.3771953582764</v>
+        <v>16.377197265625</v>
       </c>
       <c r="H1575" t="s">
         <v>8</v>
@@ -41605,7 +41605,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1586" t="n">
-        <v>16.5109691619873</v>
+        <v>16.5109672546387</v>
       </c>
       <c r="H1586" t="s">
         <v>8</v>
@@ -41761,7 +41761,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1592" t="n">
-        <v>16.3007564544678</v>
+        <v>16.3007583618164</v>
       </c>
       <c r="H1592" t="s">
         <v>8</v>
@@ -41839,7 +41839,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1595" t="n">
-        <v>15.9567794799805</v>
+        <v>15.9567813873291</v>
       </c>
       <c r="H1595" t="s">
         <v>8</v>
@@ -42021,7 +42021,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G1602" t="n">
-        <v>14.9057350158691</v>
+        <v>14.9057340621948</v>
       </c>
       <c r="H1602" t="s">
         <v>8</v>
@@ -42099,7 +42099,7 @@
         <v>15.0600004196167</v>
       </c>
       <c r="G1605" t="n">
-        <v>14.3897666931152</v>
+        <v>14.3897657394409</v>
       </c>
       <c r="H1605" t="s">
         <v>8</v>
@@ -42255,7 +42255,7 @@
         <v>14.1800003051758</v>
       </c>
       <c r="G1611" t="n">
-        <v>13.5489301681519</v>
+        <v>13.5489311218262</v>
       </c>
       <c r="H1611" t="s">
         <v>8</v>
@@ -42281,7 +42281,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G1612" t="n">
-        <v>13.4533805847168</v>
+        <v>13.4533796310425</v>
       </c>
       <c r="H1612" t="s">
         <v>8</v>
@@ -42333,7 +42333,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1614" t="n">
-        <v>12.9947423934937</v>
+        <v>12.994743347168</v>
       </c>
       <c r="H1614" t="s">
         <v>8</v>
@@ -42567,7 +42567,7 @@
         <v>14.3800001144409</v>
       </c>
       <c r="G1623" t="n">
-        <v>13.7400283813477</v>
+        <v>13.740029335022</v>
       </c>
       <c r="H1623" t="s">
         <v>8</v>
@@ -42645,7 +42645,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1626" t="n">
-        <v>13.8737993240356</v>
+        <v>13.8737983703613</v>
       </c>
       <c r="H1626" t="s">
         <v>8</v>
@@ -42671,7 +42671,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G1627" t="n">
-        <v>13.835578918457</v>
+        <v>13.8355779647827</v>
       </c>
       <c r="H1627" t="s">
         <v>8</v>
@@ -42697,7 +42697,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1628" t="n">
-        <v>13.8737993240356</v>
+        <v>13.8737983703613</v>
       </c>
       <c r="H1628" t="s">
         <v>8</v>
@@ -42723,7 +42723,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G1629" t="n">
-        <v>13.835578918457</v>
+        <v>13.8355779647827</v>
       </c>
       <c r="H1629" t="s">
         <v>8</v>
@@ -42749,7 +42749,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G1630" t="n">
-        <v>14.1222276687622</v>
+        <v>14.1222267150879</v>
       </c>
       <c r="H1630" t="s">
         <v>8</v>
@@ -42801,7 +42801,7 @@
         <v>15.3800001144409</v>
       </c>
       <c r="G1632" t="n">
-        <v>14.6955242156982</v>
+        <v>14.6955251693726</v>
       </c>
       <c r="H1632" t="s">
         <v>8</v>
@@ -42957,7 +42957,7 @@
         <v>16.8199996948242</v>
       </c>
       <c r="G1638" t="n">
-        <v>16.071439743042</v>
+        <v>16.0714378356934</v>
       </c>
       <c r="H1638" t="s">
         <v>8</v>
@@ -43035,7 +43035,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G1641" t="n">
-        <v>17.1224842071533</v>
+        <v>17.122486114502</v>
       </c>
       <c r="H1641" t="s">
         <v>8</v>
@@ -43061,7 +43061,7 @@
         <v>17.5</v>
       </c>
       <c r="G1642" t="n">
-        <v>16.7211761474609</v>
+        <v>16.7211742401123</v>
       </c>
       <c r="H1642" t="s">
         <v>8</v>
@@ -43087,7 +43087,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1643" t="n">
-        <v>17.0078258514404</v>
+        <v>17.0078239440918</v>
       </c>
       <c r="H1643" t="s">
         <v>8</v>
@@ -43113,7 +43113,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1644" t="n">
-        <v>17.0460433959961</v>
+        <v>17.0460453033447</v>
       </c>
       <c r="H1644" t="s">
         <v>8</v>
@@ -43347,7 +43347,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G1653" t="n">
-        <v>17.0269355773926</v>
+        <v>17.0269336700439</v>
       </c>
       <c r="H1653" t="s">
         <v>8</v>
@@ -43451,7 +43451,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1657" t="n">
-        <v>17.1033744812012</v>
+        <v>17.1033725738525</v>
       </c>
       <c r="H1657" t="s">
         <v>8</v>
@@ -43477,7 +43477,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1658" t="n">
-        <v>17.256254196167</v>
+        <v>17.2562522888184</v>
       </c>
       <c r="H1658" t="s">
         <v>8</v>
@@ -43555,7 +43555,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1661" t="n">
-        <v>17.1033744812012</v>
+        <v>17.1033725738525</v>
       </c>
       <c r="H1661" t="s">
         <v>8</v>
@@ -43581,7 +43581,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G1662" t="n">
-        <v>18.3264083862305</v>
+        <v>18.3264102935791</v>
       </c>
       <c r="H1662" t="s">
         <v>8</v>
@@ -43633,7 +43633,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G1664" t="n">
-        <v>18.1353092193604</v>
+        <v>18.1353073120117</v>
       </c>
       <c r="H1664" t="s">
         <v>8</v>
@@ -43763,7 +43763,7 @@
         <v>19.7600002288818</v>
       </c>
       <c r="G1669" t="n">
-        <v>18.8805980682373</v>
+        <v>18.8805961608887</v>
       </c>
       <c r="H1669" t="s">
         <v>8</v>
@@ -43893,7 +43893,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G1674" t="n">
-        <v>17.8868808746338</v>
+        <v>17.8868789672852</v>
       </c>
       <c r="H1674" t="s">
         <v>8</v>
@@ -43945,7 +43945,7 @@
         <v>19</v>
       </c>
       <c r="G1676" t="n">
-        <v>18.1544189453125</v>
+        <v>18.1544208526611</v>
       </c>
       <c r="H1676" t="s">
         <v>8</v>
@@ -44205,7 +44205,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G1686" t="n">
-        <v>17.0269355773926</v>
+        <v>17.0269336700439</v>
       </c>
       <c r="H1686" t="s">
         <v>8</v>
@@ -44257,7 +44257,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1688" t="n">
-        <v>17.332691192627</v>
+        <v>17.3326930999756</v>
       </c>
       <c r="H1688" t="s">
         <v>8</v>
@@ -44283,7 +44283,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1689" t="n">
-        <v>17.9824314117432</v>
+        <v>17.9824295043945</v>
       </c>
       <c r="H1689" t="s">
         <v>8</v>
@@ -44413,7 +44413,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1694" t="n">
-        <v>17.867769241333</v>
+        <v>17.8677711486816</v>
       </c>
       <c r="H1694" t="s">
         <v>8</v>
@@ -44517,7 +44517,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G1698" t="n">
-        <v>17.4091300964355</v>
+        <v>17.4091320037842</v>
       </c>
       <c r="H1698" t="s">
         <v>8</v>
@@ -44621,7 +44621,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G1702" t="n">
-        <v>17.4091300964355</v>
+        <v>17.4091320037842</v>
       </c>
       <c r="H1702" t="s">
         <v>8</v>
@@ -44751,7 +44751,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1707" t="n">
-        <v>17.963321685791</v>
+        <v>17.9633197784424</v>
       </c>
       <c r="H1707" t="s">
         <v>8</v>
@@ -44829,7 +44829,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G1710" t="n">
-        <v>18.3646278381348</v>
+        <v>18.3646259307861</v>
       </c>
       <c r="H1710" t="s">
         <v>8</v>
@@ -44855,7 +44855,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G1711" t="n">
-        <v>18.3072986602783</v>
+        <v>18.307300567627</v>
       </c>
       <c r="H1711" t="s">
         <v>8</v>
@@ -44881,7 +44881,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G1712" t="n">
-        <v>18.3646278381348</v>
+        <v>18.3646259307861</v>
       </c>
       <c r="H1712" t="s">
         <v>8</v>
@@ -44959,7 +44959,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1715" t="n">
-        <v>17.7913303375244</v>
+        <v>17.791332244873</v>
       </c>
       <c r="H1715" t="s">
         <v>8</v>
@@ -45011,7 +45011,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1717" t="n">
-        <v>17.2944717407227</v>
+        <v>17.2944736480713</v>
       </c>
       <c r="H1717" t="s">
         <v>8</v>
@@ -45063,7 +45063,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G1719" t="n">
-        <v>17.8868808746338</v>
+        <v>17.8868789672852</v>
       </c>
       <c r="H1719" t="s">
         <v>8</v>
@@ -45089,7 +45089,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1720" t="n">
-        <v>17.7913303375244</v>
+        <v>17.791332244873</v>
       </c>
       <c r="H1720" t="s">
         <v>8</v>
@@ -45193,7 +45193,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1724" t="n">
-        <v>17.1033744812012</v>
+        <v>17.1033725738525</v>
       </c>
       <c r="H1724" t="s">
         <v>8</v>
@@ -45245,7 +45245,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1726" t="n">
-        <v>17.0078258514404</v>
+        <v>17.0078239440918</v>
       </c>
       <c r="H1726" t="s">
         <v>8</v>
@@ -45297,7 +45297,7 @@
         <v>17.3400001525879</v>
       </c>
       <c r="G1728" t="n">
-        <v>16.5682983398438</v>
+        <v>16.5682964324951</v>
       </c>
       <c r="H1728" t="s">
         <v>8</v>
@@ -45323,7 +45323,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1729" t="n">
-        <v>16.8167247772217</v>
+        <v>16.8167266845703</v>
       </c>
       <c r="H1729" t="s">
         <v>8</v>
@@ -45349,7 +45349,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1730" t="n">
-        <v>16.8358345031738</v>
+        <v>16.8358364105225</v>
       </c>
       <c r="H1730" t="s">
         <v>8</v>
@@ -45401,7 +45401,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1732" t="n">
-        <v>17.1033744812012</v>
+        <v>17.1033725738525</v>
       </c>
       <c r="H1732" t="s">
         <v>8</v>
@@ -45453,7 +45453,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1734" t="n">
-        <v>17.256254196167</v>
+        <v>17.2562522888184</v>
       </c>
       <c r="H1734" t="s">
         <v>8</v>
@@ -45479,7 +45479,7 @@
         <v>17.5</v>
       </c>
       <c r="G1735" t="n">
-        <v>16.7211761474609</v>
+        <v>16.7211742401123</v>
       </c>
       <c r="H1735" t="s">
         <v>8</v>
@@ -45635,7 +45635,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1741" t="n">
-        <v>15.7847900390625</v>
+        <v>15.7847890853882</v>
       </c>
       <c r="H1741" t="s">
         <v>8</v>
@@ -45661,7 +45661,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G1742" t="n">
-        <v>15.9758882522583</v>
+        <v>15.9758892059326</v>
       </c>
       <c r="H1742" t="s">
         <v>8</v>
@@ -45843,7 +45843,7 @@
         <v>15.5600004196167</v>
       </c>
       <c r="G1749" t="n">
-        <v>14.8675146102905</v>
+        <v>14.8675136566162</v>
       </c>
       <c r="H1749" t="s">
         <v>8</v>
@@ -46051,7 +46051,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1757" t="n">
-        <v>15.8803396224976</v>
+        <v>15.8803405761719</v>
       </c>
       <c r="H1757" t="s">
         <v>8</v>
@@ -46077,7 +46077,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1758" t="n">
-        <v>15.7847900390625</v>
+        <v>15.7847890853882</v>
       </c>
       <c r="H1758" t="s">
         <v>8</v>
@@ -46181,7 +46181,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1762" t="n">
-        <v>15.8803396224976</v>
+        <v>15.8803405761719</v>
       </c>
       <c r="H1762" t="s">
         <v>8</v>
@@ -46233,7 +46233,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1764" t="n">
-        <v>16.4536361694336</v>
+        <v>16.4536380767822</v>
       </c>
       <c r="H1764" t="s">
         <v>8</v>
@@ -46259,7 +46259,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1765" t="n">
-        <v>16.6447372436523</v>
+        <v>16.6447353363037</v>
       </c>
       <c r="H1765" t="s">
         <v>8</v>
@@ -46311,7 +46311,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1767" t="n">
-        <v>16.8167247772217</v>
+        <v>16.8167266845703</v>
       </c>
       <c r="H1767" t="s">
         <v>8</v>
@@ -62200,6 +62200,32 @@
         <v>28.75</v>
       </c>
       <c r="H2378" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2379">
+      <c r="A2379" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B2379" t="n">
+        <v>21884</v>
+      </c>
+      <c r="C2379" t="n">
+        <v>29.7000007629395</v>
+      </c>
+      <c r="D2379" t="n">
+        <v>28.4500007629395</v>
+      </c>
+      <c r="E2379" t="n">
+        <v>28.4500007629395</v>
+      </c>
+      <c r="F2379" t="n">
+        <v>28.6499996185303</v>
+      </c>
+      <c r="G2379" t="n">
+        <v>28.6499996185303</v>
+      </c>
+      <c r="H2379" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/WIIT.MI.xlsx
+++ b/data/WIIT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2" t="n">
-        <v>4.49076414108276</v>
+        <v>4.49076461791992</v>
       </c>
       <c r="H2" t="n">
         <v>48400</v>
@@ -456,7 +456,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G3" t="n">
-        <v>4.49076414108276</v>
+        <v>4.49076461791992</v>
       </c>
       <c r="H3" t="n">
         <v>24400</v>
@@ -8315,7 +8315,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G274" t="n">
-        <v>4.51098823547363</v>
+        <v>4.51098775863647</v>
       </c>
       <c r="H274" t="n">
         <v>21200</v>
@@ -8373,7 +8373,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G276" t="n">
-        <v>4.52888917922974</v>
+        <v>4.52888870239258</v>
       </c>
       <c r="H276" t="n">
         <v>35200</v>
@@ -8402,7 +8402,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G277" t="n">
-        <v>4.49308729171753</v>
+        <v>4.49308681488037</v>
       </c>
       <c r="H277" t="n">
         <v>10800</v>
@@ -8431,7 +8431,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G278" t="n">
-        <v>4.44833564758301</v>
+        <v>4.44833517074585</v>
       </c>
       <c r="H278" t="n">
         <v>12800</v>
@@ -8460,7 +8460,7 @@
         <v>5</v>
       </c>
       <c r="G279" t="n">
-        <v>4.47518587112427</v>
+        <v>4.47518634796143</v>
       </c>
       <c r="H279" t="n">
         <v>9200</v>
@@ -8489,7 +8489,7 @@
         <v>5</v>
       </c>
       <c r="G280" t="n">
-        <v>4.47518587112427</v>
+        <v>4.47518634796143</v>
       </c>
       <c r="H280" t="n">
         <v>8800</v>
@@ -8518,7 +8518,7 @@
         <v>5</v>
       </c>
       <c r="G281" t="n">
-        <v>4.47518587112427</v>
+        <v>4.47518634796143</v>
       </c>
       <c r="H281" t="n">
         <v>10400</v>
@@ -8547,7 +8547,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G282" t="n">
-        <v>4.49308729171753</v>
+        <v>4.49308681488037</v>
       </c>
       <c r="H282" t="n">
         <v>8800</v>
@@ -8576,7 +8576,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G283" t="n">
-        <v>4.43938589096069</v>
+        <v>4.43938541412354</v>
       </c>
       <c r="H283" t="n">
         <v>6000</v>
@@ -8605,7 +8605,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G284" t="n">
-        <v>4.49308729171753</v>
+        <v>4.49308681488037</v>
       </c>
       <c r="H284" t="n">
         <v>35200</v>
@@ -8634,7 +8634,7 @@
         <v>5</v>
       </c>
       <c r="G285" t="n">
-        <v>4.47518587112427</v>
+        <v>4.47518634796143</v>
       </c>
       <c r="H285" t="n">
         <v>6000</v>
@@ -8663,7 +8663,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G286" t="n">
-        <v>4.44833564758301</v>
+        <v>4.44833517074585</v>
       </c>
       <c r="H286" t="n">
         <v>4800</v>
@@ -8692,7 +8692,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G287" t="n">
-        <v>4.44833564758301</v>
+        <v>4.44833517074585</v>
       </c>
       <c r="H287" t="n">
         <v>58000</v>
@@ -8721,7 +8721,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G288" t="n">
-        <v>4.44833564758301</v>
+        <v>4.44833517074585</v>
       </c>
       <c r="H288" t="n">
         <v>4400</v>
@@ -8750,7 +8750,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G289" t="n">
-        <v>4.44833564758301</v>
+        <v>4.44833517074585</v>
       </c>
       <c r="H289" t="n">
         <v>4800</v>
@@ -8779,7 +8779,7 @@
         <v>5</v>
       </c>
       <c r="G290" t="n">
-        <v>4.47518587112427</v>
+        <v>4.47518634796143</v>
       </c>
       <c r="H290" t="n">
         <v>2400</v>
@@ -8895,7 +8895,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G294" t="n">
-        <v>4.58259057998657</v>
+        <v>4.58259010314941</v>
       </c>
       <c r="H294" t="n">
         <v>6400</v>
@@ -8953,7 +8953,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G296" t="n">
-        <v>4.51098823547363</v>
+        <v>4.51098775863647</v>
       </c>
       <c r="H296" t="n">
         <v>400</v>
@@ -8982,7 +8982,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G297" t="n">
-        <v>4.52888917922974</v>
+        <v>4.52888870239258</v>
       </c>
       <c r="H297" t="n">
         <v>1200</v>
@@ -9011,7 +9011,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G298" t="n">
-        <v>4.51098823547363</v>
+        <v>4.51098775863647</v>
       </c>
       <c r="H298" t="n">
         <v>400</v>
@@ -9040,7 +9040,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>4.51098823547363</v>
+        <v>4.51098775863647</v>
       </c>
       <c r="H299" t="n">
         <v>1600</v>
@@ -9069,7 +9069,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G300" t="n">
-        <v>4.49308729171753</v>
+        <v>4.49308681488037</v>
       </c>
       <c r="H300" t="n">
         <v>2400</v>
@@ -9098,7 +9098,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G301" t="n">
-        <v>4.49308729171753</v>
+        <v>4.49308681488037</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -9127,7 +9127,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>4.49308729171753</v>
+        <v>4.49308681488037</v>
       </c>
       <c r="H302" t="n">
         <v>0</v>
@@ -9272,7 +9272,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G307" t="n">
-        <v>4.30513000488281</v>
+        <v>4.3051290512085</v>
       </c>
       <c r="H307" t="n">
         <v>5200</v>
@@ -9388,7 +9388,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G311" t="n">
-        <v>4.27827787399292</v>
+        <v>4.27827882766724</v>
       </c>
       <c r="H311" t="n">
         <v>2000</v>
@@ -9417,7 +9417,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G312" t="n">
-        <v>4.27827787399292</v>
+        <v>4.27827882766724</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>4.45728492736816</v>
+        <v>4.45728588104248</v>
       </c>
       <c r="H313" t="n">
         <v>5200</v>
@@ -9475,7 +9475,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>4.43938589096069</v>
+        <v>4.43938541412354</v>
       </c>
       <c r="H314" t="n">
         <v>2000</v>
@@ -9504,7 +9504,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G315" t="n">
-        <v>4.36778163909912</v>
+        <v>4.36778211593628</v>
       </c>
       <c r="H315" t="n">
         <v>1600</v>
@@ -9562,7 +9562,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G317" t="n">
-        <v>4.3230299949646</v>
+        <v>4.32303047180176</v>
       </c>
       <c r="H317" t="n">
         <v>800</v>
@@ -9591,7 +9591,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G318" t="n">
-        <v>4.3230299949646</v>
+        <v>4.32303047180176</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G319" t="n">
-        <v>4.35883188247681</v>
+        <v>4.35883140563965</v>
       </c>
       <c r="H319" t="n">
         <v>400</v>
@@ -9649,7 +9649,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G320" t="n">
-        <v>4.14402341842651</v>
+        <v>4.14402294158936</v>
       </c>
       <c r="H320" t="n">
         <v>24400</v>
@@ -9678,7 +9678,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G321" t="n">
-        <v>4.23352670669556</v>
+        <v>4.23352718353271</v>
       </c>
       <c r="H321" t="n">
         <v>800</v>
@@ -9707,7 +9707,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G322" t="n">
-        <v>4.3230299949646</v>
+        <v>4.32303047180176</v>
       </c>
       <c r="H322" t="n">
         <v>2800</v>
@@ -9736,7 +9736,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G323" t="n">
-        <v>4.34988164901733</v>
+        <v>4.34988117218018</v>
       </c>
       <c r="H323" t="n">
         <v>2400</v>
@@ -9794,7 +9794,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G325" t="n">
-        <v>4.17982387542725</v>
+        <v>4.1798243522644</v>
       </c>
       <c r="H325" t="n">
         <v>15200</v>
@@ -9823,7 +9823,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G326" t="n">
-        <v>4.0903205871582</v>
+        <v>4.09032106399536</v>
       </c>
       <c r="H326" t="n">
         <v>218400</v>
@@ -9852,7 +9852,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G327" t="n">
-        <v>4.04556846618652</v>
+        <v>4.04556894302368</v>
       </c>
       <c r="H327" t="n">
         <v>117200</v>
@@ -9881,7 +9881,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G328" t="n">
-        <v>3.90236234664917</v>
+        <v>3.90236306190491</v>
       </c>
       <c r="H328" t="n">
         <v>7600</v>
@@ -9939,7 +9939,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G330" t="n">
-        <v>4.14402341842651</v>
+        <v>4.14402294158936</v>
       </c>
       <c r="H330" t="n">
         <v>6400</v>
@@ -9997,7 +9997,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G332" t="n">
-        <v>4.13507223129272</v>
+        <v>4.13507270812988</v>
       </c>
       <c r="H332" t="n">
         <v>1600</v>
@@ -10026,7 +10026,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G333" t="n">
-        <v>4.17982387542725</v>
+        <v>4.1798243522644</v>
       </c>
       <c r="H333" t="n">
         <v>18000</v>
@@ -10055,7 +10055,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G334" t="n">
-        <v>4.14402341842651</v>
+        <v>4.14402294158936</v>
       </c>
       <c r="H334" t="n">
         <v>21600</v>
@@ -10142,7 +10142,7 @@
         <v>4.5</v>
       </c>
       <c r="G337" t="n">
-        <v>4.02766752243042</v>
+        <v>4.02766799926758</v>
       </c>
       <c r="H337" t="n">
         <v>1600</v>
@@ -10171,7 +10171,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G338" t="n">
-        <v>3.93816423416138</v>
+        <v>3.93816447257996</v>
       </c>
       <c r="H338" t="n">
         <v>6800</v>
@@ -10200,7 +10200,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G339" t="n">
-        <v>3.8844621181488</v>
+        <v>3.88446235656738</v>
       </c>
       <c r="H339" t="n">
         <v>3600</v>
@@ -10229,7 +10229,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G340" t="n">
-        <v>3.90236234664917</v>
+        <v>3.90236306190491</v>
       </c>
       <c r="H340" t="n">
         <v>3600</v>
@@ -10258,7 +10258,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G341" t="n">
-        <v>3.86656141281128</v>
+        <v>3.86656093597412</v>
       </c>
       <c r="H341" t="n">
         <v>2400</v>
@@ -10287,7 +10287,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>3.76810765266418</v>
+        <v>3.76810717582703</v>
       </c>
       <c r="H342" t="n">
         <v>6000</v>
@@ -10316,7 +10316,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G343" t="n">
-        <v>3.84866046905518</v>
+        <v>3.8486602306366</v>
       </c>
       <c r="H343" t="n">
         <v>2400</v>
@@ -10345,7 +10345,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G344" t="n">
-        <v>3.78600811958313</v>
+        <v>3.78600788116455</v>
       </c>
       <c r="H344" t="n">
         <v>1200</v>
@@ -10374,7 +10374,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G345" t="n">
-        <v>3.70545411109924</v>
+        <v>3.7054545879364</v>
       </c>
       <c r="H345" t="n">
         <v>1600</v>
@@ -10403,7 +10403,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G346" t="n">
-        <v>3.66965293884277</v>
+        <v>3.66965270042419</v>
       </c>
       <c r="H346" t="n">
         <v>800</v>
@@ -10461,7 +10461,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G348" t="n">
-        <v>3.59805011749268</v>
+        <v>3.59805035591125</v>
       </c>
       <c r="H348" t="n">
         <v>6400</v>
@@ -10490,7 +10490,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G349" t="n">
-        <v>3.59805011749268</v>
+        <v>3.59805035591125</v>
       </c>
       <c r="H349" t="n">
         <v>1600</v>
@@ -10519,7 +10519,7 @@
         <v>3.99000000953674</v>
       </c>
       <c r="G350" t="n">
-        <v>3.57119870185852</v>
+        <v>3.5711989402771</v>
       </c>
       <c r="H350" t="n">
         <v>9200</v>
@@ -10606,7 +10606,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G353" t="n">
-        <v>3.4369432926178</v>
+        <v>3.43694305419922</v>
       </c>
       <c r="H353" t="n">
         <v>2800</v>
@@ -10664,7 +10664,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G355" t="n">
-        <v>3.44589376449585</v>
+        <v>3.44589352607727</v>
       </c>
       <c r="H355" t="n">
         <v>10400</v>
@@ -10722,7 +10722,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G357" t="n">
-        <v>3.39219164848328</v>
+        <v>3.3921914100647</v>
       </c>
       <c r="H357" t="n">
         <v>43200</v>
@@ -10751,7 +10751,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G358" t="n">
-        <v>3.31163811683655</v>
+        <v>3.31163787841797</v>
       </c>
       <c r="H358" t="n">
         <v>21600</v>
@@ -10780,7 +10780,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G359" t="n">
-        <v>3.31163811683655</v>
+        <v>3.31163787841797</v>
       </c>
       <c r="H359" t="n">
         <v>10000</v>
@@ -10809,7 +10809,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G360" t="n">
-        <v>3.31163811683655</v>
+        <v>3.31163787841797</v>
       </c>
       <c r="H360" t="n">
         <v>4800</v>
@@ -10838,7 +10838,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G361" t="n">
-        <v>3.34743976593018</v>
+        <v>3.34744000434875</v>
       </c>
       <c r="H361" t="n">
         <v>9200</v>
@@ -10867,7 +10867,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G362" t="n">
-        <v>3.36534023284912</v>
+        <v>3.3653404712677</v>
       </c>
       <c r="H362" t="n">
         <v>5200</v>
@@ -10896,7 +10896,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G363" t="n">
-        <v>3.31163811683655</v>
+        <v>3.31163787841797</v>
       </c>
       <c r="H363" t="n">
         <v>11200</v>
@@ -10925,7 +10925,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G364" t="n">
-        <v>3.20423364639282</v>
+        <v>3.2042338848114</v>
       </c>
       <c r="H364" t="n">
         <v>18000</v>
@@ -10954,7 +10954,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G365" t="n">
-        <v>3.08787870407104</v>
+        <v>3.08787894248962</v>
       </c>
       <c r="H365" t="n">
         <v>6000</v>
@@ -10983,7 +10983,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G366" t="n">
-        <v>3.07892870903015</v>
+        <v>3.07892847061157</v>
       </c>
       <c r="H366" t="n">
         <v>31600</v>
@@ -11012,7 +11012,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G367" t="n">
-        <v>3.09682893753052</v>
+        <v>3.0968291759491</v>
       </c>
       <c r="H367" t="n">
         <v>28000</v>
@@ -11041,7 +11041,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G368" t="n">
-        <v>3.10577988624573</v>
+        <v>3.10577940940857</v>
       </c>
       <c r="H368" t="n">
         <v>18000</v>
@@ -11070,7 +11070,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G369" t="n">
-        <v>3.20423364639282</v>
+        <v>3.2042338848114</v>
       </c>
       <c r="H369" t="n">
         <v>68000</v>
@@ -11128,7 +11128,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G371" t="n">
-        <v>3.22213435173035</v>
+        <v>3.22213459014893</v>
       </c>
       <c r="H371" t="n">
         <v>62000</v>
@@ -11157,7 +11157,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G372" t="n">
-        <v>3.22213435173035</v>
+        <v>3.22213459014893</v>
       </c>
       <c r="H372" t="n">
         <v>21200</v>
@@ -11302,7 +11302,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G377" t="n">
-        <v>2.95362305641174</v>
+        <v>2.95362329483032</v>
       </c>
       <c r="H377" t="n">
         <v>11600</v>
@@ -11360,7 +11360,7 @@
         <v>3.25</v>
       </c>
       <c r="G379" t="n">
-        <v>2.90887141227722</v>
+        <v>2.90887117385864</v>
       </c>
       <c r="H379" t="n">
         <v>8800</v>
@@ -11418,7 +11418,7 @@
         <v>3.25</v>
       </c>
       <c r="G381" t="n">
-        <v>2.90887141227722</v>
+        <v>2.90887117385864</v>
       </c>
       <c r="H381" t="n">
         <v>67200</v>
@@ -11447,7 +11447,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G382" t="n">
-        <v>2.95362305641174</v>
+        <v>2.95362329483032</v>
       </c>
       <c r="H382" t="n">
         <v>18000</v>
@@ -11476,7 +11476,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G383" t="n">
-        <v>2.95362305641174</v>
+        <v>2.95362329483032</v>
       </c>
       <c r="H383" t="n">
         <v>24400</v>
@@ -11534,7 +11534,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G385" t="n">
-        <v>2.95362305641174</v>
+        <v>2.95362329483032</v>
       </c>
       <c r="H385" t="n">
         <v>17600</v>
@@ -11592,7 +11592,7 @@
         <v>3.25</v>
       </c>
       <c r="G387" t="n">
-        <v>2.90887141227722</v>
+        <v>2.90887117385864</v>
       </c>
       <c r="H387" t="n">
         <v>8400</v>
@@ -11708,7 +11708,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G391" t="n">
-        <v>2.84621858596802</v>
+        <v>2.84621930122375</v>
       </c>
       <c r="H391" t="n">
         <v>25200</v>
@@ -11766,7 +11766,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G393" t="n">
-        <v>2.89992094039917</v>
+        <v>2.89992070198059</v>
       </c>
       <c r="H393" t="n">
         <v>26000</v>
@@ -11795,7 +11795,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G394" t="n">
-        <v>2.94467282295227</v>
+        <v>2.94467258453369</v>
       </c>
       <c r="H394" t="n">
         <v>2000</v>
@@ -11824,7 +11824,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G395" t="n">
-        <v>3.06102776527405</v>
+        <v>3.06102752685547</v>
       </c>
       <c r="H395" t="n">
         <v>27600</v>
@@ -11882,7 +11882,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G397" t="n">
-        <v>3.17738246917725</v>
+        <v>3.17738270759583</v>
       </c>
       <c r="H397" t="n">
         <v>9200</v>
@@ -11911,7 +11911,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G398" t="n">
-        <v>3.17738246917725</v>
+        <v>3.17738270759583</v>
       </c>
       <c r="H398" t="n">
         <v>3600</v>
@@ -11940,7 +11940,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G399" t="n">
-        <v>3.26688647270203</v>
+        <v>3.26688623428345</v>
       </c>
       <c r="H399" t="n">
         <v>7600</v>
@@ -11969,7 +11969,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>3.22213435173035</v>
+        <v>3.22213459014893</v>
       </c>
       <c r="H400" t="n">
         <v>27600</v>
@@ -11998,7 +11998,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G401" t="n">
-        <v>3.26688647270203</v>
+        <v>3.26688623428345</v>
       </c>
       <c r="H401" t="n">
         <v>2400</v>
@@ -12027,7 +12027,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G402" t="n">
-        <v>3.26688647270203</v>
+        <v>3.26688623428345</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G403" t="n">
-        <v>3.31163811683655</v>
+        <v>3.31163787841797</v>
       </c>
       <c r="H403" t="n">
         <v>3600</v>
@@ -12085,7 +12085,7 @@
         <v>3.75</v>
       </c>
       <c r="G404" t="n">
-        <v>3.35639023780823</v>
+        <v>3.35638999938965</v>
       </c>
       <c r="H404" t="n">
         <v>100000</v>
@@ -12114,7 +12114,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G405" t="n">
-        <v>3.39219164848328</v>
+        <v>3.3921914100647</v>
       </c>
       <c r="H405" t="n">
         <v>8000</v>
@@ -12172,7 +12172,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G407" t="n">
-        <v>3.50854659080505</v>
+        <v>3.50854635238647</v>
       </c>
       <c r="H407" t="n">
         <v>800</v>
@@ -12201,7 +12201,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G408" t="n">
-        <v>3.66965293884277</v>
+        <v>3.66965270042419</v>
       </c>
       <c r="H408" t="n">
         <v>3600</v>
@@ -12230,7 +12230,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G409" t="n">
-        <v>3.59805011749268</v>
+        <v>3.59805035591125</v>
       </c>
       <c r="H409" t="n">
         <v>8400</v>
@@ -12259,7 +12259,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G410" t="n">
-        <v>3.56224870681763</v>
+        <v>3.56224846839905</v>
       </c>
       <c r="H410" t="n">
         <v>7200</v>
@@ -12288,7 +12288,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G411" t="n">
-        <v>3.59805011749268</v>
+        <v>3.59805035591125</v>
       </c>
       <c r="H411" t="n">
         <v>3600</v>
@@ -12375,7 +12375,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G414" t="n">
-        <v>3.6338517665863</v>
+        <v>3.63385128974915</v>
       </c>
       <c r="H414" t="n">
         <v>2800</v>
@@ -12404,7 +12404,7 @@
         <v>4.09000015258789</v>
       </c>
       <c r="G415" t="n">
-        <v>3.6607027053833</v>
+        <v>3.66070294380188</v>
       </c>
       <c r="H415" t="n">
         <v>2000</v>
@@ -12433,7 +12433,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G416" t="n">
-        <v>3.6338517665863</v>
+        <v>3.63385128974915</v>
       </c>
       <c r="H416" t="n">
         <v>7200</v>
@@ -12462,7 +12462,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G417" t="n">
-        <v>3.49064588546753</v>
+        <v>3.49064564704895</v>
       </c>
       <c r="H417" t="n">
         <v>10000</v>
@@ -12520,7 +12520,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G419" t="n">
-        <v>3.66965293884277</v>
+        <v>3.66965270042419</v>
       </c>
       <c r="H419" t="n">
         <v>2400</v>
@@ -12578,7 +12578,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G421" t="n">
-        <v>3.66965293884277</v>
+        <v>3.66965270042419</v>
       </c>
       <c r="H421" t="n">
         <v>4800</v>
@@ -12607,7 +12607,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G422" t="n">
-        <v>3.66965293884277</v>
+        <v>3.66965270042419</v>
       </c>
       <c r="H422" t="n">
         <v>0</v>
@@ -12665,7 +12665,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G424" t="n">
-        <v>3.6338517665863</v>
+        <v>3.63385128974915</v>
       </c>
       <c r="H424" t="n">
         <v>13200</v>
@@ -12694,7 +12694,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G425" t="n">
-        <v>3.62490177154541</v>
+        <v>3.62490153312683</v>
       </c>
       <c r="H425" t="n">
         <v>4800</v>
@@ -12723,7 +12723,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G426" t="n">
-        <v>3.6338517665863</v>
+        <v>3.63385128974915</v>
       </c>
       <c r="H426" t="n">
         <v>25200</v>
@@ -12781,7 +12781,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G428" t="n">
-        <v>3.6338517665863</v>
+        <v>3.63385128974915</v>
       </c>
       <c r="H428" t="n">
         <v>5200</v>
@@ -12839,7 +12839,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G430" t="n">
-        <v>3.69650387763977</v>
+        <v>3.69650435447693</v>
       </c>
       <c r="H430" t="n">
         <v>14800</v>
@@ -12868,7 +12868,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G431" t="n">
-        <v>3.75020623207092</v>
+        <v>3.75020670890808</v>
       </c>
       <c r="H431" t="n">
         <v>12000</v>
@@ -12897,7 +12897,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G432" t="n">
-        <v>3.78600811958313</v>
+        <v>3.78600788116455</v>
       </c>
       <c r="H432" t="n">
         <v>63600</v>
@@ -12926,7 +12926,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G433" t="n">
-        <v>3.90236234664917</v>
+        <v>3.90236306190491</v>
       </c>
       <c r="H433" t="n">
         <v>6800</v>
@@ -12955,7 +12955,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G434" t="n">
-        <v>4.0903205871582</v>
+        <v>4.09032106399536</v>
       </c>
       <c r="H434" t="n">
         <v>18800</v>
@@ -12984,7 +12984,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G435" t="n">
-        <v>4.14402341842651</v>
+        <v>4.14402294158936</v>
       </c>
       <c r="H435" t="n">
         <v>20800</v>
@@ -13013,7 +13013,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G436" t="n">
-        <v>4.09927082061768</v>
+        <v>4.09927129745483</v>
       </c>
       <c r="H436" t="n">
         <v>2400</v>
@@ -13042,7 +13042,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G437" t="n">
-        <v>4.09927082061768</v>
+        <v>4.09927129745483</v>
       </c>
       <c r="H437" t="n">
         <v>2000</v>
@@ -13071,7 +13071,7 @@
         <v>4.75</v>
       </c>
       <c r="G438" t="n">
-        <v>4.2514271736145</v>
+        <v>4.25142765045166</v>
       </c>
       <c r="H438" t="n">
         <v>18000</v>
@@ -13129,7 +13129,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G440" t="n">
-        <v>4.37673282623291</v>
+        <v>4.37673330307007</v>
       </c>
       <c r="H440" t="n">
         <v>29200</v>
@@ -13216,7 +13216,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G443" t="n">
-        <v>4.23352670669556</v>
+        <v>4.23352718353271</v>
       </c>
       <c r="H443" t="n">
         <v>11200</v>
@@ -13245,7 +13245,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G444" t="n">
-        <v>4.14402341842651</v>
+        <v>4.14402294158936</v>
       </c>
       <c r="H444" t="n">
         <v>27600</v>
@@ -13274,7 +13274,7 @@
         <v>4.5</v>
       </c>
       <c r="G445" t="n">
-        <v>4.02766752243042</v>
+        <v>4.02766799926758</v>
       </c>
       <c r="H445" t="n">
         <v>32400</v>
@@ -13303,7 +13303,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G446" t="n">
-        <v>3.90236234664917</v>
+        <v>3.90236306190491</v>
       </c>
       <c r="H446" t="n">
         <v>22800</v>
@@ -13332,7 +13332,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G447" t="n">
-        <v>3.92026352882385</v>
+        <v>3.92026376724243</v>
       </c>
       <c r="H447" t="n">
         <v>14400</v>
@@ -13361,7 +13361,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G448" t="n">
-        <v>3.76810765266418</v>
+        <v>3.76810717582703</v>
       </c>
       <c r="H448" t="n">
         <v>15600</v>
@@ -13390,7 +13390,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G449" t="n">
-        <v>3.77705693244934</v>
+        <v>3.7770574092865</v>
       </c>
       <c r="H449" t="n">
         <v>236000</v>
@@ -13419,7 +13419,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G450" t="n">
-        <v>3.66965293884277</v>
+        <v>3.66965270042419</v>
       </c>
       <c r="H450" t="n">
         <v>57200</v>
@@ -13448,7 +13448,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G451" t="n">
-        <v>3.70545411109924</v>
+        <v>3.7054545879364</v>
       </c>
       <c r="H451" t="n">
         <v>36400</v>
@@ -13477,7 +13477,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G452" t="n">
-        <v>3.92921423912048</v>
+        <v>3.92921352386475</v>
       </c>
       <c r="H452" t="n">
         <v>3600</v>
@@ -13506,7 +13506,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G453" t="n">
-        <v>4.00976657867432</v>
+        <v>4.00976753234863</v>
       </c>
       <c r="H453" t="n">
         <v>20800</v>
@@ -13535,7 +13535,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G454" t="n">
-        <v>4.14402341842651</v>
+        <v>4.14402294158936</v>
       </c>
       <c r="H454" t="n">
         <v>8400</v>
@@ -13564,7 +13564,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G455" t="n">
-        <v>4.13507223129272</v>
+        <v>4.13507270812988</v>
       </c>
       <c r="H455" t="n">
         <v>1600</v>
@@ -13593,7 +13593,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G456" t="n">
-        <v>4.05451917648315</v>
+        <v>4.05451965332031</v>
       </c>
       <c r="H456" t="n">
         <v>800</v>
@@ -13622,7 +13622,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G457" t="n">
-        <v>4.20667457580566</v>
+        <v>4.20667505264282</v>
       </c>
       <c r="H457" t="n">
         <v>13200</v>
@@ -13680,7 +13680,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G459" t="n">
-        <v>4.26037788391113</v>
+        <v>4.26037740707397</v>
       </c>
       <c r="H459" t="n">
         <v>10800</v>
@@ -13767,7 +13767,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G462" t="n">
-        <v>4.44833564758301</v>
+        <v>4.44833517074585</v>
       </c>
       <c r="H462" t="n">
         <v>58400</v>
@@ -13796,7 +13796,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G463" t="n">
-        <v>4.3230299949646</v>
+        <v>4.32303047180176</v>
       </c>
       <c r="H463" t="n">
         <v>47090</v>
@@ -13854,7 +13854,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G465" t="n">
-        <v>4.37673282623291</v>
+        <v>4.37673330307007</v>
       </c>
       <c r="H465" t="n">
         <v>29220</v>
@@ -13912,7 +13912,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G467" t="n">
-        <v>4.37673282623291</v>
+        <v>4.37673330307007</v>
       </c>
       <c r="H467" t="n">
         <v>41850</v>
@@ -13970,7 +13970,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G469" t="n">
-        <v>4.21562623977661</v>
+        <v>4.21562576293945</v>
       </c>
       <c r="H469" t="n">
         <v>14730</v>
@@ -13999,7 +13999,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G470" t="n">
-        <v>4.22457599639893</v>
+        <v>4.22457504272461</v>
       </c>
       <c r="H470" t="n">
         <v>24240</v>
@@ -14028,7 +14028,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G471" t="n">
-        <v>4.20667457580566</v>
+        <v>4.20667505264282</v>
       </c>
       <c r="H471" t="n">
         <v>24930</v>
@@ -14057,7 +14057,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G472" t="n">
-        <v>4.38917779922485</v>
+        <v>4.3891773223877</v>
       </c>
       <c r="H472" t="n">
         <v>31650</v>
@@ -14086,7 +14086,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G473" t="n">
-        <v>4.28880167007446</v>
+        <v>4.28880071640015</v>
       </c>
       <c r="H473" t="n">
         <v>68920</v>
@@ -14144,7 +14144,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G475" t="n">
-        <v>4.44392871856689</v>
+        <v>4.44392776489258</v>
       </c>
       <c r="H475" t="n">
         <v>50640</v>
@@ -14173,7 +14173,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G476" t="n">
-        <v>4.28880167007446</v>
+        <v>4.28880071640015</v>
       </c>
       <c r="H476" t="n">
         <v>5140</v>
@@ -14202,7 +14202,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G477" t="n">
-        <v>4.34355163574219</v>
+        <v>4.3435525894165</v>
       </c>
       <c r="H477" t="n">
         <v>8410</v>
@@ -14231,7 +14231,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G478" t="n">
-        <v>4.34355163574219</v>
+        <v>4.3435525894165</v>
       </c>
       <c r="H478" t="n">
         <v>50</v>
@@ -14260,7 +14260,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G479" t="n">
-        <v>4.34355163574219</v>
+        <v>4.3435525894165</v>
       </c>
       <c r="H479" t="n">
         <v>9430</v>
@@ -14289,7 +14289,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G480" t="n">
-        <v>4.34355163574219</v>
+        <v>4.3435525894165</v>
       </c>
       <c r="H480" t="n">
         <v>0</v>
@@ -14347,7 +14347,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G482" t="n">
-        <v>4.26142644882202</v>
+        <v>4.26142597198486</v>
       </c>
       <c r="H482" t="n">
         <v>850</v>
@@ -14376,7 +14376,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G483" t="n">
-        <v>4.28880167007446</v>
+        <v>4.28880071640015</v>
       </c>
       <c r="H483" t="n">
         <v>50</v>
@@ -14405,7 +14405,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G484" t="n">
-        <v>4.21580076217651</v>
+        <v>4.21580028533936</v>
       </c>
       <c r="H484" t="n">
         <v>9650</v>
@@ -14434,7 +14434,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G485" t="n">
-        <v>4.28880167007446</v>
+        <v>4.28880071640015</v>
       </c>
       <c r="H485" t="n">
         <v>460</v>
@@ -14492,7 +14492,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G487" t="n">
-        <v>4.36180257797241</v>
+        <v>4.36180305480957</v>
       </c>
       <c r="H487" t="n">
         <v>1620</v>
@@ -14521,7 +14521,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G488" t="n">
-        <v>4.36180257797241</v>
+        <v>4.36180305480957</v>
       </c>
       <c r="H488" t="n">
         <v>0</v>
@@ -14550,7 +14550,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G489" t="n">
-        <v>4.34355163574219</v>
+        <v>4.3435525894165</v>
       </c>
       <c r="H489" t="n">
         <v>12940</v>
@@ -14579,7 +14579,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G490" t="n">
-        <v>4.28880167007446</v>
+        <v>4.28880071640015</v>
       </c>
       <c r="H490" t="n">
         <v>2140</v>
@@ -14608,7 +14608,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G491" t="n">
-        <v>4.28880167007446</v>
+        <v>4.28880071640015</v>
       </c>
       <c r="H491" t="n">
         <v>5200</v>
@@ -14724,7 +14724,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G495" t="n">
-        <v>4.38005352020264</v>
+        <v>4.38005256652832</v>
       </c>
       <c r="H495" t="n">
         <v>24640</v>
@@ -14753,7 +14753,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G496" t="n">
-        <v>4.34355163574219</v>
+        <v>4.3435525894165</v>
       </c>
       <c r="H496" t="n">
         <v>860</v>
@@ -14782,7 +14782,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G497" t="n">
-        <v>4.38005352020264</v>
+        <v>4.38005256652832</v>
       </c>
       <c r="H497" t="n">
         <v>1050</v>
@@ -14869,7 +14869,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G500" t="n">
-        <v>4.38005352020264</v>
+        <v>4.38005256652832</v>
       </c>
       <c r="H500" t="n">
         <v>2200</v>
@@ -14927,7 +14927,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G502" t="n">
-        <v>4.34355163574219</v>
+        <v>4.3435525894165</v>
       </c>
       <c r="H502" t="n">
         <v>4870</v>
@@ -14985,7 +14985,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G504" t="n">
-        <v>4.29792642593384</v>
+        <v>4.29792594909668</v>
       </c>
       <c r="H504" t="n">
         <v>11000</v>
@@ -15014,7 +15014,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G505" t="n">
-        <v>4.29792642593384</v>
+        <v>4.29792594909668</v>
       </c>
       <c r="H505" t="n">
         <v>5650</v>
@@ -15043,7 +15043,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G506" t="n">
-        <v>4.29792642593384</v>
+        <v>4.29792594909668</v>
       </c>
       <c r="H506" t="n">
         <v>0</v>
@@ -15072,7 +15072,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G507" t="n">
-        <v>4.38005352020264</v>
+        <v>4.38005256652832</v>
       </c>
       <c r="H507" t="n">
         <v>2850</v>
@@ -15101,7 +15101,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G508" t="n">
-        <v>4.38005352020264</v>
+        <v>4.38005256652832</v>
       </c>
       <c r="H508" t="n">
         <v>3390</v>
@@ -15130,7 +15130,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G509" t="n">
-        <v>4.3161768913269</v>
+        <v>4.31617641448975</v>
       </c>
       <c r="H509" t="n">
         <v>10880</v>
@@ -15159,7 +15159,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G510" t="n">
-        <v>4.32530117034912</v>
+        <v>4.32530164718628</v>
       </c>
       <c r="H510" t="n">
         <v>8840</v>
@@ -15188,7 +15188,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G511" t="n">
-        <v>4.3161768913269</v>
+        <v>4.31617641448975</v>
       </c>
       <c r="H511" t="n">
         <v>4040</v>
@@ -15217,7 +15217,7 @@
         <v>4.73999977111816</v>
       </c>
       <c r="G512" t="n">
-        <v>4.32530117034912</v>
+        <v>4.32530164718628</v>
       </c>
       <c r="H512" t="n">
         <v>7600</v>
@@ -15246,7 +15246,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G513" t="n">
-        <v>4.30705165863037</v>
+        <v>4.30705118179321</v>
       </c>
       <c r="H513" t="n">
         <v>8080</v>
@@ -15304,7 +15304,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G515" t="n">
-        <v>4.30705165863037</v>
+        <v>4.30705118179321</v>
       </c>
       <c r="H515" t="n">
         <v>12400</v>
@@ -15333,7 +15333,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G516" t="n">
-        <v>4.28880167007446</v>
+        <v>4.28880071640015</v>
       </c>
       <c r="H516" t="n">
         <v>34580</v>
@@ -15362,7 +15362,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G517" t="n">
-        <v>4.30705165863037</v>
+        <v>4.30705118179321</v>
       </c>
       <c r="H517" t="n">
         <v>4210</v>
@@ -15420,7 +15420,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G519" t="n">
-        <v>4.59905529022217</v>
+        <v>4.59905481338501</v>
       </c>
       <c r="H519" t="n">
         <v>33900</v>
@@ -15478,7 +15478,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G521" t="n">
-        <v>4.58080434799194</v>
+        <v>4.5808048248291</v>
       </c>
       <c r="H521" t="n">
         <v>33970</v>
@@ -15507,7 +15507,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G522" t="n">
-        <v>4.48042821884155</v>
+        <v>4.48042917251587</v>
       </c>
       <c r="H522" t="n">
         <v>9600</v>
@@ -15565,7 +15565,7 @@
         <v>5.07999992370605</v>
       </c>
       <c r="G524" t="n">
-        <v>4.63555574417114</v>
+        <v>4.6355562210083</v>
       </c>
       <c r="H524" t="n">
         <v>17020</v>
@@ -15594,7 +15594,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G525" t="n">
-        <v>4.72680616378784</v>
+        <v>4.726806640625</v>
       </c>
       <c r="H525" t="n">
         <v>50940</v>
@@ -15623,7 +15623,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G526" t="n">
-        <v>4.79980754852295</v>
+        <v>4.79980802536011</v>
       </c>
       <c r="H526" t="n">
         <v>23760</v>
@@ -15652,7 +15652,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G527" t="n">
-        <v>4.90930986404419</v>
+        <v>4.90930891036987</v>
       </c>
       <c r="H527" t="n">
         <v>43970</v>
@@ -15681,7 +15681,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G528" t="n">
-        <v>4.90930986404419</v>
+        <v>4.90930891036987</v>
       </c>
       <c r="H528" t="n">
         <v>20060</v>
@@ -15710,7 +15710,7 @@
         <v>5.40000009536743</v>
       </c>
       <c r="G529" t="n">
-        <v>4.9275598526001</v>
+        <v>4.92755937576294</v>
       </c>
       <c r="H529" t="n">
         <v>34600</v>
@@ -15739,7 +15739,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G530" t="n">
-        <v>4.96405935287476</v>
+        <v>4.96406030654907</v>
       </c>
       <c r="H530" t="n">
         <v>41950</v>
@@ -15768,7 +15768,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G531" t="n">
-        <v>4.94580984115601</v>
+        <v>4.94581031799316</v>
       </c>
       <c r="H531" t="n">
         <v>25300</v>
@@ -15826,7 +15826,7 @@
         <v>5.5</v>
       </c>
       <c r="G533" t="n">
-        <v>5.01880979537964</v>
+        <v>5.01881074905396</v>
       </c>
       <c r="H533" t="n">
         <v>25630</v>
@@ -15884,7 +15884,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G535" t="n">
-        <v>5.20131206512451</v>
+        <v>5.20131158828735</v>
       </c>
       <c r="H535" t="n">
         <v>24750</v>
@@ -15913,7 +15913,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G536" t="n">
-        <v>5.27431297302246</v>
+        <v>5.27431344985962</v>
       </c>
       <c r="H536" t="n">
         <v>33770</v>
@@ -15942,7 +15942,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G537" t="n">
-        <v>5.18306255340576</v>
+        <v>5.18306159973145</v>
       </c>
       <c r="H537" t="n">
         <v>35600</v>
@@ -16058,7 +16058,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G541" t="n">
-        <v>5.00055980682373</v>
+        <v>5.00056028366089</v>
       </c>
       <c r="H541" t="n">
         <v>23360</v>
@@ -16087,7 +16087,7 @@
         <v>5.5</v>
       </c>
       <c r="G542" t="n">
-        <v>5.01880979537964</v>
+        <v>5.01881074905396</v>
       </c>
       <c r="H542" t="n">
         <v>11030</v>
@@ -16116,7 +16116,7 @@
         <v>5.51999998092651</v>
       </c>
       <c r="G543" t="n">
-        <v>5.03706073760986</v>
+        <v>5.03706026077271</v>
       </c>
       <c r="H543" t="n">
         <v>7260</v>
@@ -16145,7 +16145,7 @@
         <v>5.5</v>
       </c>
       <c r="G544" t="n">
-        <v>5.01880979537964</v>
+        <v>5.01881074905396</v>
       </c>
       <c r="H544" t="n">
         <v>14790</v>
@@ -16203,7 +16203,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G546" t="n">
-        <v>5.14656209945679</v>
+        <v>5.14656114578247</v>
       </c>
       <c r="H546" t="n">
         <v>6000</v>
@@ -16232,7 +16232,7 @@
         <v>5.6399998664856</v>
       </c>
       <c r="G547" t="n">
-        <v>5.14656209945679</v>
+        <v>5.14656114578247</v>
       </c>
       <c r="H547" t="n">
         <v>9900</v>
@@ -16261,7 +16261,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G548" t="n">
-        <v>5.20131206512451</v>
+        <v>5.20131158828735</v>
       </c>
       <c r="H548" t="n">
         <v>9250</v>
@@ -16319,7 +16319,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G550" t="n">
-        <v>5.1283106803894</v>
+        <v>5.12831163406372</v>
       </c>
       <c r="H550" t="n">
         <v>15220</v>
@@ -16348,7 +16348,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G551" t="n">
-        <v>5.18306255340576</v>
+        <v>5.18306159973145</v>
       </c>
       <c r="H551" t="n">
         <v>21670</v>
@@ -16406,7 +16406,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G553" t="n">
-        <v>5.29256343841553</v>
+        <v>5.29256391525269</v>
       </c>
       <c r="H553" t="n">
         <v>68800</v>
@@ -16435,7 +16435,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G554" t="n">
-        <v>5.29256343841553</v>
+        <v>5.29256391525269</v>
       </c>
       <c r="H554" t="n">
         <v>18450</v>
@@ -16464,7 +16464,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G555" t="n">
-        <v>5.25606346130371</v>
+        <v>5.25606298446655</v>
       </c>
       <c r="H555" t="n">
         <v>29560</v>
@@ -16493,7 +16493,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G556" t="n">
-        <v>5.32906436920166</v>
+        <v>5.3290638923645</v>
       </c>
       <c r="H556" t="n">
         <v>5650</v>
@@ -16522,7 +16522,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G557" t="n">
-        <v>5.42031478881836</v>
+        <v>5.42031574249268</v>
       </c>
       <c r="H557" t="n">
         <v>9520</v>
@@ -16551,7 +16551,7 @@
         <v>6</v>
       </c>
       <c r="G558" t="n">
-        <v>5.47506618499756</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H558" t="n">
         <v>25750</v>
@@ -16609,7 +16609,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G560" t="n">
-        <v>5.73056936264038</v>
+        <v>5.73056888580322</v>
       </c>
       <c r="H560" t="n">
         <v>16040</v>
@@ -16638,7 +16638,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G561" t="n">
-        <v>5.49331617355347</v>
+        <v>5.49331569671631</v>
       </c>
       <c r="H561" t="n">
         <v>18810</v>
@@ -16667,7 +16667,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G562" t="n">
-        <v>5.56631660461426</v>
+        <v>5.56631708145142</v>
       </c>
       <c r="H562" t="n">
         <v>6700</v>
@@ -16696,7 +16696,7 @@
         <v>6</v>
       </c>
       <c r="G563" t="n">
-        <v>5.47506618499756</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H563" t="n">
         <v>14950</v>
@@ -16725,7 +16725,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G564" t="n">
-        <v>5.42031478881836</v>
+        <v>5.42031574249268</v>
       </c>
       <c r="H564" t="n">
         <v>9900</v>
@@ -16754,7 +16754,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G565" t="n">
-        <v>5.32906436920166</v>
+        <v>5.3290638923645</v>
       </c>
       <c r="H565" t="n">
         <v>24480</v>
@@ -16783,7 +16783,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G566" t="n">
-        <v>5.29256343841553</v>
+        <v>5.29256391525269</v>
       </c>
       <c r="H566" t="n">
         <v>12560</v>
@@ -16812,7 +16812,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G567" t="n">
-        <v>5.29256343841553</v>
+        <v>5.29256391525269</v>
       </c>
       <c r="H567" t="n">
         <v>9940</v>
@@ -16841,7 +16841,7 @@
         <v>5.78000020980835</v>
       </c>
       <c r="G568" t="n">
-        <v>5.27431297302246</v>
+        <v>5.27431344985962</v>
       </c>
       <c r="H568" t="n">
         <v>20720</v>
@@ -16870,7 +16870,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G569" t="n">
-        <v>5.25606346130371</v>
+        <v>5.25606298446655</v>
       </c>
       <c r="H569" t="n">
         <v>23620</v>
@@ -16899,7 +16899,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G570" t="n">
-        <v>5.29256343841553</v>
+        <v>5.29256391525269</v>
       </c>
       <c r="H570" t="n">
         <v>10610</v>
@@ -16928,7 +16928,7 @@
         <v>5.84000015258789</v>
       </c>
       <c r="G571" t="n">
-        <v>5.32906436920166</v>
+        <v>5.3290638923645</v>
       </c>
       <c r="H571" t="n">
         <v>6910</v>
@@ -16957,7 +16957,7 @@
         <v>6</v>
       </c>
       <c r="G572" t="n">
-        <v>5.47506618499756</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H572" t="n">
         <v>21030</v>
@@ -16986,7 +16986,7 @@
         <v>6</v>
       </c>
       <c r="G573" t="n">
-        <v>5.47506618499756</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H573" t="n">
         <v>18730</v>
@@ -17015,7 +17015,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G574" t="n">
-        <v>5.42031478881836</v>
+        <v>5.42031574249268</v>
       </c>
       <c r="H574" t="n">
         <v>15810</v>
@@ -17044,7 +17044,7 @@
         <v>5.92000007629395</v>
       </c>
       <c r="G575" t="n">
-        <v>5.40206480026245</v>
+        <v>5.40206527709961</v>
       </c>
       <c r="H575" t="n">
         <v>9530</v>
@@ -17073,7 +17073,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G576" t="n">
-        <v>5.31081390380859</v>
+        <v>5.31081438064575</v>
       </c>
       <c r="H576" t="n">
         <v>56590</v>
@@ -17102,7 +17102,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G577" t="n">
-        <v>5.29256343841553</v>
+        <v>5.29256391525269</v>
       </c>
       <c r="H577" t="n">
         <v>29590</v>
@@ -17131,7 +17131,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G578" t="n">
-        <v>5.36556482315063</v>
+        <v>5.36556434631348</v>
       </c>
       <c r="H578" t="n">
         <v>30630</v>
@@ -17189,7 +17189,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G580" t="n">
-        <v>5.42031478881836</v>
+        <v>5.42031574249268</v>
       </c>
       <c r="H580" t="n">
         <v>10880</v>
@@ -17247,7 +17247,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G582" t="n">
-        <v>5.49331617355347</v>
+        <v>5.49331569671631</v>
       </c>
       <c r="H582" t="n">
         <v>11710</v>
@@ -17276,7 +17276,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G583" t="n">
-        <v>5.43856477737427</v>
+        <v>5.43856525421143</v>
       </c>
       <c r="H583" t="n">
         <v>8370</v>
@@ -17305,7 +17305,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G584" t="n">
-        <v>5.43856477737427</v>
+        <v>5.43856525421143</v>
       </c>
       <c r="H584" t="n">
         <v>8130</v>
@@ -17334,7 +17334,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G585" t="n">
-        <v>5.43856477737427</v>
+        <v>5.43856525421143</v>
       </c>
       <c r="H585" t="n">
         <v>3760</v>
@@ -17363,7 +17363,7 @@
         <v>5.94000005722046</v>
       </c>
       <c r="G586" t="n">
-        <v>5.42031478881836</v>
+        <v>5.42031574249268</v>
       </c>
       <c r="H586" t="n">
         <v>2870</v>
@@ -17392,7 +17392,7 @@
         <v>6</v>
       </c>
       <c r="G587" t="n">
-        <v>5.47506618499756</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H587" t="n">
         <v>6650</v>
@@ -17421,7 +17421,7 @@
         <v>6</v>
       </c>
       <c r="G588" t="n">
-        <v>5.47506618499756</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H588" t="n">
         <v>6150</v>
@@ -17450,7 +17450,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G589" t="n">
-        <v>5.43856477737427</v>
+        <v>5.43856525421143</v>
       </c>
       <c r="H589" t="n">
         <v>18000</v>
@@ -17479,7 +17479,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G590" t="n">
-        <v>5.43856477737427</v>
+        <v>5.43856525421143</v>
       </c>
       <c r="H590" t="n">
         <v>10770</v>
@@ -17508,7 +17508,7 @@
         <v>6</v>
       </c>
       <c r="G591" t="n">
-        <v>5.47506618499756</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H591" t="n">
         <v>16840</v>
@@ -17537,7 +17537,7 @@
         <v>6</v>
       </c>
       <c r="G592" t="n">
-        <v>5.47506618499756</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H592" t="n">
         <v>6770</v>
@@ -17566,7 +17566,7 @@
         <v>6</v>
       </c>
       <c r="G593" t="n">
-        <v>5.47506618499756</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H593" t="n">
         <v>7700</v>
@@ -17595,7 +17595,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G594" t="n">
-        <v>5.43856477737427</v>
+        <v>5.43856525421143</v>
       </c>
       <c r="H594" t="n">
         <v>8420</v>
@@ -17624,7 +17624,7 @@
         <v>6</v>
       </c>
       <c r="G595" t="n">
-        <v>5.47506618499756</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H595" t="n">
         <v>28420</v>
@@ -17653,7 +17653,7 @@
         <v>6</v>
       </c>
       <c r="G596" t="n">
-        <v>5.47506618499756</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H596" t="n">
         <v>16270</v>
@@ -17682,7 +17682,7 @@
         <v>6</v>
       </c>
       <c r="G597" t="n">
-        <v>5.47506618499756</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H597" t="n">
         <v>22430</v>
@@ -17740,7 +17740,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G599" t="n">
-        <v>5.51156568527222</v>
+        <v>5.51156616210938</v>
       </c>
       <c r="H599" t="n">
         <v>8740</v>
@@ -17769,7 +17769,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G600" t="n">
-        <v>5.49331617355347</v>
+        <v>5.49331569671631</v>
       </c>
       <c r="H600" t="n">
         <v>6490</v>
@@ -17798,7 +17798,7 @@
         <v>6</v>
       </c>
       <c r="G601" t="n">
-        <v>5.47506618499756</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H601" t="n">
         <v>12580</v>
@@ -17827,7 +17827,7 @@
         <v>6</v>
       </c>
       <c r="G602" t="n">
-        <v>5.47506618499756</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H602" t="n">
         <v>14360</v>
@@ -17856,7 +17856,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G603" t="n">
-        <v>5.51156568527222</v>
+        <v>5.51156616210938</v>
       </c>
       <c r="H603" t="n">
         <v>21920</v>
@@ -17885,7 +17885,7 @@
         <v>6</v>
       </c>
       <c r="G604" t="n">
-        <v>5.47506618499756</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H604" t="n">
         <v>7460</v>
@@ -17914,7 +17914,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G605" t="n">
-        <v>5.51156568527222</v>
+        <v>5.51156616210938</v>
       </c>
       <c r="H605" t="n">
         <v>20050</v>
@@ -17943,7 +17943,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G606" t="n">
-        <v>5.69406890869141</v>
+        <v>5.69406795501709</v>
       </c>
       <c r="H606" t="n">
         <v>42810</v>
@@ -17972,7 +17972,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G607" t="n">
-        <v>5.80356979370117</v>
+        <v>5.80356931686401</v>
       </c>
       <c r="H607" t="n">
         <v>21150</v>
@@ -18030,7 +18030,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G609" t="n">
-        <v>6.29632616043091</v>
+        <v>6.29632472991943</v>
       </c>
       <c r="H609" t="n">
         <v>137430</v>
@@ -18088,7 +18088,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G611" t="n">
-        <v>6.40582704544067</v>
+        <v>6.40582656860352</v>
       </c>
       <c r="H611" t="n">
         <v>17630</v>
@@ -18262,7 +18262,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G617" t="n">
-        <v>6.55182838439941</v>
+        <v>6.55182886123657</v>
       </c>
       <c r="H617" t="n">
         <v>32250</v>
@@ -18291,7 +18291,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G618" t="n">
-        <v>6.69783115386963</v>
+        <v>6.69783020019531</v>
       </c>
       <c r="H618" t="n">
         <v>27550</v>
@@ -18320,7 +18320,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G619" t="n">
-        <v>7.00808334350586</v>
+        <v>7.00808382034302</v>
       </c>
       <c r="H619" t="n">
         <v>96620</v>
@@ -18349,7 +18349,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G620" t="n">
-        <v>6.91683340072632</v>
+        <v>6.916832447052</v>
       </c>
       <c r="H620" t="n">
         <v>191410</v>
@@ -18436,7 +18436,7 @@
         <v>8.10000038146973</v>
       </c>
       <c r="G623" t="n">
-        <v>7.39133930206299</v>
+        <v>7.39133977890015</v>
       </c>
       <c r="H623" t="n">
         <v>44150</v>
@@ -18465,7 +18465,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G624" t="n">
-        <v>7.62859058380127</v>
+        <v>7.62859153747559</v>
       </c>
       <c r="H624" t="n">
         <v>62840</v>
@@ -18494,7 +18494,7 @@
         <v>8.5</v>
       </c>
       <c r="G625" t="n">
-        <v>7.75634384155273</v>
+        <v>7.75634288787842</v>
       </c>
       <c r="H625" t="n">
         <v>102230</v>
@@ -18523,7 +18523,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G626" t="n">
-        <v>7.73809289932251</v>
+        <v>7.73809385299683</v>
       </c>
       <c r="H626" t="n">
         <v>60240</v>
@@ -18552,7 +18552,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G627" t="n">
-        <v>7.84759521484375</v>
+        <v>7.84759426116943</v>
       </c>
       <c r="H627" t="n">
         <v>36570</v>
@@ -18581,7 +18581,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G628" t="n">
-        <v>7.88409519195557</v>
+        <v>7.88409376144409</v>
       </c>
       <c r="H628" t="n">
         <v>62240</v>
@@ -18610,7 +18610,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G629" t="n">
-        <v>7.84759521484375</v>
+        <v>7.84759426116943</v>
       </c>
       <c r="H629" t="n">
         <v>64170</v>
@@ -18639,7 +18639,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G630" t="n">
-        <v>7.93884372711182</v>
+        <v>7.93884515762329</v>
       </c>
       <c r="H630" t="n">
         <v>111190</v>
@@ -18668,7 +18668,7 @@
         <v>8.5</v>
       </c>
       <c r="G631" t="n">
-        <v>7.75634384155273</v>
+        <v>7.75634288787842</v>
       </c>
       <c r="H631" t="n">
         <v>24340</v>
@@ -18697,7 +18697,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G632" t="n">
-        <v>7.93884372711182</v>
+        <v>7.93884515762329</v>
       </c>
       <c r="H632" t="n">
         <v>34610</v>
@@ -18726,7 +18726,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G633" t="n">
-        <v>7.97534704208374</v>
+        <v>7.97534418106079</v>
       </c>
       <c r="H633" t="n">
         <v>75730</v>
@@ -18755,7 +18755,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G634" t="n">
-        <v>8.43160152435303</v>
+        <v>8.43160057067871</v>
       </c>
       <c r="H634" t="n">
         <v>84630</v>
@@ -18784,7 +18784,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G635" t="n">
-        <v>8.57760334014893</v>
+        <v>8.57760143280029</v>
       </c>
       <c r="H635" t="n">
         <v>55940</v>
@@ -18813,7 +18813,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G636" t="n">
-        <v>8.65060234069824</v>
+        <v>8.65060329437256</v>
       </c>
       <c r="H636" t="n">
         <v>62370</v>
@@ -18842,7 +18842,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G637" t="n">
-        <v>8.63235378265381</v>
+        <v>8.63235282897949</v>
       </c>
       <c r="H637" t="n">
         <v>15840</v>
@@ -18871,7 +18871,7 @@
         <v>9.47999954223633</v>
       </c>
       <c r="G638" t="n">
-        <v>8.65060234069824</v>
+        <v>8.65060329437256</v>
       </c>
       <c r="H638" t="n">
         <v>48570</v>
@@ -18987,7 +18987,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G642" t="n">
-        <v>8.61410331726074</v>
+        <v>8.61410236358643</v>
       </c>
       <c r="H642" t="n">
         <v>18550</v>
@@ -19016,7 +19016,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G643" t="n">
-        <v>8.57760334014893</v>
+        <v>8.57760143280029</v>
       </c>
       <c r="H643" t="n">
         <v>18630</v>
@@ -19045,7 +19045,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G644" t="n">
-        <v>8.43160152435303</v>
+        <v>8.43160057067871</v>
       </c>
       <c r="H644" t="n">
         <v>12650</v>
@@ -19132,7 +19132,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G647" t="n">
-        <v>8.13959789276123</v>
+        <v>8.13959884643555</v>
       </c>
       <c r="H647" t="n">
         <v>104150</v>
@@ -19161,7 +19161,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G648" t="n">
-        <v>8.3038501739502</v>
+        <v>8.30384922027588</v>
       </c>
       <c r="H648" t="n">
         <v>36710</v>
@@ -19190,7 +19190,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G649" t="n">
-        <v>8.52285289764404</v>
+        <v>8.52285194396973</v>
       </c>
       <c r="H649" t="n">
         <v>12850</v>
@@ -19364,7 +19364,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G655" t="n">
-        <v>9.08860969543457</v>
+        <v>9.08860874176025</v>
       </c>
       <c r="H655" t="n">
         <v>93420</v>
@@ -19451,7 +19451,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G658" t="n">
-        <v>9.76386642456055</v>
+        <v>9.76386547088623</v>
       </c>
       <c r="H658" t="n">
         <v>70640</v>
@@ -19509,7 +19509,7 @@
         <v>10.5</v>
       </c>
       <c r="G660" t="n">
-        <v>9.58136653900146</v>
+        <v>9.58136463165283</v>
       </c>
       <c r="H660" t="n">
         <v>113360</v>
@@ -19538,7 +19538,7 @@
         <v>10.5</v>
       </c>
       <c r="G661" t="n">
-        <v>9.58136653900146</v>
+        <v>9.58136463165283</v>
       </c>
       <c r="H661" t="n">
         <v>25080</v>
@@ -19567,7 +19567,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G662" t="n">
-        <v>9.67261695861816</v>
+        <v>9.67261600494385</v>
       </c>
       <c r="H662" t="n">
         <v>63420</v>
@@ -19596,7 +19596,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G663" t="n">
-        <v>9.53573894500732</v>
+        <v>9.53573989868164</v>
       </c>
       <c r="H663" t="n">
         <v>27690</v>
@@ -19625,7 +19625,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G664" t="n">
-        <v>9.39886283874512</v>
+        <v>9.39886379241943</v>
       </c>
       <c r="H664" t="n">
         <v>37000</v>
@@ -19654,7 +19654,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G665" t="n">
-        <v>9.53573894500732</v>
+        <v>9.53573989868164</v>
       </c>
       <c r="H665" t="n">
         <v>29270</v>
@@ -19683,7 +19683,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G666" t="n">
-        <v>9.62699127197266</v>
+        <v>9.62699222564697</v>
       </c>
       <c r="H666" t="n">
         <v>26760</v>
@@ -19712,7 +19712,7 @@
         <v>10.75</v>
       </c>
       <c r="G667" t="n">
-        <v>9.80949401855469</v>
+        <v>9.80949211120605</v>
       </c>
       <c r="H667" t="n">
         <v>19160</v>
@@ -19770,7 +19770,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G669" t="n">
-        <v>9.53573894500732</v>
+        <v>9.53573989868164</v>
       </c>
       <c r="H669" t="n">
         <v>53000</v>
@@ -19799,7 +19799,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G670" t="n">
-        <v>9.39886283874512</v>
+        <v>9.39886379241943</v>
       </c>
       <c r="H670" t="n">
         <v>8710</v>
@@ -19828,7 +19828,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G671" t="n">
-        <v>9.39886283874512</v>
+        <v>9.39886379241943</v>
       </c>
       <c r="H671" t="n">
         <v>18370</v>
@@ -19915,7 +19915,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G674" t="n">
-        <v>9.3076114654541</v>
+        <v>9.30761241912842</v>
       </c>
       <c r="H674" t="n">
         <v>24650</v>
@@ -19944,7 +19944,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>9.4901123046875</v>
+        <v>9.49011421203613</v>
       </c>
       <c r="H675" t="n">
         <v>65020</v>
@@ -19973,7 +19973,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G676" t="n">
-        <v>9.67261695861816</v>
+        <v>9.67261600494385</v>
       </c>
       <c r="H676" t="n">
         <v>54230</v>
@@ -20176,7 +20176,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G683" t="n">
-        <v>9.67261695861816</v>
+        <v>9.67261600494385</v>
       </c>
       <c r="H683" t="n">
         <v>35330</v>
@@ -20205,7 +20205,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G684" t="n">
-        <v>9.67261695861816</v>
+        <v>9.67261600494385</v>
       </c>
       <c r="H684" t="n">
         <v>10770</v>
@@ -20234,7 +20234,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G685" t="n">
-        <v>9.67261695861816</v>
+        <v>9.67261600494385</v>
       </c>
       <c r="H685" t="n">
         <v>49820</v>
@@ -20263,7 +20263,7 @@
         <v>10.75</v>
       </c>
       <c r="G686" t="n">
-        <v>9.80949401855469</v>
+        <v>9.80949211120605</v>
       </c>
       <c r="H686" t="n">
         <v>46500</v>
@@ -20292,7 +20292,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G687" t="n">
-        <v>9.71824169158936</v>
+        <v>9.71824073791504</v>
       </c>
       <c r="H687" t="n">
         <v>11900</v>
@@ -20350,7 +20350,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G689" t="n">
-        <v>9.26198577880859</v>
+        <v>9.26198482513428</v>
       </c>
       <c r="H689" t="n">
         <v>49040</v>
@@ -20379,7 +20379,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G690" t="n">
-        <v>9.62699127197266</v>
+        <v>9.62699222564697</v>
       </c>
       <c r="H690" t="n">
         <v>39680</v>
@@ -20466,7 +20466,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G693" t="n">
-        <v>8.77835559844971</v>
+        <v>8.77835464477539</v>
       </c>
       <c r="H693" t="n">
         <v>65620</v>
@@ -20524,7 +20524,7 @@
         <v>9.52000045776367</v>
       </c>
       <c r="G695" t="n">
-        <v>8.68710327148438</v>
+        <v>8.68710517883301</v>
       </c>
       <c r="H695" t="n">
         <v>22500</v>
@@ -20582,7 +20582,7 @@
         <v>8.60000038146973</v>
       </c>
       <c r="G697" t="n">
-        <v>7.84759521484375</v>
+        <v>7.84759426116943</v>
       </c>
       <c r="H697" t="n">
         <v>38820</v>
@@ -20611,7 +20611,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G698" t="n">
-        <v>7.61034202575684</v>
+        <v>7.61034154891968</v>
       </c>
       <c r="H698" t="n">
         <v>97230</v>
@@ -20698,7 +20698,7 @@
         <v>7.5</v>
       </c>
       <c r="G701" t="n">
-        <v>6.84383249282837</v>
+        <v>6.84383296966553</v>
       </c>
       <c r="H701" t="n">
         <v>39240</v>
@@ -20727,7 +20727,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G702" t="n">
-        <v>7.263587474823</v>
+        <v>7.26358699798584</v>
       </c>
       <c r="H702" t="n">
         <v>33850</v>
@@ -20814,7 +20814,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G705" t="n">
-        <v>6.91683340072632</v>
+        <v>6.916832447052</v>
       </c>
       <c r="H705" t="n">
         <v>3640</v>
@@ -20930,7 +20930,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G709" t="n">
-        <v>7.62859058380127</v>
+        <v>7.62859153747559</v>
       </c>
       <c r="H709" t="n">
         <v>49380</v>
@@ -20959,7 +20959,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G710" t="n">
-        <v>8.03009605407715</v>
+        <v>8.03009700775146</v>
       </c>
       <c r="H710" t="n">
         <v>47530</v>
@@ -20988,7 +20988,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G711" t="n">
-        <v>7.64684104919434</v>
+        <v>7.64684152603149</v>
       </c>
       <c r="H711" t="n">
         <v>22410</v>
@@ -21017,7 +21017,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G712" t="n">
-        <v>7.77459335327148</v>
+        <v>7.7745943069458</v>
       </c>
       <c r="H712" t="n">
         <v>8030</v>
@@ -21046,7 +21046,7 @@
         <v>8.5</v>
       </c>
       <c r="G713" t="n">
-        <v>7.75634384155273</v>
+        <v>7.75634288787842</v>
       </c>
       <c r="H713" t="n">
         <v>8220</v>
@@ -21075,7 +21075,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G714" t="n">
-        <v>7.88409519195557</v>
+        <v>7.88409376144409</v>
       </c>
       <c r="H714" t="n">
         <v>21440</v>
@@ -21162,7 +21162,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G717" t="n">
-        <v>8.3038501739502</v>
+        <v>8.30384922027588</v>
       </c>
       <c r="H717" t="n">
         <v>7250</v>
@@ -21191,7 +21191,7 @@
         <v>9.19999980926514</v>
       </c>
       <c r="G718" t="n">
-        <v>8.39509963989258</v>
+        <v>8.39510059356689</v>
       </c>
       <c r="H718" t="n">
         <v>24540</v>
@@ -21220,7 +21220,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G719" t="n">
-        <v>8.76010704040527</v>
+        <v>8.76010513305664</v>
       </c>
       <c r="H719" t="n">
         <v>30560</v>
@@ -21336,7 +21336,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G723" t="n">
-        <v>8.92435646057129</v>
+        <v>8.92435741424561</v>
       </c>
       <c r="H723" t="n">
         <v>29670</v>
@@ -21394,7 +21394,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G725" t="n">
-        <v>9.08860969543457</v>
+        <v>9.08860874176025</v>
       </c>
       <c r="H725" t="n">
         <v>13110</v>
@@ -21423,7 +21423,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G726" t="n">
-        <v>9.08860969543457</v>
+        <v>9.08860874176025</v>
       </c>
       <c r="H726" t="n">
         <v>16420</v>
@@ -21452,7 +21452,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G727" t="n">
-        <v>9.44448757171631</v>
+        <v>9.44448947906494</v>
       </c>
       <c r="H727" t="n">
         <v>44000</v>
@@ -21481,7 +21481,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G728" t="n">
-        <v>9.53573894500732</v>
+        <v>9.53573989868164</v>
       </c>
       <c r="H728" t="n">
         <v>20930</v>
@@ -21510,7 +21510,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G729" t="n">
-        <v>9.53573894500732</v>
+        <v>9.53573989868164</v>
       </c>
       <c r="H729" t="n">
         <v>16620</v>
@@ -21539,7 +21539,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G730" t="n">
-        <v>9.4901123046875</v>
+        <v>9.49011421203613</v>
       </c>
       <c r="H730" t="n">
         <v>12710</v>
@@ -21568,7 +21568,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>9.67261695861816</v>
+        <v>9.67261600494385</v>
       </c>
       <c r="H731" t="n">
         <v>42830</v>
@@ -21597,7 +21597,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G732" t="n">
-        <v>9.67261695861816</v>
+        <v>9.67261600494385</v>
       </c>
       <c r="H732" t="n">
         <v>33020</v>
@@ -21626,7 +21626,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G733" t="n">
-        <v>10.2201223373413</v>
+        <v>10.2201232910156</v>
       </c>
       <c r="H733" t="n">
         <v>77220</v>
@@ -21655,7 +21655,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G734" t="n">
-        <v>10.402624130249</v>
+        <v>10.4026231765747</v>
       </c>
       <c r="H734" t="n">
         <v>64310</v>
@@ -21684,7 +21684,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G735" t="n">
-        <v>10.356390953064</v>
+        <v>10.3563919067383</v>
       </c>
       <c r="H735" t="n">
         <v>21950</v>
@@ -21713,7 +21713,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G736" t="n">
-        <v>10.1252212524414</v>
+        <v>10.1252222061157</v>
       </c>
       <c r="H736" t="n">
         <v>25430</v>
@@ -21742,7 +21742,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G737" t="n">
-        <v>10.2176895141602</v>
+        <v>10.2176904678345</v>
       </c>
       <c r="H737" t="n">
         <v>35810</v>
@@ -21771,7 +21771,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G738" t="n">
-        <v>10.3101568222046</v>
+        <v>10.3101577758789</v>
       </c>
       <c r="H738" t="n">
         <v>11660</v>
@@ -21800,7 +21800,7 @@
         <v>11</v>
       </c>
       <c r="G739" t="n">
-        <v>10.1714544296265</v>
+        <v>10.1714563369751</v>
       </c>
       <c r="H739" t="n">
         <v>10800</v>
@@ -21829,7 +21829,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G740" t="n">
-        <v>10.4950942993164</v>
+        <v>10.4950923919678</v>
       </c>
       <c r="H740" t="n">
         <v>13150</v>
@@ -21858,7 +21858,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G741" t="n">
-        <v>10.3101568222046</v>
+        <v>10.3101577758789</v>
       </c>
       <c r="H741" t="n">
         <v>14980</v>
@@ -21887,7 +21887,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G742" t="n">
-        <v>9.98652076721191</v>
+        <v>9.9865198135376</v>
       </c>
       <c r="H742" t="n">
         <v>25230</v>
@@ -21916,7 +21916,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G743" t="n">
-        <v>10.0327548980713</v>
+        <v>10.032753944397</v>
       </c>
       <c r="H743" t="n">
         <v>14440</v>
@@ -21945,7 +21945,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G744" t="n">
-        <v>9.98652076721191</v>
+        <v>9.9865198135376</v>
       </c>
       <c r="H744" t="n">
         <v>5820</v>
@@ -21974,7 +21974,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G745" t="n">
-        <v>10.0327548980713</v>
+        <v>10.032753944397</v>
       </c>
       <c r="H745" t="n">
         <v>19800</v>
@@ -22003,7 +22003,7 @@
         <v>10.5</v>
       </c>
       <c r="G746" t="n">
-        <v>9.7091178894043</v>
+        <v>9.70911598205566</v>
       </c>
       <c r="H746" t="n">
         <v>22620</v>
@@ -22061,7 +22061,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G748" t="n">
-        <v>9.80158424377441</v>
+        <v>9.80158519744873</v>
       </c>
       <c r="H748" t="n">
         <v>18650</v>
@@ -22090,7 +22090,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G749" t="n">
-        <v>9.98652076721191</v>
+        <v>9.9865198135376</v>
       </c>
       <c r="H749" t="n">
         <v>5290</v>
@@ -22119,7 +22119,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G750" t="n">
-        <v>9.80158424377441</v>
+        <v>9.80158519744873</v>
       </c>
       <c r="H750" t="n">
         <v>12500</v>
@@ -22148,7 +22148,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G751" t="n">
-        <v>9.80158424377441</v>
+        <v>9.80158519744873</v>
       </c>
       <c r="H751" t="n">
         <v>12920</v>
@@ -22177,7 +22177,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G752" t="n">
-        <v>9.61664772033691</v>
+        <v>9.61664962768555</v>
       </c>
       <c r="H752" t="n">
         <v>9760</v>
@@ -22206,7 +22206,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G753" t="n">
-        <v>9.80158424377441</v>
+        <v>9.80158519744873</v>
       </c>
       <c r="H753" t="n">
         <v>19270</v>
@@ -22235,7 +22235,7 @@
         <v>10.8000001907349</v>
       </c>
       <c r="G754" t="n">
-        <v>9.98652076721191</v>
+        <v>9.9865198135376</v>
       </c>
       <c r="H754" t="n">
         <v>8900</v>
@@ -22264,7 +22264,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G755" t="n">
-        <v>10.0789890289307</v>
+        <v>10.0789861679077</v>
       </c>
       <c r="H755" t="n">
         <v>14220</v>
@@ -22293,7 +22293,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G756" t="n">
-        <v>10.356390953064</v>
+        <v>10.3563919067383</v>
       </c>
       <c r="H756" t="n">
         <v>20470</v>
@@ -22322,7 +22322,7 @@
         <v>11.1499996185303</v>
       </c>
       <c r="G757" t="n">
-        <v>10.3101568222046</v>
+        <v>10.3101577758789</v>
       </c>
       <c r="H757" t="n">
         <v>22670</v>
@@ -22351,7 +22351,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G758" t="n">
-        <v>10.4488582611084</v>
+        <v>10.4488592147827</v>
       </c>
       <c r="H758" t="n">
         <v>15180</v>
@@ -22380,7 +22380,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G759" t="n">
-        <v>10.4950942993164</v>
+        <v>10.4950923919678</v>
       </c>
       <c r="H759" t="n">
         <v>17310</v>
@@ -22409,7 +22409,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G760" t="n">
-        <v>10.4488582611084</v>
+        <v>10.4488592147827</v>
       </c>
       <c r="H760" t="n">
         <v>19520</v>
@@ -22438,7 +22438,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G761" t="n">
-        <v>10.356390953064</v>
+        <v>10.3563919067383</v>
       </c>
       <c r="H761" t="n">
         <v>13730</v>
@@ -22467,7 +22467,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G762" t="n">
-        <v>10.356390953064</v>
+        <v>10.3563919067383</v>
       </c>
       <c r="H762" t="n">
         <v>6510</v>
@@ -22496,7 +22496,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G763" t="n">
-        <v>10.4488582611084</v>
+        <v>10.4488592147827</v>
       </c>
       <c r="H763" t="n">
         <v>11290</v>
@@ -22525,7 +22525,7 @@
         <v>11</v>
       </c>
       <c r="G764" t="n">
-        <v>10.1714544296265</v>
+        <v>10.1714563369751</v>
       </c>
       <c r="H764" t="n">
         <v>11870</v>
@@ -22554,7 +22554,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G765" t="n">
-        <v>10.0789890289307</v>
+        <v>10.0789861679077</v>
       </c>
       <c r="H765" t="n">
         <v>5710</v>
@@ -22583,7 +22583,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G766" t="n">
-        <v>10.5413265228271</v>
+        <v>10.5413255691528</v>
       </c>
       <c r="H766" t="n">
         <v>11240</v>
@@ -22612,7 +22612,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G767" t="n">
-        <v>10.5413265228271</v>
+        <v>10.5413255691528</v>
       </c>
       <c r="H767" t="n">
         <v>23750</v>
@@ -22641,7 +22641,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G768" t="n">
-        <v>11.0036640167236</v>
+        <v>11.0036649703979</v>
       </c>
       <c r="H768" t="n">
         <v>17250</v>
@@ -22670,7 +22670,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G769" t="n">
-        <v>11.6047058105469</v>
+        <v>11.6047067642212</v>
       </c>
       <c r="H769" t="n">
         <v>84360</v>
@@ -22699,7 +22699,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G770" t="n">
-        <v>11.9745769500732</v>
+        <v>11.9745759963989</v>
       </c>
       <c r="H770" t="n">
         <v>78780</v>
@@ -22728,7 +22728,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G771" t="n">
-        <v>12.7605543136597</v>
+        <v>12.760552406311</v>
       </c>
       <c r="H771" t="n">
         <v>775590</v>
@@ -22757,7 +22757,7 @@
         <v>13</v>
       </c>
       <c r="G772" t="n">
-        <v>12.0208110809326</v>
+        <v>12.0208101272583</v>
       </c>
       <c r="H772" t="n">
         <v>77200</v>
@@ -22786,7 +22786,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G773" t="n">
-        <v>12.2982139587402</v>
+        <v>12.2982149124146</v>
       </c>
       <c r="H773" t="n">
         <v>15670</v>
@@ -22815,7 +22815,7 @@
         <v>13.25</v>
       </c>
       <c r="G774" t="n">
-        <v>12.2519798278809</v>
+        <v>12.2519807815552</v>
       </c>
       <c r="H774" t="n">
         <v>28340</v>
@@ -22844,7 +22844,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G775" t="n">
-        <v>12.1132802963257</v>
+        <v>12.1132783889771</v>
       </c>
       <c r="H775" t="n">
         <v>46310</v>
@@ -22873,7 +22873,7 @@
         <v>13</v>
       </c>
       <c r="G776" t="n">
-        <v>12.0208110809326</v>
+        <v>12.0208101272583</v>
       </c>
       <c r="H776" t="n">
         <v>24820</v>
@@ -22902,7 +22902,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G777" t="n">
-        <v>12.1595125198364</v>
+        <v>12.1595134735107</v>
       </c>
       <c r="H777" t="n">
         <v>41060</v>
@@ -22931,7 +22931,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G778" t="n">
-        <v>11.9745769500732</v>
+        <v>11.9745759963989</v>
       </c>
       <c r="H778" t="n">
         <v>12920</v>
@@ -23018,7 +23018,7 @@
         <v>13</v>
       </c>
       <c r="G781" t="n">
-        <v>12.0208110809326</v>
+        <v>12.0208101272583</v>
       </c>
       <c r="H781" t="n">
         <v>26420</v>
@@ -23134,7 +23134,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G785" t="n">
-        <v>11.9745769500732</v>
+        <v>11.9745759963989</v>
       </c>
       <c r="H785" t="n">
         <v>15410</v>
@@ -23163,7 +23163,7 @@
         <v>12.75</v>
       </c>
       <c r="G786" t="n">
-        <v>11.7896413803101</v>
+        <v>11.7896423339844</v>
       </c>
       <c r="H786" t="n">
         <v>23160</v>
@@ -23192,7 +23192,7 @@
         <v>12.75</v>
       </c>
       <c r="G787" t="n">
-        <v>11.7896413803101</v>
+        <v>11.7896423339844</v>
       </c>
       <c r="H787" t="n">
         <v>44680</v>
@@ -23250,7 +23250,7 @@
         <v>13</v>
       </c>
       <c r="G789" t="n">
-        <v>12.0208110809326</v>
+        <v>12.0208101272583</v>
       </c>
       <c r="H789" t="n">
         <v>50180</v>
@@ -23337,7 +23337,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G792" t="n">
-        <v>11.6509399414062</v>
+        <v>11.6509408950806</v>
       </c>
       <c r="H792" t="n">
         <v>17290</v>
@@ -23366,7 +23366,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G793" t="n">
-        <v>11.5122375488281</v>
+        <v>11.5122385025024</v>
       </c>
       <c r="H793" t="n">
         <v>31350</v>
@@ -23395,7 +23395,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G794" t="n">
-        <v>11.6509399414062</v>
+        <v>11.6509408950806</v>
       </c>
       <c r="H794" t="n">
         <v>27000</v>
@@ -23424,7 +23424,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G795" t="n">
-        <v>11.4660043716431</v>
+        <v>11.4660034179688</v>
       </c>
       <c r="H795" t="n">
         <v>2570</v>
@@ -23453,7 +23453,7 @@
         <v>12.75</v>
       </c>
       <c r="G796" t="n">
-        <v>11.7896413803101</v>
+        <v>11.7896423339844</v>
       </c>
       <c r="H796" t="n">
         <v>28200</v>
@@ -23482,7 +23482,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G797" t="n">
-        <v>11.6971750259399</v>
+        <v>11.6971740722656</v>
       </c>
       <c r="H797" t="n">
         <v>4440</v>
@@ -23511,7 +23511,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G798" t="n">
-        <v>11.419771194458</v>
+        <v>11.4197702407837</v>
       </c>
       <c r="H798" t="n">
         <v>21780</v>
@@ -23540,7 +23540,7 @@
         <v>12.25</v>
       </c>
       <c r="G799" t="n">
-        <v>11.3273029327393</v>
+        <v>11.3273019790649</v>
       </c>
       <c r="H799" t="n">
         <v>3520</v>
@@ -23598,7 +23598,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G801" t="n">
-        <v>11.1423692703247</v>
+        <v>11.1423683166504</v>
       </c>
       <c r="H801" t="n">
         <v>15210</v>
@@ -23656,7 +23656,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G803" t="n">
-        <v>11.1423692703247</v>
+        <v>11.1423683166504</v>
       </c>
       <c r="H803" t="n">
         <v>60080</v>
@@ -23685,7 +23685,7 @@
         <v>12.25</v>
       </c>
       <c r="G804" t="n">
-        <v>11.3273029327393</v>
+        <v>11.3273019790649</v>
       </c>
       <c r="H804" t="n">
         <v>15270</v>
@@ -23714,7 +23714,7 @@
         <v>12.25</v>
       </c>
       <c r="G805" t="n">
-        <v>11.3273029327393</v>
+        <v>11.3273019790649</v>
       </c>
       <c r="H805" t="n">
         <v>23490</v>
@@ -23743,7 +23743,7 @@
         <v>12.25</v>
       </c>
       <c r="G806" t="n">
-        <v>11.3273029327393</v>
+        <v>11.3273019790649</v>
       </c>
       <c r="H806" t="n">
         <v>605530</v>
@@ -23772,7 +23772,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G807" t="n">
-        <v>11.2810688018799</v>
+        <v>11.2810678482056</v>
       </c>
       <c r="H807" t="n">
         <v>7090</v>
@@ -23830,7 +23830,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G809" t="n">
-        <v>11.2810688018799</v>
+        <v>11.2810678482056</v>
       </c>
       <c r="H809" t="n">
         <v>4150</v>
@@ -23859,7 +23859,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G810" t="n">
-        <v>11.419771194458</v>
+        <v>11.4197702407837</v>
       </c>
       <c r="H810" t="n">
         <v>29160</v>
@@ -23888,7 +23888,7 @@
         <v>12.5</v>
       </c>
       <c r="G811" t="n">
-        <v>11.5584716796875</v>
+        <v>11.5584726333618</v>
       </c>
       <c r="H811" t="n">
         <v>22990</v>
@@ -23946,7 +23946,7 @@
         <v>12.5</v>
       </c>
       <c r="G813" t="n">
-        <v>11.5584716796875</v>
+        <v>11.5584726333618</v>
       </c>
       <c r="H813" t="n">
         <v>9780</v>
@@ -23975,7 +23975,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G814" t="n">
-        <v>11.6509399414062</v>
+        <v>11.6509408950806</v>
       </c>
       <c r="H814" t="n">
         <v>13880</v>
@@ -24004,7 +24004,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G815" t="n">
-        <v>11.6509399414062</v>
+        <v>11.6509408950806</v>
       </c>
       <c r="H815" t="n">
         <v>5930</v>
@@ -24033,7 +24033,7 @@
         <v>12.75</v>
       </c>
       <c r="G816" t="n">
-        <v>11.7896413803101</v>
+        <v>11.7896423339844</v>
       </c>
       <c r="H816" t="n">
         <v>2510</v>
@@ -24062,7 +24062,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G817" t="n">
-        <v>11.6509399414062</v>
+        <v>11.6509408950806</v>
       </c>
       <c r="H817" t="n">
         <v>35190</v>
@@ -24091,7 +24091,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G818" t="n">
-        <v>11.6509399414062</v>
+        <v>11.6509408950806</v>
       </c>
       <c r="H818" t="n">
         <v>2510</v>
@@ -24120,7 +24120,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G819" t="n">
-        <v>11.6971750259399</v>
+        <v>11.6971740722656</v>
       </c>
       <c r="H819" t="n">
         <v>3740</v>
@@ -24149,7 +24149,7 @@
         <v>12.3999996185303</v>
       </c>
       <c r="G820" t="n">
-        <v>11.4660043716431</v>
+        <v>11.4660034179688</v>
       </c>
       <c r="H820" t="n">
         <v>20440</v>
@@ -24178,7 +24178,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G821" t="n">
-        <v>11.2810688018799</v>
+        <v>11.2810678482056</v>
       </c>
       <c r="H821" t="n">
         <v>17320</v>
@@ -24207,7 +24207,7 @@
         <v>12.25</v>
       </c>
       <c r="G822" t="n">
-        <v>11.3273029327393</v>
+        <v>11.3273019790649</v>
       </c>
       <c r="H822" t="n">
         <v>16210</v>
@@ -24236,7 +24236,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G823" t="n">
-        <v>11.2810688018799</v>
+        <v>11.2810678482056</v>
       </c>
       <c r="H823" t="n">
         <v>22360</v>
@@ -24265,7 +24265,7 @@
         <v>12.6000003814697</v>
       </c>
       <c r="G824" t="n">
-        <v>11.6509399414062</v>
+        <v>11.6509408950806</v>
       </c>
       <c r="H824" t="n">
         <v>28340</v>
@@ -24294,7 +24294,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G825" t="n">
-        <v>11.9745769500732</v>
+        <v>11.9745759963989</v>
       </c>
       <c r="H825" t="n">
         <v>36370</v>
@@ -24352,7 +24352,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>12.3444490432739</v>
+        <v>12.3444499969482</v>
       </c>
       <c r="H827" t="n">
         <v>26740</v>
@@ -24410,7 +24410,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G829" t="n">
-        <v>13.1304244995117</v>
+        <v>13.130425453186</v>
       </c>
       <c r="H829" t="n">
         <v>64900</v>
@@ -24497,7 +24497,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G832" t="n">
-        <v>14.1938047409058</v>
+        <v>14.1938037872314</v>
       </c>
       <c r="H832" t="n">
         <v>45500</v>
@@ -24526,7 +24526,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>14.1938047409058</v>
+        <v>14.1938037872314</v>
       </c>
       <c r="H833" t="n">
         <v>64260</v>
@@ -24613,7 +24613,7 @@
         <v>16.25</v>
       </c>
       <c r="G836" t="n">
-        <v>15.0260143280029</v>
+        <v>15.0260133743286</v>
       </c>
       <c r="H836" t="n">
         <v>116230</v>
@@ -24642,7 +24642,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G837" t="n">
-        <v>16.3667964935303</v>
+        <v>16.3667984008789</v>
       </c>
       <c r="H837" t="n">
         <v>162970</v>
@@ -24671,7 +24671,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G838" t="n">
-        <v>16.4592628479004</v>
+        <v>16.459264755249</v>
       </c>
       <c r="H838" t="n">
         <v>124100</v>
@@ -24700,7 +24700,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G839" t="n">
-        <v>16.2743282318115</v>
+        <v>16.2743301391602</v>
       </c>
       <c r="H839" t="n">
         <v>58260</v>
@@ -24729,7 +24729,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G840" t="n">
-        <v>16.2280941009521</v>
+        <v>16.2280921936035</v>
       </c>
       <c r="H840" t="n">
         <v>33380</v>
@@ -24758,7 +24758,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G841" t="n">
-        <v>16.2280941009521</v>
+        <v>16.2280921936035</v>
       </c>
       <c r="H841" t="n">
         <v>35580</v>
@@ -24816,7 +24816,7 @@
         <v>17</v>
       </c>
       <c r="G843" t="n">
-        <v>15.7195234298706</v>
+        <v>15.7195224761963</v>
       </c>
       <c r="H843" t="n">
         <v>42810</v>
@@ -24903,7 +24903,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G846" t="n">
-        <v>14.9335451126099</v>
+        <v>14.9335460662842</v>
       </c>
       <c r="H846" t="n">
         <v>19060</v>
@@ -24932,7 +24932,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G847" t="n">
-        <v>14.6561422348022</v>
+        <v>14.6561431884766</v>
       </c>
       <c r="H847" t="n">
         <v>29540</v>
@@ -24961,7 +24961,7 @@
         <v>16.5</v>
       </c>
       <c r="G848" t="n">
-        <v>15.2571849822998</v>
+        <v>15.2571830749512</v>
       </c>
       <c r="H848" t="n">
         <v>57790</v>
@@ -25019,7 +25019,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G850" t="n">
-        <v>15.6270551681519</v>
+        <v>15.6270523071289</v>
       </c>
       <c r="H850" t="n">
         <v>200800</v>
@@ -25106,7 +25106,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G853" t="n">
-        <v>15.811990737915</v>
+        <v>15.8119897842407</v>
       </c>
       <c r="H853" t="n">
         <v>22700</v>
@@ -25135,7 +25135,7 @@
         <v>16.6499996185303</v>
       </c>
       <c r="G854" t="n">
-        <v>15.3958854675293</v>
+        <v>15.395884513855</v>
       </c>
       <c r="H854" t="n">
         <v>40840</v>
@@ -25222,7 +25222,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G857" t="n">
-        <v>14.7486114501953</v>
+        <v>14.748610496521</v>
       </c>
       <c r="H857" t="n">
         <v>33860</v>
@@ -25280,7 +25280,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G859" t="n">
-        <v>13.9164009094238</v>
+        <v>13.9164018630981</v>
       </c>
       <c r="H859" t="n">
         <v>29820</v>
@@ -25309,7 +25309,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G860" t="n">
-        <v>13.5465297698975</v>
+        <v>13.5465278625488</v>
       </c>
       <c r="H860" t="n">
         <v>64290</v>
@@ -25367,7 +25367,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G862" t="n">
-        <v>12.4369144439697</v>
+        <v>12.4369163513184</v>
       </c>
       <c r="H862" t="n">
         <v>44500</v>
@@ -25396,7 +25396,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G863" t="n">
-        <v>13.0379581451416</v>
+        <v>13.0379571914673</v>
       </c>
       <c r="H863" t="n">
         <v>44090</v>
@@ -25425,7 +25425,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G864" t="n">
-        <v>13.1304244995117</v>
+        <v>13.130425453186</v>
       </c>
       <c r="H864" t="n">
         <v>23780</v>
@@ -25483,7 +25483,7 @@
         <v>14.5</v>
       </c>
       <c r="G866" t="n">
-        <v>13.4078273773193</v>
+        <v>13.407826423645</v>
       </c>
       <c r="H866" t="n">
         <v>30230</v>
@@ -25541,7 +25541,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G868" t="n">
-        <v>15.6732873916626</v>
+        <v>15.6732912063599</v>
       </c>
       <c r="H868" t="n">
         <v>55200</v>
@@ -25570,7 +25570,7 @@
         <v>16.5</v>
       </c>
       <c r="G869" t="n">
-        <v>15.2571849822998</v>
+        <v>15.2571830749512</v>
       </c>
       <c r="H869" t="n">
         <v>65520</v>
@@ -25657,7 +25657,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G872" t="n">
-        <v>15.072247505188</v>
+        <v>15.0722465515137</v>
       </c>
       <c r="H872" t="n">
         <v>19800</v>
@@ -25686,7 +25686,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G873" t="n">
-        <v>14.7486114501953</v>
+        <v>14.748610496521</v>
       </c>
       <c r="H873" t="n">
         <v>34450</v>
@@ -25773,7 +25773,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G876" t="n">
-        <v>14.1475706100464</v>
+        <v>14.1475687026978</v>
       </c>
       <c r="H876" t="n">
         <v>139850</v>
@@ -25802,7 +25802,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G877" t="n">
-        <v>14.2862710952759</v>
+        <v>14.2862720489502</v>
       </c>
       <c r="H877" t="n">
         <v>37840</v>
@@ -25831,7 +25831,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G878" t="n">
-        <v>14.3787393569946</v>
+        <v>14.3787403106689</v>
       </c>
       <c r="H878" t="n">
         <v>28380</v>
@@ -25889,7 +25889,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G880" t="n">
-        <v>14.4712057113647</v>
+        <v>14.4712076187134</v>
       </c>
       <c r="H880" t="n">
         <v>18230</v>
@@ -25947,7 +25947,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G882" t="n">
-        <v>14.1938047409058</v>
+        <v>14.1938037872314</v>
       </c>
       <c r="H882" t="n">
         <v>10030</v>
@@ -26005,7 +26005,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G884" t="n">
-        <v>13.9164009094238</v>
+        <v>13.9164018630981</v>
       </c>
       <c r="H884" t="n">
         <v>4530</v>
@@ -26034,7 +26034,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>13.5465297698975</v>
+        <v>13.5465278625488</v>
       </c>
       <c r="H885" t="n">
         <v>30740</v>
@@ -26063,7 +26063,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G886" t="n">
-        <v>13.8239326477051</v>
+        <v>13.8239336013794</v>
       </c>
       <c r="H886" t="n">
         <v>12290</v>
@@ -26150,7 +26150,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G889" t="n">
-        <v>13.2228927612305</v>
+        <v>13.2228918075562</v>
       </c>
       <c r="H889" t="n">
         <v>14330</v>
@@ -26179,7 +26179,7 @@
         <v>14.75</v>
       </c>
       <c r="G890" t="n">
-        <v>13.6389961242676</v>
+        <v>13.6389980316162</v>
       </c>
       <c r="H890" t="n">
         <v>17940</v>
@@ -26266,7 +26266,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G893" t="n">
-        <v>13.6852312088013</v>
+        <v>13.6852321624756</v>
       </c>
       <c r="H893" t="n">
         <v>17190</v>
@@ -26295,7 +26295,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G894" t="n">
-        <v>14.6561422348022</v>
+        <v>14.6561431884766</v>
       </c>
       <c r="H894" t="n">
         <v>45500</v>
@@ -26382,7 +26382,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G897" t="n">
-        <v>14.6561422348022</v>
+        <v>14.6561431884766</v>
       </c>
       <c r="H897" t="n">
         <v>14350</v>
@@ -26440,7 +26440,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G899" t="n">
-        <v>15.6732873916626</v>
+        <v>15.6732912063599</v>
       </c>
       <c r="H899" t="n">
         <v>45260</v>
@@ -26469,7 +26469,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G900" t="n">
-        <v>14.8873128890991</v>
+        <v>14.8873119354248</v>
       </c>
       <c r="H900" t="n">
         <v>36170</v>
@@ -26527,7 +26527,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G902" t="n">
-        <v>15.072247505188</v>
+        <v>15.0722465515137</v>
       </c>
       <c r="H902" t="n">
         <v>35920</v>
@@ -26556,7 +26556,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G903" t="n">
-        <v>14.9335451126099</v>
+        <v>14.9335460662842</v>
       </c>
       <c r="H903" t="n">
         <v>18950</v>
@@ -26614,7 +26614,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G905" t="n">
-        <v>15.072247505188</v>
+        <v>15.0722465515137</v>
       </c>
       <c r="H905" t="n">
         <v>15930</v>
@@ -26643,7 +26643,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G906" t="n">
-        <v>15.5345869064331</v>
+        <v>15.5345859527588</v>
       </c>
       <c r="H906" t="n">
         <v>20450</v>
@@ -26701,7 +26701,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G908" t="n">
-        <v>15.118480682373</v>
+        <v>15.1184825897217</v>
       </c>
       <c r="H908" t="n">
         <v>16560</v>
@@ -26730,7 +26730,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G909" t="n">
-        <v>14.9335451126099</v>
+        <v>14.9335460662842</v>
       </c>
       <c r="H909" t="n">
         <v>19390</v>
@@ -26788,7 +26788,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G911" t="n">
-        <v>14.7486114501953</v>
+        <v>14.748610496521</v>
       </c>
       <c r="H911" t="n">
         <v>10930</v>
@@ -26817,7 +26817,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G912" t="n">
-        <v>14.6561422348022</v>
+        <v>14.6561431884766</v>
       </c>
       <c r="H912" t="n">
         <v>25210</v>
@@ -26846,7 +26846,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G913" t="n">
-        <v>14.2400379180908</v>
+        <v>14.2400369644165</v>
       </c>
       <c r="H913" t="n">
         <v>22050</v>
@@ -26904,7 +26904,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G915" t="n">
-        <v>13.9626350402832</v>
+        <v>13.9626340866089</v>
       </c>
       <c r="H915" t="n">
         <v>10060</v>
@@ -26962,7 +26962,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G917" t="n">
-        <v>14.1475706100464</v>
+        <v>14.1475687026978</v>
       </c>
       <c r="H917" t="n">
         <v>7760</v>
@@ -27049,7 +27049,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G920" t="n">
-        <v>14.1475706100464</v>
+        <v>14.1475687026978</v>
       </c>
       <c r="H920" t="n">
         <v>13660</v>
@@ -27223,7 +27223,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G926" t="n">
-        <v>14.2862710952759</v>
+        <v>14.2862720489502</v>
       </c>
       <c r="H926" t="n">
         <v>9250</v>
@@ -27252,7 +27252,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G927" t="n">
-        <v>14.0551013946533</v>
+        <v>14.055103302002</v>
       </c>
       <c r="H927" t="n">
         <v>36940</v>
@@ -27281,7 +27281,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G928" t="n">
-        <v>14.3787393569946</v>
+        <v>14.3787403106689</v>
       </c>
       <c r="H928" t="n">
         <v>14950</v>
@@ -27368,7 +27368,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G931" t="n">
-        <v>15.072247505188</v>
+        <v>15.0722465515137</v>
       </c>
       <c r="H931" t="n">
         <v>24700</v>
@@ -27397,7 +27397,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G932" t="n">
-        <v>14.8873128890991</v>
+        <v>14.8873119354248</v>
       </c>
       <c r="H932" t="n">
         <v>25180</v>
@@ -27542,7 +27542,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G937" t="n">
-        <v>14.6561422348022</v>
+        <v>14.6561431884766</v>
       </c>
       <c r="H937" t="n">
         <v>9180</v>
@@ -27571,7 +27571,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G938" t="n">
-        <v>14.7486114501953</v>
+        <v>14.748610496521</v>
       </c>
       <c r="H938" t="n">
         <v>12510</v>
@@ -27687,7 +27687,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G942" t="n">
-        <v>14.2862710952759</v>
+        <v>14.2862720489502</v>
       </c>
       <c r="H942" t="n">
         <v>14950</v>
@@ -27745,7 +27745,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G944" t="n">
-        <v>14.6561422348022</v>
+        <v>14.6561431884766</v>
       </c>
       <c r="H944" t="n">
         <v>20470</v>
@@ -27774,7 +27774,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G945" t="n">
-        <v>14.3787393569946</v>
+        <v>14.3787403106689</v>
       </c>
       <c r="H945" t="n">
         <v>11890</v>
@@ -27803,7 +27803,7 @@
         <v>15.8500003814697</v>
       </c>
       <c r="G946" t="n">
-        <v>14.6561422348022</v>
+        <v>14.6561431884766</v>
       </c>
       <c r="H946" t="n">
         <v>8460</v>
@@ -27832,7 +27832,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G947" t="n">
-        <v>14.6099090576172</v>
+        <v>14.6099100112915</v>
       </c>
       <c r="H947" t="n">
         <v>9810</v>
@@ -27919,7 +27919,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G950" t="n">
-        <v>13.6852312088013</v>
+        <v>13.6852321624756</v>
       </c>
       <c r="H950" t="n">
         <v>58020</v>
@@ -27948,7 +27948,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G951" t="n">
-        <v>13.5465297698975</v>
+        <v>13.5465278625488</v>
       </c>
       <c r="H951" t="n">
         <v>40790</v>
@@ -27977,7 +27977,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G952" t="n">
-        <v>13.9164009094238</v>
+        <v>13.9164018630981</v>
       </c>
       <c r="H952" t="n">
         <v>30340</v>
@@ -28093,7 +28093,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G956" t="n">
-        <v>14.0551013946533</v>
+        <v>14.055103302002</v>
       </c>
       <c r="H956" t="n">
         <v>14200</v>
@@ -28122,7 +28122,7 @@
         <v>15.1999998092651</v>
       </c>
       <c r="G957" t="n">
-        <v>14.0551013946533</v>
+        <v>14.055103302002</v>
       </c>
       <c r="H957" t="n">
         <v>21010</v>
@@ -28151,7 +28151,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G958" t="n">
-        <v>14.1938047409058</v>
+        <v>14.1938037872314</v>
       </c>
       <c r="H958" t="n">
         <v>15680</v>
@@ -28180,7 +28180,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G959" t="n">
-        <v>14.1475706100464</v>
+        <v>14.1475687026978</v>
       </c>
       <c r="H959" t="n">
         <v>29350</v>
@@ -28209,7 +28209,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G960" t="n">
-        <v>13.9626350402832</v>
+        <v>13.9626340866089</v>
       </c>
       <c r="H960" t="n">
         <v>16690</v>
@@ -28238,7 +28238,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G961" t="n">
-        <v>13.5465297698975</v>
+        <v>13.5465278625488</v>
       </c>
       <c r="H961" t="n">
         <v>67800</v>
@@ -28296,7 +28296,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G963" t="n">
-        <v>13.2691259384155</v>
+        <v>13.2691278457642</v>
       </c>
       <c r="H963" t="n">
         <v>32410</v>
@@ -28383,7 +28383,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G966" t="n">
-        <v>14.1475706100464</v>
+        <v>14.1475687026978</v>
       </c>
       <c r="H966" t="n">
         <v>24850</v>
@@ -28412,7 +28412,7 @@
         <v>15.6499996185303</v>
       </c>
       <c r="G967" t="n">
-        <v>14.4712057113647</v>
+        <v>14.4712076187134</v>
       </c>
       <c r="H967" t="n">
         <v>30350</v>
@@ -28441,7 +28441,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G968" t="n">
-        <v>14.2862710952759</v>
+        <v>14.2862720489502</v>
       </c>
       <c r="H968" t="n">
         <v>22610</v>
@@ -28470,7 +28470,7 @@
         <v>15.4399995803833</v>
       </c>
       <c r="G969" t="n">
-        <v>14.277024269104</v>
+        <v>14.2770252227783</v>
       </c>
       <c r="H969" t="n">
         <v>9210</v>
@@ -28499,7 +28499,7 @@
         <v>15.5</v>
       </c>
       <c r="G970" t="n">
-        <v>14.3325061798096</v>
+        <v>14.3325052261353</v>
       </c>
       <c r="H970" t="n">
         <v>9190</v>
@@ -28528,7 +28528,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G971" t="n">
-        <v>14.6099090576172</v>
+        <v>14.6099100112915</v>
       </c>
       <c r="H971" t="n">
         <v>14610</v>
@@ -28557,7 +28557,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G972" t="n">
-        <v>14.2585315704346</v>
+        <v>14.2585306167603</v>
       </c>
       <c r="H972" t="n">
         <v>9650</v>
@@ -28847,7 +28847,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G982" t="n">
-        <v>14.7763509750366</v>
+        <v>14.7763500213623</v>
       </c>
       <c r="H982" t="n">
         <v>6350</v>
@@ -28876,7 +28876,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G983" t="n">
-        <v>14.924298286438</v>
+        <v>14.9242992401123</v>
       </c>
       <c r="H983" t="n">
         <v>23440</v>
@@ -28905,7 +28905,7 @@
         <v>16.4400005340576</v>
       </c>
       <c r="G984" t="n">
-        <v>15.2017030715942</v>
+        <v>15.2017040252686</v>
       </c>
       <c r="H984" t="n">
         <v>35620</v>
@@ -28963,7 +28963,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G986" t="n">
-        <v>15.0352611541748</v>
+        <v>15.0352602005005</v>
       </c>
       <c r="H986" t="n">
         <v>11410</v>
@@ -29021,7 +29021,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G988" t="n">
-        <v>15.1092357635498</v>
+        <v>15.1092338562012</v>
       </c>
       <c r="H988" t="n">
         <v>2460</v>
@@ -29050,7 +29050,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G989" t="n">
-        <v>15.072247505188</v>
+        <v>15.0722465515137</v>
       </c>
       <c r="H989" t="n">
         <v>3450</v>
@@ -29282,7 +29282,7 @@
         <v>15.5</v>
       </c>
       <c r="G997" t="n">
-        <v>14.4261245727539</v>
+        <v>14.4261236190796</v>
       </c>
       <c r="H997" t="n">
         <v>34170</v>
@@ -29340,7 +29340,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G999" t="n">
-        <v>15.133469581604</v>
+        <v>15.1334686279297</v>
       </c>
       <c r="H999" t="n">
         <v>34630</v>
@@ -29369,7 +29369,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1000" t="n">
-        <v>15.1706991195679</v>
+        <v>15.1706972122192</v>
       </c>
       <c r="H1000" t="n">
         <v>26060</v>
@@ -29427,7 +29427,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1002" t="n">
-        <v>15.2079277038574</v>
+        <v>15.2079267501831</v>
       </c>
       <c r="H1002" t="n">
         <v>16300</v>
@@ -29485,7 +29485,7 @@
         <v>16.4699993133545</v>
       </c>
       <c r="G1004" t="n">
-        <v>15.3289194107056</v>
+        <v>15.3289213180542</v>
       </c>
       <c r="H1004" t="n">
         <v>13530</v>
@@ -29572,7 +29572,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1007" t="n">
-        <v>16.5667762756348</v>
+        <v>16.5667743682861</v>
       </c>
       <c r="H1007" t="n">
         <v>28202</v>
@@ -29601,7 +29601,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1008" t="n">
-        <v>17.9628486633301</v>
+        <v>17.9628524780273</v>
       </c>
       <c r="H1008" t="n">
         <v>110884</v>
@@ -29630,7 +29630,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1009" t="n">
-        <v>17.9814624786377</v>
+        <v>17.981466293335</v>
       </c>
       <c r="H1009" t="n">
         <v>68553</v>
@@ -29659,7 +29659,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1010" t="n">
-        <v>17.9628486633301</v>
+        <v>17.9628524780273</v>
       </c>
       <c r="H1010" t="n">
         <v>58949</v>
@@ -29688,7 +29688,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G1011" t="n">
-        <v>17.4602642059326</v>
+        <v>17.460262298584</v>
       </c>
       <c r="H1011" t="n">
         <v>31535</v>
@@ -29717,7 +29717,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1012" t="n">
-        <v>17.2741203308105</v>
+        <v>17.2741222381592</v>
       </c>
       <c r="H1012" t="n">
         <v>43758</v>
@@ -29746,7 +29746,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1013" t="n">
-        <v>17.4044208526611</v>
+        <v>17.4044227600098</v>
       </c>
       <c r="H1013" t="n">
         <v>22767</v>
@@ -29775,7 +29775,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1014" t="n">
-        <v>18.0559253692627</v>
+        <v>18.0559234619141</v>
       </c>
       <c r="H1014" t="n">
         <v>17006</v>
@@ -29833,7 +29833,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G1016" t="n">
-        <v>16.5295448303223</v>
+        <v>16.5295467376709</v>
       </c>
       <c r="H1016" t="n">
         <v>112828</v>
@@ -29862,7 +29862,7 @@
         <v>17.4599990844727</v>
       </c>
       <c r="G1017" t="n">
-        <v>16.2503280639648</v>
+        <v>16.2503299713135</v>
       </c>
       <c r="H1017" t="n">
         <v>86742</v>
@@ -29920,7 +29920,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1019" t="n">
-        <v>16.3992443084717</v>
+        <v>16.3992462158203</v>
       </c>
       <c r="H1019" t="n">
         <v>51683</v>
@@ -29949,7 +29949,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1020" t="n">
-        <v>16.492317199707</v>
+        <v>16.4923152923584</v>
       </c>
       <c r="H1020" t="n">
         <v>46375</v>
@@ -29978,7 +29978,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G1021" t="n">
-        <v>16.7715339660645</v>
+        <v>16.7715320587158</v>
       </c>
       <c r="H1021" t="n">
         <v>152606</v>
@@ -30007,7 +30007,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G1022" t="n">
-        <v>17.1624317169189</v>
+        <v>17.1624336242676</v>
       </c>
       <c r="H1022" t="n">
         <v>78439</v>
@@ -30036,7 +30036,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1023" t="n">
-        <v>17.5905647277832</v>
+        <v>17.5905628204346</v>
       </c>
       <c r="H1023" t="n">
         <v>91285</v>
@@ -30065,7 +30065,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1024" t="n">
-        <v>17.4974918365479</v>
+        <v>17.4974899291992</v>
       </c>
       <c r="H1024" t="n">
         <v>98672</v>
@@ -30094,7 +30094,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1025" t="n">
-        <v>17.4974918365479</v>
+        <v>17.4974899291992</v>
       </c>
       <c r="H1025" t="n">
         <v>49784</v>
@@ -30123,7 +30123,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1026" t="n">
-        <v>17.4974918365479</v>
+        <v>17.4974899291992</v>
       </c>
       <c r="H1026" t="n">
         <v>47587</v>
@@ -30152,7 +30152,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1027" t="n">
-        <v>17.9814624786377</v>
+        <v>17.981466293335</v>
       </c>
       <c r="H1027" t="n">
         <v>61515</v>
@@ -30210,7 +30210,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1029" t="n">
-        <v>17.7767086029053</v>
+        <v>17.7767066955566</v>
       </c>
       <c r="H1029" t="n">
         <v>39639</v>
@@ -30239,7 +30239,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1030" t="n">
-        <v>17.7767086029053</v>
+        <v>17.7767066955566</v>
       </c>
       <c r="H1030" t="n">
         <v>28008</v>
@@ -30326,7 +30326,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1033" t="n">
-        <v>17.7767086029053</v>
+        <v>17.7767066955566</v>
       </c>
       <c r="H1033" t="n">
         <v>46832</v>
@@ -30355,7 +30355,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G1034" t="n">
-        <v>17.758092880249</v>
+        <v>17.7580947875977</v>
       </c>
       <c r="H1034" t="n">
         <v>15873</v>
@@ -30413,7 +30413,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1036" t="n">
-        <v>18.297908782959</v>
+        <v>18.2979106903076</v>
       </c>
       <c r="H1036" t="n">
         <v>62131</v>
@@ -30558,7 +30558,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G1041" t="n">
-        <v>18.409595489502</v>
+        <v>18.4095973968506</v>
       </c>
       <c r="H1041" t="n">
         <v>22551</v>
@@ -30587,7 +30587,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1042" t="n">
-        <v>18.297908782959</v>
+        <v>18.2979106903076</v>
       </c>
       <c r="H1042" t="n">
         <v>30724</v>
@@ -30616,7 +30616,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1043" t="n">
-        <v>17.441650390625</v>
+        <v>17.4416484832764</v>
       </c>
       <c r="H1043" t="n">
         <v>53087</v>
@@ -30645,7 +30645,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1044" t="n">
-        <v>17.571949005127</v>
+        <v>17.5719470977783</v>
       </c>
       <c r="H1044" t="n">
         <v>64064</v>
@@ -30703,7 +30703,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G1046" t="n">
-        <v>17.348575592041</v>
+        <v>17.3485774993896</v>
       </c>
       <c r="H1046" t="n">
         <v>50622</v>
@@ -30732,7 +30732,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1047" t="n">
-        <v>17.5905647277832</v>
+        <v>17.5905628204346</v>
       </c>
       <c r="H1047" t="n">
         <v>44371</v>
@@ -30761,7 +30761,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1048" t="n">
-        <v>17.5905647277832</v>
+        <v>17.5905628204346</v>
       </c>
       <c r="H1048" t="n">
         <v>27174</v>
@@ -30819,7 +30819,7 @@
         <v>18.9599990844727</v>
       </c>
       <c r="G1050" t="n">
-        <v>17.6464080810547</v>
+        <v>17.6464061737061</v>
       </c>
       <c r="H1050" t="n">
         <v>8169</v>
@@ -30848,7 +30848,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G1051" t="n">
-        <v>17.9442386627197</v>
+        <v>17.9442367553711</v>
       </c>
       <c r="H1051" t="n">
         <v>14161</v>
@@ -30877,7 +30877,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1052" t="n">
-        <v>17.9814624786377</v>
+        <v>17.981466293335</v>
       </c>
       <c r="H1052" t="n">
         <v>30162</v>
@@ -30906,7 +30906,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1053" t="n">
-        <v>18.2420673370361</v>
+        <v>18.2420654296875</v>
       </c>
       <c r="H1053" t="n">
         <v>21943</v>
@@ -31022,7 +31022,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G1057" t="n">
-        <v>20.1500396728516</v>
+        <v>20.1500358581543</v>
       </c>
       <c r="H1057" t="n">
         <v>60713</v>
@@ -31051,7 +31051,7 @@
         <v>22.1499996185303</v>
       </c>
       <c r="G1058" t="n">
-        <v>20.6153984069824</v>
+        <v>20.6153964996338</v>
       </c>
       <c r="H1058" t="n">
         <v>57877</v>
@@ -31080,7 +31080,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1059" t="n">
-        <v>20.5688591003418</v>
+        <v>20.5688629150391</v>
       </c>
       <c r="H1059" t="n">
         <v>28721</v>
@@ -31138,7 +31138,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1061" t="n">
-        <v>21.4995765686035</v>
+        <v>21.4995784759521</v>
       </c>
       <c r="H1061" t="n">
         <v>46646</v>
@@ -31167,7 +31167,7 @@
         <v>23</v>
       </c>
       <c r="G1062" t="n">
-        <v>21.4065074920654</v>
+        <v>21.4065036773682</v>
       </c>
       <c r="H1062" t="n">
         <v>72604</v>
@@ -31196,7 +31196,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1063" t="n">
-        <v>21.4995765686035</v>
+        <v>21.4995784759521</v>
       </c>
       <c r="H1063" t="n">
         <v>17026</v>
@@ -31254,7 +31254,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1065" t="n">
-        <v>22.0580101013184</v>
+        <v>22.058012008667</v>
       </c>
       <c r="H1065" t="n">
         <v>60526</v>
@@ -31341,7 +31341,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G1068" t="n">
-        <v>22.2255363464355</v>
+        <v>22.2255382537842</v>
       </c>
       <c r="H1068" t="n">
         <v>34388</v>
@@ -31457,7 +31457,7 @@
         <v>23.5</v>
       </c>
       <c r="G1072" t="n">
-        <v>21.8718662261963</v>
+        <v>21.8718643188477</v>
       </c>
       <c r="H1072" t="n">
         <v>34002</v>
@@ -31486,7 +31486,7 @@
         <v>23.7600002288818</v>
       </c>
       <c r="G1073" t="n">
-        <v>22.1138515472412</v>
+        <v>22.1138534545898</v>
       </c>
       <c r="H1073" t="n">
         <v>51606</v>
@@ -31515,7 +31515,7 @@
         <v>23.9799995422363</v>
       </c>
       <c r="G1074" t="n">
-        <v>22.3186092376709</v>
+        <v>22.3186111450195</v>
       </c>
       <c r="H1074" t="n">
         <v>14404</v>
@@ -31544,7 +31544,7 @@
         <v>24.2399997711182</v>
       </c>
       <c r="G1075" t="n">
-        <v>22.5605983734131</v>
+        <v>22.5605945587158</v>
       </c>
       <c r="H1075" t="n">
         <v>74382</v>
@@ -31631,7 +31631,7 @@
         <v>25.5</v>
       </c>
       <c r="G1078" t="n">
-        <v>23.7333030700684</v>
+        <v>23.7333011627197</v>
       </c>
       <c r="H1078" t="n">
         <v>103954</v>
@@ -31660,7 +31660,7 @@
         <v>26.4599990844727</v>
       </c>
       <c r="G1079" t="n">
-        <v>24.6267890930176</v>
+        <v>24.6267871856689</v>
       </c>
       <c r="H1079" t="n">
         <v>48052</v>
@@ -31863,7 +31863,7 @@
         <v>26.2399997711182</v>
       </c>
       <c r="G1086" t="n">
-        <v>24.4220314025879</v>
+        <v>24.4220294952393</v>
       </c>
       <c r="H1086" t="n">
         <v>44972</v>
@@ -31892,7 +31892,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G1087" t="n">
-        <v>24.4034175872803</v>
+        <v>24.4034194946289</v>
       </c>
       <c r="H1087" t="n">
         <v>26717</v>
@@ -31921,7 +31921,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G1088" t="n">
-        <v>24.4034175872803</v>
+        <v>24.4034194946289</v>
       </c>
       <c r="H1088" t="n">
         <v>113776</v>
@@ -31950,7 +31950,7 @@
         <v>26.1599998474121</v>
       </c>
       <c r="G1089" t="n">
-        <v>24.3475761413574</v>
+        <v>24.3475742340088</v>
       </c>
       <c r="H1089" t="n">
         <v>73043</v>
@@ -31979,7 +31979,7 @@
         <v>27.3199996948242</v>
       </c>
       <c r="G1090" t="n">
-        <v>25.4272079467773</v>
+        <v>25.4272060394287</v>
       </c>
       <c r="H1090" t="n">
         <v>79008</v>
@@ -32008,7 +32008,7 @@
         <v>27.2199993133545</v>
       </c>
       <c r="G1091" t="n">
-        <v>25.334135055542</v>
+        <v>25.3341331481934</v>
       </c>
       <c r="H1091" t="n">
         <v>47633</v>
@@ -32182,7 +32182,7 @@
         <v>24.5400009155273</v>
       </c>
       <c r="G1097" t="n">
-        <v>22.8398132324219</v>
+        <v>22.8398113250732</v>
       </c>
       <c r="H1097" t="n">
         <v>65882</v>
@@ -32211,7 +32211,7 @@
         <v>25</v>
       </c>
       <c r="G1098" t="n">
-        <v>23.2679405212402</v>
+        <v>23.2679424285889</v>
       </c>
       <c r="H1098" t="n">
         <v>40418</v>
@@ -32240,7 +32240,7 @@
         <v>24.5799999237061</v>
       </c>
       <c r="G1099" t="n">
-        <v>22.8770408630371</v>
+        <v>22.8770389556885</v>
       </c>
       <c r="H1099" t="n">
         <v>68348</v>
@@ -32327,7 +32327,7 @@
         <v>25.2399997711182</v>
       </c>
       <c r="G1102" t="n">
-        <v>23.4913139343262</v>
+        <v>23.4913158416748</v>
       </c>
       <c r="H1102" t="n">
         <v>39923</v>
@@ -32356,7 +32356,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1103" t="n">
-        <v>23.6402282714844</v>
+        <v>23.640230178833</v>
       </c>
       <c r="H1103" t="n">
         <v>39101</v>
@@ -32443,7 +32443,7 @@
         <v>26.5400009155273</v>
       </c>
       <c r="G1106" t="n">
-        <v>24.7012481689453</v>
+        <v>24.7012462615967</v>
       </c>
       <c r="H1106" t="n">
         <v>56770</v>
@@ -32472,7 +32472,7 @@
         <v>26.5</v>
       </c>
       <c r="G1107" t="n">
-        <v>24.6640186309814</v>
+        <v>24.6640205383301</v>
       </c>
       <c r="H1107" t="n">
         <v>44031</v>
@@ -32559,7 +32559,7 @@
         <v>29</v>
       </c>
       <c r="G1110" t="n">
-        <v>26.9908103942871</v>
+        <v>26.9908142089844</v>
       </c>
       <c r="H1110" t="n">
         <v>160850</v>
@@ -32617,7 +32617,7 @@
         <v>31.4400005340576</v>
       </c>
       <c r="G1112" t="n">
-        <v>29.2617645263672</v>
+        <v>29.2617626190186</v>
       </c>
       <c r="H1112" t="n">
         <v>196995</v>
@@ -32675,7 +32675,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G1114" t="n">
-        <v>29.6898937225342</v>
+        <v>29.6898918151855</v>
       </c>
       <c r="H1114" t="n">
         <v>108201</v>
@@ -32733,7 +32733,7 @@
         <v>30.9799995422363</v>
       </c>
       <c r="G1116" t="n">
-        <v>28.8336315155029</v>
+        <v>28.8336334228516</v>
       </c>
       <c r="H1116" t="n">
         <v>67753</v>
@@ -32762,7 +32762,7 @@
         <v>30.6599998474121</v>
       </c>
       <c r="G1117" t="n">
-        <v>28.5358066558838</v>
+        <v>28.5358047485352</v>
       </c>
       <c r="H1117" t="n">
         <v>38809</v>
@@ -32791,7 +32791,7 @@
         <v>30.5200004577637</v>
       </c>
       <c r="G1118" t="n">
-        <v>28.4055042266846</v>
+        <v>28.4055023193359</v>
       </c>
       <c r="H1118" t="n">
         <v>107931</v>
@@ -32849,7 +32849,7 @@
         <v>31.7199993133545</v>
       </c>
       <c r="G1120" t="n">
-        <v>29.522367477417</v>
+        <v>29.5223617553711</v>
       </c>
       <c r="H1120" t="n">
         <v>40026</v>
@@ -32936,7 +32936,7 @@
         <v>32.439998626709</v>
       </c>
       <c r="G1123" t="n">
-        <v>30.1924781799316</v>
+        <v>30.1924800872803</v>
       </c>
       <c r="H1123" t="n">
         <v>84489</v>
@@ -32965,7 +32965,7 @@
         <v>33.7200012207031</v>
       </c>
       <c r="G1124" t="n">
-        <v>31.3838024139404</v>
+        <v>31.3837985992432</v>
       </c>
       <c r="H1124" t="n">
         <v>99656</v>
@@ -32994,7 +32994,7 @@
         <v>33.5800018310547</v>
       </c>
       <c r="G1125" t="n">
-        <v>31.2534999847412</v>
+        <v>31.2535018920898</v>
       </c>
       <c r="H1125" t="n">
         <v>76159</v>
@@ -33139,7 +33139,7 @@
         <v>33.6599998474121</v>
       </c>
       <c r="G1130" t="n">
-        <v>31.3279590606689</v>
+        <v>31.3279552459717</v>
       </c>
       <c r="H1130" t="n">
         <v>149267</v>
@@ -33255,7 +33255,7 @@
         <v>31.6200008392334</v>
       </c>
       <c r="G1134" t="n">
-        <v>29.429292678833</v>
+        <v>29.4292945861816</v>
       </c>
       <c r="H1134" t="n">
         <v>71038</v>
@@ -33284,7 +33284,7 @@
         <v>31.1000003814697</v>
       </c>
       <c r="G1135" t="n">
-        <v>28.9453201293945</v>
+        <v>28.9453182220459</v>
       </c>
       <c r="H1135" t="n">
         <v>86531</v>
@@ -33342,7 +33342,7 @@
         <v>32.6399993896484</v>
       </c>
       <c r="G1137" t="n">
-        <v>30.3786239624023</v>
+        <v>30.378625869751</v>
       </c>
       <c r="H1137" t="n">
         <v>69137</v>
@@ -33429,7 +33429,7 @@
         <v>32.8199996948242</v>
       </c>
       <c r="G1140" t="n">
-        <v>30.5461540222168</v>
+        <v>30.5461559295654</v>
       </c>
       <c r="H1140" t="n">
         <v>387974</v>
@@ -33458,7 +33458,7 @@
         <v>33.560001373291</v>
       </c>
       <c r="G1141" t="n">
-        <v>31.2348861694336</v>
+        <v>31.2348880767822</v>
       </c>
       <c r="H1141" t="n">
         <v>46011</v>
@@ -33487,7 +33487,7 @@
         <v>33.7200012207031</v>
       </c>
       <c r="G1142" t="n">
-        <v>31.3838024139404</v>
+        <v>31.3837985992432</v>
       </c>
       <c r="H1142" t="n">
         <v>42115</v>
@@ -33545,7 +33545,7 @@
         <v>34.439998626709</v>
       </c>
       <c r="G1144" t="n">
-        <v>32.0539169311523</v>
+        <v>32.0539131164551</v>
       </c>
       <c r="H1144" t="n">
         <v>77872</v>
@@ -33574,7 +33574,7 @@
         <v>36.1199989318848</v>
       </c>
       <c r="G1145" t="n">
-        <v>33.6175193786621</v>
+        <v>33.6175231933594</v>
       </c>
       <c r="H1145" t="n">
         <v>94752</v>
@@ -33603,7 +33603,7 @@
         <v>35.2599983215332</v>
       </c>
       <c r="G1146" t="n">
-        <v>32.8171005249023</v>
+        <v>32.8171043395996</v>
       </c>
       <c r="H1146" t="n">
         <v>46512</v>
@@ -33632,7 +33632,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G1147" t="n">
-        <v>32.7612609863281</v>
+        <v>32.7612648010254</v>
       </c>
       <c r="H1147" t="n">
         <v>39345</v>
@@ -33661,7 +33661,7 @@
         <v>36</v>
       </c>
       <c r="G1148" t="n">
-        <v>33.5058364868164</v>
+        <v>33.5058403015137</v>
       </c>
       <c r="H1148" t="n">
         <v>54194</v>
@@ -33690,7 +33690,7 @@
         <v>36.1399993896484</v>
       </c>
       <c r="G1149" t="n">
-        <v>33.6361389160156</v>
+        <v>33.6361351013184</v>
       </c>
       <c r="H1149" t="n">
         <v>43244</v>
@@ -33748,7 +33748,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G1151" t="n">
-        <v>31.5513286590576</v>
+        <v>31.5513324737549</v>
       </c>
       <c r="H1151" t="n">
         <v>40722</v>
@@ -33777,7 +33777,7 @@
         <v>33.6199989318848</v>
       </c>
       <c r="G1152" t="n">
-        <v>31.2907238006592</v>
+        <v>31.2907314300537</v>
       </c>
       <c r="H1152" t="n">
         <v>34237</v>
@@ -33835,7 +33835,7 @@
         <v>34.1800003051758</v>
       </c>
       <c r="G1154" t="n">
-        <v>31.8119258880615</v>
+        <v>31.8119316101074</v>
       </c>
       <c r="H1154" t="n">
         <v>37962</v>
@@ -33893,7 +33893,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G1156" t="n">
-        <v>33.7850494384766</v>
+        <v>33.7850532531738</v>
       </c>
       <c r="H1156" t="n">
         <v>73415</v>
@@ -33922,7 +33922,7 @@
         <v>35.7799987792969</v>
       </c>
       <c r="G1157" t="n">
-        <v>33.3010749816895</v>
+        <v>33.3010787963867</v>
       </c>
       <c r="H1157" t="n">
         <v>25412</v>
@@ -33951,7 +33951,7 @@
         <v>36.2799987792969</v>
       </c>
       <c r="G1158" t="n">
-        <v>33.7664375305176</v>
+        <v>33.7664337158203</v>
       </c>
       <c r="H1158" t="n">
         <v>24931</v>
@@ -34038,7 +34038,7 @@
         <v>35.8400001525879</v>
       </c>
       <c r="G1161" t="n">
-        <v>33.3569183349609</v>
+        <v>33.3569259643555</v>
       </c>
       <c r="H1161" t="n">
         <v>19551</v>
@@ -34096,7 +34096,7 @@
         <v>37.9799995422363</v>
       </c>
       <c r="G1163" t="n">
-        <v>35.3486518859863</v>
+        <v>35.3486595153809</v>
       </c>
       <c r="H1163" t="n">
         <v>124787</v>
@@ -34125,7 +34125,7 @@
         <v>39.7000007629395</v>
       </c>
       <c r="G1164" t="n">
-        <v>36.9494895935059</v>
+        <v>36.9494934082031</v>
       </c>
       <c r="H1164" t="n">
         <v>111327</v>
@@ -34183,7 +34183,7 @@
         <v>36</v>
       </c>
       <c r="G1166" t="n">
-        <v>33.5058364868164</v>
+        <v>33.5058403015137</v>
       </c>
       <c r="H1166" t="n">
         <v>70795</v>
@@ -34270,7 +34270,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G1169" t="n">
-        <v>32.482048034668</v>
+        <v>32.4820518493652</v>
       </c>
       <c r="H1169" t="n">
         <v>44316</v>
@@ -34328,7 +34328,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G1171" t="n">
-        <v>32.482048034668</v>
+        <v>32.4820518493652</v>
       </c>
       <c r="H1171" t="n">
         <v>55538</v>
@@ -34386,7 +34386,7 @@
         <v>33.439998626709</v>
       </c>
       <c r="G1173" t="n">
-        <v>31.1231956481934</v>
+        <v>31.123197555542</v>
       </c>
       <c r="H1173" t="n">
         <v>36381</v>
@@ -34415,7 +34415,7 @@
         <v>33.3800010681152</v>
       </c>
       <c r="G1174" t="n">
-        <v>31.067361831665</v>
+        <v>31.0673580169678</v>
       </c>
       <c r="H1174" t="n">
         <v>34144</v>
@@ -34473,7 +34473,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1176" t="n">
-        <v>30.8998279571533</v>
+        <v>30.8998260498047</v>
       </c>
       <c r="H1176" t="n">
         <v>68323</v>
@@ -34531,7 +34531,7 @@
         <v>29.9200000762939</v>
       </c>
       <c r="G1178" t="n">
-        <v>27.8470726013184</v>
+        <v>27.847074508667</v>
       </c>
       <c r="H1178" t="n">
         <v>51899</v>
@@ -34589,7 +34589,7 @@
         <v>30.2399997711182</v>
       </c>
       <c r="G1180" t="n">
-        <v>28.1449012756348</v>
+        <v>28.1449031829834</v>
       </c>
       <c r="H1180" t="n">
         <v>28467</v>
@@ -34618,7 +34618,7 @@
         <v>30.0599994659424</v>
       </c>
       <c r="G1181" t="n">
-        <v>27.9773731231689</v>
+        <v>27.9773712158203</v>
       </c>
       <c r="H1181" t="n">
         <v>20538</v>
@@ -34647,7 +34647,7 @@
         <v>31.1800003051758</v>
       </c>
       <c r="G1182" t="n">
-        <v>29.0197772979736</v>
+        <v>29.0197792053223</v>
       </c>
       <c r="H1182" t="n">
         <v>69277</v>
@@ -34676,7 +34676,7 @@
         <v>32.9799995422363</v>
       </c>
       <c r="G1183" t="n">
-        <v>30.6950721740723</v>
+        <v>30.695068359375</v>
       </c>
       <c r="H1183" t="n">
         <v>60943</v>
@@ -34705,7 +34705,7 @@
         <v>32.5400009155273</v>
       </c>
       <c r="G1184" t="n">
-        <v>30.2855567932129</v>
+        <v>30.2855529785156</v>
       </c>
       <c r="H1184" t="n">
         <v>33508</v>
@@ -34763,7 +34763,7 @@
         <v>30.7199993133545</v>
       </c>
       <c r="G1186" t="n">
-        <v>28.5916442871094</v>
+        <v>28.5916481018066</v>
       </c>
       <c r="H1186" t="n">
         <v>28678</v>
@@ -34821,7 +34821,7 @@
         <v>29.0400009155273</v>
       </c>
       <c r="G1188" t="n">
-        <v>27.0280437469482</v>
+        <v>27.0280418395996</v>
       </c>
       <c r="H1188" t="n">
         <v>63152</v>
@@ -34850,7 +34850,7 @@
         <v>30.1399993896484</v>
       </c>
       <c r="G1189" t="n">
-        <v>28.0518321990967</v>
+        <v>28.051830291748</v>
       </c>
       <c r="H1189" t="n">
         <v>25332</v>
@@ -34879,7 +34879,7 @@
         <v>29</v>
       </c>
       <c r="G1190" t="n">
-        <v>26.9908103942871</v>
+        <v>26.9908142089844</v>
       </c>
       <c r="H1190" t="n">
         <v>75084</v>
@@ -34908,7 +34908,7 @@
         <v>28.9599990844727</v>
       </c>
       <c r="G1191" t="n">
-        <v>26.9535846710205</v>
+        <v>26.9535827636719</v>
       </c>
       <c r="H1191" t="n">
         <v>45009</v>
@@ -34937,7 +34937,7 @@
         <v>28.7800006866455</v>
       </c>
       <c r="G1192" t="n">
-        <v>26.7860546112061</v>
+        <v>26.7860565185547</v>
       </c>
       <c r="H1192" t="n">
         <v>85052</v>
@@ -34995,7 +34995,7 @@
         <v>29.9799995422363</v>
       </c>
       <c r="G1194" t="n">
-        <v>27.9029159545898</v>
+        <v>27.9029178619385</v>
       </c>
       <c r="H1194" t="n">
         <v>34088</v>
@@ -35053,7 +35053,7 @@
         <v>29.0400009155273</v>
       </c>
       <c r="G1196" t="n">
-        <v>27.0280437469482</v>
+        <v>27.0280418395996</v>
       </c>
       <c r="H1196" t="n">
         <v>47048</v>
@@ -35082,7 +35082,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G1197" t="n">
-        <v>26.3579235076904</v>
+        <v>26.3579254150391</v>
       </c>
       <c r="H1197" t="n">
         <v>45867</v>
@@ -35111,7 +35111,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1198" t="n">
-        <v>26.897741317749</v>
+        <v>26.8977432250977</v>
       </c>
       <c r="H1198" t="n">
         <v>76545</v>
@@ -35198,7 +35198,7 @@
         <v>28.8799991607666</v>
       </c>
       <c r="G1201" t="n">
-        <v>26.8791255950928</v>
+        <v>26.8791275024414</v>
       </c>
       <c r="H1201" t="n">
         <v>42064</v>
@@ -35227,7 +35227,7 @@
         <v>28.5599994659424</v>
       </c>
       <c r="G1202" t="n">
-        <v>26.5812950134277</v>
+        <v>26.5812969207764</v>
       </c>
       <c r="H1202" t="n">
         <v>30947</v>
@@ -35256,7 +35256,7 @@
         <v>28.8799991607666</v>
       </c>
       <c r="G1203" t="n">
-        <v>26.8791255950928</v>
+        <v>26.8791275024414</v>
       </c>
       <c r="H1203" t="n">
         <v>47313</v>
@@ -35285,7 +35285,7 @@
         <v>28.5</v>
       </c>
       <c r="G1204" t="n">
-        <v>26.5254554748535</v>
+        <v>26.5254535675049</v>
       </c>
       <c r="H1204" t="n">
         <v>30976</v>
@@ -35343,7 +35343,7 @@
         <v>26.0400009155273</v>
       </c>
       <c r="G1206" t="n">
-        <v>24.2358894348145</v>
+        <v>24.2358913421631</v>
       </c>
       <c r="H1206" t="n">
         <v>68431</v>
@@ -35401,7 +35401,7 @@
         <v>26</v>
       </c>
       <c r="G1208" t="n">
-        <v>24.1986618041992</v>
+        <v>24.1986598968506</v>
       </c>
       <c r="H1208" t="n">
         <v>50841</v>
@@ -35459,7 +35459,7 @@
         <v>27.1200008392334</v>
       </c>
       <c r="G1210" t="n">
-        <v>25.2410640716553</v>
+        <v>25.2410659790039</v>
       </c>
       <c r="H1210" t="n">
         <v>35306</v>
@@ -35517,7 +35517,7 @@
         <v>28.4799995422363</v>
       </c>
       <c r="G1212" t="n">
-        <v>26.5068397521973</v>
+        <v>26.5068378448486</v>
       </c>
       <c r="H1212" t="n">
         <v>18028</v>
@@ -35546,7 +35546,7 @@
         <v>28.2399997711182</v>
       </c>
       <c r="G1213" t="n">
-        <v>26.2834663391113</v>
+        <v>26.28346824646</v>
       </c>
       <c r="H1213" t="n">
         <v>25247</v>
@@ -35604,7 +35604,7 @@
         <v>29.8799991607666</v>
       </c>
       <c r="G1215" t="n">
-        <v>27.8098411560059</v>
+        <v>27.8098430633545</v>
       </c>
       <c r="H1215" t="n">
         <v>75505</v>
@@ -35633,7 +35633,7 @@
         <v>29.3199996948242</v>
       </c>
       <c r="G1216" t="n">
-        <v>27.2886409759521</v>
+        <v>27.2886428833008</v>
       </c>
       <c r="H1216" t="n">
         <v>70944</v>
@@ -35662,7 +35662,7 @@
         <v>28.8400001525879</v>
       </c>
       <c r="G1217" t="n">
-        <v>26.8418960571289</v>
+        <v>26.8418998718262</v>
       </c>
       <c r="H1217" t="n">
         <v>52590</v>
@@ -35778,7 +35778,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1221" t="n">
-        <v>28.2938194274902</v>
+        <v>28.2938175201416</v>
       </c>
       <c r="H1221" t="n">
         <v>50940</v>
@@ -35836,7 +35836,7 @@
         <v>30.5</v>
       </c>
       <c r="G1223" t="n">
-        <v>28.386890411377</v>
+        <v>28.3868885040283</v>
       </c>
       <c r="H1223" t="n">
         <v>40353</v>
@@ -35865,7 +35865,7 @@
         <v>30.9200000762939</v>
       </c>
       <c r="G1224" t="n">
-        <v>28.7777900695801</v>
+        <v>28.7777919769287</v>
       </c>
       <c r="H1224" t="n">
         <v>49249</v>
@@ -35894,7 +35894,7 @@
         <v>29.9599990844727</v>
       </c>
       <c r="G1225" t="n">
-        <v>27.8843021392822</v>
+        <v>27.8843002319336</v>
       </c>
       <c r="H1225" t="n">
         <v>55762</v>
@@ -36010,7 +36010,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1229" t="n">
-        <v>25.9670238494873</v>
+        <v>25.9670219421387</v>
       </c>
       <c r="H1229" t="n">
         <v>43867</v>
@@ -36039,7 +36039,7 @@
         <v>27.7399997711182</v>
       </c>
       <c r="G1230" t="n">
-        <v>25.8181076049805</v>
+        <v>25.8181095123291</v>
       </c>
       <c r="H1230" t="n">
         <v>46441</v>
@@ -36184,7 +36184,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1235" t="n">
-        <v>25.8739490509033</v>
+        <v>25.8739528656006</v>
       </c>
       <c r="H1235" t="n">
         <v>15018</v>
@@ -36242,7 +36242,7 @@
         <v>27.2800006866455</v>
       </c>
       <c r="G1237" t="n">
-        <v>25.3899803161621</v>
+        <v>25.3899784088135</v>
       </c>
       <c r="H1237" t="n">
         <v>26942</v>
@@ -36300,7 +36300,7 @@
         <v>26.7600002288818</v>
       </c>
       <c r="G1239" t="n">
-        <v>24.906005859375</v>
+        <v>24.9060039520264</v>
       </c>
       <c r="H1239" t="n">
         <v>30671</v>
@@ -36387,7 +36387,7 @@
         <v>25</v>
       </c>
       <c r="G1242" t="n">
-        <v>23.5317497253418</v>
+        <v>23.5317516326904</v>
       </c>
       <c r="H1242" t="n">
         <v>66717</v>
@@ -36503,7 +36503,7 @@
         <v>25.2600002288818</v>
       </c>
       <c r="G1246" t="n">
-        <v>23.7764797210693</v>
+        <v>23.776481628418</v>
       </c>
       <c r="H1246" t="n">
         <v>33813</v>
@@ -36648,7 +36648,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1251" t="n">
-        <v>20.5196857452393</v>
+        <v>20.5196876525879</v>
       </c>
       <c r="H1251" t="n">
         <v>42268</v>
@@ -36793,7 +36793,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1256" t="n">
-        <v>19.9549236297607</v>
+        <v>19.9549255371094</v>
       </c>
       <c r="H1256" t="n">
         <v>41638</v>
@@ -36909,7 +36909,7 @@
         <v>21.1599998474121</v>
       </c>
       <c r="G1260" t="n">
-        <v>19.9172744750977</v>
+        <v>19.917272567749</v>
       </c>
       <c r="H1260" t="n">
         <v>26125</v>
@@ -36967,7 +36967,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G1262" t="n">
-        <v>19.7854957580566</v>
+        <v>19.7854976654053</v>
       </c>
       <c r="H1262" t="n">
         <v>37052</v>
@@ -37054,7 +37054,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G1265" t="n">
-        <v>21.0279731750488</v>
+        <v>21.0279712677002</v>
       </c>
       <c r="H1265" t="n">
         <v>61995</v>
@@ -37083,7 +37083,7 @@
         <v>22</v>
       </c>
       <c r="G1266" t="n">
-        <v>20.7079391479492</v>
+        <v>20.7079410552979</v>
       </c>
       <c r="H1266" t="n">
         <v>60949</v>
@@ -37112,7 +37112,7 @@
         <v>22.3600006103516</v>
       </c>
       <c r="G1267" t="n">
-        <v>21.0467987060547</v>
+        <v>21.0467967987061</v>
       </c>
       <c r="H1267" t="n">
         <v>47839</v>
@@ -37141,7 +37141,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1268" t="n">
-        <v>20.3314342498779</v>
+        <v>20.3314323425293</v>
       </c>
       <c r="H1268" t="n">
         <v>47908</v>
@@ -37170,7 +37170,7 @@
         <v>21</v>
       </c>
       <c r="G1269" t="n">
-        <v>19.7666721343994</v>
+        <v>19.7666702270508</v>
       </c>
       <c r="H1269" t="n">
         <v>49449</v>
@@ -37286,7 +37286,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G1273" t="n">
-        <v>19.7478446960449</v>
+        <v>19.7478427886963</v>
       </c>
       <c r="H1273" t="n">
         <v>18853</v>
@@ -37431,7 +37431,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1278" t="n">
-        <v>18.0159072875977</v>
+        <v>18.0159091949463</v>
       </c>
       <c r="H1278" t="n">
         <v>51917</v>
@@ -37460,7 +37460,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1279" t="n">
-        <v>18.2041606903076</v>
+        <v>18.2041625976562</v>
       </c>
       <c r="H1279" t="n">
         <v>46603</v>
@@ -37518,7 +37518,7 @@
         <v>18.8199996948242</v>
       </c>
       <c r="G1281" t="n">
-        <v>17.7147006988525</v>
+        <v>17.7146987915039</v>
       </c>
       <c r="H1281" t="n">
         <v>39341</v>
@@ -37547,7 +37547,7 @@
         <v>19.2900009155273</v>
       </c>
       <c r="G1282" t="n">
-        <v>18.157096862793</v>
+        <v>18.1570987701416</v>
       </c>
       <c r="H1282" t="n">
         <v>19434</v>
@@ -37634,7 +37634,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1285" t="n">
-        <v>17.5264472961426</v>
+        <v>17.5264492034912</v>
       </c>
       <c r="H1285" t="n">
         <v>17848</v>
@@ -37663,7 +37663,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G1286" t="n">
-        <v>17.3758411407471</v>
+        <v>17.3758430480957</v>
       </c>
       <c r="H1286" t="n">
         <v>16932</v>
@@ -37750,7 +37750,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G1289" t="n">
-        <v>16.293384552002</v>
+        <v>16.2933826446533</v>
       </c>
       <c r="H1289" t="n">
         <v>18435</v>
@@ -37866,7 +37866,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G1293" t="n">
-        <v>17.3852558135986</v>
+        <v>17.3852577209473</v>
       </c>
       <c r="H1293" t="n">
         <v>41683</v>
@@ -37953,7 +37953,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G1296" t="n">
-        <v>17.8088302612305</v>
+        <v>17.8088283538818</v>
       </c>
       <c r="H1296" t="n">
         <v>35661</v>
@@ -37982,7 +37982,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G1297" t="n">
-        <v>17.3570175170898</v>
+        <v>17.3570194244385</v>
       </c>
       <c r="H1297" t="n">
         <v>30644</v>
@@ -38011,7 +38011,7 @@
         <v>17.8500003814697</v>
       </c>
       <c r="G1298" t="n">
-        <v>16.8016719818115</v>
+        <v>16.8016700744629</v>
       </c>
       <c r="H1298" t="n">
         <v>43853</v>
@@ -38098,7 +38098,7 @@
         <v>18.9500007629395</v>
       </c>
       <c r="G1301" t="n">
-        <v>17.8370666503906</v>
+        <v>17.8370685577393</v>
       </c>
       <c r="H1301" t="n">
         <v>48615</v>
@@ -38127,7 +38127,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G1302" t="n">
-        <v>17.4982109069824</v>
+        <v>17.4982089996338</v>
       </c>
       <c r="H1302" t="n">
         <v>18353</v>
@@ -38185,7 +38185,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G1304" t="n">
-        <v>17.6770496368408</v>
+        <v>17.6770515441895</v>
       </c>
       <c r="H1304" t="n">
         <v>21245</v>
@@ -38214,7 +38214,7 @@
         <v>18.8299999237061</v>
       </c>
       <c r="G1305" t="n">
-        <v>17.7241134643555</v>
+        <v>17.7241153717041</v>
       </c>
       <c r="H1305" t="n">
         <v>19039</v>
@@ -38243,7 +38243,7 @@
         <v>18.75</v>
       </c>
       <c r="G1306" t="n">
-        <v>17.6488132476807</v>
+        <v>17.6488151550293</v>
       </c>
       <c r="H1306" t="n">
         <v>23164</v>
@@ -38272,7 +38272,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1307" t="n">
-        <v>17.2252407073975</v>
+        <v>17.2252388000488</v>
       </c>
       <c r="H1307" t="n">
         <v>25798</v>
@@ -38359,7 +38359,7 @@
         <v>19.7900009155273</v>
       </c>
       <c r="G1310" t="n">
-        <v>18.6277351379395</v>
+        <v>18.6277332305908</v>
       </c>
       <c r="H1310" t="n">
         <v>40761</v>
@@ -38446,7 +38446,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1313" t="n">
-        <v>19.1077823638916</v>
+        <v>19.107780456543</v>
       </c>
       <c r="H1313" t="n">
         <v>30420</v>
@@ -38475,7 +38475,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G1314" t="n">
-        <v>19.0889587402344</v>
+        <v>19.0889568328857</v>
       </c>
       <c r="H1314" t="n">
         <v>37103</v>
@@ -38562,7 +38562,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1317" t="n">
-        <v>18.4488925933838</v>
+        <v>18.4488906860352</v>
       </c>
       <c r="H1317" t="n">
         <v>44913</v>
@@ -38591,7 +38591,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G1318" t="n">
-        <v>18.3830032348633</v>
+        <v>18.3830051422119</v>
       </c>
       <c r="H1318" t="n">
         <v>19017</v>
@@ -38620,7 +38620,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G1319" t="n">
-        <v>18.6089115142822</v>
+        <v>18.608907699585</v>
       </c>
       <c r="H1319" t="n">
         <v>16339</v>
@@ -38649,7 +38649,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G1320" t="n">
-        <v>18.2982902526855</v>
+        <v>18.2982883453369</v>
       </c>
       <c r="H1320" t="n">
         <v>27815</v>
@@ -38707,7 +38707,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1322" t="n">
-        <v>17.5264472961426</v>
+        <v>17.5264492034912</v>
       </c>
       <c r="H1322" t="n">
         <v>22113</v>
@@ -38794,7 +38794,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G1325" t="n">
-        <v>16.7169551849365</v>
+        <v>16.7169570922852</v>
       </c>
       <c r="H1325" t="n">
         <v>26614</v>
@@ -38823,7 +38823,7 @@
         <v>18</v>
       </c>
       <c r="G1326" t="n">
-        <v>16.9428596496582</v>
+        <v>16.9428615570068</v>
       </c>
       <c r="H1326" t="n">
         <v>12410</v>
@@ -38852,7 +38852,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G1327" t="n">
-        <v>16.7263679504395</v>
+        <v>16.7263660430908</v>
       </c>
       <c r="H1327" t="n">
         <v>12643</v>
@@ -38881,7 +38881,7 @@
         <v>18</v>
       </c>
       <c r="G1328" t="n">
-        <v>16.9428596496582</v>
+        <v>16.9428615570068</v>
       </c>
       <c r="H1328" t="n">
         <v>25976</v>
@@ -38910,7 +38910,7 @@
         <v>17.0400009155273</v>
       </c>
       <c r="G1329" t="n">
-        <v>16.0392436981201</v>
+        <v>16.0392417907715</v>
       </c>
       <c r="H1329" t="n">
         <v>24208</v>
@@ -38939,7 +38939,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1330" t="n">
-        <v>16.2839698791504</v>
+        <v>16.283971786499</v>
       </c>
       <c r="H1330" t="n">
         <v>35031</v>
@@ -38968,7 +38968,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G1331" t="n">
-        <v>16.7263679504395</v>
+        <v>16.7263660430908</v>
       </c>
       <c r="H1331" t="n">
         <v>15512</v>
@@ -38997,7 +38997,7 @@
         <v>17.6200008392334</v>
       </c>
       <c r="G1332" t="n">
-        <v>16.5851764678955</v>
+        <v>16.5851783752441</v>
       </c>
       <c r="H1332" t="n">
         <v>31598</v>
@@ -39026,7 +39026,7 @@
         <v>17.1299991607666</v>
       </c>
       <c r="G1333" t="n">
-        <v>16.1239547729492</v>
+        <v>16.1239528656006</v>
       </c>
       <c r="H1333" t="n">
         <v>23067</v>
@@ -39142,7 +39142,7 @@
         <v>18</v>
       </c>
       <c r="G1337" t="n">
-        <v>16.9428596496582</v>
+        <v>16.9428615570068</v>
       </c>
       <c r="H1337" t="n">
         <v>30015</v>
@@ -39200,7 +39200,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G1339" t="n">
-        <v>17.6205730438232</v>
+        <v>17.6205768585205</v>
       </c>
       <c r="H1339" t="n">
         <v>23955</v>
@@ -39258,7 +39258,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1341" t="n">
-        <v>16.6793041229248</v>
+        <v>16.6793022155762</v>
       </c>
       <c r="H1341" t="n">
         <v>62269</v>
@@ -39287,7 +39287,7 @@
         <v>17.5200004577637</v>
       </c>
       <c r="G1342" t="n">
-        <v>16.4910526275635</v>
+        <v>16.4910507202148</v>
       </c>
       <c r="H1342" t="n">
         <v>53260</v>
@@ -39316,7 +39316,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1343" t="n">
-        <v>15.6815595626831</v>
+        <v>15.6815586090088</v>
       </c>
       <c r="H1343" t="n">
         <v>78437</v>
@@ -39461,7 +39461,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G1348" t="n">
-        <v>13.4695749282837</v>
+        <v>13.4695739746094</v>
       </c>
       <c r="H1348" t="n">
         <v>84418</v>
@@ -39490,7 +39490,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1349" t="n">
-        <v>13.4601621627808</v>
+        <v>13.4601612091064</v>
       </c>
       <c r="H1349" t="n">
         <v>42493</v>
@@ -39519,7 +39519,7 @@
         <v>13.8100004196167</v>
       </c>
       <c r="G1350" t="n">
-        <v>12.9989395141602</v>
+        <v>12.9989385604858</v>
       </c>
       <c r="H1350" t="n">
         <v>61445</v>
@@ -39548,7 +39548,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1351" t="n">
-        <v>13.0271778106689</v>
+        <v>13.0271759033203</v>
       </c>
       <c r="H1351" t="n">
         <v>68271</v>
@@ -39577,7 +39577,7 @@
         <v>13.2700004577637</v>
       </c>
       <c r="G1352" t="n">
-        <v>12.4906539916992</v>
+        <v>12.4906530380249</v>
       </c>
       <c r="H1352" t="n">
         <v>64810</v>
@@ -39606,7 +39606,7 @@
         <v>13.9399995803833</v>
       </c>
       <c r="G1353" t="n">
-        <v>13.1213045120239</v>
+        <v>13.1213035583496</v>
       </c>
       <c r="H1353" t="n">
         <v>173635</v>
@@ -39722,7 +39722,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G1357" t="n">
-        <v>13.7801933288574</v>
+        <v>13.7801923751831</v>
       </c>
       <c r="H1357" t="n">
         <v>26201</v>
@@ -39751,7 +39751,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G1358" t="n">
-        <v>13.3377962112427</v>
+        <v>13.3377952575684</v>
       </c>
       <c r="H1358" t="n">
         <v>47171</v>
@@ -39867,7 +39867,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G1362" t="n">
-        <v>13.4413347244263</v>
+        <v>13.4413356781006</v>
       </c>
       <c r="H1362" t="n">
         <v>44179</v>
@@ -39925,7 +39925,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1364" t="n">
-        <v>13.3660345077515</v>
+        <v>13.3660335540771</v>
       </c>
       <c r="H1364" t="n">
         <v>52821</v>
@@ -39954,7 +39954,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1365" t="n">
-        <v>13.3660345077515</v>
+        <v>13.3660335540771</v>
       </c>
       <c r="H1365" t="n">
         <v>62045</v>
@@ -39983,7 +39983,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G1366" t="n">
-        <v>13.300145149231</v>
+        <v>13.3001461029053</v>
       </c>
       <c r="H1366" t="n">
         <v>43095</v>
@@ -40012,7 +40012,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G1367" t="n">
-        <v>13.5166368484497</v>
+        <v>13.516637802124</v>
       </c>
       <c r="H1367" t="n">
         <v>35294</v>
@@ -40070,7 +40070,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G1369" t="n">
-        <v>13.9307956695557</v>
+        <v>13.93079662323</v>
       </c>
       <c r="H1369" t="n">
         <v>56668</v>
@@ -40186,7 +40186,7 @@
         <v>15.5699996948242</v>
       </c>
       <c r="G1373" t="n">
-        <v>14.6555738449097</v>
+        <v>14.6555728912354</v>
       </c>
       <c r="H1373" t="n">
         <v>22186</v>
@@ -40215,7 +40215,7 @@
         <v>15.3900003433228</v>
       </c>
       <c r="G1374" t="n">
-        <v>14.4861450195312</v>
+        <v>14.4861459732056</v>
       </c>
       <c r="H1374" t="n">
         <v>17607</v>
@@ -40302,7 +40302,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1377" t="n">
-        <v>14.2131776809692</v>
+        <v>14.2131767272949</v>
       </c>
       <c r="H1377" t="n">
         <v>26436</v>
@@ -40360,7 +40360,7 @@
         <v>15.710000038147</v>
       </c>
       <c r="G1379" t="n">
-        <v>14.7873516082764</v>
+        <v>14.7873525619507</v>
       </c>
       <c r="H1379" t="n">
         <v>21758</v>
@@ -40389,7 +40389,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1380" t="n">
-        <v>15.3897647857666</v>
+        <v>15.3897657394409</v>
       </c>
       <c r="H1380" t="n">
         <v>40488</v>
@@ -40418,7 +40418,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1381" t="n">
-        <v>15.3427019119263</v>
+        <v>15.3427000045776</v>
       </c>
       <c r="H1381" t="n">
         <v>50235</v>
@@ -40534,7 +40534,7 @@
         <v>18</v>
       </c>
       <c r="G1385" t="n">
-        <v>16.9428596496582</v>
+        <v>16.9428615570068</v>
       </c>
       <c r="H1385" t="n">
         <v>46703</v>
@@ -40563,7 +40563,7 @@
         <v>17.5</v>
       </c>
       <c r="G1386" t="n">
-        <v>16.4722270965576</v>
+        <v>16.4722232818604</v>
       </c>
       <c r="H1386" t="n">
         <v>49142</v>
@@ -40766,7 +40766,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1393" t="n">
-        <v>17.2252407073975</v>
+        <v>17.2252388000488</v>
       </c>
       <c r="H1393" t="n">
         <v>79176</v>
@@ -40824,7 +40824,7 @@
         <v>17.5100002288818</v>
       </c>
       <c r="G1395" t="n">
-        <v>16.4816379547119</v>
+        <v>16.4816398620605</v>
       </c>
       <c r="H1395" t="n">
         <v>45316</v>
@@ -40911,7 +40911,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1398" t="n">
-        <v>17.601749420166</v>
+        <v>17.6017513275146</v>
       </c>
       <c r="H1398" t="n">
         <v>58906</v>
@@ -40998,7 +40998,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1401" t="n">
-        <v>16.8110847473145</v>
+        <v>16.8110828399658</v>
       </c>
       <c r="H1401" t="n">
         <v>29256</v>
@@ -41027,7 +41027,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G1402" t="n">
-        <v>16.9240341186523</v>
+        <v>16.924036026001</v>
       </c>
       <c r="H1402" t="n">
         <v>29605</v>
@@ -41172,7 +41172,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1407" t="n">
-        <v>17.0181617736816</v>
+        <v>17.018159866333</v>
       </c>
       <c r="H1407" t="n">
         <v>21518</v>
@@ -41317,7 +41317,7 @@
         <v>17.5</v>
       </c>
       <c r="G1412" t="n">
-        <v>16.4722270965576</v>
+        <v>16.4722232818604</v>
       </c>
       <c r="H1412" t="n">
         <v>14648</v>
@@ -41375,7 +41375,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1414" t="n">
-        <v>16.2651462554932</v>
+        <v>16.2651481628418</v>
       </c>
       <c r="H1414" t="n">
         <v>10327</v>
@@ -41462,7 +41462,7 @@
         <v>18</v>
       </c>
       <c r="G1417" t="n">
-        <v>16.9428596496582</v>
+        <v>16.9428615570068</v>
       </c>
       <c r="H1417" t="n">
         <v>32250</v>
@@ -41578,7 +41578,7 @@
         <v>18.4599990844727</v>
       </c>
       <c r="G1421" t="n">
-        <v>17.3758411407471</v>
+        <v>17.3758430480957</v>
       </c>
       <c r="H1421" t="n">
         <v>19036</v>
@@ -41636,7 +41636,7 @@
         <v>19.2299995422363</v>
       </c>
       <c r="G1423" t="n">
-        <v>18.1006240844727</v>
+        <v>18.100622177124</v>
       </c>
       <c r="H1423" t="n">
         <v>38797</v>
@@ -41665,7 +41665,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1424" t="n">
-        <v>18.1665096282959</v>
+        <v>18.1665134429932</v>
       </c>
       <c r="H1424" t="n">
         <v>46129</v>
@@ -41694,7 +41694,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1425" t="n">
-        <v>18.2794647216797</v>
+        <v>18.2794628143311</v>
       </c>
       <c r="H1425" t="n">
         <v>37775</v>
@@ -41723,7 +41723,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G1426" t="n">
-        <v>18.3924179077148</v>
+        <v>18.3924160003662</v>
       </c>
       <c r="H1426" t="n">
         <v>22265</v>
@@ -41752,7 +41752,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1427" t="n">
-        <v>18.4488925933838</v>
+        <v>18.4488906860352</v>
       </c>
       <c r="H1427" t="n">
         <v>26648</v>
@@ -41781,7 +41781,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G1428" t="n">
-        <v>18.976001739502</v>
+        <v>18.9760036468506</v>
       </c>
       <c r="H1428" t="n">
         <v>59273</v>
@@ -41810,7 +41810,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1429" t="n">
-        <v>19.1077823638916</v>
+        <v>19.107780456543</v>
       </c>
       <c r="H1429" t="n">
         <v>28889</v>
@@ -41955,7 +41955,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1434" t="n">
-        <v>20.3314342498779</v>
+        <v>20.3314323425293</v>
       </c>
       <c r="H1434" t="n">
         <v>44757</v>
@@ -42042,7 +42042,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1437" t="n">
-        <v>20.1431770324707</v>
+        <v>20.1431789398193</v>
       </c>
       <c r="H1437" t="n">
         <v>55372</v>
@@ -42100,7 +42100,7 @@
         <v>21.1399993896484</v>
       </c>
       <c r="G1439" t="n">
-        <v>19.8984489440918</v>
+        <v>19.8984470367432</v>
       </c>
       <c r="H1439" t="n">
         <v>56662</v>
@@ -42129,7 +42129,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>20.3314342498779</v>
+        <v>20.3314323425293</v>
       </c>
       <c r="H1440" t="n">
         <v>62704</v>
@@ -42158,7 +42158,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G1441" t="n">
-        <v>20.9150199890137</v>
+        <v>20.915018081665</v>
       </c>
       <c r="H1441" t="n">
         <v>103997</v>
@@ -42187,7 +42187,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G1442" t="n">
-        <v>20.7455921173096</v>
+        <v>20.7455940246582</v>
       </c>
       <c r="H1442" t="n">
         <v>66317</v>
@@ -42303,7 +42303,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G1446" t="n">
-        <v>20.6891136169434</v>
+        <v>20.689115524292</v>
       </c>
       <c r="H1446" t="n">
         <v>31994</v>
@@ -42361,7 +42361,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1448" t="n">
-        <v>20.3314342498779</v>
+        <v>20.3314323425293</v>
       </c>
       <c r="H1448" t="n">
         <v>25255</v>
@@ -42477,7 +42477,7 @@
         <v>20.8199996948242</v>
       </c>
       <c r="G1452" t="n">
-        <v>19.5972423553467</v>
+        <v>19.5972385406494</v>
       </c>
       <c r="H1452" t="n">
         <v>17204</v>
@@ -42593,7 +42593,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G1456" t="n">
-        <v>19.2772102355957</v>
+        <v>19.2772083282471</v>
       </c>
       <c r="H1456" t="n">
         <v>17560</v>
@@ -42651,7 +42651,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G1458" t="n">
-        <v>18.9948291778564</v>
+        <v>18.9948272705078</v>
       </c>
       <c r="H1458" t="n">
         <v>42575</v>
@@ -42709,7 +42709,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1460" t="n">
-        <v>19.0136547088623</v>
+        <v>19.0136528015137</v>
       </c>
       <c r="H1460" t="n">
         <v>14073</v>
@@ -42738,7 +42738,7 @@
         <v>20.5</v>
       </c>
       <c r="G1461" t="n">
-        <v>19.2960338592529</v>
+        <v>19.2960357666016</v>
       </c>
       <c r="H1461" t="n">
         <v>36389</v>
@@ -42796,7 +42796,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G1463" t="n">
-        <v>19.7854957580566</v>
+        <v>19.7854976654053</v>
       </c>
       <c r="H1463" t="n">
         <v>22649</v>
@@ -42825,7 +42825,7 @@
         <v>20.5</v>
       </c>
       <c r="G1464" t="n">
-        <v>19.2960338592529</v>
+        <v>19.2960357666016</v>
       </c>
       <c r="H1464" t="n">
         <v>37266</v>
@@ -42854,7 +42854,7 @@
         <v>20.6599998474121</v>
       </c>
       <c r="G1465" t="n">
-        <v>19.4466381072998</v>
+        <v>19.4466400146484</v>
       </c>
       <c r="H1465" t="n">
         <v>19831</v>
@@ -42912,7 +42912,7 @@
         <v>19.5699996948242</v>
       </c>
       <c r="G1467" t="n">
-        <v>18.4206523895264</v>
+        <v>18.420654296875</v>
       </c>
       <c r="H1467" t="n">
         <v>29950</v>
@@ -43057,7 +43057,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1472" t="n">
-        <v>18.2794647216797</v>
+        <v>18.2794628143311</v>
       </c>
       <c r="H1472" t="n">
         <v>34855</v>
@@ -43086,7 +43086,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G1473" t="n">
-        <v>18.8818740844727</v>
+        <v>18.8818759918213</v>
       </c>
       <c r="H1473" t="n">
         <v>40832</v>
@@ -43115,7 +43115,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G1474" t="n">
-        <v>18.976001739502</v>
+        <v>18.9760036468506</v>
       </c>
       <c r="H1474" t="n">
         <v>35643</v>
@@ -43173,7 +43173,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1476" t="n">
-        <v>19.1077823638916</v>
+        <v>19.107780456543</v>
       </c>
       <c r="H1476" t="n">
         <v>12352</v>
@@ -43231,7 +43231,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1478" t="n">
-        <v>18.731273651123</v>
+        <v>18.7312717437744</v>
       </c>
       <c r="H1478" t="n">
         <v>24681</v>
@@ -43289,7 +43289,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1480" t="n">
-        <v>18.4488925933838</v>
+        <v>18.4488906860352</v>
       </c>
       <c r="H1480" t="n">
         <v>13485</v>
@@ -43318,7 +43318,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G1481" t="n">
-        <v>18.6183204650879</v>
+        <v>18.6183223724365</v>
       </c>
       <c r="H1481" t="n">
         <v>12100</v>
@@ -43347,7 +43347,7 @@
         <v>20.0599994659424</v>
       </c>
       <c r="G1482" t="n">
-        <v>18.8818740844727</v>
+        <v>18.8818759918213</v>
       </c>
       <c r="H1482" t="n">
         <v>12155</v>
@@ -43376,7 +43376,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1483" t="n">
-        <v>18.872465133667</v>
+        <v>18.8724632263184</v>
       </c>
       <c r="H1483" t="n">
         <v>21804</v>
@@ -43608,7 +43608,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1491" t="n">
-        <v>19.1077823638916</v>
+        <v>19.107780456543</v>
       </c>
       <c r="H1491" t="n">
         <v>15564</v>
@@ -43637,7 +43637,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1492" t="n">
-        <v>19.1077823638916</v>
+        <v>19.107780456543</v>
       </c>
       <c r="H1492" t="n">
         <v>14452</v>
@@ -43724,7 +43724,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1495" t="n">
-        <v>18.4488925933838</v>
+        <v>18.4488906860352</v>
       </c>
       <c r="H1495" t="n">
         <v>24453</v>
@@ -43811,7 +43811,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1498" t="n">
-        <v>18.731273651123</v>
+        <v>18.7312717437744</v>
       </c>
       <c r="H1498" t="n">
         <v>16836</v>
@@ -43869,7 +43869,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G1500" t="n">
-        <v>18.6183204650879</v>
+        <v>18.6183223724365</v>
       </c>
       <c r="H1500" t="n">
         <v>15157</v>
@@ -43956,7 +43956,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G1503" t="n">
-        <v>18.5241947174072</v>
+        <v>18.5241928100586</v>
       </c>
       <c r="H1503" t="n">
         <v>18576</v>
@@ -43985,7 +43985,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1504" t="n">
-        <v>18.9665908813477</v>
+        <v>18.966588973999</v>
       </c>
       <c r="H1504" t="n">
         <v>43665</v>
@@ -44014,7 +44014,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1505" t="n">
-        <v>19.3965644836426</v>
+        <v>19.3965625762939</v>
       </c>
       <c r="H1505" t="n">
         <v>17202</v>
@@ -44072,7 +44072,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1507" t="n">
-        <v>18.7850456237793</v>
+        <v>18.7850475311279</v>
       </c>
       <c r="H1507" t="n">
         <v>20257</v>
@@ -44101,7 +44101,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1508" t="n">
-        <v>18.4601802825928</v>
+        <v>18.4601783752441</v>
       </c>
       <c r="H1508" t="n">
         <v>27309</v>
@@ -44159,7 +44159,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1510" t="n">
-        <v>18.2881870269775</v>
+        <v>18.2881889343262</v>
       </c>
       <c r="H1510" t="n">
         <v>12281</v>
@@ -44188,7 +44188,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1511" t="n">
-        <v>18.0015411376953</v>
+        <v>18.0015392303467</v>
       </c>
       <c r="H1511" t="n">
         <v>87259</v>
@@ -44304,7 +44304,7 @@
         <v>19.5</v>
       </c>
       <c r="G1515" t="n">
-        <v>18.6321678161621</v>
+        <v>18.6321659088135</v>
       </c>
       <c r="H1515" t="n">
         <v>9138</v>
@@ -44333,7 +44333,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G1516" t="n">
-        <v>18.6130561828613</v>
+        <v>18.61305809021</v>
       </c>
       <c r="H1516" t="n">
         <v>24365</v>
@@ -44362,7 +44362,7 @@
         <v>18.6599998474121</v>
       </c>
       <c r="G1517" t="n">
-        <v>17.8295497894287</v>
+        <v>17.8295516967773</v>
       </c>
       <c r="H1517" t="n">
         <v>19742</v>
@@ -44391,7 +44391,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1518" t="n">
-        <v>18.2881870269775</v>
+        <v>18.2881889343262</v>
       </c>
       <c r="H1518" t="n">
         <v>22405</v>
@@ -44449,7 +44449,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G1520" t="n">
-        <v>18.670389175415</v>
+        <v>18.6703872680664</v>
       </c>
       <c r="H1520" t="n">
         <v>12532</v>
@@ -44478,7 +44478,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1521" t="n">
-        <v>18.5366172790527</v>
+        <v>18.5366191864014</v>
       </c>
       <c r="H1521" t="n">
         <v>11882</v>
@@ -44507,7 +44507,7 @@
         <v>19.7399997711182</v>
       </c>
       <c r="G1522" t="n">
-        <v>18.8614845275879</v>
+        <v>18.8614864349365</v>
       </c>
       <c r="H1522" t="n">
         <v>18217</v>
@@ -44565,7 +44565,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1524" t="n">
-        <v>19.3010158538818</v>
+        <v>19.3010139465332</v>
       </c>
       <c r="H1524" t="n">
         <v>15485</v>
@@ -44710,7 +44710,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1529" t="n">
-        <v>19.492115020752</v>
+        <v>19.4921131134033</v>
       </c>
       <c r="H1529" t="n">
         <v>14980</v>
@@ -44739,7 +44739,7 @@
         <v>21</v>
       </c>
       <c r="G1530" t="n">
-        <v>20.0654106140137</v>
+        <v>20.0654125213623</v>
       </c>
       <c r="H1530" t="n">
         <v>27043</v>
@@ -44768,7 +44768,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G1531" t="n">
-        <v>20.1131858825684</v>
+        <v>20.1131839752197</v>
       </c>
       <c r="H1531" t="n">
         <v>82889</v>
@@ -44971,7 +44971,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1538" t="n">
-        <v>20.2087345123291</v>
+        <v>20.2087364196777</v>
       </c>
       <c r="H1538" t="n">
         <v>18789</v>
@@ -45058,7 +45058,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1541" t="n">
-        <v>19.3965644836426</v>
+        <v>19.3965625762939</v>
       </c>
       <c r="H1541" t="n">
         <v>27277</v>
@@ -45087,7 +45087,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1542" t="n">
-        <v>19.3965644836426</v>
+        <v>19.3965625762939</v>
       </c>
       <c r="H1542" t="n">
         <v>23559</v>
@@ -45232,7 +45232,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1547" t="n">
-        <v>19.0143642425537</v>
+        <v>19.0143661499023</v>
       </c>
       <c r="H1547" t="n">
         <v>21451</v>
@@ -45261,7 +45261,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1548" t="n">
-        <v>18.8423767089844</v>
+        <v>18.8423748016357</v>
       </c>
       <c r="H1548" t="n">
         <v>47286</v>
@@ -45290,7 +45290,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1549" t="n">
-        <v>19.0143642425537</v>
+        <v>19.0143661499023</v>
       </c>
       <c r="H1549" t="n">
         <v>20675</v>
@@ -45406,7 +45406,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1553" t="n">
-        <v>18.976146697998</v>
+        <v>18.9761486053467</v>
       </c>
       <c r="H1553" t="n">
         <v>18125</v>
@@ -45464,7 +45464,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1555" t="n">
-        <v>19.0143642425537</v>
+        <v>19.0143661499023</v>
       </c>
       <c r="H1555" t="n">
         <v>23405</v>
@@ -45493,7 +45493,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1556" t="n">
-        <v>19.0143642425537</v>
+        <v>19.0143661499023</v>
       </c>
       <c r="H1556" t="n">
         <v>24871</v>
@@ -45522,7 +45522,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1557" t="n">
-        <v>19.1576881408691</v>
+        <v>19.1576900482178</v>
       </c>
       <c r="H1557" t="n">
         <v>21254</v>
@@ -45551,7 +45551,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1558" t="n">
-        <v>19.0143642425537</v>
+        <v>19.0143661499023</v>
       </c>
       <c r="H1558" t="n">
         <v>34825</v>
@@ -45609,7 +45609,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1560" t="n">
-        <v>17.963321685791</v>
+        <v>17.9633197784424</v>
       </c>
       <c r="H1560" t="n">
         <v>55586</v>
@@ -45783,7 +45783,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1566" t="n">
-        <v>18.4792881011963</v>
+        <v>18.4792861938477</v>
       </c>
       <c r="H1566" t="n">
         <v>7386</v>
@@ -45841,7 +45841,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1568" t="n">
-        <v>16.6638469696045</v>
+        <v>16.6638450622559</v>
       </c>
       <c r="H1568" t="n">
         <v>209719</v>
@@ -45870,7 +45870,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1569" t="n">
-        <v>15.803900718689</v>
+        <v>15.8038997650146</v>
       </c>
       <c r="H1569" t="n">
         <v>201281</v>
@@ -46102,7 +46102,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G1577" t="n">
-        <v>16.3580875396729</v>
+        <v>16.3580894470215</v>
       </c>
       <c r="H1577" t="n">
         <v>25812</v>
@@ -46131,7 +46131,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1578" t="n">
-        <v>16.2052059173584</v>
+        <v>16.205207824707</v>
       </c>
       <c r="H1578" t="n">
         <v>38209</v>
@@ -46160,7 +46160,7 @@
         <v>16.9599990844727</v>
       </c>
       <c r="G1579" t="n">
-        <v>16.2052059173584</v>
+        <v>16.205207824707</v>
       </c>
       <c r="H1579" t="n">
         <v>17712</v>
@@ -46189,7 +46189,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1580" t="n">
-        <v>16.4918556213379</v>
+        <v>16.4918575286865</v>
       </c>
       <c r="H1580" t="n">
         <v>20488</v>
@@ -46218,7 +46218,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1581" t="n">
-        <v>16.5874080657959</v>
+        <v>16.5874061584473</v>
       </c>
       <c r="H1581" t="n">
         <v>31323</v>
@@ -46247,7 +46247,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1582" t="n">
-        <v>16.4154167175293</v>
+        <v>16.4154186248779</v>
       </c>
       <c r="H1582" t="n">
         <v>39335</v>
@@ -46276,7 +46276,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G1583" t="n">
-        <v>16.3580875396729</v>
+        <v>16.3580894470215</v>
       </c>
       <c r="H1583" t="n">
         <v>39794</v>
@@ -46479,7 +46479,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1590" t="n">
-        <v>16.5874080657959</v>
+        <v>16.5874061584473</v>
       </c>
       <c r="H1590" t="n">
         <v>41539</v>
@@ -46508,7 +46508,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1591" t="n">
-        <v>16.4154167175293</v>
+        <v>16.4154186248779</v>
       </c>
       <c r="H1591" t="n">
         <v>34761</v>
@@ -46537,7 +46537,7 @@
         <v>17.0599994659424</v>
       </c>
       <c r="G1592" t="n">
-        <v>16.3007564544678</v>
+        <v>16.3007583618164</v>
       </c>
       <c r="H1592" t="n">
         <v>37444</v>
@@ -46769,7 +46769,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="G1600" t="n">
-        <v>15.23060131073</v>
+        <v>15.2306022644043</v>
       </c>
       <c r="H1600" t="n">
         <v>26682</v>
@@ -46943,7 +46943,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G1606" t="n">
-        <v>14.179557800293</v>
+        <v>14.1795568466187</v>
       </c>
       <c r="H1606" t="n">
         <v>63949</v>
@@ -47001,7 +47001,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1608" t="n">
-        <v>14.4662055969238</v>
+        <v>14.4662065505981</v>
       </c>
       <c r="H1608" t="n">
         <v>25595</v>
@@ -47059,7 +47059,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G1610" t="n">
-        <v>13.7209177017212</v>
+        <v>13.7209196090698</v>
       </c>
       <c r="H1610" t="n">
         <v>60330</v>
@@ -47175,7 +47175,7 @@
         <v>13.6000003814697</v>
       </c>
       <c r="G1614" t="n">
-        <v>12.9947423934937</v>
+        <v>12.994743347168</v>
       </c>
       <c r="H1614" t="n">
         <v>30697</v>
@@ -47291,7 +47291,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1618" t="n">
-        <v>13.2813901901245</v>
+        <v>13.2813911437988</v>
       </c>
       <c r="H1618" t="n">
         <v>35789</v>
@@ -47320,7 +47320,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G1619" t="n">
-        <v>13.7973585128784</v>
+        <v>13.7973575592041</v>
       </c>
       <c r="H1619" t="n">
         <v>98951</v>
@@ -47349,7 +47349,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G1620" t="n">
-        <v>13.9311285018921</v>
+        <v>13.9311275482178</v>
       </c>
       <c r="H1620" t="n">
         <v>63613</v>
@@ -47494,7 +47494,7 @@
         <v>14.5799999237061</v>
       </c>
       <c r="G1625" t="n">
-        <v>13.9311285018921</v>
+        <v>13.9311275482178</v>
       </c>
       <c r="H1625" t="n">
         <v>21084</v>
@@ -47523,7 +47523,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1626" t="n">
-        <v>13.8737993240356</v>
+        <v>13.8737983703613</v>
       </c>
       <c r="H1626" t="n">
         <v>33686</v>
@@ -47552,7 +47552,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G1627" t="n">
-        <v>13.835578918457</v>
+        <v>13.8355779647827</v>
       </c>
       <c r="H1627" t="n">
         <v>13878</v>
@@ -47581,7 +47581,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1628" t="n">
-        <v>13.8737993240356</v>
+        <v>13.8737983703613</v>
       </c>
       <c r="H1628" t="n">
         <v>22206</v>
@@ -47610,7 +47610,7 @@
         <v>14.4799995422363</v>
       </c>
       <c r="G1629" t="n">
-        <v>13.835578918457</v>
+        <v>13.8355779647827</v>
       </c>
       <c r="H1629" t="n">
         <v>17942</v>
@@ -47668,7 +47668,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G1631" t="n">
-        <v>14.5999755859375</v>
+        <v>14.5999746322632</v>
       </c>
       <c r="H1631" t="n">
         <v>13170</v>
@@ -47813,7 +47813,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G1636" t="n">
-        <v>15.6510210037231</v>
+        <v>15.6510200500488</v>
       </c>
       <c r="H1636" t="n">
         <v>64482</v>
@@ -47958,7 +47958,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G1641" t="n">
-        <v>17.1224842071533</v>
+        <v>17.122486114502</v>
       </c>
       <c r="H1641" t="n">
         <v>52653</v>
@@ -48016,7 +48016,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1643" t="n">
-        <v>17.0078239440918</v>
+        <v>17.0078258514404</v>
       </c>
       <c r="H1643" t="n">
         <v>20323</v>
@@ -48045,7 +48045,7 @@
         <v>17.8400001525879</v>
       </c>
       <c r="G1644" t="n">
-        <v>17.0460433959961</v>
+        <v>17.0460453033447</v>
       </c>
       <c r="H1644" t="n">
         <v>20721</v>
@@ -48132,7 +48132,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1647" t="n">
-        <v>16.4154167175293</v>
+        <v>16.4154186248779</v>
       </c>
       <c r="H1647" t="n">
         <v>16018</v>
@@ -48161,7 +48161,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1648" t="n">
-        <v>16.7976150512695</v>
+        <v>16.7976169586182</v>
       </c>
       <c r="H1648" t="n">
         <v>33889</v>
@@ -48219,7 +48219,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1650" t="n">
-        <v>16.6638469696045</v>
+        <v>16.6638450622559</v>
       </c>
       <c r="H1650" t="n">
         <v>27418</v>
@@ -48248,7 +48248,7 @@
         <v>18</v>
       </c>
       <c r="G1651" t="n">
-        <v>17.1989231109619</v>
+        <v>17.1989250183105</v>
       </c>
       <c r="H1651" t="n">
         <v>27198</v>
@@ -48277,7 +48277,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1652" t="n">
-        <v>17.2371444702148</v>
+        <v>17.2371463775635</v>
       </c>
       <c r="H1652" t="n">
         <v>37099</v>
@@ -48306,7 +48306,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G1653" t="n">
-        <v>17.0269355773926</v>
+        <v>17.0269336700439</v>
       </c>
       <c r="H1653" t="n">
         <v>11640</v>
@@ -48364,7 +48364,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1655" t="n">
-        <v>16.7785053253174</v>
+        <v>16.7785034179688</v>
       </c>
       <c r="H1655" t="n">
         <v>11530</v>
@@ -48422,7 +48422,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1657" t="n">
-        <v>17.1033744812012</v>
+        <v>17.1033725738525</v>
       </c>
       <c r="H1657" t="n">
         <v>10080</v>
@@ -48451,7 +48451,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1658" t="n">
-        <v>17.256254196167</v>
+        <v>17.2562522888184</v>
       </c>
       <c r="H1658" t="n">
         <v>16208</v>
@@ -48480,7 +48480,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G1659" t="n">
-        <v>17.2180347442627</v>
+        <v>17.2180328369141</v>
       </c>
       <c r="H1659" t="n">
         <v>12222</v>
@@ -48509,7 +48509,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1660" t="n">
-        <v>17.2753639221191</v>
+        <v>17.2753620147705</v>
       </c>
       <c r="H1660" t="n">
         <v>22611</v>
@@ -48538,7 +48538,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1661" t="n">
-        <v>17.1033744812012</v>
+        <v>17.1033725738525</v>
       </c>
       <c r="H1661" t="n">
         <v>5705</v>
@@ -48567,7 +48567,7 @@
         <v>19.1800003051758</v>
       </c>
       <c r="G1662" t="n">
-        <v>18.3264083862305</v>
+        <v>18.3264102935791</v>
       </c>
       <c r="H1662" t="n">
         <v>125918</v>
@@ -48712,7 +48712,7 @@
         <v>19.5</v>
       </c>
       <c r="G1667" t="n">
-        <v>18.6321678161621</v>
+        <v>18.6321659088135</v>
       </c>
       <c r="H1667" t="n">
         <v>12973</v>
@@ -48799,7 +48799,7 @@
         <v>19.6800003051758</v>
       </c>
       <c r="G1670" t="n">
-        <v>18.8041572570801</v>
+        <v>18.8041553497314</v>
       </c>
       <c r="H1670" t="n">
         <v>15382</v>
@@ -48828,7 +48828,7 @@
         <v>19.5</v>
       </c>
       <c r="G1671" t="n">
-        <v>18.6321678161621</v>
+        <v>18.6321659088135</v>
       </c>
       <c r="H1671" t="n">
         <v>17932</v>
@@ -48944,7 +48944,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1675" t="n">
-        <v>17.7722225189209</v>
+        <v>17.7722206115723</v>
       </c>
       <c r="H1675" t="n">
         <v>16152</v>
@@ -49002,7 +49002,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G1677" t="n">
-        <v>18.0970916748047</v>
+        <v>18.0970897674561</v>
       </c>
       <c r="H1677" t="n">
         <v>21233</v>
@@ -49031,7 +49031,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G1678" t="n">
-        <v>17.8104419708252</v>
+        <v>17.8104400634766</v>
       </c>
       <c r="H1678" t="n">
         <v>10106</v>
@@ -49060,7 +49060,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1679" t="n">
-        <v>17.4855709075928</v>
+        <v>17.4855728149414</v>
       </c>
       <c r="H1679" t="n">
         <v>31137</v>
@@ -49089,7 +49089,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1680" t="n">
-        <v>18.039758682251</v>
+        <v>18.0397567749023</v>
       </c>
       <c r="H1680" t="n">
         <v>44497</v>
@@ -49205,7 +49205,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G1684" t="n">
-        <v>17.0842609405518</v>
+        <v>17.084264755249</v>
       </c>
       <c r="H1684" t="n">
         <v>18670</v>
@@ -49263,7 +49263,7 @@
         <v>17.8199996948242</v>
       </c>
       <c r="G1686" t="n">
-        <v>17.0269355773926</v>
+        <v>17.0269336700439</v>
       </c>
       <c r="H1686" t="n">
         <v>35608</v>
@@ -49379,7 +49379,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1690" t="n">
-        <v>18.0015411376953</v>
+        <v>18.0015392303467</v>
       </c>
       <c r="H1690" t="n">
         <v>16217</v>
@@ -49408,7 +49408,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G1691" t="n">
-        <v>18.0206489562988</v>
+        <v>18.0206508636475</v>
       </c>
       <c r="H1691" t="n">
         <v>8110</v>
@@ -49437,7 +49437,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G1692" t="n">
-        <v>18.0206489562988</v>
+        <v>18.0206508636475</v>
       </c>
       <c r="H1692" t="n">
         <v>16310</v>
@@ -49553,7 +49553,7 @@
         <v>18.2999992370605</v>
       </c>
       <c r="G1696" t="n">
-        <v>17.4855709075928</v>
+        <v>17.4855728149414</v>
       </c>
       <c r="H1696" t="n">
         <v>22385</v>
@@ -49669,7 +49669,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1700" t="n">
-        <v>17.3900241851807</v>
+        <v>17.390022277832</v>
       </c>
       <c r="H1700" t="n">
         <v>12018</v>
@@ -49698,7 +49698,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1701" t="n">
-        <v>17.7531127929688</v>
+        <v>17.7531108856201</v>
       </c>
       <c r="H1701" t="n">
         <v>17526</v>
@@ -49785,7 +49785,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G1704" t="n">
-        <v>17.8104419708252</v>
+        <v>17.8104400634766</v>
       </c>
       <c r="H1704" t="n">
         <v>37352</v>
@@ -49814,7 +49814,7 @@
         <v>18.8600006103516</v>
       </c>
       <c r="G1705" t="n">
-        <v>18.0206489562988</v>
+        <v>18.0206508636475</v>
       </c>
       <c r="H1705" t="n">
         <v>12432</v>
@@ -49843,7 +49843,7 @@
         <v>19.5</v>
       </c>
       <c r="G1706" t="n">
-        <v>18.6321678161621</v>
+        <v>18.6321659088135</v>
       </c>
       <c r="H1706" t="n">
         <v>43334</v>
@@ -49872,7 +49872,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1707" t="n">
-        <v>17.963321685791</v>
+        <v>17.9633197784424</v>
       </c>
       <c r="H1707" t="n">
         <v>32129</v>
@@ -49901,7 +49901,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1708" t="n">
-        <v>18.039758682251</v>
+        <v>18.0397567749023</v>
       </c>
       <c r="H1708" t="n">
         <v>14891</v>
@@ -49959,7 +49959,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G1710" t="n">
-        <v>18.3646278381348</v>
+        <v>18.3646259307861</v>
       </c>
       <c r="H1710" t="n">
         <v>26025</v>
@@ -50017,7 +50017,7 @@
         <v>19.2199993133545</v>
       </c>
       <c r="G1712" t="n">
-        <v>18.3646278381348</v>
+        <v>18.3646259307861</v>
       </c>
       <c r="H1712" t="n">
         <v>26201</v>
@@ -50046,7 +50046,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1713" t="n">
-        <v>17.7531127929688</v>
+        <v>17.7531108856201</v>
       </c>
       <c r="H1713" t="n">
         <v>19082</v>
@@ -50104,7 +50104,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1715" t="n">
-        <v>17.7913303375244</v>
+        <v>17.791332244873</v>
       </c>
       <c r="H1715" t="n">
         <v>31418</v>
@@ -50133,7 +50133,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1716" t="n">
-        <v>17.7531127929688</v>
+        <v>17.7531108856201</v>
       </c>
       <c r="H1716" t="n">
         <v>11753</v>
@@ -50162,7 +50162,7 @@
         <v>18.1000003814697</v>
       </c>
       <c r="G1717" t="n">
-        <v>17.2944717407227</v>
+        <v>17.2944736480713</v>
       </c>
       <c r="H1717" t="n">
         <v>18125</v>
@@ -50191,7 +50191,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1718" t="n">
-        <v>17.7531127929688</v>
+        <v>17.7531108856201</v>
       </c>
       <c r="H1718" t="n">
         <v>19731</v>
@@ -50249,7 +50249,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1720" t="n">
-        <v>17.7913303375244</v>
+        <v>17.791332244873</v>
       </c>
       <c r="H1720" t="n">
         <v>9492</v>
@@ -50365,7 +50365,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1724" t="n">
-        <v>17.1033744812012</v>
+        <v>17.1033725738525</v>
       </c>
       <c r="H1724" t="n">
         <v>64199</v>
@@ -50394,7 +50394,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1725" t="n">
-        <v>16.5874080657959</v>
+        <v>16.5874061584473</v>
       </c>
       <c r="H1725" t="n">
         <v>40831</v>
@@ -50423,7 +50423,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1726" t="n">
-        <v>17.0078239440918</v>
+        <v>17.0078258514404</v>
       </c>
       <c r="H1726" t="n">
         <v>43506</v>
@@ -50452,7 +50452,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1727" t="n">
-        <v>16.7976150512695</v>
+        <v>16.7976169586182</v>
       </c>
       <c r="H1727" t="n">
         <v>17893</v>
@@ -50510,7 +50510,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1729" t="n">
-        <v>16.8167266845703</v>
+        <v>16.8167247772217</v>
       </c>
       <c r="H1729" t="n">
         <v>41467</v>
@@ -50568,7 +50568,7 @@
         <v>17.7399997711182</v>
       </c>
       <c r="G1731" t="n">
-        <v>16.9504947662354</v>
+        <v>16.9504928588867</v>
       </c>
       <c r="H1731" t="n">
         <v>39679</v>
@@ -50597,7 +50597,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1732" t="n">
-        <v>17.1033744812012</v>
+        <v>17.1033725738525</v>
       </c>
       <c r="H1732" t="n">
         <v>39764</v>
@@ -50626,7 +50626,7 @@
         <v>18</v>
       </c>
       <c r="G1733" t="n">
-        <v>17.1989231109619</v>
+        <v>17.1989250183105</v>
       </c>
       <c r="H1733" t="n">
         <v>31811</v>
@@ -50655,7 +50655,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1734" t="n">
-        <v>17.256254196167</v>
+        <v>17.2562522888184</v>
       </c>
       <c r="H1734" t="n">
         <v>17936</v>
@@ -50800,7 +50800,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1739" t="n">
-        <v>16.4918556213379</v>
+        <v>16.4918575286865</v>
       </c>
       <c r="H1739" t="n">
         <v>15766</v>
@@ -50829,7 +50829,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1740" t="n">
-        <v>15.899450302124</v>
+        <v>15.8994493484497</v>
       </c>
       <c r="H1740" t="n">
         <v>38766</v>
@@ -50887,7 +50887,7 @@
         <v>16.7199993133545</v>
       </c>
       <c r="G1742" t="n">
-        <v>15.9758882522583</v>
+        <v>15.9758892059326</v>
       </c>
       <c r="H1742" t="n">
         <v>23585</v>
@@ -50916,7 +50916,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G1743" t="n">
-        <v>15.6701307296753</v>
+        <v>15.670129776001</v>
       </c>
       <c r="H1743" t="n">
         <v>19313</v>
@@ -50945,7 +50945,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G1744" t="n">
-        <v>15.6510210037231</v>
+        <v>15.6510200500488</v>
       </c>
       <c r="H1744" t="n">
         <v>12504</v>
@@ -51003,7 +51003,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1746" t="n">
-        <v>15.3834829330444</v>
+        <v>15.3834819793701</v>
       </c>
       <c r="H1746" t="n">
         <v>14029</v>
@@ -51148,7 +51148,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G1751" t="n">
-        <v>15.4790315628052</v>
+        <v>15.4790325164795</v>
       </c>
       <c r="H1751" t="n">
         <v>23459</v>
@@ -51206,7 +51206,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G1753" t="n">
-        <v>15.5554714202881</v>
+        <v>15.5554723739624</v>
       </c>
       <c r="H1753" t="n">
         <v>11068</v>
@@ -51235,7 +51235,7 @@
         <v>16.3199996948242</v>
       </c>
       <c r="G1754" t="n">
-        <v>15.5936908721924</v>
+        <v>15.5936918258667</v>
       </c>
       <c r="H1754" t="n">
         <v>12564</v>
@@ -51264,7 +51264,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1755" t="n">
-        <v>15.3834829330444</v>
+        <v>15.3834819793701</v>
       </c>
       <c r="H1755" t="n">
         <v>7789</v>
@@ -51293,7 +51293,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1756" t="n">
-        <v>15.631911277771</v>
+        <v>15.6319103240967</v>
       </c>
       <c r="H1756" t="n">
         <v>11827</v>
@@ -51322,7 +51322,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1757" t="n">
-        <v>15.8803415298462</v>
+        <v>15.8803405761719</v>
       </c>
       <c r="H1757" t="n">
         <v>9083</v>
@@ -51409,7 +51409,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1760" t="n">
-        <v>15.899450302124</v>
+        <v>15.8994493484497</v>
       </c>
       <c r="H1760" t="n">
         <v>40853</v>
@@ -51438,7 +51438,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1761" t="n">
-        <v>15.9185590744019</v>
+        <v>15.9185600280762</v>
       </c>
       <c r="H1761" t="n">
         <v>13306</v>
@@ -51467,7 +51467,7 @@
         <v>16.6200008392334</v>
       </c>
       <c r="G1762" t="n">
-        <v>15.8803415298462</v>
+        <v>15.8803405761719</v>
       </c>
       <c r="H1762" t="n">
         <v>17270</v>
@@ -51496,7 +51496,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1763" t="n">
-        <v>15.9185590744019</v>
+        <v>15.9185600280762</v>
       </c>
       <c r="H1763" t="n">
         <v>8838</v>
@@ -51554,7 +51554,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1765" t="n">
-        <v>16.6447353363037</v>
+        <v>16.6447372436523</v>
       </c>
       <c r="H1765" t="n">
         <v>43406</v>
@@ -51612,7 +51612,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1767" t="n">
-        <v>16.8167266845703</v>
+        <v>16.8167247772217</v>
       </c>
       <c r="H1767" t="n">
         <v>33266</v>
@@ -51757,7 +51757,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1772" t="n">
-        <v>16.7389602661133</v>
+        <v>16.7389583587646</v>
       </c>
       <c r="H1772" t="n">
         <v>10029</v>
@@ -51815,7 +51815,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1774" t="n">
-        <v>17.3610820770264</v>
+        <v>17.361083984375</v>
       </c>
       <c r="H1774" t="n">
         <v>41611</v>
@@ -51844,7 +51844,7 @@
         <v>17.6399993896484</v>
       </c>
       <c r="G1775" t="n">
-        <v>17.1472263336182</v>
+        <v>17.1472282409668</v>
       </c>
       <c r="H1775" t="n">
         <v>31652</v>
@@ -51902,7 +51902,7 @@
         <v>18</v>
       </c>
       <c r="G1777" t="n">
-        <v>17.4971694946289</v>
+        <v>17.4971714019775</v>
       </c>
       <c r="H1777" t="n">
         <v>32138</v>
@@ -51931,7 +51931,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G1778" t="n">
-        <v>17.7110233306885</v>
+        <v>17.7110252380371</v>
       </c>
       <c r="H1778" t="n">
         <v>35550</v>
@@ -52163,7 +52163,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G1786" t="n">
-        <v>17.4388484954834</v>
+        <v>17.4388465881348</v>
       </c>
       <c r="H1786" t="n">
         <v>25645</v>
@@ -52192,7 +52192,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1787" t="n">
-        <v>16.9528160095215</v>
+        <v>16.9528141021729</v>
       </c>
       <c r="H1787" t="n">
         <v>39085</v>
@@ -52221,7 +52221,7 @@
         <v>18</v>
       </c>
       <c r="G1788" t="n">
-        <v>17.4971694946289</v>
+        <v>17.4971714019775</v>
       </c>
       <c r="H1788" t="n">
         <v>44289</v>
@@ -52337,7 +52337,7 @@
         <v>19.9400005340576</v>
       </c>
       <c r="G1792" t="n">
-        <v>19.3829765319824</v>
+        <v>19.3829784393311</v>
       </c>
       <c r="H1792" t="n">
         <v>99635</v>
@@ -52395,7 +52395,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1794" t="n">
-        <v>20.5591735839844</v>
+        <v>20.559175491333</v>
       </c>
       <c r="H1794" t="n">
         <v>122783</v>
@@ -52453,7 +52453,7 @@
         <v>22.25</v>
       </c>
       <c r="G1796" t="n">
-        <v>21.6284484863281</v>
+        <v>21.6284465789795</v>
       </c>
       <c r="H1796" t="n">
         <v>201353</v>
@@ -52598,7 +52598,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1801" t="n">
-        <v>22.0658779144287</v>
+        <v>22.0658760070801</v>
       </c>
       <c r="H1801" t="n">
         <v>119773</v>
@@ -52685,7 +52685,7 @@
         <v>22.8999996185303</v>
       </c>
       <c r="G1804" t="n">
-        <v>22.2602882385254</v>
+        <v>22.260290145874</v>
       </c>
       <c r="H1804" t="n">
         <v>108112</v>
@@ -52714,7 +52714,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1805" t="n">
-        <v>22.2116870880127</v>
+        <v>22.2116851806641</v>
       </c>
       <c r="H1805" t="n">
         <v>88716</v>
@@ -52743,7 +52743,7 @@
         <v>23.1000003814697</v>
       </c>
       <c r="G1806" t="n">
-        <v>22.454704284668</v>
+        <v>22.4547023773193</v>
       </c>
       <c r="H1806" t="n">
         <v>61860</v>
@@ -52801,7 +52801,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1808" t="n">
-        <v>22.0658779144287</v>
+        <v>22.0658760070801</v>
       </c>
       <c r="H1808" t="n">
         <v>93663</v>
@@ -53033,7 +53033,7 @@
         <v>22.5</v>
       </c>
       <c r="G1816" t="n">
-        <v>21.8714618682861</v>
+        <v>21.8714637756348</v>
       </c>
       <c r="H1816" t="n">
         <v>77399</v>
@@ -53149,7 +53149,7 @@
         <v>22.5</v>
       </c>
       <c r="G1820" t="n">
-        <v>21.8714618682861</v>
+        <v>21.8714637756348</v>
       </c>
       <c r="H1820" t="n">
         <v>26747</v>
@@ -53207,7 +53207,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1822" t="n">
-        <v>20.5591735839844</v>
+        <v>20.559175491333</v>
       </c>
       <c r="H1822" t="n">
         <v>278045</v>
@@ -53439,7 +53439,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1830" t="n">
-        <v>19.8301277160645</v>
+        <v>19.8301258087158</v>
       </c>
       <c r="H1830" t="n">
         <v>15480</v>
@@ -53468,7 +53468,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1831" t="n">
-        <v>19.8301277160645</v>
+        <v>19.8301258087158</v>
       </c>
       <c r="H1831" t="n">
         <v>23696</v>
@@ -53497,7 +53497,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1832" t="n">
-        <v>19.8301277160645</v>
+        <v>19.8301258087158</v>
       </c>
       <c r="H1832" t="n">
         <v>22344</v>
@@ -53758,7 +53758,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G1841" t="n">
-        <v>20.4619674682617</v>
+        <v>20.4619693756104</v>
       </c>
       <c r="H1841" t="n">
         <v>51856</v>
@@ -53845,7 +53845,7 @@
         <v>21.25</v>
       </c>
       <c r="G1844" t="n">
-        <v>20.6563835144043</v>
+        <v>20.6563816070557</v>
       </c>
       <c r="H1844" t="n">
         <v>39589</v>
@@ -54019,7 +54019,7 @@
         <v>22.5</v>
       </c>
       <c r="G1850" t="n">
-        <v>21.8714618682861</v>
+        <v>21.8714637756348</v>
       </c>
       <c r="H1850" t="n">
         <v>42260</v>
@@ -54048,7 +54048,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1851" t="n">
-        <v>22.0658779144287</v>
+        <v>22.0658760070801</v>
       </c>
       <c r="H1851" t="n">
         <v>28861</v>
@@ -54222,7 +54222,7 @@
         <v>22.5</v>
       </c>
       <c r="G1857" t="n">
-        <v>21.8714618682861</v>
+        <v>21.8714637756348</v>
       </c>
       <c r="H1857" t="n">
         <v>35731</v>
@@ -54251,7 +54251,7 @@
         <v>21.75</v>
       </c>
       <c r="G1858" t="n">
-        <v>21.1424160003662</v>
+        <v>21.1424140930176</v>
       </c>
       <c r="H1858" t="n">
         <v>32316</v>
@@ -54280,7 +54280,7 @@
         <v>21.75</v>
       </c>
       <c r="G1859" t="n">
-        <v>21.1424160003662</v>
+        <v>21.1424140930176</v>
       </c>
       <c r="H1859" t="n">
         <v>28315</v>
@@ -54483,7 +54483,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1866" t="n">
-        <v>22.0658779144287</v>
+        <v>22.0658760070801</v>
       </c>
       <c r="H1866" t="n">
         <v>34703</v>
@@ -54599,7 +54599,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1870" t="n">
-        <v>22.0658779144287</v>
+        <v>22.0658760070801</v>
       </c>
       <c r="H1870" t="n">
         <v>47094</v>
@@ -54628,7 +54628,7 @@
         <v>22.5</v>
       </c>
       <c r="G1871" t="n">
-        <v>21.8714618682861</v>
+        <v>21.8714637756348</v>
       </c>
       <c r="H1871" t="n">
         <v>27927</v>
@@ -54715,7 +54715,7 @@
         <v>22.7000007629395</v>
       </c>
       <c r="G1874" t="n">
-        <v>22.0658779144287</v>
+        <v>22.0658760070801</v>
       </c>
       <c r="H1874" t="n">
         <v>17598</v>
@@ -54744,7 +54744,7 @@
         <v>22.8500003814697</v>
       </c>
       <c r="G1875" t="n">
-        <v>22.2116870880127</v>
+        <v>22.2116851806641</v>
       </c>
       <c r="H1875" t="n">
         <v>14342</v>
@@ -54773,7 +54773,7 @@
         <v>22.6000003814697</v>
       </c>
       <c r="G1876" t="n">
-        <v>21.9686717987061</v>
+        <v>21.9686698913574</v>
       </c>
       <c r="H1876" t="n">
         <v>66861</v>
@@ -55005,7 +55005,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1884" t="n">
-        <v>20.9479999542236</v>
+        <v>20.9480018615723</v>
       </c>
       <c r="H1884" t="n">
         <v>32975</v>
@@ -55092,7 +55092,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1887" t="n">
-        <v>19.8301277160645</v>
+        <v>19.8301258087158</v>
       </c>
       <c r="H1887" t="n">
         <v>19365</v>
@@ -55121,7 +55121,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1888" t="n">
-        <v>19.8301277160645</v>
+        <v>19.8301258087158</v>
       </c>
       <c r="H1888" t="n">
         <v>15966</v>
@@ -55266,7 +55266,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1893" t="n">
-        <v>19.8301277160645</v>
+        <v>19.8301258087158</v>
       </c>
       <c r="H1893" t="n">
         <v>14601</v>
@@ -55498,7 +55498,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1901" t="n">
-        <v>18.9163837432861</v>
+        <v>18.9163856506348</v>
       </c>
       <c r="H1901" t="n">
         <v>36775</v>
@@ -55527,7 +55527,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1902" t="n">
-        <v>19.305212020874</v>
+        <v>19.3052139282227</v>
       </c>
       <c r="H1902" t="n">
         <v>48850</v>
@@ -55643,7 +55643,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1906" t="n">
-        <v>20.5591735839844</v>
+        <v>20.559175491333</v>
       </c>
       <c r="H1906" t="n">
         <v>29210</v>
@@ -55672,7 +55672,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G1907" t="n">
-        <v>20.4619674682617</v>
+        <v>20.4619693756104</v>
       </c>
       <c r="H1907" t="n">
         <v>20259</v>
@@ -55701,7 +55701,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G1908" t="n">
-        <v>20.4619674682617</v>
+        <v>20.4619693756104</v>
       </c>
       <c r="H1908" t="n">
         <v>20085</v>
@@ -55788,7 +55788,7 @@
         <v>20.8500003814697</v>
       </c>
       <c r="G1911" t="n">
-        <v>20.267557144165</v>
+        <v>20.2675552368164</v>
       </c>
       <c r="H1911" t="n">
         <v>10955</v>
@@ -55875,7 +55875,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1914" t="n">
-        <v>19.8301277160645</v>
+        <v>19.8301258087158</v>
       </c>
       <c r="H1914" t="n">
         <v>22311</v>
@@ -56020,7 +56020,7 @@
         <v>19.6399993896484</v>
       </c>
       <c r="G1919" t="n">
-        <v>19.0913562774658</v>
+        <v>19.0913581848145</v>
       </c>
       <c r="H1919" t="n">
         <v>21220</v>
@@ -56049,7 +56049,7 @@
         <v>19</v>
       </c>
       <c r="G1920" t="n">
-        <v>18.4692363739014</v>
+        <v>18.4692344665527</v>
       </c>
       <c r="H1920" t="n">
         <v>31649</v>
@@ -56194,7 +56194,7 @@
         <v>19.8600006103516</v>
       </c>
       <c r="G1925" t="n">
-        <v>19.305212020874</v>
+        <v>19.3052139282227</v>
       </c>
       <c r="H1925" t="n">
         <v>13381</v>
@@ -56281,7 +56281,7 @@
         <v>19.5</v>
       </c>
       <c r="G1928" t="n">
-        <v>18.9552688598633</v>
+        <v>18.9552669525146</v>
       </c>
       <c r="H1928" t="n">
         <v>8347</v>
@@ -56368,7 +56368,7 @@
         <v>19</v>
       </c>
       <c r="G1931" t="n">
-        <v>18.4692363739014</v>
+        <v>18.4692344665527</v>
       </c>
       <c r="H1931" t="n">
         <v>30050</v>
@@ -56455,7 +56455,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1934" t="n">
-        <v>18.022087097168</v>
+        <v>18.0220851898193</v>
       </c>
       <c r="H1934" t="n">
         <v>17836</v>
@@ -56513,7 +56513,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1936" t="n">
-        <v>18.3720283508301</v>
+        <v>18.3720302581787</v>
       </c>
       <c r="H1936" t="n">
         <v>21309</v>
@@ -56745,7 +56745,7 @@
         <v>18.3799991607666</v>
       </c>
       <c r="G1944" t="n">
-        <v>17.8665542602539</v>
+        <v>17.8665561676025</v>
       </c>
       <c r="H1944" t="n">
         <v>11499</v>
@@ -56861,7 +56861,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G1948" t="n">
-        <v>17.7110233306885</v>
+        <v>17.7110252380371</v>
       </c>
       <c r="H1948" t="n">
         <v>11040</v>
@@ -56919,7 +56919,7 @@
         <v>18</v>
       </c>
       <c r="G1950" t="n">
-        <v>17.4971694946289</v>
+        <v>17.4971714019775</v>
       </c>
       <c r="H1950" t="n">
         <v>13233</v>
@@ -56948,7 +56948,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G1951" t="n">
-        <v>17.5166130065918</v>
+        <v>17.5166110992432</v>
       </c>
       <c r="H1951" t="n">
         <v>23185</v>
@@ -56977,7 +56977,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1952" t="n">
-        <v>17.6527004241943</v>
+        <v>17.652702331543</v>
       </c>
       <c r="H1952" t="n">
         <v>9194</v>
@@ -57006,7 +57006,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G1953" t="n">
-        <v>17.7110233306885</v>
+        <v>17.7110252380371</v>
       </c>
       <c r="H1953" t="n">
         <v>11744</v>
@@ -57209,7 +57209,7 @@
         <v>17.2199993133545</v>
       </c>
       <c r="G1960" t="n">
-        <v>16.7389602661133</v>
+        <v>16.7389583587646</v>
       </c>
       <c r="H1960" t="n">
         <v>39575</v>
@@ -57412,7 +57412,7 @@
         <v>17.2600002288818</v>
       </c>
       <c r="G1967" t="n">
-        <v>16.7778415679932</v>
+        <v>16.7778434753418</v>
       </c>
       <c r="H1967" t="n">
         <v>11734</v>
@@ -57470,7 +57470,7 @@
         <v>16.5</v>
       </c>
       <c r="G1969" t="n">
-        <v>16.0390720367432</v>
+        <v>16.0390739440918</v>
       </c>
       <c r="H1969" t="n">
         <v>27745</v>
@@ -57586,7 +57586,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G1973" t="n">
-        <v>15.241979598999</v>
+        <v>15.2419805526733</v>
       </c>
       <c r="H1973" t="n">
         <v>71376</v>
@@ -57615,7 +57615,7 @@
         <v>16.2800006866455</v>
       </c>
       <c r="G1974" t="n">
-        <v>15.8252191543579</v>
+        <v>15.8252201080322</v>
       </c>
       <c r="H1974" t="n">
         <v>45907</v>
@@ -57731,7 +57731,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G1978" t="n">
-        <v>15.7280130386353</v>
+        <v>15.7280120849609</v>
       </c>
       <c r="H1978" t="n">
         <v>31151</v>
@@ -57789,7 +57789,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G1980" t="n">
-        <v>15.2225389480591</v>
+        <v>15.2225379943848</v>
       </c>
       <c r="H1980" t="n">
         <v>144883</v>
@@ -57905,7 +57905,7 @@
         <v>14.8400001525879</v>
       </c>
       <c r="G1984" t="n">
-        <v>14.4254455566406</v>
+        <v>14.4254446029663</v>
       </c>
       <c r="H1984" t="n">
         <v>37176</v>
@@ -58079,7 +58079,7 @@
         <v>13.8999996185303</v>
       </c>
       <c r="G1990" t="n">
-        <v>13.5117034912109</v>
+        <v>13.5117044448853</v>
       </c>
       <c r="H1990" t="n">
         <v>36143</v>
@@ -58224,7 +58224,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1995" t="n">
-        <v>13.8033227920532</v>
+        <v>13.8033237457275</v>
       </c>
       <c r="H1995" t="n">
         <v>26953</v>
@@ -58340,7 +58340,7 @@
         <v>14.6599998474121</v>
       </c>
       <c r="G1999" t="n">
-        <v>14.2504739761353</v>
+        <v>14.2504730224609</v>
       </c>
       <c r="H1999" t="n">
         <v>24691</v>
@@ -58369,7 +58369,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G2000" t="n">
-        <v>13.8810882568359</v>
+        <v>13.8810892105103</v>
       </c>
       <c r="H2000" t="n">
         <v>36600</v>
@@ -58456,7 +58456,7 @@
         <v>15.7600002288818</v>
       </c>
       <c r="G2003" t="n">
-        <v>15.3197450637817</v>
+        <v>15.3197460174561</v>
       </c>
       <c r="H2003" t="n">
         <v>73104</v>
@@ -58514,7 +58514,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G2005" t="n">
-        <v>15.3586273193359</v>
+        <v>15.3586282730103</v>
       </c>
       <c r="H2005" t="n">
         <v>27219</v>
@@ -58543,7 +58543,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G2006" t="n">
-        <v>15.241979598999</v>
+        <v>15.2419805526733</v>
       </c>
       <c r="H2006" t="n">
         <v>22019</v>
@@ -58572,7 +58572,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G2007" t="n">
-        <v>14.969801902771</v>
+        <v>14.9698009490967</v>
       </c>
       <c r="H2007" t="n">
         <v>20057</v>
@@ -58601,7 +58601,7 @@
         <v>16.5</v>
       </c>
       <c r="G2008" t="n">
-        <v>16.0390720367432</v>
+        <v>16.0390739440918</v>
       </c>
       <c r="H2008" t="n">
         <v>47229</v>
@@ -69366,6 +69366,64 @@
         <v>21884</v>
       </c>
       <c r="I2379" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2380">
+      <c r="A2380" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2380" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C2380" t="n">
+        <v>29</v>
+      </c>
+      <c r="D2380" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2380" t="n">
+        <v>28.3500003814697</v>
+      </c>
+      <c r="F2380" t="n">
+        <v>28.7000007629395</v>
+      </c>
+      <c r="G2380" t="n">
+        <v>28.7000007629395</v>
+      </c>
+      <c r="H2380" t="n">
+        <v>18927</v>
+      </c>
+      <c r="I2380" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2381">
+      <c r="A2381" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2381" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C2381" t="n">
+        <v>29.0499992370605</v>
+      </c>
+      <c r="D2381" t="n">
+        <v>29.0499992370605</v>
+      </c>
+      <c r="E2381" t="n">
+        <v>28.1499996185303</v>
+      </c>
+      <c r="F2381" t="n">
+        <v>28.7000007629395</v>
+      </c>
+      <c r="G2381" t="n">
+        <v>28.7000007629395</v>
+      </c>
+      <c r="H2381" t="n">
+        <v>12354</v>
+      </c>
+      <c r="I2381" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/WIIT.MI.xlsx
+++ b/data/WIIT.MI.xlsx
@@ -485,7 +485,7 @@
         <v>5.125</v>
       </c>
       <c r="G4" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H4" t="n">
         <v>16400</v>
@@ -514,7 +514,7 @@
         <v>5.125</v>
       </c>
       <c r="G5" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -543,7 +543,7 @@
         <v>5.125</v>
       </c>
       <c r="G6" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -572,7 +572,7 @@
         <v>5.125</v>
       </c>
       <c r="G7" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -601,7 +601,7 @@
         <v>5.125</v>
       </c>
       <c r="G8" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -630,7 +630,7 @@
         <v>5.125</v>
       </c>
       <c r="G9" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -659,7 +659,7 @@
         <v>5.125</v>
       </c>
       <c r="G10" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -688,7 +688,7 @@
         <v>5.125</v>
       </c>
       <c r="G11" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -717,7 +717,7 @@
         <v>5.125</v>
       </c>
       <c r="G12" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -746,7 +746,7 @@
         <v>5.125</v>
       </c>
       <c r="G13" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -775,7 +775,7 @@
         <v>5.125</v>
       </c>
       <c r="G14" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -804,7 +804,7 @@
         <v>5.125</v>
       </c>
       <c r="G15" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -833,7 +833,7 @@
         <v>5.125</v>
       </c>
       <c r="G16" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
         <v>5.125</v>
       </c>
       <c r="G17" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>5.125</v>
       </c>
       <c r="G18" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>5.125</v>
       </c>
       <c r="G19" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>5.125</v>
       </c>
       <c r="G20" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>5.125</v>
       </c>
       <c r="G21" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1007,7 +1007,7 @@
         <v>5.125</v>
       </c>
       <c r="G22" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1036,7 +1036,7 @@
         <v>5.125</v>
       </c>
       <c r="G23" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1065,7 +1065,7 @@
         <v>5.125</v>
       </c>
       <c r="G24" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>5.125</v>
       </c>
       <c r="G25" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         <v>5.125</v>
       </c>
       <c r="G26" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>5.125</v>
       </c>
       <c r="G27" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1181,7 +1181,7 @@
         <v>5.125</v>
       </c>
       <c r="G28" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>5.125</v>
       </c>
       <c r="G29" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1239,7 +1239,7 @@
         <v>5.125</v>
       </c>
       <c r="G30" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>5.125</v>
       </c>
       <c r="G31" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>5.125</v>
       </c>
       <c r="G32" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1326,7 +1326,7 @@
         <v>5.125</v>
       </c>
       <c r="G33" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
         <v>5.125</v>
       </c>
       <c r="G34" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>5.125</v>
       </c>
       <c r="G35" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>5.125</v>
       </c>
       <c r="G36" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>5.125</v>
       </c>
       <c r="G37" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1471,7 +1471,7 @@
         <v>5.125</v>
       </c>
       <c r="G38" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>5.125</v>
       </c>
       <c r="G39" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -1529,7 +1529,7 @@
         <v>5.125</v>
       </c>
       <c r="G40" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1558,7 +1558,7 @@
         <v>5.125</v>
       </c>
       <c r="G41" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>5.125</v>
       </c>
       <c r="G42" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>5.125</v>
       </c>
       <c r="G43" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>5.125</v>
       </c>
       <c r="G44" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>5.125</v>
       </c>
       <c r="G45" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>5.125</v>
       </c>
       <c r="G46" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>5.125</v>
       </c>
       <c r="G47" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -1761,7 +1761,7 @@
         <v>5.125</v>
       </c>
       <c r="G48" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>5.125</v>
       </c>
       <c r="G49" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1819,7 +1819,7 @@
         <v>5.125</v>
       </c>
       <c r="G50" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>5.125</v>
       </c>
       <c r="G51" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>5.125</v>
       </c>
       <c r="G52" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>5.125</v>
       </c>
       <c r="G53" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
         <v>5.125</v>
       </c>
       <c r="G54" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
         <v>5.125</v>
       </c>
       <c r="G55" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -1993,7 +1993,7 @@
         <v>5.125</v>
       </c>
       <c r="G56" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>5.125</v>
       </c>
       <c r="G57" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
         <v>5.125</v>
       </c>
       <c r="G58" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>5.125</v>
       </c>
       <c r="G59" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>5.125</v>
       </c>
       <c r="G60" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2138,7 +2138,7 @@
         <v>5.125</v>
       </c>
       <c r="G61" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>5.125</v>
       </c>
       <c r="G62" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>5.125</v>
       </c>
       <c r="G63" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2225,7 +2225,7 @@
         <v>5.125</v>
       </c>
       <c r="G64" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -2254,7 +2254,7 @@
         <v>5.125</v>
       </c>
       <c r="G65" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>5.125</v>
       </c>
       <c r="G66" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>5.125</v>
       </c>
       <c r="G67" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>5.125</v>
       </c>
       <c r="G68" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>5.125</v>
       </c>
       <c r="G69" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>5.125</v>
       </c>
       <c r="G70" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>5.125</v>
       </c>
       <c r="G71" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>5.125</v>
       </c>
       <c r="G72" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>5.125</v>
       </c>
       <c r="G73" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>5.125</v>
       </c>
       <c r="G74" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>5.125</v>
       </c>
       <c r="G75" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>5.125</v>
       </c>
       <c r="G76" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
         <v>5.125</v>
       </c>
       <c r="G77" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -2631,7 +2631,7 @@
         <v>5.125</v>
       </c>
       <c r="G78" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -2660,7 +2660,7 @@
         <v>5.125</v>
       </c>
       <c r="G79" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -2689,7 +2689,7 @@
         <v>5.125</v>
       </c>
       <c r="G80" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>5.125</v>
       </c>
       <c r="G81" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>5.125</v>
       </c>
       <c r="G82" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -2776,7 +2776,7 @@
         <v>5.125</v>
       </c>
       <c r="G83" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>5.125</v>
       </c>
       <c r="G84" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>5.125</v>
       </c>
       <c r="G85" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
         <v>5.125</v>
       </c>
       <c r="G86" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>5.125</v>
       </c>
       <c r="G87" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>5.125</v>
       </c>
       <c r="G88" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>5.125</v>
       </c>
       <c r="G89" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>5.125</v>
       </c>
       <c r="G90" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>5.125</v>
       </c>
       <c r="G91" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>5.125</v>
       </c>
       <c r="G92" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -3066,7 +3066,7 @@
         <v>5.125</v>
       </c>
       <c r="G93" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -3095,7 +3095,7 @@
         <v>5.125</v>
       </c>
       <c r="G94" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>5.125</v>
       </c>
       <c r="G95" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>5.125</v>
       </c>
       <c r="G96" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>5.125</v>
       </c>
       <c r="G97" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>5.125</v>
       </c>
       <c r="G98" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>5.125</v>
       </c>
       <c r="G99" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>5.125</v>
       </c>
       <c r="G100" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>5.125</v>
       </c>
       <c r="G101" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>5.125</v>
       </c>
       <c r="G102" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H102" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>5.125</v>
       </c>
       <c r="G103" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
         <v>5.125</v>
       </c>
       <c r="G104" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>5.125</v>
       </c>
       <c r="G105" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>5.125</v>
       </c>
       <c r="G106" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -3472,7 +3472,7 @@
         <v>5.125</v>
       </c>
       <c r="G107" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>5.125</v>
       </c>
       <c r="G108" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>5.125</v>
       </c>
       <c r="G109" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>5.125</v>
       </c>
       <c r="G110" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>5.125</v>
       </c>
       <c r="G111" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>5.125</v>
       </c>
       <c r="G112" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>5.125</v>
       </c>
       <c r="G113" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>5.125</v>
       </c>
       <c r="G114" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>5.125</v>
       </c>
       <c r="G115" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
         <v>5.125</v>
       </c>
       <c r="G116" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -3762,7 +3762,7 @@
         <v>5.125</v>
       </c>
       <c r="G117" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -3791,7 +3791,7 @@
         <v>5.125</v>
       </c>
       <c r="G118" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -3820,7 +3820,7 @@
         <v>5.125</v>
       </c>
       <c r="G119" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>5.125</v>
       </c>
       <c r="G120" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>5.125</v>
       </c>
       <c r="G121" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -3907,7 +3907,7 @@
         <v>5.125</v>
       </c>
       <c r="G122" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
         <v>5.125</v>
       </c>
       <c r="G123" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
         <v>5.125</v>
       </c>
       <c r="G124" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -3994,7 +3994,7 @@
         <v>5.125</v>
       </c>
       <c r="G125" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>5.125</v>
       </c>
       <c r="G126" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -4052,7 +4052,7 @@
         <v>5.125</v>
       </c>
       <c r="G127" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -4081,7 +4081,7 @@
         <v>5.125</v>
       </c>
       <c r="G128" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>5.125</v>
       </c>
       <c r="G129" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
         <v>5.125</v>
       </c>
       <c r="G130" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>5.125</v>
       </c>
       <c r="G131" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -4197,7 +4197,7 @@
         <v>5.125</v>
       </c>
       <c r="G132" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -4226,7 +4226,7 @@
         <v>5.125</v>
       </c>
       <c r="G133" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>5.125</v>
       </c>
       <c r="G134" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>5.125</v>
       </c>
       <c r="G135" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>5.125</v>
       </c>
       <c r="G136" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>5.125</v>
       </c>
       <c r="G137" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
         <v>5.125</v>
       </c>
       <c r="G138" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>5.125</v>
       </c>
       <c r="G139" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
         <v>5.125</v>
       </c>
       <c r="G140" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -4458,7 +4458,7 @@
         <v>5.125</v>
       </c>
       <c r="G141" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>5.125</v>
       </c>
       <c r="G142" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>5.125</v>
       </c>
       <c r="G143" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>5.125</v>
       </c>
       <c r="G144" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>5.125</v>
       </c>
       <c r="G145" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>5.125</v>
       </c>
       <c r="G146" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>5.125</v>
       </c>
       <c r="G147" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -4661,7 +4661,7 @@
         <v>5.125</v>
       </c>
       <c r="G148" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -4690,7 +4690,7 @@
         <v>5.125</v>
       </c>
       <c r="G149" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>5.125</v>
       </c>
       <c r="G150" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>5.125</v>
       </c>
       <c r="G151" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>5.125</v>
       </c>
       <c r="G152" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>5.125</v>
       </c>
       <c r="G153" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>5.125</v>
       </c>
       <c r="G154" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
         <v>5.125</v>
       </c>
       <c r="G155" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>5.125</v>
       </c>
       <c r="G156" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>5.125</v>
       </c>
       <c r="G157" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>5.125</v>
       </c>
       <c r="G158" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>5.125</v>
       </c>
       <c r="G159" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>5.125</v>
       </c>
       <c r="G160" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>5.125</v>
       </c>
       <c r="G161" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -5067,7 +5067,7 @@
         <v>5.125</v>
       </c>
       <c r="G162" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>5.125</v>
       </c>
       <c r="G163" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -5125,7 +5125,7 @@
         <v>5.125</v>
       </c>
       <c r="G164" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -5154,7 +5154,7 @@
         <v>5.125</v>
       </c>
       <c r="G165" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>5.125</v>
       </c>
       <c r="G166" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>5.125</v>
       </c>
       <c r="G167" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -5241,7 +5241,7 @@
         <v>5.125</v>
       </c>
       <c r="G168" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>5.125</v>
       </c>
       <c r="G169" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>5.125</v>
       </c>
       <c r="G170" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -5328,7 +5328,7 @@
         <v>5.125</v>
       </c>
       <c r="G171" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>5.125</v>
       </c>
       <c r="G172" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>5.125</v>
       </c>
       <c r="G173" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -5415,7 +5415,7 @@
         <v>5.125</v>
       </c>
       <c r="G174" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>5.125</v>
       </c>
       <c r="G175" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -5473,7 +5473,7 @@
         <v>5.125</v>
       </c>
       <c r="G176" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
         <v>5.125</v>
       </c>
       <c r="G177" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>5.125</v>
       </c>
       <c r="G178" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
         <v>5.125</v>
       </c>
       <c r="G179" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
         <v>5.125</v>
       </c>
       <c r="G180" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -5618,7 +5618,7 @@
         <v>5.125</v>
       </c>
       <c r="G181" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -5647,7 +5647,7 @@
         <v>5.125</v>
       </c>
       <c r="G182" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -5676,7 +5676,7 @@
         <v>5.125</v>
       </c>
       <c r="G183" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>5.125</v>
       </c>
       <c r="G184" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>5.125</v>
       </c>
       <c r="G185" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>5.125</v>
       </c>
       <c r="G186" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -5792,7 +5792,7 @@
         <v>5.125</v>
       </c>
       <c r="G187" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>5.125</v>
       </c>
       <c r="G188" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -5850,7 +5850,7 @@
         <v>5.125</v>
       </c>
       <c r="G189" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
         <v>5.125</v>
       </c>
       <c r="G190" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>5.125</v>
       </c>
       <c r="G191" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -5937,7 +5937,7 @@
         <v>5.125</v>
       </c>
       <c r="G192" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -5966,7 +5966,7 @@
         <v>5.125</v>
       </c>
       <c r="G193" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -5995,7 +5995,7 @@
         <v>5.125</v>
       </c>
       <c r="G194" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -6024,7 +6024,7 @@
         <v>5.125</v>
       </c>
       <c r="G195" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -6053,7 +6053,7 @@
         <v>5.125</v>
       </c>
       <c r="G196" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>5.125</v>
       </c>
       <c r="G197" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -6111,7 +6111,7 @@
         <v>5.125</v>
       </c>
       <c r="G198" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -6140,7 +6140,7 @@
         <v>5.125</v>
       </c>
       <c r="G199" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -6169,7 +6169,7 @@
         <v>5.125</v>
       </c>
       <c r="G200" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -6198,7 +6198,7 @@
         <v>5.125</v>
       </c>
       <c r="G201" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -6227,7 +6227,7 @@
         <v>5.125</v>
       </c>
       <c r="G202" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -6256,7 +6256,7 @@
         <v>5.125</v>
       </c>
       <c r="G203" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -6285,7 +6285,7 @@
         <v>5.125</v>
       </c>
       <c r="G204" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
         <v>5.125</v>
       </c>
       <c r="G205" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -6343,7 +6343,7 @@
         <v>5.125</v>
       </c>
       <c r="G206" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H206" t="n">
         <v>0</v>
@@ -6372,7 +6372,7 @@
         <v>5.125</v>
       </c>
       <c r="G207" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -6401,7 +6401,7 @@
         <v>5.125</v>
       </c>
       <c r="G208" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -6430,7 +6430,7 @@
         <v>5.125</v>
       </c>
       <c r="G209" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>5.125</v>
       </c>
       <c r="G210" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>5.125</v>
       </c>
       <c r="G211" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
         <v>5.125</v>
       </c>
       <c r="G212" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>5.125</v>
       </c>
       <c r="G213" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>5.125</v>
       </c>
       <c r="G214" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -6604,7 +6604,7 @@
         <v>5.125</v>
       </c>
       <c r="G215" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>5.125</v>
       </c>
       <c r="G216" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -6662,7 +6662,7 @@
         <v>5.125</v>
       </c>
       <c r="G217" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
         <v>5.125</v>
       </c>
       <c r="G218" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
         <v>5.125</v>
       </c>
       <c r="G219" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
         <v>5.125</v>
       </c>
       <c r="G220" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>5.125</v>
       </c>
       <c r="G221" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>5.125</v>
       </c>
       <c r="G222" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>5.125</v>
       </c>
       <c r="G223" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
         <v>5.125</v>
       </c>
       <c r="G224" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>5.125</v>
       </c>
       <c r="G225" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -6923,7 +6923,7 @@
         <v>5.125</v>
       </c>
       <c r="G226" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>5.125</v>
       </c>
       <c r="G227" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
         <v>5.125</v>
       </c>
       <c r="G228" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>5.125</v>
       </c>
       <c r="G229" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>5.125</v>
       </c>
       <c r="G230" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>5.125</v>
       </c>
       <c r="G231" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>5.125</v>
       </c>
       <c r="G232" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G274" t="n">
-        <v>4.51098775863647</v>
+        <v>4.51098823547363</v>
       </c>
       <c r="H274" t="n">
         <v>21200</v>
@@ -8402,7 +8402,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G277" t="n">
-        <v>4.49308681488037</v>
+        <v>4.49308729171753</v>
       </c>
       <c r="H277" t="n">
         <v>10800</v>
@@ -8431,7 +8431,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G278" t="n">
-        <v>4.44833517074585</v>
+        <v>4.44833564758301</v>
       </c>
       <c r="H278" t="n">
         <v>12800</v>
@@ -8547,7 +8547,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G282" t="n">
-        <v>4.49308681488037</v>
+        <v>4.49308729171753</v>
       </c>
       <c r="H282" t="n">
         <v>8800</v>
@@ -8576,7 +8576,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G283" t="n">
-        <v>4.43938541412354</v>
+        <v>4.43938493728638</v>
       </c>
       <c r="H283" t="n">
         <v>6000</v>
@@ -8605,7 +8605,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G284" t="n">
-        <v>4.49308681488037</v>
+        <v>4.49308729171753</v>
       </c>
       <c r="H284" t="n">
         <v>35200</v>
@@ -8663,7 +8663,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G286" t="n">
-        <v>4.44833517074585</v>
+        <v>4.44833564758301</v>
       </c>
       <c r="H286" t="n">
         <v>4800</v>
@@ -8692,7 +8692,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G287" t="n">
-        <v>4.44833517074585</v>
+        <v>4.44833564758301</v>
       </c>
       <c r="H287" t="n">
         <v>58000</v>
@@ -8721,7 +8721,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G288" t="n">
-        <v>4.44833517074585</v>
+        <v>4.44833564758301</v>
       </c>
       <c r="H288" t="n">
         <v>4400</v>
@@ -8750,7 +8750,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G289" t="n">
-        <v>4.44833517074585</v>
+        <v>4.44833564758301</v>
       </c>
       <c r="H289" t="n">
         <v>4800</v>
@@ -8895,7 +8895,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G294" t="n">
-        <v>4.58259010314941</v>
+        <v>4.58259057998657</v>
       </c>
       <c r="H294" t="n">
         <v>6400</v>
@@ -8953,7 +8953,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G296" t="n">
-        <v>4.51098775863647</v>
+        <v>4.51098823547363</v>
       </c>
       <c r="H296" t="n">
         <v>400</v>
@@ -9011,7 +9011,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G298" t="n">
-        <v>4.51098775863647</v>
+        <v>4.51098823547363</v>
       </c>
       <c r="H298" t="n">
         <v>400</v>
@@ -9040,7 +9040,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>4.51098775863647</v>
+        <v>4.51098823547363</v>
       </c>
       <c r="H299" t="n">
         <v>1600</v>
@@ -9069,7 +9069,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G300" t="n">
-        <v>4.49308681488037</v>
+        <v>4.49308729171753</v>
       </c>
       <c r="H300" t="n">
         <v>2400</v>
@@ -9098,7 +9098,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G301" t="n">
-        <v>4.49308681488037</v>
+        <v>4.49308729171753</v>
       </c>
       <c r="H301" t="n">
         <v>0</v>
@@ -9127,7 +9127,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G302" t="n">
-        <v>4.49308681488037</v>
+        <v>4.49308729171753</v>
       </c>
       <c r="H302" t="n">
         <v>0</v>
@@ -9214,7 +9214,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G305" t="n">
-        <v>4.38568305969238</v>
+        <v>4.38568353652954</v>
       </c>
       <c r="H305" t="n">
         <v>3200</v>
@@ -9301,7 +9301,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G308" t="n">
-        <v>4.29617881774902</v>
+        <v>4.29617977142334</v>
       </c>
       <c r="H308" t="n">
         <v>400</v>
@@ -9446,7 +9446,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>4.45728588104248</v>
+        <v>4.45728635787964</v>
       </c>
       <c r="H313" t="n">
         <v>5200</v>
@@ -9475,7 +9475,7 @@
         <v>4.96000003814697</v>
       </c>
       <c r="G314" t="n">
-        <v>4.43938541412354</v>
+        <v>4.43938493728638</v>
       </c>
       <c r="H314" t="n">
         <v>2000</v>
@@ -9504,7 +9504,7 @@
         <v>4.88000011444092</v>
       </c>
       <c r="G315" t="n">
-        <v>4.36778211593628</v>
+        <v>4.36778259277344</v>
       </c>
       <c r="H315" t="n">
         <v>1600</v>
@@ -9562,7 +9562,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G317" t="n">
-        <v>4.32303047180176</v>
+        <v>4.3230299949646</v>
       </c>
       <c r="H317" t="n">
         <v>800</v>
@@ -9591,7 +9591,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G318" t="n">
-        <v>4.32303047180176</v>
+        <v>4.3230299949646</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G320" t="n">
-        <v>4.14402294158936</v>
+        <v>4.1440224647522</v>
       </c>
       <c r="H320" t="n">
         <v>24400</v>
@@ -9678,7 +9678,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G321" t="n">
-        <v>4.23352718353271</v>
+        <v>4.2335262298584</v>
       </c>
       <c r="H321" t="n">
         <v>800</v>
@@ -9707,7 +9707,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G322" t="n">
-        <v>4.32303047180176</v>
+        <v>4.3230299949646</v>
       </c>
       <c r="H322" t="n">
         <v>2800</v>
@@ -9736,7 +9736,7 @@
         <v>4.8600001335144</v>
       </c>
       <c r="G323" t="n">
-        <v>4.34988117218018</v>
+        <v>4.34988164901733</v>
       </c>
       <c r="H323" t="n">
         <v>2400</v>
@@ -9823,7 +9823,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G326" t="n">
-        <v>4.09032106399536</v>
+        <v>4.09032011032104</v>
       </c>
       <c r="H326" t="n">
         <v>218400</v>
@@ -9852,7 +9852,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G327" t="n">
-        <v>4.04556894302368</v>
+        <v>4.04556798934937</v>
       </c>
       <c r="H327" t="n">
         <v>117200</v>
@@ -9910,7 +9910,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G329" t="n">
-        <v>3.99186682701111</v>
+        <v>3.99186635017395</v>
       </c>
       <c r="H329" t="n">
         <v>5200</v>
@@ -9939,7 +9939,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G330" t="n">
-        <v>4.14402294158936</v>
+        <v>4.1440224647522</v>
       </c>
       <c r="H330" t="n">
         <v>6400</v>
@@ -9968,7 +9968,7 @@
         <v>4.55999994277954</v>
       </c>
       <c r="G331" t="n">
-        <v>4.08137035369873</v>
+        <v>4.08137083053589</v>
       </c>
       <c r="H331" t="n">
         <v>4400</v>
@@ -9997,7 +9997,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G332" t="n">
-        <v>4.13507270812988</v>
+        <v>4.13507175445557</v>
       </c>
       <c r="H332" t="n">
         <v>1600</v>
@@ -10055,7 +10055,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G334" t="n">
-        <v>4.14402294158936</v>
+        <v>4.1440224647522</v>
       </c>
       <c r="H334" t="n">
         <v>21600</v>
@@ -10084,7 +10084,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G335" t="n">
-        <v>4.11717176437378</v>
+        <v>4.11717224121094</v>
       </c>
       <c r="H335" t="n">
         <v>39200</v>
@@ -10113,7 +10113,7 @@
         <v>4.46000003814697</v>
       </c>
       <c r="G336" t="n">
-        <v>3.99186682701111</v>
+        <v>3.99186635017395</v>
       </c>
       <c r="H336" t="n">
         <v>15200</v>
@@ -10142,7 +10142,7 @@
         <v>4.5</v>
       </c>
       <c r="G337" t="n">
-        <v>4.02766799926758</v>
+        <v>4.02766847610474</v>
       </c>
       <c r="H337" t="n">
         <v>1600</v>
@@ -10200,7 +10200,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G339" t="n">
-        <v>3.88446235656738</v>
+        <v>3.88446164131165</v>
       </c>
       <c r="H339" t="n">
         <v>3600</v>
@@ -10258,7 +10258,7 @@
         <v>4.32000017166138</v>
       </c>
       <c r="G341" t="n">
-        <v>3.86656093597412</v>
+        <v>3.8665611743927</v>
       </c>
       <c r="H341" t="n">
         <v>2400</v>
@@ -10287,7 +10287,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>3.76810717582703</v>
+        <v>3.76810741424561</v>
       </c>
       <c r="H342" t="n">
         <v>6000</v>
@@ -10316,7 +10316,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G343" t="n">
-        <v>3.8486602306366</v>
+        <v>3.84866046905518</v>
       </c>
       <c r="H343" t="n">
         <v>2400</v>
@@ -10345,7 +10345,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G344" t="n">
-        <v>3.78600788116455</v>
+        <v>3.78600740432739</v>
       </c>
       <c r="H344" t="n">
         <v>1200</v>
@@ -10374,7 +10374,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G345" t="n">
-        <v>3.7054545879364</v>
+        <v>3.70545434951782</v>
       </c>
       <c r="H345" t="n">
         <v>1600</v>
@@ -10403,7 +10403,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G346" t="n">
-        <v>3.66965270042419</v>
+        <v>3.66965293884277</v>
       </c>
       <c r="H346" t="n">
         <v>800</v>
@@ -10432,7 +10432,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G347" t="n">
-        <v>3.60700058937073</v>
+        <v>3.60700082778931</v>
       </c>
       <c r="H347" t="n">
         <v>18000</v>
@@ -10461,7 +10461,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G348" t="n">
-        <v>3.59805035591125</v>
+        <v>3.5980498790741</v>
       </c>
       <c r="H348" t="n">
         <v>6400</v>
@@ -10490,7 +10490,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G349" t="n">
-        <v>3.59805035591125</v>
+        <v>3.5980498790741</v>
       </c>
       <c r="H349" t="n">
         <v>1600</v>
@@ -10577,7 +10577,7 @@
         <v>4</v>
       </c>
       <c r="G352" t="n">
-        <v>3.58014917373657</v>
+        <v>3.58014965057373</v>
       </c>
       <c r="H352" t="n">
         <v>800</v>
@@ -10606,7 +10606,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G353" t="n">
-        <v>3.43694305419922</v>
+        <v>3.43694353103638</v>
       </c>
       <c r="H353" t="n">
         <v>2800</v>
@@ -10664,7 +10664,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G355" t="n">
-        <v>3.44589352607727</v>
+        <v>3.44589400291443</v>
       </c>
       <c r="H355" t="n">
         <v>10400</v>
@@ -10722,7 +10722,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G357" t="n">
-        <v>3.3921914100647</v>
+        <v>3.39219164848328</v>
       </c>
       <c r="H357" t="n">
         <v>43200</v>
@@ -10751,7 +10751,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G358" t="n">
-        <v>3.31163787841797</v>
+        <v>3.31163859367371</v>
       </c>
       <c r="H358" t="n">
         <v>21600</v>
@@ -10780,7 +10780,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G359" t="n">
-        <v>3.31163787841797</v>
+        <v>3.31163859367371</v>
       </c>
       <c r="H359" t="n">
         <v>10000</v>
@@ -10809,7 +10809,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G360" t="n">
-        <v>3.31163787841797</v>
+        <v>3.31163859367371</v>
       </c>
       <c r="H360" t="n">
         <v>4800</v>
@@ -10838,7 +10838,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G361" t="n">
-        <v>3.34744000434875</v>
+        <v>3.34743976593018</v>
       </c>
       <c r="H361" t="n">
         <v>9200</v>
@@ -10867,7 +10867,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G362" t="n">
-        <v>3.3653404712677</v>
+        <v>3.36534070968628</v>
       </c>
       <c r="H362" t="n">
         <v>5200</v>
@@ -10896,7 +10896,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G363" t="n">
-        <v>3.31163787841797</v>
+        <v>3.31163859367371</v>
       </c>
       <c r="H363" t="n">
         <v>11200</v>
@@ -10925,7 +10925,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G364" t="n">
-        <v>3.2042338848114</v>
+        <v>3.20423364639282</v>
       </c>
       <c r="H364" t="n">
         <v>18000</v>
@@ -10983,7 +10983,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G366" t="n">
-        <v>3.07892847061157</v>
+        <v>3.07892870903015</v>
       </c>
       <c r="H366" t="n">
         <v>31600</v>
@@ -11012,7 +11012,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G367" t="n">
-        <v>3.0968291759491</v>
+        <v>3.09682941436768</v>
       </c>
       <c r="H367" t="n">
         <v>28000</v>
@@ -11041,7 +11041,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G368" t="n">
-        <v>3.10577940940857</v>
+        <v>3.10577964782715</v>
       </c>
       <c r="H368" t="n">
         <v>18000</v>
@@ -11070,7 +11070,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G369" t="n">
-        <v>3.2042338848114</v>
+        <v>3.20423364639282</v>
       </c>
       <c r="H369" t="n">
         <v>68000</v>
@@ -11186,7 +11186,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G373" t="n">
-        <v>2.93572235107422</v>
+        <v>2.93572282791138</v>
       </c>
       <c r="H373" t="n">
         <v>160400</v>
@@ -11215,7 +11215,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G374" t="n">
-        <v>2.85516905784607</v>
+        <v>2.85516881942749</v>
       </c>
       <c r="H374" t="n">
         <v>86400</v>
@@ -11244,7 +11244,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G375" t="n">
-        <v>2.82831835746765</v>
+        <v>2.82831788063049</v>
       </c>
       <c r="H375" t="n">
         <v>35200</v>
@@ -11273,7 +11273,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G376" t="n">
-        <v>2.91782140731812</v>
+        <v>2.91782164573669</v>
       </c>
       <c r="H376" t="n">
         <v>90400</v>
@@ -11331,7 +11331,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G378" t="n">
-        <v>2.91782140731812</v>
+        <v>2.91782164573669</v>
       </c>
       <c r="H378" t="n">
         <v>18000</v>
@@ -11360,7 +11360,7 @@
         <v>3.25</v>
       </c>
       <c r="G379" t="n">
-        <v>2.90887117385864</v>
+        <v>2.90887141227722</v>
       </c>
       <c r="H379" t="n">
         <v>8800</v>
@@ -11389,7 +11389,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G380" t="n">
-        <v>2.86411952972412</v>
+        <v>2.86411929130554</v>
       </c>
       <c r="H380" t="n">
         <v>15600</v>
@@ -11418,7 +11418,7 @@
         <v>3.25</v>
       </c>
       <c r="G381" t="n">
-        <v>2.90887117385864</v>
+        <v>2.90887141227722</v>
       </c>
       <c r="H381" t="n">
         <v>67200</v>
@@ -11563,7 +11563,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G386" t="n">
-        <v>2.91782140731812</v>
+        <v>2.91782164573669</v>
       </c>
       <c r="H386" t="n">
         <v>2400</v>
@@ -11592,7 +11592,7 @@
         <v>3.25</v>
       </c>
       <c r="G387" t="n">
-        <v>2.90887117385864</v>
+        <v>2.90887141227722</v>
       </c>
       <c r="H387" t="n">
         <v>8400</v>
@@ -11621,7 +11621,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G388" t="n">
-        <v>2.82831835746765</v>
+        <v>2.82831788063049</v>
       </c>
       <c r="H388" t="n">
         <v>800</v>
@@ -11650,7 +11650,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G389" t="n">
-        <v>2.86411952972412</v>
+        <v>2.86411929130554</v>
       </c>
       <c r="H389" t="n">
         <v>14800</v>
@@ -11679,7 +11679,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G390" t="n">
-        <v>2.81041717529297</v>
+        <v>2.81041693687439</v>
       </c>
       <c r="H390" t="n">
         <v>11200</v>
@@ -11708,7 +11708,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G391" t="n">
-        <v>2.84621930122375</v>
+        <v>2.84621906280518</v>
       </c>
       <c r="H391" t="n">
         <v>25200</v>
@@ -11737,7 +11737,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G392" t="n">
-        <v>2.86411952972412</v>
+        <v>2.86411929130554</v>
       </c>
       <c r="H392" t="n">
         <v>18000</v>
@@ -11766,7 +11766,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G393" t="n">
-        <v>2.89992070198059</v>
+        <v>2.89992094039917</v>
       </c>
       <c r="H393" t="n">
         <v>26000</v>
@@ -11795,7 +11795,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G394" t="n">
-        <v>2.94467258453369</v>
+        <v>2.94467282295227</v>
       </c>
       <c r="H394" t="n">
         <v>2000</v>
@@ -11824,7 +11824,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G395" t="n">
-        <v>3.06102752685547</v>
+        <v>3.06102800369263</v>
       </c>
       <c r="H395" t="n">
         <v>27600</v>
@@ -11853,7 +11853,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G396" t="n">
-        <v>3.06997799873352</v>
+        <v>3.0699782371521</v>
       </c>
       <c r="H396" t="n">
         <v>10800</v>
@@ -11940,7 +11940,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G399" t="n">
-        <v>3.26688623428345</v>
+        <v>3.26688647270203</v>
       </c>
       <c r="H399" t="n">
         <v>7600</v>
@@ -11998,7 +11998,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G401" t="n">
-        <v>3.26688623428345</v>
+        <v>3.26688647270203</v>
       </c>
       <c r="H401" t="n">
         <v>2400</v>
@@ -12027,7 +12027,7 @@
         <v>3.65000009536743</v>
       </c>
       <c r="G402" t="n">
-        <v>3.26688623428345</v>
+        <v>3.26688647270203</v>
       </c>
       <c r="H402" t="n">
         <v>0</v>
@@ -12056,7 +12056,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G403" t="n">
-        <v>3.31163787841797</v>
+        <v>3.31163859367371</v>
       </c>
       <c r="H403" t="n">
         <v>3600</v>
@@ -12085,7 +12085,7 @@
         <v>3.75</v>
       </c>
       <c r="G404" t="n">
-        <v>3.35638999938965</v>
+        <v>3.35639023780823</v>
       </c>
       <c r="H404" t="n">
         <v>100000</v>
@@ -12114,7 +12114,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G405" t="n">
-        <v>3.3921914100647</v>
+        <v>3.39219164848328</v>
       </c>
       <c r="H405" t="n">
         <v>8000</v>
@@ -12143,7 +12143,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G406" t="n">
-        <v>3.499596118927</v>
+        <v>3.49959659576416</v>
       </c>
       <c r="H406" t="n">
         <v>30400</v>
@@ -12201,7 +12201,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G408" t="n">
-        <v>3.66965270042419</v>
+        <v>3.66965293884277</v>
       </c>
       <c r="H408" t="n">
         <v>3600</v>
@@ -12230,7 +12230,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G409" t="n">
-        <v>3.59805035591125</v>
+        <v>3.5980498790741</v>
       </c>
       <c r="H409" t="n">
         <v>8400</v>
@@ -12288,7 +12288,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G411" t="n">
-        <v>3.59805035591125</v>
+        <v>3.5980498790741</v>
       </c>
       <c r="H411" t="n">
         <v>3600</v>
@@ -12317,7 +12317,7 @@
         <v>4</v>
       </c>
       <c r="G412" t="n">
-        <v>3.58014917373657</v>
+        <v>3.58014965057373</v>
       </c>
       <c r="H412" t="n">
         <v>6000</v>
@@ -12375,7 +12375,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G414" t="n">
-        <v>3.63385128974915</v>
+        <v>3.63385152816772</v>
       </c>
       <c r="H414" t="n">
         <v>2800</v>
@@ -12433,7 +12433,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G416" t="n">
-        <v>3.63385128974915</v>
+        <v>3.63385152816772</v>
       </c>
       <c r="H416" t="n">
         <v>7200</v>
@@ -12462,7 +12462,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G417" t="n">
-        <v>3.49064564704895</v>
+        <v>3.49064588546753</v>
       </c>
       <c r="H417" t="n">
         <v>10000</v>
@@ -12520,7 +12520,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G419" t="n">
-        <v>3.66965270042419</v>
+        <v>3.66965293884277</v>
       </c>
       <c r="H419" t="n">
         <v>2400</v>
@@ -12549,7 +12549,7 @@
         <v>4</v>
       </c>
       <c r="G420" t="n">
-        <v>3.58014917373657</v>
+        <v>3.58014965057373</v>
       </c>
       <c r="H420" t="n">
         <v>9200</v>
@@ -12578,7 +12578,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G421" t="n">
-        <v>3.66965270042419</v>
+        <v>3.66965293884277</v>
       </c>
       <c r="H421" t="n">
         <v>4800</v>
@@ -12607,7 +12607,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G422" t="n">
-        <v>3.66965270042419</v>
+        <v>3.66965293884277</v>
       </c>
       <c r="H422" t="n">
         <v>0</v>
@@ -12665,7 +12665,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G424" t="n">
-        <v>3.63385128974915</v>
+        <v>3.63385152816772</v>
       </c>
       <c r="H424" t="n">
         <v>13200</v>
@@ -12694,7 +12694,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G425" t="n">
-        <v>3.62490153312683</v>
+        <v>3.62490177154541</v>
       </c>
       <c r="H425" t="n">
         <v>4800</v>
@@ -12723,7 +12723,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G426" t="n">
-        <v>3.63385128974915</v>
+        <v>3.63385152816772</v>
       </c>
       <c r="H426" t="n">
         <v>25200</v>
@@ -12752,7 +12752,7 @@
         <v>4</v>
       </c>
       <c r="G427" t="n">
-        <v>3.58014917373657</v>
+        <v>3.58014965057373</v>
       </c>
       <c r="H427" t="n">
         <v>10400</v>
@@ -12781,7 +12781,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G428" t="n">
-        <v>3.63385128974915</v>
+        <v>3.63385152816772</v>
       </c>
       <c r="H428" t="n">
         <v>5200</v>
@@ -12839,7 +12839,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G430" t="n">
-        <v>3.69650435447693</v>
+        <v>3.69650411605835</v>
       </c>
       <c r="H430" t="n">
         <v>14800</v>
@@ -12868,7 +12868,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G431" t="n">
-        <v>3.75020670890808</v>
+        <v>3.75020623207092</v>
       </c>
       <c r="H431" t="n">
         <v>12000</v>
@@ -12897,7 +12897,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G432" t="n">
-        <v>3.78600788116455</v>
+        <v>3.78600740432739</v>
       </c>
       <c r="H432" t="n">
         <v>63600</v>
@@ -12955,7 +12955,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G434" t="n">
-        <v>4.09032106399536</v>
+        <v>4.09032011032104</v>
       </c>
       <c r="H434" t="n">
         <v>18800</v>
@@ -12984,7 +12984,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G435" t="n">
-        <v>4.14402294158936</v>
+        <v>4.1440224647522</v>
       </c>
       <c r="H435" t="n">
         <v>20800</v>
@@ -13013,7 +13013,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G436" t="n">
-        <v>4.09927129745483</v>
+        <v>4.09927082061768</v>
       </c>
       <c r="H436" t="n">
         <v>2400</v>
@@ -13042,7 +13042,7 @@
         <v>4.57999992370605</v>
       </c>
       <c r="G437" t="n">
-        <v>4.09927129745483</v>
+        <v>4.09927082061768</v>
       </c>
       <c r="H437" t="n">
         <v>2000</v>
@@ -13071,7 +13071,7 @@
         <v>4.75</v>
       </c>
       <c r="G438" t="n">
-        <v>4.25142765045166</v>
+        <v>4.2514271736145</v>
       </c>
       <c r="H438" t="n">
         <v>18000</v>
@@ -13100,7 +13100,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G439" t="n">
-        <v>4.11717176437378</v>
+        <v>4.11717224121094</v>
       </c>
       <c r="H439" t="n">
         <v>116400</v>
@@ -13129,7 +13129,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G440" t="n">
-        <v>4.37673330307007</v>
+        <v>4.37673234939575</v>
       </c>
       <c r="H440" t="n">
         <v>29200</v>
@@ -13187,7 +13187,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>4.29617881774902</v>
+        <v>4.29617977142334</v>
       </c>
       <c r="H442" t="n">
         <v>82000</v>
@@ -13216,7 +13216,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G443" t="n">
-        <v>4.23352718353271</v>
+        <v>4.2335262298584</v>
       </c>
       <c r="H443" t="n">
         <v>11200</v>
@@ -13245,7 +13245,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G444" t="n">
-        <v>4.14402294158936</v>
+        <v>4.1440224647522</v>
       </c>
       <c r="H444" t="n">
         <v>27600</v>
@@ -13274,7 +13274,7 @@
         <v>4.5</v>
       </c>
       <c r="G445" t="n">
-        <v>4.02766799926758</v>
+        <v>4.02766847610474</v>
       </c>
       <c r="H445" t="n">
         <v>32400</v>
@@ -13332,7 +13332,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G447" t="n">
-        <v>3.92026376724243</v>
+        <v>3.92026352882385</v>
       </c>
       <c r="H447" t="n">
         <v>14400</v>
@@ -13361,7 +13361,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G448" t="n">
-        <v>3.76810717582703</v>
+        <v>3.76810741424561</v>
       </c>
       <c r="H448" t="n">
         <v>15600</v>
@@ -13390,7 +13390,7 @@
         <v>4.21999979019165</v>
       </c>
       <c r="G449" t="n">
-        <v>3.7770574092865</v>
+        <v>3.77705717086792</v>
       </c>
       <c r="H449" t="n">
         <v>236000</v>
@@ -13419,7 +13419,7 @@
         <v>4.09999990463257</v>
       </c>
       <c r="G450" t="n">
-        <v>3.66965270042419</v>
+        <v>3.66965293884277</v>
       </c>
       <c r="H450" t="n">
         <v>57200</v>
@@ -13448,7 +13448,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G451" t="n">
-        <v>3.7054545879364</v>
+        <v>3.70545434951782</v>
       </c>
       <c r="H451" t="n">
         <v>36400</v>
@@ -13477,7 +13477,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G452" t="n">
-        <v>3.92921352386475</v>
+        <v>3.92921304702759</v>
       </c>
       <c r="H452" t="n">
         <v>3600</v>
@@ -13506,7 +13506,7 @@
         <v>4.48000001907349</v>
       </c>
       <c r="G453" t="n">
-        <v>4.00976753234863</v>
+        <v>4.00976705551147</v>
       </c>
       <c r="H453" t="n">
         <v>20800</v>
@@ -13535,7 +13535,7 @@
         <v>4.63000011444092</v>
       </c>
       <c r="G454" t="n">
-        <v>4.14402294158936</v>
+        <v>4.1440224647522</v>
       </c>
       <c r="H454" t="n">
         <v>8400</v>
@@ -13564,7 +13564,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G455" t="n">
-        <v>4.13507270812988</v>
+        <v>4.13507175445557</v>
       </c>
       <c r="H455" t="n">
         <v>1600</v>
@@ -13593,7 +13593,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G456" t="n">
-        <v>4.05451965332031</v>
+        <v>4.054518699646</v>
       </c>
       <c r="H456" t="n">
         <v>800</v>
@@ -13622,7 +13622,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G457" t="n">
-        <v>4.20667505264282</v>
+        <v>4.20667552947998</v>
       </c>
       <c r="H457" t="n">
         <v>13200</v>
@@ -13651,7 +13651,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G458" t="n">
-        <v>4.29617881774902</v>
+        <v>4.29617977142334</v>
       </c>
       <c r="H458" t="n">
         <v>10800</v>
@@ -13767,7 +13767,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G462" t="n">
-        <v>4.44833517074585</v>
+        <v>4.44833564758301</v>
       </c>
       <c r="H462" t="n">
         <v>58400</v>
@@ -13796,7 +13796,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G463" t="n">
-        <v>4.32303047180176</v>
+        <v>4.3230299949646</v>
       </c>
       <c r="H463" t="n">
         <v>47090</v>
@@ -13825,7 +13825,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G464" t="n">
-        <v>4.42148494720459</v>
+        <v>4.42148399353027</v>
       </c>
       <c r="H464" t="n">
         <v>31590</v>
@@ -13854,7 +13854,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G465" t="n">
-        <v>4.37673330307007</v>
+        <v>4.37673234939575</v>
       </c>
       <c r="H465" t="n">
         <v>29220</v>
@@ -13883,7 +13883,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G466" t="n">
-        <v>4.38568305969238</v>
+        <v>4.38568353652954</v>
       </c>
       <c r="H466" t="n">
         <v>9250</v>
@@ -13912,7 +13912,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G467" t="n">
-        <v>4.37673330307007</v>
+        <v>4.37673234939575</v>
       </c>
       <c r="H467" t="n">
         <v>41850</v>
@@ -13941,7 +13941,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G468" t="n">
-        <v>4.29617881774902</v>
+        <v>4.29617977142334</v>
       </c>
       <c r="H468" t="n">
         <v>39550</v>
@@ -13970,7 +13970,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G469" t="n">
-        <v>4.21562576293945</v>
+        <v>4.21562528610229</v>
       </c>
       <c r="H469" t="n">
         <v>14730</v>
@@ -13999,7 +13999,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G470" t="n">
-        <v>4.22457504272461</v>
+        <v>4.22457551956177</v>
       </c>
       <c r="H470" t="n">
         <v>24240</v>
@@ -14028,7 +14028,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G471" t="n">
-        <v>4.20667505264282</v>
+        <v>4.20667552947998</v>
       </c>
       <c r="H471" t="n">
         <v>24930</v>
@@ -14057,7 +14057,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G472" t="n">
-        <v>4.3891773223877</v>
+        <v>4.38917779922485</v>
       </c>
       <c r="H472" t="n">
         <v>31650</v>
@@ -14086,7 +14086,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G473" t="n">
-        <v>4.28880071640015</v>
+        <v>4.28880167007446</v>
       </c>
       <c r="H473" t="n">
         <v>68920</v>
@@ -14115,7 +14115,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G474" t="n">
-        <v>4.37092733383179</v>
+        <v>4.37092781066895</v>
       </c>
       <c r="H474" t="n">
         <v>14740</v>
@@ -14144,7 +14144,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G475" t="n">
-        <v>4.44392776489258</v>
+        <v>4.44392824172974</v>
       </c>
       <c r="H475" t="n">
         <v>50640</v>
@@ -14173,7 +14173,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G476" t="n">
-        <v>4.28880071640015</v>
+        <v>4.28880167007446</v>
       </c>
       <c r="H476" t="n">
         <v>5140</v>
@@ -14347,7 +14347,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G482" t="n">
-        <v>4.26142597198486</v>
+        <v>4.26142644882202</v>
       </c>
       <c r="H482" t="n">
         <v>850</v>
@@ -14376,7 +14376,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G483" t="n">
-        <v>4.28880071640015</v>
+        <v>4.28880167007446</v>
       </c>
       <c r="H483" t="n">
         <v>50</v>
@@ -14405,7 +14405,7 @@
         <v>4.61999988555908</v>
       </c>
       <c r="G484" t="n">
-        <v>4.21580028533936</v>
+        <v>4.2157998085022</v>
       </c>
       <c r="H484" t="n">
         <v>9650</v>
@@ -14434,7 +14434,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G485" t="n">
-        <v>4.28880071640015</v>
+        <v>4.28880167007446</v>
       </c>
       <c r="H485" t="n">
         <v>460</v>
@@ -14463,7 +14463,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G486" t="n">
-        <v>4.35267734527588</v>
+        <v>4.35267686843872</v>
       </c>
       <c r="H486" t="n">
         <v>60</v>
@@ -14492,7 +14492,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G487" t="n">
-        <v>4.36180305480957</v>
+        <v>4.36180257797241</v>
       </c>
       <c r="H487" t="n">
         <v>1620</v>
@@ -14521,7 +14521,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G488" t="n">
-        <v>4.36180305480957</v>
+        <v>4.36180257797241</v>
       </c>
       <c r="H488" t="n">
         <v>0</v>
@@ -14579,7 +14579,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G490" t="n">
-        <v>4.28880071640015</v>
+        <v>4.28880167007446</v>
       </c>
       <c r="H490" t="n">
         <v>2140</v>
@@ -14608,7 +14608,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G491" t="n">
-        <v>4.28880071640015</v>
+        <v>4.28880167007446</v>
       </c>
       <c r="H491" t="n">
         <v>5200</v>
@@ -14637,7 +14637,7 @@
         <v>4.75</v>
       </c>
       <c r="G492" t="n">
-        <v>4.33442687988281</v>
+        <v>4.33442735671997</v>
       </c>
       <c r="H492" t="n">
         <v>450</v>
@@ -14666,7 +14666,7 @@
         <v>4.75</v>
       </c>
       <c r="G493" t="n">
-        <v>4.33442687988281</v>
+        <v>4.33442735671997</v>
       </c>
       <c r="H493" t="n">
         <v>1550</v>
@@ -14724,7 +14724,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G495" t="n">
-        <v>4.38005256652832</v>
+        <v>4.38005304336548</v>
       </c>
       <c r="H495" t="n">
         <v>24640</v>
@@ -14782,7 +14782,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G497" t="n">
-        <v>4.38005256652832</v>
+        <v>4.38005304336548</v>
       </c>
       <c r="H497" t="n">
         <v>1050</v>
@@ -14811,7 +14811,7 @@
         <v>4.75</v>
       </c>
       <c r="G498" t="n">
-        <v>4.33442687988281</v>
+        <v>4.33442735671997</v>
       </c>
       <c r="H498" t="n">
         <v>450</v>
@@ -14840,7 +14840,7 @@
         <v>4.75</v>
       </c>
       <c r="G499" t="n">
-        <v>4.33442687988281</v>
+        <v>4.33442735671997</v>
       </c>
       <c r="H499" t="n">
         <v>0</v>
@@ -14869,7 +14869,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G500" t="n">
-        <v>4.38005256652832</v>
+        <v>4.38005304336548</v>
       </c>
       <c r="H500" t="n">
         <v>2200</v>
@@ -14898,7 +14898,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G501" t="n">
-        <v>4.37092733383179</v>
+        <v>4.37092781066895</v>
       </c>
       <c r="H501" t="n">
         <v>800</v>
@@ -14956,7 +14956,7 @@
         <v>4.75</v>
       </c>
       <c r="G503" t="n">
-        <v>4.33442687988281</v>
+        <v>4.33442735671997</v>
       </c>
       <c r="H503" t="n">
         <v>10950</v>
@@ -15072,7 +15072,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G507" t="n">
-        <v>4.38005256652832</v>
+        <v>4.38005304336548</v>
       </c>
       <c r="H507" t="n">
         <v>2850</v>
@@ -15101,7 +15101,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G508" t="n">
-        <v>4.38005256652832</v>
+        <v>4.38005304336548</v>
       </c>
       <c r="H508" t="n">
         <v>3390</v>
@@ -15130,7 +15130,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G509" t="n">
-        <v>4.31617641448975</v>
+        <v>4.3161768913269</v>
       </c>
       <c r="H509" t="n">
         <v>10880</v>
@@ -15188,7 +15188,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G511" t="n">
-        <v>4.31617641448975</v>
+        <v>4.3161768913269</v>
       </c>
       <c r="H511" t="n">
         <v>4040</v>
@@ -15275,7 +15275,7 @@
         <v>4.75</v>
       </c>
       <c r="G514" t="n">
-        <v>4.33442687988281</v>
+        <v>4.33442735671997</v>
       </c>
       <c r="H514" t="n">
         <v>2250</v>
@@ -15333,7 +15333,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G516" t="n">
-        <v>4.28880071640015</v>
+        <v>4.28880167007446</v>
       </c>
       <c r="H516" t="n">
         <v>34580</v>
@@ -15391,7 +15391,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G518" t="n">
-        <v>4.61730527877808</v>
+        <v>4.61730575561523</v>
       </c>
       <c r="H518" t="n">
         <v>125400</v>
@@ -15449,7 +15449,7 @@
         <v>5</v>
       </c>
       <c r="G520" t="n">
-        <v>4.56255435943604</v>
+        <v>4.56255483627319</v>
       </c>
       <c r="H520" t="n">
         <v>32720</v>
@@ -15507,7 +15507,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G522" t="n">
-        <v>4.48042917251587</v>
+        <v>4.48042821884155</v>
       </c>
       <c r="H522" t="n">
         <v>9600</v>
@@ -15536,7 +15536,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G523" t="n">
-        <v>4.61730527877808</v>
+        <v>4.61730575561523</v>
       </c>
       <c r="H523" t="n">
         <v>61320</v>
@@ -15652,7 +15652,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G527" t="n">
-        <v>4.90930891036987</v>
+        <v>4.90930938720703</v>
       </c>
       <c r="H527" t="n">
         <v>43970</v>
@@ -15681,7 +15681,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G528" t="n">
-        <v>4.90930891036987</v>
+        <v>4.90930938720703</v>
       </c>
       <c r="H528" t="n">
         <v>20060</v>
@@ -15739,7 +15739,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G530" t="n">
-        <v>4.96406030654907</v>
+        <v>4.96405935287476</v>
       </c>
       <c r="H530" t="n">
         <v>41950</v>
@@ -15768,7 +15768,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G531" t="n">
-        <v>4.94581031799316</v>
+        <v>4.94580936431885</v>
       </c>
       <c r="H531" t="n">
         <v>25300</v>
@@ -15826,7 +15826,7 @@
         <v>5.5</v>
       </c>
       <c r="G533" t="n">
-        <v>5.01881074905396</v>
+        <v>5.0188102722168</v>
       </c>
       <c r="H533" t="n">
         <v>25630</v>
@@ -15855,7 +15855,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G534" t="n">
-        <v>5.16481161117554</v>
+        <v>5.1648120880127</v>
       </c>
       <c r="H534" t="n">
         <v>35950</v>
@@ -15884,7 +15884,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G535" t="n">
-        <v>5.20131158828735</v>
+        <v>5.20131206512451</v>
       </c>
       <c r="H535" t="n">
         <v>24750</v>
@@ -15942,7 +15942,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G537" t="n">
-        <v>5.18306159973145</v>
+        <v>5.18306255340576</v>
       </c>
       <c r="H537" t="n">
         <v>35600</v>
@@ -15971,7 +15971,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G538" t="n">
-        <v>5.16481161117554</v>
+        <v>5.1648120880127</v>
       </c>
       <c r="H538" t="n">
         <v>20250</v>
@@ -16000,7 +16000,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G539" t="n">
-        <v>5.16481161117554</v>
+        <v>5.1648120880127</v>
       </c>
       <c r="H539" t="n">
         <v>12270</v>
@@ -16087,7 +16087,7 @@
         <v>5.5</v>
       </c>
       <c r="G542" t="n">
-        <v>5.01881074905396</v>
+        <v>5.0188102722168</v>
       </c>
       <c r="H542" t="n">
         <v>11030</v>
@@ -16145,7 +16145,7 @@
         <v>5.5</v>
       </c>
       <c r="G544" t="n">
-        <v>5.01881074905396</v>
+        <v>5.0188102722168</v>
       </c>
       <c r="H544" t="n">
         <v>14790</v>
@@ -16174,7 +16174,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G545" t="n">
-        <v>5.05531072616577</v>
+        <v>5.05531024932861</v>
       </c>
       <c r="H545" t="n">
         <v>9250</v>
@@ -16261,7 +16261,7 @@
         <v>5.69999980926514</v>
       </c>
       <c r="G548" t="n">
-        <v>5.20131158828735</v>
+        <v>5.20131206512451</v>
       </c>
       <c r="H548" t="n">
         <v>9250</v>
@@ -16290,7 +16290,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G549" t="n">
-        <v>5.16481161117554</v>
+        <v>5.1648120880127</v>
       </c>
       <c r="H549" t="n">
         <v>11650</v>
@@ -16319,7 +16319,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G550" t="n">
-        <v>5.12831163406372</v>
+        <v>5.12831211090088</v>
       </c>
       <c r="H550" t="n">
         <v>15220</v>
@@ -16348,7 +16348,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G551" t="n">
-        <v>5.18306159973145</v>
+        <v>5.18306255340576</v>
       </c>
       <c r="H551" t="n">
         <v>21670</v>
@@ -16377,7 +16377,7 @@
         <v>5.65999984741211</v>
       </c>
       <c r="G552" t="n">
-        <v>5.16481161117554</v>
+        <v>5.1648120880127</v>
       </c>
       <c r="H552" t="n">
         <v>34590</v>
@@ -16464,7 +16464,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G555" t="n">
-        <v>5.25606298446655</v>
+        <v>5.25606346130371</v>
       </c>
       <c r="H555" t="n">
         <v>29560</v>
@@ -16609,7 +16609,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G560" t="n">
-        <v>5.73056888580322</v>
+        <v>5.73056840896606</v>
       </c>
       <c r="H560" t="n">
         <v>16040</v>
@@ -16638,7 +16638,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G561" t="n">
-        <v>5.49331569671631</v>
+        <v>5.49331617355347</v>
       </c>
       <c r="H561" t="n">
         <v>18810</v>
@@ -16667,7 +16667,7 @@
         <v>6.09999990463257</v>
       </c>
       <c r="G562" t="n">
-        <v>5.56631708145142</v>
+        <v>5.56631660461426</v>
       </c>
       <c r="H562" t="n">
         <v>6700</v>
@@ -16870,7 +16870,7 @@
         <v>5.76000022888184</v>
       </c>
       <c r="G569" t="n">
-        <v>5.25606298446655</v>
+        <v>5.25606346130371</v>
       </c>
       <c r="H569" t="n">
         <v>23620</v>
@@ -17131,7 +17131,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G578" t="n">
-        <v>5.36556434631348</v>
+        <v>5.36556482315063</v>
       </c>
       <c r="H578" t="n">
         <v>30630</v>
@@ -17160,7 +17160,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G579" t="n">
-        <v>5.34731388092041</v>
+        <v>5.34731435775757</v>
       </c>
       <c r="H579" t="n">
         <v>17360</v>
@@ -17218,7 +17218,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G581" t="n">
-        <v>5.45681571960449</v>
+        <v>5.45681524276733</v>
       </c>
       <c r="H581" t="n">
         <v>6680</v>
@@ -17247,7 +17247,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G582" t="n">
-        <v>5.49331569671631</v>
+        <v>5.49331617355347</v>
       </c>
       <c r="H582" t="n">
         <v>11710</v>
@@ -17711,7 +17711,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G598" t="n">
-        <v>5.45681571960449</v>
+        <v>5.45681524276733</v>
       </c>
       <c r="H598" t="n">
         <v>7510</v>
@@ -17769,7 +17769,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G600" t="n">
-        <v>5.49331569671631</v>
+        <v>5.49331617355347</v>
       </c>
       <c r="H600" t="n">
         <v>6490</v>
@@ -17943,7 +17943,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G606" t="n">
-        <v>5.69406795501709</v>
+        <v>5.69406843185425</v>
       </c>
       <c r="H606" t="n">
         <v>42810</v>
@@ -17972,7 +17972,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G607" t="n">
-        <v>5.80356931686401</v>
+        <v>5.80357074737549</v>
       </c>
       <c r="H607" t="n">
         <v>21150</v>
@@ -18030,7 +18030,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G609" t="n">
-        <v>6.29632472991943</v>
+        <v>6.29632616043091</v>
       </c>
       <c r="H609" t="n">
         <v>137430</v>
@@ -18059,7 +18059,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G610" t="n">
-        <v>6.27807521820068</v>
+        <v>6.27807569503784</v>
       </c>
       <c r="H610" t="n">
         <v>23360</v>
@@ -18146,7 +18146,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G613" t="n">
-        <v>6.51532793045044</v>
+        <v>6.5153284072876</v>
       </c>
       <c r="H613" t="n">
         <v>31070</v>
@@ -18291,7 +18291,7 @@
         <v>7.34000015258789</v>
       </c>
       <c r="G618" t="n">
-        <v>6.69783020019531</v>
+        <v>6.69783115386963</v>
       </c>
       <c r="H618" t="n">
         <v>27550</v>
@@ -18320,7 +18320,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G619" t="n">
-        <v>7.00808382034302</v>
+        <v>7.00808429718018</v>
       </c>
       <c r="H619" t="n">
         <v>96620</v>
@@ -18349,7 +18349,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G620" t="n">
-        <v>6.916832447052</v>
+        <v>6.91683340072632</v>
       </c>
       <c r="H620" t="n">
         <v>191410</v>
@@ -18378,7 +18378,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G621" t="n">
-        <v>7.13583564758301</v>
+        <v>7.13583660125732</v>
       </c>
       <c r="H621" t="n">
         <v>180990</v>
@@ -18407,7 +18407,7 @@
         <v>8</v>
       </c>
       <c r="G622" t="n">
-        <v>7.30008792877197</v>
+        <v>7.30008745193481</v>
       </c>
       <c r="H622" t="n">
         <v>56300</v>
@@ -18465,7 +18465,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G624" t="n">
-        <v>7.62859153747559</v>
+        <v>7.62859106063843</v>
       </c>
       <c r="H624" t="n">
         <v>62840</v>
@@ -18494,7 +18494,7 @@
         <v>8.5</v>
       </c>
       <c r="G625" t="n">
-        <v>7.75634288787842</v>
+        <v>7.75634336471558</v>
       </c>
       <c r="H625" t="n">
         <v>102230</v>
@@ -18523,7 +18523,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G626" t="n">
-        <v>7.73809385299683</v>
+        <v>7.73809194564819</v>
       </c>
       <c r="H626" t="n">
         <v>60240</v>
@@ -18581,7 +18581,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G628" t="n">
-        <v>7.88409376144409</v>
+        <v>7.88409471511841</v>
       </c>
       <c r="H628" t="n">
         <v>62240</v>
@@ -18639,7 +18639,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G630" t="n">
-        <v>7.93884515762329</v>
+        <v>7.93884468078613</v>
       </c>
       <c r="H630" t="n">
         <v>111190</v>
@@ -18668,7 +18668,7 @@
         <v>8.5</v>
       </c>
       <c r="G631" t="n">
-        <v>7.75634288787842</v>
+        <v>7.75634336471558</v>
       </c>
       <c r="H631" t="n">
         <v>24340</v>
@@ -18697,7 +18697,7 @@
         <v>8.69999980926514</v>
       </c>
       <c r="G632" t="n">
-        <v>7.93884515762329</v>
+        <v>7.93884468078613</v>
       </c>
       <c r="H632" t="n">
         <v>34610</v>
@@ -18726,7 +18726,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G633" t="n">
-        <v>7.97534418106079</v>
+        <v>7.97534513473511</v>
       </c>
       <c r="H633" t="n">
         <v>75730</v>
@@ -18755,7 +18755,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G634" t="n">
-        <v>8.43160057067871</v>
+        <v>8.43159961700439</v>
       </c>
       <c r="H634" t="n">
         <v>84630</v>
@@ -18784,7 +18784,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G635" t="n">
-        <v>8.57760143280029</v>
+        <v>8.57760334014893</v>
       </c>
       <c r="H635" t="n">
         <v>55940</v>
@@ -18842,7 +18842,7 @@
         <v>9.46000003814697</v>
       </c>
       <c r="G637" t="n">
-        <v>8.63235282897949</v>
+        <v>8.63235378265381</v>
       </c>
       <c r="H637" t="n">
         <v>15840</v>
@@ -18900,7 +18900,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G639" t="n">
-        <v>8.26735019683838</v>
+        <v>8.26734924316406</v>
       </c>
       <c r="H639" t="n">
         <v>28920</v>
@@ -18929,7 +18929,7 @@
         <v>9.0600004196167</v>
       </c>
       <c r="G640" t="n">
-        <v>8.26735019683838</v>
+        <v>8.26734924316406</v>
       </c>
       <c r="H640" t="n">
         <v>19770</v>
@@ -19016,7 +19016,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G643" t="n">
-        <v>8.57760143280029</v>
+        <v>8.57760334014893</v>
       </c>
       <c r="H643" t="n">
         <v>18630</v>
@@ -19045,7 +19045,7 @@
         <v>9.23999977111816</v>
       </c>
       <c r="G644" t="n">
-        <v>8.43160057067871</v>
+        <v>8.43159961700439</v>
       </c>
       <c r="H644" t="n">
         <v>12650</v>
@@ -19074,7 +19074,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G645" t="n">
-        <v>8.37685012817383</v>
+        <v>8.37685108184814</v>
       </c>
       <c r="H645" t="n">
         <v>15640</v>
@@ -19103,7 +19103,7 @@
         <v>9.22000026702881</v>
       </c>
       <c r="G646" t="n">
-        <v>8.41335010528564</v>
+        <v>8.41335105895996</v>
       </c>
       <c r="H646" t="n">
         <v>33130</v>
@@ -19161,7 +19161,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G648" t="n">
-        <v>8.30384922027588</v>
+        <v>8.3038501739502</v>
       </c>
       <c r="H648" t="n">
         <v>36710</v>
@@ -19190,7 +19190,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G649" t="n">
-        <v>8.52285194396973</v>
+        <v>8.52285289764404</v>
       </c>
       <c r="H649" t="n">
         <v>12850</v>
@@ -19219,7 +19219,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G650" t="n">
-        <v>8.37685012817383</v>
+        <v>8.37685108184814</v>
       </c>
       <c r="H650" t="n">
         <v>10860</v>
@@ -19335,7 +19335,7 @@
         <v>9.72000026702881</v>
       </c>
       <c r="G654" t="n">
-        <v>8.86960601806641</v>
+        <v>8.86960697174072</v>
       </c>
       <c r="H654" t="n">
         <v>32680</v>
@@ -19393,7 +19393,7 @@
         <v>10.0500001907349</v>
       </c>
       <c r="G656" t="n">
-        <v>9.17073440551758</v>
+        <v>9.17073535919189</v>
       </c>
       <c r="H656" t="n">
         <v>68000</v>
@@ -19422,7 +19422,7 @@
         <v>10.25</v>
       </c>
       <c r="G657" t="n">
-        <v>9.35323715209961</v>
+        <v>9.35323810577393</v>
       </c>
       <c r="H657" t="n">
         <v>86790</v>
@@ -19451,7 +19451,7 @@
         <v>10.6999998092651</v>
       </c>
       <c r="G658" t="n">
-        <v>9.76386547088623</v>
+        <v>9.76386737823486</v>
       </c>
       <c r="H658" t="n">
         <v>70640</v>
@@ -19480,7 +19480,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G659" t="n">
-        <v>9.99199485778809</v>
+        <v>9.9919958114624</v>
       </c>
       <c r="H659" t="n">
         <v>95020</v>
@@ -19509,7 +19509,7 @@
         <v>10.5</v>
       </c>
       <c r="G660" t="n">
-        <v>9.58136463165283</v>
+        <v>9.58136367797852</v>
       </c>
       <c r="H660" t="n">
         <v>113360</v>
@@ -19538,7 +19538,7 @@
         <v>10.5</v>
       </c>
       <c r="G661" t="n">
-        <v>9.58136463165283</v>
+        <v>9.58136367797852</v>
       </c>
       <c r="H661" t="n">
         <v>25080</v>
@@ -19567,7 +19567,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G662" t="n">
-        <v>9.67261600494385</v>
+        <v>9.67261505126953</v>
       </c>
       <c r="H662" t="n">
         <v>63420</v>
@@ -19596,7 +19596,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G663" t="n">
-        <v>9.53573989868164</v>
+        <v>9.53573894500732</v>
       </c>
       <c r="H663" t="n">
         <v>27690</v>
@@ -19625,7 +19625,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G664" t="n">
-        <v>9.39886379241943</v>
+        <v>9.3988618850708</v>
       </c>
       <c r="H664" t="n">
         <v>37000</v>
@@ -19654,7 +19654,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G665" t="n">
-        <v>9.53573989868164</v>
+        <v>9.53573894500732</v>
       </c>
       <c r="H665" t="n">
         <v>29270</v>
@@ -19712,7 +19712,7 @@
         <v>10.75</v>
       </c>
       <c r="G667" t="n">
-        <v>9.80949211120605</v>
+        <v>9.80949306488037</v>
       </c>
       <c r="H667" t="n">
         <v>19160</v>
@@ -19741,7 +19741,7 @@
         <v>10.25</v>
       </c>
       <c r="G668" t="n">
-        <v>9.35323715209961</v>
+        <v>9.35323810577393</v>
       </c>
       <c r="H668" t="n">
         <v>44150</v>
@@ -19770,7 +19770,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G669" t="n">
-        <v>9.53573989868164</v>
+        <v>9.53573894500732</v>
       </c>
       <c r="H669" t="n">
         <v>53000</v>
@@ -19799,7 +19799,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G670" t="n">
-        <v>9.39886379241943</v>
+        <v>9.3988618850708</v>
       </c>
       <c r="H670" t="n">
         <v>8710</v>
@@ -19828,7 +19828,7 @@
         <v>10.3000001907349</v>
       </c>
       <c r="G671" t="n">
-        <v>9.39886379241943</v>
+        <v>9.3988618850708</v>
       </c>
       <c r="H671" t="n">
         <v>18370</v>
@@ -19857,7 +19857,7 @@
         <v>10</v>
       </c>
       <c r="G672" t="n">
-        <v>9.12510871887207</v>
+        <v>9.12510967254639</v>
       </c>
       <c r="H672" t="n">
         <v>49670</v>
@@ -19915,7 +19915,7 @@
         <v>10.1999998092651</v>
       </c>
       <c r="G674" t="n">
-        <v>9.30761241912842</v>
+        <v>9.3076114654541</v>
       </c>
       <c r="H674" t="n">
         <v>24650</v>
@@ -19944,7 +19944,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G675" t="n">
-        <v>9.49011421203613</v>
+        <v>9.49011325836182</v>
       </c>
       <c r="H675" t="n">
         <v>65020</v>
@@ -19973,7 +19973,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G676" t="n">
-        <v>9.67261600494385</v>
+        <v>9.67261505126953</v>
       </c>
       <c r="H676" t="n">
         <v>54230</v>
@@ -20002,7 +20002,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G677" t="n">
-        <v>9.94637012481689</v>
+        <v>9.94636821746826</v>
       </c>
       <c r="H677" t="n">
         <v>77360</v>
@@ -20031,7 +20031,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G678" t="n">
-        <v>9.99199485778809</v>
+        <v>9.9919958114624</v>
       </c>
       <c r="H678" t="n">
         <v>19160</v>
@@ -20060,7 +20060,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G679" t="n">
-        <v>9.99199485778809</v>
+        <v>9.9919958114624</v>
       </c>
       <c r="H679" t="n">
         <v>67650</v>
@@ -20089,7 +20089,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G680" t="n">
-        <v>9.99199485778809</v>
+        <v>9.9919958114624</v>
       </c>
       <c r="H680" t="n">
         <v>15440</v>
@@ -20118,7 +20118,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G681" t="n">
-        <v>9.99199485778809</v>
+        <v>9.9919958114624</v>
       </c>
       <c r="H681" t="n">
         <v>10490</v>
@@ -20147,7 +20147,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G682" t="n">
-        <v>9.99199485778809</v>
+        <v>9.9919958114624</v>
       </c>
       <c r="H682" t="n">
         <v>16670</v>
@@ -20176,7 +20176,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G683" t="n">
-        <v>9.67261600494385</v>
+        <v>9.67261505126953</v>
       </c>
       <c r="H683" t="n">
         <v>35330</v>
@@ -20205,7 +20205,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G684" t="n">
-        <v>9.67261600494385</v>
+        <v>9.67261505126953</v>
       </c>
       <c r="H684" t="n">
         <v>10770</v>
@@ -20234,7 +20234,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G685" t="n">
-        <v>9.67261600494385</v>
+        <v>9.67261505126953</v>
       </c>
       <c r="H685" t="n">
         <v>49820</v>
@@ -20263,7 +20263,7 @@
         <v>10.75</v>
       </c>
       <c r="G686" t="n">
-        <v>9.80949211120605</v>
+        <v>9.80949306488037</v>
       </c>
       <c r="H686" t="n">
         <v>46500</v>
@@ -20292,7 +20292,7 @@
         <v>10.6499996185303</v>
       </c>
       <c r="G687" t="n">
-        <v>9.71824073791504</v>
+        <v>9.71824169158936</v>
       </c>
       <c r="H687" t="n">
         <v>11900</v>
@@ -20321,7 +20321,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G688" t="n">
-        <v>8.90610694885254</v>
+        <v>8.90610790252686</v>
       </c>
       <c r="H688" t="n">
         <v>56290</v>
@@ -20350,7 +20350,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G689" t="n">
-        <v>9.26198482513428</v>
+        <v>9.26198673248291</v>
       </c>
       <c r="H689" t="n">
         <v>49040</v>
@@ -20466,7 +20466,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G693" t="n">
-        <v>8.77835464477539</v>
+        <v>8.77835559844971</v>
       </c>
       <c r="H693" t="n">
         <v>65620</v>
@@ -20495,7 +20495,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G694" t="n">
-        <v>8.97910785675049</v>
+        <v>8.97910690307617</v>
       </c>
       <c r="H694" t="n">
         <v>18270</v>
@@ -20611,7 +20611,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G698" t="n">
-        <v>7.61034154891968</v>
+        <v>7.61034202575684</v>
       </c>
       <c r="H698" t="n">
         <v>97230</v>
@@ -20669,7 +20669,7 @@
         <v>8</v>
       </c>
       <c r="G700" t="n">
-        <v>7.30008792877197</v>
+        <v>7.30008745193481</v>
       </c>
       <c r="H700" t="n">
         <v>37410</v>
@@ -20698,7 +20698,7 @@
         <v>7.5</v>
       </c>
       <c r="G701" t="n">
-        <v>6.84383296966553</v>
+        <v>6.84383249282837</v>
       </c>
       <c r="H701" t="n">
         <v>39240</v>
@@ -20727,7 +20727,7 @@
         <v>7.96000003814697</v>
       </c>
       <c r="G702" t="n">
-        <v>7.26358699798584</v>
+        <v>7.263587474823</v>
       </c>
       <c r="H702" t="n">
         <v>33850</v>
@@ -20756,7 +20756,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G703" t="n">
-        <v>7.02633428573608</v>
+        <v>7.02633476257324</v>
       </c>
       <c r="H703" t="n">
         <v>17860</v>
@@ -20785,7 +20785,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G704" t="n">
-        <v>7.02633428573608</v>
+        <v>7.02633476257324</v>
       </c>
       <c r="H704" t="n">
         <v>4410</v>
@@ -20814,7 +20814,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G705" t="n">
-        <v>6.916832447052</v>
+        <v>6.91683340072632</v>
       </c>
       <c r="H705" t="n">
         <v>3640</v>
@@ -20843,7 +20843,7 @@
         <v>7.69999980926514</v>
       </c>
       <c r="G706" t="n">
-        <v>7.02633428573608</v>
+        <v>7.02633476257324</v>
       </c>
       <c r="H706" t="n">
         <v>4990</v>
@@ -20901,7 +20901,7 @@
         <v>8.23999977111816</v>
       </c>
       <c r="G708" t="n">
-        <v>7.51909017562866</v>
+        <v>7.51909065246582</v>
       </c>
       <c r="H708" t="n">
         <v>26820</v>
@@ -20930,7 +20930,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G709" t="n">
-        <v>7.62859153747559</v>
+        <v>7.62859106063843</v>
       </c>
       <c r="H709" t="n">
         <v>49380</v>
@@ -20988,7 +20988,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G711" t="n">
-        <v>7.64684152603149</v>
+        <v>7.64684200286865</v>
       </c>
       <c r="H711" t="n">
         <v>22410</v>
@@ -21046,7 +21046,7 @@
         <v>8.5</v>
       </c>
       <c r="G713" t="n">
-        <v>7.75634288787842</v>
+        <v>7.75634336471558</v>
       </c>
       <c r="H713" t="n">
         <v>8220</v>
@@ -21075,7 +21075,7 @@
         <v>8.64000034332275</v>
       </c>
       <c r="G714" t="n">
-        <v>7.88409376144409</v>
+        <v>7.88409471511841</v>
       </c>
       <c r="H714" t="n">
         <v>21440</v>
@@ -21133,7 +21133,7 @@
         <v>9.11999988555908</v>
       </c>
       <c r="G716" t="n">
-        <v>8.32210063934326</v>
+        <v>8.32209968566895</v>
       </c>
       <c r="H716" t="n">
         <v>21790</v>
@@ -21162,7 +21162,7 @@
         <v>9.10000038146973</v>
       </c>
       <c r="G717" t="n">
-        <v>8.30384922027588</v>
+        <v>8.3038501739502</v>
       </c>
       <c r="H717" t="n">
         <v>7250</v>
@@ -21220,7 +21220,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G719" t="n">
-        <v>8.76010513305664</v>
+        <v>8.76010608673096</v>
       </c>
       <c r="H719" t="n">
         <v>30560</v>
@@ -21278,7 +21278,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G721" t="n">
-        <v>9.05210971832275</v>
+        <v>9.05210876464844</v>
       </c>
       <c r="H721" t="n">
         <v>33160</v>
@@ -21365,7 +21365,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>9.05210971832275</v>
+        <v>9.05210876464844</v>
       </c>
       <c r="H724" t="n">
         <v>15780</v>
@@ -21481,7 +21481,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G728" t="n">
-        <v>9.53573989868164</v>
+        <v>9.53573894500732</v>
       </c>
       <c r="H728" t="n">
         <v>20930</v>
@@ -21510,7 +21510,7 @@
         <v>10.4499998092651</v>
       </c>
       <c r="G729" t="n">
-        <v>9.53573989868164</v>
+        <v>9.53573894500732</v>
       </c>
       <c r="H729" t="n">
         <v>16620</v>
@@ -21539,7 +21539,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G730" t="n">
-        <v>9.49011421203613</v>
+        <v>9.49011325836182</v>
       </c>
       <c r="H730" t="n">
         <v>12710</v>
@@ -21568,7 +21568,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>9.67261600494385</v>
+        <v>9.67261505126953</v>
       </c>
       <c r="H731" t="n">
         <v>42830</v>
@@ -21597,7 +21597,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G732" t="n">
-        <v>9.67261600494385</v>
+        <v>9.67261505126953</v>
       </c>
       <c r="H732" t="n">
         <v>33020</v>
@@ -21626,7 +21626,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G733" t="n">
-        <v>10.2201232910156</v>
+        <v>10.2201223373413</v>
       </c>
       <c r="H733" t="n">
         <v>77220</v>
@@ -21655,7 +21655,7 @@
         <v>11.3999996185303</v>
       </c>
       <c r="G734" t="n">
-        <v>10.4026231765747</v>
+        <v>10.402624130249</v>
       </c>
       <c r="H734" t="n">
         <v>64310</v>
@@ -21684,7 +21684,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G735" t="n">
-        <v>10.3563919067383</v>
+        <v>10.356390953064</v>
       </c>
       <c r="H735" t="n">
         <v>21950</v>
@@ -21800,7 +21800,7 @@
         <v>11</v>
       </c>
       <c r="G739" t="n">
-        <v>10.1714563369751</v>
+        <v>10.1714553833008</v>
       </c>
       <c r="H739" t="n">
         <v>10800</v>
@@ -21829,7 +21829,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G740" t="n">
-        <v>10.4950923919678</v>
+        <v>10.4950933456421</v>
       </c>
       <c r="H740" t="n">
         <v>13150</v>
@@ -21916,7 +21916,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G743" t="n">
-        <v>10.032753944397</v>
+        <v>10.0327548980713</v>
       </c>
       <c r="H743" t="n">
         <v>14440</v>
@@ -21974,7 +21974,7 @@
         <v>10.8500003814697</v>
       </c>
       <c r="G745" t="n">
-        <v>10.032753944397</v>
+        <v>10.0327548980713</v>
       </c>
       <c r="H745" t="n">
         <v>19800</v>
@@ -22061,7 +22061,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G748" t="n">
-        <v>9.80158519744873</v>
+        <v>9.80158424377441</v>
       </c>
       <c r="H748" t="n">
         <v>18650</v>
@@ -22119,7 +22119,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G750" t="n">
-        <v>9.80158519744873</v>
+        <v>9.80158424377441</v>
       </c>
       <c r="H750" t="n">
         <v>12500</v>
@@ -22148,7 +22148,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G751" t="n">
-        <v>9.80158519744873</v>
+        <v>9.80158424377441</v>
       </c>
       <c r="H751" t="n">
         <v>12920</v>
@@ -22177,7 +22177,7 @@
         <v>10.3999996185303</v>
       </c>
       <c r="G752" t="n">
-        <v>9.61664962768555</v>
+        <v>9.61664772033691</v>
       </c>
       <c r="H752" t="n">
         <v>9760</v>
@@ -22206,7 +22206,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G753" t="n">
-        <v>9.80158519744873</v>
+        <v>9.80158424377441</v>
       </c>
       <c r="H753" t="n">
         <v>19270</v>
@@ -22264,7 +22264,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G755" t="n">
-        <v>10.0789861679077</v>
+        <v>10.078987121582</v>
       </c>
       <c r="H755" t="n">
         <v>14220</v>
@@ -22293,7 +22293,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G756" t="n">
-        <v>10.3563919067383</v>
+        <v>10.356390953064</v>
       </c>
       <c r="H756" t="n">
         <v>20470</v>
@@ -22351,7 +22351,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G758" t="n">
-        <v>10.4488592147827</v>
+        <v>10.4488582611084</v>
       </c>
       <c r="H758" t="n">
         <v>15180</v>
@@ -22380,7 +22380,7 @@
         <v>11.3500003814697</v>
       </c>
       <c r="G759" t="n">
-        <v>10.4950923919678</v>
+        <v>10.4950933456421</v>
       </c>
       <c r="H759" t="n">
         <v>17310</v>
@@ -22409,7 +22409,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G760" t="n">
-        <v>10.4488592147827</v>
+        <v>10.4488582611084</v>
       </c>
       <c r="H760" t="n">
         <v>19520</v>
@@ -22438,7 +22438,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G761" t="n">
-        <v>10.3563919067383</v>
+        <v>10.356390953064</v>
       </c>
       <c r="H761" t="n">
         <v>13730</v>
@@ -22467,7 +22467,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G762" t="n">
-        <v>10.3563919067383</v>
+        <v>10.356390953064</v>
       </c>
       <c r="H762" t="n">
         <v>6510</v>
@@ -22496,7 +22496,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G763" t="n">
-        <v>10.4488592147827</v>
+        <v>10.4488582611084</v>
       </c>
       <c r="H763" t="n">
         <v>11290</v>
@@ -22525,7 +22525,7 @@
         <v>11</v>
       </c>
       <c r="G764" t="n">
-        <v>10.1714563369751</v>
+        <v>10.1714553833008</v>
       </c>
       <c r="H764" t="n">
         <v>11870</v>
@@ -22554,7 +22554,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G765" t="n">
-        <v>10.0789861679077</v>
+        <v>10.078987121582</v>
       </c>
       <c r="H765" t="n">
         <v>5710</v>
@@ -22670,7 +22670,7 @@
         <v>12.5500001907349</v>
       </c>
       <c r="G769" t="n">
-        <v>11.6047067642212</v>
+        <v>11.6047048568726</v>
       </c>
       <c r="H769" t="n">
         <v>84360</v>
@@ -22728,7 +22728,7 @@
         <v>13.8000001907349</v>
       </c>
       <c r="G771" t="n">
-        <v>12.760552406311</v>
+        <v>12.7605533599854</v>
       </c>
       <c r="H771" t="n">
         <v>775590</v>
@@ -22757,7 +22757,7 @@
         <v>13</v>
       </c>
       <c r="G772" t="n">
-        <v>12.0208101272583</v>
+        <v>12.0208110809326</v>
       </c>
       <c r="H772" t="n">
         <v>77200</v>
@@ -22786,7 +22786,7 @@
         <v>13.3000001907349</v>
       </c>
       <c r="G773" t="n">
-        <v>12.2982149124146</v>
+        <v>12.2982158660889</v>
       </c>
       <c r="H773" t="n">
         <v>15670</v>
@@ -22844,7 +22844,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G775" t="n">
-        <v>12.1132783889771</v>
+        <v>12.1132802963257</v>
       </c>
       <c r="H775" t="n">
         <v>46310</v>
@@ -22873,7 +22873,7 @@
         <v>13</v>
       </c>
       <c r="G776" t="n">
-        <v>12.0208101272583</v>
+        <v>12.0208110809326</v>
       </c>
       <c r="H776" t="n">
         <v>24820</v>
@@ -22902,7 +22902,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G777" t="n">
-        <v>12.1595134735107</v>
+        <v>12.1595125198364</v>
       </c>
       <c r="H777" t="n">
         <v>41060</v>
@@ -23018,7 +23018,7 @@
         <v>13</v>
       </c>
       <c r="G781" t="n">
-        <v>12.0208101272583</v>
+        <v>12.0208110809326</v>
       </c>
       <c r="H781" t="n">
         <v>26420</v>
@@ -23163,7 +23163,7 @@
         <v>12.75</v>
       </c>
       <c r="G786" t="n">
-        <v>11.7896423339844</v>
+        <v>11.7896394729614</v>
       </c>
       <c r="H786" t="n">
         <v>23160</v>
@@ -23192,7 +23192,7 @@
         <v>12.75</v>
       </c>
       <c r="G787" t="n">
-        <v>11.7896423339844</v>
+        <v>11.7896394729614</v>
       </c>
       <c r="H787" t="n">
         <v>44680</v>
@@ -23250,7 +23250,7 @@
         <v>13</v>
       </c>
       <c r="G789" t="n">
-        <v>12.0208101272583</v>
+        <v>12.0208110809326</v>
       </c>
       <c r="H789" t="n">
         <v>50180</v>
@@ -23308,7 +23308,7 @@
         <v>12.6999998092651</v>
       </c>
       <c r="G791" t="n">
-        <v>11.7434072494507</v>
+        <v>11.743408203125</v>
       </c>
       <c r="H791" t="n">
         <v>14180</v>
@@ -23366,7 +23366,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G793" t="n">
-        <v>11.5122385025024</v>
+        <v>11.5122375488281</v>
       </c>
       <c r="H793" t="n">
         <v>31350</v>
@@ -23453,7 +23453,7 @@
         <v>12.75</v>
       </c>
       <c r="G796" t="n">
-        <v>11.7896423339844</v>
+        <v>11.7896394729614</v>
       </c>
       <c r="H796" t="n">
         <v>28200</v>
@@ -23482,7 +23482,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G797" t="n">
-        <v>11.6971740722656</v>
+        <v>11.6971731185913</v>
       </c>
       <c r="H797" t="n">
         <v>4440</v>
@@ -23511,7 +23511,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G798" t="n">
-        <v>11.4197702407837</v>
+        <v>11.4197692871094</v>
       </c>
       <c r="H798" t="n">
         <v>21780</v>
@@ -23569,7 +23569,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G800" t="n">
-        <v>11.3735370635986</v>
+        <v>11.3735380172729</v>
       </c>
       <c r="H800" t="n">
         <v>8530</v>
@@ -23598,7 +23598,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G801" t="n">
-        <v>11.1423683166504</v>
+        <v>11.1423664093018</v>
       </c>
       <c r="H801" t="n">
         <v>15210</v>
@@ -23627,7 +23627,7 @@
         <v>11.6999998092651</v>
       </c>
       <c r="G802" t="n">
-        <v>10.8187303543091</v>
+        <v>10.8187294006348</v>
       </c>
       <c r="H802" t="n">
         <v>34950</v>
@@ -23656,7 +23656,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G803" t="n">
-        <v>11.1423683166504</v>
+        <v>11.1423664093018</v>
       </c>
       <c r="H803" t="n">
         <v>60080</v>
@@ -23772,7 +23772,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G807" t="n">
-        <v>11.2810678482056</v>
+        <v>11.2810688018799</v>
       </c>
       <c r="H807" t="n">
         <v>7090</v>
@@ -23801,7 +23801,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G808" t="n">
-        <v>11.3735370635986</v>
+        <v>11.3735380172729</v>
       </c>
       <c r="H808" t="n">
         <v>2960</v>
@@ -23830,7 +23830,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G809" t="n">
-        <v>11.2810678482056</v>
+        <v>11.2810688018799</v>
       </c>
       <c r="H809" t="n">
         <v>4150</v>
@@ -23859,7 +23859,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G810" t="n">
-        <v>11.4197702407837</v>
+        <v>11.4197692871094</v>
       </c>
       <c r="H810" t="n">
         <v>29160</v>
@@ -23888,7 +23888,7 @@
         <v>12.5</v>
       </c>
       <c r="G811" t="n">
-        <v>11.5584726333618</v>
+        <v>11.5584735870361</v>
       </c>
       <c r="H811" t="n">
         <v>22990</v>
@@ -23946,7 +23946,7 @@
         <v>12.5</v>
       </c>
       <c r="G813" t="n">
-        <v>11.5584726333618</v>
+        <v>11.5584735870361</v>
       </c>
       <c r="H813" t="n">
         <v>9780</v>
@@ -24033,7 +24033,7 @@
         <v>12.75</v>
       </c>
       <c r="G816" t="n">
-        <v>11.7896423339844</v>
+        <v>11.7896394729614</v>
       </c>
       <c r="H816" t="n">
         <v>2510</v>
@@ -24120,7 +24120,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G819" t="n">
-        <v>11.6971740722656</v>
+        <v>11.6971731185913</v>
       </c>
       <c r="H819" t="n">
         <v>3740</v>
@@ -24178,7 +24178,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G821" t="n">
-        <v>11.2810678482056</v>
+        <v>11.2810688018799</v>
       </c>
       <c r="H821" t="n">
         <v>17320</v>
@@ -24236,7 +24236,7 @@
         <v>12.1999998092651</v>
       </c>
       <c r="G823" t="n">
-        <v>11.2810678482056</v>
+        <v>11.2810688018799</v>
       </c>
       <c r="H823" t="n">
         <v>22360</v>
@@ -24352,7 +24352,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>12.3444499969482</v>
+        <v>12.3444480895996</v>
       </c>
       <c r="H827" t="n">
         <v>26740</v>
@@ -24381,7 +24381,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G828" t="n">
-        <v>12.8992557525635</v>
+        <v>12.8992547988892</v>
       </c>
       <c r="H828" t="n">
         <v>160820</v>
@@ -24410,7 +24410,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G829" t="n">
-        <v>13.130425453186</v>
+        <v>13.1304244995117</v>
       </c>
       <c r="H829" t="n">
         <v>64900</v>
@@ -24439,7 +24439,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G830" t="n">
-        <v>13.4540615081787</v>
+        <v>13.454062461853</v>
       </c>
       <c r="H830" t="n">
         <v>46270</v>
@@ -24497,7 +24497,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G832" t="n">
-        <v>14.1938037872314</v>
+        <v>14.1938047409058</v>
       </c>
       <c r="H832" t="n">
         <v>45500</v>
@@ -24526,7 +24526,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G833" t="n">
-        <v>14.1938037872314</v>
+        <v>14.1938047409058</v>
       </c>
       <c r="H833" t="n">
         <v>64260</v>
@@ -24584,7 +24584,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G835" t="n">
-        <v>15.3496513366699</v>
+        <v>15.3496522903442</v>
       </c>
       <c r="H835" t="n">
         <v>255790</v>
@@ -24613,7 +24613,7 @@
         <v>16.25</v>
       </c>
       <c r="G836" t="n">
-        <v>15.0260133743286</v>
+        <v>15.0260124206543</v>
       </c>
       <c r="H836" t="n">
         <v>116230</v>
@@ -24642,7 +24642,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G837" t="n">
-        <v>16.3667984008789</v>
+        <v>16.3667964935303</v>
       </c>
       <c r="H837" t="n">
         <v>162970</v>
@@ -24671,7 +24671,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G838" t="n">
-        <v>16.459264755249</v>
+        <v>16.4592628479004</v>
       </c>
       <c r="H838" t="n">
         <v>124100</v>
@@ -24845,7 +24845,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G844" t="n">
-        <v>15.3496513366699</v>
+        <v>15.3496522903442</v>
       </c>
       <c r="H844" t="n">
         <v>34830</v>
@@ -25019,7 +25019,7 @@
         <v>16.8999996185303</v>
       </c>
       <c r="G850" t="n">
-        <v>15.6270523071289</v>
+        <v>15.6270542144775</v>
       </c>
       <c r="H850" t="n">
         <v>200800</v>
@@ -25048,7 +25048,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G851" t="n">
-        <v>15.9969244003296</v>
+        <v>15.9969253540039</v>
       </c>
       <c r="H851" t="n">
         <v>44850</v>
@@ -25077,7 +25077,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G852" t="n">
-        <v>15.9969244003296</v>
+        <v>15.9969253540039</v>
       </c>
       <c r="H852" t="n">
         <v>16050</v>
@@ -25193,7 +25193,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>14.9797811508179</v>
+        <v>14.9797821044922</v>
       </c>
       <c r="H856" t="n">
         <v>43760</v>
@@ -25251,7 +25251,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G858" t="n">
-        <v>14.424973487854</v>
+        <v>14.4249744415283</v>
       </c>
       <c r="H858" t="n">
         <v>37180</v>
@@ -25309,7 +25309,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G860" t="n">
-        <v>13.5465278625488</v>
+        <v>13.5465288162231</v>
       </c>
       <c r="H860" t="n">
         <v>64290</v>
@@ -25367,7 +25367,7 @@
         <v>13.4499998092651</v>
       </c>
       <c r="G862" t="n">
-        <v>12.4369163513184</v>
+        <v>12.436915397644</v>
       </c>
       <c r="H862" t="n">
         <v>44500</v>
@@ -25396,7 +25396,7 @@
         <v>14.1000003814697</v>
       </c>
       <c r="G863" t="n">
-        <v>13.0379571914673</v>
+        <v>13.037956237793</v>
       </c>
       <c r="H863" t="n">
         <v>44090</v>
@@ -25425,7 +25425,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G864" t="n">
-        <v>13.130425453186</v>
+        <v>13.1304244995117</v>
       </c>
       <c r="H864" t="n">
         <v>23780</v>
@@ -25512,7 +25512,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G867" t="n">
-        <v>15.3496513366699</v>
+        <v>15.3496522903442</v>
       </c>
       <c r="H867" t="n">
         <v>95890</v>
@@ -25541,7 +25541,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G868" t="n">
-        <v>15.6732912063599</v>
+        <v>15.6732902526855</v>
       </c>
       <c r="H868" t="n">
         <v>55200</v>
@@ -25599,7 +25599,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G870" t="n">
-        <v>15.3496513366699</v>
+        <v>15.3496522903442</v>
       </c>
       <c r="H870" t="n">
         <v>41320</v>
@@ -25628,7 +25628,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G871" t="n">
-        <v>14.9797811508179</v>
+        <v>14.9797821044922</v>
       </c>
       <c r="H871" t="n">
         <v>109640</v>
@@ -25657,7 +25657,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G872" t="n">
-        <v>15.0722465515137</v>
+        <v>15.072247505188</v>
       </c>
       <c r="H872" t="n">
         <v>19800</v>
@@ -25744,7 +25744,7 @@
         <v>16</v>
       </c>
       <c r="G875" t="n">
-        <v>14.7948446273804</v>
+        <v>14.7948455810547</v>
       </c>
       <c r="H875" t="n">
         <v>58670</v>
@@ -25773,7 +25773,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G876" t="n">
-        <v>14.1475687026978</v>
+        <v>14.1475696563721</v>
       </c>
       <c r="H876" t="n">
         <v>139850</v>
@@ -25860,7 +25860,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G879" t="n">
-        <v>14.7023754119873</v>
+        <v>14.7023763656616</v>
       </c>
       <c r="H879" t="n">
         <v>26030</v>
@@ -25918,7 +25918,7 @@
         <v>15.25</v>
       </c>
       <c r="G881" t="n">
-        <v>14.101336479187</v>
+        <v>14.1013374328613</v>
       </c>
       <c r="H881" t="n">
         <v>34060</v>
@@ -25947,7 +25947,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G882" t="n">
-        <v>14.1938037872314</v>
+        <v>14.1938047409058</v>
       </c>
       <c r="H882" t="n">
         <v>10030</v>
@@ -25976,7 +25976,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G883" t="n">
-        <v>14.0088682174683</v>
+        <v>14.0088672637939</v>
       </c>
       <c r="H883" t="n">
         <v>7410</v>
@@ -26034,7 +26034,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>13.5465278625488</v>
+        <v>13.5465288162231</v>
       </c>
       <c r="H885" t="n">
         <v>30740</v>
@@ -26063,7 +26063,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G886" t="n">
-        <v>13.8239336013794</v>
+        <v>13.8239326477051</v>
       </c>
       <c r="H886" t="n">
         <v>12290</v>
@@ -26092,7 +26092,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G887" t="n">
-        <v>13.4540615081787</v>
+        <v>13.454062461853</v>
       </c>
       <c r="H887" t="n">
         <v>24830</v>
@@ -26179,7 +26179,7 @@
         <v>14.75</v>
       </c>
       <c r="G890" t="n">
-        <v>13.6389980316162</v>
+        <v>13.6389970779419</v>
       </c>
       <c r="H890" t="n">
         <v>17940</v>
@@ -26237,7 +26237,7 @@
         <v>14.6000003814697</v>
       </c>
       <c r="G892" t="n">
-        <v>13.5002956390381</v>
+        <v>13.5002965927124</v>
       </c>
       <c r="H892" t="n">
         <v>21530</v>
@@ -26266,7 +26266,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G893" t="n">
-        <v>13.6852321624756</v>
+        <v>13.6852312088013</v>
       </c>
       <c r="H893" t="n">
         <v>17190</v>
@@ -26324,7 +26324,7 @@
         <v>16</v>
       </c>
       <c r="G895" t="n">
-        <v>14.7948446273804</v>
+        <v>14.7948455810547</v>
       </c>
       <c r="H895" t="n">
         <v>22150</v>
@@ -26411,7 +26411,7 @@
         <v>16</v>
       </c>
       <c r="G898" t="n">
-        <v>14.7948446273804</v>
+        <v>14.7948455810547</v>
       </c>
       <c r="H898" t="n">
         <v>67620</v>
@@ -26440,7 +26440,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G899" t="n">
-        <v>15.6732912063599</v>
+        <v>15.6732902526855</v>
       </c>
       <c r="H899" t="n">
         <v>45260</v>
@@ -26469,7 +26469,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G900" t="n">
-        <v>14.8873119354248</v>
+        <v>14.8873128890991</v>
       </c>
       <c r="H900" t="n">
         <v>36170</v>
@@ -26527,7 +26527,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G902" t="n">
-        <v>15.0722465515137</v>
+        <v>15.072247505188</v>
       </c>
       <c r="H902" t="n">
         <v>35920</v>
@@ -26614,7 +26614,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G905" t="n">
-        <v>15.0722465515137</v>
+        <v>15.072247505188</v>
       </c>
       <c r="H905" t="n">
         <v>15930</v>
@@ -26643,7 +26643,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G906" t="n">
-        <v>15.5345859527588</v>
+        <v>15.5345869064331</v>
       </c>
       <c r="H906" t="n">
         <v>20450</v>
@@ -26672,7 +26672,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G907" t="n">
-        <v>15.3496513366699</v>
+        <v>15.3496522903442</v>
       </c>
       <c r="H907" t="n">
         <v>13600</v>
@@ -26759,7 +26759,7 @@
         <v>16</v>
       </c>
       <c r="G910" t="n">
-        <v>14.7948446273804</v>
+        <v>14.7948455810547</v>
       </c>
       <c r="H910" t="n">
         <v>12550</v>
@@ -26846,7 +26846,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G913" t="n">
-        <v>14.2400369644165</v>
+        <v>14.2400379180908</v>
       </c>
       <c r="H913" t="n">
         <v>22050</v>
@@ -26875,7 +26875,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G914" t="n">
-        <v>14.424973487854</v>
+        <v>14.4249744415283</v>
       </c>
       <c r="H914" t="n">
         <v>33230</v>
@@ -26933,7 +26933,7 @@
         <v>15.25</v>
       </c>
       <c r="G916" t="n">
-        <v>14.101336479187</v>
+        <v>14.1013374328613</v>
       </c>
       <c r="H916" t="n">
         <v>21450</v>
@@ -26962,7 +26962,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G917" t="n">
-        <v>14.1475687026978</v>
+        <v>14.1475696563721</v>
       </c>
       <c r="H917" t="n">
         <v>7760</v>
@@ -26991,7 +26991,7 @@
         <v>15.25</v>
       </c>
       <c r="G918" t="n">
-        <v>14.101336479187</v>
+        <v>14.1013374328613</v>
       </c>
       <c r="H918" t="n">
         <v>13190</v>
@@ -27049,7 +27049,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G920" t="n">
-        <v>14.1475687026978</v>
+        <v>14.1475696563721</v>
       </c>
       <c r="H920" t="n">
         <v>13660</v>
@@ -27078,7 +27078,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G921" t="n">
-        <v>14.0088682174683</v>
+        <v>14.0088672637939</v>
       </c>
       <c r="H921" t="n">
         <v>21950</v>
@@ -27107,7 +27107,7 @@
         <v>15.25</v>
       </c>
       <c r="G922" t="n">
-        <v>14.101336479187</v>
+        <v>14.1013374328613</v>
       </c>
       <c r="H922" t="n">
         <v>7700</v>
@@ -27194,7 +27194,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G925" t="n">
-        <v>14.0088682174683</v>
+        <v>14.0088672637939</v>
       </c>
       <c r="H925" t="n">
         <v>9170</v>
@@ -27310,7 +27310,7 @@
         <v>15.25</v>
       </c>
       <c r="G929" t="n">
-        <v>14.101336479187</v>
+        <v>14.1013374328613</v>
       </c>
       <c r="H929" t="n">
         <v>83710</v>
@@ -27339,7 +27339,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G930" t="n">
-        <v>14.424973487854</v>
+        <v>14.4249744415283</v>
       </c>
       <c r="H930" t="n">
         <v>16780</v>
@@ -27368,7 +27368,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G931" t="n">
-        <v>15.0722465515137</v>
+        <v>15.072247505188</v>
       </c>
       <c r="H931" t="n">
         <v>24700</v>
@@ -27397,7 +27397,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G932" t="n">
-        <v>14.8873119354248</v>
+        <v>14.8873128890991</v>
       </c>
       <c r="H932" t="n">
         <v>25180</v>
@@ -27455,7 +27455,7 @@
         <v>16</v>
       </c>
       <c r="G934" t="n">
-        <v>14.7948446273804</v>
+        <v>14.7948455810547</v>
       </c>
       <c r="H934" t="n">
         <v>26950</v>
@@ -27484,7 +27484,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G935" t="n">
-        <v>14.7023754119873</v>
+        <v>14.7023763656616</v>
       </c>
       <c r="H935" t="n">
         <v>55500</v>
@@ -27513,7 +27513,7 @@
         <v>16.2000007629395</v>
       </c>
       <c r="G936" t="n">
-        <v>14.9797811508179</v>
+        <v>14.9797821044922</v>
       </c>
       <c r="H936" t="n">
         <v>28830</v>
@@ -27629,7 +27629,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G940" t="n">
-        <v>14.7023754119873</v>
+        <v>14.7023763656616</v>
       </c>
       <c r="H940" t="n">
         <v>29950</v>
@@ -27716,7 +27716,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G943" t="n">
-        <v>14.7023754119873</v>
+        <v>14.7023763656616</v>
       </c>
       <c r="H943" t="n">
         <v>9530</v>
@@ -27832,7 +27832,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G947" t="n">
-        <v>14.6099100112915</v>
+        <v>14.6099090576172</v>
       </c>
       <c r="H947" t="n">
         <v>9810</v>
@@ -27861,7 +27861,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G948" t="n">
-        <v>14.424973487854</v>
+        <v>14.4249744415283</v>
       </c>
       <c r="H948" t="n">
         <v>12460</v>
@@ -27890,7 +27890,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G949" t="n">
-        <v>14.424973487854</v>
+        <v>14.4249744415283</v>
       </c>
       <c r="H949" t="n">
         <v>25160</v>
@@ -27919,7 +27919,7 @@
         <v>14.8000001907349</v>
       </c>
       <c r="G950" t="n">
-        <v>13.6852321624756</v>
+        <v>13.6852312088013</v>
       </c>
       <c r="H950" t="n">
         <v>58020</v>
@@ -27948,7 +27948,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G951" t="n">
-        <v>13.5465278625488</v>
+        <v>13.5465288162231</v>
       </c>
       <c r="H951" t="n">
         <v>40790</v>
@@ -28006,7 +28006,7 @@
         <v>15.25</v>
       </c>
       <c r="G953" t="n">
-        <v>14.101336479187</v>
+        <v>14.1013374328613</v>
       </c>
       <c r="H953" t="n">
         <v>23850</v>
@@ -28035,7 +28035,7 @@
         <v>15.25</v>
       </c>
       <c r="G954" t="n">
-        <v>14.101336479187</v>
+        <v>14.1013374328613</v>
       </c>
       <c r="H954" t="n">
         <v>30470</v>
@@ -28151,7 +28151,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G958" t="n">
-        <v>14.1938037872314</v>
+        <v>14.1938047409058</v>
       </c>
       <c r="H958" t="n">
         <v>15680</v>
@@ -28180,7 +28180,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G959" t="n">
-        <v>14.1475687026978</v>
+        <v>14.1475696563721</v>
       </c>
       <c r="H959" t="n">
         <v>29350</v>
@@ -28238,7 +28238,7 @@
         <v>14.6499996185303</v>
       </c>
       <c r="G961" t="n">
-        <v>13.5465278625488</v>
+        <v>13.5465288162231</v>
       </c>
       <c r="H961" t="n">
         <v>67800</v>
@@ -28296,7 +28296,7 @@
         <v>14.3500003814697</v>
       </c>
       <c r="G963" t="n">
-        <v>13.2691278457642</v>
+        <v>13.2691259384155</v>
       </c>
       <c r="H963" t="n">
         <v>32410</v>
@@ -28325,7 +28325,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G964" t="n">
-        <v>13.4540615081787</v>
+        <v>13.454062461853</v>
       </c>
       <c r="H964" t="n">
         <v>31930</v>
@@ -28383,7 +28383,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G966" t="n">
-        <v>14.1475687026978</v>
+        <v>14.1475696563721</v>
       </c>
       <c r="H966" t="n">
         <v>24850</v>
@@ -28528,7 +28528,7 @@
         <v>15.8000001907349</v>
       </c>
       <c r="G971" t="n">
-        <v>14.6099100112915</v>
+        <v>14.6099090576172</v>
       </c>
       <c r="H971" t="n">
         <v>14610</v>
@@ -28557,7 +28557,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G972" t="n">
-        <v>14.2585306167603</v>
+        <v>14.2585325241089</v>
       </c>
       <c r="H972" t="n">
         <v>9650</v>
@@ -28586,7 +28586,7 @@
         <v>15.6800003051758</v>
       </c>
       <c r="G973" t="n">
-        <v>14.4989490509033</v>
+        <v>14.498948097229</v>
       </c>
       <c r="H973" t="n">
         <v>6060</v>
@@ -28615,7 +28615,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G974" t="n">
-        <v>14.4804544448853</v>
+        <v>14.4804534912109</v>
       </c>
       <c r="H974" t="n">
         <v>10710</v>
@@ -28644,7 +28644,7 @@
         <v>15.5200004577637</v>
       </c>
       <c r="G975" t="n">
-        <v>14.3509998321533</v>
+        <v>14.350998878479</v>
       </c>
       <c r="H975" t="n">
         <v>7490</v>
@@ -28673,7 +28673,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G976" t="n">
-        <v>14.5359344482422</v>
+        <v>14.5359354019165</v>
       </c>
       <c r="H976" t="n">
         <v>7580</v>
@@ -28702,7 +28702,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G977" t="n">
-        <v>14.7023754119873</v>
+        <v>14.7023763656616</v>
       </c>
       <c r="H977" t="n">
         <v>12810</v>
@@ -28731,7 +28731,7 @@
         <v>16</v>
       </c>
       <c r="G978" t="n">
-        <v>14.7948446273804</v>
+        <v>14.7948455810547</v>
       </c>
       <c r="H978" t="n">
         <v>21690</v>
@@ -28760,7 +28760,7 @@
         <v>16</v>
       </c>
       <c r="G979" t="n">
-        <v>14.7948446273804</v>
+        <v>14.7948455810547</v>
       </c>
       <c r="H979" t="n">
         <v>6600</v>
@@ -28847,7 +28847,7 @@
         <v>15.9799995422363</v>
       </c>
       <c r="G982" t="n">
-        <v>14.7763500213623</v>
+        <v>14.7763509750366</v>
       </c>
       <c r="H982" t="n">
         <v>6350</v>
@@ -28876,7 +28876,7 @@
         <v>16.1399993896484</v>
       </c>
       <c r="G983" t="n">
-        <v>14.9242992401123</v>
+        <v>14.9243001937866</v>
       </c>
       <c r="H983" t="n">
         <v>23440</v>
@@ -28934,7 +28934,7 @@
         <v>16</v>
       </c>
       <c r="G985" t="n">
-        <v>14.7948446273804</v>
+        <v>14.7948455810547</v>
       </c>
       <c r="H985" t="n">
         <v>19830</v>
@@ -29021,7 +29021,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G988" t="n">
-        <v>15.1092338562012</v>
+        <v>15.1092357635498</v>
       </c>
       <c r="H988" t="n">
         <v>2460</v>
@@ -29050,7 +29050,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G989" t="n">
-        <v>15.0722465515137</v>
+        <v>15.072247505188</v>
       </c>
       <c r="H989" t="n">
         <v>3450</v>
@@ -29079,7 +29079,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G990" t="n">
-        <v>14.5359344482422</v>
+        <v>14.5359354019165</v>
       </c>
       <c r="H990" t="n">
         <v>18780</v>
@@ -29108,7 +29108,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G991" t="n">
-        <v>14.7023754119873</v>
+        <v>14.7023763656616</v>
       </c>
       <c r="H991" t="n">
         <v>10290</v>
@@ -29137,7 +29137,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G992" t="n">
-        <v>14.9612865447998</v>
+        <v>14.9612874984741</v>
       </c>
       <c r="H992" t="n">
         <v>15990</v>
@@ -29166,7 +29166,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G993" t="n">
-        <v>14.9612865447998</v>
+        <v>14.9612874984741</v>
       </c>
       <c r="H993" t="n">
         <v>34800</v>
@@ -29311,7 +29311,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G998" t="n">
-        <v>14.9845552444458</v>
+        <v>14.9845542907715</v>
       </c>
       <c r="H998" t="n">
         <v>17130</v>
@@ -29398,7 +29398,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1001" t="n">
-        <v>15.226541519165</v>
+        <v>15.2265405654907</v>
       </c>
       <c r="H1001" t="n">
         <v>10350</v>
@@ -29427,7 +29427,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1002" t="n">
-        <v>15.2079267501831</v>
+        <v>15.2079277038574</v>
       </c>
       <c r="H1002" t="n">
         <v>16300</v>
@@ -29456,7 +29456,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G1003" t="n">
-        <v>14.9845552444458</v>
+        <v>14.9845542907715</v>
       </c>
       <c r="H1003" t="n">
         <v>18140</v>
@@ -29485,7 +29485,7 @@
         <v>16.4699993133545</v>
       </c>
       <c r="G1004" t="n">
-        <v>15.3289213180542</v>
+        <v>15.3289194107056</v>
       </c>
       <c r="H1004" t="n">
         <v>13530</v>
@@ -29601,7 +29601,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1008" t="n">
-        <v>17.9628524780273</v>
+        <v>17.9628486633301</v>
       </c>
       <c r="H1008" t="n">
         <v>110884</v>
@@ -29630,7 +29630,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1009" t="n">
-        <v>17.981466293335</v>
+        <v>17.9814643859863</v>
       </c>
       <c r="H1009" t="n">
         <v>68553</v>
@@ -29659,7 +29659,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1010" t="n">
-        <v>17.9628524780273</v>
+        <v>17.9628486633301</v>
       </c>
       <c r="H1010" t="n">
         <v>58949</v>
@@ -29688,7 +29688,7 @@
         <v>18.7600002288818</v>
       </c>
       <c r="G1011" t="n">
-        <v>17.460262298584</v>
+        <v>17.4602661132812</v>
       </c>
       <c r="H1011" t="n">
         <v>31535</v>
@@ -29717,7 +29717,7 @@
         <v>18.5599994659424</v>
       </c>
       <c r="G1012" t="n">
-        <v>17.2741222381592</v>
+        <v>17.2741203308105</v>
       </c>
       <c r="H1012" t="n">
         <v>43758</v>
@@ -29746,7 +29746,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1013" t="n">
-        <v>17.4044227600098</v>
+        <v>17.4044208526611</v>
       </c>
       <c r="H1013" t="n">
         <v>22767</v>
@@ -29775,7 +29775,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1014" t="n">
-        <v>18.0559234619141</v>
+        <v>18.0559215545654</v>
       </c>
       <c r="H1014" t="n">
         <v>17006</v>
@@ -29833,7 +29833,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G1016" t="n">
-        <v>16.5295467376709</v>
+        <v>16.5295448303223</v>
       </c>
       <c r="H1016" t="n">
         <v>112828</v>
@@ -29949,7 +29949,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1020" t="n">
-        <v>16.4923152923584</v>
+        <v>16.492317199707</v>
       </c>
       <c r="H1020" t="n">
         <v>46375</v>
@@ -29978,7 +29978,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G1021" t="n">
-        <v>16.7715320587158</v>
+        <v>16.7715339660645</v>
       </c>
       <c r="H1021" t="n">
         <v>152606</v>
@@ -30036,7 +30036,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1023" t="n">
-        <v>17.5905628204346</v>
+        <v>17.5905647277832</v>
       </c>
       <c r="H1023" t="n">
         <v>91285</v>
@@ -30152,7 +30152,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1027" t="n">
-        <v>17.981466293335</v>
+        <v>17.9814643859863</v>
       </c>
       <c r="H1027" t="n">
         <v>61515</v>
@@ -30210,7 +30210,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1029" t="n">
-        <v>17.7767066955566</v>
+        <v>17.7767105102539</v>
       </c>
       <c r="H1029" t="n">
         <v>39639</v>
@@ -30239,7 +30239,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1030" t="n">
-        <v>17.7767066955566</v>
+        <v>17.7767105102539</v>
       </c>
       <c r="H1030" t="n">
         <v>28008</v>
@@ -30297,7 +30297,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1032" t="n">
-        <v>17.7953224182129</v>
+        <v>17.7953205108643</v>
       </c>
       <c r="H1032" t="n">
         <v>24767</v>
@@ -30326,7 +30326,7 @@
         <v>19.1000003814697</v>
       </c>
       <c r="G1033" t="n">
-        <v>17.7767066955566</v>
+        <v>17.7767105102539</v>
       </c>
       <c r="H1033" t="n">
         <v>46832</v>
@@ -30355,7 +30355,7 @@
         <v>19.0799999237061</v>
       </c>
       <c r="G1034" t="n">
-        <v>17.7580947875977</v>
+        <v>17.758092880249</v>
       </c>
       <c r="H1034" t="n">
         <v>15873</v>
@@ -30384,7 +30384,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G1035" t="n">
-        <v>17.8325500488281</v>
+        <v>17.8325519561768</v>
       </c>
       <c r="H1035" t="n">
         <v>14964</v>
@@ -30413,7 +30413,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1036" t="n">
-        <v>18.2979106903076</v>
+        <v>18.297908782959</v>
       </c>
       <c r="H1036" t="n">
         <v>62131</v>
@@ -30442,7 +30442,7 @@
         <v>19.1200008392334</v>
       </c>
       <c r="G1037" t="n">
-        <v>17.7953224182129</v>
+        <v>17.7953205108643</v>
       </c>
       <c r="H1037" t="n">
         <v>97754</v>
@@ -30471,7 +30471,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G1038" t="n">
-        <v>18.1303806304932</v>
+        <v>18.1303787231445</v>
       </c>
       <c r="H1038" t="n">
         <v>34038</v>
@@ -30500,7 +30500,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G1039" t="n">
-        <v>18.2234516143799</v>
+        <v>18.2234535217285</v>
       </c>
       <c r="H1039" t="n">
         <v>22133</v>
@@ -30558,7 +30558,7 @@
         <v>19.7800006866455</v>
       </c>
       <c r="G1041" t="n">
-        <v>18.4095973968506</v>
+        <v>18.4095993041992</v>
       </c>
       <c r="H1041" t="n">
         <v>22551</v>
@@ -30587,7 +30587,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1042" t="n">
-        <v>18.2979106903076</v>
+        <v>18.297908782959</v>
       </c>
       <c r="H1042" t="n">
         <v>30724</v>
@@ -30616,7 +30616,7 @@
         <v>18.7399997711182</v>
       </c>
       <c r="G1043" t="n">
-        <v>17.4416484832764</v>
+        <v>17.441650390625</v>
       </c>
       <c r="H1043" t="n">
         <v>53087</v>
@@ -30645,7 +30645,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1044" t="n">
-        <v>17.5719470977783</v>
+        <v>17.571949005127</v>
       </c>
       <c r="H1044" t="n">
         <v>64064</v>
@@ -30674,7 +30674,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1045" t="n">
-        <v>17.5347213745117</v>
+        <v>17.5347232818604</v>
       </c>
       <c r="H1045" t="n">
         <v>22408</v>
@@ -30732,7 +30732,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1047" t="n">
-        <v>17.5905628204346</v>
+        <v>17.5905647277832</v>
       </c>
       <c r="H1047" t="n">
         <v>44371</v>
@@ -30761,7 +30761,7 @@
         <v>18.8999996185303</v>
       </c>
       <c r="G1048" t="n">
-        <v>17.5905628204346</v>
+        <v>17.5905647277832</v>
       </c>
       <c r="H1048" t="n">
         <v>27174</v>
@@ -30848,7 +30848,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G1051" t="n">
-        <v>17.9442367553711</v>
+        <v>17.9442386627197</v>
       </c>
       <c r="H1051" t="n">
         <v>14161</v>
@@ -30877,7 +30877,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1052" t="n">
-        <v>17.981466293335</v>
+        <v>17.9814643859863</v>
       </c>
       <c r="H1052" t="n">
         <v>30162</v>
@@ -30906,7 +30906,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1053" t="n">
-        <v>18.2420654296875</v>
+        <v>18.2420673370361</v>
       </c>
       <c r="H1053" t="n">
         <v>21943</v>
@@ -30935,7 +30935,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1054" t="n">
-        <v>18.5212802886963</v>
+        <v>18.5212821960449</v>
       </c>
       <c r="H1054" t="n">
         <v>37546</v>
@@ -30964,7 +30964,7 @@
         <v>20.25</v>
       </c>
       <c r="G1055" t="n">
-        <v>18.8470344543457</v>
+        <v>18.8470363616943</v>
       </c>
       <c r="H1055" t="n">
         <v>95530</v>
@@ -31080,7 +31080,7 @@
         <v>22.1000003814697</v>
       </c>
       <c r="G1059" t="n">
-        <v>20.5688629150391</v>
+        <v>20.5688610076904</v>
       </c>
       <c r="H1059" t="n">
         <v>28721</v>
@@ -31109,7 +31109,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1060" t="n">
-        <v>20.8480758666992</v>
+        <v>20.8480777740479</v>
       </c>
       <c r="H1060" t="n">
         <v>36442</v>
@@ -31167,7 +31167,7 @@
         <v>23</v>
       </c>
       <c r="G1062" t="n">
-        <v>21.4065036773682</v>
+        <v>21.4065074920654</v>
       </c>
       <c r="H1062" t="n">
         <v>72604</v>
@@ -31254,7 +31254,7 @@
         <v>23.7000007629395</v>
       </c>
       <c r="G1065" t="n">
-        <v>22.058012008667</v>
+        <v>22.0580081939697</v>
       </c>
       <c r="H1065" t="n">
         <v>60526</v>
@@ -31283,7 +31283,7 @@
         <v>24.5</v>
       </c>
       <c r="G1066" t="n">
-        <v>22.802583694458</v>
+        <v>22.8025817871094</v>
       </c>
       <c r="H1066" t="n">
         <v>52557</v>
@@ -31341,7 +31341,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G1068" t="n">
-        <v>22.2255382537842</v>
+        <v>22.2255363464355</v>
       </c>
       <c r="H1068" t="n">
         <v>34388</v>
@@ -31457,7 +31457,7 @@
         <v>23.5</v>
       </c>
       <c r="G1072" t="n">
-        <v>21.8718643188477</v>
+        <v>21.8718662261963</v>
       </c>
       <c r="H1072" t="n">
         <v>34002</v>
@@ -31515,7 +31515,7 @@
         <v>23.9799995422363</v>
       </c>
       <c r="G1074" t="n">
-        <v>22.3186111450195</v>
+        <v>22.3186073303223</v>
       </c>
       <c r="H1074" t="n">
         <v>14404</v>
@@ -31544,7 +31544,7 @@
         <v>24.2399997711182</v>
       </c>
       <c r="G1075" t="n">
-        <v>22.5605945587158</v>
+        <v>22.5605964660645</v>
       </c>
       <c r="H1075" t="n">
         <v>74382</v>
@@ -31602,7 +31602,7 @@
         <v>26.3600006103516</v>
       </c>
       <c r="G1077" t="n">
-        <v>24.5337181091309</v>
+        <v>24.5337200164795</v>
       </c>
       <c r="H1077" t="n">
         <v>126165</v>
@@ -31660,7 +31660,7 @@
         <v>26.4599990844727</v>
       </c>
       <c r="G1079" t="n">
-        <v>24.6267871856689</v>
+        <v>24.6267890930176</v>
       </c>
       <c r="H1079" t="n">
         <v>48052</v>
@@ -31689,7 +31689,7 @@
         <v>25.6200008392334</v>
       </c>
       <c r="G1080" t="n">
-        <v>23.8449859619141</v>
+        <v>23.8449878692627</v>
       </c>
       <c r="H1080" t="n">
         <v>64788</v>
@@ -31718,7 +31718,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G1081" t="n">
-        <v>25.2969074249268</v>
+        <v>25.2969055175781</v>
       </c>
       <c r="H1081" t="n">
         <v>162903</v>
@@ -31747,7 +31747,7 @@
         <v>27.0599994659424</v>
       </c>
       <c r="G1082" t="n">
-        <v>25.1852207183838</v>
+        <v>25.1852226257324</v>
       </c>
       <c r="H1082" t="n">
         <v>111572</v>
@@ -31863,7 +31863,7 @@
         <v>26.2399997711182</v>
       </c>
       <c r="G1086" t="n">
-        <v>24.4220294952393</v>
+        <v>24.4220314025879</v>
       </c>
       <c r="H1086" t="n">
         <v>44972</v>
@@ -31892,7 +31892,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G1087" t="n">
-        <v>24.4034194946289</v>
+        <v>24.4034156799316</v>
       </c>
       <c r="H1087" t="n">
         <v>26717</v>
@@ -31921,7 +31921,7 @@
         <v>26.2199993133545</v>
       </c>
       <c r="G1088" t="n">
-        <v>24.4034194946289</v>
+        <v>24.4034156799316</v>
       </c>
       <c r="H1088" t="n">
         <v>113776</v>
@@ -31950,7 +31950,7 @@
         <v>26.1599998474121</v>
       </c>
       <c r="G1089" t="n">
-        <v>24.3475742340088</v>
+        <v>24.3475761413574</v>
       </c>
       <c r="H1089" t="n">
         <v>73043</v>
@@ -31979,7 +31979,7 @@
         <v>27.3199996948242</v>
       </c>
       <c r="G1090" t="n">
-        <v>25.4272060394287</v>
+        <v>25.4272079467773</v>
       </c>
       <c r="H1090" t="n">
         <v>79008</v>
@@ -32008,7 +32008,7 @@
         <v>27.2199993133545</v>
       </c>
       <c r="G1091" t="n">
-        <v>25.3341331481934</v>
+        <v>25.334135055542</v>
       </c>
       <c r="H1091" t="n">
         <v>47633</v>
@@ -32037,7 +32037,7 @@
         <v>26.5599994659424</v>
       </c>
       <c r="G1092" t="n">
-        <v>24.7198619842529</v>
+        <v>24.7198600769043</v>
       </c>
       <c r="H1092" t="n">
         <v>45537</v>
@@ -32095,7 +32095,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1094" t="n">
-        <v>24.0125141143799</v>
+        <v>24.0125160217285</v>
       </c>
       <c r="H1094" t="n">
         <v>46223</v>
@@ -32153,7 +32153,7 @@
         <v>24.5</v>
       </c>
       <c r="G1096" t="n">
-        <v>22.802583694458</v>
+        <v>22.8025817871094</v>
       </c>
       <c r="H1096" t="n">
         <v>65924</v>
@@ -32182,7 +32182,7 @@
         <v>24.5400009155273</v>
       </c>
       <c r="G1097" t="n">
-        <v>22.8398113250732</v>
+        <v>22.8398132324219</v>
       </c>
       <c r="H1097" t="n">
         <v>65882</v>
@@ -32211,7 +32211,7 @@
         <v>25</v>
       </c>
       <c r="G1098" t="n">
-        <v>23.2679424285889</v>
+        <v>23.2679405212402</v>
       </c>
       <c r="H1098" t="n">
         <v>40418</v>
@@ -32327,7 +32327,7 @@
         <v>25.2399997711182</v>
       </c>
       <c r="G1102" t="n">
-        <v>23.4913158416748</v>
+        <v>23.4913139343262</v>
       </c>
       <c r="H1102" t="n">
         <v>39923</v>
@@ -32356,7 +32356,7 @@
         <v>25.3999996185303</v>
       </c>
       <c r="G1103" t="n">
-        <v>23.640230178833</v>
+        <v>23.6402263641357</v>
       </c>
       <c r="H1103" t="n">
         <v>39101</v>
@@ -32385,7 +32385,7 @@
         <v>25.6399993896484</v>
       </c>
       <c r="G1104" t="n">
-        <v>23.8636016845703</v>
+        <v>23.8636035919189</v>
       </c>
       <c r="H1104" t="n">
         <v>23168</v>
@@ -32443,7 +32443,7 @@
         <v>26.5400009155273</v>
       </c>
       <c r="G1106" t="n">
-        <v>24.7012462615967</v>
+        <v>24.7012481689453</v>
       </c>
       <c r="H1106" t="n">
         <v>56770</v>
@@ -32472,7 +32472,7 @@
         <v>26.5</v>
       </c>
       <c r="G1107" t="n">
-        <v>24.6640205383301</v>
+        <v>24.6640186309814</v>
       </c>
       <c r="H1107" t="n">
         <v>44031</v>
@@ -32559,7 +32559,7 @@
         <v>29</v>
       </c>
       <c r="G1110" t="n">
-        <v>26.9908142089844</v>
+        <v>26.9908123016357</v>
       </c>
       <c r="H1110" t="n">
         <v>160850</v>
@@ -32617,7 +32617,7 @@
         <v>31.4400005340576</v>
       </c>
       <c r="G1112" t="n">
-        <v>29.2617626190186</v>
+        <v>29.2617645263672</v>
       </c>
       <c r="H1112" t="n">
         <v>196995</v>
@@ -32646,7 +32646,7 @@
         <v>32.3800010681152</v>
       </c>
       <c r="G1113" t="n">
-        <v>30.1366386413574</v>
+        <v>30.1366405487061</v>
       </c>
       <c r="H1113" t="n">
         <v>138193</v>
@@ -32675,7 +32675,7 @@
         <v>31.8999996185303</v>
       </c>
       <c r="G1114" t="n">
-        <v>29.6898918151855</v>
+        <v>29.6898956298828</v>
       </c>
       <c r="H1114" t="n">
         <v>108201</v>
@@ -32791,7 +32791,7 @@
         <v>30.5200004577637</v>
       </c>
       <c r="G1118" t="n">
-        <v>28.4055023193359</v>
+        <v>28.4055061340332</v>
       </c>
       <c r="H1118" t="n">
         <v>107931</v>
@@ -32820,7 +32820,7 @@
         <v>30.8400001525879</v>
       </c>
       <c r="G1119" t="n">
-        <v>28.7033348083496</v>
+        <v>28.703332901001</v>
       </c>
       <c r="H1119" t="n">
         <v>33295</v>
@@ -32849,7 +32849,7 @@
         <v>31.7199993133545</v>
       </c>
       <c r="G1120" t="n">
-        <v>29.5223617553711</v>
+        <v>29.5223655700684</v>
       </c>
       <c r="H1120" t="n">
         <v>40026</v>
@@ -32878,7 +32878,7 @@
         <v>32.1199989318848</v>
       </c>
       <c r="G1121" t="n">
-        <v>29.8946514129639</v>
+        <v>29.8946495056152</v>
       </c>
       <c r="H1121" t="n">
         <v>53168</v>
@@ -32907,7 +32907,7 @@
         <v>32.6199989318848</v>
       </c>
       <c r="G1122" t="n">
-        <v>30.3600101470947</v>
+        <v>30.3600082397461</v>
       </c>
       <c r="H1122" t="n">
         <v>52785</v>
@@ -32965,7 +32965,7 @@
         <v>33.7200012207031</v>
       </c>
       <c r="G1124" t="n">
-        <v>31.3837985992432</v>
+        <v>31.3838024139404</v>
       </c>
       <c r="H1124" t="n">
         <v>99656</v>
@@ -33023,7 +33023,7 @@
         <v>33</v>
       </c>
       <c r="G1126" t="n">
-        <v>30.7136859893799</v>
+        <v>30.7136878967285</v>
       </c>
       <c r="H1126" t="n">
         <v>68064</v>
@@ -33052,7 +33052,7 @@
         <v>33.5400009155273</v>
       </c>
       <c r="G1127" t="n">
-        <v>31.216272354126</v>
+        <v>31.2162685394287</v>
       </c>
       <c r="H1127" t="n">
         <v>70098</v>
@@ -33110,7 +33110,7 @@
         <v>33.5</v>
       </c>
       <c r="G1129" t="n">
-        <v>31.1790428161621</v>
+        <v>31.1790409088135</v>
       </c>
       <c r="H1129" t="n">
         <v>262770</v>
@@ -33139,7 +33139,7 @@
         <v>33.6599998474121</v>
       </c>
       <c r="G1130" t="n">
-        <v>31.3279552459717</v>
+        <v>31.3279571533203</v>
       </c>
       <c r="H1130" t="n">
         <v>149267</v>
@@ -33168,7 +33168,7 @@
         <v>34.2000007629395</v>
       </c>
       <c r="G1131" t="n">
-        <v>31.8305435180664</v>
+        <v>31.8305416107178</v>
       </c>
       <c r="H1131" t="n">
         <v>139414</v>
@@ -33313,7 +33313,7 @@
         <v>32.4199981689453</v>
       </c>
       <c r="G1136" t="n">
-        <v>30.1738662719727</v>
+        <v>30.1738681793213</v>
       </c>
       <c r="H1136" t="n">
         <v>77493</v>
@@ -33342,7 +33342,7 @@
         <v>32.6399993896484</v>
       </c>
       <c r="G1137" t="n">
-        <v>30.378625869751</v>
+        <v>30.3786277770996</v>
       </c>
       <c r="H1137" t="n">
         <v>69137</v>
@@ -33400,7 +33400,7 @@
         <v>33</v>
       </c>
       <c r="G1139" t="n">
-        <v>30.7136859893799</v>
+        <v>30.7136878967285</v>
       </c>
       <c r="H1139" t="n">
         <v>67965</v>
@@ -33429,7 +33429,7 @@
         <v>32.8199996948242</v>
       </c>
       <c r="G1140" t="n">
-        <v>30.5461559295654</v>
+        <v>30.5461521148682</v>
       </c>
       <c r="H1140" t="n">
         <v>387974</v>
@@ -33458,7 +33458,7 @@
         <v>33.560001373291</v>
       </c>
       <c r="G1141" t="n">
-        <v>31.2348880767822</v>
+        <v>31.2348861694336</v>
       </c>
       <c r="H1141" t="n">
         <v>46011</v>
@@ -33487,7 +33487,7 @@
         <v>33.7200012207031</v>
       </c>
       <c r="G1142" t="n">
-        <v>31.3837985992432</v>
+        <v>31.3838024139404</v>
       </c>
       <c r="H1142" t="n">
         <v>42115</v>
@@ -33516,7 +33516,7 @@
         <v>33.4599990844727</v>
       </c>
       <c r="G1143" t="n">
-        <v>31.1418132781982</v>
+        <v>31.1418113708496</v>
       </c>
       <c r="H1143" t="n">
         <v>57121</v>
@@ -33545,7 +33545,7 @@
         <v>34.439998626709</v>
       </c>
       <c r="G1144" t="n">
-        <v>32.0539131164551</v>
+        <v>32.0539169311523</v>
       </c>
       <c r="H1144" t="n">
         <v>77872</v>
@@ -33632,7 +33632,7 @@
         <v>35.2000007629395</v>
       </c>
       <c r="G1147" t="n">
-        <v>32.7612648010254</v>
+        <v>32.7612609863281</v>
       </c>
       <c r="H1147" t="n">
         <v>39345</v>
@@ -33690,7 +33690,7 @@
         <v>36.1399993896484</v>
       </c>
       <c r="G1149" t="n">
-        <v>33.6361351013184</v>
+        <v>33.6361389160156</v>
       </c>
       <c r="H1149" t="n">
         <v>43244</v>
@@ -33748,7 +33748,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G1151" t="n">
-        <v>31.5513324737549</v>
+        <v>31.5513286590576</v>
       </c>
       <c r="H1151" t="n">
         <v>40722</v>
@@ -33777,7 +33777,7 @@
         <v>33.6199989318848</v>
       </c>
       <c r="G1152" t="n">
-        <v>31.2907314300537</v>
+        <v>31.2907295227051</v>
       </c>
       <c r="H1152" t="n">
         <v>34237</v>
@@ -33806,7 +33806,7 @@
         <v>33.9199981689453</v>
       </c>
       <c r="G1153" t="n">
-        <v>31.5699443817139</v>
+        <v>31.5699424743652</v>
       </c>
       <c r="H1153" t="n">
         <v>24699</v>
@@ -33835,7 +33835,7 @@
         <v>34.1800003051758</v>
       </c>
       <c r="G1154" t="n">
-        <v>31.8119316101074</v>
+        <v>31.8119277954102</v>
       </c>
       <c r="H1154" t="n">
         <v>37962</v>
@@ -33864,7 +33864,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1155" t="n">
-        <v>32.2028312683105</v>
+        <v>32.2028274536133</v>
       </c>
       <c r="H1155" t="n">
         <v>22814</v>
@@ -33893,7 +33893,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G1156" t="n">
-        <v>33.7850532531738</v>
+        <v>33.7850494384766</v>
       </c>
       <c r="H1156" t="n">
         <v>73415</v>
@@ -33922,7 +33922,7 @@
         <v>35.7799987792969</v>
       </c>
       <c r="G1157" t="n">
-        <v>33.3010787963867</v>
+        <v>33.3010749816895</v>
       </c>
       <c r="H1157" t="n">
         <v>25412</v>
@@ -33951,7 +33951,7 @@
         <v>36.2799987792969</v>
       </c>
       <c r="G1158" t="n">
-        <v>33.7664337158203</v>
+        <v>33.7664375305176</v>
       </c>
       <c r="H1158" t="n">
         <v>24931</v>
@@ -33980,7 +33980,7 @@
         <v>35.7400016784668</v>
       </c>
       <c r="G1159" t="n">
-        <v>33.2638511657715</v>
+        <v>33.2638549804688</v>
       </c>
       <c r="H1159" t="n">
         <v>32163</v>
@@ -34038,7 +34038,7 @@
         <v>35.8400001525879</v>
       </c>
       <c r="G1161" t="n">
-        <v>33.3569259643555</v>
+        <v>33.3569221496582</v>
       </c>
       <c r="H1161" t="n">
         <v>19551</v>
@@ -34096,7 +34096,7 @@
         <v>37.9799995422363</v>
       </c>
       <c r="G1163" t="n">
-        <v>35.3486595153809</v>
+        <v>35.3486518859863</v>
       </c>
       <c r="H1163" t="n">
         <v>124787</v>
@@ -34154,7 +34154,7 @@
         <v>38.060001373291</v>
       </c>
       <c r="G1165" t="n">
-        <v>35.4231185913086</v>
+        <v>35.4231147766113</v>
       </c>
       <c r="H1165" t="n">
         <v>86554</v>
@@ -34212,7 +34212,7 @@
         <v>33.5400009155273</v>
       </c>
       <c r="G1167" t="n">
-        <v>31.216272354126</v>
+        <v>31.2162685394287</v>
       </c>
       <c r="H1167" t="n">
         <v>82109</v>
@@ -34241,7 +34241,7 @@
         <v>34</v>
       </c>
       <c r="G1168" t="n">
-        <v>31.644401550293</v>
+        <v>31.6443996429443</v>
       </c>
       <c r="H1168" t="n">
         <v>67914</v>
@@ -34270,7 +34270,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G1169" t="n">
-        <v>32.4820518493652</v>
+        <v>32.482048034668</v>
       </c>
       <c r="H1169" t="n">
         <v>44316</v>
@@ -34328,7 +34328,7 @@
         <v>34.9000015258789</v>
       </c>
       <c r="G1171" t="n">
-        <v>32.4820518493652</v>
+        <v>32.482048034668</v>
       </c>
       <c r="H1171" t="n">
         <v>55538</v>
@@ -34357,7 +34357,7 @@
         <v>34.5999984741211</v>
       </c>
       <c r="G1172" t="n">
-        <v>32.2028312683105</v>
+        <v>32.2028274536133</v>
       </c>
       <c r="H1172" t="n">
         <v>34927</v>
@@ -34386,7 +34386,7 @@
         <v>33.439998626709</v>
       </c>
       <c r="G1173" t="n">
-        <v>31.123197555542</v>
+        <v>31.1231994628906</v>
       </c>
       <c r="H1173" t="n">
         <v>36381</v>
@@ -34473,7 +34473,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1176" t="n">
-        <v>30.8998260498047</v>
+        <v>30.8998279571533</v>
       </c>
       <c r="H1176" t="n">
         <v>68323</v>
@@ -34502,7 +34502,7 @@
         <v>30.8400001525879</v>
       </c>
       <c r="G1177" t="n">
-        <v>28.7033348083496</v>
+        <v>28.703332901001</v>
       </c>
       <c r="H1177" t="n">
         <v>100449</v>
@@ -34560,7 +34560,7 @@
         <v>30.1800003051758</v>
       </c>
       <c r="G1179" t="n">
-        <v>28.0890598297119</v>
+        <v>28.0890617370605</v>
       </c>
       <c r="H1179" t="n">
         <v>41407</v>
@@ -34589,7 +34589,7 @@
         <v>30.2399997711182</v>
       </c>
       <c r="G1180" t="n">
-        <v>28.1449031829834</v>
+        <v>28.1449012756348</v>
       </c>
       <c r="H1180" t="n">
         <v>28467</v>
@@ -34647,7 +34647,7 @@
         <v>31.1800003051758</v>
       </c>
       <c r="G1182" t="n">
-        <v>29.0197792053223</v>
+        <v>29.0197772979736</v>
       </c>
       <c r="H1182" t="n">
         <v>69277</v>
@@ -34705,7 +34705,7 @@
         <v>32.5400009155273</v>
       </c>
       <c r="G1184" t="n">
-        <v>30.2855529785156</v>
+        <v>30.2855548858643</v>
       </c>
       <c r="H1184" t="n">
         <v>33508</v>
@@ -34734,7 +34734,7 @@
         <v>31.0200004577637</v>
       </c>
       <c r="G1185" t="n">
-        <v>28.8708629608154</v>
+        <v>28.8708648681641</v>
       </c>
       <c r="H1185" t="n">
         <v>43257</v>
@@ -34792,7 +34792,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1187" t="n">
-        <v>27.735387802124</v>
+        <v>27.7353858947754</v>
       </c>
       <c r="H1187" t="n">
         <v>31273</v>
@@ -34879,7 +34879,7 @@
         <v>29</v>
       </c>
       <c r="G1190" t="n">
-        <v>26.9908142089844</v>
+        <v>26.9908123016357</v>
       </c>
       <c r="H1190" t="n">
         <v>75084</v>
@@ -34966,7 +34966,7 @@
         <v>30.1800003051758</v>
       </c>
       <c r="G1193" t="n">
-        <v>28.0890598297119</v>
+        <v>28.0890617370605</v>
       </c>
       <c r="H1193" t="n">
         <v>48544</v>
@@ -34995,7 +34995,7 @@
         <v>29.9799995422363</v>
       </c>
       <c r="G1194" t="n">
-        <v>27.9029178619385</v>
+        <v>27.9029159545898</v>
       </c>
       <c r="H1194" t="n">
         <v>34088</v>
@@ -35082,7 +35082,7 @@
         <v>28.3199996948242</v>
       </c>
       <c r="G1197" t="n">
-        <v>26.3579254150391</v>
+        <v>26.3579235076904</v>
       </c>
       <c r="H1197" t="n">
         <v>45867</v>
@@ -35111,7 +35111,7 @@
         <v>28.8999996185303</v>
       </c>
       <c r="G1198" t="n">
-        <v>26.8977432250977</v>
+        <v>26.897741317749</v>
       </c>
       <c r="H1198" t="n">
         <v>76545</v>
@@ -35169,7 +35169,7 @@
         <v>27.6399993896484</v>
       </c>
       <c r="G1200" t="n">
-        <v>25.7250366210938</v>
+        <v>25.7250347137451</v>
       </c>
       <c r="H1200" t="n">
         <v>46762</v>
@@ -35198,7 +35198,7 @@
         <v>28.8799991607666</v>
       </c>
       <c r="G1201" t="n">
-        <v>26.8791275024414</v>
+        <v>26.8791255950928</v>
       </c>
       <c r="H1201" t="n">
         <v>42064</v>
@@ -35256,7 +35256,7 @@
         <v>28.8799991607666</v>
       </c>
       <c r="G1203" t="n">
-        <v>26.8791275024414</v>
+        <v>26.8791255950928</v>
       </c>
       <c r="H1203" t="n">
         <v>47313</v>
@@ -35285,7 +35285,7 @@
         <v>28.5</v>
       </c>
       <c r="G1204" t="n">
-        <v>26.5254535675049</v>
+        <v>26.5254554748535</v>
       </c>
       <c r="H1204" t="n">
         <v>30976</v>
@@ -35314,7 +35314,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G1205" t="n">
-        <v>25.2969074249268</v>
+        <v>25.2969055175781</v>
       </c>
       <c r="H1205" t="n">
         <v>22103</v>
@@ -35343,7 +35343,7 @@
         <v>26.0400009155273</v>
       </c>
       <c r="G1206" t="n">
-        <v>24.2358913421631</v>
+        <v>24.2358894348145</v>
       </c>
       <c r="H1206" t="n">
         <v>68431</v>
@@ -35430,7 +35430,7 @@
         <v>28.2199993133545</v>
       </c>
       <c r="G1209" t="n">
-        <v>26.2648544311523</v>
+        <v>26.2648525238037</v>
       </c>
       <c r="H1209" t="n">
         <v>45692</v>
@@ -35459,7 +35459,7 @@
         <v>27.1200008392334</v>
       </c>
       <c r="G1210" t="n">
-        <v>25.2410659790039</v>
+        <v>25.2410640716553</v>
       </c>
       <c r="H1210" t="n">
         <v>35306</v>
@@ -35517,7 +35517,7 @@
         <v>28.4799995422363</v>
       </c>
       <c r="G1212" t="n">
-        <v>26.5068378448486</v>
+        <v>26.5068397521973</v>
       </c>
       <c r="H1212" t="n">
         <v>18028</v>
@@ -35633,7 +35633,7 @@
         <v>29.3199996948242</v>
       </c>
       <c r="G1216" t="n">
-        <v>27.2886428833008</v>
+        <v>27.2886409759521</v>
       </c>
       <c r="H1216" t="n">
         <v>70944</v>
@@ -35662,7 +35662,7 @@
         <v>28.8400001525879</v>
       </c>
       <c r="G1217" t="n">
-        <v>26.8418998718262</v>
+        <v>26.8418979644775</v>
       </c>
       <c r="H1217" t="n">
         <v>52590</v>
@@ -35691,7 +35691,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1218" t="n">
-        <v>27.6423149108887</v>
+        <v>27.6423168182373</v>
       </c>
       <c r="H1218" t="n">
         <v>56043</v>
@@ -35720,7 +35720,7 @@
         <v>29.7999992370605</v>
       </c>
       <c r="G1219" t="n">
-        <v>27.735387802124</v>
+        <v>27.7353858947754</v>
       </c>
       <c r="H1219" t="n">
         <v>30031</v>
@@ -35749,7 +35749,7 @@
         <v>29.5</v>
       </c>
       <c r="G1220" t="n">
-        <v>27.4561710357666</v>
+        <v>27.4561729431152</v>
       </c>
       <c r="H1220" t="n">
         <v>32051</v>
@@ -35807,7 +35807,7 @@
         <v>30.1200008392334</v>
       </c>
       <c r="G1222" t="n">
-        <v>28.0332183837891</v>
+        <v>28.0332202911377</v>
       </c>
       <c r="H1222" t="n">
         <v>31987</v>
@@ -35865,7 +35865,7 @@
         <v>30.9200000762939</v>
       </c>
       <c r="G1224" t="n">
-        <v>28.7777919769287</v>
+        <v>28.7777900695801</v>
       </c>
       <c r="H1224" t="n">
         <v>49249</v>
@@ -35923,7 +35923,7 @@
         <v>29.6000003814697</v>
       </c>
       <c r="G1226" t="n">
-        <v>27.549243927002</v>
+        <v>27.5492458343506</v>
       </c>
       <c r="H1226" t="n">
         <v>38065</v>
@@ -35981,7 +35981,7 @@
         <v>28.9799995422363</v>
       </c>
       <c r="G1228" t="n">
-        <v>26.9721965789795</v>
+        <v>26.9721984863281</v>
       </c>
       <c r="H1228" t="n">
         <v>28562</v>
@@ -36010,7 +36010,7 @@
         <v>27.8999996185303</v>
       </c>
       <c r="G1229" t="n">
-        <v>25.9670219421387</v>
+        <v>25.9670238494873</v>
       </c>
       <c r="H1229" t="n">
         <v>43867</v>
@@ -36068,7 +36068,7 @@
         <v>28.2000007629395</v>
       </c>
       <c r="G1231" t="n">
-        <v>26.2462406158447</v>
+        <v>26.2462387084961</v>
       </c>
       <c r="H1231" t="n">
         <v>19677</v>
@@ -36097,7 +36097,7 @@
         <v>28.4400005340576</v>
       </c>
       <c r="G1232" t="n">
-        <v>26.469612121582</v>
+        <v>26.4696102142334</v>
       </c>
       <c r="H1232" t="n">
         <v>30233</v>
@@ -36155,7 +36155,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1234" t="n">
-        <v>26.4323806762695</v>
+        <v>26.4323825836182</v>
       </c>
       <c r="H1234" t="n">
         <v>24296</v>
@@ -36184,7 +36184,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1235" t="n">
-        <v>25.8739528656006</v>
+        <v>25.873950958252</v>
       </c>
       <c r="H1235" t="n">
         <v>15018</v>
@@ -36271,7 +36271,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G1238" t="n">
-        <v>25.2969074249268</v>
+        <v>25.2969055175781</v>
       </c>
       <c r="H1238" t="n">
         <v>29471</v>
@@ -36561,7 +36561,7 @@
         <v>23.0200004577637</v>
       </c>
       <c r="G1248" t="n">
-        <v>21.6680355072021</v>
+        <v>21.6680374145508</v>
       </c>
       <c r="H1248" t="n">
         <v>34661</v>
@@ -36648,7 +36648,7 @@
         <v>21.7999992370605</v>
       </c>
       <c r="G1251" t="n">
-        <v>20.5196876525879</v>
+        <v>20.5196838378906</v>
       </c>
       <c r="H1251" t="n">
         <v>42268</v>
@@ -36764,7 +36764,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1255" t="n">
-        <v>19.2019081115723</v>
+        <v>19.2019062042236</v>
       </c>
       <c r="H1255" t="n">
         <v>24612</v>
@@ -36967,7 +36967,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G1262" t="n">
-        <v>19.7854976654053</v>
+        <v>19.785493850708</v>
       </c>
       <c r="H1262" t="n">
         <v>37052</v>
@@ -37054,7 +37054,7 @@
         <v>22.3400001525879</v>
       </c>
       <c r="G1265" t="n">
-        <v>21.0279712677002</v>
+        <v>21.0279731750488</v>
       </c>
       <c r="H1265" t="n">
         <v>61995</v>
@@ -37112,7 +37112,7 @@
         <v>22.3600006103516</v>
       </c>
       <c r="G1267" t="n">
-        <v>21.0467967987061</v>
+        <v>21.0467987060547</v>
       </c>
       <c r="H1267" t="n">
         <v>47839</v>
@@ -37141,7 +37141,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1268" t="n">
-        <v>20.3314323425293</v>
+        <v>20.3314342498779</v>
       </c>
       <c r="H1268" t="n">
         <v>47908</v>
@@ -37170,7 +37170,7 @@
         <v>21</v>
       </c>
       <c r="G1269" t="n">
-        <v>19.7666702270508</v>
+        <v>19.7666721343994</v>
       </c>
       <c r="H1269" t="n">
         <v>49449</v>
@@ -37257,7 +37257,7 @@
         <v>21.0599994659424</v>
       </c>
       <c r="G1272" t="n">
-        <v>19.8231468200684</v>
+        <v>19.8231449127197</v>
       </c>
       <c r="H1272" t="n">
         <v>39163</v>
@@ -37286,7 +37286,7 @@
         <v>20.9799995422363</v>
       </c>
       <c r="G1273" t="n">
-        <v>19.7478427886963</v>
+        <v>19.7478466033936</v>
       </c>
       <c r="H1273" t="n">
         <v>18853</v>
@@ -37373,7 +37373,7 @@
         <v>18.8500003814697</v>
       </c>
       <c r="G1276" t="n">
-        <v>17.7429389953613</v>
+        <v>17.74294090271</v>
       </c>
       <c r="H1276" t="n">
         <v>46771</v>
@@ -37402,7 +37402,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G1277" t="n">
-        <v>18.4677181243896</v>
+        <v>18.4677200317383</v>
       </c>
       <c r="H1277" t="n">
         <v>43858</v>
@@ -37431,7 +37431,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1278" t="n">
-        <v>18.0159091949463</v>
+        <v>18.015905380249</v>
       </c>
       <c r="H1278" t="n">
         <v>51917</v>
@@ -37460,7 +37460,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1279" t="n">
-        <v>18.2041625976562</v>
+        <v>18.2041606903076</v>
       </c>
       <c r="H1279" t="n">
         <v>46603</v>
@@ -37634,7 +37634,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1285" t="n">
-        <v>17.5264492034912</v>
+        <v>17.5264472961426</v>
       </c>
       <c r="H1285" t="n">
         <v>17848</v>
@@ -37692,7 +37692,7 @@
         <v>17.9400005340576</v>
       </c>
       <c r="G1287" t="n">
-        <v>16.8863849639893</v>
+        <v>16.8863830566406</v>
       </c>
       <c r="H1287" t="n">
         <v>35330</v>
@@ -37721,7 +37721,7 @@
         <v>17.3999996185303</v>
       </c>
       <c r="G1288" t="n">
-        <v>16.3780975341797</v>
+        <v>16.3780956268311</v>
       </c>
       <c r="H1288" t="n">
         <v>38531</v>
@@ -37750,7 +37750,7 @@
         <v>17.3099994659424</v>
       </c>
       <c r="G1289" t="n">
-        <v>16.2933826446533</v>
+        <v>16.293384552002</v>
       </c>
       <c r="H1289" t="n">
         <v>18435</v>
@@ -37808,7 +37808,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G1291" t="n">
-        <v>16.0957164764404</v>
+        <v>16.0957183837891</v>
       </c>
       <c r="H1291" t="n">
         <v>43422</v>
@@ -37866,7 +37866,7 @@
         <v>18.4699993133545</v>
       </c>
       <c r="G1293" t="n">
-        <v>17.3852577209473</v>
+        <v>17.3852558135986</v>
       </c>
       <c r="H1293" t="n">
         <v>41683</v>
@@ -37895,7 +37895,7 @@
         <v>19.2000007629395</v>
       </c>
       <c r="G1294" t="n">
-        <v>18.0723857879639</v>
+        <v>18.0723838806152</v>
       </c>
       <c r="H1294" t="n">
         <v>52014</v>
@@ -37953,7 +37953,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G1296" t="n">
-        <v>17.8088283538818</v>
+        <v>17.8088302612305</v>
       </c>
       <c r="H1296" t="n">
         <v>35661</v>
@@ -38127,7 +38127,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G1302" t="n">
-        <v>17.4982089996338</v>
+        <v>17.4982109069824</v>
       </c>
       <c r="H1302" t="n">
         <v>18353</v>
@@ -38156,7 +38156,7 @@
         <v>18.6800003051758</v>
       </c>
       <c r="G1303" t="n">
-        <v>17.5829257965088</v>
+        <v>17.5829238891602</v>
       </c>
       <c r="H1303" t="n">
         <v>19027</v>
@@ -38214,7 +38214,7 @@
         <v>18.8299999237061</v>
       </c>
       <c r="G1305" t="n">
-        <v>17.7241153717041</v>
+        <v>17.7241134643555</v>
       </c>
       <c r="H1305" t="n">
         <v>19039</v>
@@ -38243,7 +38243,7 @@
         <v>18.75</v>
       </c>
       <c r="G1306" t="n">
-        <v>17.6488151550293</v>
+        <v>17.6488132476807</v>
       </c>
       <c r="H1306" t="n">
         <v>23164</v>
@@ -38301,7 +38301,7 @@
         <v>19.1499996185303</v>
       </c>
       <c r="G1308" t="n">
-        <v>18.0253200531006</v>
+        <v>18.025318145752</v>
       </c>
       <c r="H1308" t="n">
         <v>37775</v>
@@ -38330,7 +38330,7 @@
         <v>20</v>
       </c>
       <c r="G1309" t="n">
-        <v>18.8254013061523</v>
+        <v>18.8253974914551</v>
       </c>
       <c r="H1309" t="n">
         <v>73322</v>
@@ -38388,7 +38388,7 @@
         <v>20</v>
       </c>
       <c r="G1311" t="n">
-        <v>18.8254013061523</v>
+        <v>18.8253974914551</v>
       </c>
       <c r="H1311" t="n">
         <v>26090</v>
@@ -38417,7 +38417,7 @@
         <v>20</v>
       </c>
       <c r="G1312" t="n">
-        <v>18.8254013061523</v>
+        <v>18.8253974914551</v>
       </c>
       <c r="H1312" t="n">
         <v>42674</v>
@@ -38504,7 +38504,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G1315" t="n">
-        <v>18.4677181243896</v>
+        <v>18.4677200317383</v>
       </c>
       <c r="H1315" t="n">
         <v>28577</v>
@@ -38562,7 +38562,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1317" t="n">
-        <v>18.4488906860352</v>
+        <v>18.4488925933838</v>
       </c>
       <c r="H1317" t="n">
         <v>44913</v>
@@ -38591,7 +38591,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G1318" t="n">
-        <v>18.3830051422119</v>
+        <v>18.3830032348633</v>
       </c>
       <c r="H1318" t="n">
         <v>19017</v>
@@ -38620,7 +38620,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G1319" t="n">
-        <v>18.608907699585</v>
+        <v>18.6089096069336</v>
       </c>
       <c r="H1319" t="n">
         <v>16339</v>
@@ -38649,7 +38649,7 @@
         <v>19.4400005340576</v>
       </c>
       <c r="G1320" t="n">
-        <v>18.2982883453369</v>
+        <v>18.2982902526855</v>
       </c>
       <c r="H1320" t="n">
         <v>27815</v>
@@ -38678,7 +38678,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G1321" t="n">
-        <v>18.0347328186035</v>
+        <v>18.0347347259521</v>
       </c>
       <c r="H1321" t="n">
         <v>30697</v>
@@ -38707,7 +38707,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1322" t="n">
-        <v>17.5264492034912</v>
+        <v>17.5264472961426</v>
       </c>
       <c r="H1322" t="n">
         <v>22113</v>
@@ -38765,7 +38765,7 @@
         <v>18.5799999237061</v>
       </c>
       <c r="G1324" t="n">
-        <v>17.4887981414795</v>
+        <v>17.4887962341309</v>
       </c>
       <c r="H1324" t="n">
         <v>30109</v>
@@ -38794,7 +38794,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G1325" t="n">
-        <v>16.7169570922852</v>
+        <v>16.7169551849365</v>
       </c>
       <c r="H1325" t="n">
         <v>26614</v>
@@ -38852,7 +38852,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G1327" t="n">
-        <v>16.7263660430908</v>
+        <v>16.7263679504395</v>
       </c>
       <c r="H1327" t="n">
         <v>12643</v>
@@ -38939,7 +38939,7 @@
         <v>17.2999992370605</v>
       </c>
       <c r="G1330" t="n">
-        <v>16.283971786499</v>
+        <v>16.2839698791504</v>
       </c>
       <c r="H1330" t="n">
         <v>35031</v>
@@ -38968,7 +38968,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G1331" t="n">
-        <v>16.7263660430908</v>
+        <v>16.7263679504395</v>
       </c>
       <c r="H1331" t="n">
         <v>15512</v>
@@ -39026,7 +39026,7 @@
         <v>17.1299991607666</v>
       </c>
       <c r="G1333" t="n">
-        <v>16.1239528656006</v>
+        <v>16.1239547729492</v>
       </c>
       <c r="H1333" t="n">
         <v>23067</v>
@@ -39200,7 +39200,7 @@
         <v>18.7199993133545</v>
       </c>
       <c r="G1339" t="n">
-        <v>17.6205768585205</v>
+        <v>17.6205730438232</v>
       </c>
       <c r="H1339" t="n">
         <v>23955</v>
@@ -39258,7 +39258,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1341" t="n">
-        <v>16.6793022155762</v>
+        <v>16.6793041229248</v>
       </c>
       <c r="H1341" t="n">
         <v>62269</v>
@@ -39345,7 +39345,7 @@
         <v>16</v>
       </c>
       <c r="G1344" t="n">
-        <v>15.060320854187</v>
+        <v>15.0603199005127</v>
       </c>
       <c r="H1344" t="n">
         <v>84138</v>
@@ -39403,7 +39403,7 @@
         <v>15.289999961853</v>
       </c>
       <c r="G1346" t="n">
-        <v>14.3920183181763</v>
+        <v>14.392017364502</v>
       </c>
       <c r="H1346" t="n">
         <v>50933</v>
@@ -39432,7 +39432,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1347" t="n">
-        <v>13.6954784393311</v>
+        <v>13.6954793930054</v>
       </c>
       <c r="H1347" t="n">
         <v>95494</v>
@@ -39461,7 +39461,7 @@
         <v>14.3100004196167</v>
       </c>
       <c r="G1348" t="n">
-        <v>13.4695739746094</v>
+        <v>13.469575881958</v>
       </c>
       <c r="H1348" t="n">
         <v>84418</v>
@@ -39548,7 +39548,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1351" t="n">
-        <v>13.0271759033203</v>
+        <v>13.0271778106689</v>
       </c>
       <c r="H1351" t="n">
         <v>68271</v>
@@ -39577,7 +39577,7 @@
         <v>13.2700004577637</v>
       </c>
       <c r="G1352" t="n">
-        <v>12.4906530380249</v>
+        <v>12.4906539916992</v>
       </c>
       <c r="H1352" t="n">
         <v>64810</v>
@@ -39635,7 +39635,7 @@
         <v>14.2700004577637</v>
       </c>
       <c r="G1354" t="n">
-        <v>13.4319229125977</v>
+        <v>13.431923866272</v>
       </c>
       <c r="H1354" t="n">
         <v>126733</v>
@@ -39693,7 +39693,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G1356" t="n">
-        <v>13.6954784393311</v>
+        <v>13.6954793930054</v>
       </c>
       <c r="H1356" t="n">
         <v>24807</v>
@@ -39722,7 +39722,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G1357" t="n">
-        <v>13.7801923751831</v>
+        <v>13.7801933288574</v>
       </c>
       <c r="H1357" t="n">
         <v>26201</v>
@@ -39751,7 +39751,7 @@
         <v>14.1700000762939</v>
       </c>
       <c r="G1358" t="n">
-        <v>13.3377952575684</v>
+        <v>13.3377962112427</v>
       </c>
       <c r="H1358" t="n">
         <v>47171</v>
@@ -39838,7 +39838,7 @@
         <v>14.0699996948242</v>
       </c>
       <c r="G1361" t="n">
-        <v>13.2436685562134</v>
+        <v>13.2436676025391</v>
       </c>
       <c r="H1361" t="n">
         <v>25872</v>
@@ -39925,7 +39925,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1364" t="n">
-        <v>13.3660335540771</v>
+        <v>13.3660345077515</v>
       </c>
       <c r="H1364" t="n">
         <v>52821</v>
@@ -39954,7 +39954,7 @@
         <v>14.1999998092651</v>
       </c>
       <c r="G1365" t="n">
-        <v>13.3660335540771</v>
+        <v>13.3660345077515</v>
       </c>
       <c r="H1365" t="n">
         <v>62045</v>
@@ -39983,7 +39983,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G1366" t="n">
-        <v>13.3001461029053</v>
+        <v>13.300145149231</v>
       </c>
       <c r="H1366" t="n">
         <v>43095</v>
@@ -40128,7 +40128,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G1371" t="n">
-        <v>15.1356220245361</v>
+        <v>15.1356210708618</v>
       </c>
       <c r="H1371" t="n">
         <v>83342</v>
@@ -40186,7 +40186,7 @@
         <v>15.5699996948242</v>
       </c>
       <c r="G1373" t="n">
-        <v>14.6555728912354</v>
+        <v>14.6555738449097</v>
       </c>
       <c r="H1373" t="n">
         <v>22186</v>
@@ -40273,7 +40273,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G1376" t="n">
-        <v>14.1567010879517</v>
+        <v>14.1567001342773</v>
       </c>
       <c r="H1376" t="n">
         <v>26012</v>
@@ -40302,7 +40302,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1377" t="n">
-        <v>14.2131767272949</v>
+        <v>14.2131776809692</v>
       </c>
       <c r="H1377" t="n">
         <v>26436</v>
@@ -40331,7 +40331,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1378" t="n">
-        <v>14.4484949111938</v>
+        <v>14.4484958648682</v>
       </c>
       <c r="H1378" t="n">
         <v>24491</v>
@@ -40360,7 +40360,7 @@
         <v>15.710000038147</v>
       </c>
       <c r="G1379" t="n">
-        <v>14.7873525619507</v>
+        <v>14.7873516082764</v>
       </c>
       <c r="H1379" t="n">
         <v>21758</v>
@@ -40389,7 +40389,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G1380" t="n">
-        <v>15.3897657394409</v>
+        <v>15.3897638320923</v>
       </c>
       <c r="H1380" t="n">
         <v>40488</v>
@@ -40418,7 +40418,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G1381" t="n">
-        <v>15.3427000045776</v>
+        <v>15.342700958252</v>
       </c>
       <c r="H1381" t="n">
         <v>50235</v>
@@ -40447,7 +40447,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G1382" t="n">
-        <v>16.3310356140137</v>
+        <v>16.331033706665</v>
       </c>
       <c r="H1382" t="n">
         <v>103542</v>
@@ -40563,7 +40563,7 @@
         <v>17.5</v>
       </c>
       <c r="G1386" t="n">
-        <v>16.4722232818604</v>
+        <v>16.4722270965576</v>
       </c>
       <c r="H1386" t="n">
         <v>49142</v>
@@ -40650,7 +40650,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1389" t="n">
-        <v>16.1427803039551</v>
+        <v>16.1427822113037</v>
       </c>
       <c r="H1389" t="n">
         <v>29540</v>
@@ -40824,7 +40824,7 @@
         <v>17.5100002288818</v>
       </c>
       <c r="G1395" t="n">
-        <v>16.4816398620605</v>
+        <v>16.4816379547119</v>
       </c>
       <c r="H1395" t="n">
         <v>45316</v>
@@ -40853,7 +40853,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1396" t="n">
-        <v>16.3027973175049</v>
+        <v>16.3027954101562</v>
       </c>
       <c r="H1396" t="n">
         <v>25665</v>
@@ -40911,7 +40911,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1398" t="n">
-        <v>17.6017513275146</v>
+        <v>17.601749420166</v>
       </c>
       <c r="H1398" t="n">
         <v>58906</v>
@@ -40940,7 +40940,7 @@
         <v>18.6100006103516</v>
       </c>
       <c r="G1399" t="n">
-        <v>17.5170364379883</v>
+        <v>17.5170345306396</v>
       </c>
       <c r="H1399" t="n">
         <v>37800</v>
@@ -40969,7 +40969,7 @@
         <v>18.3899993896484</v>
       </c>
       <c r="G1400" t="n">
-        <v>17.3099555969238</v>
+        <v>17.3099536895752</v>
       </c>
       <c r="H1400" t="n">
         <v>41196</v>
@@ -41027,7 +41027,7 @@
         <v>17.9799995422363</v>
       </c>
       <c r="G1402" t="n">
-        <v>16.924036026001</v>
+        <v>16.9240341186523</v>
       </c>
       <c r="H1402" t="n">
         <v>29605</v>
@@ -41259,7 +41259,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1410" t="n">
-        <v>16.1427803039551</v>
+        <v>16.1427822113037</v>
       </c>
       <c r="H1410" t="n">
         <v>34518</v>
@@ -41288,7 +41288,7 @@
         <v>17.75</v>
       </c>
       <c r="G1411" t="n">
-        <v>16.7075424194336</v>
+        <v>16.707540512085</v>
       </c>
       <c r="H1411" t="n">
         <v>19844</v>
@@ -41317,7 +41317,7 @@
         <v>17.5</v>
       </c>
       <c r="G1412" t="n">
-        <v>16.4722232818604</v>
+        <v>16.4722270965576</v>
       </c>
       <c r="H1412" t="n">
         <v>14648</v>
@@ -41375,7 +41375,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1414" t="n">
-        <v>16.2651481628418</v>
+        <v>16.2651462554932</v>
       </c>
       <c r="H1414" t="n">
         <v>10327</v>
@@ -41549,7 +41549,7 @@
         <v>18.5400009155273</v>
       </c>
       <c r="G1420" t="n">
-        <v>17.4511470794678</v>
+        <v>17.4511489868164</v>
       </c>
       <c r="H1420" t="n">
         <v>19501</v>
@@ -41665,7 +41665,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1424" t="n">
-        <v>18.1665134429932</v>
+        <v>18.1665115356445</v>
       </c>
       <c r="H1424" t="n">
         <v>46129</v>
@@ -41694,7 +41694,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1425" t="n">
-        <v>18.2794628143311</v>
+        <v>18.2794647216797</v>
       </c>
       <c r="H1425" t="n">
         <v>37775</v>
@@ -41723,7 +41723,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G1426" t="n">
-        <v>18.3924160003662</v>
+        <v>18.3924179077148</v>
       </c>
       <c r="H1426" t="n">
         <v>22265</v>
@@ -41752,7 +41752,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1427" t="n">
-        <v>18.4488906860352</v>
+        <v>18.4488925933838</v>
       </c>
       <c r="H1427" t="n">
         <v>26648</v>
@@ -41781,7 +41781,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G1428" t="n">
-        <v>18.9760036468506</v>
+        <v>18.976001739502</v>
       </c>
       <c r="H1428" t="n">
         <v>59273</v>
@@ -41868,7 +41868,7 @@
         <v>20.6200008392334</v>
       </c>
       <c r="G1431" t="n">
-        <v>19.4089889526367</v>
+        <v>19.4089870452881</v>
       </c>
       <c r="H1431" t="n">
         <v>93143</v>
@@ -41955,7 +41955,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1434" t="n">
-        <v>20.3314323425293</v>
+        <v>20.3314342498779</v>
       </c>
       <c r="H1434" t="n">
         <v>44757</v>
@@ -42013,7 +42013,7 @@
         <v>21.5</v>
       </c>
       <c r="G1436" t="n">
-        <v>20.2373046875</v>
+        <v>20.2373065948486</v>
       </c>
       <c r="H1436" t="n">
         <v>70267</v>
@@ -42042,7 +42042,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1437" t="n">
-        <v>20.1431789398193</v>
+        <v>20.1431770324707</v>
       </c>
       <c r="H1437" t="n">
         <v>55372</v>
@@ -42129,7 +42129,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1440" t="n">
-        <v>20.3314323425293</v>
+        <v>20.3314342498779</v>
       </c>
       <c r="H1440" t="n">
         <v>62704</v>
@@ -42187,7 +42187,7 @@
         <v>22.0400009155273</v>
       </c>
       <c r="G1442" t="n">
-        <v>20.7455940246582</v>
+        <v>20.7455921173096</v>
       </c>
       <c r="H1442" t="n">
         <v>66317</v>
@@ -42216,7 +42216,7 @@
         <v>21.9599990844727</v>
       </c>
       <c r="G1443" t="n">
-        <v>20.6702899932861</v>
+        <v>20.6702880859375</v>
       </c>
       <c r="H1443" t="n">
         <v>19170</v>
@@ -42245,7 +42245,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1444" t="n">
-        <v>20.6138134002686</v>
+        <v>20.6138114929199</v>
       </c>
       <c r="H1444" t="n">
         <v>23345</v>
@@ -42303,7 +42303,7 @@
         <v>21.9799995422363</v>
       </c>
       <c r="G1446" t="n">
-        <v>20.689115524292</v>
+        <v>20.6891136169434</v>
       </c>
       <c r="H1446" t="n">
         <v>31994</v>
@@ -42361,7 +42361,7 @@
         <v>21.6000003814697</v>
       </c>
       <c r="G1448" t="n">
-        <v>20.3314323425293</v>
+        <v>20.3314342498779</v>
       </c>
       <c r="H1448" t="n">
         <v>25255</v>
@@ -42477,7 +42477,7 @@
         <v>20.8199996948242</v>
       </c>
       <c r="G1452" t="n">
-        <v>19.5972385406494</v>
+        <v>19.5972423553467</v>
       </c>
       <c r="H1452" t="n">
         <v>17204</v>
@@ -42535,7 +42535,7 @@
         <v>20.6399993896484</v>
       </c>
       <c r="G1454" t="n">
-        <v>19.4278125762939</v>
+        <v>19.4278106689453</v>
       </c>
       <c r="H1454" t="n">
         <v>22893</v>
@@ -42564,7 +42564,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1455" t="n">
-        <v>18.919527053833</v>
+        <v>18.9195289611816</v>
       </c>
       <c r="H1455" t="n">
         <v>30892</v>
@@ -42593,7 +42593,7 @@
         <v>20.4799995422363</v>
       </c>
       <c r="G1456" t="n">
-        <v>19.2772083282471</v>
+        <v>19.2772102355957</v>
       </c>
       <c r="H1456" t="n">
         <v>17560</v>
@@ -42622,7 +42622,7 @@
         <v>20</v>
       </c>
       <c r="G1457" t="n">
-        <v>18.8254013061523</v>
+        <v>18.8253974914551</v>
       </c>
       <c r="H1457" t="n">
         <v>34122</v>
@@ -42651,7 +42651,7 @@
         <v>20.1800003051758</v>
       </c>
       <c r="G1458" t="n">
-        <v>18.9948272705078</v>
+        <v>18.9948291778564</v>
       </c>
       <c r="H1458" t="n">
         <v>42575</v>
@@ -42709,7 +42709,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1460" t="n">
-        <v>19.0136528015137</v>
+        <v>19.0136547088623</v>
       </c>
       <c r="H1460" t="n">
         <v>14073</v>
@@ -42738,7 +42738,7 @@
         <v>20.5</v>
       </c>
       <c r="G1461" t="n">
-        <v>19.2960357666016</v>
+        <v>19.2960338592529</v>
       </c>
       <c r="H1461" t="n">
         <v>36389</v>
@@ -42796,7 +42796,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G1463" t="n">
-        <v>19.7854976654053</v>
+        <v>19.785493850708</v>
       </c>
       <c r="H1463" t="n">
         <v>22649</v>
@@ -42825,7 +42825,7 @@
         <v>20.5</v>
       </c>
       <c r="G1464" t="n">
-        <v>19.2960357666016</v>
+        <v>19.2960338592529</v>
       </c>
       <c r="H1464" t="n">
         <v>37266</v>
@@ -42883,7 +42883,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1466" t="n">
-        <v>18.919527053833</v>
+        <v>18.9195289611816</v>
       </c>
       <c r="H1466" t="n">
         <v>63807</v>
@@ -42912,7 +42912,7 @@
         <v>19.5699996948242</v>
       </c>
       <c r="G1467" t="n">
-        <v>18.420654296875</v>
+        <v>18.4206523895264</v>
       </c>
       <c r="H1467" t="n">
         <v>29950</v>
@@ -42941,7 +42941,7 @@
         <v>19.1599998474121</v>
       </c>
       <c r="G1468" t="n">
-        <v>18.0347328186035</v>
+        <v>18.0347347259521</v>
       </c>
       <c r="H1468" t="n">
         <v>60355</v>
@@ -42999,7 +42999,7 @@
         <v>20</v>
       </c>
       <c r="G1470" t="n">
-        <v>18.8254013061523</v>
+        <v>18.8253974914551</v>
       </c>
       <c r="H1470" t="n">
         <v>59374</v>
@@ -43057,7 +43057,7 @@
         <v>19.4200000762939</v>
       </c>
       <c r="G1472" t="n">
-        <v>18.2794628143311</v>
+        <v>18.2794647216797</v>
       </c>
       <c r="H1472" t="n">
         <v>34855</v>
@@ -43115,7 +43115,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G1474" t="n">
-        <v>18.9760036468506</v>
+        <v>18.976001739502</v>
       </c>
       <c r="H1474" t="n">
         <v>35643</v>
@@ -43144,7 +43144,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1475" t="n">
-        <v>18.919527053833</v>
+        <v>18.9195289611816</v>
       </c>
       <c r="H1475" t="n">
         <v>16452</v>
@@ -43202,7 +43202,7 @@
         <v>20</v>
       </c>
       <c r="G1477" t="n">
-        <v>18.8254013061523</v>
+        <v>18.8253974914551</v>
       </c>
       <c r="H1477" t="n">
         <v>12872</v>
@@ -43231,7 +43231,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1478" t="n">
-        <v>18.7312717437744</v>
+        <v>18.731273651123</v>
       </c>
       <c r="H1478" t="n">
         <v>24681</v>
@@ -43289,7 +43289,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1480" t="n">
-        <v>18.4488906860352</v>
+        <v>18.4488925933838</v>
       </c>
       <c r="H1480" t="n">
         <v>13485</v>
@@ -43405,7 +43405,7 @@
         <v>20</v>
       </c>
       <c r="G1484" t="n">
-        <v>18.8254013061523</v>
+        <v>18.8253974914551</v>
       </c>
       <c r="H1484" t="n">
         <v>18628</v>
@@ -43434,7 +43434,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G1485" t="n">
-        <v>18.787748336792</v>
+        <v>18.7877502441406</v>
       </c>
       <c r="H1485" t="n">
         <v>16716</v>
@@ -43463,7 +43463,7 @@
         <v>20.1000003814697</v>
       </c>
       <c r="G1486" t="n">
-        <v>18.919527053833</v>
+        <v>18.9195289611816</v>
       </c>
       <c r="H1486" t="n">
         <v>12322</v>
@@ -43492,7 +43492,7 @@
         <v>20</v>
       </c>
       <c r="G1487" t="n">
-        <v>18.8254013061523</v>
+        <v>18.8253974914551</v>
       </c>
       <c r="H1487" t="n">
         <v>28899</v>
@@ -43521,7 +43521,7 @@
         <v>20</v>
       </c>
       <c r="G1488" t="n">
-        <v>18.8254013061523</v>
+        <v>18.8253974914551</v>
       </c>
       <c r="H1488" t="n">
         <v>32266</v>
@@ -43550,7 +43550,7 @@
         <v>20</v>
       </c>
       <c r="G1489" t="n">
-        <v>18.8254013061523</v>
+        <v>18.8253974914551</v>
       </c>
       <c r="H1489" t="n">
         <v>14782</v>
@@ -43579,7 +43579,7 @@
         <v>20.3999996185303</v>
       </c>
       <c r="G1490" t="n">
-        <v>19.2019081115723</v>
+        <v>19.2019062042236</v>
       </c>
       <c r="H1490" t="n">
         <v>30756</v>
@@ -43666,7 +43666,7 @@
         <v>20</v>
       </c>
       <c r="G1493" t="n">
-        <v>18.8254013061523</v>
+        <v>18.8253974914551</v>
       </c>
       <c r="H1493" t="n">
         <v>10389</v>
@@ -43695,7 +43695,7 @@
         <v>20</v>
       </c>
       <c r="G1494" t="n">
-        <v>18.8254013061523</v>
+        <v>18.8253974914551</v>
       </c>
       <c r="H1494" t="n">
         <v>14503</v>
@@ -43724,7 +43724,7 @@
         <v>19.6000003814697</v>
       </c>
       <c r="G1495" t="n">
-        <v>18.4488906860352</v>
+        <v>18.4488925933838</v>
       </c>
       <c r="H1495" t="n">
         <v>24453</v>
@@ -43753,7 +43753,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G1496" t="n">
-        <v>18.787748336792</v>
+        <v>18.7877502441406</v>
       </c>
       <c r="H1496" t="n">
         <v>12980</v>
@@ -43782,7 +43782,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G1497" t="n">
-        <v>18.4300670623779</v>
+        <v>18.4300689697266</v>
       </c>
       <c r="H1497" t="n">
         <v>12302</v>
@@ -43811,7 +43811,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1498" t="n">
-        <v>18.7312717437744</v>
+        <v>18.731273651123</v>
       </c>
       <c r="H1498" t="n">
         <v>16836</v>
@@ -43927,7 +43927,7 @@
         <v>19.6200008392334</v>
       </c>
       <c r="G1502" t="n">
-        <v>18.4677181243896</v>
+        <v>18.4677200317383</v>
       </c>
       <c r="H1502" t="n">
         <v>24161</v>
@@ -43985,7 +43985,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1504" t="n">
-        <v>18.966588973999</v>
+        <v>18.9665927886963</v>
       </c>
       <c r="H1504" t="n">
         <v>43665</v>
@@ -44072,7 +44072,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1507" t="n">
-        <v>18.7850475311279</v>
+        <v>18.7850456237793</v>
       </c>
       <c r="H1507" t="n">
         <v>20257</v>
@@ -44159,7 +44159,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1510" t="n">
-        <v>18.2881889343262</v>
+        <v>18.2881870269775</v>
       </c>
       <c r="H1510" t="n">
         <v>12281</v>
@@ -44188,7 +44188,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1511" t="n">
-        <v>18.0015392303467</v>
+        <v>18.0015411376953</v>
       </c>
       <c r="H1511" t="n">
         <v>87259</v>
@@ -44391,7 +44391,7 @@
         <v>19.1399993896484</v>
       </c>
       <c r="G1518" t="n">
-        <v>18.2881889343262</v>
+        <v>18.2881870269775</v>
       </c>
       <c r="H1518" t="n">
         <v>22405</v>
@@ -44449,7 +44449,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G1520" t="n">
-        <v>18.6703872680664</v>
+        <v>18.670389175415</v>
       </c>
       <c r="H1520" t="n">
         <v>12532</v>
@@ -44507,7 +44507,7 @@
         <v>19.7399997711182</v>
       </c>
       <c r="G1522" t="n">
-        <v>18.8614864349365</v>
+        <v>18.8614845275879</v>
       </c>
       <c r="H1522" t="n">
         <v>18217</v>
@@ -44536,7 +44536,7 @@
         <v>20</v>
       </c>
       <c r="G1523" t="n">
-        <v>19.1099147796631</v>
+        <v>19.1099166870117</v>
       </c>
       <c r="H1523" t="n">
         <v>19100</v>
@@ -44623,7 +44623,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1526" t="n">
-        <v>19.2532386779785</v>
+        <v>19.2532405853271</v>
       </c>
       <c r="H1526" t="n">
         <v>11500</v>
@@ -44652,7 +44652,7 @@
         <v>20</v>
       </c>
       <c r="G1527" t="n">
-        <v>19.1099147796631</v>
+        <v>19.1099166870117</v>
       </c>
       <c r="H1527" t="n">
         <v>17288</v>
@@ -44739,7 +44739,7 @@
         <v>21</v>
       </c>
       <c r="G1530" t="n">
-        <v>20.0654125213623</v>
+        <v>20.0654106140137</v>
       </c>
       <c r="H1530" t="n">
         <v>27043</v>
@@ -44768,7 +44768,7 @@
         <v>21.0499992370605</v>
       </c>
       <c r="G1531" t="n">
-        <v>20.1131839752197</v>
+        <v>20.1131858825684</v>
       </c>
       <c r="H1531" t="n">
         <v>82889</v>
@@ -44797,7 +44797,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1532" t="n">
-        <v>20.4476089477539</v>
+        <v>20.4476108551025</v>
       </c>
       <c r="H1532" t="n">
         <v>43093</v>
@@ -44826,7 +44826,7 @@
         <v>21.3999996185303</v>
       </c>
       <c r="G1533" t="n">
-        <v>20.4476089477539</v>
+        <v>20.4476108551025</v>
       </c>
       <c r="H1533" t="n">
         <v>28092</v>
@@ -44855,7 +44855,7 @@
         <v>21.5499992370605</v>
       </c>
       <c r="G1534" t="n">
-        <v>20.5909328460693</v>
+        <v>20.590934753418</v>
       </c>
       <c r="H1534" t="n">
         <v>33246</v>
@@ -44971,7 +44971,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1538" t="n">
-        <v>20.2087364196777</v>
+        <v>20.2087345123291</v>
       </c>
       <c r="H1538" t="n">
         <v>18789</v>
@@ -45174,7 +45174,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1545" t="n">
-        <v>19.2532386779785</v>
+        <v>19.2532405853271</v>
       </c>
       <c r="H1545" t="n">
         <v>56735</v>
@@ -45203,7 +45203,7 @@
         <v>20.1499996185303</v>
       </c>
       <c r="G1546" t="n">
-        <v>19.2532386779785</v>
+        <v>19.2532405853271</v>
       </c>
       <c r="H1546" t="n">
         <v>18845</v>
@@ -45232,7 +45232,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1547" t="n">
-        <v>19.0143661499023</v>
+        <v>19.0143642425537</v>
       </c>
       <c r="H1547" t="n">
         <v>21451</v>
@@ -45261,7 +45261,7 @@
         <v>19.7199993133545</v>
       </c>
       <c r="G1548" t="n">
-        <v>18.8423748016357</v>
+        <v>18.8423767089844</v>
       </c>
       <c r="H1548" t="n">
         <v>47286</v>
@@ -45290,7 +45290,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1549" t="n">
-        <v>19.0143661499023</v>
+        <v>19.0143642425537</v>
       </c>
       <c r="H1549" t="n">
         <v>20675</v>
@@ -45348,7 +45348,7 @@
         <v>20</v>
       </c>
       <c r="G1551" t="n">
-        <v>19.1099147796631</v>
+        <v>19.1099166870117</v>
       </c>
       <c r="H1551" t="n">
         <v>8161</v>
@@ -45464,7 +45464,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1555" t="n">
-        <v>19.0143661499023</v>
+        <v>19.0143642425537</v>
       </c>
       <c r="H1555" t="n">
         <v>23405</v>
@@ -45493,7 +45493,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1556" t="n">
-        <v>19.0143661499023</v>
+        <v>19.0143642425537</v>
       </c>
       <c r="H1556" t="n">
         <v>24871</v>
@@ -45522,7 +45522,7 @@
         <v>20.0499992370605</v>
       </c>
       <c r="G1557" t="n">
-        <v>19.1576900482178</v>
+        <v>19.1576881408691</v>
       </c>
       <c r="H1557" t="n">
         <v>21254</v>
@@ -45551,7 +45551,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1558" t="n">
-        <v>19.0143661499023</v>
+        <v>19.0143642425537</v>
       </c>
       <c r="H1558" t="n">
         <v>34825</v>
@@ -45580,7 +45580,7 @@
         <v>19.3799991607666</v>
       </c>
       <c r="G1559" t="n">
-        <v>18.517505645752</v>
+        <v>18.5175075531006</v>
       </c>
       <c r="H1559" t="n">
         <v>135355</v>
@@ -45696,7 +45696,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G1563" t="n">
-        <v>18.4219589233398</v>
+        <v>18.4219570159912</v>
       </c>
       <c r="H1563" t="n">
         <v>37743</v>
@@ -45725,7 +45725,7 @@
         <v>19.3600006103516</v>
       </c>
       <c r="G1564" t="n">
-        <v>18.4983997344971</v>
+        <v>18.4983978271484</v>
       </c>
       <c r="H1564" t="n">
         <v>11595</v>
@@ -45754,7 +45754,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1565" t="n">
-        <v>18.4410667419434</v>
+        <v>18.441068649292</v>
       </c>
       <c r="H1565" t="n">
         <v>16172</v>
@@ -45783,7 +45783,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1566" t="n">
-        <v>18.4792861938477</v>
+        <v>18.4792881011963</v>
       </c>
       <c r="H1566" t="n">
         <v>7386</v>
@@ -45986,7 +45986,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1573" t="n">
-        <v>16.4345283508301</v>
+        <v>16.4345264434814</v>
       </c>
       <c r="H1573" t="n">
         <v>46583</v>
@@ -46015,7 +46015,7 @@
         <v>17.2000007629395</v>
       </c>
       <c r="G1574" t="n">
-        <v>16.4345283508301</v>
+        <v>16.4345264434814</v>
       </c>
       <c r="H1574" t="n">
         <v>30982</v>
@@ -46334,7 +46334,7 @@
         <v>17.3199996948242</v>
       </c>
       <c r="G1585" t="n">
-        <v>16.5491847991943</v>
+        <v>16.549186706543</v>
       </c>
       <c r="H1585" t="n">
         <v>15882</v>
@@ -46363,7 +46363,7 @@
         <v>17.2800006866455</v>
       </c>
       <c r="G1586" t="n">
-        <v>16.5109672546387</v>
+        <v>16.51096534729</v>
       </c>
       <c r="H1586" t="n">
         <v>19063</v>
@@ -46653,7 +46653,7 @@
         <v>15.960000038147</v>
       </c>
       <c r="G1596" t="n">
-        <v>15.2497119903564</v>
+        <v>15.2497129440308</v>
       </c>
       <c r="H1596" t="n">
         <v>106268</v>
@@ -46885,7 +46885,7 @@
         <v>15.2200002670288</v>
       </c>
       <c r="G1604" t="n">
-        <v>14.5426454544067</v>
+        <v>14.5426464080811</v>
       </c>
       <c r="H1604" t="n">
         <v>27387</v>
@@ -47001,7 +47001,7 @@
         <v>15.1400003433228</v>
       </c>
       <c r="G1608" t="n">
-        <v>14.4662065505981</v>
+        <v>14.4662055969238</v>
       </c>
       <c r="H1608" t="n">
         <v>25595</v>
@@ -47059,7 +47059,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G1610" t="n">
-        <v>13.7209196090698</v>
+        <v>13.7209186553955</v>
       </c>
       <c r="H1610" t="n">
         <v>60330</v>
@@ -47407,7 +47407,7 @@
         <v>14.5</v>
       </c>
       <c r="G1622" t="n">
-        <v>13.8546886444092</v>
+        <v>13.8546895980835</v>
       </c>
       <c r="H1622" t="n">
         <v>18389</v>
@@ -47465,7 +47465,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1624" t="n">
-        <v>13.7591390609741</v>
+        <v>13.7591381072998</v>
       </c>
       <c r="H1624" t="n">
         <v>47166</v>
@@ -47639,7 +47639,7 @@
         <v>14.7799997329712</v>
       </c>
       <c r="G1630" t="n">
-        <v>14.1222276687622</v>
+        <v>14.1222267150879</v>
       </c>
       <c r="H1630" t="n">
         <v>20458</v>
@@ -47668,7 +47668,7 @@
         <v>15.2799997329712</v>
       </c>
       <c r="G1631" t="n">
-        <v>14.5999746322632</v>
+        <v>14.5999755859375</v>
       </c>
       <c r="H1631" t="n">
         <v>13170</v>
@@ -47813,7 +47813,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G1636" t="n">
-        <v>15.6510200500488</v>
+        <v>15.6510210037231</v>
       </c>
       <c r="H1636" t="n">
         <v>64482</v>
@@ -47929,7 +47929,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1640" t="n">
-        <v>16.9313850402832</v>
+        <v>16.9313831329346</v>
       </c>
       <c r="H1640" t="n">
         <v>66899</v>
@@ -47987,7 +47987,7 @@
         <v>17.5</v>
       </c>
       <c r="G1642" t="n">
-        <v>16.7211761474609</v>
+        <v>16.7211742401123</v>
       </c>
       <c r="H1642" t="n">
         <v>22492</v>
@@ -48016,7 +48016,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1643" t="n">
-        <v>17.0078258514404</v>
+        <v>17.0078239440918</v>
       </c>
       <c r="H1643" t="n">
         <v>20323</v>
@@ -48161,7 +48161,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1648" t="n">
-        <v>16.7976169586182</v>
+        <v>16.7976150512695</v>
       </c>
       <c r="H1648" t="n">
         <v>33889</v>
@@ -48277,7 +48277,7 @@
         <v>18.0400009155273</v>
       </c>
       <c r="G1652" t="n">
-        <v>17.2371463775635</v>
+        <v>17.2371444702148</v>
       </c>
       <c r="H1652" t="n">
         <v>37099</v>
@@ -48335,7 +48335,7 @@
         <v>17.4799995422363</v>
       </c>
       <c r="G1654" t="n">
-        <v>16.7020645141602</v>
+        <v>16.7020664215088</v>
       </c>
       <c r="H1654" t="n">
         <v>25281</v>
@@ -48364,7 +48364,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1655" t="n">
-        <v>16.7785034179688</v>
+        <v>16.7785053253174</v>
       </c>
       <c r="H1655" t="n">
         <v>11530</v>
@@ -48393,7 +48393,7 @@
         <v>17.7800006866455</v>
       </c>
       <c r="G1656" t="n">
-        <v>16.9887142181396</v>
+        <v>16.9887161254883</v>
       </c>
       <c r="H1656" t="n">
         <v>9755</v>
@@ -48509,7 +48509,7 @@
         <v>18.0799999237061</v>
       </c>
       <c r="G1660" t="n">
-        <v>17.2753620147705</v>
+        <v>17.2753639221191</v>
       </c>
       <c r="H1660" t="n">
         <v>22611</v>
@@ -48596,7 +48596,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1663" t="n">
-        <v>18.5939464569092</v>
+        <v>18.5939483642578</v>
       </c>
       <c r="H1663" t="n">
         <v>24039</v>
@@ -48625,7 +48625,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G1664" t="n">
-        <v>18.1353092193604</v>
+        <v>18.1353073120117</v>
       </c>
       <c r="H1664" t="n">
         <v>31573</v>
@@ -48741,7 +48741,7 @@
         <v>19.4599990844727</v>
       </c>
       <c r="G1668" t="n">
-        <v>18.5939464569092</v>
+        <v>18.5939483642578</v>
       </c>
       <c r="H1668" t="n">
         <v>10258</v>
@@ -49089,7 +49089,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1680" t="n">
-        <v>18.0397567749023</v>
+        <v>18.039758682251</v>
       </c>
       <c r="H1680" t="n">
         <v>44497</v>
@@ -49147,7 +49147,7 @@
         <v>18.1599998474121</v>
       </c>
       <c r="G1682" t="n">
-        <v>17.3518028259277</v>
+        <v>17.3518047332764</v>
       </c>
       <c r="H1682" t="n">
         <v>23697</v>
@@ -49176,7 +49176,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1683" t="n">
-        <v>16.8740558624268</v>
+        <v>16.8740539550781</v>
       </c>
       <c r="H1683" t="n">
         <v>17529</v>
@@ -49205,7 +49205,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G1684" t="n">
-        <v>17.084264755249</v>
+        <v>17.0842628479004</v>
       </c>
       <c r="H1684" t="n">
         <v>18670</v>
@@ -49292,7 +49292,7 @@
         <v>17.8600006103516</v>
       </c>
       <c r="G1687" t="n">
-        <v>17.0651550292969</v>
+        <v>17.0651569366455</v>
       </c>
       <c r="H1687" t="n">
         <v>12268</v>
@@ -49321,7 +49321,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1688" t="n">
-        <v>17.332691192627</v>
+        <v>17.3326930999756</v>
       </c>
       <c r="H1688" t="n">
         <v>12378</v>
@@ -49379,7 +49379,7 @@
         <v>18.8400001525879</v>
       </c>
       <c r="G1690" t="n">
-        <v>18.0015392303467</v>
+        <v>18.0015411376953</v>
       </c>
       <c r="H1690" t="n">
         <v>16217</v>
@@ -49611,7 +49611,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G1698" t="n">
-        <v>17.4091320037842</v>
+        <v>17.4091339111328</v>
       </c>
       <c r="H1698" t="n">
         <v>13046</v>
@@ -49727,7 +49727,7 @@
         <v>18.2199993133545</v>
       </c>
       <c r="G1702" t="n">
-        <v>17.4091320037842</v>
+        <v>17.4091339111328</v>
       </c>
       <c r="H1702" t="n">
         <v>26535</v>
@@ -49901,7 +49901,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1708" t="n">
-        <v>18.0397567749023</v>
+        <v>18.039758682251</v>
       </c>
       <c r="H1708" t="n">
         <v>14891</v>
@@ -50075,7 +50075,7 @@
         <v>18.3400001525879</v>
       </c>
       <c r="G1714" t="n">
-        <v>17.5237941741943</v>
+        <v>17.5237922668457</v>
       </c>
       <c r="H1714" t="n">
         <v>11856</v>
@@ -50423,7 +50423,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1726" t="n">
-        <v>17.0078258514404</v>
+        <v>17.0078239440918</v>
       </c>
       <c r="H1726" t="n">
         <v>43506</v>
@@ -50452,7 +50452,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1727" t="n">
-        <v>16.7976169586182</v>
+        <v>16.7976150512695</v>
       </c>
       <c r="H1727" t="n">
         <v>17893</v>
@@ -50510,7 +50510,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1729" t="n">
-        <v>16.8167247772217</v>
+        <v>16.8167266845703</v>
       </c>
       <c r="H1729" t="n">
         <v>41467</v>
@@ -50684,7 +50684,7 @@
         <v>17.5</v>
       </c>
       <c r="G1735" t="n">
-        <v>16.7211761474609</v>
+        <v>16.7211742401123</v>
       </c>
       <c r="H1735" t="n">
         <v>21086</v>
@@ -50713,7 +50713,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1736" t="n">
-        <v>16.8740558624268</v>
+        <v>16.8740539550781</v>
       </c>
       <c r="H1736" t="n">
         <v>15731</v>
@@ -50829,7 +50829,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1740" t="n">
-        <v>15.8994493484497</v>
+        <v>15.8994483947754</v>
       </c>
       <c r="H1740" t="n">
         <v>38766</v>
@@ -50858,7 +50858,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1741" t="n">
-        <v>15.7847900390625</v>
+        <v>15.7847909927368</v>
       </c>
       <c r="H1741" t="n">
         <v>50266</v>
@@ -50945,7 +50945,7 @@
         <v>16.3799991607666</v>
       </c>
       <c r="G1744" t="n">
-        <v>15.6510200500488</v>
+        <v>15.6510210037231</v>
       </c>
       <c r="H1744" t="n">
         <v>12504</v>
@@ -50974,7 +50974,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G1745" t="n">
-        <v>15.459921836853</v>
+        <v>15.4599208831787</v>
       </c>
       <c r="H1745" t="n">
         <v>20801</v>
@@ -51293,7 +51293,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1756" t="n">
-        <v>15.6319103240967</v>
+        <v>15.631911277771</v>
       </c>
       <c r="H1756" t="n">
         <v>11827</v>
@@ -51351,7 +51351,7 @@
         <v>16.5200004577637</v>
       </c>
       <c r="G1758" t="n">
-        <v>15.7847900390625</v>
+        <v>15.7847909927368</v>
       </c>
       <c r="H1758" t="n">
         <v>7728</v>
@@ -51409,7 +51409,7 @@
         <v>16.6399993896484</v>
       </c>
       <c r="G1760" t="n">
-        <v>15.8994493484497</v>
+        <v>15.8994483947754</v>
       </c>
       <c r="H1760" t="n">
         <v>40853</v>
@@ -51438,7 +51438,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1761" t="n">
-        <v>15.9185600280762</v>
+        <v>15.9185609817505</v>
       </c>
       <c r="H1761" t="n">
         <v>13306</v>
@@ -51496,7 +51496,7 @@
         <v>16.6599998474121</v>
       </c>
       <c r="G1763" t="n">
-        <v>15.9185600280762</v>
+        <v>15.9185609817505</v>
       </c>
       <c r="H1763" t="n">
         <v>8838</v>
@@ -51554,7 +51554,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1765" t="n">
-        <v>16.6447372436523</v>
+        <v>16.6447353363037</v>
       </c>
       <c r="H1765" t="n">
         <v>43406</v>
@@ -51583,7 +51583,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1766" t="n">
-        <v>16.8740558624268</v>
+        <v>16.8740539550781</v>
       </c>
       <c r="H1766" t="n">
         <v>32815</v>
@@ -51612,7 +51612,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G1767" t="n">
-        <v>16.8167247772217</v>
+        <v>16.8167266845703</v>
       </c>
       <c r="H1767" t="n">
         <v>33266</v>
@@ -69424,6 +69424,35 @@
         <v>12354</v>
       </c>
       <c r="I2381" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2382">
+      <c r="A2382" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2382" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C2382" t="n">
+        <v>28.5499992370605</v>
+      </c>
+      <c r="D2382" t="n">
+        <v>29.3500003814697</v>
+      </c>
+      <c r="E2382" t="n">
+        <v>28.5499992370605</v>
+      </c>
+      <c r="F2382" t="n">
+        <v>28.8999996185303</v>
+      </c>
+      <c r="G2382" t="n">
+        <v>28.8999996185303</v>
+      </c>
+      <c r="H2382" t="n">
+        <v>11551</v>
+      </c>
+      <c r="I2382" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/WIIT.MI.xlsx
+++ b/data/WIIT.MI.xlsx
@@ -427,7 +427,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G2" t="n">
-        <v>4.49076414108276</v>
+        <v>4.49076509475708</v>
       </c>
       <c r="H2" t="n">
         <v>48400</v>
@@ -456,7 +456,7 @@
         <v>5.09999990463257</v>
       </c>
       <c r="G3" t="n">
-        <v>4.49076414108276</v>
+        <v>4.49076509475708</v>
       </c>
       <c r="H3" t="n">
         <v>24400</v>
@@ -485,7 +485,7 @@
         <v>5.125</v>
       </c>
       <c r="G4" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H4" t="n">
         <v>16400</v>
@@ -514,7 +514,7 @@
         <v>5.125</v>
       </c>
       <c r="G5" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -543,7 +543,7 @@
         <v>5.125</v>
       </c>
       <c r="G6" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -572,7 +572,7 @@
         <v>5.125</v>
       </c>
       <c r="G7" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -601,7 +601,7 @@
         <v>5.125</v>
       </c>
       <c r="G8" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H8" t="n">
         <v>0</v>
@@ -630,7 +630,7 @@
         <v>5.125</v>
       </c>
       <c r="G9" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H9" t="n">
         <v>0</v>
@@ -659,7 +659,7 @@
         <v>5.125</v>
       </c>
       <c r="G10" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H10" t="n">
         <v>0</v>
@@ -688,7 +688,7 @@
         <v>5.125</v>
       </c>
       <c r="G11" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -717,7 +717,7 @@
         <v>5.125</v>
       </c>
       <c r="G12" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -746,7 +746,7 @@
         <v>5.125</v>
       </c>
       <c r="G13" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -775,7 +775,7 @@
         <v>5.125</v>
       </c>
       <c r="G14" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H14" t="n">
         <v>0</v>
@@ -804,7 +804,7 @@
         <v>5.125</v>
       </c>
       <c r="G15" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -833,7 +833,7 @@
         <v>5.125</v>
       </c>
       <c r="G16" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -862,7 +862,7 @@
         <v>5.125</v>
       </c>
       <c r="G17" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -891,7 +891,7 @@
         <v>5.125</v>
       </c>
       <c r="G18" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -920,7 +920,7 @@
         <v>5.125</v>
       </c>
       <c r="G19" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -949,7 +949,7 @@
         <v>5.125</v>
       </c>
       <c r="G20" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -978,7 +978,7 @@
         <v>5.125</v>
       </c>
       <c r="G21" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H21" t="n">
         <v>0</v>
@@ -1007,7 +1007,7 @@
         <v>5.125</v>
       </c>
       <c r="G22" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -1036,7 +1036,7 @@
         <v>5.125</v>
       </c>
       <c r="G23" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
@@ -1065,7 +1065,7 @@
         <v>5.125</v>
       </c>
       <c r="G24" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
@@ -1094,7 +1094,7 @@
         <v>5.125</v>
       </c>
       <c r="G25" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -1123,7 +1123,7 @@
         <v>5.125</v>
       </c>
       <c r="G26" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
@@ -1152,7 +1152,7 @@
         <v>5.125</v>
       </c>
       <c r="G27" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -1181,7 +1181,7 @@
         <v>5.125</v>
       </c>
       <c r="G28" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H28" t="n">
         <v>0</v>
@@ -1210,7 +1210,7 @@
         <v>5.125</v>
       </c>
       <c r="G29" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1239,7 +1239,7 @@
         <v>5.125</v>
       </c>
       <c r="G30" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>5.125</v>
       </c>
       <c r="G31" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H31" t="n">
         <v>0</v>
@@ -1297,7 +1297,7 @@
         <v>5.125</v>
       </c>
       <c r="G32" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1326,7 +1326,7 @@
         <v>5.125</v>
       </c>
       <c r="G33" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
@@ -1355,7 +1355,7 @@
         <v>5.125</v>
       </c>
       <c r="G34" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>5.125</v>
       </c>
       <c r="G35" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
@@ -1413,7 +1413,7 @@
         <v>5.125</v>
       </c>
       <c r="G36" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -1442,7 +1442,7 @@
         <v>5.125</v>
       </c>
       <c r="G37" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -1471,7 +1471,7 @@
         <v>5.125</v>
       </c>
       <c r="G38" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1500,7 +1500,7 @@
         <v>5.125</v>
       </c>
       <c r="G39" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H39" t="n">
         <v>0</v>
@@ -1529,7 +1529,7 @@
         <v>5.125</v>
       </c>
       <c r="G40" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H40" t="n">
         <v>0</v>
@@ -1558,7 +1558,7 @@
         <v>5.125</v>
       </c>
       <c r="G41" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1587,7 +1587,7 @@
         <v>5.125</v>
       </c>
       <c r="G42" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>5.125</v>
       </c>
       <c r="G43" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H43" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>5.125</v>
       </c>
       <c r="G44" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>5.125</v>
       </c>
       <c r="G45" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
@@ -1703,7 +1703,7 @@
         <v>5.125</v>
       </c>
       <c r="G46" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>5.125</v>
       </c>
       <c r="G47" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -1761,7 +1761,7 @@
         <v>5.125</v>
       </c>
       <c r="G48" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H48" t="n">
         <v>0</v>
@@ -1790,7 +1790,7 @@
         <v>5.125</v>
       </c>
       <c r="G49" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H49" t="n">
         <v>0</v>
@@ -1819,7 +1819,7 @@
         <v>5.125</v>
       </c>
       <c r="G50" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -1848,7 +1848,7 @@
         <v>5.125</v>
       </c>
       <c r="G51" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -1877,7 +1877,7 @@
         <v>5.125</v>
       </c>
       <c r="G52" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1906,7 +1906,7 @@
         <v>5.125</v>
       </c>
       <c r="G53" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
         <v>5.125</v>
       </c>
       <c r="G54" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -1964,7 +1964,7 @@
         <v>5.125</v>
       </c>
       <c r="G55" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H55" t="n">
         <v>0</v>
@@ -1993,7 +1993,7 @@
         <v>5.125</v>
       </c>
       <c r="G56" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         <v>5.125</v>
       </c>
       <c r="G57" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
         <v>5.125</v>
       </c>
       <c r="G58" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2080,7 +2080,7 @@
         <v>5.125</v>
       </c>
       <c r="G59" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
         <v>5.125</v>
       </c>
       <c r="G60" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
@@ -2138,7 +2138,7 @@
         <v>5.125</v>
       </c>
       <c r="G61" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
@@ -2167,7 +2167,7 @@
         <v>5.125</v>
       </c>
       <c r="G62" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
@@ -2196,7 +2196,7 @@
         <v>5.125</v>
       </c>
       <c r="G63" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2225,7 +2225,7 @@
         <v>5.125</v>
       </c>
       <c r="G64" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H64" t="n">
         <v>0</v>
@@ -2254,7 +2254,7 @@
         <v>5.125</v>
       </c>
       <c r="G65" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
@@ -2283,7 +2283,7 @@
         <v>5.125</v>
       </c>
       <c r="G66" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H66" t="n">
         <v>0</v>
@@ -2312,7 +2312,7 @@
         <v>5.125</v>
       </c>
       <c r="G67" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H67" t="n">
         <v>0</v>
@@ -2341,7 +2341,7 @@
         <v>5.125</v>
       </c>
       <c r="G68" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
@@ -2370,7 +2370,7 @@
         <v>5.125</v>
       </c>
       <c r="G69" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H69" t="n">
         <v>0</v>
@@ -2399,7 +2399,7 @@
         <v>5.125</v>
       </c>
       <c r="G70" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H70" t="n">
         <v>0</v>
@@ -2428,7 +2428,7 @@
         <v>5.125</v>
       </c>
       <c r="G71" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H71" t="n">
         <v>0</v>
@@ -2457,7 +2457,7 @@
         <v>5.125</v>
       </c>
       <c r="G72" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H72" t="n">
         <v>0</v>
@@ -2486,7 +2486,7 @@
         <v>5.125</v>
       </c>
       <c r="G73" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -2515,7 +2515,7 @@
         <v>5.125</v>
       </c>
       <c r="G74" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H74" t="n">
         <v>0</v>
@@ -2544,7 +2544,7 @@
         <v>5.125</v>
       </c>
       <c r="G75" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>5.125</v>
       </c>
       <c r="G76" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -2602,7 +2602,7 @@
         <v>5.125</v>
       </c>
       <c r="G77" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
@@ -2631,7 +2631,7 @@
         <v>5.125</v>
       </c>
       <c r="G78" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H78" t="n">
         <v>0</v>
@@ -2660,7 +2660,7 @@
         <v>5.125</v>
       </c>
       <c r="G79" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
@@ -2689,7 +2689,7 @@
         <v>5.125</v>
       </c>
       <c r="G80" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H80" t="n">
         <v>0</v>
@@ -2718,7 +2718,7 @@
         <v>5.125</v>
       </c>
       <c r="G81" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H81" t="n">
         <v>0</v>
@@ -2747,7 +2747,7 @@
         <v>5.125</v>
       </c>
       <c r="G82" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -2776,7 +2776,7 @@
         <v>5.125</v>
       </c>
       <c r="G83" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H83" t="n">
         <v>0</v>
@@ -2805,7 +2805,7 @@
         <v>5.125</v>
       </c>
       <c r="G84" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>5.125</v>
       </c>
       <c r="G85" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
@@ -2863,7 +2863,7 @@
         <v>5.125</v>
       </c>
       <c r="G86" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H86" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
         <v>5.125</v>
       </c>
       <c r="G87" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
@@ -2921,7 +2921,7 @@
         <v>5.125</v>
       </c>
       <c r="G88" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
@@ -2950,7 +2950,7 @@
         <v>5.125</v>
       </c>
       <c r="G89" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
@@ -2979,7 +2979,7 @@
         <v>5.125</v>
       </c>
       <c r="G90" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H90" t="n">
         <v>0</v>
@@ -3008,7 +3008,7 @@
         <v>5.125</v>
       </c>
       <c r="G91" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H91" t="n">
         <v>0</v>
@@ -3037,7 +3037,7 @@
         <v>5.125</v>
       </c>
       <c r="G92" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
@@ -3066,7 +3066,7 @@
         <v>5.125</v>
       </c>
       <c r="G93" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H93" t="n">
         <v>0</v>
@@ -3095,7 +3095,7 @@
         <v>5.125</v>
       </c>
       <c r="G94" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H94" t="n">
         <v>0</v>
@@ -3124,7 +3124,7 @@
         <v>5.125</v>
       </c>
       <c r="G95" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H95" t="n">
         <v>0</v>
@@ -3153,7 +3153,7 @@
         <v>5.125</v>
       </c>
       <c r="G96" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H96" t="n">
         <v>0</v>
@@ -3182,7 +3182,7 @@
         <v>5.125</v>
       </c>
       <c r="G97" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H97" t="n">
         <v>0</v>
@@ -3211,7 +3211,7 @@
         <v>5.125</v>
       </c>
       <c r="G98" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H98" t="n">
         <v>0</v>
@@ -3240,7 +3240,7 @@
         <v>5.125</v>
       </c>
       <c r="G99" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H99" t="n">
         <v>0</v>
@@ -3269,7 +3269,7 @@
         <v>5.125</v>
       </c>
       <c r="G100" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H100" t="n">
         <v>0</v>
@@ -3298,7 +3298,7 @@
         <v>5.125</v>
       </c>
       <c r="G101" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H101" t="n">
         <v>0</v>
@@ -3327,7 +3327,7 @@
         <v>5.125</v>
       </c>
       <c r="G102" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H102" t="n">
         <v>0</v>
@@ -3356,7 +3356,7 @@
         <v>5.125</v>
       </c>
       <c r="G103" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H103" t="n">
         <v>0</v>
@@ -3385,7 +3385,7 @@
         <v>5.125</v>
       </c>
       <c r="G104" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H104" t="n">
         <v>0</v>
@@ -3414,7 +3414,7 @@
         <v>5.125</v>
       </c>
       <c r="G105" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H105" t="n">
         <v>0</v>
@@ -3443,7 +3443,7 @@
         <v>5.125</v>
       </c>
       <c r="G106" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H106" t="n">
         <v>0</v>
@@ -3472,7 +3472,7 @@
         <v>5.125</v>
       </c>
       <c r="G107" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H107" t="n">
         <v>0</v>
@@ -3501,7 +3501,7 @@
         <v>5.125</v>
       </c>
       <c r="G108" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H108" t="n">
         <v>0</v>
@@ -3530,7 +3530,7 @@
         <v>5.125</v>
       </c>
       <c r="G109" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H109" t="n">
         <v>0</v>
@@ -3559,7 +3559,7 @@
         <v>5.125</v>
       </c>
       <c r="G110" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H110" t="n">
         <v>0</v>
@@ -3588,7 +3588,7 @@
         <v>5.125</v>
       </c>
       <c r="G111" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3617,7 +3617,7 @@
         <v>5.125</v>
       </c>
       <c r="G112" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3646,7 +3646,7 @@
         <v>5.125</v>
       </c>
       <c r="G113" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -3675,7 +3675,7 @@
         <v>5.125</v>
       </c>
       <c r="G114" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3704,7 +3704,7 @@
         <v>5.125</v>
       </c>
       <c r="G115" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H115" t="n">
         <v>0</v>
@@ -3733,7 +3733,7 @@
         <v>5.125</v>
       </c>
       <c r="G116" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -3762,7 +3762,7 @@
         <v>5.125</v>
       </c>
       <c r="G117" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H117" t="n">
         <v>0</v>
@@ -3791,7 +3791,7 @@
         <v>5.125</v>
       </c>
       <c r="G118" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H118" t="n">
         <v>0</v>
@@ -3820,7 +3820,7 @@
         <v>5.125</v>
       </c>
       <c r="G119" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H119" t="n">
         <v>0</v>
@@ -3849,7 +3849,7 @@
         <v>5.125</v>
       </c>
       <c r="G120" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H120" t="n">
         <v>0</v>
@@ -3878,7 +3878,7 @@
         <v>5.125</v>
       </c>
       <c r="G121" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H121" t="n">
         <v>0</v>
@@ -3907,7 +3907,7 @@
         <v>5.125</v>
       </c>
       <c r="G122" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H122" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
         <v>5.125</v>
       </c>
       <c r="G123" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H123" t="n">
         <v>0</v>
@@ -3965,7 +3965,7 @@
         <v>5.125</v>
       </c>
       <c r="G124" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H124" t="n">
         <v>0</v>
@@ -3994,7 +3994,7 @@
         <v>5.125</v>
       </c>
       <c r="G125" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H125" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>5.125</v>
       </c>
       <c r="G126" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H126" t="n">
         <v>0</v>
@@ -4052,7 +4052,7 @@
         <v>5.125</v>
       </c>
       <c r="G127" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H127" t="n">
         <v>0</v>
@@ -4081,7 +4081,7 @@
         <v>5.125</v>
       </c>
       <c r="G128" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H128" t="n">
         <v>0</v>
@@ -4110,7 +4110,7 @@
         <v>5.125</v>
       </c>
       <c r="G129" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
         <v>5.125</v>
       </c>
       <c r="G130" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H130" t="n">
         <v>0</v>
@@ -4168,7 +4168,7 @@
         <v>5.125</v>
       </c>
       <c r="G131" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H131" t="n">
         <v>0</v>
@@ -4197,7 +4197,7 @@
         <v>5.125</v>
       </c>
       <c r="G132" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H132" t="n">
         <v>0</v>
@@ -4226,7 +4226,7 @@
         <v>5.125</v>
       </c>
       <c r="G133" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H133" t="n">
         <v>0</v>
@@ -4255,7 +4255,7 @@
         <v>5.125</v>
       </c>
       <c r="G134" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H134" t="n">
         <v>0</v>
@@ -4284,7 +4284,7 @@
         <v>5.125</v>
       </c>
       <c r="G135" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H135" t="n">
         <v>0</v>
@@ -4313,7 +4313,7 @@
         <v>5.125</v>
       </c>
       <c r="G136" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>5.125</v>
       </c>
       <c r="G137" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H137" t="n">
         <v>0</v>
@@ -4371,7 +4371,7 @@
         <v>5.125</v>
       </c>
       <c r="G138" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>5.125</v>
       </c>
       <c r="G139" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H139" t="n">
         <v>0</v>
@@ -4429,7 +4429,7 @@
         <v>5.125</v>
       </c>
       <c r="G140" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H140" t="n">
         <v>0</v>
@@ -4458,7 +4458,7 @@
         <v>5.125</v>
       </c>
       <c r="G141" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H141" t="n">
         <v>0</v>
@@ -4487,7 +4487,7 @@
         <v>5.125</v>
       </c>
       <c r="G142" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H142" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>5.125</v>
       </c>
       <c r="G143" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H143" t="n">
         <v>0</v>
@@ -4545,7 +4545,7 @@
         <v>5.125</v>
       </c>
       <c r="G144" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H144" t="n">
         <v>0</v>
@@ -4574,7 +4574,7 @@
         <v>5.125</v>
       </c>
       <c r="G145" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H145" t="n">
         <v>0</v>
@@ -4603,7 +4603,7 @@
         <v>5.125</v>
       </c>
       <c r="G146" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H146" t="n">
         <v>0</v>
@@ -4632,7 +4632,7 @@
         <v>5.125</v>
       </c>
       <c r="G147" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H147" t="n">
         <v>0</v>
@@ -4661,7 +4661,7 @@
         <v>5.125</v>
       </c>
       <c r="G148" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H148" t="n">
         <v>0</v>
@@ -4690,7 +4690,7 @@
         <v>5.125</v>
       </c>
       <c r="G149" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H149" t="n">
         <v>0</v>
@@ -4719,7 +4719,7 @@
         <v>5.125</v>
       </c>
       <c r="G150" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H150" t="n">
         <v>0</v>
@@ -4748,7 +4748,7 @@
         <v>5.125</v>
       </c>
       <c r="G151" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H151" t="n">
         <v>0</v>
@@ -4777,7 +4777,7 @@
         <v>5.125</v>
       </c>
       <c r="G152" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H152" t="n">
         <v>0</v>
@@ -4806,7 +4806,7 @@
         <v>5.125</v>
       </c>
       <c r="G153" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H153" t="n">
         <v>0</v>
@@ -4835,7 +4835,7 @@
         <v>5.125</v>
       </c>
       <c r="G154" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H154" t="n">
         <v>0</v>
@@ -4864,7 +4864,7 @@
         <v>5.125</v>
       </c>
       <c r="G155" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H155" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         <v>5.125</v>
       </c>
       <c r="G156" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H156" t="n">
         <v>0</v>
@@ -4922,7 +4922,7 @@
         <v>5.125</v>
       </c>
       <c r="G157" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H157" t="n">
         <v>0</v>
@@ -4951,7 +4951,7 @@
         <v>5.125</v>
       </c>
       <c r="G158" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H158" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
         <v>5.125</v>
       </c>
       <c r="G159" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>5.125</v>
       </c>
       <c r="G160" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>5.125</v>
       </c>
       <c r="G161" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H161" t="n">
         <v>0</v>
@@ -5067,7 +5067,7 @@
         <v>5.125</v>
       </c>
       <c r="G162" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H162" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>5.125</v>
       </c>
       <c r="G163" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H163" t="n">
         <v>0</v>
@@ -5125,7 +5125,7 @@
         <v>5.125</v>
       </c>
       <c r="G164" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H164" t="n">
         <v>0</v>
@@ -5154,7 +5154,7 @@
         <v>5.125</v>
       </c>
       <c r="G165" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>5.125</v>
       </c>
       <c r="G166" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H166" t="n">
         <v>0</v>
@@ -5212,7 +5212,7 @@
         <v>5.125</v>
       </c>
       <c r="G167" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H167" t="n">
         <v>0</v>
@@ -5241,7 +5241,7 @@
         <v>5.125</v>
       </c>
       <c r="G168" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H168" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>5.125</v>
       </c>
       <c r="G169" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H169" t="n">
         <v>0</v>
@@ -5299,7 +5299,7 @@
         <v>5.125</v>
       </c>
       <c r="G170" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H170" t="n">
         <v>0</v>
@@ -5328,7 +5328,7 @@
         <v>5.125</v>
       </c>
       <c r="G171" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H171" t="n">
         <v>0</v>
@@ -5357,7 +5357,7 @@
         <v>5.125</v>
       </c>
       <c r="G172" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H172" t="n">
         <v>0</v>
@@ -5386,7 +5386,7 @@
         <v>5.125</v>
       </c>
       <c r="G173" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H173" t="n">
         <v>0</v>
@@ -5415,7 +5415,7 @@
         <v>5.125</v>
       </c>
       <c r="G174" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>5.125</v>
       </c>
       <c r="G175" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -5473,7 +5473,7 @@
         <v>5.125</v>
       </c>
       <c r="G176" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
         <v>5.125</v>
       </c>
       <c r="G177" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -5531,7 +5531,7 @@
         <v>5.125</v>
       </c>
       <c r="G178" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
         <v>5.125</v>
       </c>
       <c r="G179" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H179" t="n">
         <v>0</v>
@@ -5589,7 +5589,7 @@
         <v>5.125</v>
       </c>
       <c r="G180" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -5618,7 +5618,7 @@
         <v>5.125</v>
       </c>
       <c r="G181" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H181" t="n">
         <v>0</v>
@@ -5647,7 +5647,7 @@
         <v>5.125</v>
       </c>
       <c r="G182" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H182" t="n">
         <v>0</v>
@@ -5676,7 +5676,7 @@
         <v>5.125</v>
       </c>
       <c r="G183" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H183" t="n">
         <v>0</v>
@@ -5705,7 +5705,7 @@
         <v>5.125</v>
       </c>
       <c r="G184" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H184" t="n">
         <v>0</v>
@@ -5734,7 +5734,7 @@
         <v>5.125</v>
       </c>
       <c r="G185" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H185" t="n">
         <v>0</v>
@@ -5763,7 +5763,7 @@
         <v>5.125</v>
       </c>
       <c r="G186" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H186" t="n">
         <v>0</v>
@@ -5792,7 +5792,7 @@
         <v>5.125</v>
       </c>
       <c r="G187" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H187" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>5.125</v>
       </c>
       <c r="G188" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H188" t="n">
         <v>0</v>
@@ -5850,7 +5850,7 @@
         <v>5.125</v>
       </c>
       <c r="G189" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H189" t="n">
         <v>0</v>
@@ -5879,7 +5879,7 @@
         <v>5.125</v>
       </c>
       <c r="G190" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>5.125</v>
       </c>
       <c r="G191" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H191" t="n">
         <v>0</v>
@@ -5937,7 +5937,7 @@
         <v>5.125</v>
       </c>
       <c r="G192" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H192" t="n">
         <v>0</v>
@@ -5966,7 +5966,7 @@
         <v>5.125</v>
       </c>
       <c r="G193" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -5995,7 +5995,7 @@
         <v>5.125</v>
       </c>
       <c r="G194" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -6024,7 +6024,7 @@
         <v>5.125</v>
       </c>
       <c r="G195" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -6053,7 +6053,7 @@
         <v>5.125</v>
       </c>
       <c r="G196" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H196" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>5.125</v>
       </c>
       <c r="G197" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H197" t="n">
         <v>0</v>
@@ -6111,7 +6111,7 @@
         <v>5.125</v>
       </c>
       <c r="G198" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H198" t="n">
         <v>0</v>
@@ -6140,7 +6140,7 @@
         <v>5.125</v>
       </c>
       <c r="G199" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H199" t="n">
         <v>0</v>
@@ -6169,7 +6169,7 @@
         <v>5.125</v>
       </c>
       <c r="G200" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H200" t="n">
         <v>0</v>
@@ -6198,7 +6198,7 @@
         <v>5.125</v>
       </c>
       <c r="G201" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H201" t="n">
         <v>0</v>
@@ -6227,7 +6227,7 @@
         <v>5.125</v>
       </c>
       <c r="G202" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H202" t="n">
         <v>0</v>
@@ -6256,7 +6256,7 @@
         <v>5.125</v>
       </c>
       <c r="G203" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H203" t="n">
         <v>0</v>
@@ -6285,7 +6285,7 @@
         <v>5.125</v>
       </c>
       <c r="G204" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H204" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
         <v>5.125</v>
       </c>
       <c r="G205" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H205" t="n">
         <v>0</v>
@@ -6343,7 +6343,7 @@
         <v>5.125</v>
       </c>
       <c r="G206" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H206" t="n">
         <v>0</v>
@@ -6372,7 +6372,7 @@
         <v>5.125</v>
       </c>
       <c r="G207" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -6401,7 +6401,7 @@
         <v>5.125</v>
       </c>
       <c r="G208" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H208" t="n">
         <v>0</v>
@@ -6430,7 +6430,7 @@
         <v>5.125</v>
       </c>
       <c r="G209" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H209" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>5.125</v>
       </c>
       <c r="G210" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H210" t="n">
         <v>0</v>
@@ -6488,7 +6488,7 @@
         <v>5.125</v>
       </c>
       <c r="G211" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H211" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
         <v>5.125</v>
       </c>
       <c r="G212" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H212" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>5.125</v>
       </c>
       <c r="G213" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H213" t="n">
         <v>0</v>
@@ -6575,7 +6575,7 @@
         <v>5.125</v>
       </c>
       <c r="G214" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H214" t="n">
         <v>0</v>
@@ -6604,7 +6604,7 @@
         <v>5.125</v>
       </c>
       <c r="G215" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H215" t="n">
         <v>0</v>
@@ -6633,7 +6633,7 @@
         <v>5.125</v>
       </c>
       <c r="G216" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H216" t="n">
         <v>0</v>
@@ -6662,7 +6662,7 @@
         <v>5.125</v>
       </c>
       <c r="G217" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H217" t="n">
         <v>0</v>
@@ -6691,7 +6691,7 @@
         <v>5.125</v>
       </c>
       <c r="G218" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H218" t="n">
         <v>0</v>
@@ -6720,7 +6720,7 @@
         <v>5.125</v>
       </c>
       <c r="G219" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H219" t="n">
         <v>0</v>
@@ -6749,7 +6749,7 @@
         <v>5.125</v>
       </c>
       <c r="G220" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H220" t="n">
         <v>0</v>
@@ -6778,7 +6778,7 @@
         <v>5.125</v>
       </c>
       <c r="G221" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H221" t="n">
         <v>0</v>
@@ -6807,7 +6807,7 @@
         <v>5.125</v>
       </c>
       <c r="G222" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H222" t="n">
         <v>0</v>
@@ -6836,7 +6836,7 @@
         <v>5.125</v>
       </c>
       <c r="G223" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H223" t="n">
         <v>0</v>
@@ -6865,7 +6865,7 @@
         <v>5.125</v>
       </c>
       <c r="G224" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H224" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>5.125</v>
       </c>
       <c r="G225" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H225" t="n">
         <v>0</v>
@@ -6923,7 +6923,7 @@
         <v>5.125</v>
       </c>
       <c r="G226" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H226" t="n">
         <v>0</v>
@@ -6952,7 +6952,7 @@
         <v>5.125</v>
       </c>
       <c r="G227" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
         <v>5.125</v>
       </c>
       <c r="G228" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H228" t="n">
         <v>0</v>
@@ -7010,7 +7010,7 @@
         <v>5.125</v>
       </c>
       <c r="G229" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H229" t="n">
         <v>0</v>
@@ -7039,7 +7039,7 @@
         <v>5.125</v>
       </c>
       <c r="G230" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H230" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>5.125</v>
       </c>
       <c r="G231" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H231" t="n">
         <v>0</v>
@@ -7097,7 +7097,7 @@
         <v>5.125</v>
       </c>
       <c r="G232" t="n">
-        <v>4.51277828216553</v>
+        <v>4.51277780532837</v>
       </c>
       <c r="H232" t="n">
         <v>0</v>
@@ -7126,7 +7126,7 @@
         <v>5.125</v>
       </c>
       <c r="G233" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H233" t="n">
         <v>0</v>
@@ -7155,7 +7155,7 @@
         <v>5.125</v>
       </c>
       <c r="G234" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H234" t="n">
         <v>0</v>
@@ -7184,7 +7184,7 @@
         <v>5.125</v>
       </c>
       <c r="G235" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H235" t="n">
         <v>0</v>
@@ -7213,7 +7213,7 @@
         <v>5.125</v>
       </c>
       <c r="G236" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H236" t="n">
         <v>0</v>
@@ -7242,7 +7242,7 @@
         <v>5.125</v>
       </c>
       <c r="G237" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -7271,7 +7271,7 @@
         <v>5.125</v>
       </c>
       <c r="G238" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -7300,7 +7300,7 @@
         <v>5.125</v>
       </c>
       <c r="G239" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -7329,7 +7329,7 @@
         <v>5.125</v>
       </c>
       <c r="G240" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -7358,7 +7358,7 @@
         <v>5.125</v>
       </c>
       <c r="G241" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -7387,7 +7387,7 @@
         <v>5.125</v>
       </c>
       <c r="G242" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -7416,7 +7416,7 @@
         <v>5.125</v>
       </c>
       <c r="G243" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H243" t="n">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         <v>5.125</v>
       </c>
       <c r="G244" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H244" t="n">
         <v>0</v>
@@ -7474,7 +7474,7 @@
         <v>5.125</v>
       </c>
       <c r="G245" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H245" t="n">
         <v>0</v>
@@ -7503,7 +7503,7 @@
         <v>5.125</v>
       </c>
       <c r="G246" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H246" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>5.125</v>
       </c>
       <c r="G247" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H247" t="n">
         <v>0</v>
@@ -7561,7 +7561,7 @@
         <v>5.125</v>
       </c>
       <c r="G248" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H248" t="n">
         <v>0</v>
@@ -7590,7 +7590,7 @@
         <v>5.125</v>
       </c>
       <c r="G249" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -7619,7 +7619,7 @@
         <v>5.125</v>
       </c>
       <c r="G250" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H250" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
         <v>5.125</v>
       </c>
       <c r="G251" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H251" t="n">
         <v>0</v>
@@ -7677,7 +7677,7 @@
         <v>5.125</v>
       </c>
       <c r="G252" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -7706,7 +7706,7 @@
         <v>5.125</v>
       </c>
       <c r="G253" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H253" t="n">
         <v>0</v>
@@ -7735,7 +7735,7 @@
         <v>5.125</v>
       </c>
       <c r="G254" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H254" t="n">
         <v>0</v>
@@ -7764,7 +7764,7 @@
         <v>5.125</v>
       </c>
       <c r="G255" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H255" t="n">
         <v>0</v>
@@ -7793,7 +7793,7 @@
         <v>5.125</v>
       </c>
       <c r="G256" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H256" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
         <v>5.125</v>
       </c>
       <c r="G257" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H257" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>5.125</v>
       </c>
       <c r="G258" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H258" t="n">
         <v>0</v>
@@ -7880,7 +7880,7 @@
         <v>5.125</v>
       </c>
       <c r="G259" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
@@ -7909,7 +7909,7 @@
         <v>5.125</v>
       </c>
       <c r="G260" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H260" t="n">
         <v>0</v>
@@ -7938,7 +7938,7 @@
         <v>5.125</v>
       </c>
       <c r="G261" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>5.125</v>
       </c>
       <c r="G262" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H262" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>5.125</v>
       </c>
       <c r="G263" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H263" t="n">
         <v>0</v>
@@ -8025,7 +8025,7 @@
         <v>5.125</v>
       </c>
       <c r="G264" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H264" t="n">
         <v>0</v>
@@ -8054,7 +8054,7 @@
         <v>5.125</v>
       </c>
       <c r="G265" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H265" t="n">
         <v>0</v>
@@ -8083,7 +8083,7 @@
         <v>5.125</v>
       </c>
       <c r="G266" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H266" t="n">
         <v>0</v>
@@ -8112,7 +8112,7 @@
         <v>5.125</v>
       </c>
       <c r="G267" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H267" t="n">
         <v>0</v>
@@ -8141,7 +8141,7 @@
         <v>5.125</v>
       </c>
       <c r="G268" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H268" t="n">
         <v>0</v>
@@ -8170,7 +8170,7 @@
         <v>5.125</v>
       </c>
       <c r="G269" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H269" t="n">
         <v>0</v>
@@ -8199,7 +8199,7 @@
         <v>5.125</v>
       </c>
       <c r="G270" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H270" t="n">
         <v>0</v>
@@ -8228,7 +8228,7 @@
         <v>5.125</v>
       </c>
       <c r="G271" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H271" t="n">
         <v>0</v>
@@ -8257,7 +8257,7 @@
         <v>5.125</v>
       </c>
       <c r="G272" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H272" t="n">
         <v>0</v>
@@ -8286,7 +8286,7 @@
         <v>5.125</v>
       </c>
       <c r="G273" t="n">
-        <v>4.58706665039062</v>
+        <v>4.58706617355347</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G274" t="n">
-        <v>4.51098775863647</v>
+        <v>4.51098823547363</v>
       </c>
       <c r="H274" t="n">
         <v>21200</v>
@@ -8344,7 +8344,7 @@
         <v>4.92999982833862</v>
       </c>
       <c r="G275" t="n">
-        <v>4.41253423690796</v>
+        <v>4.4125337600708</v>
       </c>
       <c r="H275" t="n">
         <v>16800</v>
@@ -8373,7 +8373,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G276" t="n">
-        <v>4.52888917922974</v>
+        <v>4.52888822555542</v>
       </c>
       <c r="H276" t="n">
         <v>35200</v>
@@ -8431,7 +8431,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G278" t="n">
-        <v>4.44833564758301</v>
+        <v>4.44833517074585</v>
       </c>
       <c r="H278" t="n">
         <v>12800</v>
@@ -8460,7 +8460,7 @@
         <v>5</v>
       </c>
       <c r="G279" t="n">
-        <v>4.47518682479858</v>
+        <v>4.47518730163574</v>
       </c>
       <c r="H279" t="n">
         <v>9200</v>
@@ -8489,7 +8489,7 @@
         <v>5</v>
       </c>
       <c r="G280" t="n">
-        <v>4.47518682479858</v>
+        <v>4.47518730163574</v>
       </c>
       <c r="H280" t="n">
         <v>8800</v>
@@ -8518,7 +8518,7 @@
         <v>5</v>
       </c>
       <c r="G281" t="n">
-        <v>4.47518682479858</v>
+        <v>4.47518730163574</v>
       </c>
       <c r="H281" t="n">
         <v>10400</v>
@@ -8634,7 +8634,7 @@
         <v>5</v>
       </c>
       <c r="G285" t="n">
-        <v>4.47518682479858</v>
+        <v>4.47518730163574</v>
       </c>
       <c r="H285" t="n">
         <v>6000</v>
@@ -8663,7 +8663,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G286" t="n">
-        <v>4.44833564758301</v>
+        <v>4.44833517074585</v>
       </c>
       <c r="H286" t="n">
         <v>4800</v>
@@ -8692,7 +8692,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G287" t="n">
-        <v>4.44833564758301</v>
+        <v>4.44833517074585</v>
       </c>
       <c r="H287" t="n">
         <v>58000</v>
@@ -8721,7 +8721,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G288" t="n">
-        <v>4.44833564758301</v>
+        <v>4.44833517074585</v>
       </c>
       <c r="H288" t="n">
         <v>4400</v>
@@ -8750,7 +8750,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G289" t="n">
-        <v>4.44833564758301</v>
+        <v>4.44833517074585</v>
       </c>
       <c r="H289" t="n">
         <v>4800</v>
@@ -8779,7 +8779,7 @@
         <v>5</v>
       </c>
       <c r="G290" t="n">
-        <v>4.47518682479858</v>
+        <v>4.47518730163574</v>
       </c>
       <c r="H290" t="n">
         <v>2400</v>
@@ -8895,7 +8895,7 @@
         <v>5.11999988555908</v>
       </c>
       <c r="G294" t="n">
-        <v>4.58259105682373</v>
+        <v>4.58259153366089</v>
       </c>
       <c r="H294" t="n">
         <v>6400</v>
@@ -8953,7 +8953,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G296" t="n">
-        <v>4.51098775863647</v>
+        <v>4.51098823547363</v>
       </c>
       <c r="H296" t="n">
         <v>400</v>
@@ -8982,7 +8982,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G297" t="n">
-        <v>4.52888917922974</v>
+        <v>4.52888822555542</v>
       </c>
       <c r="H297" t="n">
         <v>1200</v>
@@ -9011,7 +9011,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G298" t="n">
-        <v>4.51098775863647</v>
+        <v>4.51098823547363</v>
       </c>
       <c r="H298" t="n">
         <v>400</v>
@@ -9040,7 +9040,7 @@
         <v>5.03999996185303</v>
       </c>
       <c r="G299" t="n">
-        <v>4.51098775863647</v>
+        <v>4.51098823547363</v>
       </c>
       <c r="H299" t="n">
         <v>1600</v>
@@ -9156,7 +9156,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G303" t="n">
-        <v>4.43043422698975</v>
+        <v>4.43043375015259</v>
       </c>
       <c r="H303" t="n">
         <v>1600</v>
@@ -9185,7 +9185,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G304" t="n">
-        <v>4.43043422698975</v>
+        <v>4.43043375015259</v>
       </c>
       <c r="H304" t="n">
         <v>2000</v>
@@ -9214,7 +9214,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G305" t="n">
-        <v>4.38568305969238</v>
+        <v>4.38568258285522</v>
       </c>
       <c r="H305" t="n">
         <v>3200</v>
@@ -9243,7 +9243,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G306" t="n">
-        <v>4.3409309387207</v>
+        <v>4.34093046188354</v>
       </c>
       <c r="H306" t="n">
         <v>800</v>
@@ -9272,7 +9272,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G307" t="n">
-        <v>4.30512952804565</v>
+        <v>4.30513000488281</v>
       </c>
       <c r="H307" t="n">
         <v>5200</v>
@@ -9301,7 +9301,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G308" t="n">
-        <v>4.2961802482605</v>
+        <v>4.29617929458618</v>
       </c>
       <c r="H308" t="n">
         <v>400</v>
@@ -9330,7 +9330,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G309" t="n">
-        <v>4.33198118209839</v>
+        <v>4.33198165893555</v>
       </c>
       <c r="H309" t="n">
         <v>400</v>
@@ -9359,7 +9359,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G310" t="n">
-        <v>4.33198118209839</v>
+        <v>4.33198165893555</v>
       </c>
       <c r="H310" t="n">
         <v>400</v>
@@ -9388,7 +9388,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G311" t="n">
-        <v>4.27827930450439</v>
+        <v>4.27827882766724</v>
       </c>
       <c r="H311" t="n">
         <v>2000</v>
@@ -9417,7 +9417,7 @@
         <v>4.78000020980835</v>
       </c>
       <c r="G312" t="n">
-        <v>4.27827930450439</v>
+        <v>4.27827882766724</v>
       </c>
       <c r="H312" t="n">
         <v>0</v>
@@ -9446,7 +9446,7 @@
         <v>4.98000001907349</v>
       </c>
       <c r="G313" t="n">
-        <v>4.45728635787964</v>
+        <v>4.45728588104248</v>
       </c>
       <c r="H313" t="n">
         <v>5200</v>
@@ -9533,7 +9533,7 @@
         <v>4.84000015258789</v>
       </c>
       <c r="G316" t="n">
-        <v>4.33198118209839</v>
+        <v>4.33198165893555</v>
       </c>
       <c r="H316" t="n">
         <v>2800</v>
@@ -9562,7 +9562,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G317" t="n">
-        <v>4.3230299949646</v>
+        <v>4.32303047180176</v>
       </c>
       <c r="H317" t="n">
         <v>800</v>
@@ -9591,7 +9591,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G318" t="n">
-        <v>4.3230299949646</v>
+        <v>4.32303047180176</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>4.86999988555908</v>
       </c>
       <c r="G319" t="n">
-        <v>4.35883235931396</v>
+        <v>4.35883188247681</v>
       </c>
       <c r="H319" t="n">
         <v>400</v>
@@ -9678,7 +9678,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G321" t="n">
-        <v>4.2335262298584</v>
+        <v>4.23352670669556</v>
       </c>
       <c r="H321" t="n">
         <v>800</v>
@@ -9707,7 +9707,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G322" t="n">
-        <v>4.3230299949646</v>
+        <v>4.32303047180176</v>
       </c>
       <c r="H322" t="n">
         <v>2800</v>
@@ -9765,7 +9765,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G324" t="n">
-        <v>4.28722858428955</v>
+        <v>4.28722810745239</v>
       </c>
       <c r="H324" t="n">
         <v>20400</v>
@@ -9794,7 +9794,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G325" t="n">
-        <v>4.1798243522644</v>
+        <v>4.17982339859009</v>
       </c>
       <c r="H325" t="n">
         <v>15200</v>
@@ -9823,7 +9823,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G326" t="n">
-        <v>4.0903205871582</v>
+        <v>4.09032011032104</v>
       </c>
       <c r="H326" t="n">
         <v>218400</v>
@@ -9852,7 +9852,7 @@
         <v>4.51999998092651</v>
       </c>
       <c r="G327" t="n">
-        <v>4.04556941986084</v>
+        <v>4.04556894302368</v>
       </c>
       <c r="H327" t="n">
         <v>117200</v>
@@ -9881,7 +9881,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G328" t="n">
-        <v>3.90236330032349</v>
+        <v>3.90236306190491</v>
       </c>
       <c r="H328" t="n">
         <v>7600</v>
@@ -10026,7 +10026,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G333" t="n">
-        <v>4.1798243522644</v>
+        <v>4.17982339859009</v>
       </c>
       <c r="H333" t="n">
         <v>18000</v>
@@ -10084,7 +10084,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G335" t="n">
-        <v>4.11717176437378</v>
+        <v>4.11717128753662</v>
       </c>
       <c r="H335" t="n">
         <v>39200</v>
@@ -10171,7 +10171,7 @@
         <v>4.40000009536743</v>
       </c>
       <c r="G338" t="n">
-        <v>3.93816471099854</v>
+        <v>3.93816423416138</v>
       </c>
       <c r="H338" t="n">
         <v>6800</v>
@@ -10200,7 +10200,7 @@
         <v>4.34000015258789</v>
       </c>
       <c r="G339" t="n">
-        <v>3.8844621181488</v>
+        <v>3.88446187973022</v>
       </c>
       <c r="H339" t="n">
         <v>3600</v>
@@ -10229,7 +10229,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G340" t="n">
-        <v>3.90236330032349</v>
+        <v>3.90236306190491</v>
       </c>
       <c r="H340" t="n">
         <v>3600</v>
@@ -10287,7 +10287,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G342" t="n">
-        <v>3.76810765266418</v>
+        <v>3.76810693740845</v>
       </c>
       <c r="H342" t="n">
         <v>6000</v>
@@ -10316,7 +10316,7 @@
         <v>4.30000019073486</v>
       </c>
       <c r="G343" t="n">
-        <v>3.84866070747375</v>
+        <v>3.84866046905518</v>
       </c>
       <c r="H343" t="n">
         <v>2400</v>
@@ -10345,7 +10345,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G344" t="n">
-        <v>3.78600835800171</v>
+        <v>3.78600788116455</v>
       </c>
       <c r="H344" t="n">
         <v>1200</v>
@@ -10374,7 +10374,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G345" t="n">
-        <v>3.70545434951782</v>
+        <v>3.7054545879364</v>
       </c>
       <c r="H345" t="n">
         <v>1600</v>
@@ -10432,7 +10432,7 @@
         <v>4.03000020980835</v>
       </c>
       <c r="G347" t="n">
-        <v>3.60700035095215</v>
+        <v>3.60700082778931</v>
       </c>
       <c r="H347" t="n">
         <v>18000</v>
@@ -10548,7 +10548,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G351" t="n">
-        <v>3.53539776802063</v>
+        <v>3.53539729118347</v>
       </c>
       <c r="H351" t="n">
         <v>7200</v>
@@ -10577,7 +10577,7 @@
         <v>4</v>
       </c>
       <c r="G352" t="n">
-        <v>3.58014917373657</v>
+        <v>3.58014941215515</v>
       </c>
       <c r="H352" t="n">
         <v>800</v>
@@ -10606,7 +10606,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G353" t="n">
-        <v>3.43694353103638</v>
+        <v>3.43694305419922</v>
       </c>
       <c r="H353" t="n">
         <v>2800</v>
@@ -10635,7 +10635,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G354" t="n">
-        <v>3.47274494171143</v>
+        <v>3.47274518013</v>
       </c>
       <c r="H354" t="n">
         <v>400</v>
@@ -10664,7 +10664,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G355" t="n">
-        <v>3.44589352607727</v>
+        <v>3.44589376449585</v>
       </c>
       <c r="H355" t="n">
         <v>10400</v>
@@ -10722,7 +10722,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G357" t="n">
-        <v>3.39219117164612</v>
+        <v>3.3921914100647</v>
       </c>
       <c r="H357" t="n">
         <v>43200</v>
@@ -10751,7 +10751,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G358" t="n">
-        <v>3.31163835525513</v>
+        <v>3.31163787841797</v>
       </c>
       <c r="H358" t="n">
         <v>21600</v>
@@ -10780,7 +10780,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G359" t="n">
-        <v>3.31163835525513</v>
+        <v>3.31163787841797</v>
       </c>
       <c r="H359" t="n">
         <v>10000</v>
@@ -10809,7 +10809,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G360" t="n">
-        <v>3.31163835525513</v>
+        <v>3.31163787841797</v>
       </c>
       <c r="H360" t="n">
         <v>4800</v>
@@ -10838,7 +10838,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G361" t="n">
-        <v>3.34743976593018</v>
+        <v>3.34744000434875</v>
       </c>
       <c r="H361" t="n">
         <v>9200</v>
@@ -10896,7 +10896,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G363" t="n">
-        <v>3.31163835525513</v>
+        <v>3.31163787841797</v>
       </c>
       <c r="H363" t="n">
         <v>11200</v>
@@ -10925,7 +10925,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G364" t="n">
-        <v>3.20423364639282</v>
+        <v>3.20423340797424</v>
       </c>
       <c r="H364" t="n">
         <v>18000</v>
@@ -10954,7 +10954,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G365" t="n">
-        <v>3.08787870407104</v>
+        <v>3.08787894248962</v>
       </c>
       <c r="H365" t="n">
         <v>6000</v>
@@ -11041,7 +11041,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G368" t="n">
-        <v>3.10577988624573</v>
+        <v>3.10577940940857</v>
       </c>
       <c r="H368" t="n">
         <v>18000</v>
@@ -11070,7 +11070,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G369" t="n">
-        <v>3.20423364639282</v>
+        <v>3.20423340797424</v>
       </c>
       <c r="H369" t="n">
         <v>68000</v>
@@ -11099,7 +11099,7 @@
         <v>3.58999991416931</v>
       </c>
       <c r="G370" t="n">
-        <v>3.21318387985229</v>
+        <v>3.21318411827087</v>
       </c>
       <c r="H370" t="n">
         <v>22400</v>
@@ -11128,7 +11128,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G371" t="n">
-        <v>3.22213459014893</v>
+        <v>3.22213435173035</v>
       </c>
       <c r="H371" t="n">
         <v>62000</v>
@@ -11157,7 +11157,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G372" t="n">
-        <v>3.22213459014893</v>
+        <v>3.22213435173035</v>
       </c>
       <c r="H372" t="n">
         <v>21200</v>
@@ -11273,7 +11273,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G376" t="n">
-        <v>2.91782140731812</v>
+        <v>2.91782188415527</v>
       </c>
       <c r="H376" t="n">
         <v>90400</v>
@@ -11302,7 +11302,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G377" t="n">
-        <v>2.95362305641174</v>
+        <v>2.95362329483032</v>
       </c>
       <c r="H377" t="n">
         <v>11600</v>
@@ -11331,7 +11331,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G378" t="n">
-        <v>2.91782140731812</v>
+        <v>2.91782188415527</v>
       </c>
       <c r="H378" t="n">
         <v>18000</v>
@@ -11360,7 +11360,7 @@
         <v>3.25</v>
       </c>
       <c r="G379" t="n">
-        <v>2.90887141227722</v>
+        <v>2.9088716506958</v>
       </c>
       <c r="H379" t="n">
         <v>8800</v>
@@ -11389,7 +11389,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G380" t="n">
-        <v>2.86411929130554</v>
+        <v>2.86411952972412</v>
       </c>
       <c r="H380" t="n">
         <v>15600</v>
@@ -11418,7 +11418,7 @@
         <v>3.25</v>
       </c>
       <c r="G381" t="n">
-        <v>2.90887141227722</v>
+        <v>2.9088716506958</v>
       </c>
       <c r="H381" t="n">
         <v>67200</v>
@@ -11447,7 +11447,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G382" t="n">
-        <v>2.95362305641174</v>
+        <v>2.95362329483032</v>
       </c>
       <c r="H382" t="n">
         <v>18000</v>
@@ -11476,7 +11476,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G383" t="n">
-        <v>2.95362305641174</v>
+        <v>2.95362329483032</v>
       </c>
       <c r="H383" t="n">
         <v>24400</v>
@@ -11505,7 +11505,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G384" t="n">
-        <v>3.00732564926147</v>
+        <v>3.0073254108429</v>
       </c>
       <c r="H384" t="n">
         <v>5200</v>
@@ -11534,7 +11534,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G385" t="n">
-        <v>2.95362305641174</v>
+        <v>2.95362329483032</v>
       </c>
       <c r="H385" t="n">
         <v>17600</v>
@@ -11563,7 +11563,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G386" t="n">
-        <v>2.91782140731812</v>
+        <v>2.91782188415527</v>
       </c>
       <c r="H386" t="n">
         <v>2400</v>
@@ -11592,7 +11592,7 @@
         <v>3.25</v>
       </c>
       <c r="G387" t="n">
-        <v>2.90887141227722</v>
+        <v>2.9088716506958</v>
       </c>
       <c r="H387" t="n">
         <v>8400</v>
@@ -11650,7 +11650,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G389" t="n">
-        <v>2.86411929130554</v>
+        <v>2.86411952972412</v>
       </c>
       <c r="H389" t="n">
         <v>14800</v>
@@ -11679,7 +11679,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G390" t="n">
-        <v>2.81041765213013</v>
+        <v>2.81041741371155</v>
       </c>
       <c r="H390" t="n">
         <v>11200</v>
@@ -11737,7 +11737,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G392" t="n">
-        <v>2.86411929130554</v>
+        <v>2.86411952972412</v>
       </c>
       <c r="H392" t="n">
         <v>18000</v>
@@ -11795,7 +11795,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G394" t="n">
-        <v>2.94467282295227</v>
+        <v>2.94467258453369</v>
       </c>
       <c r="H394" t="n">
         <v>2000</v>
@@ -11824,7 +11824,7 @@
         <v>3.42000007629395</v>
       </c>
       <c r="G395" t="n">
-        <v>3.06102776527405</v>
+        <v>3.06102752685547</v>
       </c>
       <c r="H395" t="n">
         <v>27600</v>
@@ -11853,7 +11853,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G396" t="n">
-        <v>3.06997799873352</v>
+        <v>3.06997847557068</v>
       </c>
       <c r="H396" t="n">
         <v>10800</v>
@@ -11882,7 +11882,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G397" t="n">
-        <v>3.17738246917725</v>
+        <v>3.17738270759583</v>
       </c>
       <c r="H397" t="n">
         <v>9200</v>
@@ -11911,7 +11911,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G398" t="n">
-        <v>3.17738246917725</v>
+        <v>3.17738270759583</v>
       </c>
       <c r="H398" t="n">
         <v>3600</v>
@@ -11969,7 +11969,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G400" t="n">
-        <v>3.22213459014893</v>
+        <v>3.22213435173035</v>
       </c>
       <c r="H400" t="n">
         <v>27600</v>
@@ -12056,7 +12056,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G403" t="n">
-        <v>3.31163835525513</v>
+        <v>3.31163787841797</v>
       </c>
       <c r="H403" t="n">
         <v>3600</v>
@@ -12085,7 +12085,7 @@
         <v>3.75</v>
       </c>
       <c r="G404" t="n">
-        <v>3.35638976097107</v>
+        <v>3.35638952255249</v>
       </c>
       <c r="H404" t="n">
         <v>100000</v>
@@ -12114,7 +12114,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G405" t="n">
-        <v>3.39219117164612</v>
+        <v>3.3921914100647</v>
       </c>
       <c r="H405" t="n">
         <v>8000</v>
@@ -12143,7 +12143,7 @@
         <v>3.91000008583069</v>
       </c>
       <c r="G406" t="n">
-        <v>3.49959588050842</v>
+        <v>3.499596118927</v>
       </c>
       <c r="H406" t="n">
         <v>30400</v>
@@ -12172,7 +12172,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G407" t="n">
-        <v>3.50854587554932</v>
+        <v>3.50854635238647</v>
       </c>
       <c r="H407" t="n">
         <v>800</v>
@@ -12259,7 +12259,7 @@
         <v>3.98000001907349</v>
       </c>
       <c r="G410" t="n">
-        <v>3.56224846839905</v>
+        <v>3.56224822998047</v>
       </c>
       <c r="H410" t="n">
         <v>7200</v>
@@ -12317,7 +12317,7 @@
         <v>4</v>
       </c>
       <c r="G412" t="n">
-        <v>3.58014917373657</v>
+        <v>3.58014941215515</v>
       </c>
       <c r="H412" t="n">
         <v>6000</v>
@@ -12346,7 +12346,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G413" t="n">
-        <v>3.58910012245178</v>
+        <v>3.58909964561462</v>
       </c>
       <c r="H413" t="n">
         <v>2000</v>
@@ -12375,7 +12375,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G414" t="n">
-        <v>3.63385152816772</v>
+        <v>3.63385128974915</v>
       </c>
       <c r="H414" t="n">
         <v>2800</v>
@@ -12433,7 +12433,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G416" t="n">
-        <v>3.63385152816772</v>
+        <v>3.63385128974915</v>
       </c>
       <c r="H416" t="n">
         <v>7200</v>
@@ -12462,7 +12462,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G417" t="n">
-        <v>3.49064564704895</v>
+        <v>3.49064588546753</v>
       </c>
       <c r="H417" t="n">
         <v>10000</v>
@@ -12491,7 +12491,7 @@
         <v>3.95000004768372</v>
       </c>
       <c r="G418" t="n">
-        <v>3.53539776802063</v>
+        <v>3.53539729118347</v>
       </c>
       <c r="H418" t="n">
         <v>3200</v>
@@ -12549,7 +12549,7 @@
         <v>4</v>
       </c>
       <c r="G420" t="n">
-        <v>3.58014917373657</v>
+        <v>3.58014941215515</v>
       </c>
       <c r="H420" t="n">
         <v>9200</v>
@@ -12636,7 +12636,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G423" t="n">
-        <v>3.58910012245178</v>
+        <v>3.58909964561462</v>
       </c>
       <c r="H423" t="n">
         <v>10800</v>
@@ -12665,7 +12665,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G424" t="n">
-        <v>3.63385152816772</v>
+        <v>3.63385128974915</v>
       </c>
       <c r="H424" t="n">
         <v>13200</v>
@@ -12694,7 +12694,7 @@
         <v>4.05000019073486</v>
       </c>
       <c r="G425" t="n">
-        <v>3.62490105628967</v>
+        <v>3.62490153312683</v>
       </c>
       <c r="H425" t="n">
         <v>4800</v>
@@ -12723,7 +12723,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G426" t="n">
-        <v>3.63385152816772</v>
+        <v>3.63385128974915</v>
       </c>
       <c r="H426" t="n">
         <v>25200</v>
@@ -12752,7 +12752,7 @@
         <v>4</v>
       </c>
       <c r="G427" t="n">
-        <v>3.58014917373657</v>
+        <v>3.58014941215515</v>
       </c>
       <c r="H427" t="n">
         <v>10400</v>
@@ -12781,7 +12781,7 @@
         <v>4.05999994277954</v>
       </c>
       <c r="G428" t="n">
-        <v>3.63385152816772</v>
+        <v>3.63385128974915</v>
       </c>
       <c r="H428" t="n">
         <v>5200</v>
@@ -12810,7 +12810,7 @@
         <v>4.01000022888184</v>
       </c>
       <c r="G429" t="n">
-        <v>3.58910012245178</v>
+        <v>3.58909964561462</v>
       </c>
       <c r="H429" t="n">
         <v>22400</v>
@@ -12839,7 +12839,7 @@
         <v>4.13000011444092</v>
       </c>
       <c r="G430" t="n">
-        <v>3.69650411605835</v>
+        <v>3.69650435447693</v>
       </c>
       <c r="H430" t="n">
         <v>14800</v>
@@ -12868,7 +12868,7 @@
         <v>4.19000005722046</v>
       </c>
       <c r="G431" t="n">
-        <v>3.75020670890808</v>
+        <v>3.75020599365234</v>
       </c>
       <c r="H431" t="n">
         <v>12000</v>
@@ -12897,7 +12897,7 @@
         <v>4.23000001907349</v>
       </c>
       <c r="G432" t="n">
-        <v>3.78600835800171</v>
+        <v>3.78600788116455</v>
       </c>
       <c r="H432" t="n">
         <v>63600</v>
@@ -12926,7 +12926,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G433" t="n">
-        <v>3.90236330032349</v>
+        <v>3.90236306190491</v>
       </c>
       <c r="H433" t="n">
         <v>6800</v>
@@ -12955,7 +12955,7 @@
         <v>4.57000017166138</v>
       </c>
       <c r="G434" t="n">
-        <v>4.0903205871582</v>
+        <v>4.09032011032104</v>
       </c>
       <c r="H434" t="n">
         <v>18800</v>
@@ -13071,7 +13071,7 @@
         <v>4.75</v>
       </c>
       <c r="G438" t="n">
-        <v>4.2514271736145</v>
+        <v>4.25142765045166</v>
       </c>
       <c r="H438" t="n">
         <v>18000</v>
@@ -13100,7 +13100,7 @@
         <v>4.59999990463257</v>
       </c>
       <c r="G439" t="n">
-        <v>4.11717176437378</v>
+        <v>4.11717128753662</v>
       </c>
       <c r="H439" t="n">
         <v>116400</v>
@@ -13129,7 +13129,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G440" t="n">
-        <v>4.37673282623291</v>
+        <v>4.37673234939575</v>
       </c>
       <c r="H440" t="n">
         <v>29200</v>
@@ -13158,7 +13158,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G441" t="n">
-        <v>4.43043422698975</v>
+        <v>4.43043375015259</v>
       </c>
       <c r="H441" t="n">
         <v>10000</v>
@@ -13187,7 +13187,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G442" t="n">
-        <v>4.2961802482605</v>
+        <v>4.29617929458618</v>
       </c>
       <c r="H442" t="n">
         <v>82000</v>
@@ -13216,7 +13216,7 @@
         <v>4.73000001907349</v>
       </c>
       <c r="G443" t="n">
-        <v>4.2335262298584</v>
+        <v>4.23352670669556</v>
       </c>
       <c r="H443" t="n">
         <v>11200</v>
@@ -13303,7 +13303,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G446" t="n">
-        <v>3.90236330032349</v>
+        <v>3.90236306190491</v>
       </c>
       <c r="H446" t="n">
         <v>22800</v>
@@ -13332,7 +13332,7 @@
         <v>4.38000011444092</v>
       </c>
       <c r="G447" t="n">
-        <v>3.92026376724243</v>
+        <v>3.92026400566101</v>
       </c>
       <c r="H447" t="n">
         <v>14400</v>
@@ -13361,7 +13361,7 @@
         <v>4.21000003814697</v>
       </c>
       <c r="G448" t="n">
-        <v>3.76810765266418</v>
+        <v>3.76810693740845</v>
       </c>
       <c r="H448" t="n">
         <v>15600</v>
@@ -13448,7 +13448,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G451" t="n">
-        <v>3.70545434951782</v>
+        <v>3.7054545879364</v>
       </c>
       <c r="H451" t="n">
         <v>36400</v>
@@ -13477,7 +13477,7 @@
         <v>4.3899998664856</v>
       </c>
       <c r="G452" t="n">
-        <v>3.92921352386475</v>
+        <v>3.9292140007019</v>
       </c>
       <c r="H452" t="n">
         <v>3600</v>
@@ -13593,7 +13593,7 @@
         <v>4.53000020980835</v>
       </c>
       <c r="G456" t="n">
-        <v>4.05451965332031</v>
+        <v>4.05452013015747</v>
       </c>
       <c r="H456" t="n">
         <v>800</v>
@@ -13651,7 +13651,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G458" t="n">
-        <v>4.2961802482605</v>
+        <v>4.29617929458618</v>
       </c>
       <c r="H458" t="n">
         <v>10800</v>
@@ -13680,7 +13680,7 @@
         <v>4.76000022888184</v>
       </c>
       <c r="G459" t="n">
-        <v>4.26037836074829</v>
+        <v>4.26037788391113</v>
       </c>
       <c r="H459" t="n">
         <v>10800</v>
@@ -13709,7 +13709,7 @@
         <v>4.84999990463257</v>
       </c>
       <c r="G460" t="n">
-        <v>4.3409309387207</v>
+        <v>4.34093046188354</v>
       </c>
       <c r="H460" t="n">
         <v>5600</v>
@@ -13767,7 +13767,7 @@
         <v>4.96999979019165</v>
       </c>
       <c r="G462" t="n">
-        <v>4.44833564758301</v>
+        <v>4.44833517074585</v>
       </c>
       <c r="H462" t="n">
         <v>58400</v>
@@ -13796,7 +13796,7 @@
         <v>4.82999992370605</v>
       </c>
       <c r="G463" t="n">
-        <v>4.3230299949646</v>
+        <v>4.32303047180176</v>
       </c>
       <c r="H463" t="n">
         <v>47090</v>
@@ -13825,7 +13825,7 @@
         <v>4.94000005722046</v>
       </c>
       <c r="G464" t="n">
-        <v>4.42148447036743</v>
+        <v>4.42148494720459</v>
       </c>
       <c r="H464" t="n">
         <v>31590</v>
@@ -13854,7 +13854,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G465" t="n">
-        <v>4.37673282623291</v>
+        <v>4.37673234939575</v>
       </c>
       <c r="H465" t="n">
         <v>29220</v>
@@ -13883,7 +13883,7 @@
         <v>4.90000009536743</v>
       </c>
       <c r="G466" t="n">
-        <v>4.38568305969238</v>
+        <v>4.38568258285522</v>
       </c>
       <c r="H466" t="n">
         <v>9250</v>
@@ -13912,7 +13912,7 @@
         <v>4.8899998664856</v>
       </c>
       <c r="G467" t="n">
-        <v>4.37673282623291</v>
+        <v>4.37673234939575</v>
       </c>
       <c r="H467" t="n">
         <v>41850</v>
@@ -13941,7 +13941,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G468" t="n">
-        <v>4.2961802482605</v>
+        <v>4.29617929458618</v>
       </c>
       <c r="H468" t="n">
         <v>39550</v>
@@ -14057,7 +14057,7 @@
         <v>4.80999994277954</v>
       </c>
       <c r="G472" t="n">
-        <v>4.38917779922485</v>
+        <v>4.3891773223877</v>
       </c>
       <c r="H472" t="n">
         <v>31650</v>
@@ -14086,7 +14086,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G473" t="n">
-        <v>4.28880071640015</v>
+        <v>4.2888011932373</v>
       </c>
       <c r="H473" t="n">
         <v>68920</v>
@@ -14115,7 +14115,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G474" t="n">
-        <v>4.37092733383179</v>
+        <v>4.37092685699463</v>
       </c>
       <c r="H474" t="n">
         <v>14740</v>
@@ -14173,7 +14173,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G476" t="n">
-        <v>4.28880071640015</v>
+        <v>4.2888011932373</v>
       </c>
       <c r="H476" t="n">
         <v>5140</v>
@@ -14318,7 +14318,7 @@
         <v>4.67999982833862</v>
       </c>
       <c r="G481" t="n">
-        <v>4.27055168151855</v>
+        <v>4.27055072784424</v>
       </c>
       <c r="H481" t="n">
         <v>1720</v>
@@ -14347,7 +14347,7 @@
         <v>4.67000007629395</v>
       </c>
       <c r="G482" t="n">
-        <v>4.26142644882202</v>
+        <v>4.26142597198486</v>
       </c>
       <c r="H482" t="n">
         <v>850</v>
@@ -14376,7 +14376,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G483" t="n">
-        <v>4.28880071640015</v>
+        <v>4.2888011932373</v>
       </c>
       <c r="H483" t="n">
         <v>50</v>
@@ -14434,7 +14434,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G485" t="n">
-        <v>4.28880071640015</v>
+        <v>4.2888011932373</v>
       </c>
       <c r="H485" t="n">
         <v>460</v>
@@ -14463,7 +14463,7 @@
         <v>4.76999998092651</v>
       </c>
       <c r="G486" t="n">
-        <v>4.35267734527588</v>
+        <v>4.35267686843872</v>
       </c>
       <c r="H486" t="n">
         <v>60</v>
@@ -14579,7 +14579,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G490" t="n">
-        <v>4.28880071640015</v>
+        <v>4.2888011932373</v>
       </c>
       <c r="H490" t="n">
         <v>2140</v>
@@ -14608,7 +14608,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G491" t="n">
-        <v>4.28880071640015</v>
+        <v>4.2888011932373</v>
       </c>
       <c r="H491" t="n">
         <v>5200</v>
@@ -14637,7 +14637,7 @@
         <v>4.75</v>
       </c>
       <c r="G492" t="n">
-        <v>4.33442640304565</v>
+        <v>4.33442687988281</v>
       </c>
       <c r="H492" t="n">
         <v>450</v>
@@ -14666,7 +14666,7 @@
         <v>4.75</v>
       </c>
       <c r="G493" t="n">
-        <v>4.33442640304565</v>
+        <v>4.33442687988281</v>
       </c>
       <c r="H493" t="n">
         <v>1550</v>
@@ -14695,7 +14695,7 @@
         <v>4.65000009536743</v>
       </c>
       <c r="G494" t="n">
-        <v>4.2431755065918</v>
+        <v>4.24317646026611</v>
       </c>
       <c r="H494" t="n">
         <v>7300</v>
@@ -14724,7 +14724,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G495" t="n">
-        <v>4.38005256652832</v>
+        <v>4.38005304336548</v>
       </c>
       <c r="H495" t="n">
         <v>24640</v>
@@ -14782,7 +14782,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G497" t="n">
-        <v>4.38005256652832</v>
+        <v>4.38005304336548</v>
       </c>
       <c r="H497" t="n">
         <v>1050</v>
@@ -14811,7 +14811,7 @@
         <v>4.75</v>
       </c>
       <c r="G498" t="n">
-        <v>4.33442640304565</v>
+        <v>4.33442687988281</v>
       </c>
       <c r="H498" t="n">
         <v>450</v>
@@ -14840,7 +14840,7 @@
         <v>4.75</v>
       </c>
       <c r="G499" t="n">
-        <v>4.33442640304565</v>
+        <v>4.33442687988281</v>
       </c>
       <c r="H499" t="n">
         <v>0</v>
@@ -14869,7 +14869,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G500" t="n">
-        <v>4.38005256652832</v>
+        <v>4.38005304336548</v>
       </c>
       <c r="H500" t="n">
         <v>2200</v>
@@ -14898,7 +14898,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G501" t="n">
-        <v>4.37092733383179</v>
+        <v>4.37092685699463</v>
       </c>
       <c r="H501" t="n">
         <v>800</v>
@@ -14956,7 +14956,7 @@
         <v>4.75</v>
       </c>
       <c r="G503" t="n">
-        <v>4.33442640304565</v>
+        <v>4.33442687988281</v>
       </c>
       <c r="H503" t="n">
         <v>10950</v>
@@ -14985,7 +14985,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G504" t="n">
-        <v>4.29792642593384</v>
+        <v>4.297926902771</v>
       </c>
       <c r="H504" t="n">
         <v>11000</v>
@@ -15014,7 +15014,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G505" t="n">
-        <v>4.29792642593384</v>
+        <v>4.297926902771</v>
       </c>
       <c r="H505" t="n">
         <v>5650</v>
@@ -15043,7 +15043,7 @@
         <v>4.71000003814697</v>
       </c>
       <c r="G506" t="n">
-        <v>4.29792642593384</v>
+        <v>4.297926902771</v>
       </c>
       <c r="H506" t="n">
         <v>0</v>
@@ -15072,7 +15072,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G507" t="n">
-        <v>4.38005256652832</v>
+        <v>4.38005304336548</v>
       </c>
       <c r="H507" t="n">
         <v>2850</v>
@@ -15101,7 +15101,7 @@
         <v>4.80000019073486</v>
       </c>
       <c r="G508" t="n">
-        <v>4.38005256652832</v>
+        <v>4.38005304336548</v>
       </c>
       <c r="H508" t="n">
         <v>3390</v>
@@ -15246,7 +15246,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G513" t="n">
-        <v>4.30705118179321</v>
+        <v>4.30705165863037</v>
       </c>
       <c r="H513" t="n">
         <v>8080</v>
@@ -15275,7 +15275,7 @@
         <v>4.75</v>
       </c>
       <c r="G514" t="n">
-        <v>4.33442640304565</v>
+        <v>4.33442687988281</v>
       </c>
       <c r="H514" t="n">
         <v>2250</v>
@@ -15304,7 +15304,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G515" t="n">
-        <v>4.30705118179321</v>
+        <v>4.30705165863037</v>
       </c>
       <c r="H515" t="n">
         <v>12400</v>
@@ -15333,7 +15333,7 @@
         <v>4.69999980926514</v>
       </c>
       <c r="G516" t="n">
-        <v>4.28880071640015</v>
+        <v>4.2888011932373</v>
       </c>
       <c r="H516" t="n">
         <v>34580</v>
@@ -15362,7 +15362,7 @@
         <v>4.71999979019165</v>
       </c>
       <c r="G517" t="n">
-        <v>4.30705118179321</v>
+        <v>4.30705165863037</v>
       </c>
       <c r="H517" t="n">
         <v>4210</v>
@@ -15391,7 +15391,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G518" t="n">
-        <v>4.61730480194092</v>
+        <v>4.61730527877808</v>
       </c>
       <c r="H518" t="n">
         <v>125400</v>
@@ -15449,7 +15449,7 @@
         <v>5</v>
       </c>
       <c r="G520" t="n">
-        <v>4.56255531311035</v>
+        <v>4.56255435943604</v>
       </c>
       <c r="H520" t="n">
         <v>32720</v>
@@ -15478,7 +15478,7 @@
         <v>5.01999998092651</v>
       </c>
       <c r="G521" t="n">
-        <v>4.5808048248291</v>
+        <v>4.58080530166626</v>
       </c>
       <c r="H521" t="n">
         <v>33970</v>
@@ -15507,7 +15507,7 @@
         <v>4.90999984741211</v>
       </c>
       <c r="G522" t="n">
-        <v>4.48042917251587</v>
+        <v>4.48042964935303</v>
       </c>
       <c r="H522" t="n">
         <v>9600</v>
@@ -15536,7 +15536,7 @@
         <v>5.05999994277954</v>
       </c>
       <c r="G523" t="n">
-        <v>4.61730480194092</v>
+        <v>4.61730527877808</v>
       </c>
       <c r="H523" t="n">
         <v>61320</v>
@@ -15594,7 +15594,7 @@
         <v>5.17999982833862</v>
       </c>
       <c r="G525" t="n">
-        <v>4.72680711746216</v>
+        <v>4.726806640625</v>
       </c>
       <c r="H525" t="n">
         <v>50940</v>
@@ -15623,7 +15623,7 @@
         <v>5.26000022888184</v>
       </c>
       <c r="G526" t="n">
-        <v>4.79980802536011</v>
+        <v>4.79980754852295</v>
       </c>
       <c r="H526" t="n">
         <v>23760</v>
@@ -15652,7 +15652,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G527" t="n">
-        <v>4.90930938720703</v>
+        <v>4.90930891036987</v>
       </c>
       <c r="H527" t="n">
         <v>43970</v>
@@ -15681,7 +15681,7 @@
         <v>5.38000011444092</v>
       </c>
       <c r="G528" t="n">
-        <v>4.90930938720703</v>
+        <v>4.90930891036987</v>
       </c>
       <c r="H528" t="n">
         <v>20060</v>
@@ -15739,7 +15739,7 @@
         <v>5.44000005722046</v>
       </c>
       <c r="G530" t="n">
-        <v>4.96406030654907</v>
+        <v>4.96405935287476</v>
       </c>
       <c r="H530" t="n">
         <v>41950</v>
@@ -15768,7 +15768,7 @@
         <v>5.42000007629395</v>
       </c>
       <c r="G531" t="n">
-        <v>4.94580888748169</v>
+        <v>4.94580984115601</v>
       </c>
       <c r="H531" t="n">
         <v>25300</v>
@@ -15797,7 +15797,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G532" t="n">
-        <v>4.98230981826782</v>
+        <v>4.98231029510498</v>
       </c>
       <c r="H532" t="n">
         <v>8850</v>
@@ -15942,7 +15942,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G537" t="n">
-        <v>5.1830620765686</v>
+        <v>5.18306303024292</v>
       </c>
       <c r="H537" t="n">
         <v>35600</v>
@@ -16029,7 +16029,7 @@
         <v>5.46000003814697</v>
       </c>
       <c r="G540" t="n">
-        <v>4.98230981826782</v>
+        <v>4.98231029510498</v>
       </c>
       <c r="H540" t="n">
         <v>54360</v>
@@ -16058,7 +16058,7 @@
         <v>5.48000001907349</v>
       </c>
       <c r="G541" t="n">
-        <v>5.00055980682373</v>
+        <v>5.00056028366089</v>
       </c>
       <c r="H541" t="n">
         <v>23360</v>
@@ -16174,7 +16174,7 @@
         <v>5.53999996185303</v>
       </c>
       <c r="G545" t="n">
-        <v>5.05531072616577</v>
+        <v>5.05531024932861</v>
       </c>
       <c r="H545" t="n">
         <v>9250</v>
@@ -16319,7 +16319,7 @@
         <v>5.61999988555908</v>
       </c>
       <c r="G550" t="n">
-        <v>5.12831211090088</v>
+        <v>5.12831115722656</v>
       </c>
       <c r="H550" t="n">
         <v>15220</v>
@@ -16348,7 +16348,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G551" t="n">
-        <v>5.1830620765686</v>
+        <v>5.18306303024292</v>
       </c>
       <c r="H551" t="n">
         <v>21670</v>
@@ -16406,7 +16406,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G553" t="n">
-        <v>5.29256391525269</v>
+        <v>5.29256343841553</v>
       </c>
       <c r="H553" t="n">
         <v>68800</v>
@@ -16435,7 +16435,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G554" t="n">
-        <v>5.29256391525269</v>
+        <v>5.29256343841553</v>
       </c>
       <c r="H554" t="n">
         <v>18450</v>
@@ -16551,7 +16551,7 @@
         <v>6</v>
       </c>
       <c r="G558" t="n">
-        <v>5.47506618499756</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H558" t="n">
         <v>25750</v>
@@ -16580,7 +16580,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G559" t="n">
-        <v>5.60281658172607</v>
+        <v>5.60281801223755</v>
       </c>
       <c r="H559" t="n">
         <v>27190</v>
@@ -16609,7 +16609,7 @@
         <v>6.28000020980835</v>
       </c>
       <c r="G560" t="n">
-        <v>5.73056936264038</v>
+        <v>5.73056888580322</v>
       </c>
       <c r="H560" t="n">
         <v>16040</v>
@@ -16638,7 +16638,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G561" t="n">
-        <v>5.49331521987915</v>
+        <v>5.49331569671631</v>
       </c>
       <c r="H561" t="n">
         <v>18810</v>
@@ -16696,7 +16696,7 @@
         <v>6</v>
       </c>
       <c r="G563" t="n">
-        <v>5.47506618499756</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H563" t="n">
         <v>14950</v>
@@ -16783,7 +16783,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G566" t="n">
-        <v>5.29256391525269</v>
+        <v>5.29256343841553</v>
       </c>
       <c r="H566" t="n">
         <v>12560</v>
@@ -16812,7 +16812,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G567" t="n">
-        <v>5.29256391525269</v>
+        <v>5.29256343841553</v>
       </c>
       <c r="H567" t="n">
         <v>9940</v>
@@ -16899,7 +16899,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G570" t="n">
-        <v>5.29256391525269</v>
+        <v>5.29256343841553</v>
       </c>
       <c r="H570" t="n">
         <v>10610</v>
@@ -16957,7 +16957,7 @@
         <v>6</v>
       </c>
       <c r="G572" t="n">
-        <v>5.47506618499756</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H572" t="n">
         <v>21030</v>
@@ -16986,7 +16986,7 @@
         <v>6</v>
       </c>
       <c r="G573" t="n">
-        <v>5.47506618499756</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H573" t="n">
         <v>18730</v>
@@ -17073,7 +17073,7 @@
         <v>5.82000017166138</v>
       </c>
       <c r="G576" t="n">
-        <v>5.31081390380859</v>
+        <v>5.31081438064575</v>
       </c>
       <c r="H576" t="n">
         <v>56590</v>
@@ -17102,7 +17102,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G577" t="n">
-        <v>5.29256391525269</v>
+        <v>5.29256343841553</v>
       </c>
       <c r="H577" t="n">
         <v>29590</v>
@@ -17131,7 +17131,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G578" t="n">
-        <v>5.36556529998779</v>
+        <v>5.36556482315063</v>
       </c>
       <c r="H578" t="n">
         <v>30630</v>
@@ -17160,7 +17160,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G579" t="n">
-        <v>5.34731388092041</v>
+        <v>5.34731435775757</v>
       </c>
       <c r="H579" t="n">
         <v>17360</v>
@@ -17218,7 +17218,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G581" t="n">
-        <v>5.45681619644165</v>
+        <v>5.45681476593018</v>
       </c>
       <c r="H581" t="n">
         <v>6680</v>
@@ -17247,7 +17247,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G582" t="n">
-        <v>5.49331521987915</v>
+        <v>5.49331569671631</v>
       </c>
       <c r="H582" t="n">
         <v>11710</v>
@@ -17276,7 +17276,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G583" t="n">
-        <v>5.43856477737427</v>
+        <v>5.43856573104858</v>
       </c>
       <c r="H583" t="n">
         <v>8370</v>
@@ -17305,7 +17305,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G584" t="n">
-        <v>5.43856477737427</v>
+        <v>5.43856573104858</v>
       </c>
       <c r="H584" t="n">
         <v>8130</v>
@@ -17334,7 +17334,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G585" t="n">
-        <v>5.43856477737427</v>
+        <v>5.43856573104858</v>
       </c>
       <c r="H585" t="n">
         <v>3760</v>
@@ -17392,7 +17392,7 @@
         <v>6</v>
       </c>
       <c r="G587" t="n">
-        <v>5.47506618499756</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H587" t="n">
         <v>6650</v>
@@ -17421,7 +17421,7 @@
         <v>6</v>
       </c>
       <c r="G588" t="n">
-        <v>5.47506618499756</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H588" t="n">
         <v>6150</v>
@@ -17450,7 +17450,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G589" t="n">
-        <v>5.43856477737427</v>
+        <v>5.43856573104858</v>
       </c>
       <c r="H589" t="n">
         <v>18000</v>
@@ -17479,7 +17479,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G590" t="n">
-        <v>5.43856477737427</v>
+        <v>5.43856573104858</v>
       </c>
       <c r="H590" t="n">
         <v>10770</v>
@@ -17508,7 +17508,7 @@
         <v>6</v>
       </c>
       <c r="G591" t="n">
-        <v>5.47506618499756</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H591" t="n">
         <v>16840</v>
@@ -17537,7 +17537,7 @@
         <v>6</v>
       </c>
       <c r="G592" t="n">
-        <v>5.47506618499756</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H592" t="n">
         <v>6770</v>
@@ -17566,7 +17566,7 @@
         <v>6</v>
       </c>
       <c r="G593" t="n">
-        <v>5.47506618499756</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H593" t="n">
         <v>7700</v>
@@ -17595,7 +17595,7 @@
         <v>5.96000003814697</v>
       </c>
       <c r="G594" t="n">
-        <v>5.43856477737427</v>
+        <v>5.43856573104858</v>
       </c>
       <c r="H594" t="n">
         <v>8420</v>
@@ -17624,7 +17624,7 @@
         <v>6</v>
       </c>
       <c r="G595" t="n">
-        <v>5.47506618499756</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H595" t="n">
         <v>28420</v>
@@ -17653,7 +17653,7 @@
         <v>6</v>
       </c>
       <c r="G596" t="n">
-        <v>5.47506618499756</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H596" t="n">
         <v>16270</v>
@@ -17682,7 +17682,7 @@
         <v>6</v>
       </c>
       <c r="G597" t="n">
-        <v>5.47506618499756</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H597" t="n">
         <v>22430</v>
@@ -17711,7 +17711,7 @@
         <v>5.98000001907349</v>
       </c>
       <c r="G598" t="n">
-        <v>5.45681619644165</v>
+        <v>5.45681476593018</v>
       </c>
       <c r="H598" t="n">
         <v>7510</v>
@@ -17769,7 +17769,7 @@
         <v>6.01999998092651</v>
       </c>
       <c r="G600" t="n">
-        <v>5.49331521987915</v>
+        <v>5.49331569671631</v>
       </c>
       <c r="H600" t="n">
         <v>6490</v>
@@ -17798,7 +17798,7 @@
         <v>6</v>
       </c>
       <c r="G601" t="n">
-        <v>5.47506618499756</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H601" t="n">
         <v>12580</v>
@@ -17827,7 +17827,7 @@
         <v>6</v>
       </c>
       <c r="G602" t="n">
-        <v>5.47506618499756</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H602" t="n">
         <v>14360</v>
@@ -17885,7 +17885,7 @@
         <v>6</v>
       </c>
       <c r="G604" t="n">
-        <v>5.47506618499756</v>
+        <v>5.4750657081604</v>
       </c>
       <c r="H604" t="n">
         <v>7460</v>
@@ -17943,7 +17943,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G606" t="n">
-        <v>5.69406843185425</v>
+        <v>5.69406795501709</v>
       </c>
       <c r="H606" t="n">
         <v>42810</v>
@@ -17972,7 +17972,7 @@
         <v>6.3600001335144</v>
       </c>
       <c r="G607" t="n">
-        <v>5.80356979370117</v>
+        <v>5.80357027053833</v>
       </c>
       <c r="H607" t="n">
         <v>21150</v>
@@ -18030,7 +18030,7 @@
         <v>6.90000009536743</v>
       </c>
       <c r="G609" t="n">
-        <v>6.29632568359375</v>
+        <v>6.29632616043091</v>
       </c>
       <c r="H609" t="n">
         <v>137430</v>
@@ -18059,7 +18059,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G610" t="n">
-        <v>6.278076171875</v>
+        <v>6.27807521820068</v>
       </c>
       <c r="H610" t="n">
         <v>23360</v>
@@ -18088,7 +18088,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G611" t="n">
-        <v>6.40582609176636</v>
+        <v>6.40582704544067</v>
       </c>
       <c r="H611" t="n">
         <v>17630</v>
@@ -18117,7 +18117,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G612" t="n">
-        <v>6.49707746505737</v>
+        <v>6.49707794189453</v>
       </c>
       <c r="H612" t="n">
         <v>5680</v>
@@ -18146,7 +18146,7 @@
         <v>7.1399998664856</v>
       </c>
       <c r="G613" t="n">
-        <v>6.51532888412476</v>
+        <v>6.5153284072876</v>
       </c>
       <c r="H613" t="n">
         <v>31070</v>
@@ -18175,7 +18175,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G614" t="n">
-        <v>6.49707746505737</v>
+        <v>6.49707794189453</v>
       </c>
       <c r="H614" t="n">
         <v>25230</v>
@@ -18233,7 +18233,7 @@
         <v>7.11999988555908</v>
       </c>
       <c r="G616" t="n">
-        <v>6.49707746505737</v>
+        <v>6.49707794189453</v>
       </c>
       <c r="H616" t="n">
         <v>64600</v>
@@ -18262,7 +18262,7 @@
         <v>7.17999982833862</v>
       </c>
       <c r="G617" t="n">
-        <v>6.55182886123657</v>
+        <v>6.55182838439941</v>
       </c>
       <c r="H617" t="n">
         <v>32250</v>
@@ -18320,7 +18320,7 @@
         <v>7.67999982833862</v>
       </c>
       <c r="G619" t="n">
-        <v>7.00808429718018</v>
+        <v>7.00808382034302</v>
       </c>
       <c r="H619" t="n">
         <v>96620</v>
@@ -18349,7 +18349,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G620" t="n">
-        <v>6.91683340072632</v>
+        <v>6.916832447052</v>
       </c>
       <c r="H620" t="n">
         <v>191410</v>
@@ -18378,7 +18378,7 @@
         <v>7.82000017166138</v>
       </c>
       <c r="G621" t="n">
-        <v>7.13583564758301</v>
+        <v>7.13583612442017</v>
       </c>
       <c r="H621" t="n">
         <v>180990</v>
@@ -18407,7 +18407,7 @@
         <v>8</v>
       </c>
       <c r="G622" t="n">
-        <v>7.30008745193481</v>
+        <v>7.30008840560913</v>
       </c>
       <c r="H622" t="n">
         <v>56300</v>
@@ -18465,7 +18465,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G624" t="n">
-        <v>7.62859106063843</v>
+        <v>7.62859153747559</v>
       </c>
       <c r="H624" t="n">
         <v>62840</v>
@@ -18494,7 +18494,7 @@
         <v>8.5</v>
       </c>
       <c r="G625" t="n">
-        <v>7.75634431838989</v>
+        <v>7.75634336471558</v>
       </c>
       <c r="H625" t="n">
         <v>102230</v>
@@ -18523,7 +18523,7 @@
         <v>8.47999954223633</v>
       </c>
       <c r="G626" t="n">
-        <v>7.73809242248535</v>
+        <v>7.73809146881104</v>
       </c>
       <c r="H626" t="n">
         <v>60240</v>
@@ -18668,7 +18668,7 @@
         <v>8.5</v>
       </c>
       <c r="G631" t="n">
-        <v>7.75634431838989</v>
+        <v>7.75634336471558</v>
       </c>
       <c r="H631" t="n">
         <v>24340</v>
@@ -18726,7 +18726,7 @@
         <v>8.73999977111816</v>
       </c>
       <c r="G633" t="n">
-        <v>7.97534513473511</v>
+        <v>7.97534608840942</v>
       </c>
       <c r="H633" t="n">
         <v>75730</v>
@@ -18784,7 +18784,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G635" t="n">
-        <v>8.57760143280029</v>
+        <v>8.57760238647461</v>
       </c>
       <c r="H635" t="n">
         <v>55940</v>
@@ -18958,7 +18958,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G641" t="n">
-        <v>8.55935192108154</v>
+        <v>8.55935382843018</v>
       </c>
       <c r="H641" t="n">
         <v>30110</v>
@@ -18987,7 +18987,7 @@
         <v>9.4399995803833</v>
       </c>
       <c r="G642" t="n">
-        <v>8.61410236358643</v>
+        <v>8.61410331726074</v>
       </c>
       <c r="H642" t="n">
         <v>18550</v>
@@ -19016,7 +19016,7 @@
         <v>9.39999961853027</v>
       </c>
       <c r="G643" t="n">
-        <v>8.57760143280029</v>
+        <v>8.57760238647461</v>
       </c>
       <c r="H643" t="n">
         <v>18630</v>
@@ -19074,7 +19074,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G645" t="n">
-        <v>8.37685012817383</v>
+        <v>8.37685108184814</v>
       </c>
       <c r="H645" t="n">
         <v>15640</v>
@@ -19132,7 +19132,7 @@
         <v>8.92000007629395</v>
       </c>
       <c r="G647" t="n">
-        <v>8.13959789276123</v>
+        <v>8.13959693908691</v>
       </c>
       <c r="H647" t="n">
         <v>104150</v>
@@ -19190,7 +19190,7 @@
         <v>9.34000015258789</v>
       </c>
       <c r="G649" t="n">
-        <v>8.52285289764404</v>
+        <v>8.52285194396973</v>
       </c>
       <c r="H649" t="n">
         <v>12850</v>
@@ -19219,7 +19219,7 @@
         <v>9.18000030517578</v>
       </c>
       <c r="G650" t="n">
-        <v>8.37685012817383</v>
+        <v>8.37685108184814</v>
       </c>
       <c r="H650" t="n">
         <v>10860</v>
@@ -19248,7 +19248,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G651" t="n">
-        <v>8.55935192108154</v>
+        <v>8.55935382843018</v>
       </c>
       <c r="H651" t="n">
         <v>24170</v>
@@ -19277,7 +19277,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G652" t="n">
-        <v>8.54110336303711</v>
+        <v>8.54110145568848</v>
       </c>
       <c r="H652" t="n">
         <v>13040</v>
@@ -19306,7 +19306,7 @@
         <v>9.35999965667725</v>
       </c>
       <c r="G653" t="n">
-        <v>8.54110336303711</v>
+        <v>8.54110145568848</v>
       </c>
       <c r="H653" t="n">
         <v>7250</v>
@@ -19364,7 +19364,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G655" t="n">
-        <v>9.08860969543457</v>
+        <v>9.08860874176025</v>
       </c>
       <c r="H655" t="n">
         <v>93420</v>
@@ -19480,7 +19480,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G659" t="n">
-        <v>9.9919958114624</v>
+        <v>9.99199390411377</v>
       </c>
       <c r="H659" t="n">
         <v>95020</v>
@@ -19567,7 +19567,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G662" t="n">
-        <v>9.67261600494385</v>
+        <v>9.67261695861816</v>
       </c>
       <c r="H662" t="n">
         <v>63420</v>
@@ -19683,7 +19683,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G666" t="n">
-        <v>9.62699031829834</v>
+        <v>9.62698936462402</v>
       </c>
       <c r="H666" t="n">
         <v>26760</v>
@@ -19712,7 +19712,7 @@
         <v>10.75</v>
       </c>
       <c r="G667" t="n">
-        <v>9.80949211120605</v>
+        <v>9.80949306488037</v>
       </c>
       <c r="H667" t="n">
         <v>19160</v>
@@ -19857,7 +19857,7 @@
         <v>10</v>
       </c>
       <c r="G672" t="n">
-        <v>9.1251106262207</v>
+        <v>9.12510871887207</v>
       </c>
       <c r="H672" t="n">
         <v>49670</v>
@@ -19973,7 +19973,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G676" t="n">
-        <v>9.67261600494385</v>
+        <v>9.67261695861816</v>
       </c>
       <c r="H676" t="n">
         <v>54230</v>
@@ -20002,7 +20002,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G677" t="n">
-        <v>9.94637107849121</v>
+        <v>9.94636917114258</v>
       </c>
       <c r="H677" t="n">
         <v>77360</v>
@@ -20031,7 +20031,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G678" t="n">
-        <v>9.9919958114624</v>
+        <v>9.99199390411377</v>
       </c>
       <c r="H678" t="n">
         <v>19160</v>
@@ -20060,7 +20060,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G679" t="n">
-        <v>9.9919958114624</v>
+        <v>9.99199390411377</v>
       </c>
       <c r="H679" t="n">
         <v>67650</v>
@@ -20089,7 +20089,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G680" t="n">
-        <v>9.9919958114624</v>
+        <v>9.99199390411377</v>
       </c>
       <c r="H680" t="n">
         <v>15440</v>
@@ -20118,7 +20118,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G681" t="n">
-        <v>9.9919958114624</v>
+        <v>9.99199390411377</v>
       </c>
       <c r="H681" t="n">
         <v>10490</v>
@@ -20147,7 +20147,7 @@
         <v>10.9499998092651</v>
       </c>
       <c r="G682" t="n">
-        <v>9.9919958114624</v>
+        <v>9.99199390411377</v>
       </c>
       <c r="H682" t="n">
         <v>16670</v>
@@ -20176,7 +20176,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G683" t="n">
-        <v>9.67261600494385</v>
+        <v>9.67261695861816</v>
       </c>
       <c r="H683" t="n">
         <v>35330</v>
@@ -20205,7 +20205,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G684" t="n">
-        <v>9.67261600494385</v>
+        <v>9.67261695861816</v>
       </c>
       <c r="H684" t="n">
         <v>10770</v>
@@ -20234,7 +20234,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G685" t="n">
-        <v>9.67261600494385</v>
+        <v>9.67261695861816</v>
       </c>
       <c r="H685" t="n">
         <v>49820</v>
@@ -20263,7 +20263,7 @@
         <v>10.75</v>
       </c>
       <c r="G686" t="n">
-        <v>9.80949211120605</v>
+        <v>9.80949306488037</v>
       </c>
       <c r="H686" t="n">
         <v>46500</v>
@@ -20321,7 +20321,7 @@
         <v>9.76000022888184</v>
       </c>
       <c r="G688" t="n">
-        <v>8.90610599517822</v>
+        <v>8.90610694885254</v>
       </c>
       <c r="H688" t="n">
         <v>56290</v>
@@ -20350,7 +20350,7 @@
         <v>10.1499996185303</v>
       </c>
       <c r="G689" t="n">
-        <v>9.26198482513428</v>
+        <v>9.26198577880859</v>
       </c>
       <c r="H689" t="n">
         <v>49040</v>
@@ -20379,7 +20379,7 @@
         <v>10.5500001907349</v>
       </c>
       <c r="G690" t="n">
-        <v>9.62699031829834</v>
+        <v>9.62698936462402</v>
       </c>
       <c r="H690" t="n">
         <v>39680</v>
@@ -20408,7 +20408,7 @@
         <v>9.97999954223633</v>
       </c>
       <c r="G691" t="n">
-        <v>9.106858253479</v>
+        <v>9.10685920715332</v>
       </c>
       <c r="H691" t="n">
         <v>118490</v>
@@ -20437,7 +20437,7 @@
         <v>9.85999965667725</v>
       </c>
       <c r="G692" t="n">
-        <v>8.99735736846924</v>
+        <v>8.99735832214355</v>
       </c>
       <c r="H692" t="n">
         <v>50390</v>
@@ -20466,7 +20466,7 @@
         <v>9.61999988555908</v>
       </c>
       <c r="G693" t="n">
-        <v>8.77835559844971</v>
+        <v>8.77835464477539</v>
       </c>
       <c r="H693" t="n">
         <v>65620</v>
@@ -20495,7 +20495,7 @@
         <v>9.84000015258789</v>
       </c>
       <c r="G694" t="n">
-        <v>8.9791088104248</v>
+        <v>8.97910785675049</v>
       </c>
       <c r="H694" t="n">
         <v>18270</v>
@@ -20553,7 +20553,7 @@
         <v>9.38000011444092</v>
       </c>
       <c r="G696" t="n">
-        <v>8.55935192108154</v>
+        <v>8.55935382843018</v>
       </c>
       <c r="H696" t="n">
         <v>17980</v>
@@ -20611,7 +20611,7 @@
         <v>8.34000015258789</v>
       </c>
       <c r="G698" t="n">
-        <v>7.61034107208252</v>
+        <v>7.61034202575684</v>
       </c>
       <c r="H698" t="n">
         <v>97230</v>
@@ -20669,7 +20669,7 @@
         <v>8</v>
       </c>
       <c r="G700" t="n">
-        <v>7.30008745193481</v>
+        <v>7.30008840560913</v>
       </c>
       <c r="H700" t="n">
         <v>37410</v>
@@ -20698,7 +20698,7 @@
         <v>7.5</v>
       </c>
       <c r="G701" t="n">
-        <v>6.84383249282837</v>
+        <v>6.84383201599121</v>
       </c>
       <c r="H701" t="n">
         <v>39240</v>
@@ -20814,7 +20814,7 @@
         <v>7.57999992370605</v>
       </c>
       <c r="G705" t="n">
-        <v>6.91683340072632</v>
+        <v>6.916832447052</v>
       </c>
       <c r="H705" t="n">
         <v>3640</v>
@@ -20930,7 +20930,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G709" t="n">
-        <v>7.62859106063843</v>
+        <v>7.62859153747559</v>
       </c>
       <c r="H709" t="n">
         <v>49380</v>
@@ -20959,7 +20959,7 @@
         <v>8.80000019073486</v>
       </c>
       <c r="G710" t="n">
-        <v>8.03009700775146</v>
+        <v>8.03009605407715</v>
       </c>
       <c r="H710" t="n">
         <v>47530</v>
@@ -20988,7 +20988,7 @@
         <v>8.38000011444092</v>
       </c>
       <c r="G711" t="n">
-        <v>7.64684104919434</v>
+        <v>7.64684152603149</v>
       </c>
       <c r="H711" t="n">
         <v>22410</v>
@@ -21017,7 +21017,7 @@
         <v>8.52000045776367</v>
       </c>
       <c r="G712" t="n">
-        <v>7.77459335327148</v>
+        <v>7.7745943069458</v>
       </c>
       <c r="H712" t="n">
         <v>8030</v>
@@ -21046,7 +21046,7 @@
         <v>8.5</v>
       </c>
       <c r="G713" t="n">
-        <v>7.75634431838989</v>
+        <v>7.75634336471558</v>
       </c>
       <c r="H713" t="n">
         <v>8220</v>
@@ -21104,7 +21104,7 @@
         <v>8.81999969482422</v>
       </c>
       <c r="G715" t="n">
-        <v>8.04834651947021</v>
+        <v>8.04834747314453</v>
       </c>
       <c r="H715" t="n">
         <v>3610</v>
@@ -21220,7 +21220,7 @@
         <v>9.60000038146973</v>
       </c>
       <c r="G719" t="n">
-        <v>8.76010513305664</v>
+        <v>8.76010608673096</v>
       </c>
       <c r="H719" t="n">
         <v>30560</v>
@@ -21278,7 +21278,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G721" t="n">
-        <v>9.05210971832275</v>
+        <v>9.05210876464844</v>
       </c>
       <c r="H721" t="n">
         <v>33160</v>
@@ -21307,7 +21307,7 @@
         <v>10.1000003814697</v>
       </c>
       <c r="G722" t="n">
-        <v>9.21636009216309</v>
+        <v>9.2163610458374</v>
       </c>
       <c r="H722" t="n">
         <v>12760</v>
@@ -21336,7 +21336,7 @@
         <v>9.77999973297119</v>
       </c>
       <c r="G723" t="n">
-        <v>8.92435646057129</v>
+        <v>8.92435550689697</v>
       </c>
       <c r="H723" t="n">
         <v>29670</v>
@@ -21365,7 +21365,7 @@
         <v>9.92000007629395</v>
       </c>
       <c r="G724" t="n">
-        <v>9.05210971832275</v>
+        <v>9.05210876464844</v>
       </c>
       <c r="H724" t="n">
         <v>15780</v>
@@ -21394,7 +21394,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G725" t="n">
-        <v>9.08860969543457</v>
+        <v>9.08860874176025</v>
       </c>
       <c r="H725" t="n">
         <v>13110</v>
@@ -21423,7 +21423,7 @@
         <v>9.96000003814697</v>
       </c>
       <c r="G726" t="n">
-        <v>9.08860969543457</v>
+        <v>9.08860874176025</v>
       </c>
       <c r="H726" t="n">
         <v>16420</v>
@@ -21452,7 +21452,7 @@
         <v>10.3500003814697</v>
       </c>
       <c r="G727" t="n">
-        <v>9.44448947906494</v>
+        <v>9.44448852539062</v>
       </c>
       <c r="H727" t="n">
         <v>44000</v>
@@ -21568,7 +21568,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G731" t="n">
-        <v>9.67261600494385</v>
+        <v>9.67261695861816</v>
       </c>
       <c r="H731" t="n">
         <v>42830</v>
@@ -21597,7 +21597,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G732" t="n">
-        <v>9.67261600494385</v>
+        <v>9.67261695861816</v>
       </c>
       <c r="H732" t="n">
         <v>33020</v>
@@ -21626,7 +21626,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G733" t="n">
-        <v>10.2201223373413</v>
+        <v>10.2201232910156</v>
       </c>
       <c r="H733" t="n">
         <v>77220</v>
@@ -21684,7 +21684,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G735" t="n">
-        <v>10.356390953064</v>
+        <v>10.3563919067383</v>
       </c>
       <c r="H735" t="n">
         <v>21950</v>
@@ -21742,7 +21742,7 @@
         <v>11.0500001907349</v>
       </c>
       <c r="G737" t="n">
-        <v>10.2176895141602</v>
+        <v>10.2176904678345</v>
       </c>
       <c r="H737" t="n">
         <v>35810</v>
@@ -21800,7 +21800,7 @@
         <v>11</v>
       </c>
       <c r="G739" t="n">
-        <v>10.1714563369751</v>
+        <v>10.1714553833008</v>
       </c>
       <c r="H739" t="n">
         <v>10800</v>
@@ -22003,7 +22003,7 @@
         <v>10.5</v>
       </c>
       <c r="G746" t="n">
-        <v>9.70911693572998</v>
+        <v>9.70911598205566</v>
       </c>
       <c r="H746" t="n">
         <v>22620</v>
@@ -22032,7 +22032,7 @@
         <v>10.25</v>
       </c>
       <c r="G747" t="n">
-        <v>9.47794818878174</v>
+        <v>9.47794723510742</v>
       </c>
       <c r="H747" t="n">
         <v>44360</v>
@@ -22061,7 +22061,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G748" t="n">
-        <v>9.80158424377441</v>
+        <v>9.80158519744873</v>
       </c>
       <c r="H748" t="n">
         <v>18650</v>
@@ -22119,7 +22119,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G750" t="n">
-        <v>9.80158424377441</v>
+        <v>9.80158519744873</v>
       </c>
       <c r="H750" t="n">
         <v>12500</v>
@@ -22148,7 +22148,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G751" t="n">
-        <v>9.80158424377441</v>
+        <v>9.80158519744873</v>
       </c>
       <c r="H751" t="n">
         <v>12920</v>
@@ -22206,7 +22206,7 @@
         <v>10.6000003814697</v>
       </c>
       <c r="G753" t="n">
-        <v>9.80158424377441</v>
+        <v>9.80158519744873</v>
       </c>
       <c r="H753" t="n">
         <v>19270</v>
@@ -22264,7 +22264,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G755" t="n">
-        <v>10.0789880752563</v>
+        <v>10.078987121582</v>
       </c>
       <c r="H755" t="n">
         <v>14220</v>
@@ -22293,7 +22293,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G756" t="n">
-        <v>10.356390953064</v>
+        <v>10.3563919067383</v>
       </c>
       <c r="H756" t="n">
         <v>20470</v>
@@ -22351,7 +22351,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G758" t="n">
-        <v>10.4488582611084</v>
+        <v>10.4488592147827</v>
       </c>
       <c r="H758" t="n">
         <v>15180</v>
@@ -22409,7 +22409,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G760" t="n">
-        <v>10.4488582611084</v>
+        <v>10.4488592147827</v>
       </c>
       <c r="H760" t="n">
         <v>19520</v>
@@ -22438,7 +22438,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G761" t="n">
-        <v>10.356390953064</v>
+        <v>10.3563919067383</v>
       </c>
       <c r="H761" t="n">
         <v>13730</v>
@@ -22467,7 +22467,7 @@
         <v>11.1999998092651</v>
       </c>
       <c r="G762" t="n">
-        <v>10.356390953064</v>
+        <v>10.3563919067383</v>
       </c>
       <c r="H762" t="n">
         <v>6510</v>
@@ -22496,7 +22496,7 @@
         <v>11.3000001907349</v>
       </c>
       <c r="G763" t="n">
-        <v>10.4488582611084</v>
+        <v>10.4488592147827</v>
       </c>
       <c r="H763" t="n">
         <v>11290</v>
@@ -22525,7 +22525,7 @@
         <v>11</v>
       </c>
       <c r="G764" t="n">
-        <v>10.1714563369751</v>
+        <v>10.1714553833008</v>
       </c>
       <c r="H764" t="n">
         <v>11870</v>
@@ -22554,7 +22554,7 @@
         <v>10.8999996185303</v>
       </c>
       <c r="G765" t="n">
-        <v>10.0789880752563</v>
+        <v>10.078987121582</v>
       </c>
       <c r="H765" t="n">
         <v>5710</v>
@@ -22641,7 +22641,7 @@
         <v>11.8999996185303</v>
       </c>
       <c r="G768" t="n">
-        <v>11.0036649703979</v>
+        <v>11.0036659240723</v>
       </c>
       <c r="H768" t="n">
         <v>17250</v>
@@ -22699,7 +22699,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G770" t="n">
-        <v>11.9745769500732</v>
+        <v>11.9745788574219</v>
       </c>
       <c r="H770" t="n">
         <v>78780</v>
@@ -22757,7 +22757,7 @@
         <v>13</v>
       </c>
       <c r="G772" t="n">
-        <v>12.0208101272583</v>
+        <v>12.0208110809326</v>
       </c>
       <c r="H772" t="n">
         <v>77200</v>
@@ -22815,7 +22815,7 @@
         <v>13.25</v>
       </c>
       <c r="G774" t="n">
-        <v>12.2519817352295</v>
+        <v>12.2519807815552</v>
       </c>
       <c r="H774" t="n">
         <v>28340</v>
@@ -22844,7 +22844,7 @@
         <v>13.1000003814697</v>
       </c>
       <c r="G775" t="n">
-        <v>12.1132783889771</v>
+        <v>12.1132793426514</v>
       </c>
       <c r="H775" t="n">
         <v>46310</v>
@@ -22873,7 +22873,7 @@
         <v>13</v>
       </c>
       <c r="G776" t="n">
-        <v>12.0208101272583</v>
+        <v>12.0208110809326</v>
       </c>
       <c r="H776" t="n">
         <v>24820</v>
@@ -22902,7 +22902,7 @@
         <v>13.1499996185303</v>
       </c>
       <c r="G777" t="n">
-        <v>12.1595115661621</v>
+        <v>12.1595125198364</v>
       </c>
       <c r="H777" t="n">
         <v>41060</v>
@@ -22931,7 +22931,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G778" t="n">
-        <v>11.9745769500732</v>
+        <v>11.9745788574219</v>
       </c>
       <c r="H778" t="n">
         <v>12920</v>
@@ -22960,7 +22960,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G779" t="n">
-        <v>11.8821096420288</v>
+        <v>11.8821086883545</v>
       </c>
       <c r="H779" t="n">
         <v>65190</v>
@@ -22989,7 +22989,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G780" t="n">
-        <v>12.0670442581177</v>
+        <v>12.067045211792</v>
       </c>
       <c r="H780" t="n">
         <v>23490</v>
@@ -23018,7 +23018,7 @@
         <v>13</v>
       </c>
       <c r="G781" t="n">
-        <v>12.0208101272583</v>
+        <v>12.0208110809326</v>
       </c>
       <c r="H781" t="n">
         <v>26420</v>
@@ -23047,7 +23047,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G782" t="n">
-        <v>11.8821096420288</v>
+        <v>11.8821086883545</v>
       </c>
       <c r="H782" t="n">
         <v>16280</v>
@@ -23076,7 +23076,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G783" t="n">
-        <v>11.9283437728882</v>
+        <v>11.9283428192139</v>
       </c>
       <c r="H783" t="n">
         <v>13400</v>
@@ -23134,7 +23134,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G785" t="n">
-        <v>11.9745769500732</v>
+        <v>11.9745788574219</v>
       </c>
       <c r="H785" t="n">
         <v>15410</v>
@@ -23221,7 +23221,7 @@
         <v>12.8500003814697</v>
       </c>
       <c r="G788" t="n">
-        <v>11.8821096420288</v>
+        <v>11.8821086883545</v>
       </c>
       <c r="H788" t="n">
         <v>39850</v>
@@ -23250,7 +23250,7 @@
         <v>13</v>
       </c>
       <c r="G789" t="n">
-        <v>12.0208101272583</v>
+        <v>12.0208110809326</v>
       </c>
       <c r="H789" t="n">
         <v>50180</v>
@@ -23279,7 +23279,7 @@
         <v>12.8999996185303</v>
       </c>
       <c r="G790" t="n">
-        <v>11.9283437728882</v>
+        <v>11.9283428192139</v>
       </c>
       <c r="H790" t="n">
         <v>20180</v>
@@ -23366,7 +23366,7 @@
         <v>12.4499998092651</v>
       </c>
       <c r="G793" t="n">
-        <v>11.5122385025024</v>
+        <v>11.5122375488281</v>
       </c>
       <c r="H793" t="n">
         <v>31350</v>
@@ -23482,7 +23482,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G797" t="n">
-        <v>11.6971740722656</v>
+        <v>11.6971731185913</v>
       </c>
       <c r="H797" t="n">
         <v>4440</v>
@@ -23511,7 +23511,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G798" t="n">
-        <v>11.4197702407837</v>
+        <v>11.419771194458</v>
       </c>
       <c r="H798" t="n">
         <v>21780</v>
@@ -23540,7 +23540,7 @@
         <v>12.25</v>
       </c>
       <c r="G799" t="n">
-        <v>11.3273029327393</v>
+        <v>11.3273019790649</v>
       </c>
       <c r="H799" t="n">
         <v>3520</v>
@@ -23569,7 +23569,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G800" t="n">
-        <v>11.3735370635986</v>
+        <v>11.3735380172729</v>
       </c>
       <c r="H800" t="n">
         <v>8530</v>
@@ -23598,7 +23598,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G801" t="n">
-        <v>11.1423673629761</v>
+        <v>11.1423664093018</v>
       </c>
       <c r="H801" t="n">
         <v>15210</v>
@@ -23656,7 +23656,7 @@
         <v>12.0500001907349</v>
       </c>
       <c r="G803" t="n">
-        <v>11.1423673629761</v>
+        <v>11.1423664093018</v>
       </c>
       <c r="H803" t="n">
         <v>60080</v>
@@ -23685,7 +23685,7 @@
         <v>12.25</v>
       </c>
       <c r="G804" t="n">
-        <v>11.3273029327393</v>
+        <v>11.3273019790649</v>
       </c>
       <c r="H804" t="n">
         <v>15270</v>
@@ -23714,7 +23714,7 @@
         <v>12.25</v>
       </c>
       <c r="G805" t="n">
-        <v>11.3273029327393</v>
+        <v>11.3273019790649</v>
       </c>
       <c r="H805" t="n">
         <v>23490</v>
@@ -23743,7 +23743,7 @@
         <v>12.25</v>
       </c>
       <c r="G806" t="n">
-        <v>11.3273029327393</v>
+        <v>11.3273019790649</v>
       </c>
       <c r="H806" t="n">
         <v>605530</v>
@@ -23801,7 +23801,7 @@
         <v>12.3000001907349</v>
       </c>
       <c r="G808" t="n">
-        <v>11.3735370635986</v>
+        <v>11.3735380172729</v>
       </c>
       <c r="H808" t="n">
         <v>2960</v>
@@ -23859,7 +23859,7 @@
         <v>12.3500003814697</v>
       </c>
       <c r="G810" t="n">
-        <v>11.4197702407837</v>
+        <v>11.419771194458</v>
       </c>
       <c r="H810" t="n">
         <v>29160</v>
@@ -23888,7 +23888,7 @@
         <v>12.5</v>
       </c>
       <c r="G811" t="n">
-        <v>11.5584716796875</v>
+        <v>11.5584726333618</v>
       </c>
       <c r="H811" t="n">
         <v>22990</v>
@@ -23946,7 +23946,7 @@
         <v>12.5</v>
       </c>
       <c r="G813" t="n">
-        <v>11.5584716796875</v>
+        <v>11.5584726333618</v>
       </c>
       <c r="H813" t="n">
         <v>9780</v>
@@ -24120,7 +24120,7 @@
         <v>12.6499996185303</v>
       </c>
       <c r="G819" t="n">
-        <v>11.6971740722656</v>
+        <v>11.6971731185913</v>
       </c>
       <c r="H819" t="n">
         <v>3740</v>
@@ -24207,7 +24207,7 @@
         <v>12.25</v>
       </c>
       <c r="G822" t="n">
-        <v>11.3273029327393</v>
+        <v>11.3273019790649</v>
       </c>
       <c r="H822" t="n">
         <v>16210</v>
@@ -24294,7 +24294,7 @@
         <v>12.9499998092651</v>
       </c>
       <c r="G825" t="n">
-        <v>11.9745769500732</v>
+        <v>11.9745788574219</v>
       </c>
       <c r="H825" t="n">
         <v>36370</v>
@@ -24323,7 +24323,7 @@
         <v>13.0500001907349</v>
       </c>
       <c r="G826" t="n">
-        <v>12.0670442581177</v>
+        <v>12.067045211792</v>
       </c>
       <c r="H826" t="n">
         <v>21820</v>
@@ -24352,7 +24352,7 @@
         <v>13.3500003814697</v>
       </c>
       <c r="G827" t="n">
-        <v>12.3444480895996</v>
+        <v>12.3444490432739</v>
       </c>
       <c r="H827" t="n">
         <v>26740</v>
@@ -24381,7 +24381,7 @@
         <v>13.9499998092651</v>
       </c>
       <c r="G828" t="n">
-        <v>12.8992538452148</v>
+        <v>12.8992547988892</v>
       </c>
       <c r="H828" t="n">
         <v>160820</v>
@@ -24439,7 +24439,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G830" t="n">
-        <v>13.4540615081787</v>
+        <v>13.454062461853</v>
       </c>
       <c r="H830" t="n">
         <v>46270</v>
@@ -24468,7 +24468,7 @@
         <v>14.8500003814697</v>
       </c>
       <c r="G831" t="n">
-        <v>13.731466293335</v>
+        <v>13.7314653396606</v>
       </c>
       <c r="H831" t="n">
         <v>44910</v>
@@ -24584,7 +24584,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G835" t="n">
-        <v>15.3496503829956</v>
+        <v>15.3496522903442</v>
       </c>
       <c r="H835" t="n">
         <v>255790</v>
@@ -24613,7 +24613,7 @@
         <v>16.25</v>
       </c>
       <c r="G836" t="n">
-        <v>15.0260133743286</v>
+        <v>15.0260143280029</v>
       </c>
       <c r="H836" t="n">
         <v>116230</v>
@@ -24642,7 +24642,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G837" t="n">
-        <v>16.3667984008789</v>
+        <v>16.3667964935303</v>
       </c>
       <c r="H837" t="n">
         <v>162970</v>
@@ -24671,7 +24671,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G838" t="n">
-        <v>16.4592666625977</v>
+        <v>16.459264755249</v>
       </c>
       <c r="H838" t="n">
         <v>124100</v>
@@ -24700,7 +24700,7 @@
         <v>17.6000003814697</v>
       </c>
       <c r="G839" t="n">
-        <v>16.2743301391602</v>
+        <v>16.2743282318115</v>
       </c>
       <c r="H839" t="n">
         <v>58260</v>
@@ -24729,7 +24729,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G840" t="n">
-        <v>16.2280960083008</v>
+        <v>16.2280941009521</v>
       </c>
       <c r="H840" t="n">
         <v>33380</v>
@@ -24758,7 +24758,7 @@
         <v>17.5499992370605</v>
       </c>
       <c r="G841" t="n">
-        <v>16.2280960083008</v>
+        <v>16.2280941009521</v>
       </c>
       <c r="H841" t="n">
         <v>35580</v>
@@ -24787,7 +24787,7 @@
         <v>17.3500003814697</v>
       </c>
       <c r="G842" t="n">
-        <v>16.0431594848633</v>
+        <v>16.0431613922119</v>
       </c>
       <c r="H842" t="n">
         <v>56920</v>
@@ -24816,7 +24816,7 @@
         <v>17</v>
       </c>
       <c r="G843" t="n">
-        <v>15.7195243835449</v>
+        <v>15.7195234298706</v>
       </c>
       <c r="H843" t="n">
         <v>42810</v>
@@ -24845,7 +24845,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G844" t="n">
-        <v>15.3496503829956</v>
+        <v>15.3496522903442</v>
       </c>
       <c r="H844" t="n">
         <v>34830</v>
@@ -24874,7 +24874,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G845" t="n">
-        <v>15.1647157669067</v>
+        <v>15.1647138595581</v>
       </c>
       <c r="H845" t="n">
         <v>20040</v>
@@ -24903,7 +24903,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G846" t="n">
-        <v>14.9335460662842</v>
+        <v>14.9335470199585</v>
       </c>
       <c r="H846" t="n">
         <v>19060</v>
@@ -24990,7 +24990,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G849" t="n">
-        <v>15.2109498977661</v>
+        <v>15.2109508514404</v>
       </c>
       <c r="H849" t="n">
         <v>26350</v>
@@ -25106,7 +25106,7 @@
         <v>17.1000003814697</v>
       </c>
       <c r="G853" t="n">
-        <v>15.8119897842407</v>
+        <v>15.8119878768921</v>
       </c>
       <c r="H853" t="n">
         <v>22700</v>
@@ -25164,7 +25164,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G855" t="n">
-        <v>15.1647157669067</v>
+        <v>15.1647138595581</v>
       </c>
       <c r="H855" t="n">
         <v>18370</v>
@@ -25222,7 +25222,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G857" t="n">
-        <v>14.748610496521</v>
+        <v>14.7486095428467</v>
       </c>
       <c r="H857" t="n">
         <v>33860</v>
@@ -25251,7 +25251,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G858" t="n">
-        <v>14.4249725341797</v>
+        <v>14.424973487854</v>
       </c>
       <c r="H858" t="n">
         <v>37180</v>
@@ -25280,7 +25280,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G859" t="n">
-        <v>13.9163999557495</v>
+        <v>13.9164009094238</v>
       </c>
       <c r="H859" t="n">
         <v>29820</v>
@@ -25483,7 +25483,7 @@
         <v>14.5</v>
       </c>
       <c r="G866" t="n">
-        <v>13.4078273773193</v>
+        <v>13.4078283309937</v>
       </c>
       <c r="H866" t="n">
         <v>30230</v>
@@ -25512,7 +25512,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G867" t="n">
-        <v>15.3496503829956</v>
+        <v>15.3496522903442</v>
       </c>
       <c r="H867" t="n">
         <v>95890</v>
@@ -25541,7 +25541,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G868" t="n">
-        <v>15.6732873916626</v>
+        <v>15.6732892990112</v>
       </c>
       <c r="H868" t="n">
         <v>55200</v>
@@ -25599,7 +25599,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G870" t="n">
-        <v>15.3496503829956</v>
+        <v>15.3496522903442</v>
       </c>
       <c r="H870" t="n">
         <v>41320</v>
@@ -25657,7 +25657,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G872" t="n">
-        <v>15.0722465515137</v>
+        <v>15.0722455978394</v>
       </c>
       <c r="H872" t="n">
         <v>19800</v>
@@ -25686,7 +25686,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G873" t="n">
-        <v>14.748610496521</v>
+        <v>14.7486095428467</v>
       </c>
       <c r="H873" t="n">
         <v>34450</v>
@@ -25715,7 +25715,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G874" t="n">
-        <v>14.5174407958984</v>
+        <v>14.5174417495728</v>
       </c>
       <c r="H874" t="n">
         <v>46760</v>
@@ -25773,7 +25773,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G876" t="n">
-        <v>14.1475687026978</v>
+        <v>14.1475696563721</v>
       </c>
       <c r="H876" t="n">
         <v>139850</v>
@@ -25802,7 +25802,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G877" t="n">
-        <v>14.2862720489502</v>
+        <v>14.2862701416016</v>
       </c>
       <c r="H877" t="n">
         <v>37840</v>
@@ -25831,7 +25831,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G878" t="n">
-        <v>14.3787393569946</v>
+        <v>14.3787403106689</v>
       </c>
       <c r="H878" t="n">
         <v>28380</v>
@@ -25860,7 +25860,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G879" t="n">
-        <v>14.7023773193359</v>
+        <v>14.7023763656616</v>
       </c>
       <c r="H879" t="n">
         <v>26030</v>
@@ -25976,7 +25976,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G883" t="n">
-        <v>14.0088663101196</v>
+        <v>14.0088672637939</v>
       </c>
       <c r="H883" t="n">
         <v>7410</v>
@@ -26005,7 +26005,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G884" t="n">
-        <v>13.9163999557495</v>
+        <v>13.9164009094238</v>
       </c>
       <c r="H884" t="n">
         <v>4530</v>
@@ -26063,7 +26063,7 @@
         <v>14.9499998092651</v>
       </c>
       <c r="G886" t="n">
-        <v>13.8239316940308</v>
+        <v>13.8239326477051</v>
       </c>
       <c r="H886" t="n">
         <v>12290</v>
@@ -26092,7 +26092,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G887" t="n">
-        <v>13.4540615081787</v>
+        <v>13.454062461853</v>
       </c>
       <c r="H887" t="n">
         <v>24830</v>
@@ -26121,7 +26121,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G888" t="n">
-        <v>13.3153591156006</v>
+        <v>13.3153600692749</v>
       </c>
       <c r="H888" t="n">
         <v>25250</v>
@@ -26150,7 +26150,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G889" t="n">
-        <v>13.2228908538818</v>
+        <v>13.2228918075562</v>
       </c>
       <c r="H889" t="n">
         <v>14330</v>
@@ -26208,7 +26208,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G891" t="n">
-        <v>13.5927629470825</v>
+        <v>13.5927648544312</v>
       </c>
       <c r="H891" t="n">
         <v>11060</v>
@@ -26353,7 +26353,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G896" t="n">
-        <v>14.5174407958984</v>
+        <v>14.5174417495728</v>
       </c>
       <c r="H896" t="n">
         <v>32480</v>
@@ -26440,7 +26440,7 @@
         <v>16.9500007629395</v>
       </c>
       <c r="G899" t="n">
-        <v>15.6732873916626</v>
+        <v>15.6732892990112</v>
       </c>
       <c r="H899" t="n">
         <v>45260</v>
@@ -26469,7 +26469,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G900" t="n">
-        <v>14.8873128890991</v>
+        <v>14.8873119354248</v>
       </c>
       <c r="H900" t="n">
         <v>36170</v>
@@ -26498,7 +26498,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G901" t="n">
-        <v>15.1647157669067</v>
+        <v>15.1647138595581</v>
       </c>
       <c r="H901" t="n">
         <v>29720</v>
@@ -26527,7 +26527,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G902" t="n">
-        <v>15.0722465515137</v>
+        <v>15.0722455978394</v>
       </c>
       <c r="H902" t="n">
         <v>35920</v>
@@ -26556,7 +26556,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G903" t="n">
-        <v>14.9335460662842</v>
+        <v>14.9335470199585</v>
       </c>
       <c r="H903" t="n">
         <v>18950</v>
@@ -26585,7 +26585,7 @@
         <v>16.4500007629395</v>
       </c>
       <c r="G904" t="n">
-        <v>15.2109498977661</v>
+        <v>15.2109508514404</v>
       </c>
       <c r="H904" t="n">
         <v>27460</v>
@@ -26614,7 +26614,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G905" t="n">
-        <v>15.0722465515137</v>
+        <v>15.0722455978394</v>
       </c>
       <c r="H905" t="n">
         <v>15930</v>
@@ -26643,7 +26643,7 @@
         <v>16.7999992370605</v>
       </c>
       <c r="G906" t="n">
-        <v>15.5345859527588</v>
+        <v>15.5345840454102</v>
       </c>
       <c r="H906" t="n">
         <v>20450</v>
@@ -26672,7 +26672,7 @@
         <v>16.6000003814697</v>
       </c>
       <c r="G907" t="n">
-        <v>15.3496503829956</v>
+        <v>15.3496522903442</v>
       </c>
       <c r="H907" t="n">
         <v>13600</v>
@@ -26701,7 +26701,7 @@
         <v>16.3500003814697</v>
       </c>
       <c r="G908" t="n">
-        <v>15.118483543396</v>
+        <v>15.1184816360474</v>
       </c>
       <c r="H908" t="n">
         <v>16560</v>
@@ -26730,7 +26730,7 @@
         <v>16.1499996185303</v>
       </c>
       <c r="G909" t="n">
-        <v>14.9335460662842</v>
+        <v>14.9335470199585</v>
       </c>
       <c r="H909" t="n">
         <v>19390</v>
@@ -26788,7 +26788,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G911" t="n">
-        <v>14.748610496521</v>
+        <v>14.7486095428467</v>
       </c>
       <c r="H911" t="n">
         <v>10930</v>
@@ -26846,7 +26846,7 @@
         <v>15.3999996185303</v>
       </c>
       <c r="G913" t="n">
-        <v>14.2400369644165</v>
+        <v>14.2400379180908</v>
       </c>
       <c r="H913" t="n">
         <v>22050</v>
@@ -26875,7 +26875,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G914" t="n">
-        <v>14.4249725341797</v>
+        <v>14.424973487854</v>
       </c>
       <c r="H914" t="n">
         <v>33230</v>
@@ -26904,7 +26904,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G915" t="n">
-        <v>13.9626340866089</v>
+        <v>13.9626350402832</v>
       </c>
       <c r="H915" t="n">
         <v>10060</v>
@@ -26962,7 +26962,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G917" t="n">
-        <v>14.1475687026978</v>
+        <v>14.1475696563721</v>
       </c>
       <c r="H917" t="n">
         <v>7760</v>
@@ -27020,7 +27020,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G919" t="n">
-        <v>14.5174407958984</v>
+        <v>14.5174417495728</v>
       </c>
       <c r="H919" t="n">
         <v>24510</v>
@@ -27049,7 +27049,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G920" t="n">
-        <v>14.1475687026978</v>
+        <v>14.1475696563721</v>
       </c>
       <c r="H920" t="n">
         <v>13660</v>
@@ -27078,7 +27078,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G921" t="n">
-        <v>14.0088663101196</v>
+        <v>14.0088672637939</v>
       </c>
       <c r="H921" t="n">
         <v>21950</v>
@@ -27136,7 +27136,7 @@
         <v>14.6999998092651</v>
       </c>
       <c r="G923" t="n">
-        <v>13.5927629470825</v>
+        <v>13.5927648544312</v>
       </c>
       <c r="H923" t="n">
         <v>28750</v>
@@ -27194,7 +27194,7 @@
         <v>15.1499996185303</v>
       </c>
       <c r="G925" t="n">
-        <v>14.0088663101196</v>
+        <v>14.0088672637939</v>
       </c>
       <c r="H925" t="n">
         <v>9170</v>
@@ -27223,7 +27223,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G926" t="n">
-        <v>14.2862720489502</v>
+        <v>14.2862701416016</v>
       </c>
       <c r="H926" t="n">
         <v>9250</v>
@@ -27281,7 +27281,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G928" t="n">
-        <v>14.3787393569946</v>
+        <v>14.3787403106689</v>
       </c>
       <c r="H928" t="n">
         <v>14950</v>
@@ -27339,7 +27339,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G930" t="n">
-        <v>14.4249725341797</v>
+        <v>14.424973487854</v>
       </c>
       <c r="H930" t="n">
         <v>16780</v>
@@ -27368,7 +27368,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G931" t="n">
-        <v>15.0722465515137</v>
+        <v>15.0722455978394</v>
       </c>
       <c r="H931" t="n">
         <v>24700</v>
@@ -27397,7 +27397,7 @@
         <v>16.1000003814697</v>
       </c>
       <c r="G932" t="n">
-        <v>14.8873128890991</v>
+        <v>14.8873119354248</v>
       </c>
       <c r="H932" t="n">
         <v>25180</v>
@@ -27426,7 +27426,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G933" t="n">
-        <v>15.1647157669067</v>
+        <v>15.1647138595581</v>
       </c>
       <c r="H933" t="n">
         <v>30100</v>
@@ -27484,7 +27484,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G935" t="n">
-        <v>14.7023773193359</v>
+        <v>14.7023763656616</v>
       </c>
       <c r="H935" t="n">
         <v>55500</v>
@@ -27571,7 +27571,7 @@
         <v>15.9499998092651</v>
       </c>
       <c r="G938" t="n">
-        <v>14.748610496521</v>
+        <v>14.7486095428467</v>
       </c>
       <c r="H938" t="n">
         <v>12510</v>
@@ -27600,7 +27600,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G939" t="n">
-        <v>14.5174407958984</v>
+        <v>14.5174417495728</v>
       </c>
       <c r="H939" t="n">
         <v>22480</v>
@@ -27629,7 +27629,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G940" t="n">
-        <v>14.7023773193359</v>
+        <v>14.7023763656616</v>
       </c>
       <c r="H940" t="n">
         <v>29950</v>
@@ -27687,7 +27687,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G942" t="n">
-        <v>14.2862720489502</v>
+        <v>14.2862701416016</v>
       </c>
       <c r="H942" t="n">
         <v>14950</v>
@@ -27716,7 +27716,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G943" t="n">
-        <v>14.7023773193359</v>
+        <v>14.7023763656616</v>
       </c>
       <c r="H943" t="n">
         <v>9530</v>
@@ -27774,7 +27774,7 @@
         <v>15.5500001907349</v>
       </c>
       <c r="G945" t="n">
-        <v>14.3787393569946</v>
+        <v>14.3787403106689</v>
       </c>
       <c r="H945" t="n">
         <v>11890</v>
@@ -27861,7 +27861,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G948" t="n">
-        <v>14.4249725341797</v>
+        <v>14.424973487854</v>
       </c>
       <c r="H948" t="n">
         <v>12460</v>
@@ -27890,7 +27890,7 @@
         <v>15.6000003814697</v>
       </c>
       <c r="G949" t="n">
-        <v>14.4249725341797</v>
+        <v>14.424973487854</v>
       </c>
       <c r="H949" t="n">
         <v>25160</v>
@@ -27977,7 +27977,7 @@
         <v>15.0500001907349</v>
       </c>
       <c r="G952" t="n">
-        <v>13.9163999557495</v>
+        <v>13.9164009094238</v>
       </c>
       <c r="H952" t="n">
         <v>30340</v>
@@ -28180,7 +28180,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G959" t="n">
-        <v>14.1475687026978</v>
+        <v>14.1475696563721</v>
       </c>
       <c r="H959" t="n">
         <v>29350</v>
@@ -28209,7 +28209,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G960" t="n">
-        <v>13.9626340866089</v>
+        <v>13.9626350402832</v>
       </c>
       <c r="H960" t="n">
         <v>16690</v>
@@ -28325,7 +28325,7 @@
         <v>14.5500001907349</v>
       </c>
       <c r="G964" t="n">
-        <v>13.4540615081787</v>
+        <v>13.454062461853</v>
       </c>
       <c r="H964" t="n">
         <v>31930</v>
@@ -28383,7 +28383,7 @@
         <v>15.3000001907349</v>
       </c>
       <c r="G966" t="n">
-        <v>14.1475687026978</v>
+        <v>14.1475696563721</v>
       </c>
       <c r="H966" t="n">
         <v>24850</v>
@@ -28441,7 +28441,7 @@
         <v>15.4499998092651</v>
       </c>
       <c r="G968" t="n">
-        <v>14.2862720489502</v>
+        <v>14.2862701416016</v>
       </c>
       <c r="H968" t="n">
         <v>22610</v>
@@ -28499,7 +28499,7 @@
         <v>15.5</v>
       </c>
       <c r="G970" t="n">
-        <v>14.3325052261353</v>
+        <v>14.3325061798096</v>
       </c>
       <c r="H970" t="n">
         <v>9190</v>
@@ -28557,7 +28557,7 @@
         <v>15.4200000762939</v>
       </c>
       <c r="G972" t="n">
-        <v>14.2585325241089</v>
+        <v>14.2585315704346</v>
       </c>
       <c r="H972" t="n">
         <v>9650</v>
@@ -28615,7 +28615,7 @@
         <v>15.6599998474121</v>
       </c>
       <c r="G974" t="n">
-        <v>14.4804544448853</v>
+        <v>14.4804534912109</v>
       </c>
       <c r="H974" t="n">
         <v>10710</v>
@@ -28673,7 +28673,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G976" t="n">
-        <v>14.5359354019165</v>
+        <v>14.5359344482422</v>
       </c>
       <c r="H976" t="n">
         <v>7580</v>
@@ -28702,7 +28702,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G977" t="n">
-        <v>14.7023773193359</v>
+        <v>14.7023763656616</v>
       </c>
       <c r="H977" t="n">
         <v>12810</v>
@@ -28789,7 +28789,7 @@
         <v>15.6999998092651</v>
       </c>
       <c r="G980" t="n">
-        <v>14.5174407958984</v>
+        <v>14.5174417495728</v>
       </c>
       <c r="H980" t="n">
         <v>15090</v>
@@ -28963,7 +28963,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G986" t="n">
-        <v>15.0352611541748</v>
+        <v>15.0352602005005</v>
       </c>
       <c r="H986" t="n">
         <v>11410</v>
@@ -28992,7 +28992,7 @@
         <v>16.2199993133545</v>
       </c>
       <c r="G987" t="n">
-        <v>14.9982738494873</v>
+        <v>14.998272895813</v>
       </c>
       <c r="H987" t="n">
         <v>12170</v>
@@ -29021,7 +29021,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G988" t="n">
-        <v>15.1092357635498</v>
+        <v>15.1092348098755</v>
       </c>
       <c r="H988" t="n">
         <v>2460</v>
@@ -29050,7 +29050,7 @@
         <v>16.2999992370605</v>
       </c>
       <c r="G989" t="n">
-        <v>15.0722465515137</v>
+        <v>15.0722455978394</v>
       </c>
       <c r="H989" t="n">
         <v>3450</v>
@@ -29079,7 +29079,7 @@
         <v>15.7200002670288</v>
       </c>
       <c r="G990" t="n">
-        <v>14.5359354019165</v>
+        <v>14.5359344482422</v>
       </c>
       <c r="H990" t="n">
         <v>18780</v>
@@ -29108,7 +29108,7 @@
         <v>15.8999996185303</v>
       </c>
       <c r="G991" t="n">
-        <v>14.7023773193359</v>
+        <v>14.7023763656616</v>
       </c>
       <c r="H991" t="n">
         <v>10290</v>
@@ -29137,7 +29137,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G992" t="n">
-        <v>14.9612855911255</v>
+        <v>14.9612865447998</v>
       </c>
       <c r="H992" t="n">
         <v>15990</v>
@@ -29166,7 +29166,7 @@
         <v>16.1800003051758</v>
       </c>
       <c r="G993" t="n">
-        <v>14.9612855911255</v>
+        <v>14.9612865447998</v>
       </c>
       <c r="H993" t="n">
         <v>34800</v>
@@ -29195,7 +29195,7 @@
         <v>16.3999996185303</v>
       </c>
       <c r="G994" t="n">
-        <v>15.2637701034546</v>
+        <v>15.2637691497803</v>
       </c>
       <c r="H994" t="n">
         <v>6910</v>
@@ -29282,7 +29282,7 @@
         <v>15.5</v>
       </c>
       <c r="G997" t="n">
-        <v>14.4261236190796</v>
+        <v>14.4261245727539</v>
       </c>
       <c r="H997" t="n">
         <v>34170</v>
@@ -29340,7 +29340,7 @@
         <v>16.2600002288818</v>
       </c>
       <c r="G999" t="n">
-        <v>15.133469581604</v>
+        <v>15.1334686279297</v>
       </c>
       <c r="H999" t="n">
         <v>34630</v>
@@ -29398,7 +29398,7 @@
         <v>16.3600006103516</v>
       </c>
       <c r="G1001" t="n">
-        <v>15.226541519165</v>
+        <v>15.2265424728394</v>
       </c>
       <c r="H1001" t="n">
         <v>10350</v>
@@ -29427,7 +29427,7 @@
         <v>16.3400001525879</v>
       </c>
       <c r="G1002" t="n">
-        <v>15.2079277038574</v>
+        <v>15.2079267501831</v>
       </c>
       <c r="H1002" t="n">
         <v>16300</v>
@@ -29485,7 +29485,7 @@
         <v>16.4699993133545</v>
       </c>
       <c r="G1004" t="n">
-        <v>15.3289203643799</v>
+        <v>15.3289194107056</v>
       </c>
       <c r="H1004" t="n">
         <v>13530</v>
@@ -29514,7 +29514,7 @@
         <v>17.3120002746582</v>
       </c>
       <c r="G1005" t="n">
-        <v>16.1125831604004</v>
+        <v>16.112585067749</v>
       </c>
       <c r="H1005" t="n">
         <v>55813</v>
@@ -29543,7 +29543,7 @@
         <v>17.75</v>
       </c>
       <c r="G1006" t="n">
-        <v>16.5202369689941</v>
+        <v>16.5202407836914</v>
       </c>
       <c r="H1006" t="n">
         <v>55169</v>
@@ -29601,7 +29601,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1008" t="n">
-        <v>17.9628524780273</v>
+        <v>17.9628505706787</v>
       </c>
       <c r="H1008" t="n">
         <v>110884</v>
@@ -29630,7 +29630,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1009" t="n">
-        <v>17.9814643859863</v>
+        <v>17.981466293335</v>
       </c>
       <c r="H1009" t="n">
         <v>68553</v>
@@ -29659,7 +29659,7 @@
         <v>19.2999992370605</v>
       </c>
       <c r="G1010" t="n">
-        <v>17.9628524780273</v>
+        <v>17.9628505706787</v>
       </c>
       <c r="H1010" t="n">
         <v>58949</v>
@@ -29746,7 +29746,7 @@
         <v>18.7000007629395</v>
       </c>
       <c r="G1013" t="n">
-        <v>17.4044208526611</v>
+        <v>17.4044227600098</v>
       </c>
       <c r="H1013" t="n">
         <v>22767</v>
@@ -29775,7 +29775,7 @@
         <v>19.3999996185303</v>
       </c>
       <c r="G1014" t="n">
-        <v>18.0559234619141</v>
+        <v>18.0559215545654</v>
       </c>
       <c r="H1014" t="n">
         <v>17006</v>
@@ -29833,7 +29833,7 @@
         <v>17.7600002288818</v>
       </c>
       <c r="G1016" t="n">
-        <v>16.5295486450195</v>
+        <v>16.5295467376709</v>
       </c>
       <c r="H1016" t="n">
         <v>112828</v>
@@ -29891,7 +29891,7 @@
         <v>17.7000007629395</v>
       </c>
       <c r="G1018" t="n">
-        <v>16.4737033843994</v>
+        <v>16.4737014770508</v>
       </c>
       <c r="H1018" t="n">
         <v>65525</v>
@@ -29978,7 +29978,7 @@
         <v>18.0200004577637</v>
       </c>
       <c r="G1021" t="n">
-        <v>16.7715320587158</v>
+        <v>16.7715339660645</v>
       </c>
       <c r="H1021" t="n">
         <v>152606</v>
@@ -30007,7 +30007,7 @@
         <v>18.4400005340576</v>
       </c>
       <c r="G1022" t="n">
-        <v>17.1624355316162</v>
+        <v>17.1624336242676</v>
       </c>
       <c r="H1022" t="n">
         <v>78439</v>
@@ -30152,7 +30152,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1027" t="n">
-        <v>17.9814643859863</v>
+        <v>17.981466293335</v>
       </c>
       <c r="H1027" t="n">
         <v>61515</v>
@@ -30268,7 +30268,7 @@
         <v>18.9799995422363</v>
       </c>
       <c r="G1031" t="n">
-        <v>17.6650199890137</v>
+        <v>17.6650218963623</v>
       </c>
       <c r="H1031" t="n">
         <v>65367</v>
@@ -30413,7 +30413,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1036" t="n">
-        <v>18.297908782959</v>
+        <v>18.2979106903076</v>
       </c>
       <c r="H1036" t="n">
         <v>62131</v>
@@ -30471,7 +30471,7 @@
         <v>19.4799995422363</v>
       </c>
       <c r="G1038" t="n">
-        <v>18.1303787231445</v>
+        <v>18.1303768157959</v>
       </c>
       <c r="H1038" t="n">
         <v>34038</v>
@@ -30500,7 +30500,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G1039" t="n">
-        <v>18.2234535217285</v>
+        <v>18.2234516143799</v>
       </c>
       <c r="H1039" t="n">
         <v>22133</v>
@@ -30587,7 +30587,7 @@
         <v>19.6599998474121</v>
       </c>
       <c r="G1042" t="n">
-        <v>18.297908782959</v>
+        <v>18.2979106903076</v>
       </c>
       <c r="H1042" t="n">
         <v>30724</v>
@@ -30819,7 +30819,7 @@
         <v>18.9599990844727</v>
       </c>
       <c r="G1050" t="n">
-        <v>17.6464080810547</v>
+        <v>17.6464061737061</v>
       </c>
       <c r="H1050" t="n">
         <v>8169</v>
@@ -30848,7 +30848,7 @@
         <v>19.2800006866455</v>
       </c>
       <c r="G1051" t="n">
-        <v>17.9442348480225</v>
+        <v>17.9442367553711</v>
       </c>
       <c r="H1051" t="n">
         <v>14161</v>
@@ -30877,7 +30877,7 @@
         <v>19.3199996948242</v>
       </c>
       <c r="G1052" t="n">
-        <v>17.9814643859863</v>
+        <v>17.981466293335</v>
       </c>
       <c r="H1052" t="n">
         <v>30162</v>
@@ -30935,7 +30935,7 @@
         <v>19.8999996185303</v>
       </c>
       <c r="G1054" t="n">
-        <v>18.5212802886963</v>
+        <v>18.5212821960449</v>
       </c>
       <c r="H1054" t="n">
         <v>37546</v>
@@ -30964,7 +30964,7 @@
         <v>20.25</v>
       </c>
       <c r="G1055" t="n">
-        <v>18.8470344543457</v>
+        <v>18.8470306396484</v>
       </c>
       <c r="H1055" t="n">
         <v>95530</v>
@@ -31022,7 +31022,7 @@
         <v>21.6499996185303</v>
       </c>
       <c r="G1057" t="n">
-        <v>20.1500358581543</v>
+        <v>20.1500377655029</v>
       </c>
       <c r="H1057" t="n">
         <v>60713</v>
@@ -31109,7 +31109,7 @@
         <v>22.3999996185303</v>
       </c>
       <c r="G1060" t="n">
-        <v>20.8480758666992</v>
+        <v>20.8480777740479</v>
       </c>
       <c r="H1060" t="n">
         <v>36442</v>
@@ -31167,7 +31167,7 @@
         <v>23</v>
       </c>
       <c r="G1062" t="n">
-        <v>21.4065055847168</v>
+        <v>21.4065074920654</v>
       </c>
       <c r="H1062" t="n">
         <v>72604</v>
@@ -31283,7 +31283,7 @@
         <v>24.5</v>
       </c>
       <c r="G1066" t="n">
-        <v>22.802583694458</v>
+        <v>22.8025817871094</v>
       </c>
       <c r="H1066" t="n">
         <v>52557</v>
@@ -31341,7 +31341,7 @@
         <v>23.8799991607666</v>
       </c>
       <c r="G1068" t="n">
-        <v>22.2255382537842</v>
+        <v>22.2255401611328</v>
       </c>
       <c r="H1068" t="n">
         <v>34388</v>
@@ -31399,7 +31399,7 @@
         <v>23.6800003051758</v>
       </c>
       <c r="G1070" t="n">
-        <v>22.0393943786621</v>
+        <v>22.0393962860107</v>
       </c>
       <c r="H1070" t="n">
         <v>44414</v>
@@ -31457,7 +31457,7 @@
         <v>23.5</v>
       </c>
       <c r="G1072" t="n">
-        <v>21.8718643188477</v>
+        <v>21.8718662261963</v>
       </c>
       <c r="H1072" t="n">
         <v>34002</v>
@@ -31660,7 +31660,7 @@
         <v>26.4599990844727</v>
       </c>
       <c r="G1079" t="n">
-        <v>24.6267890930176</v>
+        <v>24.6267871856689</v>
       </c>
       <c r="H1079" t="n">
         <v>48052</v>
@@ -31718,7 +31718,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G1081" t="n">
-        <v>25.2969093322754</v>
+        <v>25.2969074249268</v>
       </c>
       <c r="H1081" t="n">
         <v>162903</v>
@@ -31776,7 +31776,7 @@
         <v>26.2000007629395</v>
       </c>
       <c r="G1083" t="n">
-        <v>24.384801864624</v>
+        <v>24.3848037719727</v>
       </c>
       <c r="H1083" t="n">
         <v>83697</v>
@@ -32008,7 +32008,7 @@
         <v>27.2199993133545</v>
       </c>
       <c r="G1091" t="n">
-        <v>25.334135055542</v>
+        <v>25.3341369628906</v>
       </c>
       <c r="H1091" t="n">
         <v>47633</v>
@@ -32037,7 +32037,7 @@
         <v>26.5599994659424</v>
       </c>
       <c r="G1092" t="n">
-        <v>24.7198619842529</v>
+        <v>24.7198600769043</v>
       </c>
       <c r="H1092" t="n">
         <v>45537</v>
@@ -32095,7 +32095,7 @@
         <v>25.7999992370605</v>
       </c>
       <c r="G1094" t="n">
-        <v>24.0125179290771</v>
+        <v>24.0125160217285</v>
       </c>
       <c r="H1094" t="n">
         <v>46223</v>
@@ -32153,7 +32153,7 @@
         <v>24.5</v>
       </c>
       <c r="G1096" t="n">
-        <v>22.802583694458</v>
+        <v>22.8025817871094</v>
       </c>
       <c r="H1096" t="n">
         <v>65924</v>
@@ -32182,7 +32182,7 @@
         <v>24.5400009155273</v>
       </c>
       <c r="G1097" t="n">
-        <v>22.8398113250732</v>
+        <v>22.8398132324219</v>
       </c>
       <c r="H1097" t="n">
         <v>65882</v>
@@ -32211,7 +32211,7 @@
         <v>25</v>
       </c>
       <c r="G1098" t="n">
-        <v>23.2679424285889</v>
+        <v>23.2679443359375</v>
       </c>
       <c r="H1098" t="n">
         <v>40418</v>
@@ -32269,7 +32269,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1100" t="n">
-        <v>23.5471572875977</v>
+        <v>23.547155380249</v>
       </c>
       <c r="H1100" t="n">
         <v>59431</v>
@@ -32298,7 +32298,7 @@
         <v>25.2999992370605</v>
       </c>
       <c r="G1101" t="n">
-        <v>23.5471572875977</v>
+        <v>23.547155380249</v>
       </c>
       <c r="H1101" t="n">
         <v>99339</v>
@@ -32385,7 +32385,7 @@
         <v>25.6399993896484</v>
       </c>
       <c r="G1104" t="n">
-        <v>23.8636016845703</v>
+        <v>23.8635997772217</v>
       </c>
       <c r="H1104" t="n">
         <v>23168</v>
@@ -32443,7 +32443,7 @@
         <v>26.5400009155273</v>
       </c>
       <c r="G1106" t="n">
-        <v>24.701244354248</v>
+        <v>24.7012462615967</v>
       </c>
       <c r="H1106" t="n">
         <v>56770</v>
@@ -32472,7 +32472,7 @@
         <v>26.5</v>
       </c>
       <c r="G1107" t="n">
-        <v>24.6640186309814</v>
+        <v>24.6640167236328</v>
       </c>
       <c r="H1107" t="n">
         <v>44031</v>
@@ -32501,7 +32501,7 @@
         <v>26.5799999237061</v>
       </c>
       <c r="G1108" t="n">
-        <v>24.7384738922119</v>
+        <v>24.7384757995605</v>
       </c>
       <c r="H1108" t="n">
         <v>21837</v>
@@ -32530,7 +32530,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1109" t="n">
-        <v>26.804666519165</v>
+        <v>26.8046684265137</v>
       </c>
       <c r="H1109" t="n">
         <v>161580</v>
@@ -32588,7 +32588,7 @@
         <v>28.7999992370605</v>
       </c>
       <c r="G1111" t="n">
-        <v>26.804666519165</v>
+        <v>26.8046684265137</v>
       </c>
       <c r="H1111" t="n">
         <v>112411</v>
@@ -32617,7 +32617,7 @@
         <v>31.4400005340576</v>
       </c>
       <c r="G1112" t="n">
-        <v>29.2617645263672</v>
+        <v>29.2617626190186</v>
       </c>
       <c r="H1112" t="n">
         <v>196995</v>
@@ -32704,7 +32704,7 @@
         <v>31.8600006103516</v>
       </c>
       <c r="G1115" t="n">
-        <v>29.6526679992676</v>
+        <v>29.6526660919189</v>
       </c>
       <c r="H1115" t="n">
         <v>67346</v>
@@ -32733,7 +32733,7 @@
         <v>30.9799995422363</v>
       </c>
       <c r="G1116" t="n">
-        <v>28.8336334228516</v>
+        <v>28.8336315155029</v>
       </c>
       <c r="H1116" t="n">
         <v>67753</v>
@@ -32762,7 +32762,7 @@
         <v>30.6599998474121</v>
       </c>
       <c r="G1117" t="n">
-        <v>28.5358047485352</v>
+        <v>28.5358028411865</v>
       </c>
       <c r="H1117" t="n">
         <v>38809</v>
@@ -32820,7 +32820,7 @@
         <v>30.8400001525879</v>
       </c>
       <c r="G1119" t="n">
-        <v>28.7033348083496</v>
+        <v>28.703332901001</v>
       </c>
       <c r="H1119" t="n">
         <v>33295</v>
@@ -32878,7 +32878,7 @@
         <v>32.1199989318848</v>
       </c>
       <c r="G1121" t="n">
-        <v>29.8946495056152</v>
+        <v>29.8946514129639</v>
       </c>
       <c r="H1121" t="n">
         <v>53168</v>
@@ -32907,7 +32907,7 @@
         <v>32.6199989318848</v>
       </c>
       <c r="G1122" t="n">
-        <v>30.3600101470947</v>
+        <v>30.3600082397461</v>
       </c>
       <c r="H1122" t="n">
         <v>52785</v>
@@ -32936,7 +32936,7 @@
         <v>32.439998626709</v>
       </c>
       <c r="G1123" t="n">
-        <v>30.1924819946289</v>
+        <v>30.1924781799316</v>
       </c>
       <c r="H1123" t="n">
         <v>84489</v>
@@ -32965,7 +32965,7 @@
         <v>33.7200012207031</v>
       </c>
       <c r="G1124" t="n">
-        <v>31.3838005065918</v>
+        <v>31.3838024139404</v>
       </c>
       <c r="H1124" t="n">
         <v>99656</v>
@@ -32994,7 +32994,7 @@
         <v>33.5800018310547</v>
       </c>
       <c r="G1125" t="n">
-        <v>31.2534980773926</v>
+        <v>31.2535018920898</v>
       </c>
       <c r="H1125" t="n">
         <v>76159</v>
@@ -33052,7 +33052,7 @@
         <v>33.5400009155273</v>
       </c>
       <c r="G1127" t="n">
-        <v>31.2162742614746</v>
+        <v>31.2162704467773</v>
       </c>
       <c r="H1127" t="n">
         <v>70098</v>
@@ -33197,7 +33197,7 @@
         <v>32.9599990844727</v>
       </c>
       <c r="G1132" t="n">
-        <v>30.6764507293701</v>
+        <v>30.6764526367188</v>
       </c>
       <c r="H1132" t="n">
         <v>80720</v>
@@ -33226,7 +33226,7 @@
         <v>32.7999992370605</v>
       </c>
       <c r="G1133" t="n">
-        <v>30.5275402069092</v>
+        <v>30.5275382995605</v>
       </c>
       <c r="H1133" t="n">
         <v>60975</v>
@@ -33255,7 +33255,7 @@
         <v>31.6200008392334</v>
       </c>
       <c r="G1134" t="n">
-        <v>29.4292945861816</v>
+        <v>29.4292964935303</v>
       </c>
       <c r="H1134" t="n">
         <v>71038</v>
@@ -33313,7 +33313,7 @@
         <v>32.4199981689453</v>
       </c>
       <c r="G1136" t="n">
-        <v>30.173864364624</v>
+        <v>30.1738662719727</v>
       </c>
       <c r="H1136" t="n">
         <v>77493</v>
@@ -33487,7 +33487,7 @@
         <v>33.7200012207031</v>
       </c>
       <c r="G1142" t="n">
-        <v>31.3838005065918</v>
+        <v>31.3838024139404</v>
       </c>
       <c r="H1142" t="n">
         <v>42115</v>
@@ -33516,7 +33516,7 @@
         <v>33.4599990844727</v>
       </c>
       <c r="G1143" t="n">
-        <v>31.1418113708496</v>
+        <v>31.1418132781982</v>
       </c>
       <c r="H1143" t="n">
         <v>57121</v>
@@ -33603,7 +33603,7 @@
         <v>35.2599983215332</v>
       </c>
       <c r="G1146" t="n">
-        <v>32.8171043395996</v>
+        <v>32.8171081542969</v>
       </c>
       <c r="H1146" t="n">
         <v>46512</v>
@@ -33748,7 +33748,7 @@
         <v>33.9000015258789</v>
       </c>
       <c r="G1151" t="n">
-        <v>31.5513286590576</v>
+        <v>31.5513324737549</v>
       </c>
       <c r="H1151" t="n">
         <v>40722</v>
@@ -33893,7 +33893,7 @@
         <v>36.2999992370605</v>
       </c>
       <c r="G1156" t="n">
-        <v>33.7850494384766</v>
+        <v>33.7850532531738</v>
       </c>
       <c r="H1156" t="n">
         <v>73415</v>
@@ -33922,7 +33922,7 @@
         <v>35.7799987792969</v>
       </c>
       <c r="G1157" t="n">
-        <v>33.301082611084</v>
+        <v>33.3010787963867</v>
       </c>
       <c r="H1157" t="n">
         <v>25412</v>
@@ -33951,7 +33951,7 @@
         <v>36.2799987792969</v>
       </c>
       <c r="G1158" t="n">
-        <v>33.7664375305176</v>
+        <v>33.7664337158203</v>
       </c>
       <c r="H1158" t="n">
         <v>24931</v>
@@ -34067,7 +34067,7 @@
         <v>36.0200004577637</v>
       </c>
       <c r="G1162" t="n">
-        <v>33.5244522094727</v>
+        <v>33.5244483947754</v>
       </c>
       <c r="H1162" t="n">
         <v>36498</v>
@@ -34096,7 +34096,7 @@
         <v>37.9799995422363</v>
       </c>
       <c r="G1163" t="n">
-        <v>35.3486595153809</v>
+        <v>35.3486557006836</v>
       </c>
       <c r="H1163" t="n">
         <v>124787</v>
@@ -34212,7 +34212,7 @@
         <v>33.5400009155273</v>
       </c>
       <c r="G1167" t="n">
-        <v>31.2162742614746</v>
+        <v>31.2162704467773</v>
       </c>
       <c r="H1167" t="n">
         <v>82109</v>
@@ -34299,7 +34299,7 @@
         <v>35.5</v>
       </c>
       <c r="G1170" t="n">
-        <v>33.0404739379883</v>
+        <v>33.0404815673828</v>
       </c>
       <c r="H1170" t="n">
         <v>43902</v>
@@ -34415,7 +34415,7 @@
         <v>33.3800010681152</v>
       </c>
       <c r="G1174" t="n">
-        <v>31.067361831665</v>
+        <v>31.0673561096191</v>
       </c>
       <c r="H1174" t="n">
         <v>34144</v>
@@ -34473,7 +34473,7 @@
         <v>33.2000007629395</v>
       </c>
       <c r="G1176" t="n">
-        <v>30.8998260498047</v>
+        <v>30.899829864502</v>
       </c>
       <c r="H1176" t="n">
         <v>68323</v>
@@ -34502,7 +34502,7 @@
         <v>30.8400001525879</v>
       </c>
       <c r="G1177" t="n">
-        <v>28.7033348083496</v>
+        <v>28.703332901001</v>
       </c>
       <c r="H1177" t="n">
         <v>100449</v>
@@ -34560,7 +34560,7 @@
         <v>30.1800003051758</v>
       </c>
       <c r="G1179" t="n">
-        <v>28.0890598297119</v>
+        <v>28.0890579223633</v>
       </c>
       <c r="H1179" t="n">
         <v>41407</v>
@@ -34618,7 +34618,7 @@
         <v>30.0599994659424</v>
       </c>
       <c r="G1181" t="n">
-        <v>27.9773712158203</v>
+        <v>27.9773731231689</v>
       </c>
       <c r="H1181" t="n">
         <v>20538</v>
@@ -34676,7 +34676,7 @@
         <v>32.9799995422363</v>
       </c>
       <c r="G1183" t="n">
-        <v>30.6950702667236</v>
+        <v>30.695068359375</v>
       </c>
       <c r="H1183" t="n">
         <v>60943</v>
@@ -34705,7 +34705,7 @@
         <v>32.5400009155273</v>
       </c>
       <c r="G1184" t="n">
-        <v>30.2855529785156</v>
+        <v>30.2855567932129</v>
       </c>
       <c r="H1184" t="n">
         <v>33508</v>
@@ -34850,7 +34850,7 @@
         <v>30.1399993896484</v>
       </c>
       <c r="G1189" t="n">
-        <v>28.0518283843994</v>
+        <v>28.051830291748</v>
       </c>
       <c r="H1189" t="n">
         <v>25332</v>
@@ -34908,7 +34908,7 @@
         <v>28.9599990844727</v>
       </c>
       <c r="G1191" t="n">
-        <v>26.9535827636719</v>
+        <v>26.9535808563232</v>
       </c>
       <c r="H1191" t="n">
         <v>45009</v>
@@ -34937,7 +34937,7 @@
         <v>28.7800006866455</v>
       </c>
       <c r="G1192" t="n">
-        <v>26.7860584259033</v>
+        <v>26.7860565185547</v>
       </c>
       <c r="H1192" t="n">
         <v>85052</v>
@@ -34966,7 +34966,7 @@
         <v>30.1800003051758</v>
       </c>
       <c r="G1193" t="n">
-        <v>28.0890598297119</v>
+        <v>28.0890579223633</v>
       </c>
       <c r="H1193" t="n">
         <v>48544</v>
@@ -35024,7 +35024,7 @@
         <v>30.2800006866455</v>
       </c>
       <c r="G1195" t="n">
-        <v>28.1821327209473</v>
+        <v>28.1821346282959</v>
       </c>
       <c r="H1195" t="n">
         <v>73845</v>
@@ -35140,7 +35140,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G1199" t="n">
-        <v>26.1903953552246</v>
+        <v>26.1903972625732</v>
       </c>
       <c r="H1199" t="n">
         <v>38178</v>
@@ -35314,7 +35314,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G1205" t="n">
-        <v>25.2969093322754</v>
+        <v>25.2969074249268</v>
       </c>
       <c r="H1205" t="n">
         <v>22103</v>
@@ -35401,7 +35401,7 @@
         <v>26</v>
       </c>
       <c r="G1208" t="n">
-        <v>24.198657989502</v>
+        <v>24.1986598968506</v>
       </c>
       <c r="H1208" t="n">
         <v>50841</v>
@@ -35430,7 +35430,7 @@
         <v>28.2199993133545</v>
       </c>
       <c r="G1209" t="n">
-        <v>26.2648525238037</v>
+        <v>26.2648544311523</v>
       </c>
       <c r="H1209" t="n">
         <v>45692</v>
@@ -35488,7 +35488,7 @@
         <v>28.1399993896484</v>
       </c>
       <c r="G1211" t="n">
-        <v>26.1903953552246</v>
+        <v>26.1903972625732</v>
       </c>
       <c r="H1211" t="n">
         <v>31255</v>
@@ -35517,7 +35517,7 @@
         <v>28.4799995422363</v>
       </c>
       <c r="G1212" t="n">
-        <v>26.5068378448486</v>
+        <v>26.5068397521973</v>
       </c>
       <c r="H1212" t="n">
         <v>18028</v>
@@ -35546,7 +35546,7 @@
         <v>28.2399997711182</v>
       </c>
       <c r="G1213" t="n">
-        <v>26.28346824646</v>
+        <v>26.2834663391113</v>
       </c>
       <c r="H1213" t="n">
         <v>25247</v>
@@ -35575,7 +35575,7 @@
         <v>29.2399997711182</v>
       </c>
       <c r="G1214" t="n">
-        <v>27.2141876220703</v>
+        <v>27.2141857147217</v>
       </c>
       <c r="H1214" t="n">
         <v>61896</v>
@@ -35662,7 +35662,7 @@
         <v>28.8400001525879</v>
       </c>
       <c r="G1217" t="n">
-        <v>26.8418979644775</v>
+        <v>26.8418960571289</v>
       </c>
       <c r="H1217" t="n">
         <v>52590</v>
@@ -35691,7 +35691,7 @@
         <v>29.7000007629395</v>
       </c>
       <c r="G1218" t="n">
-        <v>27.6423168182373</v>
+        <v>27.6423149108887</v>
       </c>
       <c r="H1218" t="n">
         <v>56043</v>
@@ -35749,7 +35749,7 @@
         <v>29.5</v>
       </c>
       <c r="G1220" t="n">
-        <v>27.4561710357666</v>
+        <v>27.456169128418</v>
       </c>
       <c r="H1220" t="n">
         <v>32051</v>
@@ -35778,7 +35778,7 @@
         <v>30.3999996185303</v>
       </c>
       <c r="G1221" t="n">
-        <v>28.2938175201416</v>
+        <v>28.293815612793</v>
       </c>
       <c r="H1221" t="n">
         <v>50940</v>
@@ -35836,7 +35836,7 @@
         <v>30.5</v>
       </c>
       <c r="G1223" t="n">
-        <v>28.3868885040283</v>
+        <v>28.3868865966797</v>
       </c>
       <c r="H1223" t="n">
         <v>40353</v>
@@ -35894,7 +35894,7 @@
         <v>29.9599990844727</v>
       </c>
       <c r="G1225" t="n">
-        <v>27.8843002319336</v>
+        <v>27.8843021392822</v>
       </c>
       <c r="H1225" t="n">
         <v>55762</v>
@@ -35952,7 +35952,7 @@
         <v>29.6399993896484</v>
       </c>
       <c r="G1227" t="n">
-        <v>27.5864734649658</v>
+        <v>27.5864715576172</v>
       </c>
       <c r="H1227" t="n">
         <v>15950</v>
@@ -36039,7 +36039,7 @@
         <v>27.7399997711182</v>
       </c>
       <c r="G1230" t="n">
-        <v>25.8181076049805</v>
+        <v>25.8181114196777</v>
       </c>
       <c r="H1230" t="n">
         <v>46441</v>
@@ -36097,7 +36097,7 @@
         <v>28.4400005340576</v>
       </c>
       <c r="G1232" t="n">
-        <v>26.469612121582</v>
+        <v>26.4696102142334</v>
       </c>
       <c r="H1232" t="n">
         <v>30233</v>
@@ -36126,7 +36126,7 @@
         <v>28.6000003814697</v>
       </c>
       <c r="G1233" t="n">
-        <v>26.618522644043</v>
+        <v>26.6185245513916</v>
       </c>
       <c r="H1233" t="n">
         <v>20689</v>
@@ -36155,7 +36155,7 @@
         <v>28.3999996185303</v>
       </c>
       <c r="G1234" t="n">
-        <v>26.4323806762695</v>
+        <v>26.4323825836182</v>
       </c>
       <c r="H1234" t="n">
         <v>24296</v>
@@ -36184,7 +36184,7 @@
         <v>27.7999992370605</v>
       </c>
       <c r="G1235" t="n">
-        <v>25.873950958252</v>
+        <v>25.8739490509033</v>
       </c>
       <c r="H1235" t="n">
         <v>15018</v>
@@ -36242,7 +36242,7 @@
         <v>27.2800006866455</v>
       </c>
       <c r="G1237" t="n">
-        <v>25.3899784088135</v>
+        <v>25.3899803161621</v>
       </c>
       <c r="H1237" t="n">
         <v>26942</v>
@@ -36271,7 +36271,7 @@
         <v>27.1800003051758</v>
       </c>
       <c r="G1238" t="n">
-        <v>25.2969093322754</v>
+        <v>25.2969074249268</v>
       </c>
       <c r="H1238" t="n">
         <v>29471</v>
@@ -36300,7 +36300,7 @@
         <v>26.7600002288818</v>
       </c>
       <c r="G1239" t="n">
-        <v>24.906005859375</v>
+        <v>24.9060039520264</v>
       </c>
       <c r="H1239" t="n">
         <v>30671</v>
@@ -36358,7 +36358,7 @@
         <v>25.4599990844727</v>
       </c>
       <c r="G1241" t="n">
-        <v>23.9647331237793</v>
+        <v>23.9647312164307</v>
       </c>
       <c r="H1241" t="n">
         <v>30227</v>
@@ -36416,7 +36416,7 @@
         <v>25.5599994659424</v>
       </c>
       <c r="G1243" t="n">
-        <v>24.0588626861572</v>
+        <v>24.0588607788086</v>
       </c>
       <c r="H1243" t="n">
         <v>34595</v>
@@ -36503,7 +36503,7 @@
         <v>25.2600002288818</v>
       </c>
       <c r="G1246" t="n">
-        <v>23.776481628418</v>
+        <v>23.7764797210693</v>
       </c>
       <c r="H1246" t="n">
         <v>33813</v>
@@ -36677,7 +36677,7 @@
         <v>21.1800003051758</v>
       </c>
       <c r="G1252" t="n">
-        <v>19.9361000061035</v>
+        <v>19.9360980987549</v>
       </c>
       <c r="H1252" t="n">
         <v>38370</v>
@@ -36793,7 +36793,7 @@
         <v>21.2000007629395</v>
       </c>
       <c r="G1256" t="n">
-        <v>19.9549236297607</v>
+        <v>19.9549255371094</v>
       </c>
       <c r="H1256" t="n">
         <v>41638</v>
@@ -36967,7 +36967,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G1262" t="n">
-        <v>19.7854976654053</v>
+        <v>19.7854957580566</v>
       </c>
       <c r="H1262" t="n">
         <v>37052</v>
@@ -37257,7 +37257,7 @@
         <v>21.0599994659424</v>
       </c>
       <c r="G1272" t="n">
-        <v>19.8231468200684</v>
+        <v>19.8231449127197</v>
       </c>
       <c r="H1272" t="n">
         <v>39163</v>
@@ -37460,7 +37460,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1279" t="n">
-        <v>18.2041606903076</v>
+        <v>18.2041625976562</v>
       </c>
       <c r="H1279" t="n">
         <v>46603</v>
@@ -37489,7 +37489,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G1280" t="n">
-        <v>18.1288585662842</v>
+        <v>18.1288604736328</v>
       </c>
       <c r="H1280" t="n">
         <v>33243</v>
@@ -37634,7 +37634,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1285" t="n">
-        <v>17.5264492034912</v>
+        <v>17.5264472961426</v>
       </c>
       <c r="H1285" t="n">
         <v>17848</v>
@@ -37779,7 +37779,7 @@
         <v>17.0200004577637</v>
       </c>
       <c r="G1290" t="n">
-        <v>16.0204162597656</v>
+        <v>16.020414352417</v>
       </c>
       <c r="H1290" t="n">
         <v>25236</v>
@@ -37953,7 +37953,7 @@
         <v>18.9200000762939</v>
       </c>
       <c r="G1296" t="n">
-        <v>17.8088283538818</v>
+        <v>17.8088264465332</v>
       </c>
       <c r="H1296" t="n">
         <v>35661</v>
@@ -38040,7 +38040,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1299" t="n">
-        <v>16.4157485961914</v>
+        <v>16.41575050354</v>
       </c>
       <c r="H1299" t="n">
         <v>55688</v>
@@ -38127,7 +38127,7 @@
         <v>18.5900001525879</v>
       </c>
       <c r="G1302" t="n">
-        <v>17.4982109069824</v>
+        <v>17.4982089996338</v>
       </c>
       <c r="H1302" t="n">
         <v>18353</v>
@@ -38185,7 +38185,7 @@
         <v>18.7800006866455</v>
       </c>
       <c r="G1304" t="n">
-        <v>17.6770515441895</v>
+        <v>17.6770496368408</v>
       </c>
       <c r="H1304" t="n">
         <v>21245</v>
@@ -38214,7 +38214,7 @@
         <v>18.8299999237061</v>
       </c>
       <c r="G1305" t="n">
-        <v>17.7241134643555</v>
+        <v>17.7241153717041</v>
       </c>
       <c r="H1305" t="n">
         <v>19039</v>
@@ -38330,7 +38330,7 @@
         <v>20</v>
       </c>
       <c r="G1309" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1309" t="n">
         <v>73322</v>
@@ -38359,7 +38359,7 @@
         <v>19.7900009155273</v>
       </c>
       <c r="G1310" t="n">
-        <v>18.6277332305908</v>
+        <v>18.6277313232422</v>
       </c>
       <c r="H1310" t="n">
         <v>40761</v>
@@ -38388,7 +38388,7 @@
         <v>20</v>
       </c>
       <c r="G1311" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1311" t="n">
         <v>26090</v>
@@ -38417,7 +38417,7 @@
         <v>20</v>
       </c>
       <c r="G1312" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1312" t="n">
         <v>42674</v>
@@ -38446,7 +38446,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1313" t="n">
-        <v>19.107780456543</v>
+        <v>19.1077823638916</v>
       </c>
       <c r="H1313" t="n">
         <v>30420</v>
@@ -38475,7 +38475,7 @@
         <v>20.2800006866455</v>
       </c>
       <c r="G1314" t="n">
-        <v>19.0889587402344</v>
+        <v>19.0889568328857</v>
       </c>
       <c r="H1314" t="n">
         <v>37103</v>
@@ -38591,7 +38591,7 @@
         <v>19.5300006866455</v>
       </c>
       <c r="G1318" t="n">
-        <v>18.3830032348633</v>
+        <v>18.3830051422119</v>
       </c>
       <c r="H1318" t="n">
         <v>19017</v>
@@ -38620,7 +38620,7 @@
         <v>19.7700004577637</v>
       </c>
       <c r="G1319" t="n">
-        <v>18.608907699585</v>
+        <v>18.6089096069336</v>
       </c>
       <c r="H1319" t="n">
         <v>16339</v>
@@ -38707,7 +38707,7 @@
         <v>18.6200008392334</v>
       </c>
       <c r="G1322" t="n">
-        <v>17.5264492034912</v>
+        <v>17.5264472961426</v>
       </c>
       <c r="H1322" t="n">
         <v>22113</v>
@@ -38736,7 +38736,7 @@
         <v>18.1700000762939</v>
       </c>
       <c r="G1323" t="n">
-        <v>17.1028747558594</v>
+        <v>17.102876663208</v>
       </c>
       <c r="H1323" t="n">
         <v>17656</v>
@@ -38852,7 +38852,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G1327" t="n">
-        <v>16.7263679504395</v>
+        <v>16.7263698577881</v>
       </c>
       <c r="H1327" t="n">
         <v>12643</v>
@@ -38968,7 +38968,7 @@
         <v>17.7700004577637</v>
       </c>
       <c r="G1331" t="n">
-        <v>16.7263679504395</v>
+        <v>16.7263698577881</v>
       </c>
       <c r="H1331" t="n">
         <v>15512</v>
@@ -39026,7 +39026,7 @@
         <v>17.1299991607666</v>
       </c>
       <c r="G1333" t="n">
-        <v>16.1239528656006</v>
+        <v>16.1239547729492</v>
       </c>
       <c r="H1333" t="n">
         <v>23067</v>
@@ -39055,7 +39055,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1334" t="n">
-        <v>16.6228294372559</v>
+        <v>16.6228313446045</v>
       </c>
       <c r="H1334" t="n">
         <v>34947</v>
@@ -39171,7 +39171,7 @@
         <v>18.3199996948242</v>
       </c>
       <c r="G1338" t="n">
-        <v>17.2440662384033</v>
+        <v>17.2440643310547</v>
       </c>
       <c r="H1338" t="n">
         <v>23359</v>
@@ -39258,7 +39258,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1341" t="n">
-        <v>16.6793041229248</v>
+        <v>16.6793022155762</v>
       </c>
       <c r="H1341" t="n">
         <v>62269</v>
@@ -39490,7 +39490,7 @@
         <v>14.3000001907349</v>
       </c>
       <c r="G1349" t="n">
-        <v>13.4601612091064</v>
+        <v>13.4601621627808</v>
       </c>
       <c r="H1349" t="n">
         <v>42493</v>
@@ -39548,7 +39548,7 @@
         <v>13.8400001525879</v>
       </c>
       <c r="G1351" t="n">
-        <v>13.0271768569946</v>
+        <v>13.0271778106689</v>
       </c>
       <c r="H1351" t="n">
         <v>68271</v>
@@ -39635,7 +39635,7 @@
         <v>14.2700004577637</v>
       </c>
       <c r="G1354" t="n">
-        <v>13.4319229125977</v>
+        <v>13.431923866272</v>
       </c>
       <c r="H1354" t="n">
         <v>126733</v>
@@ -39722,7 +39722,7 @@
         <v>14.6400003433228</v>
       </c>
       <c r="G1357" t="n">
-        <v>13.7801923751831</v>
+        <v>13.7801933288574</v>
       </c>
       <c r="H1357" t="n">
         <v>26201</v>
@@ -39838,7 +39838,7 @@
         <v>14.0699996948242</v>
       </c>
       <c r="G1361" t="n">
-        <v>13.2436685562134</v>
+        <v>13.2436695098877</v>
       </c>
       <c r="H1361" t="n">
         <v>25872</v>
@@ -39867,7 +39867,7 @@
         <v>14.2799997329712</v>
       </c>
       <c r="G1362" t="n">
-        <v>13.4413356781006</v>
+        <v>13.4413347244263</v>
       </c>
       <c r="H1362" t="n">
         <v>44179</v>
@@ -39983,7 +39983,7 @@
         <v>14.1300001144409</v>
       </c>
       <c r="G1366" t="n">
-        <v>13.3001461029053</v>
+        <v>13.300145149231</v>
       </c>
       <c r="H1366" t="n">
         <v>43095</v>
@@ -40012,7 +40012,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G1367" t="n">
-        <v>13.516637802124</v>
+        <v>13.5166368484497</v>
       </c>
       <c r="H1367" t="n">
         <v>35294</v>
@@ -40128,7 +40128,7 @@
         <v>16.0799999237061</v>
       </c>
       <c r="G1371" t="n">
-        <v>15.1356220245361</v>
+        <v>15.1356210708618</v>
       </c>
       <c r="H1371" t="n">
         <v>83342</v>
@@ -40186,7 +40186,7 @@
         <v>15.5699996948242</v>
       </c>
       <c r="G1373" t="n">
-        <v>14.6555738449097</v>
+        <v>14.655574798584</v>
       </c>
       <c r="H1373" t="n">
         <v>22186</v>
@@ -40273,7 +40273,7 @@
         <v>15.039999961853</v>
       </c>
       <c r="G1376" t="n">
-        <v>14.1567010879517</v>
+        <v>14.156702041626</v>
       </c>
       <c r="H1376" t="n">
         <v>26012</v>
@@ -40302,7 +40302,7 @@
         <v>15.1000003814697</v>
       </c>
       <c r="G1377" t="n">
-        <v>14.2131776809692</v>
+        <v>14.2131786346436</v>
       </c>
       <c r="H1377" t="n">
         <v>26436</v>
@@ -40331,7 +40331,7 @@
         <v>15.3500003814697</v>
       </c>
       <c r="G1378" t="n">
-        <v>14.4484949111938</v>
+        <v>14.4484958648682</v>
       </c>
       <c r="H1378" t="n">
         <v>24491</v>
@@ -40360,7 +40360,7 @@
         <v>15.710000038147</v>
       </c>
       <c r="G1379" t="n">
-        <v>14.7873525619507</v>
+        <v>14.7873516082764</v>
       </c>
       <c r="H1379" t="n">
         <v>21758</v>
@@ -40505,7 +40505,7 @@
         <v>18.1900005340576</v>
       </c>
       <c r="G1384" t="n">
-        <v>17.1217041015625</v>
+        <v>17.1217021942139</v>
       </c>
       <c r="H1384" t="n">
         <v>37407</v>
@@ -40650,7 +40650,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1389" t="n">
-        <v>16.1427822113037</v>
+        <v>16.1427803039551</v>
       </c>
       <c r="H1389" t="n">
         <v>29540</v>
@@ -40737,7 +40737,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1392" t="n">
-        <v>16.9993343353271</v>
+        <v>16.9993362426758</v>
       </c>
       <c r="H1392" t="n">
         <v>48277</v>
@@ -41056,7 +41056,7 @@
         <v>17.8700008392334</v>
       </c>
       <c r="G1403" t="n">
-        <v>16.8204956054688</v>
+        <v>16.8204975128174</v>
       </c>
       <c r="H1403" t="n">
         <v>10087</v>
@@ -41085,7 +41085,7 @@
         <v>17.9599990844727</v>
       </c>
       <c r="G1404" t="n">
-        <v>16.9052085876465</v>
+        <v>16.9052104949951</v>
       </c>
       <c r="H1404" t="n">
         <v>7550</v>
@@ -41143,7 +41143,7 @@
         <v>18.4500007629395</v>
       </c>
       <c r="G1406" t="n">
-        <v>17.3664321899414</v>
+        <v>17.36643409729</v>
       </c>
       <c r="H1406" t="n">
         <v>21598</v>
@@ -41201,7 +41201,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1408" t="n">
-        <v>16.5475273132324</v>
+        <v>16.5475254058838</v>
       </c>
       <c r="H1408" t="n">
         <v>28564</v>
@@ -41230,7 +41230,7 @@
         <v>17.4500007629395</v>
       </c>
       <c r="G1409" t="n">
-        <v>16.425163269043</v>
+        <v>16.4251613616943</v>
       </c>
       <c r="H1409" t="n">
         <v>18148</v>
@@ -41259,7 +41259,7 @@
         <v>17.1499996185303</v>
       </c>
       <c r="G1410" t="n">
-        <v>16.1427822113037</v>
+        <v>16.1427803039551</v>
       </c>
       <c r="H1410" t="n">
         <v>34518</v>
@@ -41404,7 +41404,7 @@
         <v>17.4200000762939</v>
       </c>
       <c r="G1415" t="n">
-        <v>16.3969249725342</v>
+        <v>16.3969230651855</v>
       </c>
       <c r="H1415" t="n">
         <v>10556</v>
@@ -41723,7 +41723,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G1426" t="n">
-        <v>18.3924160003662</v>
+        <v>18.3924179077148</v>
       </c>
       <c r="H1426" t="n">
         <v>22265</v>
@@ -41781,7 +41781,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G1428" t="n">
-        <v>18.9760036468506</v>
+        <v>18.9760055541992</v>
       </c>
       <c r="H1428" t="n">
         <v>59273</v>
@@ -41810,7 +41810,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1429" t="n">
-        <v>19.107780456543</v>
+        <v>19.1077823638916</v>
       </c>
       <c r="H1429" t="n">
         <v>28889</v>
@@ -41839,7 +41839,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1430" t="n">
-        <v>19.4842891693115</v>
+        <v>19.4842910766602</v>
       </c>
       <c r="H1430" t="n">
         <v>92615</v>
@@ -42013,7 +42013,7 @@
         <v>21.5</v>
       </c>
       <c r="G1436" t="n">
-        <v>20.2373065948486</v>
+        <v>20.2373085021973</v>
       </c>
       <c r="H1436" t="n">
         <v>70267</v>
@@ -42071,7 +42071,7 @@
         <v>21.1800003051758</v>
       </c>
       <c r="G1438" t="n">
-        <v>19.9361000061035</v>
+        <v>19.9360980987549</v>
       </c>
       <c r="H1438" t="n">
         <v>51729</v>
@@ -42158,7 +42158,7 @@
         <v>22.2199993133545</v>
       </c>
       <c r="G1441" t="n">
-        <v>20.9150218963623</v>
+        <v>20.9150199890137</v>
       </c>
       <c r="H1441" t="n">
         <v>103997</v>
@@ -42245,7 +42245,7 @@
         <v>21.8999996185303</v>
       </c>
       <c r="G1444" t="n">
-        <v>20.6138114929199</v>
+        <v>20.6138134002686</v>
       </c>
       <c r="H1444" t="n">
         <v>23345</v>
@@ -42274,7 +42274,7 @@
         <v>21.7199993133545</v>
       </c>
       <c r="G1445" t="n">
-        <v>20.4443855285645</v>
+        <v>20.4443836212158</v>
       </c>
       <c r="H1445" t="n">
         <v>32693</v>
@@ -42448,7 +42448,7 @@
         <v>21.2600002288818</v>
       </c>
       <c r="G1451" t="n">
-        <v>20.011402130127</v>
+        <v>20.0114002227783</v>
       </c>
       <c r="H1451" t="n">
         <v>10789</v>
@@ -42477,7 +42477,7 @@
         <v>20.8199996948242</v>
       </c>
       <c r="G1452" t="n">
-        <v>19.5972385406494</v>
+        <v>19.597240447998</v>
       </c>
       <c r="H1452" t="n">
         <v>17204</v>
@@ -42622,7 +42622,7 @@
         <v>20</v>
       </c>
       <c r="G1457" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1457" t="n">
         <v>34122</v>
@@ -42680,7 +42680,7 @@
         <v>20.7000007629395</v>
       </c>
       <c r="G1459" t="n">
-        <v>19.4842891693115</v>
+        <v>19.4842910766602</v>
       </c>
       <c r="H1459" t="n">
         <v>48716</v>
@@ -42796,7 +42796,7 @@
         <v>21.0200004577637</v>
       </c>
       <c r="G1463" t="n">
-        <v>19.7854976654053</v>
+        <v>19.7854957580566</v>
       </c>
       <c r="H1463" t="n">
         <v>22649</v>
@@ -42970,7 +42970,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G1469" t="n">
-        <v>18.1288585662842</v>
+        <v>18.1288604736328</v>
       </c>
       <c r="H1469" t="n">
         <v>44752</v>
@@ -42999,7 +42999,7 @@
         <v>20</v>
       </c>
       <c r="G1470" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1470" t="n">
         <v>59374</v>
@@ -43115,7 +43115,7 @@
         <v>20.1599998474121</v>
       </c>
       <c r="G1474" t="n">
-        <v>18.9760036468506</v>
+        <v>18.9760055541992</v>
       </c>
       <c r="H1474" t="n">
         <v>35643</v>
@@ -43173,7 +43173,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1476" t="n">
-        <v>19.107780456543</v>
+        <v>19.1077823638916</v>
       </c>
       <c r="H1476" t="n">
         <v>12352</v>
@@ -43202,7 +43202,7 @@
         <v>20</v>
       </c>
       <c r="G1477" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1477" t="n">
         <v>12872</v>
@@ -43260,7 +43260,7 @@
         <v>19.5</v>
       </c>
       <c r="G1479" t="n">
-        <v>18.3547630310059</v>
+        <v>18.3547649383545</v>
       </c>
       <c r="H1479" t="n">
         <v>17282</v>
@@ -43405,7 +43405,7 @@
         <v>20</v>
       </c>
       <c r="G1484" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1484" t="n">
         <v>18628</v>
@@ -43434,7 +43434,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G1485" t="n">
-        <v>18.787748336792</v>
+        <v>18.7877502441406</v>
       </c>
       <c r="H1485" t="n">
         <v>16716</v>
@@ -43492,7 +43492,7 @@
         <v>20</v>
       </c>
       <c r="G1487" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1487" t="n">
         <v>28899</v>
@@ -43521,7 +43521,7 @@
         <v>20</v>
       </c>
       <c r="G1488" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1488" t="n">
         <v>32266</v>
@@ -43550,7 +43550,7 @@
         <v>20</v>
       </c>
       <c r="G1489" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1489" t="n">
         <v>14782</v>
@@ -43608,7 +43608,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1491" t="n">
-        <v>19.107780456543</v>
+        <v>19.1077823638916</v>
       </c>
       <c r="H1491" t="n">
         <v>15564</v>
@@ -43637,7 +43637,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1492" t="n">
-        <v>19.107780456543</v>
+        <v>19.1077823638916</v>
       </c>
       <c r="H1492" t="n">
         <v>14452</v>
@@ -43666,7 +43666,7 @@
         <v>20</v>
       </c>
       <c r="G1493" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1493" t="n">
         <v>10389</v>
@@ -43695,7 +43695,7 @@
         <v>20</v>
       </c>
       <c r="G1494" t="n">
-        <v>18.8253993988037</v>
+        <v>18.8254013061523</v>
       </c>
       <c r="H1494" t="n">
         <v>14503</v>
@@ -43753,7 +43753,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G1496" t="n">
-        <v>18.787748336792</v>
+        <v>18.7877502441406</v>
       </c>
       <c r="H1496" t="n">
         <v>12980</v>
@@ -43782,7 +43782,7 @@
         <v>19.5799999237061</v>
       </c>
       <c r="G1497" t="n">
-        <v>18.4300689697266</v>
+        <v>18.4300670623779</v>
       </c>
       <c r="H1497" t="n">
         <v>12302</v>
@@ -43898,7 +43898,7 @@
         <v>19.2600002288818</v>
       </c>
       <c r="G1501" t="n">
-        <v>18.1288585662842</v>
+        <v>18.1288604736328</v>
       </c>
       <c r="H1501" t="n">
         <v>16482</v>
@@ -44014,7 +44014,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1505" t="n">
-        <v>19.3965625762939</v>
+        <v>19.3965644836426</v>
       </c>
       <c r="H1505" t="n">
         <v>17202</v>
@@ -44304,7 +44304,7 @@
         <v>19.5</v>
       </c>
       <c r="G1515" t="n">
-        <v>18.6321659088135</v>
+        <v>18.6321678161621</v>
       </c>
       <c r="H1515" t="n">
         <v>9138</v>
@@ -44449,7 +44449,7 @@
         <v>19.5400009155273</v>
       </c>
       <c r="G1520" t="n">
-        <v>18.6703872680664</v>
+        <v>18.670389175415</v>
       </c>
       <c r="H1520" t="n">
         <v>12532</v>
@@ -44536,7 +44536,7 @@
         <v>20</v>
       </c>
       <c r="G1523" t="n">
-        <v>19.1099147796631</v>
+        <v>19.1099166870117</v>
       </c>
       <c r="H1523" t="n">
         <v>19100</v>
@@ -44565,7 +44565,7 @@
         <v>20.2000007629395</v>
       </c>
       <c r="G1524" t="n">
-        <v>19.3010139465332</v>
+        <v>19.3010158538818</v>
       </c>
       <c r="H1524" t="n">
         <v>15485</v>
@@ -44594,7 +44594,7 @@
         <v>20.25</v>
       </c>
       <c r="G1525" t="n">
-        <v>19.3487892150879</v>
+        <v>19.3487873077393</v>
       </c>
       <c r="H1525" t="n">
         <v>18304</v>
@@ -44652,7 +44652,7 @@
         <v>20</v>
       </c>
       <c r="G1527" t="n">
-        <v>19.1099147796631</v>
+        <v>19.1099166870117</v>
       </c>
       <c r="H1527" t="n">
         <v>17288</v>
@@ -44681,7 +44681,7 @@
         <v>20.25</v>
       </c>
       <c r="G1528" t="n">
-        <v>19.3487892150879</v>
+        <v>19.3487873077393</v>
       </c>
       <c r="H1528" t="n">
         <v>13003</v>
@@ -44942,7 +44942,7 @@
         <v>20.75</v>
       </c>
       <c r="G1537" t="n">
-        <v>19.8265380859375</v>
+        <v>19.8265361785889</v>
       </c>
       <c r="H1537" t="n">
         <v>41572</v>
@@ -44971,7 +44971,7 @@
         <v>21.1499996185303</v>
       </c>
       <c r="G1538" t="n">
-        <v>20.2087364196777</v>
+        <v>20.2087345123291</v>
       </c>
       <c r="H1538" t="n">
         <v>18789</v>
@@ -45058,7 +45058,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1541" t="n">
-        <v>19.3965625762939</v>
+        <v>19.3965644836426</v>
       </c>
       <c r="H1541" t="n">
         <v>27277</v>
@@ -45087,7 +45087,7 @@
         <v>20.2999992370605</v>
       </c>
       <c r="G1542" t="n">
-        <v>19.3965625762939</v>
+        <v>19.3965644836426</v>
       </c>
       <c r="H1542" t="n">
         <v>23559</v>
@@ -45116,7 +45116,7 @@
         <v>20.25</v>
       </c>
       <c r="G1543" t="n">
-        <v>19.3487892150879</v>
+        <v>19.3487873077393</v>
       </c>
       <c r="H1543" t="n">
         <v>25309</v>
@@ -45145,7 +45145,7 @@
         <v>20.25</v>
       </c>
       <c r="G1544" t="n">
-        <v>19.3487892150879</v>
+        <v>19.3487873077393</v>
       </c>
       <c r="H1544" t="n">
         <v>21479</v>
@@ -45319,7 +45319,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G1550" t="n">
-        <v>19.0716934204102</v>
+        <v>19.0716953277588</v>
       </c>
       <c r="H1550" t="n">
         <v>19416</v>
@@ -45348,7 +45348,7 @@
         <v>20</v>
       </c>
       <c r="G1551" t="n">
-        <v>19.1099147796631</v>
+        <v>19.1099166870117</v>
       </c>
       <c r="H1551" t="n">
         <v>8161</v>
@@ -45435,7 +45435,7 @@
         <v>19.9599990844727</v>
       </c>
       <c r="G1554" t="n">
-        <v>19.0716934204102</v>
+        <v>19.0716953277588</v>
       </c>
       <c r="H1554" t="n">
         <v>14822</v>
@@ -45609,7 +45609,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1560" t="n">
-        <v>17.9633197784424</v>
+        <v>17.963321685791</v>
       </c>
       <c r="H1560" t="n">
         <v>55586</v>
@@ -45783,7 +45783,7 @@
         <v>19.3400001525879</v>
       </c>
       <c r="G1566" t="n">
-        <v>18.4792861938477</v>
+        <v>18.4792881011963</v>
       </c>
       <c r="H1566" t="n">
         <v>7386</v>
@@ -45841,7 +45841,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1568" t="n">
-        <v>16.6638450622559</v>
+        <v>16.6638469696045</v>
       </c>
       <c r="H1568" t="n">
         <v>209719</v>
@@ -45870,7 +45870,7 @@
         <v>16.5400009155273</v>
       </c>
       <c r="G1569" t="n">
-        <v>15.8038997650146</v>
+        <v>15.8039016723633</v>
       </c>
       <c r="H1569" t="n">
         <v>201281</v>
@@ -46102,7 +46102,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G1577" t="n">
-        <v>16.3580894470215</v>
+        <v>16.3580875396729</v>
       </c>
       <c r="H1577" t="n">
         <v>25812</v>
@@ -46218,7 +46218,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1581" t="n">
-        <v>16.5874061584473</v>
+        <v>16.5874080657959</v>
       </c>
       <c r="H1581" t="n">
         <v>31323</v>
@@ -46247,7 +46247,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1582" t="n">
-        <v>16.4154186248779</v>
+        <v>16.4154167175293</v>
       </c>
       <c r="H1582" t="n">
         <v>39335</v>
@@ -46276,7 +46276,7 @@
         <v>17.1200008392334</v>
       </c>
       <c r="G1583" t="n">
-        <v>16.3580894470215</v>
+        <v>16.3580875396729</v>
       </c>
       <c r="H1583" t="n">
         <v>39794</v>
@@ -46479,7 +46479,7 @@
         <v>17.3600006103516</v>
       </c>
       <c r="G1590" t="n">
-        <v>16.5874061584473</v>
+        <v>16.5874080657959</v>
       </c>
       <c r="H1590" t="n">
         <v>41539</v>
@@ -46508,7 +46508,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1591" t="n">
-        <v>16.4154186248779</v>
+        <v>16.4154167175293</v>
       </c>
       <c r="H1591" t="n">
         <v>34761</v>
@@ -46624,7 +46624,7 @@
         <v>16.7000007629395</v>
       </c>
       <c r="G1595" t="n">
-        <v>15.9567794799805</v>
+        <v>15.9567813873291</v>
       </c>
       <c r="H1595" t="n">
         <v>56367</v>
@@ -47059,7 +47059,7 @@
         <v>14.3599996566772</v>
       </c>
       <c r="G1610" t="n">
-        <v>13.7209196090698</v>
+        <v>13.7209186553955</v>
       </c>
       <c r="H1610" t="n">
         <v>60330</v>
@@ -47117,7 +47117,7 @@
         <v>14.0799999237061</v>
       </c>
       <c r="G1612" t="n">
-        <v>13.4533805847168</v>
+        <v>13.4533796310425</v>
       </c>
       <c r="H1612" t="n">
         <v>42969</v>
@@ -47146,7 +47146,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1613" t="n">
-        <v>13.4342708587646</v>
+        <v>13.4342699050903</v>
       </c>
       <c r="H1613" t="n">
         <v>38565</v>
@@ -47204,7 +47204,7 @@
         <v>14.0600004196167</v>
       </c>
       <c r="G1615" t="n">
-        <v>13.4342708587646</v>
+        <v>13.4342699050903</v>
       </c>
       <c r="H1615" t="n">
         <v>41707</v>
@@ -47320,7 +47320,7 @@
         <v>14.4399995803833</v>
       </c>
       <c r="G1619" t="n">
-        <v>13.7973575592041</v>
+        <v>13.7973585128784</v>
       </c>
       <c r="H1619" t="n">
         <v>98951</v>
@@ -47465,7 +47465,7 @@
         <v>14.3999996185303</v>
       </c>
       <c r="G1624" t="n">
-        <v>13.7591390609741</v>
+        <v>13.7591400146484</v>
       </c>
       <c r="H1624" t="n">
         <v>47166</v>
@@ -47523,7 +47523,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1626" t="n">
-        <v>13.8737983703613</v>
+        <v>13.8737993240356</v>
       </c>
       <c r="H1626" t="n">
         <v>33686</v>
@@ -47581,7 +47581,7 @@
         <v>14.5200004577637</v>
       </c>
       <c r="G1628" t="n">
-        <v>13.8737983703613</v>
+        <v>13.8737993240356</v>
       </c>
       <c r="H1628" t="n">
         <v>22206</v>
@@ -47900,7 +47900,7 @@
         <v>17.1599998474121</v>
       </c>
       <c r="G1639" t="n">
-        <v>16.3963069915771</v>
+        <v>16.3963088989258</v>
       </c>
       <c r="H1639" t="n">
         <v>43548</v>
@@ -47929,7 +47929,7 @@
         <v>17.7199993133545</v>
       </c>
       <c r="G1640" t="n">
-        <v>16.9313850402832</v>
+        <v>16.9313831329346</v>
       </c>
       <c r="H1640" t="n">
         <v>66899</v>
@@ -47958,7 +47958,7 @@
         <v>17.9200000762939</v>
       </c>
       <c r="G1641" t="n">
-        <v>17.122486114502</v>
+        <v>17.1224842071533</v>
       </c>
       <c r="H1641" t="n">
         <v>52653</v>
@@ -48016,7 +48016,7 @@
         <v>17.7999992370605</v>
       </c>
       <c r="G1643" t="n">
-        <v>17.0078258514404</v>
+        <v>17.0078239440918</v>
       </c>
       <c r="H1643" t="n">
         <v>20323</v>
@@ -48132,7 +48132,7 @@
         <v>17.1800003051758</v>
       </c>
       <c r="G1647" t="n">
-        <v>16.4154186248779</v>
+        <v>16.4154167175293</v>
       </c>
       <c r="H1647" t="n">
         <v>16018</v>
@@ -48161,7 +48161,7 @@
         <v>17.5799999237061</v>
       </c>
       <c r="G1648" t="n">
-        <v>16.7976169586182</v>
+        <v>16.7976150512695</v>
       </c>
       <c r="H1648" t="n">
         <v>33889</v>
@@ -48219,7 +48219,7 @@
         <v>17.4400005340576</v>
       </c>
       <c r="G1650" t="n">
-        <v>16.6638450622559</v>
+        <v>16.6638469696045</v>
       </c>
       <c r="H1650" t="n">
         <v>27418</v>
@@ -48364,7 +48364,7 @@
         <v>17.5599994659424</v>
       </c>
       <c r="G1655" t="n">
-        <v>16.7785034179688</v>
+        <v>16.7785053253174</v>
       </c>
       <c r="H1655" t="n">
         <v>11530</v>
@@ -48422,7 +48422,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1657" t="n">
-        <v>17.1033725738525</v>
+        <v>17.1033744812012</v>
       </c>
       <c r="H1657" t="n">
         <v>10080</v>
@@ -48451,7 +48451,7 @@
         <v>18.0599994659424</v>
       </c>
       <c r="G1658" t="n">
-        <v>17.2562522888184</v>
+        <v>17.256254196167</v>
       </c>
       <c r="H1658" t="n">
         <v>16208</v>
@@ -48538,7 +48538,7 @@
         <v>17.8999996185303</v>
       </c>
       <c r="G1661" t="n">
-        <v>17.1033725738525</v>
+        <v>17.1033744812012</v>
       </c>
       <c r="H1661" t="n">
         <v>5705</v>
@@ -48712,7 +48712,7 @@
         <v>19.5</v>
       </c>
       <c r="G1667" t="n">
-        <v>18.6321659088135</v>
+        <v>18.6321678161621</v>
       </c>
       <c r="H1667" t="n">
         <v>12973</v>
@@ -48828,7 +48828,7 @@
         <v>19.5</v>
       </c>
       <c r="G1671" t="n">
-        <v>18.6321659088135</v>
+        <v>18.6321678161621</v>
       </c>
       <c r="H1671" t="n">
         <v>17932</v>
@@ -48886,7 +48886,7 @@
         <v>18.3600006103516</v>
       </c>
       <c r="G1673" t="n">
-        <v>17.5429019927979</v>
+        <v>17.5429039001465</v>
       </c>
       <c r="H1673" t="n">
         <v>41152</v>
@@ -48944,7 +48944,7 @@
         <v>18.6000003814697</v>
       </c>
       <c r="G1675" t="n">
-        <v>17.7722206115723</v>
+        <v>17.7722225189209</v>
       </c>
       <c r="H1675" t="n">
         <v>16152</v>
@@ -49002,7 +49002,7 @@
         <v>18.9400005340576</v>
       </c>
       <c r="G1677" t="n">
-        <v>18.0970897674561</v>
+        <v>18.0970916748047</v>
       </c>
       <c r="H1677" t="n">
         <v>21233</v>
@@ -49031,7 +49031,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G1678" t="n">
-        <v>17.8104400634766</v>
+        <v>17.8104419708252</v>
       </c>
       <c r="H1678" t="n">
         <v>10106</v>
@@ -49089,7 +49089,7 @@
         <v>18.8799991607666</v>
       </c>
       <c r="G1680" t="n">
-        <v>18.0397567749023</v>
+        <v>18.039758682251</v>
       </c>
       <c r="H1680" t="n">
         <v>44497</v>
@@ -49176,7 +49176,7 @@
         <v>17.6599998474121</v>
       </c>
       <c r="G1683" t="n">
-        <v>16.8740558624268</v>
+        <v>16.8740577697754</v>
       </c>
       <c r="H1683" t="n">
         <v>17529</v>
@@ -49205,7 +49205,7 @@
         <v>17.8799991607666</v>
       </c>
       <c r="G1684" t="n">
-        <v>17.084264755249</v>
+        <v>17.0842628479004</v>
       </c>
       <c r="H1684" t="n">
         <v>18670</v>
@@ -49321,7 +49321,7 @@
         <v>18.1399993896484</v>
       </c>
       <c r="G1688" t="n">
-        <v>17.332691192627</v>
+        <v>17.3326930999756</v>
       </c>
       <c r="H1688" t="n">
         <v>12378</v>
@@ -49524,7 +49524,7 @@
         <v>18.2600002288818</v>
       </c>
       <c r="G1695" t="n">
-        <v>17.4473533630371</v>
+        <v>17.4473552703857</v>
       </c>
       <c r="H1695" t="n">
         <v>17398</v>
@@ -49669,7 +49669,7 @@
         <v>18.2000007629395</v>
       </c>
       <c r="G1700" t="n">
-        <v>17.390022277832</v>
+        <v>17.3900241851807</v>
       </c>
       <c r="H1700" t="n">
         <v>12018</v>
@@ -49785,7 +49785,7 @@
         <v>18.6399993896484</v>
       </c>
       <c r="G1704" t="n">
-        <v>17.8104400634766</v>
+        <v>17.8104419708252</v>
       </c>
       <c r="H1704" t="n">
         <v>37352</v>
@@ -49843,7 +49843,7 @@
         <v>19.5</v>
       </c>
       <c r="G1706" t="n">
-        <v>18.6321659088135</v>
+        <v>18.6321678161621</v>
       </c>
       <c r="H1706" t="n">
         <v>43334</v>
@@ -49872,7 +49872,7 @@
         <v>18.7999992370605</v>
       </c>
       <c r="G1707" t="n">
-        <v>17.9633197784424</v>
+        <v>17.963321685791</v>
       </c>
       <c r="H1707" t="n">
         <v>32129</v>
@@ -49901,7 +49901,7 @@
         <v>18.8799991607666</v>
       </c>
       <